--- a/data/bandi_export.xlsx
+++ b/data/bandi_export.xlsx
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -152,6 +152,18 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -517,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -532,7 +544,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏛️  Nuovi Bandi — 10/03/2026 21:36</t>
+          <t>🏛️  Nuovi Bandi — 13/03/2026 07:41</t>
         </is>
       </c>
     </row>
@@ -577,555 +589,47 @@
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Emilia-Romagna</t>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>FLAG GALPA Costa E-R. Sostituzione del motore principale e dei motori secondari. Secondo bando</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>https://agricoltura.regione.emilia-romagna.it/feampa-2021-2027/bandi-galpa/2026/galpa-sostituzione-motori-secondo-bando</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr"/>
-      <c r="F3" s="4" t="inlineStr"/>
+          <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per ROMICS – Primavera 2026ApertoFESR</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-romics-primavera-2026/</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr"/>
+      <c r="F3" s="13" t="inlineStr"/>
       <c r="G3" s="5" t="inlineStr"/>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0PRE-SEED 3.0Prossima AperturaFESR</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>https://www.lazioeuropa.it/bandi/pre-seed-3-0/</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr"/>
-      <c r="F4" s="8" t="inlineStr"/>
+          <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Cinema International 2026 – I edizioneApertoFESR</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/lazio-cinema-international-2026-i-edizione/</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr"/>
+      <c r="F4" s="15" t="inlineStr"/>
       <c r="G4" s="9" t="inlineStr"/>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Lazio</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>ACCESSO AL CREDITO E ALLE GARANZIE PER LE IMPRESEContributo su finanziamenti alle imprese del Lazio erogati su provvista BEIProssima AperturaFESR</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>https://www.lazioeuropa.it/bandi/contributo-su-finanziamenti-alle-imprese-del-lazio-erogati-su-provvista-bei/</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Lazio</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>LAVORO, FORMAZIONE E INCLUSIONEIndividuazione degli enti iscritti al Registro unico nazionale del Terzo settoreApertoBandi Regionali</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>https://www.lazioeuropa.it/bandi/individuazione-degli-enti-iscritti-al-registro-unico-nazionale-del-terzo-settore/</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr"/>
-      <c r="F6" s="8" t="inlineStr"/>
-      <c r="G6" s="9" t="inlineStr"/>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Lazio</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Technology Transfer LazioApertoFESR</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>https://www.lazioeuropa.it/bandi/technology-transfer-lazio/</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Lazio</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Percorso di tutoraggio per le impreseApertoFESR</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>https://www.lazioeuropa.it/bandi/percorso-di-tutoraggio-per-le-imprese/</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr"/>
-      <c r="F8" s="8" t="inlineStr"/>
-      <c r="G8" s="9" t="inlineStr"/>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Lazio</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per partecipare a SMAU Parigi 2026ApertoFESR</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-partecipare-a-smau-parigi-2026/</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="5" t="inlineStr"/>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Lazio</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>LAVORO, FORMAZIONE E INCLUSIONERiconoscimento della funzione sociale ed educativa degli oratoriApertoBandi Regionali</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>https://www.lazioeuropa.it/bandi/riconoscimento-della-funzione-sociale-ed-educativa-degli-oratori/</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr"/>
-      <c r="F10" s="8" t="inlineStr"/>
-      <c r="G10" s="9" t="inlineStr"/>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Lazio</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>GovernanceIscrizione nell’elenco regionale degli idonei all’esercizio dell’attività di direttore dell’Istituto JemoloApertoBandi Regionali</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>https://www.lazioeuropa.it/bandi/iscrizione-nellelenco-regionale-degli-idonei-allesercizio-dellattivita-di-direttore-dellistituto-jemolo/</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>Lazio</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>LAVORO, FORMAZIONE E INCLUSIONEVoucher per lo sport – seconda annualitàApertoFSE / FSE+</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>https://www.lazioeuropa.it/bandi/voucher-per-lo-sport-seconda-annualita/</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr"/>
-      <c r="F12" s="8" t="inlineStr"/>
-      <c r="G12" s="9" t="inlineStr"/>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Lazio</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>LAVORO, FORMAZIONE E INCLUSIONEBonus occupazionale SALGOApertoFSE / FSE+</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>https://www.lazioeuropa.it/bandi/bonus-occupazionale-salgo/</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr"/>
-      <c r="G13" s="5" t="inlineStr"/>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Lazio</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>LAVORO, FORMAZIONE E INCLUSIONEContributo di Libertà per le donne che hanno subito violenzaApertoBandi Regionali</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>https://www.lazioeuropa.it/bandi/contributo-di-liberta-per-le-donne-che-hanno-subito-violenza/</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr"/>
-      <c r="F14" s="8" t="inlineStr"/>
-      <c r="G14" s="9" t="inlineStr"/>
-    </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Lazio</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>CREATIVITÀ, CINEMA, TURISMO E CULTURAInterventi straordinari di valorizzazione del patrimonio culturale del LazioApertoBandi Regionali</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>https://www.lazioeuropa.it/bandi/interventi-straordinari-di-valorizzazione-del-patrimonio-culturale-del-lazio/</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr"/>
-      <c r="G15" s="5" t="inlineStr"/>
-    </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>Sicilia</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>Bandi di garaBANDO ATTUAZIONE Ob. 1.1 Azione 1 codice 111102 _DIV - "SOSTEGNO ALLA DIVERSIFICAZIONE E NUOVE FORME DI REDDITO PER LA PICCOLA PESCA COST</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/bando-avviso-regia-ob-11-azione-1-codice-111102-div-sostegno-alla-diversificazione-nuove-forme-reddito-piccola-pesca-costiera</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>07/06/2026 - 23:59</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="G16" s="9" t="inlineStr"/>
-    </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Sicilia</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Avvisi pubblici09 marzo 2026 - ST SIRACUSA - AVVISO PUBBLICO PER LA COSTITUZIONE DI ELENCHI DI OPERATORI ECONOMICI PER L’ACQUISIZIONE DI BENI E SERVIZ</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/09-marzo-2026-st-siracusa-avviso-pubblico-costituzione-elenchi-operatori-economici-l-acquisizione-beni-servizi</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>31/12/2026 - 23:59</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>31/12/2026</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr"/>
-    </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>Sicilia</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScade il:19/03/2026 - 12:00Leggi di più</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>19/03/2026 - 12:00</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>19/03/2026</t>
-        </is>
-      </c>
-      <c r="G18" s="9" t="inlineStr"/>
-    </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Sicilia</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Manifestazioni di interesseAvviso Manifestazione Interesse DISTRIBUTORI AUTOMATICI di bevande e snackScadutoLeggi di più</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-distributori-automatici-bevande-snack</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr"/>
-      <c r="G19" s="5" t="inlineStr"/>
-    </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>Sicilia</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>30/03/2026 - 23:59</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>30/03/2026</t>
-        </is>
-      </c>
-      <c r="G20" s="9" t="inlineStr"/>
-    </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Sicilia</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo-0</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>30/03/2026 - 23:59</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>30/03/2026</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr"/>
-    </row>
-    <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>Sicilia</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>Manifestazioni di interesseST SIRACUSA - AVVISO DI MANIFESTAZIONE DI INTERESSE - Fornitura applicativo extracontabile per la gestione progetti, ecc. e</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-siracusa-avviso-manifestazione-interesse-fornitura-applicativo-extracontabile-gestione-progetti-ecc-applicativo-gestione-ed-elaborazione-informatizzata-paghe</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr"/>
-      <c r="F22" s="8" t="inlineStr"/>
-      <c r="G22" s="9" t="inlineStr"/>
-    </row>
-    <row r="23" ht="32" customHeight="1">
-      <c r="A23" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Sicilia</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile sito nel Comune di Capo D'Orlando, Via Trazzera MarinaScade il:25/03/2026 - 12:00Leggi di più</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-sito-nel-comune-capo-d-orlando-trazzera-marina</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>25/03/2026 - 12:00</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>25/03/2026</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr"/>
-    </row>
-    <row r="24" ht="32" customHeight="1">
-      <c r="A24" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Sicilia</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Avvisi pubbliciST CATANIA - Programma Regionale FESR Sicilia 2021-2027 - Azione 2.4.4 - “Interventi per la riduzione del rischio incendi” - AVVISO DI </t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-catania-programma-regionale-fesr-sicilia-2021-2027-azione-244-interventi-riduzione-rischio-incendi-avviso-indagine-mercato</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr"/>
-      <c r="F24" s="8" t="inlineStr"/>
-      <c r="G24" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1134,26 +638,6 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1165,7 +649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1811,6 +1295,56 @@
       <c r="E23" s="4" t="inlineStr"/>
       <c r="F23" s="4" t="inlineStr"/>
       <c r="G23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per ROMICS – Primavera 2026ApertoFESR</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-romics-primavera-2026/</t>
+        </is>
+      </c>
+      <c r="E24" s="15" t="inlineStr"/>
+      <c r="F24" s="15" t="inlineStr"/>
+      <c r="G24" s="15" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Cinema International 2026 – I edizioneApertoFESR</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/lazio-cinema-international-2026-i-edizione/</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr"/>
+      <c r="F25" s="13" t="inlineStr"/>
+      <c r="G25" s="13" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1836,6 +1370,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1880,7 +1416,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -1889,24 +1425,24 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1915,7 +1451,7 @@
         <v>9</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">

--- a/data/bandi_export.xlsx
+++ b/data/bandi_export.xlsx
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -152,6 +152,18 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -529,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -544,7 +556,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏛️  Nuovi Bandi — 13/03/2026 07:41</t>
+          <t>🏛️  Nuovi Bandi — 14/03/2026 07:30</t>
         </is>
       </c>
     </row>
@@ -589,47 +601,109 @@
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per ROMICS – Primavera 2026ApertoFESR</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-romics-primavera-2026/</t>
-        </is>
-      </c>
-      <c r="E3" s="13" t="inlineStr"/>
-      <c r="F3" s="13" t="inlineStr"/>
+          <t>LAVORO, FORMAZIONE E INCLUSIONEManifestazioni di interesse alla costituzione di due nuove Fondazioni I.T.S. AcademyApertoBandi Regionali</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/manifestazioni-di-interesse-alla-costituzione-di-due-nuove-fondazioni-i-t-s-academy/</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr"/>
+      <c r="F3" s="17" t="inlineStr"/>
       <c r="G3" s="5" t="inlineStr"/>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Cinema International 2026 – I edizioneApertoFESR</t>
-        </is>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
-        <is>
-          <t>https://www.lazioeuropa.it/bandi/lazio-cinema-international-2026-i-edizione/</t>
-        </is>
-      </c>
-      <c r="E4" s="15" t="inlineStr"/>
-      <c r="F4" s="15" t="inlineStr"/>
+          <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURAContributi per sostenere la ripresa del settore della pescaApertoBandi Regionali</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/contributi-per-sostenere-la-ripresa-del-settore-della-pesca/</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr"/>
+      <c r="F4" s="19" t="inlineStr"/>
       <c r="G4" s="9" t="inlineStr"/>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Manifestazioni di interesseAVVISO - Manifestazione Interesse “Storytelling aziendale” Expo Wild Natura - Caccia - Pesca. Misterbianco (CT), 10-12 apri</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-storytelling-aziendale-expo-wild-natura-caccia-pesca-misterbianco-ct-10-12-aprile-2026</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>30/03/2026 - 13:00</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Manifestazioni di interesseInvaso Lentini - Interventi di ripristino delle pareti esterne in cls della Torre di presa Sud e della trave d’appoggio del</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/invaso-lentini-interventi-ripristino-pareti-esterne-cls-torre-presa-sud-trave-d-appoggio-cavalcavia-collegamento-alla-stessa-torre</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="inlineStr">
+        <is>
+          <t>19/03/2026 - 23:59</t>
+        </is>
+      </c>
+      <c r="F6" s="19" t="inlineStr">
+        <is>
+          <t>19/03/2026</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -638,6 +712,8 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -649,7 +725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -699,12 +775,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="15" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -714,22 +790,22 @@
           <t>FLAG GALPA Costa E-R. Sostituzione del motore principale e dei motori secondari. Secondo bando</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="16" t="inlineStr">
         <is>
           <t>https://agricoltura.regione.emilia-romagna.it/feampa-2021-2027/bandi-galpa/2026/galpa-sostituzione-motori-secondo-bando</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr"/>
-      <c r="F2" s="8" t="inlineStr"/>
-      <c r="G2" s="8" t="inlineStr"/>
+      <c r="E2" s="15" t="inlineStr"/>
+      <c r="F2" s="15" t="inlineStr"/>
+      <c r="G2" s="15" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -739,22 +815,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0PRE-SEED 3.0Prossima AperturaFESR</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/pre-seed-3-0/</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr"/>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="inlineStr"/>
+      <c r="E3" s="13" t="inlineStr"/>
+      <c r="F3" s="13" t="inlineStr"/>
+      <c r="G3" s="13" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -764,22 +840,22 @@
           <t>ACCESSO AL CREDITO E ALLE GARANZIE PER LE IMPRESEContributo su finanziamenti alle imprese del Lazio erogati su provvista BEIProssima AperturaFESR</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-su-finanziamenti-alle-imprese-del-lazio-erogati-su-provvista-bei/</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr"/>
-      <c r="F4" s="8" t="inlineStr"/>
-      <c r="G4" s="8" t="inlineStr"/>
+      <c r="E4" s="15" t="inlineStr"/>
+      <c r="F4" s="15" t="inlineStr"/>
+      <c r="G4" s="15" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -789,22 +865,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEIndividuazione degli enti iscritti al Registro unico nazionale del Terzo settoreApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/individuazione-degli-enti-iscritti-al-registro-unico-nazionale-del-terzo-settore/</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr"/>
+      <c r="E5" s="13" t="inlineStr"/>
+      <c r="F5" s="13" t="inlineStr"/>
+      <c r="G5" s="13" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -814,22 +890,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Technology Transfer LazioApertoFESR</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/technology-transfer-lazio/</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr"/>
-      <c r="F6" s="8" t="inlineStr"/>
-      <c r="G6" s="8" t="inlineStr"/>
+      <c r="E6" s="15" t="inlineStr"/>
+      <c r="F6" s="15" t="inlineStr"/>
+      <c r="G6" s="15" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -839,22 +915,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Percorso di tutoraggio per le impreseApertoFESR</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/percorso-di-tutoraggio-per-le-imprese/</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr"/>
+      <c r="E7" s="13" t="inlineStr"/>
+      <c r="F7" s="13" t="inlineStr"/>
+      <c r="G7" s="13" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -864,22 +940,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per partecipare a SMAU Parigi 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-partecipare-a-smau-parigi-2026/</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr"/>
-      <c r="F8" s="8" t="inlineStr"/>
-      <c r="G8" s="8" t="inlineStr"/>
+      <c r="E8" s="15" t="inlineStr"/>
+      <c r="F8" s="15" t="inlineStr"/>
+      <c r="G8" s="15" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -889,22 +965,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONERiconoscimento della funzione sociale ed educativa degli oratoriApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/riconoscimento-della-funzione-sociale-ed-educativa-degli-oratori/</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="4" t="inlineStr"/>
+      <c r="E9" s="13" t="inlineStr"/>
+      <c r="F9" s="13" t="inlineStr"/>
+      <c r="G9" s="13" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -914,22 +990,22 @@
           <t>GovernanceIscrizione nell’elenco regionale degli idonei all’esercizio dell’attività di direttore dell’Istituto JemoloApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/iscrizione-nellelenco-regionale-degli-idonei-allesercizio-dellattivita-di-direttore-dellistituto-jemolo/</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr"/>
-      <c r="F10" s="8" t="inlineStr"/>
-      <c r="G10" s="8" t="inlineStr"/>
+      <c r="E10" s="15" t="inlineStr"/>
+      <c r="F10" s="15" t="inlineStr"/>
+      <c r="G10" s="15" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -939,22 +1015,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEVoucher per lo sport – seconda annualitàApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/voucher-per-lo-sport-seconda-annualita/</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr"/>
-      <c r="G11" s="4" t="inlineStr"/>
+      <c r="E11" s="13" t="inlineStr"/>
+      <c r="F11" s="13" t="inlineStr"/>
+      <c r="G11" s="13" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -964,22 +1040,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEBonus occupazionale SALGOApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/bonus-occupazionale-salgo/</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr"/>
-      <c r="F12" s="8" t="inlineStr"/>
-      <c r="G12" s="8" t="inlineStr"/>
+      <c r="E12" s="15" t="inlineStr"/>
+      <c r="F12" s="15" t="inlineStr"/>
+      <c r="G12" s="15" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -989,22 +1065,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEContributo di Libertà per le donne che hanno subito violenzaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-di-liberta-per-le-donne-che-hanno-subito-violenza/</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr"/>
-      <c r="G13" s="4" t="inlineStr"/>
+      <c r="E13" s="13" t="inlineStr"/>
+      <c r="F13" s="13" t="inlineStr"/>
+      <c r="G13" s="13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1014,22 +1090,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURAInterventi straordinari di valorizzazione del patrimonio culturale del LazioApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="16" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/interventi-straordinari-di-valorizzazione-del-patrimonio-culturale-del-lazio/</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr"/>
-      <c r="F14" s="8" t="inlineStr"/>
-      <c r="G14" s="8" t="inlineStr"/>
+      <c r="E14" s="15" t="inlineStr"/>
+      <c r="F14" s="15" t="inlineStr"/>
+      <c r="G14" s="15" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1039,30 +1115,30 @@
           <t>Bandi di garaBANDO ATTUAZIONE Ob. 1.1 Azione 1 codice 111102 _DIV - "SOSTEGNO ALLA DIVERSIFICAZIONE E NUOVE FORME DI REDDITO PER LA PICCOLA PESCA COST</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/bando-avviso-regia-ob-11-azione-1-codice-111102-div-sostegno-alla-diversificazione-nuove-forme-reddito-piccola-pesca-costiera</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>07/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr"/>
+      <c r="G15" s="13" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1072,30 +1148,30 @@
           <t>Avvisi pubblici09 marzo 2026 - ST SIRACUSA - AVVISO PUBBLICO PER LA COSTITUZIONE DI ELENCHI DI OPERATORI ECONOMICI PER L’ACQUISIZIONE DI BENI E SERVIZ</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/09-marzo-2026-st-siracusa-avviso-pubblico-costituzione-elenchi-operatori-economici-l-acquisizione-beni-servizi</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E16" s="15" t="inlineStr">
         <is>
           <t>31/12/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="F16" s="15" t="inlineStr">
         <is>
           <t>31/12/2026</t>
         </is>
       </c>
-      <c r="G16" s="8" t="inlineStr"/>
+      <c r="G16" s="15" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1105,30 +1181,30 @@
           <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScade il:19/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="14" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>19/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F17" s="13" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr"/>
+      <c r="G17" s="13" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1138,22 +1214,22 @@
           <t>Manifestazioni di interesseAvviso Manifestazione Interesse DISTRIBUTORI AUTOMATICI di bevande e snackScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-distributori-automatici-bevande-snack</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr"/>
-      <c r="F18" s="8" t="inlineStr"/>
-      <c r="G18" s="8" t="inlineStr"/>
+      <c r="E18" s="15" t="inlineStr"/>
+      <c r="F18" s="15" t="inlineStr"/>
+      <c r="G18" s="15" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1163,30 +1239,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="14" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F19" s="13" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr"/>
+      <c r="G19" s="13" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1196,30 +1272,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="16" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo-0</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="E20" s="15" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F20" s="15" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G20" s="8" t="inlineStr"/>
+      <c r="G20" s="15" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1229,22 +1305,22 @@
           <t>Manifestazioni di interesseST SIRACUSA - AVVISO DI MANIFESTAZIONE DI INTERESSE - Fornitura applicativo extracontabile per la gestione progetti, ecc. e</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="14" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-siracusa-avviso-manifestazione-interesse-fornitura-applicativo-extracontabile-gestione-progetti-ecc-applicativo-gestione-ed-elaborazione-informatizzata-paghe</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr"/>
-      <c r="F21" s="4" t="inlineStr"/>
-      <c r="G21" s="4" t="inlineStr"/>
+      <c r="E21" s="13" t="inlineStr"/>
+      <c r="F21" s="13" t="inlineStr"/>
+      <c r="G21" s="13" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1254,30 +1330,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile sito nel Comune di Capo D'Orlando, Via Trazzera MarinaScade il:25/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="16" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-sito-nel-comune-capo-d-orlando-trazzera-marina</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E22" s="15" t="inlineStr">
         <is>
           <t>25/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="F22" s="15" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="G22" s="8" t="inlineStr"/>
+      <c r="G22" s="15" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1287,14 +1363,14 @@
           <t xml:space="preserve">Avvisi pubbliciST CATANIA - Programma Regionale FESR Sicilia 2021-2027 - Azione 2.4.4 - “Interventi per la riduzione del rischio incendi” - AVVISO DI </t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="14" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-catania-programma-regionale-fesr-sicilia-2021-2027-azione-244-interventi-riduzione-rischio-incendi-avviso-indagine-mercato</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr"/>
-      <c r="F23" s="4" t="inlineStr"/>
-      <c r="G23" s="4" t="inlineStr"/>
+      <c r="E23" s="13" t="inlineStr"/>
+      <c r="F23" s="13" t="inlineStr"/>
+      <c r="G23" s="13" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
@@ -1345,6 +1421,122 @@
       <c r="E25" s="13" t="inlineStr"/>
       <c r="F25" s="13" t="inlineStr"/>
       <c r="G25" s="13" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>14/03/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="19" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>LAVORO, FORMAZIONE E INCLUSIONEManifestazioni di interesse alla costituzione di due nuove Fondazioni I.T.S. AcademyApertoBandi Regionali</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/manifestazioni-di-interesse-alla-costituzione-di-due-nuove-fondazioni-i-t-s-academy/</t>
+        </is>
+      </c>
+      <c r="E26" s="19" t="inlineStr"/>
+      <c r="F26" s="19" t="inlineStr"/>
+      <c r="G26" s="19" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>14/03/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURAContributi per sostenere la ripresa del settore della pescaApertoBandi Regionali</t>
+        </is>
+      </c>
+      <c r="D27" s="18" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/contributi-per-sostenere-la-ripresa-del-settore-della-pesca/</t>
+        </is>
+      </c>
+      <c r="E27" s="17" t="inlineStr"/>
+      <c r="F27" s="17" t="inlineStr"/>
+      <c r="G27" s="17" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>14/03/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="19" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Manifestazioni di interesseAVVISO - Manifestazione Interesse “Storytelling aziendale” Expo Wild Natura - Caccia - Pesca. Misterbianco (CT), 10-12 apri</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-storytelling-aziendale-expo-wild-natura-caccia-pesca-misterbianco-ct-10-12-aprile-2026</t>
+        </is>
+      </c>
+      <c r="E28" s="19" t="inlineStr">
+        <is>
+          <t>30/03/2026 - 13:00</t>
+        </is>
+      </c>
+      <c r="F28" s="19" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="G28" s="19" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>14/03/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Manifestazioni di interesseInvaso Lentini - Interventi di ripristino delle pareti esterne in cls della Torre di presa Sud e della trave d’appoggio del</t>
+        </is>
+      </c>
+      <c r="D29" s="18" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/invaso-lentini-interventi-ripristino-pareti-esterne-cls-torre-presa-sud-trave-d-appoggio-cavalcavia-collegamento-alla-stessa-torre</t>
+        </is>
+      </c>
+      <c r="E29" s="17" t="inlineStr">
+        <is>
+          <t>19/03/2026 - 23:59</t>
+        </is>
+      </c>
+      <c r="F29" s="17" t="inlineStr">
+        <is>
+          <t>19/03/2026</t>
+        </is>
+      </c>
+      <c r="G29" s="17" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1372,6 +1564,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1416,7 +1612,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -1429,29 +1625,29 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">

--- a/data/bandi_export.xlsx
+++ b/data/bandi_export.xlsx
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -152,6 +152,18 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -541,7 +553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -556,7 +568,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏛️  Nuovi Bandi — 14/03/2026 07:30</t>
+          <t>🏛️  Nuovi Bandi — 17/03/2026 07:50</t>
         </is>
       </c>
     </row>
@@ -601,109 +613,55 @@
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>LAVORO, FORMAZIONE E INCLUSIONEManifestazioni di interesse alla costituzione di due nuove Fondazioni I.T.S. AcademyApertoBandi Regionali</t>
-        </is>
-      </c>
-      <c r="D3" s="18" t="inlineStr">
-        <is>
-          <t>https://www.lazioeuropa.it/bandi/manifestazioni-di-interesse-alla-costituzione-di-due-nuove-fondazioni-i-t-s-academy/</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr"/>
-      <c r="F3" s="17" t="inlineStr"/>
+          <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURARistrutturazione e riconversione vigneti – campagna 2026-2027ApertoBandi Regionali</t>
+        </is>
+      </c>
+      <c r="D3" s="22" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/ristrutturazione-e-riconversione-vigneti-campagna-2026-2027/</t>
+        </is>
+      </c>
+      <c r="E3" s="21" t="inlineStr"/>
+      <c r="F3" s="21" t="inlineStr"/>
       <c r="G3" s="5" t="inlineStr"/>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="19" t="inlineStr">
-        <is>
-          <t>Lazio</t>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURAContributi per sostenere la ripresa del settore della pescaApertoBandi Regionali</t>
-        </is>
-      </c>
-      <c r="D4" s="20" t="inlineStr">
-        <is>
-          <t>https://www.lazioeuropa.it/bandi/contributi-per-sostenere-la-ripresa-del-settore-della-pesca/</t>
-        </is>
-      </c>
-      <c r="E4" s="19" t="inlineStr"/>
-      <c r="F4" s="19" t="inlineStr"/>
+          <t>Manifestazioni di interessePR FESR 2021/27 Azione 1.3.3 e del POC 2014/20 - Azione 1.3.1  - Avviso a manifestazione d’interesse eventi fieristici inte</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-d-interesse-eventi-fieristici-internazionali-marzo-dicembre-2026</t>
+        </is>
+      </c>
+      <c r="E4" s="23" t="inlineStr">
+        <is>
+          <t>30/06/2026 - 23:59</t>
+        </is>
+      </c>
+      <c r="F4" s="23" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
       <c r="G4" s="9" t="inlineStr"/>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t>Sicilia</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Manifestazioni di interesseAVVISO - Manifestazione Interesse “Storytelling aziendale” Expo Wild Natura - Caccia - Pesca. Misterbianco (CT), 10-12 apri</t>
-        </is>
-      </c>
-      <c r="D5" s="18" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-storytelling-aziendale-expo-wild-natura-caccia-pesca-misterbianco-ct-10-12-aprile-2026</t>
-        </is>
-      </c>
-      <c r="E5" s="17" t="inlineStr">
-        <is>
-          <t>30/03/2026 - 13:00</t>
-        </is>
-      </c>
-      <c r="F5" s="17" t="inlineStr">
-        <is>
-          <t>30/03/2026</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="19" t="inlineStr">
-        <is>
-          <t>Sicilia</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>Manifestazioni di interesseInvaso Lentini - Interventi di ripristino delle pareti esterne in cls della Torre di presa Sud e della trave d’appoggio del</t>
-        </is>
-      </c>
-      <c r="D6" s="20" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/invaso-lentini-interventi-ripristino-pareti-esterne-cls-torre-presa-sud-trave-d-appoggio-cavalcavia-collegamento-alla-stessa-torre</t>
-        </is>
-      </c>
-      <c r="E6" s="19" t="inlineStr">
-        <is>
-          <t>19/03/2026 - 23:59</t>
-        </is>
-      </c>
-      <c r="F6" s="19" t="inlineStr">
-        <is>
-          <t>19/03/2026</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -712,8 +670,6 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -725,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -775,12 +731,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="19" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -790,22 +746,22 @@
           <t>FLAG GALPA Costa E-R. Sostituzione del motore principale e dei motori secondari. Secondo bando</t>
         </is>
       </c>
-      <c r="D2" s="16" t="inlineStr">
+      <c r="D2" s="20" t="inlineStr">
         <is>
           <t>https://agricoltura.regione.emilia-romagna.it/feampa-2021-2027/bandi-galpa/2026/galpa-sostituzione-motori-secondo-bando</t>
         </is>
       </c>
-      <c r="E2" s="15" t="inlineStr"/>
-      <c r="F2" s="15" t="inlineStr"/>
-      <c r="G2" s="15" t="inlineStr"/>
+      <c r="E2" s="19" t="inlineStr"/>
+      <c r="F2" s="19" t="inlineStr"/>
+      <c r="G2" s="19" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -815,22 +771,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0PRE-SEED 3.0Prossima AperturaFESR</t>
         </is>
       </c>
-      <c r="D3" s="14" t="inlineStr">
+      <c r="D3" s="18" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/pre-seed-3-0/</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr"/>
-      <c r="F3" s="13" t="inlineStr"/>
-      <c r="G3" s="13" t="inlineStr"/>
+      <c r="E3" s="17" t="inlineStr"/>
+      <c r="F3" s="17" t="inlineStr"/>
+      <c r="G3" s="17" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -840,22 +796,22 @@
           <t>ACCESSO AL CREDITO E ALLE GARANZIE PER LE IMPRESEContributo su finanziamenti alle imprese del Lazio erogati su provvista BEIProssima AperturaFESR</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="20" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-su-finanziamenti-alle-imprese-del-lazio-erogati-su-provvista-bei/</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr"/>
-      <c r="F4" s="15" t="inlineStr"/>
-      <c r="G4" s="15" t="inlineStr"/>
+      <c r="E4" s="19" t="inlineStr"/>
+      <c r="F4" s="19" t="inlineStr"/>
+      <c r="G4" s="19" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -865,22 +821,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEIndividuazione degli enti iscritti al Registro unico nazionale del Terzo settoreApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D5" s="18" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/individuazione-degli-enti-iscritti-al-registro-unico-nazionale-del-terzo-settore/</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr"/>
-      <c r="F5" s="13" t="inlineStr"/>
-      <c r="G5" s="13" t="inlineStr"/>
+      <c r="E5" s="17" t="inlineStr"/>
+      <c r="F5" s="17" t="inlineStr"/>
+      <c r="G5" s="17" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -890,22 +846,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Technology Transfer LazioApertoFESR</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/technology-transfer-lazio/</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr"/>
-      <c r="F6" s="15" t="inlineStr"/>
-      <c r="G6" s="15" t="inlineStr"/>
+      <c r="E6" s="19" t="inlineStr"/>
+      <c r="F6" s="19" t="inlineStr"/>
+      <c r="G6" s="19" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -915,22 +871,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Percorso di tutoraggio per le impreseApertoFESR</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="18" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/percorso-di-tutoraggio-per-le-imprese/</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr"/>
-      <c r="F7" s="13" t="inlineStr"/>
-      <c r="G7" s="13" t="inlineStr"/>
+      <c r="E7" s="17" t="inlineStr"/>
+      <c r="F7" s="17" t="inlineStr"/>
+      <c r="G7" s="17" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -940,22 +896,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per partecipare a SMAU Parigi 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-partecipare-a-smau-parigi-2026/</t>
         </is>
       </c>
-      <c r="E8" s="15" t="inlineStr"/>
-      <c r="F8" s="15" t="inlineStr"/>
-      <c r="G8" s="15" t="inlineStr"/>
+      <c r="E8" s="19" t="inlineStr"/>
+      <c r="F8" s="19" t="inlineStr"/>
+      <c r="G8" s="19" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -965,22 +921,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONERiconoscimento della funzione sociale ed educativa degli oratoriApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="18" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/riconoscimento-della-funzione-sociale-ed-educativa-degli-oratori/</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr"/>
-      <c r="F9" s="13" t="inlineStr"/>
-      <c r="G9" s="13" t="inlineStr"/>
+      <c r="E9" s="17" t="inlineStr"/>
+      <c r="F9" s="17" t="inlineStr"/>
+      <c r="G9" s="17" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -990,22 +946,22 @@
           <t>GovernanceIscrizione nell’elenco regionale degli idonei all’esercizio dell’attività di direttore dell’Istituto JemoloApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/iscrizione-nellelenco-regionale-degli-idonei-allesercizio-dellattivita-di-direttore-dellistituto-jemolo/</t>
         </is>
       </c>
-      <c r="E10" s="15" t="inlineStr"/>
-      <c r="F10" s="15" t="inlineStr"/>
-      <c r="G10" s="15" t="inlineStr"/>
+      <c r="E10" s="19" t="inlineStr"/>
+      <c r="F10" s="19" t="inlineStr"/>
+      <c r="G10" s="19" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1015,22 +971,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEVoucher per lo sport – seconda annualitàApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D11" s="18" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/voucher-per-lo-sport-seconda-annualita/</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr"/>
-      <c r="F11" s="13" t="inlineStr"/>
-      <c r="G11" s="13" t="inlineStr"/>
+      <c r="E11" s="17" t="inlineStr"/>
+      <c r="F11" s="17" t="inlineStr"/>
+      <c r="G11" s="17" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1040,22 +996,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEBonus occupazionale SALGOApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/bonus-occupazionale-salgo/</t>
         </is>
       </c>
-      <c r="E12" s="15" t="inlineStr"/>
-      <c r="F12" s="15" t="inlineStr"/>
-      <c r="G12" s="15" t="inlineStr"/>
+      <c r="E12" s="19" t="inlineStr"/>
+      <c r="F12" s="19" t="inlineStr"/>
+      <c r="G12" s="19" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1065,22 +1021,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEContributo di Libertà per le donne che hanno subito violenzaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="18" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-di-liberta-per-le-donne-che-hanno-subito-violenza/</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr"/>
-      <c r="F13" s="13" t="inlineStr"/>
-      <c r="G13" s="13" t="inlineStr"/>
+      <c r="E13" s="17" t="inlineStr"/>
+      <c r="F13" s="17" t="inlineStr"/>
+      <c r="G13" s="17" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1090,22 +1046,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURAInterventi straordinari di valorizzazione del patrimonio culturale del LazioApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/interventi-straordinari-di-valorizzazione-del-patrimonio-culturale-del-lazio/</t>
         </is>
       </c>
-      <c r="E14" s="15" t="inlineStr"/>
-      <c r="F14" s="15" t="inlineStr"/>
-      <c r="G14" s="15" t="inlineStr"/>
+      <c r="E14" s="19" t="inlineStr"/>
+      <c r="F14" s="19" t="inlineStr"/>
+      <c r="G14" s="19" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1115,30 +1071,30 @@
           <t>Bandi di garaBANDO ATTUAZIONE Ob. 1.1 Azione 1 codice 111102 _DIV - "SOSTEGNO ALLA DIVERSIFICAZIONE E NUOVE FORME DI REDDITO PER LA PICCOLA PESCA COST</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D15" s="18" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/bando-avviso-regia-ob-11-azione-1-codice-111102-div-sostegno-alla-diversificazione-nuove-forme-reddito-piccola-pesca-costiera</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>07/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F15" s="13" t="inlineStr">
+      <c r="F15" s="17" t="inlineStr">
         <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="G15" s="13" t="inlineStr"/>
+      <c r="G15" s="17" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1148,30 +1104,30 @@
           <t>Avvisi pubblici09 marzo 2026 - ST SIRACUSA - AVVISO PUBBLICO PER LA COSTITUZIONE DI ELENCHI DI OPERATORI ECONOMICI PER L’ACQUISIZIONE DI BENI E SERVIZ</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/09-marzo-2026-st-siracusa-avviso-pubblico-costituzione-elenchi-operatori-economici-l-acquisizione-beni-servizi</t>
         </is>
       </c>
-      <c r="E16" s="15" t="inlineStr">
+      <c r="E16" s="19" t="inlineStr">
         <is>
           <t>31/12/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F16" s="15" t="inlineStr">
+      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>31/12/2026</t>
         </is>
       </c>
-      <c r="G16" s="15" t="inlineStr"/>
+      <c r="G16" s="19" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1181,30 +1137,30 @@
           <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScade il:19/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D17" s="18" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>19/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F17" s="13" t="inlineStr">
+      <c r="F17" s="17" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G17" s="13" t="inlineStr"/>
+      <c r="G17" s="17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1214,22 +1170,22 @@
           <t>Manifestazioni di interesseAvviso Manifestazione Interesse DISTRIBUTORI AUTOMATICI di bevande e snackScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-distributori-automatici-bevande-snack</t>
         </is>
       </c>
-      <c r="E18" s="15" t="inlineStr"/>
-      <c r="F18" s="15" t="inlineStr"/>
-      <c r="G18" s="15" t="inlineStr"/>
+      <c r="E18" s="19" t="inlineStr"/>
+      <c r="F18" s="19" t="inlineStr"/>
+      <c r="G18" s="19" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1239,30 +1195,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D19" s="18" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F19" s="13" t="inlineStr">
+      <c r="F19" s="17" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G19" s="13" t="inlineStr"/>
+      <c r="G19" s="17" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1272,30 +1228,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo-0</t>
         </is>
       </c>
-      <c r="E20" s="15" t="inlineStr">
+      <c r="E20" s="19" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F20" s="15" t="inlineStr">
+      <c r="F20" s="19" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G20" s="15" t="inlineStr"/>
+      <c r="G20" s="19" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1305,22 +1261,22 @@
           <t>Manifestazioni di interesseST SIRACUSA - AVVISO DI MANIFESTAZIONE DI INTERESSE - Fornitura applicativo extracontabile per la gestione progetti, ecc. e</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr">
+      <c r="D21" s="18" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-siracusa-avviso-manifestazione-interesse-fornitura-applicativo-extracontabile-gestione-progetti-ecc-applicativo-gestione-ed-elaborazione-informatizzata-paghe</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr"/>
-      <c r="F21" s="13" t="inlineStr"/>
-      <c r="G21" s="13" t="inlineStr"/>
+      <c r="E21" s="17" t="inlineStr"/>
+      <c r="F21" s="17" t="inlineStr"/>
+      <c r="G21" s="17" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1330,30 +1286,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile sito nel Comune di Capo D'Orlando, Via Trazzera MarinaScade il:25/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-sito-nel-comune-capo-d-orlando-trazzera-marina</t>
         </is>
       </c>
-      <c r="E22" s="15" t="inlineStr">
+      <c r="E22" s="19" t="inlineStr">
         <is>
           <t>25/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F22" s="15" t="inlineStr">
+      <c r="F22" s="19" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="G22" s="15" t="inlineStr"/>
+      <c r="G22" s="19" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1363,22 +1319,22 @@
           <t xml:space="preserve">Avvisi pubbliciST CATANIA - Programma Regionale FESR Sicilia 2021-2027 - Azione 2.4.4 - “Interventi per la riduzione del rischio incendi” - AVVISO DI </t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr">
+      <c r="D23" s="18" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-catania-programma-regionale-fesr-sicilia-2021-2027-azione-244-interventi-riduzione-rischio-incendi-avviso-indagine-mercato</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr"/>
-      <c r="F23" s="13" t="inlineStr"/>
-      <c r="G23" s="13" t="inlineStr"/>
+      <c r="E23" s="17" t="inlineStr"/>
+      <c r="F23" s="17" t="inlineStr"/>
+      <c r="G23" s="17" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B24" s="19" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1388,22 +1344,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per ROMICS – Primavera 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-romics-primavera-2026/</t>
         </is>
       </c>
-      <c r="E24" s="15" t="inlineStr"/>
-      <c r="F24" s="15" t="inlineStr"/>
-      <c r="G24" s="15" t="inlineStr"/>
+      <c r="E24" s="19" t="inlineStr"/>
+      <c r="F24" s="19" t="inlineStr"/>
+      <c r="G24" s="19" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="A25" s="17" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B25" s="17" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1413,14 +1369,14 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Cinema International 2026 – I edizioneApertoFESR</t>
         </is>
       </c>
-      <c r="D25" s="14" t="inlineStr">
+      <c r="D25" s="18" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lazio-cinema-international-2026-i-edizione/</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr"/>
-      <c r="F25" s="13" t="inlineStr"/>
-      <c r="G25" s="13" t="inlineStr"/>
+      <c r="E25" s="17" t="inlineStr"/>
+      <c r="F25" s="17" t="inlineStr"/>
+      <c r="G25" s="17" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="19" t="inlineStr">
@@ -1537,6 +1493,64 @@
         </is>
       </c>
       <c r="G29" s="17" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="23" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURARistrutturazione e riconversione vigneti – campagna 2026-2027ApertoBandi Regionali</t>
+        </is>
+      </c>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/ristrutturazione-e-riconversione-vigneti-campagna-2026-2027/</t>
+        </is>
+      </c>
+      <c r="E30" s="23" t="inlineStr"/>
+      <c r="F30" s="23" t="inlineStr"/>
+      <c r="G30" s="23" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="21" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Manifestazioni di interessePR FESR 2021/27 Azione 1.3.3 e del POC 2014/20 - Azione 1.3.1  - Avviso a manifestazione d’interesse eventi fieristici inte</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-d-interesse-eventi-fieristici-internazionali-marzo-dicembre-2026</t>
+        </is>
+      </c>
+      <c r="E31" s="21" t="inlineStr">
+        <is>
+          <t>30/06/2026 - 23:59</t>
+        </is>
+      </c>
+      <c r="F31" s="21" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="G31" s="21" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1568,6 +1582,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1612,7 +1628,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -1625,29 +1641,29 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="19" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">

--- a/data/bandi_export.xlsx
+++ b/data/bandi_export.xlsx
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -152,6 +152,18 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -568,7 +580,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏛️  Nuovi Bandi — 17/03/2026 07:50</t>
+          <t>🏛️  Nuovi Bandi — 18/03/2026 07:48</t>
         </is>
       </c>
     </row>
@@ -613,54 +625,46 @@
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="21" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURARistrutturazione e riconversione vigneti – campagna 2026-2027ApertoBandi Regionali</t>
-        </is>
-      </c>
-      <c r="D3" s="22" t="inlineStr">
-        <is>
-          <t>https://www.lazioeuropa.it/bandi/ristrutturazione-e-riconversione-vigneti-campagna-2026-2027/</t>
-        </is>
-      </c>
-      <c r="E3" s="21" t="inlineStr"/>
-      <c r="F3" s="21" t="inlineStr"/>
+          <t>INTERNAZIONALIZZAZIONEL’Ecosistema dell’Innovazione a INNOVIT – Focus S3ApertoFESR</t>
+        </is>
+      </c>
+      <c r="D3" s="26" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/lecosistema-dellinnovazione-a-innovit-focus-s3/</t>
+        </is>
+      </c>
+      <c r="E3" s="25" t="inlineStr"/>
+      <c r="F3" s="25" t="inlineStr"/>
       <c r="G3" s="5" t="inlineStr"/>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="27" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>Manifestazioni di interessePR FESR 2021/27 Azione 1.3.3 e del POC 2014/20 - Azione 1.3.1  - Avviso a manifestazione d’interesse eventi fieristici inte</t>
-        </is>
-      </c>
-      <c r="D4" s="24" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-d-interesse-eventi-fieristici-internazionali-marzo-dicembre-2026</t>
-        </is>
-      </c>
-      <c r="E4" s="23" t="inlineStr">
-        <is>
-          <t>30/06/2026 - 23:59</t>
-        </is>
-      </c>
-      <c r="F4" s="23" t="inlineStr">
-        <is>
-          <t>30/06/2026</t>
-        </is>
-      </c>
+          <t>Manifestazioni di interessePR FESR SICILIA 2021/27 - NUOVO Avviso a manifestazione d’interesse per esperti valutatoriScadutoLeggi di più</t>
+        </is>
+      </c>
+      <c r="D4" s="28" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/pr-fesr-sicilia-202127-nuovo-avviso-manifestazione-d-interesse-esperti-valutatori</t>
+        </is>
+      </c>
+      <c r="E4" s="27" t="inlineStr"/>
+      <c r="F4" s="27" t="inlineStr"/>
       <c r="G4" s="9" t="inlineStr"/>
     </row>
   </sheetData>
@@ -681,7 +685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -731,12 +735,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="19" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B2" s="19" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -746,22 +750,22 @@
           <t>FLAG GALPA Costa E-R. Sostituzione del motore principale e dei motori secondari. Secondo bando</t>
         </is>
       </c>
-      <c r="D2" s="20" t="inlineStr">
+      <c r="D2" s="24" t="inlineStr">
         <is>
           <t>https://agricoltura.regione.emilia-romagna.it/feampa-2021-2027/bandi-galpa/2026/galpa-sostituzione-motori-secondo-bando</t>
         </is>
       </c>
-      <c r="E2" s="19" t="inlineStr"/>
-      <c r="F2" s="19" t="inlineStr"/>
-      <c r="G2" s="19" t="inlineStr"/>
+      <c r="E2" s="23" t="inlineStr"/>
+      <c r="F2" s="23" t="inlineStr"/>
+      <c r="G2" s="23" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -771,22 +775,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0PRE-SEED 3.0Prossima AperturaFESR</t>
         </is>
       </c>
-      <c r="D3" s="18" t="inlineStr">
+      <c r="D3" s="22" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/pre-seed-3-0/</t>
         </is>
       </c>
-      <c r="E3" s="17" t="inlineStr"/>
-      <c r="F3" s="17" t="inlineStr"/>
-      <c r="G3" s="17" t="inlineStr"/>
+      <c r="E3" s="21" t="inlineStr"/>
+      <c r="F3" s="21" t="inlineStr"/>
+      <c r="G3" s="21" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="19" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -796,22 +800,22 @@
           <t>ACCESSO AL CREDITO E ALLE GARANZIE PER LE IMPRESEContributo su finanziamenti alle imprese del Lazio erogati su provvista BEIProssima AperturaFESR</t>
         </is>
       </c>
-      <c r="D4" s="20" t="inlineStr">
+      <c r="D4" s="24" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-su-finanziamenti-alle-imprese-del-lazio-erogati-su-provvista-bei/</t>
         </is>
       </c>
-      <c r="E4" s="19" t="inlineStr"/>
-      <c r="F4" s="19" t="inlineStr"/>
-      <c r="G4" s="19" t="inlineStr"/>
+      <c r="E4" s="23" t="inlineStr"/>
+      <c r="F4" s="23" t="inlineStr"/>
+      <c r="G4" s="23" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -821,22 +825,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEIndividuazione degli enti iscritti al Registro unico nazionale del Terzo settoreApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D5" s="18" t="inlineStr">
+      <c r="D5" s="22" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/individuazione-degli-enti-iscritti-al-registro-unico-nazionale-del-terzo-settore/</t>
         </is>
       </c>
-      <c r="E5" s="17" t="inlineStr"/>
-      <c r="F5" s="17" t="inlineStr"/>
-      <c r="G5" s="17" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr"/>
+      <c r="F5" s="21" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="19" t="inlineStr">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -846,22 +850,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Technology Transfer LazioApertoFESR</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D6" s="24" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/technology-transfer-lazio/</t>
         </is>
       </c>
-      <c r="E6" s="19" t="inlineStr"/>
-      <c r="F6" s="19" t="inlineStr"/>
-      <c r="G6" s="19" t="inlineStr"/>
+      <c r="E6" s="23" t="inlineStr"/>
+      <c r="F6" s="23" t="inlineStr"/>
+      <c r="G6" s="23" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -871,22 +875,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Percorso di tutoraggio per le impreseApertoFESR</t>
         </is>
       </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/percorso-di-tutoraggio-per-le-imprese/</t>
         </is>
       </c>
-      <c r="E7" s="17" t="inlineStr"/>
-      <c r="F7" s="17" t="inlineStr"/>
-      <c r="G7" s="17" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="21" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -896,22 +900,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per partecipare a SMAU Parigi 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="24" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-partecipare-a-smau-parigi-2026/</t>
         </is>
       </c>
-      <c r="E8" s="19" t="inlineStr"/>
-      <c r="F8" s="19" t="inlineStr"/>
-      <c r="G8" s="19" t="inlineStr"/>
+      <c r="E8" s="23" t="inlineStr"/>
+      <c r="F8" s="23" t="inlineStr"/>
+      <c r="G8" s="23" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -921,22 +925,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONERiconoscimento della funzione sociale ed educativa degli oratoriApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/riconoscimento-della-funzione-sociale-ed-educativa-degli-oratori/</t>
         </is>
       </c>
-      <c r="E9" s="17" t="inlineStr"/>
-      <c r="F9" s="17" t="inlineStr"/>
-      <c r="G9" s="17" t="inlineStr"/>
+      <c r="E9" s="21" t="inlineStr"/>
+      <c r="F9" s="21" t="inlineStr"/>
+      <c r="G9" s="21" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -946,22 +950,22 @@
           <t>GovernanceIscrizione nell’elenco regionale degli idonei all’esercizio dell’attività di direttore dell’Istituto JemoloApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="24" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/iscrizione-nellelenco-regionale-degli-idonei-allesercizio-dellattivita-di-direttore-dellistituto-jemolo/</t>
         </is>
       </c>
-      <c r="E10" s="19" t="inlineStr"/>
-      <c r="F10" s="19" t="inlineStr"/>
-      <c r="G10" s="19" t="inlineStr"/>
+      <c r="E10" s="23" t="inlineStr"/>
+      <c r="F10" s="23" t="inlineStr"/>
+      <c r="G10" s="23" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -971,22 +975,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEVoucher per lo sport – seconda annualitàApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/voucher-per-lo-sport-seconda-annualita/</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr"/>
-      <c r="F11" s="17" t="inlineStr"/>
-      <c r="G11" s="17" t="inlineStr"/>
+      <c r="E11" s="21" t="inlineStr"/>
+      <c r="F11" s="21" t="inlineStr"/>
+      <c r="G11" s="21" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -996,22 +1000,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEBonus occupazionale SALGOApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="D12" s="24" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/bonus-occupazionale-salgo/</t>
         </is>
       </c>
-      <c r="E12" s="19" t="inlineStr"/>
-      <c r="F12" s="19" t="inlineStr"/>
-      <c r="G12" s="19" t="inlineStr"/>
+      <c r="E12" s="23" t="inlineStr"/>
+      <c r="F12" s="23" t="inlineStr"/>
+      <c r="G12" s="23" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1021,22 +1025,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEContributo di Libertà per le donne che hanno subito violenzaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D13" s="18" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-di-liberta-per-le-donne-che-hanno-subito-violenza/</t>
         </is>
       </c>
-      <c r="E13" s="17" t="inlineStr"/>
-      <c r="F13" s="17" t="inlineStr"/>
-      <c r="G13" s="17" t="inlineStr"/>
+      <c r="E13" s="21" t="inlineStr"/>
+      <c r="F13" s="21" t="inlineStr"/>
+      <c r="G13" s="21" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1046,22 +1050,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURAInterventi straordinari di valorizzazione del patrimonio culturale del LazioApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
+      <c r="D14" s="24" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/interventi-straordinari-di-valorizzazione-del-patrimonio-culturale-del-lazio/</t>
         </is>
       </c>
-      <c r="E14" s="19" t="inlineStr"/>
-      <c r="F14" s="19" t="inlineStr"/>
-      <c r="G14" s="19" t="inlineStr"/>
+      <c r="E14" s="23" t="inlineStr"/>
+      <c r="F14" s="23" t="inlineStr"/>
+      <c r="G14" s="23" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="A15" s="21" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1071,30 +1075,30 @@
           <t>Bandi di garaBANDO ATTUAZIONE Ob. 1.1 Azione 1 codice 111102 _DIV - "SOSTEGNO ALLA DIVERSIFICAZIONE E NUOVE FORME DI REDDITO PER LA PICCOLA PESCA COST</t>
         </is>
       </c>
-      <c r="D15" s="18" t="inlineStr">
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/bando-avviso-regia-ob-11-azione-1-codice-111102-div-sostegno-alla-diversificazione-nuove-forme-reddito-piccola-pesca-costiera</t>
         </is>
       </c>
-      <c r="E15" s="17" t="inlineStr">
+      <c r="E15" s="21" t="inlineStr">
         <is>
           <t>07/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="F15" s="21" t="inlineStr">
         <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="G15" s="17" t="inlineStr"/>
+      <c r="G15" s="21" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1104,30 +1108,30 @@
           <t>Avvisi pubblici09 marzo 2026 - ST SIRACUSA - AVVISO PUBBLICO PER LA COSTITUZIONE DI ELENCHI DI OPERATORI ECONOMICI PER L’ACQUISIZIONE DI BENI E SERVIZ</t>
         </is>
       </c>
-      <c r="D16" s="20" t="inlineStr">
+      <c r="D16" s="24" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/09-marzo-2026-st-siracusa-avviso-pubblico-costituzione-elenchi-operatori-economici-l-acquisizione-beni-servizi</t>
         </is>
       </c>
-      <c r="E16" s="19" t="inlineStr">
+      <c r="E16" s="23" t="inlineStr">
         <is>
           <t>31/12/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F16" s="19" t="inlineStr">
+      <c r="F16" s="23" t="inlineStr">
         <is>
           <t>31/12/2026</t>
         </is>
       </c>
-      <c r="G16" s="19" t="inlineStr"/>
+      <c r="G16" s="23" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="A17" s="21" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1137,30 +1141,30 @@
           <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScade il:19/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D17" s="18" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
         </is>
       </c>
-      <c r="E17" s="17" t="inlineStr">
+      <c r="E17" s="21" t="inlineStr">
         <is>
           <t>19/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F17" s="17" t="inlineStr">
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G17" s="17" t="inlineStr"/>
+      <c r="G17" s="21" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="inlineStr">
+      <c r="A18" s="23" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1170,22 +1174,22 @@
           <t>Manifestazioni di interesseAvviso Manifestazione Interesse DISTRIBUTORI AUTOMATICI di bevande e snackScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D18" s="20" t="inlineStr">
+      <c r="D18" s="24" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-distributori-automatici-bevande-snack</t>
         </is>
       </c>
-      <c r="E18" s="19" t="inlineStr"/>
-      <c r="F18" s="19" t="inlineStr"/>
-      <c r="G18" s="19" t="inlineStr"/>
+      <c r="E18" s="23" t="inlineStr"/>
+      <c r="F18" s="23" t="inlineStr"/>
+      <c r="G18" s="23" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="A19" s="21" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1195,30 +1199,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D19" s="18" t="inlineStr">
+      <c r="D19" s="22" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo</t>
         </is>
       </c>
-      <c r="E19" s="17" t="inlineStr">
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F19" s="17" t="inlineStr">
+      <c r="F19" s="21" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G19" s="17" t="inlineStr"/>
+      <c r="G19" s="21" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="A20" s="23" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1228,30 +1232,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D20" s="20" t="inlineStr">
+      <c r="D20" s="24" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo-0</t>
         </is>
       </c>
-      <c r="E20" s="19" t="inlineStr">
+      <c r="E20" s="23" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F20" s="19" t="inlineStr">
+      <c r="F20" s="23" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G20" s="19" t="inlineStr"/>
+      <c r="G20" s="23" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="17" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="A21" s="21" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1261,22 +1265,22 @@
           <t>Manifestazioni di interesseST SIRACUSA - AVVISO DI MANIFESTAZIONE DI INTERESSE - Fornitura applicativo extracontabile per la gestione progetti, ecc. e</t>
         </is>
       </c>
-      <c r="D21" s="18" t="inlineStr">
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-siracusa-avviso-manifestazione-interesse-fornitura-applicativo-extracontabile-gestione-progetti-ecc-applicativo-gestione-ed-elaborazione-informatizzata-paghe</t>
         </is>
       </c>
-      <c r="E21" s="17" t="inlineStr"/>
-      <c r="F21" s="17" t="inlineStr"/>
-      <c r="G21" s="17" t="inlineStr"/>
+      <c r="E21" s="21" t="inlineStr"/>
+      <c r="F21" s="21" t="inlineStr"/>
+      <c r="G21" s="21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr">
+      <c r="A22" s="23" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1286,30 +1290,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile sito nel Comune di Capo D'Orlando, Via Trazzera MarinaScade il:25/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D22" s="20" t="inlineStr">
+      <c r="D22" s="24" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-sito-nel-comune-capo-d-orlando-trazzera-marina</t>
         </is>
       </c>
-      <c r="E22" s="19" t="inlineStr">
+      <c r="E22" s="23" t="inlineStr">
         <is>
           <t>25/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F22" s="19" t="inlineStr">
+      <c r="F22" s="23" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="G22" s="19" t="inlineStr"/>
+      <c r="G22" s="23" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
+      <c r="A23" s="21" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1319,22 +1323,22 @@
           <t xml:space="preserve">Avvisi pubbliciST CATANIA - Programma Regionale FESR Sicilia 2021-2027 - Azione 2.4.4 - “Interventi per la riduzione del rischio incendi” - AVVISO DI </t>
         </is>
       </c>
-      <c r="D23" s="18" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-catania-programma-regionale-fesr-sicilia-2021-2027-azione-244-interventi-riduzione-rischio-incendi-avviso-indagine-mercato</t>
         </is>
       </c>
-      <c r="E23" s="17" t="inlineStr"/>
-      <c r="F23" s="17" t="inlineStr"/>
-      <c r="G23" s="17" t="inlineStr"/>
+      <c r="E23" s="21" t="inlineStr"/>
+      <c r="F23" s="21" t="inlineStr"/>
+      <c r="G23" s="21" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="19" t="inlineStr">
+      <c r="A24" s="23" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B24" s="19" t="inlineStr">
+      <c r="B24" s="23" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1344,22 +1348,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per ROMICS – Primavera 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D24" s="20" t="inlineStr">
+      <c r="D24" s="24" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-romics-primavera-2026/</t>
         </is>
       </c>
-      <c r="E24" s="19" t="inlineStr"/>
-      <c r="F24" s="19" t="inlineStr"/>
-      <c r="G24" s="19" t="inlineStr"/>
+      <c r="E24" s="23" t="inlineStr"/>
+      <c r="F24" s="23" t="inlineStr"/>
+      <c r="G24" s="23" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="17" t="inlineStr">
+      <c r="A25" s="21" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B25" s="17" t="inlineStr">
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1369,22 +1373,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Cinema International 2026 – I edizioneApertoFESR</t>
         </is>
       </c>
-      <c r="D25" s="18" t="inlineStr">
+      <c r="D25" s="22" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lazio-cinema-international-2026-i-edizione/</t>
         </is>
       </c>
-      <c r="E25" s="17" t="inlineStr"/>
-      <c r="F25" s="17" t="inlineStr"/>
-      <c r="G25" s="17" t="inlineStr"/>
+      <c r="E25" s="21" t="inlineStr"/>
+      <c r="F25" s="21" t="inlineStr"/>
+      <c r="G25" s="21" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="19" t="inlineStr">
+      <c r="A26" s="23" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B26" s="19" t="inlineStr">
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1394,22 +1398,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEManifestazioni di interesse alla costituzione di due nuove Fondazioni I.T.S. AcademyApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D26" s="20" t="inlineStr">
+      <c r="D26" s="24" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazioni-di-interesse-alla-costituzione-di-due-nuove-fondazioni-i-t-s-academy/</t>
         </is>
       </c>
-      <c r="E26" s="19" t="inlineStr"/>
-      <c r="F26" s="19" t="inlineStr"/>
-      <c r="G26" s="19" t="inlineStr"/>
+      <c r="E26" s="23" t="inlineStr"/>
+      <c r="F26" s="23" t="inlineStr"/>
+      <c r="G26" s="23" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="21" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B27" s="17" t="inlineStr">
+      <c r="B27" s="21" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1419,22 +1423,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURAContributi per sostenere la ripresa del settore della pescaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D27" s="18" t="inlineStr">
+      <c r="D27" s="22" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributi-per-sostenere-la-ripresa-del-settore-della-pesca/</t>
         </is>
       </c>
-      <c r="E27" s="17" t="inlineStr"/>
-      <c r="F27" s="17" t="inlineStr"/>
-      <c r="G27" s="17" t="inlineStr"/>
+      <c r="E27" s="21" t="inlineStr"/>
+      <c r="F27" s="21" t="inlineStr"/>
+      <c r="G27" s="21" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="19" t="inlineStr">
+      <c r="A28" s="23" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B28" s="19" t="inlineStr">
+      <c r="B28" s="23" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1444,30 +1448,30 @@
           <t>Manifestazioni di interesseAVVISO - Manifestazione Interesse “Storytelling aziendale” Expo Wild Natura - Caccia - Pesca. Misterbianco (CT), 10-12 apri</t>
         </is>
       </c>
-      <c r="D28" s="20" t="inlineStr">
+      <c r="D28" s="24" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-storytelling-aziendale-expo-wild-natura-caccia-pesca-misterbianco-ct-10-12-aprile-2026</t>
         </is>
       </c>
-      <c r="E28" s="19" t="inlineStr">
+      <c r="E28" s="23" t="inlineStr">
         <is>
           <t>30/03/2026 - 13:00</t>
         </is>
       </c>
-      <c r="F28" s="19" t="inlineStr">
+      <c r="F28" s="23" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G28" s="19" t="inlineStr"/>
+      <c r="G28" s="23" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="17" t="inlineStr">
+      <c r="A29" s="21" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B29" s="17" t="inlineStr">
+      <c r="B29" s="21" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1477,22 +1481,22 @@
           <t>Manifestazioni di interesseInvaso Lentini - Interventi di ripristino delle pareti esterne in cls della Torre di presa Sud e della trave d’appoggio del</t>
         </is>
       </c>
-      <c r="D29" s="18" t="inlineStr">
+      <c r="D29" s="22" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/invaso-lentini-interventi-ripristino-pareti-esterne-cls-torre-presa-sud-trave-d-appoggio-cavalcavia-collegamento-alla-stessa-torre</t>
         </is>
       </c>
-      <c r="E29" s="17" t="inlineStr">
+      <c r="E29" s="21" t="inlineStr">
         <is>
           <t>19/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F29" s="17" t="inlineStr">
+      <c r="F29" s="21" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G29" s="17" t="inlineStr"/>
+      <c r="G29" s="21" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="23" t="inlineStr">
@@ -1551,6 +1555,56 @@
         </is>
       </c>
       <c r="G31" s="21" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="27" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="27" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>INTERNAZIONALIZZAZIONEL’Ecosistema dell’Innovazione a INNOVIT – Focus S3ApertoFESR</t>
+        </is>
+      </c>
+      <c r="D32" s="28" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/lecosistema-dellinnovazione-a-innovit-focus-s3/</t>
+        </is>
+      </c>
+      <c r="E32" s="27" t="inlineStr"/>
+      <c r="F32" s="27" t="inlineStr"/>
+      <c r="G32" s="27" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="25" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Manifestazioni di interessePR FESR SICILIA 2021/27 - NUOVO Avviso a manifestazione d’interesse per esperti valutatoriScadutoLeggi di più</t>
+        </is>
+      </c>
+      <c r="D33" s="26" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/pr-fesr-sicilia-202127-nuovo-avviso-manifestazione-d-interesse-esperti-valutatori</t>
+        </is>
+      </c>
+      <c r="E33" s="25" t="inlineStr"/>
+      <c r="F33" s="25" t="inlineStr"/>
+      <c r="G33" s="25" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1584,6 +1638,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1628,7 +1684,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="25" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -1641,26 +1697,26 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="23" t="inlineStr">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>1</v>

--- a/data/bandi_export.xlsx
+++ b/data/bandi_export.xlsx
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -152,6 +152,18 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -580,7 +592,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏛️  Nuovi Bandi — 18/03/2026 07:48</t>
+          <t>🏛️  Nuovi Bandi — 19/03/2026 07:42</t>
         </is>
       </c>
     </row>
@@ -625,46 +637,46 @@
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="25" t="inlineStr">
-        <is>
-          <t>Lazio</t>
+      <c r="B3" s="29" t="inlineStr">
+        <is>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>INTERNAZIONALIZZAZIONEL’Ecosistema dell’Innovazione a INNOVIT – Focus S3ApertoFESR</t>
-        </is>
-      </c>
-      <c r="D3" s="26" t="inlineStr">
-        <is>
-          <t>https://www.lazioeuropa.it/bandi/lecosistema-dellinnovazione-a-innovit-focus-s3/</t>
-        </is>
-      </c>
-      <c r="E3" s="25" t="inlineStr"/>
-      <c r="F3" s="25" t="inlineStr"/>
+          <t>Bando 2026 per contributi dedicati alla manutenzione della rete dei percorsi escursionistici</t>
+        </is>
+      </c>
+      <c r="D3" s="30" t="inlineStr">
+        <is>
+          <t>https://ambiente.regione.emilia-romagna.it/it/parchi-natura2000/bandi/bando-2026-per-contributi-dedicati-alla-manutenzione-della-rete-dei-percorsi-escursionistici</t>
+        </is>
+      </c>
+      <c r="E3" s="29" t="inlineStr"/>
+      <c r="F3" s="29" t="inlineStr"/>
       <c r="G3" s="5" t="inlineStr"/>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="27" t="inlineStr">
-        <is>
-          <t>Sicilia</t>
+      <c r="B4" s="31" t="inlineStr">
+        <is>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>Manifestazioni di interessePR FESR SICILIA 2021/27 - NUOVO Avviso a manifestazione d’interesse per esperti valutatoriScadutoLeggi di più</t>
-        </is>
-      </c>
-      <c r="D4" s="28" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/pr-fesr-sicilia-202127-nuovo-avviso-manifestazione-d-interesse-esperti-valutatori</t>
-        </is>
-      </c>
-      <c r="E4" s="27" t="inlineStr"/>
-      <c r="F4" s="27" t="inlineStr"/>
+          <t>Programma regionale in favore delle tradizioni storiche, artistiche, religiose e popolari (2026) – manifestazioni d’interesseApertoBandi Regionali</t>
+        </is>
+      </c>
+      <c r="D4" s="32" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/programma-regionale-in-favore-delle-tradizioni-storiche-artistiche-religiose-e-popolari-2026-manifestazioni-dinteresse/</t>
+        </is>
+      </c>
+      <c r="E4" s="31" t="inlineStr"/>
+      <c r="F4" s="31" t="inlineStr"/>
       <c r="G4" s="9" t="inlineStr"/>
     </row>
   </sheetData>
@@ -685,7 +697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -735,12 +747,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="23" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B2" s="23" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="27" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -750,22 +762,22 @@
           <t>FLAG GALPA Costa E-R. Sostituzione del motore principale e dei motori secondari. Secondo bando</t>
         </is>
       </c>
-      <c r="D2" s="24" t="inlineStr">
+      <c r="D2" s="28" t="inlineStr">
         <is>
           <t>https://agricoltura.regione.emilia-romagna.it/feampa-2021-2027/bandi-galpa/2026/galpa-sostituzione-motori-secondo-bando</t>
         </is>
       </c>
-      <c r="E2" s="23" t="inlineStr"/>
-      <c r="F2" s="23" t="inlineStr"/>
-      <c r="G2" s="23" t="inlineStr"/>
+      <c r="E2" s="27" t="inlineStr"/>
+      <c r="F2" s="27" t="inlineStr"/>
+      <c r="G2" s="27" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="21" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="21" t="inlineStr">
+      <c r="A3" s="25" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -775,22 +787,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0PRE-SEED 3.0Prossima AperturaFESR</t>
         </is>
       </c>
-      <c r="D3" s="22" t="inlineStr">
+      <c r="D3" s="26" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/pre-seed-3-0/</t>
         </is>
       </c>
-      <c r="E3" s="21" t="inlineStr"/>
-      <c r="F3" s="21" t="inlineStr"/>
-      <c r="G3" s="21" t="inlineStr"/>
+      <c r="E3" s="25" t="inlineStr"/>
+      <c r="F3" s="25" t="inlineStr"/>
+      <c r="G3" s="25" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="23" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="A4" s="27" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="27" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -800,22 +812,22 @@
           <t>ACCESSO AL CREDITO E ALLE GARANZIE PER LE IMPRESEContributo su finanziamenti alle imprese del Lazio erogati su provvista BEIProssima AperturaFESR</t>
         </is>
       </c>
-      <c r="D4" s="24" t="inlineStr">
+      <c r="D4" s="28" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-su-finanziamenti-alle-imprese-del-lazio-erogati-su-provvista-bei/</t>
         </is>
       </c>
-      <c r="E4" s="23" t="inlineStr"/>
-      <c r="F4" s="23" t="inlineStr"/>
-      <c r="G4" s="23" t="inlineStr"/>
+      <c r="E4" s="27" t="inlineStr"/>
+      <c r="F4" s="27" t="inlineStr"/>
+      <c r="G4" s="27" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -825,22 +837,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEIndividuazione degli enti iscritti al Registro unico nazionale del Terzo settoreApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D5" s="22" t="inlineStr">
+      <c r="D5" s="26" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/individuazione-degli-enti-iscritti-al-registro-unico-nazionale-del-terzo-settore/</t>
         </is>
       </c>
-      <c r="E5" s="21" t="inlineStr"/>
-      <c r="F5" s="21" t="inlineStr"/>
-      <c r="G5" s="21" t="inlineStr"/>
+      <c r="E5" s="25" t="inlineStr"/>
+      <c r="F5" s="25" t="inlineStr"/>
+      <c r="G5" s="25" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="23" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="27" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -850,22 +862,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Technology Transfer LazioApertoFESR</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="28" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/technology-transfer-lazio/</t>
         </is>
       </c>
-      <c r="E6" s="23" t="inlineStr"/>
-      <c r="F6" s="23" t="inlineStr"/>
-      <c r="G6" s="23" t="inlineStr"/>
+      <c r="E6" s="27" t="inlineStr"/>
+      <c r="F6" s="27" t="inlineStr"/>
+      <c r="G6" s="27" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -875,22 +887,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Percorso di tutoraggio per le impreseApertoFESR</t>
         </is>
       </c>
-      <c r="D7" s="22" t="inlineStr">
+      <c r="D7" s="26" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/percorso-di-tutoraggio-per-le-imprese/</t>
         </is>
       </c>
-      <c r="E7" s="21" t="inlineStr"/>
-      <c r="F7" s="21" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr"/>
+      <c r="E7" s="25" t="inlineStr"/>
+      <c r="F7" s="25" t="inlineStr"/>
+      <c r="G7" s="25" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="23" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="A8" s="27" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="27" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -900,22 +912,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per partecipare a SMAU Parigi 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D8" s="24" t="inlineStr">
+      <c r="D8" s="28" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-partecipare-a-smau-parigi-2026/</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr"/>
-      <c r="F8" s="23" t="inlineStr"/>
-      <c r="G8" s="23" t="inlineStr"/>
+      <c r="E8" s="27" t="inlineStr"/>
+      <c r="F8" s="27" t="inlineStr"/>
+      <c r="G8" s="27" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="25" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -925,22 +937,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONERiconoscimento della funzione sociale ed educativa degli oratoriApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr">
+      <c r="D9" s="26" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/riconoscimento-della-funzione-sociale-ed-educativa-degli-oratori/</t>
         </is>
       </c>
-      <c r="E9" s="21" t="inlineStr"/>
-      <c r="F9" s="21" t="inlineStr"/>
-      <c r="G9" s="21" t="inlineStr"/>
+      <c r="E9" s="25" t="inlineStr"/>
+      <c r="F9" s="25" t="inlineStr"/>
+      <c r="G9" s="25" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="23" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="A10" s="27" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="27" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -950,22 +962,22 @@
           <t>GovernanceIscrizione nell’elenco regionale degli idonei all’esercizio dell’attività di direttore dell’Istituto JemoloApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D10" s="24" t="inlineStr">
+      <c r="D10" s="28" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/iscrizione-nellelenco-regionale-degli-idonei-allesercizio-dellattivita-di-direttore-dellistituto-jemolo/</t>
         </is>
       </c>
-      <c r="E10" s="23" t="inlineStr"/>
-      <c r="F10" s="23" t="inlineStr"/>
-      <c r="G10" s="23" t="inlineStr"/>
+      <c r="E10" s="27" t="inlineStr"/>
+      <c r="F10" s="27" t="inlineStr"/>
+      <c r="G10" s="27" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="A11" s="25" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="25" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -975,22 +987,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEVoucher per lo sport – seconda annualitàApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D11" s="22" t="inlineStr">
+      <c r="D11" s="26" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/voucher-per-lo-sport-seconda-annualita/</t>
         </is>
       </c>
-      <c r="E11" s="21" t="inlineStr"/>
-      <c r="F11" s="21" t="inlineStr"/>
-      <c r="G11" s="21" t="inlineStr"/>
+      <c r="E11" s="25" t="inlineStr"/>
+      <c r="F11" s="25" t="inlineStr"/>
+      <c r="G11" s="25" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="23" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="A12" s="27" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="27" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1000,22 +1012,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEBonus occupazionale SALGOApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D12" s="24" t="inlineStr">
+      <c r="D12" s="28" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/bonus-occupazionale-salgo/</t>
         </is>
       </c>
-      <c r="E12" s="23" t="inlineStr"/>
-      <c r="F12" s="23" t="inlineStr"/>
-      <c r="G12" s="23" t="inlineStr"/>
+      <c r="E12" s="27" t="inlineStr"/>
+      <c r="F12" s="27" t="inlineStr"/>
+      <c r="G12" s="27" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="25" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1025,22 +1037,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEContributo di Libertà per le donne che hanno subito violenzaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D13" s="22" t="inlineStr">
+      <c r="D13" s="26" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-di-liberta-per-le-donne-che-hanno-subito-violenza/</t>
         </is>
       </c>
-      <c r="E13" s="21" t="inlineStr"/>
-      <c r="F13" s="21" t="inlineStr"/>
-      <c r="G13" s="21" t="inlineStr"/>
+      <c r="E13" s="25" t="inlineStr"/>
+      <c r="F13" s="25" t="inlineStr"/>
+      <c r="G13" s="25" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="23" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="23" t="inlineStr">
+      <c r="A14" s="27" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="27" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1050,22 +1062,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURAInterventi straordinari di valorizzazione del patrimonio culturale del LazioApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D14" s="24" t="inlineStr">
+      <c r="D14" s="28" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/interventi-straordinari-di-valorizzazione-del-patrimonio-culturale-del-lazio/</t>
         </is>
       </c>
-      <c r="E14" s="23" t="inlineStr"/>
-      <c r="F14" s="23" t="inlineStr"/>
-      <c r="G14" s="23" t="inlineStr"/>
+      <c r="E14" s="27" t="inlineStr"/>
+      <c r="F14" s="27" t="inlineStr"/>
+      <c r="G14" s="27" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="A15" s="25" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="25" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1075,30 +1087,30 @@
           <t>Bandi di garaBANDO ATTUAZIONE Ob. 1.1 Azione 1 codice 111102 _DIV - "SOSTEGNO ALLA DIVERSIFICAZIONE E NUOVE FORME DI REDDITO PER LA PICCOLA PESCA COST</t>
         </is>
       </c>
-      <c r="D15" s="22" t="inlineStr">
+      <c r="D15" s="26" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/bando-avviso-regia-ob-11-azione-1-codice-111102-div-sostegno-alla-diversificazione-nuove-forme-reddito-piccola-pesca-costiera</t>
         </is>
       </c>
-      <c r="E15" s="21" t="inlineStr">
+      <c r="E15" s="25" t="inlineStr">
         <is>
           <t>07/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F15" s="21" t="inlineStr">
+      <c r="F15" s="25" t="inlineStr">
         <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="G15" s="21" t="inlineStr"/>
+      <c r="G15" s="25" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="23" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="23" t="inlineStr">
+      <c r="A16" s="27" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="27" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1108,30 +1120,30 @@
           <t>Avvisi pubblici09 marzo 2026 - ST SIRACUSA - AVVISO PUBBLICO PER LA COSTITUZIONE DI ELENCHI DI OPERATORI ECONOMICI PER L’ACQUISIZIONE DI BENI E SERVIZ</t>
         </is>
       </c>
-      <c r="D16" s="24" t="inlineStr">
+      <c r="D16" s="28" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/09-marzo-2026-st-siracusa-avviso-pubblico-costituzione-elenchi-operatori-economici-l-acquisizione-beni-servizi</t>
         </is>
       </c>
-      <c r="E16" s="23" t="inlineStr">
+      <c r="E16" s="27" t="inlineStr">
         <is>
           <t>31/12/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F16" s="23" t="inlineStr">
+      <c r="F16" s="27" t="inlineStr">
         <is>
           <t>31/12/2026</t>
         </is>
       </c>
-      <c r="G16" s="23" t="inlineStr"/>
+      <c r="G16" s="27" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="21" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="21" t="inlineStr">
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1141,30 +1153,30 @@
           <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScade il:19/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D17" s="22" t="inlineStr">
+      <c r="D17" s="26" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
         </is>
       </c>
-      <c r="E17" s="21" t="inlineStr">
+      <c r="E17" s="25" t="inlineStr">
         <is>
           <t>19/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F17" s="21" t="inlineStr">
+      <c r="F17" s="25" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G17" s="21" t="inlineStr"/>
+      <c r="G17" s="25" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="23" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="A18" s="27" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="27" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1174,22 +1186,22 @@
           <t>Manifestazioni di interesseAvviso Manifestazione Interesse DISTRIBUTORI AUTOMATICI di bevande e snackScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D18" s="24" t="inlineStr">
+      <c r="D18" s="28" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-distributori-automatici-bevande-snack</t>
         </is>
       </c>
-      <c r="E18" s="23" t="inlineStr"/>
-      <c r="F18" s="23" t="inlineStr"/>
-      <c r="G18" s="23" t="inlineStr"/>
+      <c r="E18" s="27" t="inlineStr"/>
+      <c r="F18" s="27" t="inlineStr"/>
+      <c r="G18" s="27" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="21" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="21" t="inlineStr">
+      <c r="A19" s="25" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="25" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1199,30 +1211,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D19" s="22" t="inlineStr">
+      <c r="D19" s="26" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo</t>
         </is>
       </c>
-      <c r="E19" s="21" t="inlineStr">
+      <c r="E19" s="25" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F19" s="21" t="inlineStr">
+      <c r="F19" s="25" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G19" s="21" t="inlineStr"/>
+      <c r="G19" s="25" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="23" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="23" t="inlineStr">
+      <c r="A20" s="27" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="27" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1232,30 +1244,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D20" s="24" t="inlineStr">
+      <c r="D20" s="28" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo-0</t>
         </is>
       </c>
-      <c r="E20" s="23" t="inlineStr">
+      <c r="E20" s="27" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F20" s="23" t="inlineStr">
+      <c r="F20" s="27" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G20" s="23" t="inlineStr"/>
+      <c r="G20" s="27" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="21" t="inlineStr">
+      <c r="A21" s="25" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="25" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1265,22 +1277,22 @@
           <t>Manifestazioni di interesseST SIRACUSA - AVVISO DI MANIFESTAZIONE DI INTERESSE - Fornitura applicativo extracontabile per la gestione progetti, ecc. e</t>
         </is>
       </c>
-      <c r="D21" s="22" t="inlineStr">
+      <c r="D21" s="26" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-siracusa-avviso-manifestazione-interesse-fornitura-applicativo-extracontabile-gestione-progetti-ecc-applicativo-gestione-ed-elaborazione-informatizzata-paghe</t>
         </is>
       </c>
-      <c r="E21" s="21" t="inlineStr"/>
-      <c r="F21" s="21" t="inlineStr"/>
-      <c r="G21" s="21" t="inlineStr"/>
+      <c r="E21" s="25" t="inlineStr"/>
+      <c r="F21" s="25" t="inlineStr"/>
+      <c r="G21" s="25" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="23" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="23" t="inlineStr">
+      <c r="A22" s="27" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="27" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1290,30 +1302,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile sito nel Comune di Capo D'Orlando, Via Trazzera MarinaScade il:25/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D22" s="24" t="inlineStr">
+      <c r="D22" s="28" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-sito-nel-comune-capo-d-orlando-trazzera-marina</t>
         </is>
       </c>
-      <c r="E22" s="23" t="inlineStr">
+      <c r="E22" s="27" t="inlineStr">
         <is>
           <t>25/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F22" s="23" t="inlineStr">
+      <c r="F22" s="27" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="G22" s="23" t="inlineStr"/>
+      <c r="G22" s="27" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="21" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="21" t="inlineStr">
+      <c r="A23" s="25" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="25" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1323,22 +1335,22 @@
           <t xml:space="preserve">Avvisi pubbliciST CATANIA - Programma Regionale FESR Sicilia 2021-2027 - Azione 2.4.4 - “Interventi per la riduzione del rischio incendi” - AVVISO DI </t>
         </is>
       </c>
-      <c r="D23" s="22" t="inlineStr">
+      <c r="D23" s="26" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-catania-programma-regionale-fesr-sicilia-2021-2027-azione-244-interventi-riduzione-rischio-incendi-avviso-indagine-mercato</t>
         </is>
       </c>
-      <c r="E23" s="21" t="inlineStr"/>
-      <c r="F23" s="21" t="inlineStr"/>
-      <c r="G23" s="21" t="inlineStr"/>
+      <c r="E23" s="25" t="inlineStr"/>
+      <c r="F23" s="25" t="inlineStr"/>
+      <c r="G23" s="25" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="23" t="inlineStr">
+      <c r="A24" s="27" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B24" s="23" t="inlineStr">
+      <c r="B24" s="27" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1348,22 +1360,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per ROMICS – Primavera 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D24" s="24" t="inlineStr">
+      <c r="D24" s="28" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-romics-primavera-2026/</t>
         </is>
       </c>
-      <c r="E24" s="23" t="inlineStr"/>
-      <c r="F24" s="23" t="inlineStr"/>
-      <c r="G24" s="23" t="inlineStr"/>
+      <c r="E24" s="27" t="inlineStr"/>
+      <c r="F24" s="27" t="inlineStr"/>
+      <c r="G24" s="27" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="21" t="inlineStr">
+      <c r="A25" s="25" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B25" s="25" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1373,22 +1385,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Cinema International 2026 – I edizioneApertoFESR</t>
         </is>
       </c>
-      <c r="D25" s="22" t="inlineStr">
+      <c r="D25" s="26" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lazio-cinema-international-2026-i-edizione/</t>
         </is>
       </c>
-      <c r="E25" s="21" t="inlineStr"/>
-      <c r="F25" s="21" t="inlineStr"/>
-      <c r="G25" s="21" t="inlineStr"/>
+      <c r="E25" s="25" t="inlineStr"/>
+      <c r="F25" s="25" t="inlineStr"/>
+      <c r="G25" s="25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="23" t="inlineStr">
+      <c r="A26" s="27" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B26" s="23" t="inlineStr">
+      <c r="B26" s="27" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1398,22 +1410,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEManifestazioni di interesse alla costituzione di due nuove Fondazioni I.T.S. AcademyApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D26" s="24" t="inlineStr">
+      <c r="D26" s="28" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazioni-di-interesse-alla-costituzione-di-due-nuove-fondazioni-i-t-s-academy/</t>
         </is>
       </c>
-      <c r="E26" s="23" t="inlineStr"/>
-      <c r="F26" s="23" t="inlineStr"/>
-      <c r="G26" s="23" t="inlineStr"/>
+      <c r="E26" s="27" t="inlineStr"/>
+      <c r="F26" s="27" t="inlineStr"/>
+      <c r="G26" s="27" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="21" t="inlineStr">
+      <c r="A27" s="25" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B27" s="21" t="inlineStr">
+      <c r="B27" s="25" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1423,22 +1435,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURAContributi per sostenere la ripresa del settore della pescaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D27" s="22" t="inlineStr">
+      <c r="D27" s="26" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributi-per-sostenere-la-ripresa-del-settore-della-pesca/</t>
         </is>
       </c>
-      <c r="E27" s="21" t="inlineStr"/>
-      <c r="F27" s="21" t="inlineStr"/>
-      <c r="G27" s="21" t="inlineStr"/>
+      <c r="E27" s="25" t="inlineStr"/>
+      <c r="F27" s="25" t="inlineStr"/>
+      <c r="G27" s="25" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="23" t="inlineStr">
+      <c r="A28" s="27" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B28" s="23" t="inlineStr">
+      <c r="B28" s="27" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1448,30 +1460,30 @@
           <t>Manifestazioni di interesseAVVISO - Manifestazione Interesse “Storytelling aziendale” Expo Wild Natura - Caccia - Pesca. Misterbianco (CT), 10-12 apri</t>
         </is>
       </c>
-      <c r="D28" s="24" t="inlineStr">
+      <c r="D28" s="28" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-storytelling-aziendale-expo-wild-natura-caccia-pesca-misterbianco-ct-10-12-aprile-2026</t>
         </is>
       </c>
-      <c r="E28" s="23" t="inlineStr">
+      <c r="E28" s="27" t="inlineStr">
         <is>
           <t>30/03/2026 - 13:00</t>
         </is>
       </c>
-      <c r="F28" s="23" t="inlineStr">
+      <c r="F28" s="27" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G28" s="23" t="inlineStr"/>
+      <c r="G28" s="27" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="21" t="inlineStr">
+      <c r="A29" s="25" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B29" s="21" t="inlineStr">
+      <c r="B29" s="25" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1481,30 +1493,30 @@
           <t>Manifestazioni di interesseInvaso Lentini - Interventi di ripristino delle pareti esterne in cls della Torre di presa Sud e della trave d’appoggio del</t>
         </is>
       </c>
-      <c r="D29" s="22" t="inlineStr">
+      <c r="D29" s="26" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/invaso-lentini-interventi-ripristino-pareti-esterne-cls-torre-presa-sud-trave-d-appoggio-cavalcavia-collegamento-alla-stessa-torre</t>
         </is>
       </c>
-      <c r="E29" s="21" t="inlineStr">
+      <c r="E29" s="25" t="inlineStr">
         <is>
           <t>19/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F29" s="21" t="inlineStr">
+      <c r="F29" s="25" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G29" s="21" t="inlineStr"/>
+      <c r="G29" s="25" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="23" t="inlineStr">
+      <c r="A30" s="27" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="B30" s="23" t="inlineStr">
+      <c r="B30" s="27" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1514,22 +1526,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURARistrutturazione e riconversione vigneti – campagna 2026-2027ApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D30" s="24" t="inlineStr">
+      <c r="D30" s="28" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/ristrutturazione-e-riconversione-vigneti-campagna-2026-2027/</t>
         </is>
       </c>
-      <c r="E30" s="23" t="inlineStr"/>
-      <c r="F30" s="23" t="inlineStr"/>
-      <c r="G30" s="23" t="inlineStr"/>
+      <c r="E30" s="27" t="inlineStr"/>
+      <c r="F30" s="27" t="inlineStr"/>
+      <c r="G30" s="27" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="21" t="inlineStr">
+      <c r="A31" s="25" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="B31" s="21" t="inlineStr">
+      <c r="B31" s="25" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1539,22 +1551,22 @@
           <t>Manifestazioni di interessePR FESR 2021/27 Azione 1.3.3 e del POC 2014/20 - Azione 1.3.1  - Avviso a manifestazione d’interesse eventi fieristici inte</t>
         </is>
       </c>
-      <c r="D31" s="22" t="inlineStr">
+      <c r="D31" s="26" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-d-interesse-eventi-fieristici-internazionali-marzo-dicembre-2026</t>
         </is>
       </c>
-      <c r="E31" s="21" t="inlineStr">
+      <c r="E31" s="25" t="inlineStr">
         <is>
           <t>30/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F31" s="21" t="inlineStr">
+      <c r="F31" s="25" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="G31" s="21" t="inlineStr"/>
+      <c r="G31" s="25" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="27" t="inlineStr">
@@ -1605,6 +1617,56 @@
       <c r="E33" s="25" t="inlineStr"/>
       <c r="F33" s="25" t="inlineStr"/>
       <c r="G33" s="25" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="31" t="inlineStr">
+        <is>
+          <t>19/03/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="31" t="inlineStr">
+        <is>
+          <t>Emilia-Romagna</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Bando 2026 per contributi dedicati alla manutenzione della rete dei percorsi escursionistici</t>
+        </is>
+      </c>
+      <c r="D34" s="32" t="inlineStr">
+        <is>
+          <t>https://ambiente.regione.emilia-romagna.it/it/parchi-natura2000/bandi/bando-2026-per-contributi-dedicati-alla-manutenzione-della-rete-dei-percorsi-escursionistici</t>
+        </is>
+      </c>
+      <c r="E34" s="31" t="inlineStr"/>
+      <c r="F34" s="31" t="inlineStr"/>
+      <c r="G34" s="31" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="29" t="inlineStr">
+        <is>
+          <t>19/03/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="29" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Programma regionale in favore delle tradizioni storiche, artistiche, religiose e popolari (2026) – manifestazioni d’interesseApertoBandi Regionali</t>
+        </is>
+      </c>
+      <c r="D35" s="30" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/programma-regionale-in-favore-delle-tradizioni-storiche-artistiche-religiose-e-popolari-2026-manifestazioni-dinteresse/</t>
+        </is>
+      </c>
+      <c r="E35" s="29" t="inlineStr"/>
+      <c r="F35" s="29" t="inlineStr"/>
+      <c r="G35" s="29" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1640,6 +1702,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId34"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1684,33 +1748,33 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="25" t="inlineStr">
+      <c r="A3" s="29" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" s="27" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1719,7 +1783,7 @@
         <v>13</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">

--- a/data/bandi_export.xlsx
+++ b/data/bandi_export.xlsx
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -152,6 +152,18 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -577,7 +589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -592,7 +604,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏛️  Nuovi Bandi — 19/03/2026 07:42</t>
+          <t>🏛️  Nuovi Bandi — 20/03/2026 07:41</t>
         </is>
       </c>
     </row>
@@ -637,47 +649,163 @@
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="29" t="inlineStr">
-        <is>
-          <t>Emilia-Romagna</t>
+      <c r="B3" s="33" t="inlineStr">
+        <is>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Bando 2026 per contributi dedicati alla manutenzione della rete dei percorsi escursionistici</t>
-        </is>
-      </c>
-      <c r="D3" s="30" t="inlineStr">
-        <is>
-          <t>https://ambiente.regione.emilia-romagna.it/it/parchi-natura2000/bandi/bando-2026-per-contributi-dedicati-alla-manutenzione-della-rete-dei-percorsi-escursionistici</t>
-        </is>
-      </c>
-      <c r="E3" s="29" t="inlineStr"/>
-      <c r="F3" s="29" t="inlineStr"/>
+          <t>LAVORO, FORMAZIONE E INCLUSIONEBuoni servizio per le persone non autosufficienti nel territorio del LazioProssima AperturaFSE / FSE+</t>
+        </is>
+      </c>
+      <c r="D3" s="34" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/buoni-servizio-per-le-persone-non-autosufficienti-nel-territorio-del-lazio/</t>
+        </is>
+      </c>
+      <c r="E3" s="33" t="inlineStr"/>
+      <c r="F3" s="33" t="inlineStr"/>
       <c r="G3" s="5" t="inlineStr"/>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="31" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>Programma regionale in favore delle tradizioni storiche, artistiche, religiose e popolari (2026) – manifestazioni d’interesseApertoBandi Regionali</t>
-        </is>
-      </c>
-      <c r="D4" s="32" t="inlineStr">
-        <is>
-          <t>https://www.lazioeuropa.it/bandi/programma-regionale-in-favore-delle-tradizioni-storiche-artistiche-religiose-e-popolari-2026-manifestazioni-dinteresse/</t>
-        </is>
-      </c>
-      <c r="E4" s="31" t="inlineStr"/>
-      <c r="F4" s="31" t="inlineStr"/>
+          <t>LAVORO, FORMAZIONE E INCLUSIONERimborso delle rette dei servizi educativi nel territorio del LazioProssima AperturaFSE / FSE+</t>
+        </is>
+      </c>
+      <c r="D4" s="36" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/rimborso-delle-rette-dei-servizi-educativi-nel-territorio-del-lazio/</t>
+        </is>
+      </c>
+      <c r="E4" s="35" t="inlineStr"/>
+      <c r="F4" s="35" t="inlineStr"/>
       <c r="G4" s="9" t="inlineStr"/>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="33" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Manifestazioni di interesseATTO DI INTERPELLO PER L’AFFIDAMENTO DELL’INCARICO DI COLLAUDO STATICO DELLE STRUTTURE - Diga di Pietrarossa (Progetto ex C</t>
+        </is>
+      </c>
+      <c r="D5" s="34" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/atto-interpello-l-affidamento-incarico-collaudo-statico-strutture-diga-pietrarossa-progetto-ex-casmez-303219</t>
+        </is>
+      </c>
+      <c r="E5" s="33" t="inlineStr">
+        <is>
+          <t>27/03/2026 - 23:59</t>
+        </is>
+      </c>
+      <c r="F5" s="33" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Manifestazioni di interesseAvviso alle Case  Editrici della Regione siciliana per la partecipazione al Salone del Libro di Torino, 14-18  maggio 2026.</t>
+        </is>
+      </c>
+      <c r="D6" s="36" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/manifestazione-d-interesse-partecipare-al-xxxviii-salone-libro-torino-14-al-18-maggio-2026-attraverso-l-esposizione-pubblicazioni-presso-stand-assessorato-beni</t>
+        </is>
+      </c>
+      <c r="E6" s="35" t="inlineStr">
+        <is>
+          <t>30/04/2026 - 23:59</t>
+        </is>
+      </c>
+      <c r="F6" s="35" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr"/>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="33" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manifestazioni di interessePR FESR SICILIA 2021/27 - NUOVO Avviso a manifestazione d’interesse per esperti valutatoriScade il:06/04/2026 - 23:59Leggi </t>
+        </is>
+      </c>
+      <c r="D7" s="34" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/pr-fesr-sicilia-202127-nuovo-avviso-manifestazione-d-interesse-esperti-valutatori</t>
+        </is>
+      </c>
+      <c r="E7" s="33" t="inlineStr">
+        <is>
+          <t>06/04/2026 - 23:59</t>
+        </is>
+      </c>
+      <c r="F7" s="33" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="35" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScadutoLeggi di più</t>
+        </is>
+      </c>
+      <c r="D8" s="36" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
+        </is>
+      </c>
+      <c r="E8" s="35" t="inlineStr"/>
+      <c r="F8" s="35" t="inlineStr"/>
+      <c r="G8" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -686,6 +814,10 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -697,7 +829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -747,12 +879,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="27" t="inlineStr">
+      <c r="A2" s="31" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B2" s="27" t="inlineStr">
+      <c r="B2" s="31" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -762,22 +894,22 @@
           <t>FLAG GALPA Costa E-R. Sostituzione del motore principale e dei motori secondari. Secondo bando</t>
         </is>
       </c>
-      <c r="D2" s="28" t="inlineStr">
+      <c r="D2" s="32" t="inlineStr">
         <is>
           <t>https://agricoltura.regione.emilia-romagna.it/feampa-2021-2027/bandi-galpa/2026/galpa-sostituzione-motori-secondo-bando</t>
         </is>
       </c>
-      <c r="E2" s="27" t="inlineStr"/>
-      <c r="F2" s="27" t="inlineStr"/>
-      <c r="G2" s="27" t="inlineStr"/>
+      <c r="E2" s="31" t="inlineStr"/>
+      <c r="F2" s="31" t="inlineStr"/>
+      <c r="G2" s="31" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="25" t="inlineStr">
+      <c r="A3" s="29" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B3" s="25" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -787,22 +919,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0PRE-SEED 3.0Prossima AperturaFESR</t>
         </is>
       </c>
-      <c r="D3" s="26" t="inlineStr">
+      <c r="D3" s="30" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/pre-seed-3-0/</t>
         </is>
       </c>
-      <c r="E3" s="25" t="inlineStr"/>
-      <c r="F3" s="25" t="inlineStr"/>
-      <c r="G3" s="25" t="inlineStr"/>
+      <c r="E3" s="29" t="inlineStr"/>
+      <c r="F3" s="29" t="inlineStr"/>
+      <c r="G3" s="29" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="27" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B4" s="27" t="inlineStr">
+      <c r="B4" s="31" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -812,22 +944,22 @@
           <t>ACCESSO AL CREDITO E ALLE GARANZIE PER LE IMPRESEContributo su finanziamenti alle imprese del Lazio erogati su provvista BEIProssima AperturaFESR</t>
         </is>
       </c>
-      <c r="D4" s="28" t="inlineStr">
+      <c r="D4" s="32" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-su-finanziamenti-alle-imprese-del-lazio-erogati-su-provvista-bei/</t>
         </is>
       </c>
-      <c r="E4" s="27" t="inlineStr"/>
-      <c r="F4" s="27" t="inlineStr"/>
-      <c r="G4" s="27" t="inlineStr"/>
+      <c r="E4" s="31" t="inlineStr"/>
+      <c r="F4" s="31" t="inlineStr"/>
+      <c r="G4" s="31" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -837,22 +969,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEIndividuazione degli enti iscritti al Registro unico nazionale del Terzo settoreApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D5" s="26" t="inlineStr">
+      <c r="D5" s="30" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/individuazione-degli-enti-iscritti-al-registro-unico-nazionale-del-terzo-settore/</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr"/>
-      <c r="F5" s="25" t="inlineStr"/>
-      <c r="G5" s="25" t="inlineStr"/>
+      <c r="E5" s="29" t="inlineStr"/>
+      <c r="F5" s="29" t="inlineStr"/>
+      <c r="G5" s="29" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="inlineStr">
+      <c r="A6" s="31" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B6" s="27" t="inlineStr">
+      <c r="B6" s="31" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -862,22 +994,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Technology Transfer LazioApertoFESR</t>
         </is>
       </c>
-      <c r="D6" s="28" t="inlineStr">
+      <c r="D6" s="32" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/technology-transfer-lazio/</t>
         </is>
       </c>
-      <c r="E6" s="27" t="inlineStr"/>
-      <c r="F6" s="27" t="inlineStr"/>
-      <c r="G6" s="27" t="inlineStr"/>
+      <c r="E6" s="31" t="inlineStr"/>
+      <c r="F6" s="31" t="inlineStr"/>
+      <c r="G6" s="31" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -887,22 +1019,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Percorso di tutoraggio per le impreseApertoFESR</t>
         </is>
       </c>
-      <c r="D7" s="26" t="inlineStr">
+      <c r="D7" s="30" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/percorso-di-tutoraggio-per-le-imprese/</t>
         </is>
       </c>
-      <c r="E7" s="25" t="inlineStr"/>
-      <c r="F7" s="25" t="inlineStr"/>
-      <c r="G7" s="25" t="inlineStr"/>
+      <c r="E7" s="29" t="inlineStr"/>
+      <c r="F7" s="29" t="inlineStr"/>
+      <c r="G7" s="29" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="inlineStr">
+      <c r="A8" s="31" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B8" s="27" t="inlineStr">
+      <c r="B8" s="31" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -912,22 +1044,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per partecipare a SMAU Parigi 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D8" s="28" t="inlineStr">
+      <c r="D8" s="32" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-partecipare-a-smau-parigi-2026/</t>
         </is>
       </c>
-      <c r="E8" s="27" t="inlineStr"/>
-      <c r="F8" s="27" t="inlineStr"/>
-      <c r="G8" s="27" t="inlineStr"/>
+      <c r="E8" s="31" t="inlineStr"/>
+      <c r="F8" s="31" t="inlineStr"/>
+      <c r="G8" s="31" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="29" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B9" s="25" t="inlineStr">
+      <c r="B9" s="29" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -937,22 +1069,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONERiconoscimento della funzione sociale ed educativa degli oratoriApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D9" s="26" t="inlineStr">
+      <c r="D9" s="30" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/riconoscimento-della-funzione-sociale-ed-educativa-degli-oratori/</t>
         </is>
       </c>
-      <c r="E9" s="25" t="inlineStr"/>
-      <c r="F9" s="25" t="inlineStr"/>
-      <c r="G9" s="25" t="inlineStr"/>
+      <c r="E9" s="29" t="inlineStr"/>
+      <c r="F9" s="29" t="inlineStr"/>
+      <c r="G9" s="29" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="inlineStr">
+      <c r="A10" s="31" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B10" s="27" t="inlineStr">
+      <c r="B10" s="31" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -962,22 +1094,22 @@
           <t>GovernanceIscrizione nell’elenco regionale degli idonei all’esercizio dell’attività di direttore dell’Istituto JemoloApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D10" s="28" t="inlineStr">
+      <c r="D10" s="32" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/iscrizione-nellelenco-regionale-degli-idonei-allesercizio-dellattivita-di-direttore-dellistituto-jemolo/</t>
         </is>
       </c>
-      <c r="E10" s="27" t="inlineStr"/>
-      <c r="F10" s="27" t="inlineStr"/>
-      <c r="G10" s="27" t="inlineStr"/>
+      <c r="E10" s="31" t="inlineStr"/>
+      <c r="F10" s="31" t="inlineStr"/>
+      <c r="G10" s="31" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="25" t="inlineStr">
+      <c r="A11" s="29" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -987,22 +1119,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEVoucher per lo sport – seconda annualitàApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D11" s="26" t="inlineStr">
+      <c r="D11" s="30" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/voucher-per-lo-sport-seconda-annualita/</t>
         </is>
       </c>
-      <c r="E11" s="25" t="inlineStr"/>
-      <c r="F11" s="25" t="inlineStr"/>
-      <c r="G11" s="25" t="inlineStr"/>
+      <c r="E11" s="29" t="inlineStr"/>
+      <c r="F11" s="29" t="inlineStr"/>
+      <c r="G11" s="29" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="27" t="inlineStr">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B12" s="27" t="inlineStr">
+      <c r="B12" s="31" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1012,22 +1144,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEBonus occupazionale SALGOApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D12" s="28" t="inlineStr">
+      <c r="D12" s="32" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/bonus-occupazionale-salgo/</t>
         </is>
       </c>
-      <c r="E12" s="27" t="inlineStr"/>
-      <c r="F12" s="27" t="inlineStr"/>
-      <c r="G12" s="27" t="inlineStr"/>
+      <c r="E12" s="31" t="inlineStr"/>
+      <c r="F12" s="31" t="inlineStr"/>
+      <c r="G12" s="31" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="25" t="inlineStr">
+      <c r="A13" s="29" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1037,22 +1169,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEContributo di Libertà per le donne che hanno subito violenzaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D13" s="26" t="inlineStr">
+      <c r="D13" s="30" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-di-liberta-per-le-donne-che-hanno-subito-violenza/</t>
         </is>
       </c>
-      <c r="E13" s="25" t="inlineStr"/>
-      <c r="F13" s="25" t="inlineStr"/>
-      <c r="G13" s="25" t="inlineStr"/>
+      <c r="E13" s="29" t="inlineStr"/>
+      <c r="F13" s="29" t="inlineStr"/>
+      <c r="G13" s="29" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="inlineStr">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B14" s="27" t="inlineStr">
+      <c r="B14" s="31" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1062,22 +1194,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURAInterventi straordinari di valorizzazione del patrimonio culturale del LazioApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D14" s="28" t="inlineStr">
+      <c r="D14" s="32" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/interventi-straordinari-di-valorizzazione-del-patrimonio-culturale-del-lazio/</t>
         </is>
       </c>
-      <c r="E14" s="27" t="inlineStr"/>
-      <c r="F14" s="27" t="inlineStr"/>
-      <c r="G14" s="27" t="inlineStr"/>
+      <c r="E14" s="31" t="inlineStr"/>
+      <c r="F14" s="31" t="inlineStr"/>
+      <c r="G14" s="31" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="25" t="inlineStr">
+      <c r="A15" s="29" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B15" s="25" t="inlineStr">
+      <c r="B15" s="29" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1087,30 +1219,30 @@
           <t>Bandi di garaBANDO ATTUAZIONE Ob. 1.1 Azione 1 codice 111102 _DIV - "SOSTEGNO ALLA DIVERSIFICAZIONE E NUOVE FORME DI REDDITO PER LA PICCOLA PESCA COST</t>
         </is>
       </c>
-      <c r="D15" s="26" t="inlineStr">
+      <c r="D15" s="30" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/bando-avviso-regia-ob-11-azione-1-codice-111102-div-sostegno-alla-diversificazione-nuove-forme-reddito-piccola-pesca-costiera</t>
         </is>
       </c>
-      <c r="E15" s="25" t="inlineStr">
+      <c r="E15" s="29" t="inlineStr">
         <is>
           <t>07/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F15" s="25" t="inlineStr">
+      <c r="F15" s="29" t="inlineStr">
         <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="G15" s="25" t="inlineStr"/>
+      <c r="G15" s="29" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="27" t="inlineStr">
+      <c r="A16" s="31" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B16" s="27" t="inlineStr">
+      <c r="B16" s="31" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1120,30 +1252,30 @@
           <t>Avvisi pubblici09 marzo 2026 - ST SIRACUSA - AVVISO PUBBLICO PER LA COSTITUZIONE DI ELENCHI DI OPERATORI ECONOMICI PER L’ACQUISIZIONE DI BENI E SERVIZ</t>
         </is>
       </c>
-      <c r="D16" s="28" t="inlineStr">
+      <c r="D16" s="32" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/09-marzo-2026-st-siracusa-avviso-pubblico-costituzione-elenchi-operatori-economici-l-acquisizione-beni-servizi</t>
         </is>
       </c>
-      <c r="E16" s="27" t="inlineStr">
+      <c r="E16" s="31" t="inlineStr">
         <is>
           <t>31/12/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F16" s="27" t="inlineStr">
+      <c r="F16" s="31" t="inlineStr">
         <is>
           <t>31/12/2026</t>
         </is>
       </c>
-      <c r="G16" s="27" t="inlineStr"/>
+      <c r="G16" s="31" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="25" t="inlineStr">
+      <c r="A17" s="29" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B17" s="25" t="inlineStr">
+      <c r="B17" s="29" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1153,30 +1285,30 @@
           <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScade il:19/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D17" s="26" t="inlineStr">
+      <c r="D17" s="30" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
         </is>
       </c>
-      <c r="E17" s="25" t="inlineStr">
+      <c r="E17" s="29" t="inlineStr">
         <is>
           <t>19/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F17" s="25" t="inlineStr">
+      <c r="F17" s="29" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G17" s="25" t="inlineStr"/>
+      <c r="G17" s="29" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="27" t="inlineStr">
+      <c r="A18" s="31" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B18" s="27" t="inlineStr">
+      <c r="B18" s="31" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1186,22 +1318,22 @@
           <t>Manifestazioni di interesseAvviso Manifestazione Interesse DISTRIBUTORI AUTOMATICI di bevande e snackScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D18" s="28" t="inlineStr">
+      <c r="D18" s="32" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-distributori-automatici-bevande-snack</t>
         </is>
       </c>
-      <c r="E18" s="27" t="inlineStr"/>
-      <c r="F18" s="27" t="inlineStr"/>
-      <c r="G18" s="27" t="inlineStr"/>
+      <c r="E18" s="31" t="inlineStr"/>
+      <c r="F18" s="31" t="inlineStr"/>
+      <c r="G18" s="31" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="25" t="inlineStr">
+      <c r="A19" s="29" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B19" s="25" t="inlineStr">
+      <c r="B19" s="29" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1211,30 +1343,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D19" s="26" t="inlineStr">
+      <c r="D19" s="30" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo</t>
         </is>
       </c>
-      <c r="E19" s="25" t="inlineStr">
+      <c r="E19" s="29" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F19" s="25" t="inlineStr">
+      <c r="F19" s="29" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G19" s="25" t="inlineStr"/>
+      <c r="G19" s="29" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="27" t="inlineStr">
+      <c r="A20" s="31" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B20" s="27" t="inlineStr">
+      <c r="B20" s="31" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1244,30 +1376,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D20" s="28" t="inlineStr">
+      <c r="D20" s="32" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo-0</t>
         </is>
       </c>
-      <c r="E20" s="27" t="inlineStr">
+      <c r="E20" s="31" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F20" s="27" t="inlineStr">
+      <c r="F20" s="31" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G20" s="27" t="inlineStr"/>
+      <c r="G20" s="31" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="25" t="inlineStr">
+      <c r="A21" s="29" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B21" s="25" t="inlineStr">
+      <c r="B21" s="29" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1277,22 +1409,22 @@
           <t>Manifestazioni di interesseST SIRACUSA - AVVISO DI MANIFESTAZIONE DI INTERESSE - Fornitura applicativo extracontabile per la gestione progetti, ecc. e</t>
         </is>
       </c>
-      <c r="D21" s="26" t="inlineStr">
+      <c r="D21" s="30" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-siracusa-avviso-manifestazione-interesse-fornitura-applicativo-extracontabile-gestione-progetti-ecc-applicativo-gestione-ed-elaborazione-informatizzata-paghe</t>
         </is>
       </c>
-      <c r="E21" s="25" t="inlineStr"/>
-      <c r="F21" s="25" t="inlineStr"/>
-      <c r="G21" s="25" t="inlineStr"/>
+      <c r="E21" s="29" t="inlineStr"/>
+      <c r="F21" s="29" t="inlineStr"/>
+      <c r="G21" s="29" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="27" t="inlineStr">
+      <c r="A22" s="31" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B22" s="27" t="inlineStr">
+      <c r="B22" s="31" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1302,30 +1434,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile sito nel Comune di Capo D'Orlando, Via Trazzera MarinaScade il:25/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D22" s="28" t="inlineStr">
+      <c r="D22" s="32" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-sito-nel-comune-capo-d-orlando-trazzera-marina</t>
         </is>
       </c>
-      <c r="E22" s="27" t="inlineStr">
+      <c r="E22" s="31" t="inlineStr">
         <is>
           <t>25/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F22" s="27" t="inlineStr">
+      <c r="F22" s="31" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="G22" s="27" t="inlineStr"/>
+      <c r="G22" s="31" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="25" t="inlineStr">
+      <c r="A23" s="29" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B23" s="25" t="inlineStr">
+      <c r="B23" s="29" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1335,22 +1467,22 @@
           <t xml:space="preserve">Avvisi pubbliciST CATANIA - Programma Regionale FESR Sicilia 2021-2027 - Azione 2.4.4 - “Interventi per la riduzione del rischio incendi” - AVVISO DI </t>
         </is>
       </c>
-      <c r="D23" s="26" t="inlineStr">
+      <c r="D23" s="30" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-catania-programma-regionale-fesr-sicilia-2021-2027-azione-244-interventi-riduzione-rischio-incendi-avviso-indagine-mercato</t>
         </is>
       </c>
-      <c r="E23" s="25" t="inlineStr"/>
-      <c r="F23" s="25" t="inlineStr"/>
-      <c r="G23" s="25" t="inlineStr"/>
+      <c r="E23" s="29" t="inlineStr"/>
+      <c r="F23" s="29" t="inlineStr"/>
+      <c r="G23" s="29" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="27" t="inlineStr">
+      <c r="A24" s="31" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B24" s="27" t="inlineStr">
+      <c r="B24" s="31" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1360,22 +1492,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per ROMICS – Primavera 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D24" s="28" t="inlineStr">
+      <c r="D24" s="32" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-romics-primavera-2026/</t>
         </is>
       </c>
-      <c r="E24" s="27" t="inlineStr"/>
-      <c r="F24" s="27" t="inlineStr"/>
-      <c r="G24" s="27" t="inlineStr"/>
+      <c r="E24" s="31" t="inlineStr"/>
+      <c r="F24" s="31" t="inlineStr"/>
+      <c r="G24" s="31" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="25" t="inlineStr">
+      <c r="A25" s="29" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B25" s="25" t="inlineStr">
+      <c r="B25" s="29" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1385,22 +1517,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Cinema International 2026 – I edizioneApertoFESR</t>
         </is>
       </c>
-      <c r="D25" s="26" t="inlineStr">
+      <c r="D25" s="30" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lazio-cinema-international-2026-i-edizione/</t>
         </is>
       </c>
-      <c r="E25" s="25" t="inlineStr"/>
-      <c r="F25" s="25" t="inlineStr"/>
-      <c r="G25" s="25" t="inlineStr"/>
+      <c r="E25" s="29" t="inlineStr"/>
+      <c r="F25" s="29" t="inlineStr"/>
+      <c r="G25" s="29" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="27" t="inlineStr">
+      <c r="A26" s="31" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B26" s="27" t="inlineStr">
+      <c r="B26" s="31" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1410,22 +1542,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEManifestazioni di interesse alla costituzione di due nuove Fondazioni I.T.S. AcademyApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D26" s="28" t="inlineStr">
+      <c r="D26" s="32" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazioni-di-interesse-alla-costituzione-di-due-nuove-fondazioni-i-t-s-academy/</t>
         </is>
       </c>
-      <c r="E26" s="27" t="inlineStr"/>
-      <c r="F26" s="27" t="inlineStr"/>
-      <c r="G26" s="27" t="inlineStr"/>
+      <c r="E26" s="31" t="inlineStr"/>
+      <c r="F26" s="31" t="inlineStr"/>
+      <c r="G26" s="31" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="25" t="inlineStr">
+      <c r="A27" s="29" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B27" s="25" t="inlineStr">
+      <c r="B27" s="29" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1435,22 +1567,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURAContributi per sostenere la ripresa del settore della pescaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D27" s="26" t="inlineStr">
+      <c r="D27" s="30" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributi-per-sostenere-la-ripresa-del-settore-della-pesca/</t>
         </is>
       </c>
-      <c r="E27" s="25" t="inlineStr"/>
-      <c r="F27" s="25" t="inlineStr"/>
-      <c r="G27" s="25" t="inlineStr"/>
+      <c r="E27" s="29" t="inlineStr"/>
+      <c r="F27" s="29" t="inlineStr"/>
+      <c r="G27" s="29" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="27" t="inlineStr">
+      <c r="A28" s="31" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B28" s="27" t="inlineStr">
+      <c r="B28" s="31" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1460,30 +1592,30 @@
           <t>Manifestazioni di interesseAVVISO - Manifestazione Interesse “Storytelling aziendale” Expo Wild Natura - Caccia - Pesca. Misterbianco (CT), 10-12 apri</t>
         </is>
       </c>
-      <c r="D28" s="28" t="inlineStr">
+      <c r="D28" s="32" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-storytelling-aziendale-expo-wild-natura-caccia-pesca-misterbianco-ct-10-12-aprile-2026</t>
         </is>
       </c>
-      <c r="E28" s="27" t="inlineStr">
+      <c r="E28" s="31" t="inlineStr">
         <is>
           <t>30/03/2026 - 13:00</t>
         </is>
       </c>
-      <c r="F28" s="27" t="inlineStr">
+      <c r="F28" s="31" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G28" s="27" t="inlineStr"/>
+      <c r="G28" s="31" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="25" t="inlineStr">
+      <c r="A29" s="29" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B29" s="25" t="inlineStr">
+      <c r="B29" s="29" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1493,30 +1625,30 @@
           <t>Manifestazioni di interesseInvaso Lentini - Interventi di ripristino delle pareti esterne in cls della Torre di presa Sud e della trave d’appoggio del</t>
         </is>
       </c>
-      <c r="D29" s="26" t="inlineStr">
+      <c r="D29" s="30" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/invaso-lentini-interventi-ripristino-pareti-esterne-cls-torre-presa-sud-trave-d-appoggio-cavalcavia-collegamento-alla-stessa-torre</t>
         </is>
       </c>
-      <c r="E29" s="25" t="inlineStr">
+      <c r="E29" s="29" t="inlineStr">
         <is>
           <t>19/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F29" s="25" t="inlineStr">
+      <c r="F29" s="29" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G29" s="25" t="inlineStr"/>
+      <c r="G29" s="29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="27" t="inlineStr">
+      <c r="A30" s="31" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="B30" s="27" t="inlineStr">
+      <c r="B30" s="31" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1526,22 +1658,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURARistrutturazione e riconversione vigneti – campagna 2026-2027ApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D30" s="28" t="inlineStr">
+      <c r="D30" s="32" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/ristrutturazione-e-riconversione-vigneti-campagna-2026-2027/</t>
         </is>
       </c>
-      <c r="E30" s="27" t="inlineStr"/>
-      <c r="F30" s="27" t="inlineStr"/>
-      <c r="G30" s="27" t="inlineStr"/>
+      <c r="E30" s="31" t="inlineStr"/>
+      <c r="F30" s="31" t="inlineStr"/>
+      <c r="G30" s="31" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="25" t="inlineStr">
+      <c r="A31" s="29" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="B31" s="25" t="inlineStr">
+      <c r="B31" s="29" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1551,30 +1683,30 @@
           <t>Manifestazioni di interessePR FESR 2021/27 Azione 1.3.3 e del POC 2014/20 - Azione 1.3.1  - Avviso a manifestazione d’interesse eventi fieristici inte</t>
         </is>
       </c>
-      <c r="D31" s="26" t="inlineStr">
+      <c r="D31" s="30" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-d-interesse-eventi-fieristici-internazionali-marzo-dicembre-2026</t>
         </is>
       </c>
-      <c r="E31" s="25" t="inlineStr">
+      <c r="E31" s="29" t="inlineStr">
         <is>
           <t>30/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F31" s="25" t="inlineStr">
+      <c r="F31" s="29" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="G31" s="25" t="inlineStr"/>
+      <c r="G31" s="29" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="27" t="inlineStr">
+      <c r="A32" s="31" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="B32" s="27" t="inlineStr">
+      <c r="B32" s="31" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1584,22 +1716,22 @@
           <t>INTERNAZIONALIZZAZIONEL’Ecosistema dell’Innovazione a INNOVIT – Focus S3ApertoFESR</t>
         </is>
       </c>
-      <c r="D32" s="28" t="inlineStr">
+      <c r="D32" s="32" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lecosistema-dellinnovazione-a-innovit-focus-s3/</t>
         </is>
       </c>
-      <c r="E32" s="27" t="inlineStr"/>
-      <c r="F32" s="27" t="inlineStr"/>
-      <c r="G32" s="27" t="inlineStr"/>
+      <c r="E32" s="31" t="inlineStr"/>
+      <c r="F32" s="31" t="inlineStr"/>
+      <c r="G32" s="31" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="25" t="inlineStr">
+      <c r="A33" s="29" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="B33" s="25" t="inlineStr">
+      <c r="B33" s="29" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1609,14 +1741,14 @@
           <t>Manifestazioni di interessePR FESR SICILIA 2021/27 - NUOVO Avviso a manifestazione d’interesse per esperti valutatoriScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D33" s="26" t="inlineStr">
+      <c r="D33" s="30" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/pr-fesr-sicilia-202127-nuovo-avviso-manifestazione-d-interesse-esperti-valutatori</t>
         </is>
       </c>
-      <c r="E33" s="25" t="inlineStr"/>
-      <c r="F33" s="25" t="inlineStr"/>
-      <c r="G33" s="25" t="inlineStr"/>
+      <c r="E33" s="29" t="inlineStr"/>
+      <c r="F33" s="29" t="inlineStr"/>
+      <c r="G33" s="29" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="31" t="inlineStr">
@@ -1667,6 +1799,180 @@
       <c r="E35" s="29" t="inlineStr"/>
       <c r="F35" s="29" t="inlineStr"/>
       <c r="G35" s="29" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="35" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="35" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>LAVORO, FORMAZIONE E INCLUSIONEBuoni servizio per le persone non autosufficienti nel territorio del LazioProssima AperturaFSE / FSE+</t>
+        </is>
+      </c>
+      <c r="D36" s="36" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/buoni-servizio-per-le-persone-non-autosufficienti-nel-territorio-del-lazio/</t>
+        </is>
+      </c>
+      <c r="E36" s="35" t="inlineStr"/>
+      <c r="F36" s="35" t="inlineStr"/>
+      <c r="G36" s="35" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="33" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="33" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>LAVORO, FORMAZIONE E INCLUSIONERimborso delle rette dei servizi educativi nel territorio del LazioProssima AperturaFSE / FSE+</t>
+        </is>
+      </c>
+      <c r="D37" s="34" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/rimborso-delle-rette-dei-servizi-educativi-nel-territorio-del-lazio/</t>
+        </is>
+      </c>
+      <c r="E37" s="33" t="inlineStr"/>
+      <c r="F37" s="33" t="inlineStr"/>
+      <c r="G37" s="33" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="35" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="35" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>Manifestazioni di interesseATTO DI INTERPELLO PER L’AFFIDAMENTO DELL’INCARICO DI COLLAUDO STATICO DELLE STRUTTURE - Diga di Pietrarossa (Progetto ex C</t>
+        </is>
+      </c>
+      <c r="D38" s="36" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/atto-interpello-l-affidamento-incarico-collaudo-statico-strutture-diga-pietrarossa-progetto-ex-casmez-303219</t>
+        </is>
+      </c>
+      <c r="E38" s="35" t="inlineStr">
+        <is>
+          <t>27/03/2026 - 23:59</t>
+        </is>
+      </c>
+      <c r="F38" s="35" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G38" s="35" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="33" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="33" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Manifestazioni di interesseAvviso alle Case  Editrici della Regione siciliana per la partecipazione al Salone del Libro di Torino, 14-18  maggio 2026.</t>
+        </is>
+      </c>
+      <c r="D39" s="34" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/manifestazione-d-interesse-partecipare-al-xxxviii-salone-libro-torino-14-al-18-maggio-2026-attraverso-l-esposizione-pubblicazioni-presso-stand-assessorato-beni</t>
+        </is>
+      </c>
+      <c r="E39" s="33" t="inlineStr">
+        <is>
+          <t>30/04/2026 - 23:59</t>
+        </is>
+      </c>
+      <c r="F39" s="33" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="G39" s="33" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="35" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="35" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manifestazioni di interessePR FESR SICILIA 2021/27 - NUOVO Avviso a manifestazione d’interesse per esperti valutatoriScade il:06/04/2026 - 23:59Leggi </t>
+        </is>
+      </c>
+      <c r="D40" s="36" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/pr-fesr-sicilia-202127-nuovo-avviso-manifestazione-d-interesse-esperti-valutatori</t>
+        </is>
+      </c>
+      <c r="E40" s="35" t="inlineStr">
+        <is>
+          <t>06/04/2026 - 23:59</t>
+        </is>
+      </c>
+      <c r="F40" s="35" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="G40" s="35" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="33" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="33" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScadutoLeggi di più</t>
+        </is>
+      </c>
+      <c r="D41" s="34" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
+        </is>
+      </c>
+      <c r="E41" s="33" t="inlineStr"/>
+      <c r="F41" s="33" t="inlineStr"/>
+      <c r="G41" s="33" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1704,6 +2010,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1748,7 +2060,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="29" t="inlineStr">
+      <c r="A3" s="33" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -1757,33 +2069,33 @@
         <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="31" t="inlineStr">
+      <c r="A4" s="35" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="33" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">

--- a/data/bandi_export.xlsx
+++ b/data/bandi_export.xlsx
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -152,6 +152,18 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -589,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -604,7 +616,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏛️  Nuovi Bandi — 20/03/2026 07:41</t>
+          <t>🏛️  Nuovi Bandi — 24/03/2026 07:50</t>
         </is>
       </c>
     </row>
@@ -649,163 +661,55 @@
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="33" t="inlineStr">
-        <is>
-          <t>Lazio</t>
+      <c r="B3" s="37" t="inlineStr">
+        <is>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>LAVORO, FORMAZIONE E INCLUSIONEBuoni servizio per le persone non autosufficienti nel territorio del LazioProssima AperturaFSE / FSE+</t>
-        </is>
-      </c>
-      <c r="D3" s="34" t="inlineStr">
-        <is>
-          <t>https://www.lazioeuropa.it/bandi/buoni-servizio-per-le-persone-non-autosufficienti-nel-territorio-del-lazio/</t>
-        </is>
-      </c>
-      <c r="E3" s="33" t="inlineStr"/>
-      <c r="F3" s="33" t="inlineStr"/>
+          <t>GAL del Ducato - Promozione di fiere agroalimentari e delle filiere del cibo – Bando per Enti pubblici (DU AS 05B)</t>
+        </is>
+      </c>
+      <c r="D3" s="38" t="inlineStr">
+        <is>
+          <t>https://agricoltura.regione.emilia-romagna.it/sviluppo-rurale-23-27/opportunita/bandi-gal/2026/du_as05b-promozione-di-fiere-agroalimentari-e-delle-filiere-del-cibo-bando-per-enti-pubblici</t>
+        </is>
+      </c>
+      <c r="E3" s="37" t="inlineStr"/>
+      <c r="F3" s="37" t="inlineStr"/>
       <c r="G3" s="5" t="inlineStr"/>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="35" t="inlineStr">
-        <is>
-          <t>Lazio</t>
+      <c r="B4" s="39" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>LAVORO, FORMAZIONE E INCLUSIONERimborso delle rette dei servizi educativi nel territorio del LazioProssima AperturaFSE / FSE+</t>
-        </is>
-      </c>
-      <c r="D4" s="36" t="inlineStr">
-        <is>
-          <t>https://www.lazioeuropa.it/bandi/rimborso-delle-rette-dei-servizi-educativi-nel-territorio-del-lazio/</t>
-        </is>
-      </c>
-      <c r="E4" s="35" t="inlineStr"/>
-      <c r="F4" s="35" t="inlineStr"/>
+          <t>Manifestazioni di interesseAVVISO PUBBLICO PER MANIFESTAZIONE DI INTERESSE FINALIZZATA ALL'ASSEGNAZIONE DI SPAZI ESPOSITIVI (CORNER GRATUITI) ALL'INTE</t>
+        </is>
+      </c>
+      <c r="D4" s="40" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-manifestazione-interesse-finalizzata-all-assegnazione-spazi-espositivi-corner-gratuiti-all-interno-stand-istituzionale-dsrt-manifestazione</t>
+        </is>
+      </c>
+      <c r="E4" s="39" t="inlineStr">
+        <is>
+          <t>30/03/2026 - 13:00</t>
+        </is>
+      </c>
+      <c r="F4" s="39" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
       <c r="G4" s="9" t="inlineStr"/>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" s="33" t="inlineStr">
-        <is>
-          <t>Sicilia</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Manifestazioni di interesseATTO DI INTERPELLO PER L’AFFIDAMENTO DELL’INCARICO DI COLLAUDO STATICO DELLE STRUTTURE - Diga di Pietrarossa (Progetto ex C</t>
-        </is>
-      </c>
-      <c r="D5" s="34" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/atto-interpello-l-affidamento-incarico-collaudo-statico-strutture-diga-pietrarossa-progetto-ex-casmez-303219</t>
-        </is>
-      </c>
-      <c r="E5" s="33" t="inlineStr">
-        <is>
-          <t>27/03/2026 - 23:59</t>
-        </is>
-      </c>
-      <c r="F5" s="33" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="35" t="inlineStr">
-        <is>
-          <t>Sicilia</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>Manifestazioni di interesseAvviso alle Case  Editrici della Regione siciliana per la partecipazione al Salone del Libro di Torino, 14-18  maggio 2026.</t>
-        </is>
-      </c>
-      <c r="D6" s="36" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/manifestazione-d-interesse-partecipare-al-xxxviii-salone-libro-torino-14-al-18-maggio-2026-attraverso-l-esposizione-pubblicazioni-presso-stand-assessorato-beni</t>
-        </is>
-      </c>
-      <c r="E6" s="35" t="inlineStr">
-        <is>
-          <t>30/04/2026 - 23:59</t>
-        </is>
-      </c>
-      <c r="F6" s="35" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr"/>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" s="33" t="inlineStr">
-        <is>
-          <t>Sicilia</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manifestazioni di interessePR FESR SICILIA 2021/27 - NUOVO Avviso a manifestazione d’interesse per esperti valutatoriScade il:06/04/2026 - 23:59Leggi </t>
-        </is>
-      </c>
-      <c r="D7" s="34" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/pr-fesr-sicilia-202127-nuovo-avviso-manifestazione-d-interesse-esperti-valutatori</t>
-        </is>
-      </c>
-      <c r="E7" s="33" t="inlineStr">
-        <is>
-          <t>06/04/2026 - 23:59</t>
-        </is>
-      </c>
-      <c r="F7" s="33" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" s="35" t="inlineStr">
-        <is>
-          <t>Sicilia</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScadutoLeggi di più</t>
-        </is>
-      </c>
-      <c r="D8" s="36" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
-        </is>
-      </c>
-      <c r="E8" s="35" t="inlineStr"/>
-      <c r="F8" s="35" t="inlineStr"/>
-      <c r="G8" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -814,10 +718,6 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -829,7 +729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -879,12 +779,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="31" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B2" s="31" t="inlineStr">
+      <c r="A2" s="35" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="35" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -894,22 +794,22 @@
           <t>FLAG GALPA Costa E-R. Sostituzione del motore principale e dei motori secondari. Secondo bando</t>
         </is>
       </c>
-      <c r="D2" s="32" t="inlineStr">
+      <c r="D2" s="36" t="inlineStr">
         <is>
           <t>https://agricoltura.regione.emilia-romagna.it/feampa-2021-2027/bandi-galpa/2026/galpa-sostituzione-motori-secondo-bando</t>
         </is>
       </c>
-      <c r="E2" s="31" t="inlineStr"/>
-      <c r="F2" s="31" t="inlineStr"/>
-      <c r="G2" s="31" t="inlineStr"/>
+      <c r="E2" s="35" t="inlineStr"/>
+      <c r="F2" s="35" t="inlineStr"/>
+      <c r="G2" s="35" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="29" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="29" t="inlineStr">
+      <c r="A3" s="33" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="33" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -919,22 +819,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0PRE-SEED 3.0Prossima AperturaFESR</t>
         </is>
       </c>
-      <c r="D3" s="30" t="inlineStr">
+      <c r="D3" s="34" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/pre-seed-3-0/</t>
         </is>
       </c>
-      <c r="E3" s="29" t="inlineStr"/>
-      <c r="F3" s="29" t="inlineStr"/>
-      <c r="G3" s="29" t="inlineStr"/>
+      <c r="E3" s="33" t="inlineStr"/>
+      <c r="F3" s="33" t="inlineStr"/>
+      <c r="G3" s="33" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="31" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="31" t="inlineStr">
+      <c r="A4" s="35" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -944,22 +844,22 @@
           <t>ACCESSO AL CREDITO E ALLE GARANZIE PER LE IMPRESEContributo su finanziamenti alle imprese del Lazio erogati su provvista BEIProssima AperturaFESR</t>
         </is>
       </c>
-      <c r="D4" s="32" t="inlineStr">
+      <c r="D4" s="36" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-su-finanziamenti-alle-imprese-del-lazio-erogati-su-provvista-bei/</t>
         </is>
       </c>
-      <c r="E4" s="31" t="inlineStr"/>
-      <c r="F4" s="31" t="inlineStr"/>
-      <c r="G4" s="31" t="inlineStr"/>
+      <c r="E4" s="35" t="inlineStr"/>
+      <c r="F4" s="35" t="inlineStr"/>
+      <c r="G4" s="35" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="29" t="inlineStr">
+      <c r="A5" s="33" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="33" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -969,22 +869,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEIndividuazione degli enti iscritti al Registro unico nazionale del Terzo settoreApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D5" s="30" t="inlineStr">
+      <c r="D5" s="34" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/individuazione-degli-enti-iscritti-al-registro-unico-nazionale-del-terzo-settore/</t>
         </is>
       </c>
-      <c r="E5" s="29" t="inlineStr"/>
-      <c r="F5" s="29" t="inlineStr"/>
-      <c r="G5" s="29" t="inlineStr"/>
+      <c r="E5" s="33" t="inlineStr"/>
+      <c r="F5" s="33" t="inlineStr"/>
+      <c r="G5" s="33" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="31" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="A6" s="35" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -994,22 +894,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Technology Transfer LazioApertoFESR</t>
         </is>
       </c>
-      <c r="D6" s="32" t="inlineStr">
+      <c r="D6" s="36" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/technology-transfer-lazio/</t>
         </is>
       </c>
-      <c r="E6" s="31" t="inlineStr"/>
-      <c r="F6" s="31" t="inlineStr"/>
-      <c r="G6" s="31" t="inlineStr"/>
+      <c r="E6" s="35" t="inlineStr"/>
+      <c r="F6" s="35" t="inlineStr"/>
+      <c r="G6" s="35" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="29" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="29" t="inlineStr">
+      <c r="A7" s="33" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1019,22 +919,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Percorso di tutoraggio per le impreseApertoFESR</t>
         </is>
       </c>
-      <c r="D7" s="30" t="inlineStr">
+      <c r="D7" s="34" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/percorso-di-tutoraggio-per-le-imprese/</t>
         </is>
       </c>
-      <c r="E7" s="29" t="inlineStr"/>
-      <c r="F7" s="29" t="inlineStr"/>
-      <c r="G7" s="29" t="inlineStr"/>
+      <c r="E7" s="33" t="inlineStr"/>
+      <c r="F7" s="33" t="inlineStr"/>
+      <c r="G7" s="33" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="31" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="31" t="inlineStr">
+      <c r="A8" s="35" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="35" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1044,22 +944,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per partecipare a SMAU Parigi 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D8" s="32" t="inlineStr">
+      <c r="D8" s="36" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-partecipare-a-smau-parigi-2026/</t>
         </is>
       </c>
-      <c r="E8" s="31" t="inlineStr"/>
-      <c r="F8" s="31" t="inlineStr"/>
-      <c r="G8" s="31" t="inlineStr"/>
+      <c r="E8" s="35" t="inlineStr"/>
+      <c r="F8" s="35" t="inlineStr"/>
+      <c r="G8" s="35" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="29" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="29" t="inlineStr">
+      <c r="A9" s="33" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="33" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1069,22 +969,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONERiconoscimento della funzione sociale ed educativa degli oratoriApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D9" s="30" t="inlineStr">
+      <c r="D9" s="34" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/riconoscimento-della-funzione-sociale-ed-educativa-degli-oratori/</t>
         </is>
       </c>
-      <c r="E9" s="29" t="inlineStr"/>
-      <c r="F9" s="29" t="inlineStr"/>
-      <c r="G9" s="29" t="inlineStr"/>
+      <c r="E9" s="33" t="inlineStr"/>
+      <c r="F9" s="33" t="inlineStr"/>
+      <c r="G9" s="33" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="31" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="31" t="inlineStr">
+      <c r="A10" s="35" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="35" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1094,22 +994,22 @@
           <t>GovernanceIscrizione nell’elenco regionale degli idonei all’esercizio dell’attività di direttore dell’Istituto JemoloApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D10" s="32" t="inlineStr">
+      <c r="D10" s="36" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/iscrizione-nellelenco-regionale-degli-idonei-allesercizio-dellattivita-di-direttore-dellistituto-jemolo/</t>
         </is>
       </c>
-      <c r="E10" s="31" t="inlineStr"/>
-      <c r="F10" s="31" t="inlineStr"/>
-      <c r="G10" s="31" t="inlineStr"/>
+      <c r="E10" s="35" t="inlineStr"/>
+      <c r="F10" s="35" t="inlineStr"/>
+      <c r="G10" s="35" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="29" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="29" t="inlineStr">
+      <c r="A11" s="33" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1119,22 +1019,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEVoucher per lo sport – seconda annualitàApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D11" s="30" t="inlineStr">
+      <c r="D11" s="34" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/voucher-per-lo-sport-seconda-annualita/</t>
         </is>
       </c>
-      <c r="E11" s="29" t="inlineStr"/>
-      <c r="F11" s="29" t="inlineStr"/>
-      <c r="G11" s="29" t="inlineStr"/>
+      <c r="E11" s="33" t="inlineStr"/>
+      <c r="F11" s="33" t="inlineStr"/>
+      <c r="G11" s="33" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="31" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="31" t="inlineStr">
+      <c r="A12" s="35" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="35" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1144,22 +1044,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEBonus occupazionale SALGOApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D12" s="32" t="inlineStr">
+      <c r="D12" s="36" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/bonus-occupazionale-salgo/</t>
         </is>
       </c>
-      <c r="E12" s="31" t="inlineStr"/>
-      <c r="F12" s="31" t="inlineStr"/>
-      <c r="G12" s="31" t="inlineStr"/>
+      <c r="E12" s="35" t="inlineStr"/>
+      <c r="F12" s="35" t="inlineStr"/>
+      <c r="G12" s="35" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="29" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="29" t="inlineStr">
+      <c r="A13" s="33" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="33" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1169,22 +1069,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEContributo di Libertà per le donne che hanno subito violenzaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D13" s="30" t="inlineStr">
+      <c r="D13" s="34" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-di-liberta-per-le-donne-che-hanno-subito-violenza/</t>
         </is>
       </c>
-      <c r="E13" s="29" t="inlineStr"/>
-      <c r="F13" s="29" t="inlineStr"/>
-      <c r="G13" s="29" t="inlineStr"/>
+      <c r="E13" s="33" t="inlineStr"/>
+      <c r="F13" s="33" t="inlineStr"/>
+      <c r="G13" s="33" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="31" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="31" t="inlineStr">
+      <c r="A14" s="35" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1194,22 +1094,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURAInterventi straordinari di valorizzazione del patrimonio culturale del LazioApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D14" s="32" t="inlineStr">
+      <c r="D14" s="36" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/interventi-straordinari-di-valorizzazione-del-patrimonio-culturale-del-lazio/</t>
         </is>
       </c>
-      <c r="E14" s="31" t="inlineStr"/>
-      <c r="F14" s="31" t="inlineStr"/>
-      <c r="G14" s="31" t="inlineStr"/>
+      <c r="E14" s="35" t="inlineStr"/>
+      <c r="F14" s="35" t="inlineStr"/>
+      <c r="G14" s="35" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="29" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="29" t="inlineStr">
+      <c r="A15" s="33" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="33" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1219,30 +1119,30 @@
           <t>Bandi di garaBANDO ATTUAZIONE Ob. 1.1 Azione 1 codice 111102 _DIV - "SOSTEGNO ALLA DIVERSIFICAZIONE E NUOVE FORME DI REDDITO PER LA PICCOLA PESCA COST</t>
         </is>
       </c>
-      <c r="D15" s="30" t="inlineStr">
+      <c r="D15" s="34" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/bando-avviso-regia-ob-11-azione-1-codice-111102-div-sostegno-alla-diversificazione-nuove-forme-reddito-piccola-pesca-costiera</t>
         </is>
       </c>
-      <c r="E15" s="29" t="inlineStr">
+      <c r="E15" s="33" t="inlineStr">
         <is>
           <t>07/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F15" s="29" t="inlineStr">
+      <c r="F15" s="33" t="inlineStr">
         <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="G15" s="29" t="inlineStr"/>
+      <c r="G15" s="33" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="31" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="31" t="inlineStr">
+      <c r="A16" s="35" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="35" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1252,30 +1152,30 @@
           <t>Avvisi pubblici09 marzo 2026 - ST SIRACUSA - AVVISO PUBBLICO PER LA COSTITUZIONE DI ELENCHI DI OPERATORI ECONOMICI PER L’ACQUISIZIONE DI BENI E SERVIZ</t>
         </is>
       </c>
-      <c r="D16" s="32" t="inlineStr">
+      <c r="D16" s="36" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/09-marzo-2026-st-siracusa-avviso-pubblico-costituzione-elenchi-operatori-economici-l-acquisizione-beni-servizi</t>
         </is>
       </c>
-      <c r="E16" s="31" t="inlineStr">
+      <c r="E16" s="35" t="inlineStr">
         <is>
           <t>31/12/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F16" s="31" t="inlineStr">
+      <c r="F16" s="35" t="inlineStr">
         <is>
           <t>31/12/2026</t>
         </is>
       </c>
-      <c r="G16" s="31" t="inlineStr"/>
+      <c r="G16" s="35" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="29" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="29" t="inlineStr">
+      <c r="A17" s="33" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="33" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1285,30 +1185,30 @@
           <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScade il:19/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D17" s="30" t="inlineStr">
+      <c r="D17" s="34" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
         </is>
       </c>
-      <c r="E17" s="29" t="inlineStr">
+      <c r="E17" s="33" t="inlineStr">
         <is>
           <t>19/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F17" s="29" t="inlineStr">
+      <c r="F17" s="33" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G17" s="29" t="inlineStr"/>
+      <c r="G17" s="33" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="31" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="31" t="inlineStr">
+      <c r="A18" s="35" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="35" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1318,22 +1218,22 @@
           <t>Manifestazioni di interesseAvviso Manifestazione Interesse DISTRIBUTORI AUTOMATICI di bevande e snackScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D18" s="32" t="inlineStr">
+      <c r="D18" s="36" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-distributori-automatici-bevande-snack</t>
         </is>
       </c>
-      <c r="E18" s="31" t="inlineStr"/>
-      <c r="F18" s="31" t="inlineStr"/>
-      <c r="G18" s="31" t="inlineStr"/>
+      <c r="E18" s="35" t="inlineStr"/>
+      <c r="F18" s="35" t="inlineStr"/>
+      <c r="G18" s="35" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="29" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="29" t="inlineStr">
+      <c r="A19" s="33" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="33" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1343,30 +1243,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D19" s="30" t="inlineStr">
+      <c r="D19" s="34" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo</t>
         </is>
       </c>
-      <c r="E19" s="29" t="inlineStr">
+      <c r="E19" s="33" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F19" s="29" t="inlineStr">
+      <c r="F19" s="33" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G19" s="29" t="inlineStr"/>
+      <c r="G19" s="33" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="31" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="31" t="inlineStr">
+      <c r="A20" s="35" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="35" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1376,30 +1276,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D20" s="32" t="inlineStr">
+      <c r="D20" s="36" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo-0</t>
         </is>
       </c>
-      <c r="E20" s="31" t="inlineStr">
+      <c r="E20" s="35" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F20" s="31" t="inlineStr">
+      <c r="F20" s="35" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G20" s="31" t="inlineStr"/>
+      <c r="G20" s="35" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="29" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="29" t="inlineStr">
+      <c r="A21" s="33" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="33" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1409,22 +1309,22 @@
           <t>Manifestazioni di interesseST SIRACUSA - AVVISO DI MANIFESTAZIONE DI INTERESSE - Fornitura applicativo extracontabile per la gestione progetti, ecc. e</t>
         </is>
       </c>
-      <c r="D21" s="30" t="inlineStr">
+      <c r="D21" s="34" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-siracusa-avviso-manifestazione-interesse-fornitura-applicativo-extracontabile-gestione-progetti-ecc-applicativo-gestione-ed-elaborazione-informatizzata-paghe</t>
         </is>
       </c>
-      <c r="E21" s="29" t="inlineStr"/>
-      <c r="F21" s="29" t="inlineStr"/>
-      <c r="G21" s="29" t="inlineStr"/>
+      <c r="E21" s="33" t="inlineStr"/>
+      <c r="F21" s="33" t="inlineStr"/>
+      <c r="G21" s="33" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="31" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="31" t="inlineStr">
+      <c r="A22" s="35" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="35" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1434,30 +1334,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile sito nel Comune di Capo D'Orlando, Via Trazzera MarinaScade il:25/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D22" s="32" t="inlineStr">
+      <c r="D22" s="36" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-sito-nel-comune-capo-d-orlando-trazzera-marina</t>
         </is>
       </c>
-      <c r="E22" s="31" t="inlineStr">
+      <c r="E22" s="35" t="inlineStr">
         <is>
           <t>25/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F22" s="31" t="inlineStr">
+      <c r="F22" s="35" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="G22" s="31" t="inlineStr"/>
+      <c r="G22" s="35" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="29" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="29" t="inlineStr">
+      <c r="A23" s="33" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="33" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1467,22 +1367,22 @@
           <t xml:space="preserve">Avvisi pubbliciST CATANIA - Programma Regionale FESR Sicilia 2021-2027 - Azione 2.4.4 - “Interventi per la riduzione del rischio incendi” - AVVISO DI </t>
         </is>
       </c>
-      <c r="D23" s="30" t="inlineStr">
+      <c r="D23" s="34" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-catania-programma-regionale-fesr-sicilia-2021-2027-azione-244-interventi-riduzione-rischio-incendi-avviso-indagine-mercato</t>
         </is>
       </c>
-      <c r="E23" s="29" t="inlineStr"/>
-      <c r="F23" s="29" t="inlineStr"/>
-      <c r="G23" s="29" t="inlineStr"/>
+      <c r="E23" s="33" t="inlineStr"/>
+      <c r="F23" s="33" t="inlineStr"/>
+      <c r="G23" s="33" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="31" t="inlineStr">
+      <c r="A24" s="35" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B24" s="31" t="inlineStr">
+      <c r="B24" s="35" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1492,22 +1392,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per ROMICS – Primavera 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D24" s="32" t="inlineStr">
+      <c r="D24" s="36" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-romics-primavera-2026/</t>
         </is>
       </c>
-      <c r="E24" s="31" t="inlineStr"/>
-      <c r="F24" s="31" t="inlineStr"/>
-      <c r="G24" s="31" t="inlineStr"/>
+      <c r="E24" s="35" t="inlineStr"/>
+      <c r="F24" s="35" t="inlineStr"/>
+      <c r="G24" s="35" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="29" t="inlineStr">
+      <c r="A25" s="33" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B25" s="29" t="inlineStr">
+      <c r="B25" s="33" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1517,22 +1417,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Cinema International 2026 – I edizioneApertoFESR</t>
         </is>
       </c>
-      <c r="D25" s="30" t="inlineStr">
+      <c r="D25" s="34" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lazio-cinema-international-2026-i-edizione/</t>
         </is>
       </c>
-      <c r="E25" s="29" t="inlineStr"/>
-      <c r="F25" s="29" t="inlineStr"/>
-      <c r="G25" s="29" t="inlineStr"/>
+      <c r="E25" s="33" t="inlineStr"/>
+      <c r="F25" s="33" t="inlineStr"/>
+      <c r="G25" s="33" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="31" t="inlineStr">
+      <c r="A26" s="35" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B26" s="31" t="inlineStr">
+      <c r="B26" s="35" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1542,22 +1442,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEManifestazioni di interesse alla costituzione di due nuove Fondazioni I.T.S. AcademyApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D26" s="32" t="inlineStr">
+      <c r="D26" s="36" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazioni-di-interesse-alla-costituzione-di-due-nuove-fondazioni-i-t-s-academy/</t>
         </is>
       </c>
-      <c r="E26" s="31" t="inlineStr"/>
-      <c r="F26" s="31" t="inlineStr"/>
-      <c r="G26" s="31" t="inlineStr"/>
+      <c r="E26" s="35" t="inlineStr"/>
+      <c r="F26" s="35" t="inlineStr"/>
+      <c r="G26" s="35" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="29" t="inlineStr">
+      <c r="A27" s="33" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B27" s="29" t="inlineStr">
+      <c r="B27" s="33" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1567,22 +1467,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURAContributi per sostenere la ripresa del settore della pescaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D27" s="30" t="inlineStr">
+      <c r="D27" s="34" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributi-per-sostenere-la-ripresa-del-settore-della-pesca/</t>
         </is>
       </c>
-      <c r="E27" s="29" t="inlineStr"/>
-      <c r="F27" s="29" t="inlineStr"/>
-      <c r="G27" s="29" t="inlineStr"/>
+      <c r="E27" s="33" t="inlineStr"/>
+      <c r="F27" s="33" t="inlineStr"/>
+      <c r="G27" s="33" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="31" t="inlineStr">
+      <c r="A28" s="35" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B28" s="31" t="inlineStr">
+      <c r="B28" s="35" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1592,30 +1492,30 @@
           <t>Manifestazioni di interesseAVVISO - Manifestazione Interesse “Storytelling aziendale” Expo Wild Natura - Caccia - Pesca. Misterbianco (CT), 10-12 apri</t>
         </is>
       </c>
-      <c r="D28" s="32" t="inlineStr">
+      <c r="D28" s="36" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-storytelling-aziendale-expo-wild-natura-caccia-pesca-misterbianco-ct-10-12-aprile-2026</t>
         </is>
       </c>
-      <c r="E28" s="31" t="inlineStr">
+      <c r="E28" s="35" t="inlineStr">
         <is>
           <t>30/03/2026 - 13:00</t>
         </is>
       </c>
-      <c r="F28" s="31" t="inlineStr">
+      <c r="F28" s="35" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G28" s="31" t="inlineStr"/>
+      <c r="G28" s="35" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="29" t="inlineStr">
+      <c r="A29" s="33" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B29" s="29" t="inlineStr">
+      <c r="B29" s="33" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1625,30 +1525,30 @@
           <t>Manifestazioni di interesseInvaso Lentini - Interventi di ripristino delle pareti esterne in cls della Torre di presa Sud e della trave d’appoggio del</t>
         </is>
       </c>
-      <c r="D29" s="30" t="inlineStr">
+      <c r="D29" s="34" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/invaso-lentini-interventi-ripristino-pareti-esterne-cls-torre-presa-sud-trave-d-appoggio-cavalcavia-collegamento-alla-stessa-torre</t>
         </is>
       </c>
-      <c r="E29" s="29" t="inlineStr">
+      <c r="E29" s="33" t="inlineStr">
         <is>
           <t>19/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F29" s="29" t="inlineStr">
+      <c r="F29" s="33" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G29" s="29" t="inlineStr"/>
+      <c r="G29" s="33" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="31" t="inlineStr">
+      <c r="A30" s="35" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="B30" s="31" t="inlineStr">
+      <c r="B30" s="35" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1658,22 +1558,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURARistrutturazione e riconversione vigneti – campagna 2026-2027ApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D30" s="32" t="inlineStr">
+      <c r="D30" s="36" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/ristrutturazione-e-riconversione-vigneti-campagna-2026-2027/</t>
         </is>
       </c>
-      <c r="E30" s="31" t="inlineStr"/>
-      <c r="F30" s="31" t="inlineStr"/>
-      <c r="G30" s="31" t="inlineStr"/>
+      <c r="E30" s="35" t="inlineStr"/>
+      <c r="F30" s="35" t="inlineStr"/>
+      <c r="G30" s="35" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="29" t="inlineStr">
+      <c r="A31" s="33" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="B31" s="29" t="inlineStr">
+      <c r="B31" s="33" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1683,30 +1583,30 @@
           <t>Manifestazioni di interessePR FESR 2021/27 Azione 1.3.3 e del POC 2014/20 - Azione 1.3.1  - Avviso a manifestazione d’interesse eventi fieristici inte</t>
         </is>
       </c>
-      <c r="D31" s="30" t="inlineStr">
+      <c r="D31" s="34" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-d-interesse-eventi-fieristici-internazionali-marzo-dicembre-2026</t>
         </is>
       </c>
-      <c r="E31" s="29" t="inlineStr">
+      <c r="E31" s="33" t="inlineStr">
         <is>
           <t>30/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F31" s="29" t="inlineStr">
+      <c r="F31" s="33" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="G31" s="29" t="inlineStr"/>
+      <c r="G31" s="33" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="31" t="inlineStr">
+      <c r="A32" s="35" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="B32" s="31" t="inlineStr">
+      <c r="B32" s="35" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1716,22 +1616,22 @@
           <t>INTERNAZIONALIZZAZIONEL’Ecosistema dell’Innovazione a INNOVIT – Focus S3ApertoFESR</t>
         </is>
       </c>
-      <c r="D32" s="32" t="inlineStr">
+      <c r="D32" s="36" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lecosistema-dellinnovazione-a-innovit-focus-s3/</t>
         </is>
       </c>
-      <c r="E32" s="31" t="inlineStr"/>
-      <c r="F32" s="31" t="inlineStr"/>
-      <c r="G32" s="31" t="inlineStr"/>
+      <c r="E32" s="35" t="inlineStr"/>
+      <c r="F32" s="35" t="inlineStr"/>
+      <c r="G32" s="35" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="29" t="inlineStr">
+      <c r="A33" s="33" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="B33" s="29" t="inlineStr">
+      <c r="B33" s="33" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1741,22 +1641,22 @@
           <t>Manifestazioni di interessePR FESR SICILIA 2021/27 - NUOVO Avviso a manifestazione d’interesse per esperti valutatoriScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D33" s="30" t="inlineStr">
+      <c r="D33" s="34" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/pr-fesr-sicilia-202127-nuovo-avviso-manifestazione-d-interesse-esperti-valutatori</t>
         </is>
       </c>
-      <c r="E33" s="29" t="inlineStr"/>
-      <c r="F33" s="29" t="inlineStr"/>
-      <c r="G33" s="29" t="inlineStr"/>
+      <c r="E33" s="33" t="inlineStr"/>
+      <c r="F33" s="33" t="inlineStr"/>
+      <c r="G33" s="33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="31" t="inlineStr">
+      <c r="A34" s="35" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="B34" s="31" t="inlineStr">
+      <c r="B34" s="35" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -1766,22 +1666,22 @@
           <t>Bando 2026 per contributi dedicati alla manutenzione della rete dei percorsi escursionistici</t>
         </is>
       </c>
-      <c r="D34" s="32" t="inlineStr">
+      <c r="D34" s="36" t="inlineStr">
         <is>
           <t>https://ambiente.regione.emilia-romagna.it/it/parchi-natura2000/bandi/bando-2026-per-contributi-dedicati-alla-manutenzione-della-rete-dei-percorsi-escursionistici</t>
         </is>
       </c>
-      <c r="E34" s="31" t="inlineStr"/>
-      <c r="F34" s="31" t="inlineStr"/>
-      <c r="G34" s="31" t="inlineStr"/>
+      <c r="E34" s="35" t="inlineStr"/>
+      <c r="F34" s="35" t="inlineStr"/>
+      <c r="G34" s="35" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="29" t="inlineStr">
+      <c r="A35" s="33" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="B35" s="29" t="inlineStr">
+      <c r="B35" s="33" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1791,14 +1691,14 @@
           <t>Programma regionale in favore delle tradizioni storiche, artistiche, religiose e popolari (2026) – manifestazioni d’interesseApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D35" s="30" t="inlineStr">
+      <c r="D35" s="34" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/programma-regionale-in-favore-delle-tradizioni-storiche-artistiche-religiose-e-popolari-2026-manifestazioni-dinteresse/</t>
         </is>
       </c>
-      <c r="E35" s="29" t="inlineStr"/>
-      <c r="F35" s="29" t="inlineStr"/>
-      <c r="G35" s="29" t="inlineStr"/>
+      <c r="E35" s="33" t="inlineStr"/>
+      <c r="F35" s="33" t="inlineStr"/>
+      <c r="G35" s="33" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="35" t="inlineStr">
@@ -1973,6 +1873,64 @@
       <c r="E41" s="33" t="inlineStr"/>
       <c r="F41" s="33" t="inlineStr"/>
       <c r="G41" s="33" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="39" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="39" t="inlineStr">
+        <is>
+          <t>Emilia-Romagna</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>GAL del Ducato - Promozione di fiere agroalimentari e delle filiere del cibo – Bando per Enti pubblici (DU AS 05B)</t>
+        </is>
+      </c>
+      <c r="D42" s="40" t="inlineStr">
+        <is>
+          <t>https://agricoltura.regione.emilia-romagna.it/sviluppo-rurale-23-27/opportunita/bandi-gal/2026/du_as05b-promozione-di-fiere-agroalimentari-e-delle-filiere-del-cibo-bando-per-enti-pubblici</t>
+        </is>
+      </c>
+      <c r="E42" s="39" t="inlineStr"/>
+      <c r="F42" s="39" t="inlineStr"/>
+      <c r="G42" s="39" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="37" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="37" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Manifestazioni di interesseAVVISO PUBBLICO PER MANIFESTAZIONE DI INTERESSE FINALIZZATA ALL'ASSEGNAZIONE DI SPAZI ESPOSITIVI (CORNER GRATUITI) ALL'INTE</t>
+        </is>
+      </c>
+      <c r="D43" s="38" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-manifestazione-interesse-finalizzata-all-assegnazione-spazi-espositivi-corner-gratuiti-all-interno-stand-istituzionale-dsrt-manifestazione</t>
+        </is>
+      </c>
+      <c r="E43" s="37" t="inlineStr">
+        <is>
+          <t>30/03/2026 - 13:00</t>
+        </is>
+      </c>
+      <c r="F43" s="37" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="G43" s="37" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2016,6 +1974,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2060,20 +2020,20 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="33" t="inlineStr">
+      <c r="A3" s="37" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="35" t="inlineStr">
+      <c r="A4" s="39" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2082,20 +2042,20 @@
         <v>21</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="33" t="inlineStr">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">

--- a/data/bandi_export.xlsx
+++ b/data/bandi_export.xlsx
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -152,6 +152,18 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -601,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -616,7 +628,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏛️  Nuovi Bandi — 24/03/2026 07:50</t>
+          <t>🏛️  Nuovi Bandi — 25/03/2026 07:49</t>
         </is>
       </c>
     </row>
@@ -661,55 +673,140 @@
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="37" t="inlineStr">
+      <c r="B3" s="41" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>GAL del Ducato - Promozione di fiere agroalimentari e delle filiere del cibo – Bando per Enti pubblici (DU AS 05B)</t>
-        </is>
-      </c>
-      <c r="D3" s="38" t="inlineStr">
-        <is>
-          <t>https://agricoltura.regione.emilia-romagna.it/sviluppo-rurale-23-27/opportunita/bandi-gal/2026/du_as05b-promozione-di-fiere-agroalimentari-e-delle-filiere-del-cibo-bando-per-enti-pubblici</t>
-        </is>
-      </c>
-      <c r="E3" s="37" t="inlineStr"/>
-      <c r="F3" s="37" t="inlineStr"/>
+          <t>Avviso per la concessione di contributi per eventi sportivi realizzati in Emilia-Romagna - Anno 2026</t>
+        </is>
+      </c>
+      <c r="D3" s="42" t="inlineStr">
+        <is>
+          <t>https://www.regione.emilia-romagna.it/sport/bandi/2026/bando-2026</t>
+        </is>
+      </c>
+      <c r="E3" s="41" t="inlineStr"/>
+      <c r="F3" s="41" t="inlineStr"/>
       <c r="G3" s="5" t="inlineStr"/>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="39" t="inlineStr">
-        <is>
-          <t>Sicilia</t>
+      <c r="B4" s="43" t="inlineStr">
+        <is>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>Manifestazioni di interesseAVVISO PUBBLICO PER MANIFESTAZIONE DI INTERESSE FINALIZZATA ALL'ASSEGNAZIONE DI SPAZI ESPOSITIVI (CORNER GRATUITI) ALL'INTE</t>
-        </is>
-      </c>
-      <c r="D4" s="40" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-manifestazione-interesse-finalizzata-all-assegnazione-spazi-espositivi-corner-gratuiti-all-interno-stand-istituzionale-dsrt-manifestazione</t>
-        </is>
-      </c>
-      <c r="E4" s="39" t="inlineStr">
-        <is>
-          <t>30/03/2026 - 13:00</t>
-        </is>
-      </c>
-      <c r="F4" s="39" t="inlineStr">
-        <is>
-          <t>30/03/2026</t>
-        </is>
-      </c>
+          <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Street art 2026Prossima AperturaBandi Regionali</t>
+        </is>
+      </c>
+      <c r="D4" s="44" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/lazio-street-art-2026/</t>
+        </is>
+      </c>
+      <c r="E4" s="43" t="inlineStr"/>
+      <c r="F4" s="43" t="inlineStr"/>
       <c r="G4" s="9" t="inlineStr"/>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="41" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Manifestazioni di interesseManifestazione di interesse per la partecipazione all’evento “R2I Italy 2026” – Bologna, 12-13/05/2026Scade il:03/04/2026 -</t>
+        </is>
+      </c>
+      <c r="D5" s="42" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/manifestazione-interesse-partecipazione-all-evento-r2i-italy-2026-bologna-12-13052026</t>
+        </is>
+      </c>
+      <c r="E5" s="41" t="inlineStr">
+        <is>
+          <t>03/04/2026 - 23:59</t>
+        </is>
+      </c>
+      <c r="F5" s="41" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="43" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Manifestazioni di interesseST SIRACUSA - AVVISO PER MANIFESTAZIONE DI INTERESSE - Selezione di n. 5 unità di personale internoScade il:20/04/2026 - 12</t>
+        </is>
+      </c>
+      <c r="D6" s="44" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/24-marzo-2026-st-siracusa-avviso-manifestazione-interesse-selezione-n-5-unita-personale-interno</t>
+        </is>
+      </c>
+      <c r="E6" s="43" t="inlineStr">
+        <is>
+          <t>20/04/2026 - 12:00</t>
+        </is>
+      </c>
+      <c r="F6" s="43" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr"/>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="41" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Avvisi pubbliciRevoca dell’avviso di concessione a titolo gratuito del 16.12.2025 inerente all’immobile di seguito identificato e contestuale nuovo av</t>
+        </is>
+      </c>
+      <c r="D7" s="42" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/revoca-avviso-concessione-titolo-gratuito-16122025-inerente-all-immobile-seguito-identificato-contestuale-nuovo-avviso-concessione-titolo-oneroso-stesso-sito-nel</t>
+        </is>
+      </c>
+      <c r="E7" s="41" t="inlineStr">
+        <is>
+          <t>08/04/2026 - 12:00</t>
+        </is>
+      </c>
+      <c r="F7" s="41" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -718,6 +815,9 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -729,7 +829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -779,12 +879,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="35" t="inlineStr">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B2" s="35" t="inlineStr">
+      <c r="B2" s="39" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -794,22 +894,22 @@
           <t>FLAG GALPA Costa E-R. Sostituzione del motore principale e dei motori secondari. Secondo bando</t>
         </is>
       </c>
-      <c r="D2" s="36" t="inlineStr">
+      <c r="D2" s="40" t="inlineStr">
         <is>
           <t>https://agricoltura.regione.emilia-romagna.it/feampa-2021-2027/bandi-galpa/2026/galpa-sostituzione-motori-secondo-bando</t>
         </is>
       </c>
-      <c r="E2" s="35" t="inlineStr"/>
-      <c r="F2" s="35" t="inlineStr"/>
-      <c r="G2" s="35" t="inlineStr"/>
+      <c r="E2" s="39" t="inlineStr"/>
+      <c r="F2" s="39" t="inlineStr"/>
+      <c r="G2" s="39" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="33" t="inlineStr">
+      <c r="A3" s="37" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B3" s="33" t="inlineStr">
+      <c r="B3" s="37" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -819,22 +919,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0PRE-SEED 3.0Prossima AperturaFESR</t>
         </is>
       </c>
-      <c r="D3" s="34" t="inlineStr">
+      <c r="D3" s="38" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/pre-seed-3-0/</t>
         </is>
       </c>
-      <c r="E3" s="33" t="inlineStr"/>
-      <c r="F3" s="33" t="inlineStr"/>
-      <c r="G3" s="33" t="inlineStr"/>
+      <c r="E3" s="37" t="inlineStr"/>
+      <c r="F3" s="37" t="inlineStr"/>
+      <c r="G3" s="37" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="35" t="inlineStr">
+      <c r="A4" s="39" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B4" s="35" t="inlineStr">
+      <c r="B4" s="39" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -844,22 +944,22 @@
           <t>ACCESSO AL CREDITO E ALLE GARANZIE PER LE IMPRESEContributo su finanziamenti alle imprese del Lazio erogati su provvista BEIProssima AperturaFESR</t>
         </is>
       </c>
-      <c r="D4" s="36" t="inlineStr">
+      <c r="D4" s="40" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-su-finanziamenti-alle-imprese-del-lazio-erogati-su-provvista-bei/</t>
         </is>
       </c>
-      <c r="E4" s="35" t="inlineStr"/>
-      <c r="F4" s="35" t="inlineStr"/>
-      <c r="G4" s="35" t="inlineStr"/>
+      <c r="E4" s="39" t="inlineStr"/>
+      <c r="F4" s="39" t="inlineStr"/>
+      <c r="G4" s="39" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="33" t="inlineStr">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B5" s="33" t="inlineStr">
+      <c r="B5" s="37" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -869,22 +969,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEIndividuazione degli enti iscritti al Registro unico nazionale del Terzo settoreApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D5" s="34" t="inlineStr">
+      <c r="D5" s="38" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/individuazione-degli-enti-iscritti-al-registro-unico-nazionale-del-terzo-settore/</t>
         </is>
       </c>
-      <c r="E5" s="33" t="inlineStr"/>
-      <c r="F5" s="33" t="inlineStr"/>
-      <c r="G5" s="33" t="inlineStr"/>
+      <c r="E5" s="37" t="inlineStr"/>
+      <c r="F5" s="37" t="inlineStr"/>
+      <c r="G5" s="37" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="35" t="inlineStr">
+      <c r="A6" s="39" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B6" s="35" t="inlineStr">
+      <c r="B6" s="39" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -894,22 +994,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Technology Transfer LazioApertoFESR</t>
         </is>
       </c>
-      <c r="D6" s="36" t="inlineStr">
+      <c r="D6" s="40" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/technology-transfer-lazio/</t>
         </is>
       </c>
-      <c r="E6" s="35" t="inlineStr"/>
-      <c r="F6" s="35" t="inlineStr"/>
-      <c r="G6" s="35" t="inlineStr"/>
+      <c r="E6" s="39" t="inlineStr"/>
+      <c r="F6" s="39" t="inlineStr"/>
+      <c r="G6" s="39" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="33" t="inlineStr">
+      <c r="A7" s="37" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B7" s="33" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -919,22 +1019,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Percorso di tutoraggio per le impreseApertoFESR</t>
         </is>
       </c>
-      <c r="D7" s="34" t="inlineStr">
+      <c r="D7" s="38" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/percorso-di-tutoraggio-per-le-imprese/</t>
         </is>
       </c>
-      <c r="E7" s="33" t="inlineStr"/>
-      <c r="F7" s="33" t="inlineStr"/>
-      <c r="G7" s="33" t="inlineStr"/>
+      <c r="E7" s="37" t="inlineStr"/>
+      <c r="F7" s="37" t="inlineStr"/>
+      <c r="G7" s="37" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="35" t="inlineStr">
+      <c r="A8" s="39" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B8" s="35" t="inlineStr">
+      <c r="B8" s="39" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -944,22 +1044,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per partecipare a SMAU Parigi 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D8" s="36" t="inlineStr">
+      <c r="D8" s="40" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-partecipare-a-smau-parigi-2026/</t>
         </is>
       </c>
-      <c r="E8" s="35" t="inlineStr"/>
-      <c r="F8" s="35" t="inlineStr"/>
-      <c r="G8" s="35" t="inlineStr"/>
+      <c r="E8" s="39" t="inlineStr"/>
+      <c r="F8" s="39" t="inlineStr"/>
+      <c r="G8" s="39" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="33" t="inlineStr">
+      <c r="A9" s="37" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B9" s="33" t="inlineStr">
+      <c r="B9" s="37" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -969,22 +1069,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONERiconoscimento della funzione sociale ed educativa degli oratoriApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D9" s="34" t="inlineStr">
+      <c r="D9" s="38" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/riconoscimento-della-funzione-sociale-ed-educativa-degli-oratori/</t>
         </is>
       </c>
-      <c r="E9" s="33" t="inlineStr"/>
-      <c r="F9" s="33" t="inlineStr"/>
-      <c r="G9" s="33" t="inlineStr"/>
+      <c r="E9" s="37" t="inlineStr"/>
+      <c r="F9" s="37" t="inlineStr"/>
+      <c r="G9" s="37" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="35" t="inlineStr">
+      <c r="A10" s="39" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B10" s="35" t="inlineStr">
+      <c r="B10" s="39" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -994,22 +1094,22 @@
           <t>GovernanceIscrizione nell’elenco regionale degli idonei all’esercizio dell’attività di direttore dell’Istituto JemoloApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D10" s="36" t="inlineStr">
+      <c r="D10" s="40" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/iscrizione-nellelenco-regionale-degli-idonei-allesercizio-dellattivita-di-direttore-dellistituto-jemolo/</t>
         </is>
       </c>
-      <c r="E10" s="35" t="inlineStr"/>
-      <c r="F10" s="35" t="inlineStr"/>
-      <c r="G10" s="35" t="inlineStr"/>
+      <c r="E10" s="39" t="inlineStr"/>
+      <c r="F10" s="39" t="inlineStr"/>
+      <c r="G10" s="39" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="A11" s="37" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B11" s="33" t="inlineStr">
+      <c r="B11" s="37" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1019,22 +1119,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEVoucher per lo sport – seconda annualitàApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D11" s="34" t="inlineStr">
+      <c r="D11" s="38" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/voucher-per-lo-sport-seconda-annualita/</t>
         </is>
       </c>
-      <c r="E11" s="33" t="inlineStr"/>
-      <c r="F11" s="33" t="inlineStr"/>
-      <c r="G11" s="33" t="inlineStr"/>
+      <c r="E11" s="37" t="inlineStr"/>
+      <c r="F11" s="37" t="inlineStr"/>
+      <c r="G11" s="37" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="35" t="inlineStr">
+      <c r="A12" s="39" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B12" s="35" t="inlineStr">
+      <c r="B12" s="39" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1044,22 +1144,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEBonus occupazionale SALGOApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D12" s="36" t="inlineStr">
+      <c r="D12" s="40" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/bonus-occupazionale-salgo/</t>
         </is>
       </c>
-      <c r="E12" s="35" t="inlineStr"/>
-      <c r="F12" s="35" t="inlineStr"/>
-      <c r="G12" s="35" t="inlineStr"/>
+      <c r="E12" s="39" t="inlineStr"/>
+      <c r="F12" s="39" t="inlineStr"/>
+      <c r="G12" s="39" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="33" t="inlineStr">
+      <c r="A13" s="37" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B13" s="33" t="inlineStr">
+      <c r="B13" s="37" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1069,22 +1169,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEContributo di Libertà per le donne che hanno subito violenzaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D13" s="34" t="inlineStr">
+      <c r="D13" s="38" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-di-liberta-per-le-donne-che-hanno-subito-violenza/</t>
         </is>
       </c>
-      <c r="E13" s="33" t="inlineStr"/>
-      <c r="F13" s="33" t="inlineStr"/>
-      <c r="G13" s="33" t="inlineStr"/>
+      <c r="E13" s="37" t="inlineStr"/>
+      <c r="F13" s="37" t="inlineStr"/>
+      <c r="G13" s="37" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="35" t="inlineStr">
+      <c r="A14" s="39" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B14" s="35" t="inlineStr">
+      <c r="B14" s="39" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1094,22 +1194,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURAInterventi straordinari di valorizzazione del patrimonio culturale del LazioApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D14" s="36" t="inlineStr">
+      <c r="D14" s="40" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/interventi-straordinari-di-valorizzazione-del-patrimonio-culturale-del-lazio/</t>
         </is>
       </c>
-      <c r="E14" s="35" t="inlineStr"/>
-      <c r="F14" s="35" t="inlineStr"/>
-      <c r="G14" s="35" t="inlineStr"/>
+      <c r="E14" s="39" t="inlineStr"/>
+      <c r="F14" s="39" t="inlineStr"/>
+      <c r="G14" s="39" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="33" t="inlineStr">
+      <c r="A15" s="37" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B15" s="33" t="inlineStr">
+      <c r="B15" s="37" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1119,30 +1219,30 @@
           <t>Bandi di garaBANDO ATTUAZIONE Ob. 1.1 Azione 1 codice 111102 _DIV - "SOSTEGNO ALLA DIVERSIFICAZIONE E NUOVE FORME DI REDDITO PER LA PICCOLA PESCA COST</t>
         </is>
       </c>
-      <c r="D15" s="34" t="inlineStr">
+      <c r="D15" s="38" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/bando-avviso-regia-ob-11-azione-1-codice-111102-div-sostegno-alla-diversificazione-nuove-forme-reddito-piccola-pesca-costiera</t>
         </is>
       </c>
-      <c r="E15" s="33" t="inlineStr">
+      <c r="E15" s="37" t="inlineStr">
         <is>
           <t>07/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F15" s="33" t="inlineStr">
+      <c r="F15" s="37" t="inlineStr">
         <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="G15" s="33" t="inlineStr"/>
+      <c r="G15" s="37" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="35" t="inlineStr">
+      <c r="A16" s="39" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B16" s="35" t="inlineStr">
+      <c r="B16" s="39" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1152,30 +1252,30 @@
           <t>Avvisi pubblici09 marzo 2026 - ST SIRACUSA - AVVISO PUBBLICO PER LA COSTITUZIONE DI ELENCHI DI OPERATORI ECONOMICI PER L’ACQUISIZIONE DI BENI E SERVIZ</t>
         </is>
       </c>
-      <c r="D16" s="36" t="inlineStr">
+      <c r="D16" s="40" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/09-marzo-2026-st-siracusa-avviso-pubblico-costituzione-elenchi-operatori-economici-l-acquisizione-beni-servizi</t>
         </is>
       </c>
-      <c r="E16" s="35" t="inlineStr">
+      <c r="E16" s="39" t="inlineStr">
         <is>
           <t>31/12/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F16" s="35" t="inlineStr">
+      <c r="F16" s="39" t="inlineStr">
         <is>
           <t>31/12/2026</t>
         </is>
       </c>
-      <c r="G16" s="35" t="inlineStr"/>
+      <c r="G16" s="39" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="33" t="inlineStr">
+      <c r="A17" s="37" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B17" s="33" t="inlineStr">
+      <c r="B17" s="37" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1185,30 +1285,30 @@
           <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScade il:19/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D17" s="34" t="inlineStr">
+      <c r="D17" s="38" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
         </is>
       </c>
-      <c r="E17" s="33" t="inlineStr">
+      <c r="E17" s="37" t="inlineStr">
         <is>
           <t>19/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F17" s="33" t="inlineStr">
+      <c r="F17" s="37" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G17" s="33" t="inlineStr"/>
+      <c r="G17" s="37" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="35" t="inlineStr">
+      <c r="A18" s="39" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B18" s="35" t="inlineStr">
+      <c r="B18" s="39" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1218,22 +1318,22 @@
           <t>Manifestazioni di interesseAvviso Manifestazione Interesse DISTRIBUTORI AUTOMATICI di bevande e snackScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D18" s="36" t="inlineStr">
+      <c r="D18" s="40" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-distributori-automatici-bevande-snack</t>
         </is>
       </c>
-      <c r="E18" s="35" t="inlineStr"/>
-      <c r="F18" s="35" t="inlineStr"/>
-      <c r="G18" s="35" t="inlineStr"/>
+      <c r="E18" s="39" t="inlineStr"/>
+      <c r="F18" s="39" t="inlineStr"/>
+      <c r="G18" s="39" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="33" t="inlineStr">
+      <c r="A19" s="37" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B19" s="33" t="inlineStr">
+      <c r="B19" s="37" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1243,30 +1343,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D19" s="34" t="inlineStr">
+      <c r="D19" s="38" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo</t>
         </is>
       </c>
-      <c r="E19" s="33" t="inlineStr">
+      <c r="E19" s="37" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F19" s="33" t="inlineStr">
+      <c r="F19" s="37" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G19" s="33" t="inlineStr"/>
+      <c r="G19" s="37" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="35" t="inlineStr">
+      <c r="A20" s="39" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B20" s="35" t="inlineStr">
+      <c r="B20" s="39" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1276,30 +1376,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D20" s="36" t="inlineStr">
+      <c r="D20" s="40" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo-0</t>
         </is>
       </c>
-      <c r="E20" s="35" t="inlineStr">
+      <c r="E20" s="39" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F20" s="35" t="inlineStr">
+      <c r="F20" s="39" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G20" s="35" t="inlineStr"/>
+      <c r="G20" s="39" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="33" t="inlineStr">
+      <c r="A21" s="37" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B21" s="33" t="inlineStr">
+      <c r="B21" s="37" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1309,22 +1409,22 @@
           <t>Manifestazioni di interesseST SIRACUSA - AVVISO DI MANIFESTAZIONE DI INTERESSE - Fornitura applicativo extracontabile per la gestione progetti, ecc. e</t>
         </is>
       </c>
-      <c r="D21" s="34" t="inlineStr">
+      <c r="D21" s="38" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-siracusa-avviso-manifestazione-interesse-fornitura-applicativo-extracontabile-gestione-progetti-ecc-applicativo-gestione-ed-elaborazione-informatizzata-paghe</t>
         </is>
       </c>
-      <c r="E21" s="33" t="inlineStr"/>
-      <c r="F21" s="33" t="inlineStr"/>
-      <c r="G21" s="33" t="inlineStr"/>
+      <c r="E21" s="37" t="inlineStr"/>
+      <c r="F21" s="37" t="inlineStr"/>
+      <c r="G21" s="37" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="35" t="inlineStr">
+      <c r="A22" s="39" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B22" s="35" t="inlineStr">
+      <c r="B22" s="39" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1334,30 +1434,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile sito nel Comune di Capo D'Orlando, Via Trazzera MarinaScade il:25/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D22" s="36" t="inlineStr">
+      <c r="D22" s="40" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-sito-nel-comune-capo-d-orlando-trazzera-marina</t>
         </is>
       </c>
-      <c r="E22" s="35" t="inlineStr">
+      <c r="E22" s="39" t="inlineStr">
         <is>
           <t>25/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F22" s="35" t="inlineStr">
+      <c r="F22" s="39" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="G22" s="35" t="inlineStr"/>
+      <c r="G22" s="39" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="33" t="inlineStr">
+      <c r="A23" s="37" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B23" s="33" t="inlineStr">
+      <c r="B23" s="37" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1367,22 +1467,22 @@
           <t xml:space="preserve">Avvisi pubbliciST CATANIA - Programma Regionale FESR Sicilia 2021-2027 - Azione 2.4.4 - “Interventi per la riduzione del rischio incendi” - AVVISO DI </t>
         </is>
       </c>
-      <c r="D23" s="34" t="inlineStr">
+      <c r="D23" s="38" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-catania-programma-regionale-fesr-sicilia-2021-2027-azione-244-interventi-riduzione-rischio-incendi-avviso-indagine-mercato</t>
         </is>
       </c>
-      <c r="E23" s="33" t="inlineStr"/>
-      <c r="F23" s="33" t="inlineStr"/>
-      <c r="G23" s="33" t="inlineStr"/>
+      <c r="E23" s="37" t="inlineStr"/>
+      <c r="F23" s="37" t="inlineStr"/>
+      <c r="G23" s="37" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="35" t="inlineStr">
+      <c r="A24" s="39" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B24" s="35" t="inlineStr">
+      <c r="B24" s="39" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1392,22 +1492,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per ROMICS – Primavera 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D24" s="36" t="inlineStr">
+      <c r="D24" s="40" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-romics-primavera-2026/</t>
         </is>
       </c>
-      <c r="E24" s="35" t="inlineStr"/>
-      <c r="F24" s="35" t="inlineStr"/>
-      <c r="G24" s="35" t="inlineStr"/>
+      <c r="E24" s="39" t="inlineStr"/>
+      <c r="F24" s="39" t="inlineStr"/>
+      <c r="G24" s="39" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="33" t="inlineStr">
+      <c r="A25" s="37" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B25" s="33" t="inlineStr">
+      <c r="B25" s="37" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1417,22 +1517,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Cinema International 2026 – I edizioneApertoFESR</t>
         </is>
       </c>
-      <c r="D25" s="34" t="inlineStr">
+      <c r="D25" s="38" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lazio-cinema-international-2026-i-edizione/</t>
         </is>
       </c>
-      <c r="E25" s="33" t="inlineStr"/>
-      <c r="F25" s="33" t="inlineStr"/>
-      <c r="G25" s="33" t="inlineStr"/>
+      <c r="E25" s="37" t="inlineStr"/>
+      <c r="F25" s="37" t="inlineStr"/>
+      <c r="G25" s="37" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="35" t="inlineStr">
+      <c r="A26" s="39" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B26" s="35" t="inlineStr">
+      <c r="B26" s="39" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1442,22 +1542,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEManifestazioni di interesse alla costituzione di due nuove Fondazioni I.T.S. AcademyApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D26" s="36" t="inlineStr">
+      <c r="D26" s="40" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazioni-di-interesse-alla-costituzione-di-due-nuove-fondazioni-i-t-s-academy/</t>
         </is>
       </c>
-      <c r="E26" s="35" t="inlineStr"/>
-      <c r="F26" s="35" t="inlineStr"/>
-      <c r="G26" s="35" t="inlineStr"/>
+      <c r="E26" s="39" t="inlineStr"/>
+      <c r="F26" s="39" t="inlineStr"/>
+      <c r="G26" s="39" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="33" t="inlineStr">
+      <c r="A27" s="37" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B27" s="33" t="inlineStr">
+      <c r="B27" s="37" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1467,22 +1567,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURAContributi per sostenere la ripresa del settore della pescaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D27" s="34" t="inlineStr">
+      <c r="D27" s="38" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributi-per-sostenere-la-ripresa-del-settore-della-pesca/</t>
         </is>
       </c>
-      <c r="E27" s="33" t="inlineStr"/>
-      <c r="F27" s="33" t="inlineStr"/>
-      <c r="G27" s="33" t="inlineStr"/>
+      <c r="E27" s="37" t="inlineStr"/>
+      <c r="F27" s="37" t="inlineStr"/>
+      <c r="G27" s="37" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="35" t="inlineStr">
+      <c r="A28" s="39" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B28" s="35" t="inlineStr">
+      <c r="B28" s="39" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1492,30 +1592,30 @@
           <t>Manifestazioni di interesseAVVISO - Manifestazione Interesse “Storytelling aziendale” Expo Wild Natura - Caccia - Pesca. Misterbianco (CT), 10-12 apri</t>
         </is>
       </c>
-      <c r="D28" s="36" t="inlineStr">
+      <c r="D28" s="40" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-storytelling-aziendale-expo-wild-natura-caccia-pesca-misterbianco-ct-10-12-aprile-2026</t>
         </is>
       </c>
-      <c r="E28" s="35" t="inlineStr">
+      <c r="E28" s="39" t="inlineStr">
         <is>
           <t>30/03/2026 - 13:00</t>
         </is>
       </c>
-      <c r="F28" s="35" t="inlineStr">
+      <c r="F28" s="39" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G28" s="35" t="inlineStr"/>
+      <c r="G28" s="39" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="33" t="inlineStr">
+      <c r="A29" s="37" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B29" s="33" t="inlineStr">
+      <c r="B29" s="37" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1525,30 +1625,30 @@
           <t>Manifestazioni di interesseInvaso Lentini - Interventi di ripristino delle pareti esterne in cls della Torre di presa Sud e della trave d’appoggio del</t>
         </is>
       </c>
-      <c r="D29" s="34" t="inlineStr">
+      <c r="D29" s="38" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/invaso-lentini-interventi-ripristino-pareti-esterne-cls-torre-presa-sud-trave-d-appoggio-cavalcavia-collegamento-alla-stessa-torre</t>
         </is>
       </c>
-      <c r="E29" s="33" t="inlineStr">
+      <c r="E29" s="37" t="inlineStr">
         <is>
           <t>19/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F29" s="33" t="inlineStr">
+      <c r="F29" s="37" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G29" s="33" t="inlineStr"/>
+      <c r="G29" s="37" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="35" t="inlineStr">
+      <c r="A30" s="39" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="B30" s="35" t="inlineStr">
+      <c r="B30" s="39" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1558,22 +1658,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURARistrutturazione e riconversione vigneti – campagna 2026-2027ApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D30" s="36" t="inlineStr">
+      <c r="D30" s="40" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/ristrutturazione-e-riconversione-vigneti-campagna-2026-2027/</t>
         </is>
       </c>
-      <c r="E30" s="35" t="inlineStr"/>
-      <c r="F30" s="35" t="inlineStr"/>
-      <c r="G30" s="35" t="inlineStr"/>
+      <c r="E30" s="39" t="inlineStr"/>
+      <c r="F30" s="39" t="inlineStr"/>
+      <c r="G30" s="39" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="33" t="inlineStr">
+      <c r="A31" s="37" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="B31" s="33" t="inlineStr">
+      <c r="B31" s="37" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1583,30 +1683,30 @@
           <t>Manifestazioni di interessePR FESR 2021/27 Azione 1.3.3 e del POC 2014/20 - Azione 1.3.1  - Avviso a manifestazione d’interesse eventi fieristici inte</t>
         </is>
       </c>
-      <c r="D31" s="34" t="inlineStr">
+      <c r="D31" s="38" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-d-interesse-eventi-fieristici-internazionali-marzo-dicembre-2026</t>
         </is>
       </c>
-      <c r="E31" s="33" t="inlineStr">
+      <c r="E31" s="37" t="inlineStr">
         <is>
           <t>30/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F31" s="33" t="inlineStr">
+      <c r="F31" s="37" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="G31" s="33" t="inlineStr"/>
+      <c r="G31" s="37" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="35" t="inlineStr">
+      <c r="A32" s="39" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="B32" s="35" t="inlineStr">
+      <c r="B32" s="39" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1616,22 +1716,22 @@
           <t>INTERNAZIONALIZZAZIONEL’Ecosistema dell’Innovazione a INNOVIT – Focus S3ApertoFESR</t>
         </is>
       </c>
-      <c r="D32" s="36" t="inlineStr">
+      <c r="D32" s="40" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lecosistema-dellinnovazione-a-innovit-focus-s3/</t>
         </is>
       </c>
-      <c r="E32" s="35" t="inlineStr"/>
-      <c r="F32" s="35" t="inlineStr"/>
-      <c r="G32" s="35" t="inlineStr"/>
+      <c r="E32" s="39" t="inlineStr"/>
+      <c r="F32" s="39" t="inlineStr"/>
+      <c r="G32" s="39" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="33" t="inlineStr">
+      <c r="A33" s="37" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="B33" s="33" t="inlineStr">
+      <c r="B33" s="37" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1641,22 +1741,22 @@
           <t>Manifestazioni di interessePR FESR SICILIA 2021/27 - NUOVO Avviso a manifestazione d’interesse per esperti valutatoriScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D33" s="34" t="inlineStr">
+      <c r="D33" s="38" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/pr-fesr-sicilia-202127-nuovo-avviso-manifestazione-d-interesse-esperti-valutatori</t>
         </is>
       </c>
-      <c r="E33" s="33" t="inlineStr"/>
-      <c r="F33" s="33" t="inlineStr"/>
-      <c r="G33" s="33" t="inlineStr"/>
+      <c r="E33" s="37" t="inlineStr"/>
+      <c r="F33" s="37" t="inlineStr"/>
+      <c r="G33" s="37" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="35" t="inlineStr">
+      <c r="A34" s="39" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="B34" s="35" t="inlineStr">
+      <c r="B34" s="39" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -1666,22 +1766,22 @@
           <t>Bando 2026 per contributi dedicati alla manutenzione della rete dei percorsi escursionistici</t>
         </is>
       </c>
-      <c r="D34" s="36" t="inlineStr">
+      <c r="D34" s="40" t="inlineStr">
         <is>
           <t>https://ambiente.regione.emilia-romagna.it/it/parchi-natura2000/bandi/bando-2026-per-contributi-dedicati-alla-manutenzione-della-rete-dei-percorsi-escursionistici</t>
         </is>
       </c>
-      <c r="E34" s="35" t="inlineStr"/>
-      <c r="F34" s="35" t="inlineStr"/>
-      <c r="G34" s="35" t="inlineStr"/>
+      <c r="E34" s="39" t="inlineStr"/>
+      <c r="F34" s="39" t="inlineStr"/>
+      <c r="G34" s="39" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="33" t="inlineStr">
+      <c r="A35" s="37" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="B35" s="33" t="inlineStr">
+      <c r="B35" s="37" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1691,22 +1791,22 @@
           <t>Programma regionale in favore delle tradizioni storiche, artistiche, religiose e popolari (2026) – manifestazioni d’interesseApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D35" s="34" t="inlineStr">
+      <c r="D35" s="38" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/programma-regionale-in-favore-delle-tradizioni-storiche-artistiche-religiose-e-popolari-2026-manifestazioni-dinteresse/</t>
         </is>
       </c>
-      <c r="E35" s="33" t="inlineStr"/>
-      <c r="F35" s="33" t="inlineStr"/>
-      <c r="G35" s="33" t="inlineStr"/>
+      <c r="E35" s="37" t="inlineStr"/>
+      <c r="F35" s="37" t="inlineStr"/>
+      <c r="G35" s="37" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="35" t="inlineStr">
+      <c r="A36" s="39" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B36" s="35" t="inlineStr">
+      <c r="B36" s="39" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1716,22 +1816,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEBuoni servizio per le persone non autosufficienti nel territorio del LazioProssima AperturaFSE / FSE+</t>
         </is>
       </c>
-      <c r="D36" s="36" t="inlineStr">
+      <c r="D36" s="40" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/buoni-servizio-per-le-persone-non-autosufficienti-nel-territorio-del-lazio/</t>
         </is>
       </c>
-      <c r="E36" s="35" t="inlineStr"/>
-      <c r="F36" s="35" t="inlineStr"/>
-      <c r="G36" s="35" t="inlineStr"/>
+      <c r="E36" s="39" t="inlineStr"/>
+      <c r="F36" s="39" t="inlineStr"/>
+      <c r="G36" s="39" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="33" t="inlineStr">
+      <c r="A37" s="37" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B37" s="33" t="inlineStr">
+      <c r="B37" s="37" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1741,22 +1841,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONERimborso delle rette dei servizi educativi nel territorio del LazioProssima AperturaFSE / FSE+</t>
         </is>
       </c>
-      <c r="D37" s="34" t="inlineStr">
+      <c r="D37" s="38" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/rimborso-delle-rette-dei-servizi-educativi-nel-territorio-del-lazio/</t>
         </is>
       </c>
-      <c r="E37" s="33" t="inlineStr"/>
-      <c r="F37" s="33" t="inlineStr"/>
-      <c r="G37" s="33" t="inlineStr"/>
+      <c r="E37" s="37" t="inlineStr"/>
+      <c r="F37" s="37" t="inlineStr"/>
+      <c r="G37" s="37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="35" t="inlineStr">
+      <c r="A38" s="39" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B38" s="35" t="inlineStr">
+      <c r="B38" s="39" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1766,30 +1866,30 @@
           <t>Manifestazioni di interesseATTO DI INTERPELLO PER L’AFFIDAMENTO DELL’INCARICO DI COLLAUDO STATICO DELLE STRUTTURE - Diga di Pietrarossa (Progetto ex C</t>
         </is>
       </c>
-      <c r="D38" s="36" t="inlineStr">
+      <c r="D38" s="40" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/atto-interpello-l-affidamento-incarico-collaudo-statico-strutture-diga-pietrarossa-progetto-ex-casmez-303219</t>
         </is>
       </c>
-      <c r="E38" s="35" t="inlineStr">
+      <c r="E38" s="39" t="inlineStr">
         <is>
           <t>27/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F38" s="35" t="inlineStr">
+      <c r="F38" s="39" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="G38" s="35" t="inlineStr"/>
+      <c r="G38" s="39" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="33" t="inlineStr">
+      <c r="A39" s="37" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B39" s="33" t="inlineStr">
+      <c r="B39" s="37" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1799,30 +1899,30 @@
           <t>Manifestazioni di interesseAvviso alle Case  Editrici della Regione siciliana per la partecipazione al Salone del Libro di Torino, 14-18  maggio 2026.</t>
         </is>
       </c>
-      <c r="D39" s="34" t="inlineStr">
+      <c r="D39" s="38" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/manifestazione-d-interesse-partecipare-al-xxxviii-salone-libro-torino-14-al-18-maggio-2026-attraverso-l-esposizione-pubblicazioni-presso-stand-assessorato-beni</t>
         </is>
       </c>
-      <c r="E39" s="33" t="inlineStr">
+      <c r="E39" s="37" t="inlineStr">
         <is>
           <t>30/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F39" s="33" t="inlineStr">
+      <c r="F39" s="37" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="G39" s="33" t="inlineStr"/>
+      <c r="G39" s="37" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="35" t="inlineStr">
+      <c r="A40" s="39" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B40" s="35" t="inlineStr">
+      <c r="B40" s="39" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1832,30 +1932,30 @@
           <t xml:space="preserve">Manifestazioni di interessePR FESR SICILIA 2021/27 - NUOVO Avviso a manifestazione d’interesse per esperti valutatoriScade il:06/04/2026 - 23:59Leggi </t>
         </is>
       </c>
-      <c r="D40" s="36" t="inlineStr">
+      <c r="D40" s="40" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/pr-fesr-sicilia-202127-nuovo-avviso-manifestazione-d-interesse-esperti-valutatori</t>
         </is>
       </c>
-      <c r="E40" s="35" t="inlineStr">
+      <c r="E40" s="39" t="inlineStr">
         <is>
           <t>06/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F40" s="35" t="inlineStr">
+      <c r="F40" s="39" t="inlineStr">
         <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="G40" s="35" t="inlineStr"/>
+      <c r="G40" s="39" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="33" t="inlineStr">
+      <c r="A41" s="37" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B41" s="33" t="inlineStr">
+      <c r="B41" s="37" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1865,14 +1965,14 @@
           <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D41" s="34" t="inlineStr">
+      <c r="D41" s="38" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
         </is>
       </c>
-      <c r="E41" s="33" t="inlineStr"/>
-      <c r="F41" s="33" t="inlineStr"/>
-      <c r="G41" s="33" t="inlineStr"/>
+      <c r="E41" s="37" t="inlineStr"/>
+      <c r="F41" s="37" t="inlineStr"/>
+      <c r="G41" s="37" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="39" t="inlineStr">
@@ -1931,6 +2031,155 @@
         </is>
       </c>
       <c r="G43" s="37" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="43" t="inlineStr">
+        <is>
+          <t>25/03/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="43" t="inlineStr">
+        <is>
+          <t>Emilia-Romagna</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>Avviso per la concessione di contributi per eventi sportivi realizzati in Emilia-Romagna - Anno 2026</t>
+        </is>
+      </c>
+      <c r="D44" s="44" t="inlineStr">
+        <is>
+          <t>https://www.regione.emilia-romagna.it/sport/bandi/2026/bando-2026</t>
+        </is>
+      </c>
+      <c r="E44" s="43" t="inlineStr"/>
+      <c r="F44" s="43" t="inlineStr"/>
+      <c r="G44" s="43" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="41" t="inlineStr">
+        <is>
+          <t>25/03/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="41" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Street art 2026Prossima AperturaBandi Regionali</t>
+        </is>
+      </c>
+      <c r="D45" s="42" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/lazio-street-art-2026/</t>
+        </is>
+      </c>
+      <c r="E45" s="41" t="inlineStr"/>
+      <c r="F45" s="41" t="inlineStr"/>
+      <c r="G45" s="41" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="43" t="inlineStr">
+        <is>
+          <t>25/03/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="43" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>Manifestazioni di interesseManifestazione di interesse per la partecipazione all’evento “R2I Italy 2026” – Bologna, 12-13/05/2026Scade il:03/04/2026 -</t>
+        </is>
+      </c>
+      <c r="D46" s="44" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/manifestazione-interesse-partecipazione-all-evento-r2i-italy-2026-bologna-12-13052026</t>
+        </is>
+      </c>
+      <c r="E46" s="43" t="inlineStr">
+        <is>
+          <t>03/04/2026 - 23:59</t>
+        </is>
+      </c>
+      <c r="F46" s="43" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="G46" s="43" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="41" t="inlineStr">
+        <is>
+          <t>25/03/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="41" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Manifestazioni di interesseST SIRACUSA - AVVISO PER MANIFESTAZIONE DI INTERESSE - Selezione di n. 5 unità di personale internoScade il:20/04/2026 - 12</t>
+        </is>
+      </c>
+      <c r="D47" s="42" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/24-marzo-2026-st-siracusa-avviso-manifestazione-interesse-selezione-n-5-unita-personale-interno</t>
+        </is>
+      </c>
+      <c r="E47" s="41" t="inlineStr">
+        <is>
+          <t>20/04/2026 - 12:00</t>
+        </is>
+      </c>
+      <c r="F47" s="41" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="G47" s="41" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="43" t="inlineStr">
+        <is>
+          <t>25/03/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="43" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>Avvisi pubbliciRevoca dell’avviso di concessione a titolo gratuito del 16.12.2025 inerente all’immobile di seguito identificato e contestuale nuovo av</t>
+        </is>
+      </c>
+      <c r="D48" s="44" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/revoca-avviso-concessione-titolo-gratuito-16122025-inerente-all-immobile-seguito-identificato-contestuale-nuovo-avviso-concessione-titolo-oneroso-stesso-sito-nel</t>
+        </is>
+      </c>
+      <c r="E48" s="43" t="inlineStr">
+        <is>
+          <t>08/04/2026 - 12:00</t>
+        </is>
+      </c>
+      <c r="F48" s="43" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="G48" s="43" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1976,6 +2225,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId47"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2020,42 +2274,42 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="37" t="inlineStr">
+      <c r="A3" s="41" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="39" t="inlineStr">
+      <c r="A4" s="43" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
       </c>
       <c r="B4" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="41" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="C4" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="37" t="inlineStr">
-        <is>
-          <t>Sicilia</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>18</v>
-      </c>
       <c r="C5" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">

--- a/data/bandi_export.xlsx
+++ b/data/bandi_export.xlsx
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -152,6 +152,18 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -613,7 +625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -628,7 +640,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏛️  Nuovi Bandi — 25/03/2026 07:49</t>
+          <t>🏛️  Nuovi Bandi — 26/03/2026 07:58</t>
         </is>
       </c>
     </row>
@@ -673,140 +685,55 @@
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="41" t="inlineStr">
+      <c r="B3" s="45" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Avviso per la concessione di contributi per eventi sportivi realizzati in Emilia-Romagna - Anno 2026</t>
-        </is>
-      </c>
-      <c r="D3" s="42" t="inlineStr">
-        <is>
-          <t>https://www.regione.emilia-romagna.it/sport/bandi/2026/bando-2026</t>
-        </is>
-      </c>
-      <c r="E3" s="41" t="inlineStr"/>
-      <c r="F3" s="41" t="inlineStr"/>
+          <t>Bando studi di fattibilità per fusioni di Comuni</t>
+        </is>
+      </c>
+      <c r="D3" s="46" t="inlineStr">
+        <is>
+          <t>https://www.regione.emilia-romagna.it/autonomie-locali/bandi/bando_studi_fattibilita_fusioni_comuni</t>
+        </is>
+      </c>
+      <c r="E3" s="45" t="inlineStr"/>
+      <c r="F3" s="45" t="inlineStr"/>
       <c r="G3" s="5" t="inlineStr"/>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="43" t="inlineStr">
-        <is>
-          <t>Lazio</t>
+      <c r="B4" s="47" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Street art 2026Prossima AperturaBandi Regionali</t>
-        </is>
-      </c>
-      <c r="D4" s="44" t="inlineStr">
-        <is>
-          <t>https://www.lazioeuropa.it/bandi/lazio-street-art-2026/</t>
-        </is>
-      </c>
-      <c r="E4" s="43" t="inlineStr"/>
-      <c r="F4" s="43" t="inlineStr"/>
+          <t xml:space="preserve">Manifestazioni di interesseAvviso pubblico di selezione interna, per titoli, per il conferimento di PO e professionali, ai sensi degli artt. 19, 20 e </t>
+        </is>
+      </c>
+      <c r="D4" s="48" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-selezione-interna-titoli-conferimento-po-professionali-ai-sensi-artt-19-20-21-ccrl-20222024-comparto-non-dirigenziale</t>
+        </is>
+      </c>
+      <c r="E4" s="47" t="inlineStr">
+        <is>
+          <t>30/03/2026 - 12:00</t>
+        </is>
+      </c>
+      <c r="F4" s="47" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
       <c r="G4" s="9" t="inlineStr"/>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" s="41" t="inlineStr">
-        <is>
-          <t>Sicilia</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Manifestazioni di interesseManifestazione di interesse per la partecipazione all’evento “R2I Italy 2026” – Bologna, 12-13/05/2026Scade il:03/04/2026 -</t>
-        </is>
-      </c>
-      <c r="D5" s="42" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/manifestazione-interesse-partecipazione-all-evento-r2i-italy-2026-bologna-12-13052026</t>
-        </is>
-      </c>
-      <c r="E5" s="41" t="inlineStr">
-        <is>
-          <t>03/04/2026 - 23:59</t>
-        </is>
-      </c>
-      <c r="F5" s="41" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="43" t="inlineStr">
-        <is>
-          <t>Sicilia</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>Manifestazioni di interesseST SIRACUSA - AVVISO PER MANIFESTAZIONE DI INTERESSE - Selezione di n. 5 unità di personale internoScade il:20/04/2026 - 12</t>
-        </is>
-      </c>
-      <c r="D6" s="44" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/24-marzo-2026-st-siracusa-avviso-manifestazione-interesse-selezione-n-5-unita-personale-interno</t>
-        </is>
-      </c>
-      <c r="E6" s="43" t="inlineStr">
-        <is>
-          <t>20/04/2026 - 12:00</t>
-        </is>
-      </c>
-      <c r="F6" s="43" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr"/>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" s="41" t="inlineStr">
-        <is>
-          <t>Sicilia</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Avvisi pubbliciRevoca dell’avviso di concessione a titolo gratuito del 16.12.2025 inerente all’immobile di seguito identificato e contestuale nuovo av</t>
-        </is>
-      </c>
-      <c r="D7" s="42" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/revoca-avviso-concessione-titolo-gratuito-16122025-inerente-all-immobile-seguito-identificato-contestuale-nuovo-avviso-concessione-titolo-oneroso-stesso-sito-nel</t>
-        </is>
-      </c>
-      <c r="E7" s="41" t="inlineStr">
-        <is>
-          <t>08/04/2026 - 12:00</t>
-        </is>
-      </c>
-      <c r="F7" s="41" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -815,9 +742,6 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -829,7 +753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -879,12 +803,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="39" t="inlineStr">
+      <c r="A2" s="43" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B2" s="39" t="inlineStr">
+      <c r="B2" s="43" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -894,22 +818,22 @@
           <t>FLAG GALPA Costa E-R. Sostituzione del motore principale e dei motori secondari. Secondo bando</t>
         </is>
       </c>
-      <c r="D2" s="40" t="inlineStr">
+      <c r="D2" s="44" t="inlineStr">
         <is>
           <t>https://agricoltura.regione.emilia-romagna.it/feampa-2021-2027/bandi-galpa/2026/galpa-sostituzione-motori-secondo-bando</t>
         </is>
       </c>
-      <c r="E2" s="39" t="inlineStr"/>
-      <c r="F2" s="39" t="inlineStr"/>
-      <c r="G2" s="39" t="inlineStr"/>
+      <c r="E2" s="43" t="inlineStr"/>
+      <c r="F2" s="43" t="inlineStr"/>
+      <c r="G2" s="43" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="37" t="inlineStr">
+      <c r="A3" s="41" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B3" s="37" t="inlineStr">
+      <c r="B3" s="41" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -919,22 +843,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0PRE-SEED 3.0Prossima AperturaFESR</t>
         </is>
       </c>
-      <c r="D3" s="38" t="inlineStr">
+      <c r="D3" s="42" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/pre-seed-3-0/</t>
         </is>
       </c>
-      <c r="E3" s="37" t="inlineStr"/>
-      <c r="F3" s="37" t="inlineStr"/>
-      <c r="G3" s="37" t="inlineStr"/>
+      <c r="E3" s="41" t="inlineStr"/>
+      <c r="F3" s="41" t="inlineStr"/>
+      <c r="G3" s="41" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="39" t="inlineStr">
+      <c r="A4" s="43" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B4" s="39" t="inlineStr">
+      <c r="B4" s="43" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -944,22 +868,22 @@
           <t>ACCESSO AL CREDITO E ALLE GARANZIE PER LE IMPRESEContributo su finanziamenti alle imprese del Lazio erogati su provvista BEIProssima AperturaFESR</t>
         </is>
       </c>
-      <c r="D4" s="40" t="inlineStr">
+      <c r="D4" s="44" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-su-finanziamenti-alle-imprese-del-lazio-erogati-su-provvista-bei/</t>
         </is>
       </c>
-      <c r="E4" s="39" t="inlineStr"/>
-      <c r="F4" s="39" t="inlineStr"/>
-      <c r="G4" s="39" t="inlineStr"/>
+      <c r="E4" s="43" t="inlineStr"/>
+      <c r="F4" s="43" t="inlineStr"/>
+      <c r="G4" s="43" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="41" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B5" s="37" t="inlineStr">
+      <c r="B5" s="41" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -969,22 +893,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEIndividuazione degli enti iscritti al Registro unico nazionale del Terzo settoreApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D5" s="38" t="inlineStr">
+      <c r="D5" s="42" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/individuazione-degli-enti-iscritti-al-registro-unico-nazionale-del-terzo-settore/</t>
         </is>
       </c>
-      <c r="E5" s="37" t="inlineStr"/>
-      <c r="F5" s="37" t="inlineStr"/>
-      <c r="G5" s="37" t="inlineStr"/>
+      <c r="E5" s="41" t="inlineStr"/>
+      <c r="F5" s="41" t="inlineStr"/>
+      <c r="G5" s="41" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="39" t="inlineStr">
+      <c r="A6" s="43" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B6" s="39" t="inlineStr">
+      <c r="B6" s="43" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -994,22 +918,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Technology Transfer LazioApertoFESR</t>
         </is>
       </c>
-      <c r="D6" s="40" t="inlineStr">
+      <c r="D6" s="44" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/technology-transfer-lazio/</t>
         </is>
       </c>
-      <c r="E6" s="39" t="inlineStr"/>
-      <c r="F6" s="39" t="inlineStr"/>
-      <c r="G6" s="39" t="inlineStr"/>
+      <c r="E6" s="43" t="inlineStr"/>
+      <c r="F6" s="43" t="inlineStr"/>
+      <c r="G6" s="43" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="37" t="inlineStr">
+      <c r="A7" s="41" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B7" s="37" t="inlineStr">
+      <c r="B7" s="41" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1019,22 +943,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Percorso di tutoraggio per le impreseApertoFESR</t>
         </is>
       </c>
-      <c r="D7" s="38" t="inlineStr">
+      <c r="D7" s="42" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/percorso-di-tutoraggio-per-le-imprese/</t>
         </is>
       </c>
-      <c r="E7" s="37" t="inlineStr"/>
-      <c r="F7" s="37" t="inlineStr"/>
-      <c r="G7" s="37" t="inlineStr"/>
+      <c r="E7" s="41" t="inlineStr"/>
+      <c r="F7" s="41" t="inlineStr"/>
+      <c r="G7" s="41" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="39" t="inlineStr">
+      <c r="A8" s="43" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B8" s="39" t="inlineStr">
+      <c r="B8" s="43" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1044,22 +968,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per partecipare a SMAU Parigi 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D8" s="40" t="inlineStr">
+      <c r="D8" s="44" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-partecipare-a-smau-parigi-2026/</t>
         </is>
       </c>
-      <c r="E8" s="39" t="inlineStr"/>
-      <c r="F8" s="39" t="inlineStr"/>
-      <c r="G8" s="39" t="inlineStr"/>
+      <c r="E8" s="43" t="inlineStr"/>
+      <c r="F8" s="43" t="inlineStr"/>
+      <c r="G8" s="43" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="37" t="inlineStr">
+      <c r="A9" s="41" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B9" s="37" t="inlineStr">
+      <c r="B9" s="41" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1069,22 +993,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONERiconoscimento della funzione sociale ed educativa degli oratoriApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D9" s="38" t="inlineStr">
+      <c r="D9" s="42" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/riconoscimento-della-funzione-sociale-ed-educativa-degli-oratori/</t>
         </is>
       </c>
-      <c r="E9" s="37" t="inlineStr"/>
-      <c r="F9" s="37" t="inlineStr"/>
-      <c r="G9" s="37" t="inlineStr"/>
+      <c r="E9" s="41" t="inlineStr"/>
+      <c r="F9" s="41" t="inlineStr"/>
+      <c r="G9" s="41" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="39" t="inlineStr">
+      <c r="A10" s="43" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B10" s="39" t="inlineStr">
+      <c r="B10" s="43" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1094,22 +1018,22 @@
           <t>GovernanceIscrizione nell’elenco regionale degli idonei all’esercizio dell’attività di direttore dell’Istituto JemoloApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D10" s="40" t="inlineStr">
+      <c r="D10" s="44" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/iscrizione-nellelenco-regionale-degli-idonei-allesercizio-dellattivita-di-direttore-dellistituto-jemolo/</t>
         </is>
       </c>
-      <c r="E10" s="39" t="inlineStr"/>
-      <c r="F10" s="39" t="inlineStr"/>
-      <c r="G10" s="39" t="inlineStr"/>
+      <c r="E10" s="43" t="inlineStr"/>
+      <c r="F10" s="43" t="inlineStr"/>
+      <c r="G10" s="43" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="37" t="inlineStr">
+      <c r="A11" s="41" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B11" s="37" t="inlineStr">
+      <c r="B11" s="41" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1119,22 +1043,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEVoucher per lo sport – seconda annualitàApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D11" s="38" t="inlineStr">
+      <c r="D11" s="42" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/voucher-per-lo-sport-seconda-annualita/</t>
         </is>
       </c>
-      <c r="E11" s="37" t="inlineStr"/>
-      <c r="F11" s="37" t="inlineStr"/>
-      <c r="G11" s="37" t="inlineStr"/>
+      <c r="E11" s="41" t="inlineStr"/>
+      <c r="F11" s="41" t="inlineStr"/>
+      <c r="G11" s="41" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="39" t="inlineStr">
+      <c r="A12" s="43" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B12" s="39" t="inlineStr">
+      <c r="B12" s="43" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1144,22 +1068,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEBonus occupazionale SALGOApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D12" s="40" t="inlineStr">
+      <c r="D12" s="44" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/bonus-occupazionale-salgo/</t>
         </is>
       </c>
-      <c r="E12" s="39" t="inlineStr"/>
-      <c r="F12" s="39" t="inlineStr"/>
-      <c r="G12" s="39" t="inlineStr"/>
+      <c r="E12" s="43" t="inlineStr"/>
+      <c r="F12" s="43" t="inlineStr"/>
+      <c r="G12" s="43" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="37" t="inlineStr">
+      <c r="A13" s="41" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B13" s="37" t="inlineStr">
+      <c r="B13" s="41" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1169,22 +1093,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEContributo di Libertà per le donne che hanno subito violenzaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D13" s="38" t="inlineStr">
+      <c r="D13" s="42" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-di-liberta-per-le-donne-che-hanno-subito-violenza/</t>
         </is>
       </c>
-      <c r="E13" s="37" t="inlineStr"/>
-      <c r="F13" s="37" t="inlineStr"/>
-      <c r="G13" s="37" t="inlineStr"/>
+      <c r="E13" s="41" t="inlineStr"/>
+      <c r="F13" s="41" t="inlineStr"/>
+      <c r="G13" s="41" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="39" t="inlineStr">
+      <c r="A14" s="43" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B14" s="39" t="inlineStr">
+      <c r="B14" s="43" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1194,22 +1118,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURAInterventi straordinari di valorizzazione del patrimonio culturale del LazioApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D14" s="40" t="inlineStr">
+      <c r="D14" s="44" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/interventi-straordinari-di-valorizzazione-del-patrimonio-culturale-del-lazio/</t>
         </is>
       </c>
-      <c r="E14" s="39" t="inlineStr"/>
-      <c r="F14" s="39" t="inlineStr"/>
-      <c r="G14" s="39" t="inlineStr"/>
+      <c r="E14" s="43" t="inlineStr"/>
+      <c r="F14" s="43" t="inlineStr"/>
+      <c r="G14" s="43" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="37" t="inlineStr">
+      <c r="A15" s="41" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B15" s="37" t="inlineStr">
+      <c r="B15" s="41" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1219,30 +1143,30 @@
           <t>Bandi di garaBANDO ATTUAZIONE Ob. 1.1 Azione 1 codice 111102 _DIV - "SOSTEGNO ALLA DIVERSIFICAZIONE E NUOVE FORME DI REDDITO PER LA PICCOLA PESCA COST</t>
         </is>
       </c>
-      <c r="D15" s="38" t="inlineStr">
+      <c r="D15" s="42" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/bando-avviso-regia-ob-11-azione-1-codice-111102-div-sostegno-alla-diversificazione-nuove-forme-reddito-piccola-pesca-costiera</t>
         </is>
       </c>
-      <c r="E15" s="37" t="inlineStr">
+      <c r="E15" s="41" t="inlineStr">
         <is>
           <t>07/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F15" s="37" t="inlineStr">
+      <c r="F15" s="41" t="inlineStr">
         <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="G15" s="37" t="inlineStr"/>
+      <c r="G15" s="41" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="39" t="inlineStr">
+      <c r="A16" s="43" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B16" s="39" t="inlineStr">
+      <c r="B16" s="43" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1252,30 +1176,30 @@
           <t>Avvisi pubblici09 marzo 2026 - ST SIRACUSA - AVVISO PUBBLICO PER LA COSTITUZIONE DI ELENCHI DI OPERATORI ECONOMICI PER L’ACQUISIZIONE DI BENI E SERVIZ</t>
         </is>
       </c>
-      <c r="D16" s="40" t="inlineStr">
+      <c r="D16" s="44" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/09-marzo-2026-st-siracusa-avviso-pubblico-costituzione-elenchi-operatori-economici-l-acquisizione-beni-servizi</t>
         </is>
       </c>
-      <c r="E16" s="39" t="inlineStr">
+      <c r="E16" s="43" t="inlineStr">
         <is>
           <t>31/12/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F16" s="39" t="inlineStr">
+      <c r="F16" s="43" t="inlineStr">
         <is>
           <t>31/12/2026</t>
         </is>
       </c>
-      <c r="G16" s="39" t="inlineStr"/>
+      <c r="G16" s="43" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="37" t="inlineStr">
+      <c r="A17" s="41" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B17" s="37" t="inlineStr">
+      <c r="B17" s="41" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1285,30 +1209,30 @@
           <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScade il:19/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D17" s="38" t="inlineStr">
+      <c r="D17" s="42" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
         </is>
       </c>
-      <c r="E17" s="37" t="inlineStr">
+      <c r="E17" s="41" t="inlineStr">
         <is>
           <t>19/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F17" s="37" t="inlineStr">
+      <c r="F17" s="41" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G17" s="37" t="inlineStr"/>
+      <c r="G17" s="41" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="39" t="inlineStr">
+      <c r="A18" s="43" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B18" s="39" t="inlineStr">
+      <c r="B18" s="43" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1318,22 +1242,22 @@
           <t>Manifestazioni di interesseAvviso Manifestazione Interesse DISTRIBUTORI AUTOMATICI di bevande e snackScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D18" s="40" t="inlineStr">
+      <c r="D18" s="44" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-distributori-automatici-bevande-snack</t>
         </is>
       </c>
-      <c r="E18" s="39" t="inlineStr"/>
-      <c r="F18" s="39" t="inlineStr"/>
-      <c r="G18" s="39" t="inlineStr"/>
+      <c r="E18" s="43" t="inlineStr"/>
+      <c r="F18" s="43" t="inlineStr"/>
+      <c r="G18" s="43" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="37" t="inlineStr">
+      <c r="A19" s="41" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B19" s="37" t="inlineStr">
+      <c r="B19" s="41" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1343,30 +1267,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D19" s="38" t="inlineStr">
+      <c r="D19" s="42" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo</t>
         </is>
       </c>
-      <c r="E19" s="37" t="inlineStr">
+      <c r="E19" s="41" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F19" s="37" t="inlineStr">
+      <c r="F19" s="41" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G19" s="37" t="inlineStr"/>
+      <c r="G19" s="41" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="39" t="inlineStr">
+      <c r="A20" s="43" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B20" s="39" t="inlineStr">
+      <c r="B20" s="43" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1376,30 +1300,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D20" s="40" t="inlineStr">
+      <c r="D20" s="44" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo-0</t>
         </is>
       </c>
-      <c r="E20" s="39" t="inlineStr">
+      <c r="E20" s="43" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F20" s="39" t="inlineStr">
+      <c r="F20" s="43" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G20" s="39" t="inlineStr"/>
+      <c r="G20" s="43" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="37" t="inlineStr">
+      <c r="A21" s="41" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B21" s="37" t="inlineStr">
+      <c r="B21" s="41" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1409,22 +1333,22 @@
           <t>Manifestazioni di interesseST SIRACUSA - AVVISO DI MANIFESTAZIONE DI INTERESSE - Fornitura applicativo extracontabile per la gestione progetti, ecc. e</t>
         </is>
       </c>
-      <c r="D21" s="38" t="inlineStr">
+      <c r="D21" s="42" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-siracusa-avviso-manifestazione-interesse-fornitura-applicativo-extracontabile-gestione-progetti-ecc-applicativo-gestione-ed-elaborazione-informatizzata-paghe</t>
         </is>
       </c>
-      <c r="E21" s="37" t="inlineStr"/>
-      <c r="F21" s="37" t="inlineStr"/>
-      <c r="G21" s="37" t="inlineStr"/>
+      <c r="E21" s="41" t="inlineStr"/>
+      <c r="F21" s="41" t="inlineStr"/>
+      <c r="G21" s="41" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="39" t="inlineStr">
+      <c r="A22" s="43" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B22" s="39" t="inlineStr">
+      <c r="B22" s="43" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1434,30 +1358,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile sito nel Comune di Capo D'Orlando, Via Trazzera MarinaScade il:25/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D22" s="40" t="inlineStr">
+      <c r="D22" s="44" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-sito-nel-comune-capo-d-orlando-trazzera-marina</t>
         </is>
       </c>
-      <c r="E22" s="39" t="inlineStr">
+      <c r="E22" s="43" t="inlineStr">
         <is>
           <t>25/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F22" s="39" t="inlineStr">
+      <c r="F22" s="43" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="G22" s="39" t="inlineStr"/>
+      <c r="G22" s="43" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="37" t="inlineStr">
+      <c r="A23" s="41" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B23" s="37" t="inlineStr">
+      <c r="B23" s="41" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1467,22 +1391,22 @@
           <t xml:space="preserve">Avvisi pubbliciST CATANIA - Programma Regionale FESR Sicilia 2021-2027 - Azione 2.4.4 - “Interventi per la riduzione del rischio incendi” - AVVISO DI </t>
         </is>
       </c>
-      <c r="D23" s="38" t="inlineStr">
+      <c r="D23" s="42" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-catania-programma-regionale-fesr-sicilia-2021-2027-azione-244-interventi-riduzione-rischio-incendi-avviso-indagine-mercato</t>
         </is>
       </c>
-      <c r="E23" s="37" t="inlineStr"/>
-      <c r="F23" s="37" t="inlineStr"/>
-      <c r="G23" s="37" t="inlineStr"/>
+      <c r="E23" s="41" t="inlineStr"/>
+      <c r="F23" s="41" t="inlineStr"/>
+      <c r="G23" s="41" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="39" t="inlineStr">
+      <c r="A24" s="43" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B24" s="39" t="inlineStr">
+      <c r="B24" s="43" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1492,22 +1416,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per ROMICS – Primavera 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D24" s="40" t="inlineStr">
+      <c r="D24" s="44" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-romics-primavera-2026/</t>
         </is>
       </c>
-      <c r="E24" s="39" t="inlineStr"/>
-      <c r="F24" s="39" t="inlineStr"/>
-      <c r="G24" s="39" t="inlineStr"/>
+      <c r="E24" s="43" t="inlineStr"/>
+      <c r="F24" s="43" t="inlineStr"/>
+      <c r="G24" s="43" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="37" t="inlineStr">
+      <c r="A25" s="41" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B25" s="37" t="inlineStr">
+      <c r="B25" s="41" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1517,22 +1441,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Cinema International 2026 – I edizioneApertoFESR</t>
         </is>
       </c>
-      <c r="D25" s="38" t="inlineStr">
+      <c r="D25" s="42" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lazio-cinema-international-2026-i-edizione/</t>
         </is>
       </c>
-      <c r="E25" s="37" t="inlineStr"/>
-      <c r="F25" s="37" t="inlineStr"/>
-      <c r="G25" s="37" t="inlineStr"/>
+      <c r="E25" s="41" t="inlineStr"/>
+      <c r="F25" s="41" t="inlineStr"/>
+      <c r="G25" s="41" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="39" t="inlineStr">
+      <c r="A26" s="43" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B26" s="39" t="inlineStr">
+      <c r="B26" s="43" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1542,22 +1466,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEManifestazioni di interesse alla costituzione di due nuove Fondazioni I.T.S. AcademyApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D26" s="40" t="inlineStr">
+      <c r="D26" s="44" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazioni-di-interesse-alla-costituzione-di-due-nuove-fondazioni-i-t-s-academy/</t>
         </is>
       </c>
-      <c r="E26" s="39" t="inlineStr"/>
-      <c r="F26" s="39" t="inlineStr"/>
-      <c r="G26" s="39" t="inlineStr"/>
+      <c r="E26" s="43" t="inlineStr"/>
+      <c r="F26" s="43" t="inlineStr"/>
+      <c r="G26" s="43" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="37" t="inlineStr">
+      <c r="A27" s="41" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B27" s="37" t="inlineStr">
+      <c r="B27" s="41" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1567,22 +1491,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURAContributi per sostenere la ripresa del settore della pescaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D27" s="38" t="inlineStr">
+      <c r="D27" s="42" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributi-per-sostenere-la-ripresa-del-settore-della-pesca/</t>
         </is>
       </c>
-      <c r="E27" s="37" t="inlineStr"/>
-      <c r="F27" s="37" t="inlineStr"/>
-      <c r="G27" s="37" t="inlineStr"/>
+      <c r="E27" s="41" t="inlineStr"/>
+      <c r="F27" s="41" t="inlineStr"/>
+      <c r="G27" s="41" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="39" t="inlineStr">
+      <c r="A28" s="43" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B28" s="39" t="inlineStr">
+      <c r="B28" s="43" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1592,30 +1516,30 @@
           <t>Manifestazioni di interesseAVVISO - Manifestazione Interesse “Storytelling aziendale” Expo Wild Natura - Caccia - Pesca. Misterbianco (CT), 10-12 apri</t>
         </is>
       </c>
-      <c r="D28" s="40" t="inlineStr">
+      <c r="D28" s="44" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-storytelling-aziendale-expo-wild-natura-caccia-pesca-misterbianco-ct-10-12-aprile-2026</t>
         </is>
       </c>
-      <c r="E28" s="39" t="inlineStr">
+      <c r="E28" s="43" t="inlineStr">
         <is>
           <t>30/03/2026 - 13:00</t>
         </is>
       </c>
-      <c r="F28" s="39" t="inlineStr">
+      <c r="F28" s="43" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G28" s="39" t="inlineStr"/>
+      <c r="G28" s="43" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="37" t="inlineStr">
+      <c r="A29" s="41" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B29" s="37" t="inlineStr">
+      <c r="B29" s="41" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1625,30 +1549,30 @@
           <t>Manifestazioni di interesseInvaso Lentini - Interventi di ripristino delle pareti esterne in cls della Torre di presa Sud e della trave d’appoggio del</t>
         </is>
       </c>
-      <c r="D29" s="38" t="inlineStr">
+      <c r="D29" s="42" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/invaso-lentini-interventi-ripristino-pareti-esterne-cls-torre-presa-sud-trave-d-appoggio-cavalcavia-collegamento-alla-stessa-torre</t>
         </is>
       </c>
-      <c r="E29" s="37" t="inlineStr">
+      <c r="E29" s="41" t="inlineStr">
         <is>
           <t>19/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F29" s="37" t="inlineStr">
+      <c r="F29" s="41" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G29" s="37" t="inlineStr"/>
+      <c r="G29" s="41" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="39" t="inlineStr">
+      <c r="A30" s="43" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="B30" s="39" t="inlineStr">
+      <c r="B30" s="43" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1658,22 +1582,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURARistrutturazione e riconversione vigneti – campagna 2026-2027ApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D30" s="40" t="inlineStr">
+      <c r="D30" s="44" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/ristrutturazione-e-riconversione-vigneti-campagna-2026-2027/</t>
         </is>
       </c>
-      <c r="E30" s="39" t="inlineStr"/>
-      <c r="F30" s="39" t="inlineStr"/>
-      <c r="G30" s="39" t="inlineStr"/>
+      <c r="E30" s="43" t="inlineStr"/>
+      <c r="F30" s="43" t="inlineStr"/>
+      <c r="G30" s="43" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="37" t="inlineStr">
+      <c r="A31" s="41" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="B31" s="37" t="inlineStr">
+      <c r="B31" s="41" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1683,30 +1607,30 @@
           <t>Manifestazioni di interessePR FESR 2021/27 Azione 1.3.3 e del POC 2014/20 - Azione 1.3.1  - Avviso a manifestazione d’interesse eventi fieristici inte</t>
         </is>
       </c>
-      <c r="D31" s="38" t="inlineStr">
+      <c r="D31" s="42" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-d-interesse-eventi-fieristici-internazionali-marzo-dicembre-2026</t>
         </is>
       </c>
-      <c r="E31" s="37" t="inlineStr">
+      <c r="E31" s="41" t="inlineStr">
         <is>
           <t>30/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F31" s="37" t="inlineStr">
+      <c r="F31" s="41" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="G31" s="37" t="inlineStr"/>
+      <c r="G31" s="41" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="39" t="inlineStr">
+      <c r="A32" s="43" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="B32" s="39" t="inlineStr">
+      <c r="B32" s="43" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1716,22 +1640,22 @@
           <t>INTERNAZIONALIZZAZIONEL’Ecosistema dell’Innovazione a INNOVIT – Focus S3ApertoFESR</t>
         </is>
       </c>
-      <c r="D32" s="40" t="inlineStr">
+      <c r="D32" s="44" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lecosistema-dellinnovazione-a-innovit-focus-s3/</t>
         </is>
       </c>
-      <c r="E32" s="39" t="inlineStr"/>
-      <c r="F32" s="39" t="inlineStr"/>
-      <c r="G32" s="39" t="inlineStr"/>
+      <c r="E32" s="43" t="inlineStr"/>
+      <c r="F32" s="43" t="inlineStr"/>
+      <c r="G32" s="43" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="37" t="inlineStr">
+      <c r="A33" s="41" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="B33" s="37" t="inlineStr">
+      <c r="B33" s="41" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1741,22 +1665,22 @@
           <t>Manifestazioni di interessePR FESR SICILIA 2021/27 - NUOVO Avviso a manifestazione d’interesse per esperti valutatoriScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D33" s="38" t="inlineStr">
+      <c r="D33" s="42" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/pr-fesr-sicilia-202127-nuovo-avviso-manifestazione-d-interesse-esperti-valutatori</t>
         </is>
       </c>
-      <c r="E33" s="37" t="inlineStr"/>
-      <c r="F33" s="37" t="inlineStr"/>
-      <c r="G33" s="37" t="inlineStr"/>
+      <c r="E33" s="41" t="inlineStr"/>
+      <c r="F33" s="41" t="inlineStr"/>
+      <c r="G33" s="41" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="39" t="inlineStr">
+      <c r="A34" s="43" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="B34" s="39" t="inlineStr">
+      <c r="B34" s="43" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -1766,22 +1690,22 @@
           <t>Bando 2026 per contributi dedicati alla manutenzione della rete dei percorsi escursionistici</t>
         </is>
       </c>
-      <c r="D34" s="40" t="inlineStr">
+      <c r="D34" s="44" t="inlineStr">
         <is>
           <t>https://ambiente.regione.emilia-romagna.it/it/parchi-natura2000/bandi/bando-2026-per-contributi-dedicati-alla-manutenzione-della-rete-dei-percorsi-escursionistici</t>
         </is>
       </c>
-      <c r="E34" s="39" t="inlineStr"/>
-      <c r="F34" s="39" t="inlineStr"/>
-      <c r="G34" s="39" t="inlineStr"/>
+      <c r="E34" s="43" t="inlineStr"/>
+      <c r="F34" s="43" t="inlineStr"/>
+      <c r="G34" s="43" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="37" t="inlineStr">
+      <c r="A35" s="41" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="B35" s="37" t="inlineStr">
+      <c r="B35" s="41" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1791,22 +1715,22 @@
           <t>Programma regionale in favore delle tradizioni storiche, artistiche, religiose e popolari (2026) – manifestazioni d’interesseApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D35" s="38" t="inlineStr">
+      <c r="D35" s="42" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/programma-regionale-in-favore-delle-tradizioni-storiche-artistiche-religiose-e-popolari-2026-manifestazioni-dinteresse/</t>
         </is>
       </c>
-      <c r="E35" s="37" t="inlineStr"/>
-      <c r="F35" s="37" t="inlineStr"/>
-      <c r="G35" s="37" t="inlineStr"/>
+      <c r="E35" s="41" t="inlineStr"/>
+      <c r="F35" s="41" t="inlineStr"/>
+      <c r="G35" s="41" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="39" t="inlineStr">
+      <c r="A36" s="43" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B36" s="39" t="inlineStr">
+      <c r="B36" s="43" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1816,22 +1740,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEBuoni servizio per le persone non autosufficienti nel territorio del LazioProssima AperturaFSE / FSE+</t>
         </is>
       </c>
-      <c r="D36" s="40" t="inlineStr">
+      <c r="D36" s="44" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/buoni-servizio-per-le-persone-non-autosufficienti-nel-territorio-del-lazio/</t>
         </is>
       </c>
-      <c r="E36" s="39" t="inlineStr"/>
-      <c r="F36" s="39" t="inlineStr"/>
-      <c r="G36" s="39" t="inlineStr"/>
+      <c r="E36" s="43" t="inlineStr"/>
+      <c r="F36" s="43" t="inlineStr"/>
+      <c r="G36" s="43" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="37" t="inlineStr">
+      <c r="A37" s="41" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B37" s="37" t="inlineStr">
+      <c r="B37" s="41" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1841,22 +1765,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONERimborso delle rette dei servizi educativi nel territorio del LazioProssima AperturaFSE / FSE+</t>
         </is>
       </c>
-      <c r="D37" s="38" t="inlineStr">
+      <c r="D37" s="42" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/rimborso-delle-rette-dei-servizi-educativi-nel-territorio-del-lazio/</t>
         </is>
       </c>
-      <c r="E37" s="37" t="inlineStr"/>
-      <c r="F37" s="37" t="inlineStr"/>
-      <c r="G37" s="37" t="inlineStr"/>
+      <c r="E37" s="41" t="inlineStr"/>
+      <c r="F37" s="41" t="inlineStr"/>
+      <c r="G37" s="41" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="39" t="inlineStr">
+      <c r="A38" s="43" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B38" s="39" t="inlineStr">
+      <c r="B38" s="43" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1866,30 +1790,30 @@
           <t>Manifestazioni di interesseATTO DI INTERPELLO PER L’AFFIDAMENTO DELL’INCARICO DI COLLAUDO STATICO DELLE STRUTTURE - Diga di Pietrarossa (Progetto ex C</t>
         </is>
       </c>
-      <c r="D38" s="40" t="inlineStr">
+      <c r="D38" s="44" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/atto-interpello-l-affidamento-incarico-collaudo-statico-strutture-diga-pietrarossa-progetto-ex-casmez-303219</t>
         </is>
       </c>
-      <c r="E38" s="39" t="inlineStr">
+      <c r="E38" s="43" t="inlineStr">
         <is>
           <t>27/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F38" s="39" t="inlineStr">
+      <c r="F38" s="43" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="G38" s="39" t="inlineStr"/>
+      <c r="G38" s="43" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="37" t="inlineStr">
+      <c r="A39" s="41" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B39" s="37" t="inlineStr">
+      <c r="B39" s="41" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1899,30 +1823,30 @@
           <t>Manifestazioni di interesseAvviso alle Case  Editrici della Regione siciliana per la partecipazione al Salone del Libro di Torino, 14-18  maggio 2026.</t>
         </is>
       </c>
-      <c r="D39" s="38" t="inlineStr">
+      <c r="D39" s="42" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/manifestazione-d-interesse-partecipare-al-xxxviii-salone-libro-torino-14-al-18-maggio-2026-attraverso-l-esposizione-pubblicazioni-presso-stand-assessorato-beni</t>
         </is>
       </c>
-      <c r="E39" s="37" t="inlineStr">
+      <c r="E39" s="41" t="inlineStr">
         <is>
           <t>30/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F39" s="37" t="inlineStr">
+      <c r="F39" s="41" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="G39" s="37" t="inlineStr"/>
+      <c r="G39" s="41" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="39" t="inlineStr">
+      <c r="A40" s="43" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B40" s="39" t="inlineStr">
+      <c r="B40" s="43" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1932,30 +1856,30 @@
           <t xml:space="preserve">Manifestazioni di interessePR FESR SICILIA 2021/27 - NUOVO Avviso a manifestazione d’interesse per esperti valutatoriScade il:06/04/2026 - 23:59Leggi </t>
         </is>
       </c>
-      <c r="D40" s="40" t="inlineStr">
+      <c r="D40" s="44" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/pr-fesr-sicilia-202127-nuovo-avviso-manifestazione-d-interesse-esperti-valutatori</t>
         </is>
       </c>
-      <c r="E40" s="39" t="inlineStr">
+      <c r="E40" s="43" t="inlineStr">
         <is>
           <t>06/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F40" s="39" t="inlineStr">
+      <c r="F40" s="43" t="inlineStr">
         <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="G40" s="39" t="inlineStr"/>
+      <c r="G40" s="43" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="37" t="inlineStr">
+      <c r="A41" s="41" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B41" s="37" t="inlineStr">
+      <c r="B41" s="41" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1965,22 +1889,22 @@
           <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D41" s="38" t="inlineStr">
+      <c r="D41" s="42" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
         </is>
       </c>
-      <c r="E41" s="37" t="inlineStr"/>
-      <c r="F41" s="37" t="inlineStr"/>
-      <c r="G41" s="37" t="inlineStr"/>
+      <c r="E41" s="41" t="inlineStr"/>
+      <c r="F41" s="41" t="inlineStr"/>
+      <c r="G41" s="41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="39" t="inlineStr">
+      <c r="A42" s="43" t="inlineStr">
         <is>
           <t>24/03/2026</t>
         </is>
       </c>
-      <c r="B42" s="39" t="inlineStr">
+      <c r="B42" s="43" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -1990,22 +1914,22 @@
           <t>GAL del Ducato - Promozione di fiere agroalimentari e delle filiere del cibo – Bando per Enti pubblici (DU AS 05B)</t>
         </is>
       </c>
-      <c r="D42" s="40" t="inlineStr">
+      <c r="D42" s="44" t="inlineStr">
         <is>
           <t>https://agricoltura.regione.emilia-romagna.it/sviluppo-rurale-23-27/opportunita/bandi-gal/2026/du_as05b-promozione-di-fiere-agroalimentari-e-delle-filiere-del-cibo-bando-per-enti-pubblici</t>
         </is>
       </c>
-      <c r="E42" s="39" t="inlineStr"/>
-      <c r="F42" s="39" t="inlineStr"/>
-      <c r="G42" s="39" t="inlineStr"/>
+      <c r="E42" s="43" t="inlineStr"/>
+      <c r="F42" s="43" t="inlineStr"/>
+      <c r="G42" s="43" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="37" t="inlineStr">
+      <c r="A43" s="41" t="inlineStr">
         <is>
           <t>24/03/2026</t>
         </is>
       </c>
-      <c r="B43" s="37" t="inlineStr">
+      <c r="B43" s="41" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2015,22 +1939,22 @@
           <t>Manifestazioni di interesseAVVISO PUBBLICO PER MANIFESTAZIONE DI INTERESSE FINALIZZATA ALL'ASSEGNAZIONE DI SPAZI ESPOSITIVI (CORNER GRATUITI) ALL'INTE</t>
         </is>
       </c>
-      <c r="D43" s="38" t="inlineStr">
+      <c r="D43" s="42" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-manifestazione-interesse-finalizzata-all-assegnazione-spazi-espositivi-corner-gratuiti-all-interno-stand-istituzionale-dsrt-manifestazione</t>
         </is>
       </c>
-      <c r="E43" s="37" t="inlineStr">
+      <c r="E43" s="41" t="inlineStr">
         <is>
           <t>30/03/2026 - 13:00</t>
         </is>
       </c>
-      <c r="F43" s="37" t="inlineStr">
+      <c r="F43" s="41" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G43" s="37" t="inlineStr"/>
+      <c r="G43" s="41" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="43" t="inlineStr">
@@ -2180,6 +2104,64 @@
         </is>
       </c>
       <c r="G48" s="43" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="45" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="45" t="inlineStr">
+        <is>
+          <t>Emilia-Romagna</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Bando studi di fattibilità per fusioni di Comuni</t>
+        </is>
+      </c>
+      <c r="D49" s="46" t="inlineStr">
+        <is>
+          <t>https://www.regione.emilia-romagna.it/autonomie-locali/bandi/bando_studi_fattibilita_fusioni_comuni</t>
+        </is>
+      </c>
+      <c r="E49" s="45" t="inlineStr"/>
+      <c r="F49" s="45" t="inlineStr"/>
+      <c r="G49" s="45" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="47" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="47" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manifestazioni di interesseAvviso pubblico di selezione interna, per titoli, per il conferimento di PO e professionali, ai sensi degli artt. 19, 20 e </t>
+        </is>
+      </c>
+      <c r="D50" s="48" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-selezione-interna-titoli-conferimento-po-professionali-ai-sensi-artt-19-20-21-ccrl-20222024-comparto-non-dirigenziale</t>
+        </is>
+      </c>
+      <c r="E50" s="47" t="inlineStr">
+        <is>
+          <t>30/03/2026 - 12:00</t>
+        </is>
+      </c>
+      <c r="F50" s="47" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="G50" s="47" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2230,6 +2212,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId49"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2274,20 +2258,20 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="41" t="inlineStr">
+      <c r="A3" s="45" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="43" t="inlineStr">
+      <c r="A4" s="47" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2296,20 +2280,20 @@
         <v>22</v>
       </c>
       <c r="C4" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="45" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="41" t="inlineStr">
-        <is>
-          <t>Sicilia</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="6">

--- a/data/bandi_export.xlsx
+++ b/data/bandi_export.xlsx
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -258,6 +258,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -625,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -640,7 +649,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏛️  Nuovi Bandi — 26/03/2026 07:58</t>
+          <t>🏛️  Nuovi Bandi — 27/03/2026 07:56</t>
         </is>
       </c>
     </row>
@@ -685,55 +694,24 @@
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="45" t="inlineStr">
-        <is>
-          <t>Emilia-Romagna</t>
+      <c r="B3" s="49" t="inlineStr">
+        <is>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Bando studi di fattibilità per fusioni di Comuni</t>
-        </is>
-      </c>
-      <c r="D3" s="46" t="inlineStr">
-        <is>
-          <t>https://www.regione.emilia-romagna.it/autonomie-locali/bandi/bando_studi_fattibilita_fusioni_comuni</t>
-        </is>
-      </c>
-      <c r="E3" s="45" t="inlineStr"/>
-      <c r="F3" s="45" t="inlineStr"/>
+          <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0PRE-SEED 3.0ApertoFESR</t>
+        </is>
+      </c>
+      <c r="D3" s="50" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/pre-seed-3-0/</t>
+        </is>
+      </c>
+      <c r="E3" s="49" t="inlineStr"/>
+      <c r="F3" s="49" t="inlineStr"/>
       <c r="G3" s="5" t="inlineStr"/>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="47" t="inlineStr">
-        <is>
-          <t>Sicilia</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manifestazioni di interesseAvviso pubblico di selezione interna, per titoli, per il conferimento di PO e professionali, ai sensi degli artt. 19, 20 e </t>
-        </is>
-      </c>
-      <c r="D4" s="48" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-selezione-interna-titoli-conferimento-po-professionali-ai-sensi-artt-19-20-21-ccrl-20222024-comparto-non-dirigenziale</t>
-        </is>
-      </c>
-      <c r="E4" s="47" t="inlineStr">
-        <is>
-          <t>30/03/2026 - 12:00</t>
-        </is>
-      </c>
-      <c r="F4" s="47" t="inlineStr">
-        <is>
-          <t>30/03/2026</t>
-        </is>
-      </c>
-      <c r="G4" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -741,7 +719,6 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -753,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -803,12 +780,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="43" t="inlineStr">
+      <c r="A2" s="47" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B2" s="43" t="inlineStr">
+      <c r="B2" s="47" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -818,22 +795,22 @@
           <t>FLAG GALPA Costa E-R. Sostituzione del motore principale e dei motori secondari. Secondo bando</t>
         </is>
       </c>
-      <c r="D2" s="44" t="inlineStr">
+      <c r="D2" s="48" t="inlineStr">
         <is>
           <t>https://agricoltura.regione.emilia-romagna.it/feampa-2021-2027/bandi-galpa/2026/galpa-sostituzione-motori-secondo-bando</t>
         </is>
       </c>
-      <c r="E2" s="43" t="inlineStr"/>
-      <c r="F2" s="43" t="inlineStr"/>
-      <c r="G2" s="43" t="inlineStr"/>
+      <c r="E2" s="47" t="inlineStr"/>
+      <c r="F2" s="47" t="inlineStr"/>
+      <c r="G2" s="47" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="41" t="inlineStr">
+      <c r="A3" s="45" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B3" s="41" t="inlineStr">
+      <c r="B3" s="45" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -843,22 +820,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0PRE-SEED 3.0Prossima AperturaFESR</t>
         </is>
       </c>
-      <c r="D3" s="42" t="inlineStr">
+      <c r="D3" s="46" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/pre-seed-3-0/</t>
         </is>
       </c>
-      <c r="E3" s="41" t="inlineStr"/>
-      <c r="F3" s="41" t="inlineStr"/>
-      <c r="G3" s="41" t="inlineStr"/>
+      <c r="E3" s="45" t="inlineStr"/>
+      <c r="F3" s="45" t="inlineStr"/>
+      <c r="G3" s="45" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="43" t="inlineStr">
+      <c r="A4" s="47" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B4" s="43" t="inlineStr">
+      <c r="B4" s="47" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -868,22 +845,22 @@
           <t>ACCESSO AL CREDITO E ALLE GARANZIE PER LE IMPRESEContributo su finanziamenti alle imprese del Lazio erogati su provvista BEIProssima AperturaFESR</t>
         </is>
       </c>
-      <c r="D4" s="44" t="inlineStr">
+      <c r="D4" s="48" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-su-finanziamenti-alle-imprese-del-lazio-erogati-su-provvista-bei/</t>
         </is>
       </c>
-      <c r="E4" s="43" t="inlineStr"/>
-      <c r="F4" s="43" t="inlineStr"/>
-      <c r="G4" s="43" t="inlineStr"/>
+      <c r="E4" s="47" t="inlineStr"/>
+      <c r="F4" s="47" t="inlineStr"/>
+      <c r="G4" s="47" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="41" t="inlineStr">
+      <c r="A5" s="45" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B5" s="41" t="inlineStr">
+      <c r="B5" s="45" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -893,22 +870,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEIndividuazione degli enti iscritti al Registro unico nazionale del Terzo settoreApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D5" s="42" t="inlineStr">
+      <c r="D5" s="46" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/individuazione-degli-enti-iscritti-al-registro-unico-nazionale-del-terzo-settore/</t>
         </is>
       </c>
-      <c r="E5" s="41" t="inlineStr"/>
-      <c r="F5" s="41" t="inlineStr"/>
-      <c r="G5" s="41" t="inlineStr"/>
+      <c r="E5" s="45" t="inlineStr"/>
+      <c r="F5" s="45" t="inlineStr"/>
+      <c r="G5" s="45" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="43" t="inlineStr">
+      <c r="A6" s="47" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B6" s="43" t="inlineStr">
+      <c r="B6" s="47" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -918,22 +895,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Technology Transfer LazioApertoFESR</t>
         </is>
       </c>
-      <c r="D6" s="44" t="inlineStr">
+      <c r="D6" s="48" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/technology-transfer-lazio/</t>
         </is>
       </c>
-      <c r="E6" s="43" t="inlineStr"/>
-      <c r="F6" s="43" t="inlineStr"/>
-      <c r="G6" s="43" t="inlineStr"/>
+      <c r="E6" s="47" t="inlineStr"/>
+      <c r="F6" s="47" t="inlineStr"/>
+      <c r="G6" s="47" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="41" t="inlineStr">
+      <c r="A7" s="45" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B7" s="41" t="inlineStr">
+      <c r="B7" s="45" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -943,22 +920,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Percorso di tutoraggio per le impreseApertoFESR</t>
         </is>
       </c>
-      <c r="D7" s="42" t="inlineStr">
+      <c r="D7" s="46" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/percorso-di-tutoraggio-per-le-imprese/</t>
         </is>
       </c>
-      <c r="E7" s="41" t="inlineStr"/>
-      <c r="F7" s="41" t="inlineStr"/>
-      <c r="G7" s="41" t="inlineStr"/>
+      <c r="E7" s="45" t="inlineStr"/>
+      <c r="F7" s="45" t="inlineStr"/>
+      <c r="G7" s="45" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="43" t="inlineStr">
+      <c r="A8" s="47" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B8" s="43" t="inlineStr">
+      <c r="B8" s="47" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -968,22 +945,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per partecipare a SMAU Parigi 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D8" s="44" t="inlineStr">
+      <c r="D8" s="48" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-partecipare-a-smau-parigi-2026/</t>
         </is>
       </c>
-      <c r="E8" s="43" t="inlineStr"/>
-      <c r="F8" s="43" t="inlineStr"/>
-      <c r="G8" s="43" t="inlineStr"/>
+      <c r="E8" s="47" t="inlineStr"/>
+      <c r="F8" s="47" t="inlineStr"/>
+      <c r="G8" s="47" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="41" t="inlineStr">
+      <c r="A9" s="45" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B9" s="41" t="inlineStr">
+      <c r="B9" s="45" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -993,22 +970,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONERiconoscimento della funzione sociale ed educativa degli oratoriApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D9" s="42" t="inlineStr">
+      <c r="D9" s="46" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/riconoscimento-della-funzione-sociale-ed-educativa-degli-oratori/</t>
         </is>
       </c>
-      <c r="E9" s="41" t="inlineStr"/>
-      <c r="F9" s="41" t="inlineStr"/>
-      <c r="G9" s="41" t="inlineStr"/>
+      <c r="E9" s="45" t="inlineStr"/>
+      <c r="F9" s="45" t="inlineStr"/>
+      <c r="G9" s="45" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="43" t="inlineStr">
+      <c r="A10" s="47" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B10" s="43" t="inlineStr">
+      <c r="B10" s="47" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1018,22 +995,22 @@
           <t>GovernanceIscrizione nell’elenco regionale degli idonei all’esercizio dell’attività di direttore dell’Istituto JemoloApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D10" s="44" t="inlineStr">
+      <c r="D10" s="48" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/iscrizione-nellelenco-regionale-degli-idonei-allesercizio-dellattivita-di-direttore-dellistituto-jemolo/</t>
         </is>
       </c>
-      <c r="E10" s="43" t="inlineStr"/>
-      <c r="F10" s="43" t="inlineStr"/>
-      <c r="G10" s="43" t="inlineStr"/>
+      <c r="E10" s="47" t="inlineStr"/>
+      <c r="F10" s="47" t="inlineStr"/>
+      <c r="G10" s="47" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="41" t="inlineStr">
+      <c r="A11" s="45" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B11" s="41" t="inlineStr">
+      <c r="B11" s="45" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1043,22 +1020,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEVoucher per lo sport – seconda annualitàApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D11" s="42" t="inlineStr">
+      <c r="D11" s="46" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/voucher-per-lo-sport-seconda-annualita/</t>
         </is>
       </c>
-      <c r="E11" s="41" t="inlineStr"/>
-      <c r="F11" s="41" t="inlineStr"/>
-      <c r="G11" s="41" t="inlineStr"/>
+      <c r="E11" s="45" t="inlineStr"/>
+      <c r="F11" s="45" t="inlineStr"/>
+      <c r="G11" s="45" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="43" t="inlineStr">
+      <c r="A12" s="47" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B12" s="43" t="inlineStr">
+      <c r="B12" s="47" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1068,22 +1045,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEBonus occupazionale SALGOApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D12" s="44" t="inlineStr">
+      <c r="D12" s="48" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/bonus-occupazionale-salgo/</t>
         </is>
       </c>
-      <c r="E12" s="43" t="inlineStr"/>
-      <c r="F12" s="43" t="inlineStr"/>
-      <c r="G12" s="43" t="inlineStr"/>
+      <c r="E12" s="47" t="inlineStr"/>
+      <c r="F12" s="47" t="inlineStr"/>
+      <c r="G12" s="47" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="41" t="inlineStr">
+      <c r="A13" s="45" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B13" s="41" t="inlineStr">
+      <c r="B13" s="45" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1093,22 +1070,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEContributo di Libertà per le donne che hanno subito violenzaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D13" s="42" t="inlineStr">
+      <c r="D13" s="46" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-di-liberta-per-le-donne-che-hanno-subito-violenza/</t>
         </is>
       </c>
-      <c r="E13" s="41" t="inlineStr"/>
-      <c r="F13" s="41" t="inlineStr"/>
-      <c r="G13" s="41" t="inlineStr"/>
+      <c r="E13" s="45" t="inlineStr"/>
+      <c r="F13" s="45" t="inlineStr"/>
+      <c r="G13" s="45" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="43" t="inlineStr">
+      <c r="A14" s="47" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B14" s="43" t="inlineStr">
+      <c r="B14" s="47" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1118,22 +1095,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURAInterventi straordinari di valorizzazione del patrimonio culturale del LazioApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D14" s="44" t="inlineStr">
+      <c r="D14" s="48" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/interventi-straordinari-di-valorizzazione-del-patrimonio-culturale-del-lazio/</t>
         </is>
       </c>
-      <c r="E14" s="43" t="inlineStr"/>
-      <c r="F14" s="43" t="inlineStr"/>
-      <c r="G14" s="43" t="inlineStr"/>
+      <c r="E14" s="47" t="inlineStr"/>
+      <c r="F14" s="47" t="inlineStr"/>
+      <c r="G14" s="47" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="41" t="inlineStr">
+      <c r="A15" s="45" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B15" s="41" t="inlineStr">
+      <c r="B15" s="45" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1143,30 +1120,30 @@
           <t>Bandi di garaBANDO ATTUAZIONE Ob. 1.1 Azione 1 codice 111102 _DIV - "SOSTEGNO ALLA DIVERSIFICAZIONE E NUOVE FORME DI REDDITO PER LA PICCOLA PESCA COST</t>
         </is>
       </c>
-      <c r="D15" s="42" t="inlineStr">
+      <c r="D15" s="46" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/bando-avviso-regia-ob-11-azione-1-codice-111102-div-sostegno-alla-diversificazione-nuove-forme-reddito-piccola-pesca-costiera</t>
         </is>
       </c>
-      <c r="E15" s="41" t="inlineStr">
+      <c r="E15" s="45" t="inlineStr">
         <is>
           <t>07/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F15" s="41" t="inlineStr">
+      <c r="F15" s="45" t="inlineStr">
         <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="G15" s="41" t="inlineStr"/>
+      <c r="G15" s="45" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="43" t="inlineStr">
+      <c r="A16" s="47" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B16" s="43" t="inlineStr">
+      <c r="B16" s="47" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1176,30 +1153,30 @@
           <t>Avvisi pubblici09 marzo 2026 - ST SIRACUSA - AVVISO PUBBLICO PER LA COSTITUZIONE DI ELENCHI DI OPERATORI ECONOMICI PER L’ACQUISIZIONE DI BENI E SERVIZ</t>
         </is>
       </c>
-      <c r="D16" s="44" t="inlineStr">
+      <c r="D16" s="48" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/09-marzo-2026-st-siracusa-avviso-pubblico-costituzione-elenchi-operatori-economici-l-acquisizione-beni-servizi</t>
         </is>
       </c>
-      <c r="E16" s="43" t="inlineStr">
+      <c r="E16" s="47" t="inlineStr">
         <is>
           <t>31/12/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F16" s="43" t="inlineStr">
+      <c r="F16" s="47" t="inlineStr">
         <is>
           <t>31/12/2026</t>
         </is>
       </c>
-      <c r="G16" s="43" t="inlineStr"/>
+      <c r="G16" s="47" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="41" t="inlineStr">
+      <c r="A17" s="45" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B17" s="41" t="inlineStr">
+      <c r="B17" s="45" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1209,30 +1186,30 @@
           <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScade il:19/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D17" s="42" t="inlineStr">
+      <c r="D17" s="46" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
         </is>
       </c>
-      <c r="E17" s="41" t="inlineStr">
+      <c r="E17" s="45" t="inlineStr">
         <is>
           <t>19/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F17" s="41" t="inlineStr">
+      <c r="F17" s="45" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G17" s="41" t="inlineStr"/>
+      <c r="G17" s="45" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="43" t="inlineStr">
+      <c r="A18" s="47" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B18" s="43" t="inlineStr">
+      <c r="B18" s="47" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1242,22 +1219,22 @@
           <t>Manifestazioni di interesseAvviso Manifestazione Interesse DISTRIBUTORI AUTOMATICI di bevande e snackScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D18" s="44" t="inlineStr">
+      <c r="D18" s="48" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-distributori-automatici-bevande-snack</t>
         </is>
       </c>
-      <c r="E18" s="43" t="inlineStr"/>
-      <c r="F18" s="43" t="inlineStr"/>
-      <c r="G18" s="43" t="inlineStr"/>
+      <c r="E18" s="47" t="inlineStr"/>
+      <c r="F18" s="47" t="inlineStr"/>
+      <c r="G18" s="47" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="41" t="inlineStr">
+      <c r="A19" s="45" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B19" s="41" t="inlineStr">
+      <c r="B19" s="45" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1267,30 +1244,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D19" s="42" t="inlineStr">
+      <c r="D19" s="46" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo</t>
         </is>
       </c>
-      <c r="E19" s="41" t="inlineStr">
+      <c r="E19" s="45" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F19" s="41" t="inlineStr">
+      <c r="F19" s="45" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G19" s="41" t="inlineStr"/>
+      <c r="G19" s="45" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="43" t="inlineStr">
+      <c r="A20" s="47" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B20" s="43" t="inlineStr">
+      <c r="B20" s="47" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1300,30 +1277,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D20" s="44" t="inlineStr">
+      <c r="D20" s="48" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo-0</t>
         </is>
       </c>
-      <c r="E20" s="43" t="inlineStr">
+      <c r="E20" s="47" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F20" s="43" t="inlineStr">
+      <c r="F20" s="47" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G20" s="43" t="inlineStr"/>
+      <c r="G20" s="47" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="41" t="inlineStr">
+      <c r="A21" s="45" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B21" s="41" t="inlineStr">
+      <c r="B21" s="45" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1333,22 +1310,22 @@
           <t>Manifestazioni di interesseST SIRACUSA - AVVISO DI MANIFESTAZIONE DI INTERESSE - Fornitura applicativo extracontabile per la gestione progetti, ecc. e</t>
         </is>
       </c>
-      <c r="D21" s="42" t="inlineStr">
+      <c r="D21" s="46" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-siracusa-avviso-manifestazione-interesse-fornitura-applicativo-extracontabile-gestione-progetti-ecc-applicativo-gestione-ed-elaborazione-informatizzata-paghe</t>
         </is>
       </c>
-      <c r="E21" s="41" t="inlineStr"/>
-      <c r="F21" s="41" t="inlineStr"/>
-      <c r="G21" s="41" t="inlineStr"/>
+      <c r="E21" s="45" t="inlineStr"/>
+      <c r="F21" s="45" t="inlineStr"/>
+      <c r="G21" s="45" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="43" t="inlineStr">
+      <c r="A22" s="47" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B22" s="43" t="inlineStr">
+      <c r="B22" s="47" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1358,30 +1335,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile sito nel Comune di Capo D'Orlando, Via Trazzera MarinaScade il:25/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D22" s="44" t="inlineStr">
+      <c r="D22" s="48" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-sito-nel-comune-capo-d-orlando-trazzera-marina</t>
         </is>
       </c>
-      <c r="E22" s="43" t="inlineStr">
+      <c r="E22" s="47" t="inlineStr">
         <is>
           <t>25/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F22" s="43" t="inlineStr">
+      <c r="F22" s="47" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="G22" s="43" t="inlineStr"/>
+      <c r="G22" s="47" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="41" t="inlineStr">
+      <c r="A23" s="45" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B23" s="41" t="inlineStr">
+      <c r="B23" s="45" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1391,22 +1368,22 @@
           <t xml:space="preserve">Avvisi pubbliciST CATANIA - Programma Regionale FESR Sicilia 2021-2027 - Azione 2.4.4 - “Interventi per la riduzione del rischio incendi” - AVVISO DI </t>
         </is>
       </c>
-      <c r="D23" s="42" t="inlineStr">
+      <c r="D23" s="46" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-catania-programma-regionale-fesr-sicilia-2021-2027-azione-244-interventi-riduzione-rischio-incendi-avviso-indagine-mercato</t>
         </is>
       </c>
-      <c r="E23" s="41" t="inlineStr"/>
-      <c r="F23" s="41" t="inlineStr"/>
-      <c r="G23" s="41" t="inlineStr"/>
+      <c r="E23" s="45" t="inlineStr"/>
+      <c r="F23" s="45" t="inlineStr"/>
+      <c r="G23" s="45" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="43" t="inlineStr">
+      <c r="A24" s="47" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B24" s="43" t="inlineStr">
+      <c r="B24" s="47" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1416,22 +1393,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per ROMICS – Primavera 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D24" s="44" t="inlineStr">
+      <c r="D24" s="48" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-romics-primavera-2026/</t>
         </is>
       </c>
-      <c r="E24" s="43" t="inlineStr"/>
-      <c r="F24" s="43" t="inlineStr"/>
-      <c r="G24" s="43" t="inlineStr"/>
+      <c r="E24" s="47" t="inlineStr"/>
+      <c r="F24" s="47" t="inlineStr"/>
+      <c r="G24" s="47" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="41" t="inlineStr">
+      <c r="A25" s="45" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B25" s="41" t="inlineStr">
+      <c r="B25" s="45" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1441,22 +1418,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Cinema International 2026 – I edizioneApertoFESR</t>
         </is>
       </c>
-      <c r="D25" s="42" t="inlineStr">
+      <c r="D25" s="46" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lazio-cinema-international-2026-i-edizione/</t>
         </is>
       </c>
-      <c r="E25" s="41" t="inlineStr"/>
-      <c r="F25" s="41" t="inlineStr"/>
-      <c r="G25" s="41" t="inlineStr"/>
+      <c r="E25" s="45" t="inlineStr"/>
+      <c r="F25" s="45" t="inlineStr"/>
+      <c r="G25" s="45" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="43" t="inlineStr">
+      <c r="A26" s="47" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B26" s="43" t="inlineStr">
+      <c r="B26" s="47" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1466,22 +1443,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEManifestazioni di interesse alla costituzione di due nuove Fondazioni I.T.S. AcademyApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D26" s="44" t="inlineStr">
+      <c r="D26" s="48" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazioni-di-interesse-alla-costituzione-di-due-nuove-fondazioni-i-t-s-academy/</t>
         </is>
       </c>
-      <c r="E26" s="43" t="inlineStr"/>
-      <c r="F26" s="43" t="inlineStr"/>
-      <c r="G26" s="43" t="inlineStr"/>
+      <c r="E26" s="47" t="inlineStr"/>
+      <c r="F26" s="47" t="inlineStr"/>
+      <c r="G26" s="47" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="41" t="inlineStr">
+      <c r="A27" s="45" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B27" s="41" t="inlineStr">
+      <c r="B27" s="45" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1491,22 +1468,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURAContributi per sostenere la ripresa del settore della pescaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D27" s="42" t="inlineStr">
+      <c r="D27" s="46" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributi-per-sostenere-la-ripresa-del-settore-della-pesca/</t>
         </is>
       </c>
-      <c r="E27" s="41" t="inlineStr"/>
-      <c r="F27" s="41" t="inlineStr"/>
-      <c r="G27" s="41" t="inlineStr"/>
+      <c r="E27" s="45" t="inlineStr"/>
+      <c r="F27" s="45" t="inlineStr"/>
+      <c r="G27" s="45" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="43" t="inlineStr">
+      <c r="A28" s="47" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B28" s="43" t="inlineStr">
+      <c r="B28" s="47" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1516,30 +1493,30 @@
           <t>Manifestazioni di interesseAVVISO - Manifestazione Interesse “Storytelling aziendale” Expo Wild Natura - Caccia - Pesca. Misterbianco (CT), 10-12 apri</t>
         </is>
       </c>
-      <c r="D28" s="44" t="inlineStr">
+      <c r="D28" s="48" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-storytelling-aziendale-expo-wild-natura-caccia-pesca-misterbianco-ct-10-12-aprile-2026</t>
         </is>
       </c>
-      <c r="E28" s="43" t="inlineStr">
+      <c r="E28" s="47" t="inlineStr">
         <is>
           <t>30/03/2026 - 13:00</t>
         </is>
       </c>
-      <c r="F28" s="43" t="inlineStr">
+      <c r="F28" s="47" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G28" s="43" t="inlineStr"/>
+      <c r="G28" s="47" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="41" t="inlineStr">
+      <c r="A29" s="45" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B29" s="41" t="inlineStr">
+      <c r="B29" s="45" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1549,30 +1526,30 @@
           <t>Manifestazioni di interesseInvaso Lentini - Interventi di ripristino delle pareti esterne in cls della Torre di presa Sud e della trave d’appoggio del</t>
         </is>
       </c>
-      <c r="D29" s="42" t="inlineStr">
+      <c r="D29" s="46" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/invaso-lentini-interventi-ripristino-pareti-esterne-cls-torre-presa-sud-trave-d-appoggio-cavalcavia-collegamento-alla-stessa-torre</t>
         </is>
       </c>
-      <c r="E29" s="41" t="inlineStr">
+      <c r="E29" s="45" t="inlineStr">
         <is>
           <t>19/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F29" s="41" t="inlineStr">
+      <c r="F29" s="45" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G29" s="41" t="inlineStr"/>
+      <c r="G29" s="45" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="43" t="inlineStr">
+      <c r="A30" s="47" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="B30" s="43" t="inlineStr">
+      <c r="B30" s="47" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1582,22 +1559,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURARistrutturazione e riconversione vigneti – campagna 2026-2027ApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D30" s="44" t="inlineStr">
+      <c r="D30" s="48" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/ristrutturazione-e-riconversione-vigneti-campagna-2026-2027/</t>
         </is>
       </c>
-      <c r="E30" s="43" t="inlineStr"/>
-      <c r="F30" s="43" t="inlineStr"/>
-      <c r="G30" s="43" t="inlineStr"/>
+      <c r="E30" s="47" t="inlineStr"/>
+      <c r="F30" s="47" t="inlineStr"/>
+      <c r="G30" s="47" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="41" t="inlineStr">
+      <c r="A31" s="45" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="B31" s="41" t="inlineStr">
+      <c r="B31" s="45" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1607,30 +1584,30 @@
           <t>Manifestazioni di interessePR FESR 2021/27 Azione 1.3.3 e del POC 2014/20 - Azione 1.3.1  - Avviso a manifestazione d’interesse eventi fieristici inte</t>
         </is>
       </c>
-      <c r="D31" s="42" t="inlineStr">
+      <c r="D31" s="46" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-d-interesse-eventi-fieristici-internazionali-marzo-dicembre-2026</t>
         </is>
       </c>
-      <c r="E31" s="41" t="inlineStr">
+      <c r="E31" s="45" t="inlineStr">
         <is>
           <t>30/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F31" s="41" t="inlineStr">
+      <c r="F31" s="45" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="G31" s="41" t="inlineStr"/>
+      <c r="G31" s="45" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="43" t="inlineStr">
+      <c r="A32" s="47" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="B32" s="43" t="inlineStr">
+      <c r="B32" s="47" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1640,22 +1617,22 @@
           <t>INTERNAZIONALIZZAZIONEL’Ecosistema dell’Innovazione a INNOVIT – Focus S3ApertoFESR</t>
         </is>
       </c>
-      <c r="D32" s="44" t="inlineStr">
+      <c r="D32" s="48" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lecosistema-dellinnovazione-a-innovit-focus-s3/</t>
         </is>
       </c>
-      <c r="E32" s="43" t="inlineStr"/>
-      <c r="F32" s="43" t="inlineStr"/>
-      <c r="G32" s="43" t="inlineStr"/>
+      <c r="E32" s="47" t="inlineStr"/>
+      <c r="F32" s="47" t="inlineStr"/>
+      <c r="G32" s="47" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="41" t="inlineStr">
+      <c r="A33" s="45" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="B33" s="41" t="inlineStr">
+      <c r="B33" s="45" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1665,22 +1642,22 @@
           <t>Manifestazioni di interessePR FESR SICILIA 2021/27 - NUOVO Avviso a manifestazione d’interesse per esperti valutatoriScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D33" s="42" t="inlineStr">
+      <c r="D33" s="46" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/pr-fesr-sicilia-202127-nuovo-avviso-manifestazione-d-interesse-esperti-valutatori</t>
         </is>
       </c>
-      <c r="E33" s="41" t="inlineStr"/>
-      <c r="F33" s="41" t="inlineStr"/>
-      <c r="G33" s="41" t="inlineStr"/>
+      <c r="E33" s="45" t="inlineStr"/>
+      <c r="F33" s="45" t="inlineStr"/>
+      <c r="G33" s="45" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="43" t="inlineStr">
+      <c r="A34" s="47" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="B34" s="43" t="inlineStr">
+      <c r="B34" s="47" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -1690,22 +1667,22 @@
           <t>Bando 2026 per contributi dedicati alla manutenzione della rete dei percorsi escursionistici</t>
         </is>
       </c>
-      <c r="D34" s="44" t="inlineStr">
+      <c r="D34" s="48" t="inlineStr">
         <is>
           <t>https://ambiente.regione.emilia-romagna.it/it/parchi-natura2000/bandi/bando-2026-per-contributi-dedicati-alla-manutenzione-della-rete-dei-percorsi-escursionistici</t>
         </is>
       </c>
-      <c r="E34" s="43" t="inlineStr"/>
-      <c r="F34" s="43" t="inlineStr"/>
-      <c r="G34" s="43" t="inlineStr"/>
+      <c r="E34" s="47" t="inlineStr"/>
+      <c r="F34" s="47" t="inlineStr"/>
+      <c r="G34" s="47" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="41" t="inlineStr">
+      <c r="A35" s="45" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="B35" s="41" t="inlineStr">
+      <c r="B35" s="45" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1715,22 +1692,22 @@
           <t>Programma regionale in favore delle tradizioni storiche, artistiche, religiose e popolari (2026) – manifestazioni d’interesseApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D35" s="42" t="inlineStr">
+      <c r="D35" s="46" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/programma-regionale-in-favore-delle-tradizioni-storiche-artistiche-religiose-e-popolari-2026-manifestazioni-dinteresse/</t>
         </is>
       </c>
-      <c r="E35" s="41" t="inlineStr"/>
-      <c r="F35" s="41" t="inlineStr"/>
-      <c r="G35" s="41" t="inlineStr"/>
+      <c r="E35" s="45" t="inlineStr"/>
+      <c r="F35" s="45" t="inlineStr"/>
+      <c r="G35" s="45" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="43" t="inlineStr">
+      <c r="A36" s="47" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B36" s="43" t="inlineStr">
+      <c r="B36" s="47" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1740,22 +1717,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEBuoni servizio per le persone non autosufficienti nel territorio del LazioProssima AperturaFSE / FSE+</t>
         </is>
       </c>
-      <c r="D36" s="44" t="inlineStr">
+      <c r="D36" s="48" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/buoni-servizio-per-le-persone-non-autosufficienti-nel-territorio-del-lazio/</t>
         </is>
       </c>
-      <c r="E36" s="43" t="inlineStr"/>
-      <c r="F36" s="43" t="inlineStr"/>
-      <c r="G36" s="43" t="inlineStr"/>
+      <c r="E36" s="47" t="inlineStr"/>
+      <c r="F36" s="47" t="inlineStr"/>
+      <c r="G36" s="47" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="41" t="inlineStr">
+      <c r="A37" s="45" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B37" s="41" t="inlineStr">
+      <c r="B37" s="45" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1765,22 +1742,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONERimborso delle rette dei servizi educativi nel territorio del LazioProssima AperturaFSE / FSE+</t>
         </is>
       </c>
-      <c r="D37" s="42" t="inlineStr">
+      <c r="D37" s="46" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/rimborso-delle-rette-dei-servizi-educativi-nel-territorio-del-lazio/</t>
         </is>
       </c>
-      <c r="E37" s="41" t="inlineStr"/>
-      <c r="F37" s="41" t="inlineStr"/>
-      <c r="G37" s="41" t="inlineStr"/>
+      <c r="E37" s="45" t="inlineStr"/>
+      <c r="F37" s="45" t="inlineStr"/>
+      <c r="G37" s="45" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="43" t="inlineStr">
+      <c r="A38" s="47" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B38" s="43" t="inlineStr">
+      <c r="B38" s="47" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1790,30 +1767,30 @@
           <t>Manifestazioni di interesseATTO DI INTERPELLO PER L’AFFIDAMENTO DELL’INCARICO DI COLLAUDO STATICO DELLE STRUTTURE - Diga di Pietrarossa (Progetto ex C</t>
         </is>
       </c>
-      <c r="D38" s="44" t="inlineStr">
+      <c r="D38" s="48" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/atto-interpello-l-affidamento-incarico-collaudo-statico-strutture-diga-pietrarossa-progetto-ex-casmez-303219</t>
         </is>
       </c>
-      <c r="E38" s="43" t="inlineStr">
+      <c r="E38" s="47" t="inlineStr">
         <is>
           <t>27/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F38" s="43" t="inlineStr">
+      <c r="F38" s="47" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="G38" s="43" t="inlineStr"/>
+      <c r="G38" s="47" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="41" t="inlineStr">
+      <c r="A39" s="45" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B39" s="41" t="inlineStr">
+      <c r="B39" s="45" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1823,30 +1800,30 @@
           <t>Manifestazioni di interesseAvviso alle Case  Editrici della Regione siciliana per la partecipazione al Salone del Libro di Torino, 14-18  maggio 2026.</t>
         </is>
       </c>
-      <c r="D39" s="42" t="inlineStr">
+      <c r="D39" s="46" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/manifestazione-d-interesse-partecipare-al-xxxviii-salone-libro-torino-14-al-18-maggio-2026-attraverso-l-esposizione-pubblicazioni-presso-stand-assessorato-beni</t>
         </is>
       </c>
-      <c r="E39" s="41" t="inlineStr">
+      <c r="E39" s="45" t="inlineStr">
         <is>
           <t>30/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F39" s="41" t="inlineStr">
+      <c r="F39" s="45" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="G39" s="41" t="inlineStr"/>
+      <c r="G39" s="45" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="43" t="inlineStr">
+      <c r="A40" s="47" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B40" s="43" t="inlineStr">
+      <c r="B40" s="47" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1856,30 +1833,30 @@
           <t xml:space="preserve">Manifestazioni di interessePR FESR SICILIA 2021/27 - NUOVO Avviso a manifestazione d’interesse per esperti valutatoriScade il:06/04/2026 - 23:59Leggi </t>
         </is>
       </c>
-      <c r="D40" s="44" t="inlineStr">
+      <c r="D40" s="48" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/pr-fesr-sicilia-202127-nuovo-avviso-manifestazione-d-interesse-esperti-valutatori</t>
         </is>
       </c>
-      <c r="E40" s="43" t="inlineStr">
+      <c r="E40" s="47" t="inlineStr">
         <is>
           <t>06/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F40" s="43" t="inlineStr">
+      <c r="F40" s="47" t="inlineStr">
         <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="G40" s="43" t="inlineStr"/>
+      <c r="G40" s="47" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="41" t="inlineStr">
+      <c r="A41" s="45" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B41" s="41" t="inlineStr">
+      <c r="B41" s="45" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1889,22 +1866,22 @@
           <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D41" s="42" t="inlineStr">
+      <c r="D41" s="46" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
         </is>
       </c>
-      <c r="E41" s="41" t="inlineStr"/>
-      <c r="F41" s="41" t="inlineStr"/>
-      <c r="G41" s="41" t="inlineStr"/>
+      <c r="E41" s="45" t="inlineStr"/>
+      <c r="F41" s="45" t="inlineStr"/>
+      <c r="G41" s="45" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="43" t="inlineStr">
+      <c r="A42" s="47" t="inlineStr">
         <is>
           <t>24/03/2026</t>
         </is>
       </c>
-      <c r="B42" s="43" t="inlineStr">
+      <c r="B42" s="47" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -1914,22 +1891,22 @@
           <t>GAL del Ducato - Promozione di fiere agroalimentari e delle filiere del cibo – Bando per Enti pubblici (DU AS 05B)</t>
         </is>
       </c>
-      <c r="D42" s="44" t="inlineStr">
+      <c r="D42" s="48" t="inlineStr">
         <is>
           <t>https://agricoltura.regione.emilia-romagna.it/sviluppo-rurale-23-27/opportunita/bandi-gal/2026/du_as05b-promozione-di-fiere-agroalimentari-e-delle-filiere-del-cibo-bando-per-enti-pubblici</t>
         </is>
       </c>
-      <c r="E42" s="43" t="inlineStr"/>
-      <c r="F42" s="43" t="inlineStr"/>
-      <c r="G42" s="43" t="inlineStr"/>
+      <c r="E42" s="47" t="inlineStr"/>
+      <c r="F42" s="47" t="inlineStr"/>
+      <c r="G42" s="47" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="41" t="inlineStr">
+      <c r="A43" s="45" t="inlineStr">
         <is>
           <t>24/03/2026</t>
         </is>
       </c>
-      <c r="B43" s="41" t="inlineStr">
+      <c r="B43" s="45" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1939,30 +1916,30 @@
           <t>Manifestazioni di interesseAVVISO PUBBLICO PER MANIFESTAZIONE DI INTERESSE FINALIZZATA ALL'ASSEGNAZIONE DI SPAZI ESPOSITIVI (CORNER GRATUITI) ALL'INTE</t>
         </is>
       </c>
-      <c r="D43" s="42" t="inlineStr">
+      <c r="D43" s="46" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-manifestazione-interesse-finalizzata-all-assegnazione-spazi-espositivi-corner-gratuiti-all-interno-stand-istituzionale-dsrt-manifestazione</t>
         </is>
       </c>
-      <c r="E43" s="41" t="inlineStr">
+      <c r="E43" s="45" t="inlineStr">
         <is>
           <t>30/03/2026 - 13:00</t>
         </is>
       </c>
-      <c r="F43" s="41" t="inlineStr">
+      <c r="F43" s="45" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G43" s="41" t="inlineStr"/>
+      <c r="G43" s="45" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="43" t="inlineStr">
+      <c r="A44" s="47" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B44" s="43" t="inlineStr">
+      <c r="B44" s="47" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -1972,22 +1949,22 @@
           <t>Avviso per la concessione di contributi per eventi sportivi realizzati in Emilia-Romagna - Anno 2026</t>
         </is>
       </c>
-      <c r="D44" s="44" t="inlineStr">
+      <c r="D44" s="48" t="inlineStr">
         <is>
           <t>https://www.regione.emilia-romagna.it/sport/bandi/2026/bando-2026</t>
         </is>
       </c>
-      <c r="E44" s="43" t="inlineStr"/>
-      <c r="F44" s="43" t="inlineStr"/>
-      <c r="G44" s="43" t="inlineStr"/>
+      <c r="E44" s="47" t="inlineStr"/>
+      <c r="F44" s="47" t="inlineStr"/>
+      <c r="G44" s="47" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="41" t="inlineStr">
+      <c r="A45" s="45" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B45" s="41" t="inlineStr">
+      <c r="B45" s="45" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1997,22 +1974,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Street art 2026Prossima AperturaBandi Regionali</t>
         </is>
       </c>
-      <c r="D45" s="42" t="inlineStr">
+      <c r="D45" s="46" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lazio-street-art-2026/</t>
         </is>
       </c>
-      <c r="E45" s="41" t="inlineStr"/>
-      <c r="F45" s="41" t="inlineStr"/>
-      <c r="G45" s="41" t="inlineStr"/>
+      <c r="E45" s="45" t="inlineStr"/>
+      <c r="F45" s="45" t="inlineStr"/>
+      <c r="G45" s="45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="43" t="inlineStr">
+      <c r="A46" s="47" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B46" s="43" t="inlineStr">
+      <c r="B46" s="47" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2022,30 +1999,30 @@
           <t>Manifestazioni di interesseManifestazione di interesse per la partecipazione all’evento “R2I Italy 2026” – Bologna, 12-13/05/2026Scade il:03/04/2026 -</t>
         </is>
       </c>
-      <c r="D46" s="44" t="inlineStr">
+      <c r="D46" s="48" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/manifestazione-interesse-partecipazione-all-evento-r2i-italy-2026-bologna-12-13052026</t>
         </is>
       </c>
-      <c r="E46" s="43" t="inlineStr">
+      <c r="E46" s="47" t="inlineStr">
         <is>
           <t>03/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F46" s="43" t="inlineStr">
+      <c r="F46" s="47" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="G46" s="43" t="inlineStr"/>
+      <c r="G46" s="47" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="41" t="inlineStr">
+      <c r="A47" s="45" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B47" s="41" t="inlineStr">
+      <c r="B47" s="45" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2055,30 +2032,30 @@
           <t>Manifestazioni di interesseST SIRACUSA - AVVISO PER MANIFESTAZIONE DI INTERESSE - Selezione di n. 5 unità di personale internoScade il:20/04/2026 - 12</t>
         </is>
       </c>
-      <c r="D47" s="42" t="inlineStr">
+      <c r="D47" s="46" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/24-marzo-2026-st-siracusa-avviso-manifestazione-interesse-selezione-n-5-unita-personale-interno</t>
         </is>
       </c>
-      <c r="E47" s="41" t="inlineStr">
+      <c r="E47" s="45" t="inlineStr">
         <is>
           <t>20/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F47" s="41" t="inlineStr">
+      <c r="F47" s="45" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="G47" s="41" t="inlineStr"/>
+      <c r="G47" s="45" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="43" t="inlineStr">
+      <c r="A48" s="47" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B48" s="43" t="inlineStr">
+      <c r="B48" s="47" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2088,22 +2065,22 @@
           <t>Avvisi pubbliciRevoca dell’avviso di concessione a titolo gratuito del 16.12.2025 inerente all’immobile di seguito identificato e contestuale nuovo av</t>
         </is>
       </c>
-      <c r="D48" s="44" t="inlineStr">
+      <c r="D48" s="48" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/revoca-avviso-concessione-titolo-gratuito-16122025-inerente-all-immobile-seguito-identificato-contestuale-nuovo-avviso-concessione-titolo-oneroso-stesso-sito-nel</t>
         </is>
       </c>
-      <c r="E48" s="43" t="inlineStr">
+      <c r="E48" s="47" t="inlineStr">
         <is>
           <t>08/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F48" s="43" t="inlineStr">
+      <c r="F48" s="47" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="G48" s="43" t="inlineStr"/>
+      <c r="G48" s="47" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="45" t="inlineStr">
@@ -2162,6 +2139,31 @@
         </is>
       </c>
       <c r="G50" s="47" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="49" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="49" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0PRE-SEED 3.0ApertoFESR</t>
+        </is>
+      </c>
+      <c r="D51" s="50" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/pre-seed-3-0/</t>
+        </is>
+      </c>
+      <c r="E51" s="49" t="inlineStr"/>
+      <c r="F51" s="49" t="inlineStr"/>
+      <c r="G51" s="49" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2214,6 +2216,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId50"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2258,7 +2261,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="45" t="inlineStr">
+      <c r="A3" s="49" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2267,24 +2270,24 @@
         <v>5</v>
       </c>
       <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="51" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="C4" s="7" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="47" t="inlineStr">
-        <is>
-          <t>Lazio</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="C4" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
     <row r="5">
-      <c r="A5" s="45" t="inlineStr">
+      <c r="A5" s="49" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2293,7 +2296,7 @@
         <v>22</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">

--- a/data/bandi_export.xlsx
+++ b/data/bandi_export.xlsx
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -267,6 +267,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -634,7 +646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -649,7 +661,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏛️  Nuovi Bandi — 27/03/2026 07:56</t>
+          <t>🏛️  Nuovi Bandi — 28/03/2026 07:40</t>
         </is>
       </c>
     </row>
@@ -694,24 +706,187 @@
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="49" t="inlineStr">
-        <is>
-          <t>Lazio</t>
+      <c r="B3" s="52" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0PRE-SEED 3.0ApertoFESR</t>
-        </is>
-      </c>
-      <c r="D3" s="50" t="inlineStr">
-        <is>
-          <t>https://www.lazioeuropa.it/bandi/pre-seed-3-0/</t>
-        </is>
-      </c>
-      <c r="E3" s="49" t="inlineStr"/>
-      <c r="F3" s="49" t="inlineStr"/>
+          <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “So</t>
+        </is>
+      </c>
+      <c r="D3" s="53" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-termini-imerese-locta-piazza-marina</t>
+        </is>
+      </c>
+      <c r="E3" s="52" t="inlineStr">
+        <is>
+          <t>26/04/2026 - 12:00</t>
+        </is>
+      </c>
+      <c r="F3" s="52" t="inlineStr">
+        <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
       <c r="G3" s="5" t="inlineStr"/>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="54" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, Sig</t>
+        </is>
+      </c>
+      <c r="D4" s="55" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-porto-empedocle-locta-punta-piccola</t>
+        </is>
+      </c>
+      <c r="E4" s="54" t="inlineStr">
+        <is>
+          <t>26/04/2026 - 12:00</t>
+        </is>
+      </c>
+      <c r="F4" s="54" t="inlineStr">
+        <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr"/>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="52" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “Società </t>
+        </is>
+      </c>
+      <c r="D5" s="53" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-messina-locta-torrente-bordonaro</t>
+        </is>
+      </c>
+      <c r="E5" s="52" t="inlineStr">
+        <is>
+          <t>26/04/2026 - 12:00</t>
+        </is>
+      </c>
+      <c r="F5" s="52" t="inlineStr">
+        <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="54" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “Condomin</t>
+        </is>
+      </c>
+      <c r="D6" s="55" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-mascali-spiaggia-n-144150</t>
+        </is>
+      </c>
+      <c r="E6" s="54" t="inlineStr">
+        <is>
+          <t>26/04/2026 - 12:00</t>
+        </is>
+      </c>
+      <c r="F6" s="54" t="inlineStr">
+        <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr"/>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="52" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione sito nel Comune di Lipari, isola di Stromboli, </t>
+        </is>
+      </c>
+      <c r="D7" s="53" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-lipari-isola-stromboli-locta-fico-grande</t>
+        </is>
+      </c>
+      <c r="E7" s="52" t="inlineStr">
+        <is>
+          <t>26/04/2026 - 12:00</t>
+        </is>
+      </c>
+      <c r="F7" s="52" t="inlineStr">
+        <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="54" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione sito nel Comune di Favignana, isola di Le</t>
+        </is>
+      </c>
+      <c r="D8" s="55" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-favignana-isola-levanzo</t>
+        </is>
+      </c>
+      <c r="E8" s="54" t="inlineStr">
+        <is>
+          <t>26/04/2026 - 12:00</t>
+        </is>
+      </c>
+      <c r="F8" s="54" t="inlineStr">
+        <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -719,6 +894,11 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -730,7 +910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -780,12 +960,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="47" t="inlineStr">
+      <c r="A2" s="51" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B2" s="47" t="inlineStr">
+      <c r="B2" s="51" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -800,17 +980,17 @@
           <t>https://agricoltura.regione.emilia-romagna.it/feampa-2021-2027/bandi-galpa/2026/galpa-sostituzione-motori-secondo-bando</t>
         </is>
       </c>
-      <c r="E2" s="47" t="inlineStr"/>
-      <c r="F2" s="47" t="inlineStr"/>
-      <c r="G2" s="47" t="inlineStr"/>
+      <c r="E2" s="51" t="inlineStr"/>
+      <c r="F2" s="51" t="inlineStr"/>
+      <c r="G2" s="51" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="45" t="inlineStr">
+      <c r="A3" s="49" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B3" s="45" t="inlineStr">
+      <c r="B3" s="49" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -820,22 +1000,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0PRE-SEED 3.0Prossima AperturaFESR</t>
         </is>
       </c>
-      <c r="D3" s="46" t="inlineStr">
+      <c r="D3" s="50" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/pre-seed-3-0/</t>
         </is>
       </c>
-      <c r="E3" s="45" t="inlineStr"/>
-      <c r="F3" s="45" t="inlineStr"/>
-      <c r="G3" s="45" t="inlineStr"/>
+      <c r="E3" s="49" t="inlineStr"/>
+      <c r="F3" s="49" t="inlineStr"/>
+      <c r="G3" s="49" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="47" t="inlineStr">
+      <c r="A4" s="51" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B4" s="47" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -850,17 +1030,17 @@
           <t>https://www.lazioeuropa.it/bandi/contributo-su-finanziamenti-alle-imprese-del-lazio-erogati-su-provvista-bei/</t>
         </is>
       </c>
-      <c r="E4" s="47" t="inlineStr"/>
-      <c r="F4" s="47" t="inlineStr"/>
-      <c r="G4" s="47" t="inlineStr"/>
+      <c r="E4" s="51" t="inlineStr"/>
+      <c r="F4" s="51" t="inlineStr"/>
+      <c r="G4" s="51" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="45" t="inlineStr">
+      <c r="A5" s="49" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B5" s="45" t="inlineStr">
+      <c r="B5" s="49" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -870,22 +1050,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEIndividuazione degli enti iscritti al Registro unico nazionale del Terzo settoreApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D5" s="46" t="inlineStr">
+      <c r="D5" s="50" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/individuazione-degli-enti-iscritti-al-registro-unico-nazionale-del-terzo-settore/</t>
         </is>
       </c>
-      <c r="E5" s="45" t="inlineStr"/>
-      <c r="F5" s="45" t="inlineStr"/>
-      <c r="G5" s="45" t="inlineStr"/>
+      <c r="E5" s="49" t="inlineStr"/>
+      <c r="F5" s="49" t="inlineStr"/>
+      <c r="G5" s="49" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="47" t="inlineStr">
+      <c r="A6" s="51" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B6" s="47" t="inlineStr">
+      <c r="B6" s="51" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -900,17 +1080,17 @@
           <t>https://www.lazioeuropa.it/bandi/technology-transfer-lazio/</t>
         </is>
       </c>
-      <c r="E6" s="47" t="inlineStr"/>
-      <c r="F6" s="47" t="inlineStr"/>
-      <c r="G6" s="47" t="inlineStr"/>
+      <c r="E6" s="51" t="inlineStr"/>
+      <c r="F6" s="51" t="inlineStr"/>
+      <c r="G6" s="51" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="45" t="inlineStr">
+      <c r="A7" s="49" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B7" s="45" t="inlineStr">
+      <c r="B7" s="49" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -920,22 +1100,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Percorso di tutoraggio per le impreseApertoFESR</t>
         </is>
       </c>
-      <c r="D7" s="46" t="inlineStr">
+      <c r="D7" s="50" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/percorso-di-tutoraggio-per-le-imprese/</t>
         </is>
       </c>
-      <c r="E7" s="45" t="inlineStr"/>
-      <c r="F7" s="45" t="inlineStr"/>
-      <c r="G7" s="45" t="inlineStr"/>
+      <c r="E7" s="49" t="inlineStr"/>
+      <c r="F7" s="49" t="inlineStr"/>
+      <c r="G7" s="49" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="47" t="inlineStr">
+      <c r="A8" s="51" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B8" s="47" t="inlineStr">
+      <c r="B8" s="51" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -950,17 +1130,17 @@
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-partecipare-a-smau-parigi-2026/</t>
         </is>
       </c>
-      <c r="E8" s="47" t="inlineStr"/>
-      <c r="F8" s="47" t="inlineStr"/>
-      <c r="G8" s="47" t="inlineStr"/>
+      <c r="E8" s="51" t="inlineStr"/>
+      <c r="F8" s="51" t="inlineStr"/>
+      <c r="G8" s="51" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="45" t="inlineStr">
+      <c r="A9" s="49" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B9" s="45" t="inlineStr">
+      <c r="B9" s="49" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -970,22 +1150,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONERiconoscimento della funzione sociale ed educativa degli oratoriApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D9" s="46" t="inlineStr">
+      <c r="D9" s="50" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/riconoscimento-della-funzione-sociale-ed-educativa-degli-oratori/</t>
         </is>
       </c>
-      <c r="E9" s="45" t="inlineStr"/>
-      <c r="F9" s="45" t="inlineStr"/>
-      <c r="G9" s="45" t="inlineStr"/>
+      <c r="E9" s="49" t="inlineStr"/>
+      <c r="F9" s="49" t="inlineStr"/>
+      <c r="G9" s="49" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="47" t="inlineStr">
+      <c r="A10" s="51" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B10" s="47" t="inlineStr">
+      <c r="B10" s="51" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1000,17 +1180,17 @@
           <t>https://www.lazioeuropa.it/bandi/iscrizione-nellelenco-regionale-degli-idonei-allesercizio-dellattivita-di-direttore-dellistituto-jemolo/</t>
         </is>
       </c>
-      <c r="E10" s="47" t="inlineStr"/>
-      <c r="F10" s="47" t="inlineStr"/>
-      <c r="G10" s="47" t="inlineStr"/>
+      <c r="E10" s="51" t="inlineStr"/>
+      <c r="F10" s="51" t="inlineStr"/>
+      <c r="G10" s="51" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="45" t="inlineStr">
+      <c r="A11" s="49" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B11" s="45" t="inlineStr">
+      <c r="B11" s="49" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1020,22 +1200,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEVoucher per lo sport – seconda annualitàApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D11" s="46" t="inlineStr">
+      <c r="D11" s="50" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/voucher-per-lo-sport-seconda-annualita/</t>
         </is>
       </c>
-      <c r="E11" s="45" t="inlineStr"/>
-      <c r="F11" s="45" t="inlineStr"/>
-      <c r="G11" s="45" t="inlineStr"/>
+      <c r="E11" s="49" t="inlineStr"/>
+      <c r="F11" s="49" t="inlineStr"/>
+      <c r="G11" s="49" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="47" t="inlineStr">
+      <c r="A12" s="51" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B12" s="47" t="inlineStr">
+      <c r="B12" s="51" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1050,17 +1230,17 @@
           <t>https://www.lazioeuropa.it/bandi/bonus-occupazionale-salgo/</t>
         </is>
       </c>
-      <c r="E12" s="47" t="inlineStr"/>
-      <c r="F12" s="47" t="inlineStr"/>
-      <c r="G12" s="47" t="inlineStr"/>
+      <c r="E12" s="51" t="inlineStr"/>
+      <c r="F12" s="51" t="inlineStr"/>
+      <c r="G12" s="51" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="45" t="inlineStr">
+      <c r="A13" s="49" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B13" s="45" t="inlineStr">
+      <c r="B13" s="49" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1070,22 +1250,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEContributo di Libertà per le donne che hanno subito violenzaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D13" s="46" t="inlineStr">
+      <c r="D13" s="50" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-di-liberta-per-le-donne-che-hanno-subito-violenza/</t>
         </is>
       </c>
-      <c r="E13" s="45" t="inlineStr"/>
-      <c r="F13" s="45" t="inlineStr"/>
-      <c r="G13" s="45" t="inlineStr"/>
+      <c r="E13" s="49" t="inlineStr"/>
+      <c r="F13" s="49" t="inlineStr"/>
+      <c r="G13" s="49" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="47" t="inlineStr">
+      <c r="A14" s="51" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B14" s="47" t="inlineStr">
+      <c r="B14" s="51" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1100,17 +1280,17 @@
           <t>https://www.lazioeuropa.it/bandi/interventi-straordinari-di-valorizzazione-del-patrimonio-culturale-del-lazio/</t>
         </is>
       </c>
-      <c r="E14" s="47" t="inlineStr"/>
-      <c r="F14" s="47" t="inlineStr"/>
-      <c r="G14" s="47" t="inlineStr"/>
+      <c r="E14" s="51" t="inlineStr"/>
+      <c r="F14" s="51" t="inlineStr"/>
+      <c r="G14" s="51" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="45" t="inlineStr">
+      <c r="A15" s="49" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B15" s="45" t="inlineStr">
+      <c r="B15" s="49" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1120,30 +1300,30 @@
           <t>Bandi di garaBANDO ATTUAZIONE Ob. 1.1 Azione 1 codice 111102 _DIV - "SOSTEGNO ALLA DIVERSIFICAZIONE E NUOVE FORME DI REDDITO PER LA PICCOLA PESCA COST</t>
         </is>
       </c>
-      <c r="D15" s="46" t="inlineStr">
+      <c r="D15" s="50" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/bando-avviso-regia-ob-11-azione-1-codice-111102-div-sostegno-alla-diversificazione-nuove-forme-reddito-piccola-pesca-costiera</t>
         </is>
       </c>
-      <c r="E15" s="45" t="inlineStr">
+      <c r="E15" s="49" t="inlineStr">
         <is>
           <t>07/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F15" s="45" t="inlineStr">
+      <c r="F15" s="49" t="inlineStr">
         <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="G15" s="45" t="inlineStr"/>
+      <c r="G15" s="49" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="47" t="inlineStr">
+      <c r="A16" s="51" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B16" s="47" t="inlineStr">
+      <c r="B16" s="51" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1158,25 +1338,25 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/09-marzo-2026-st-siracusa-avviso-pubblico-costituzione-elenchi-operatori-economici-l-acquisizione-beni-servizi</t>
         </is>
       </c>
-      <c r="E16" s="47" t="inlineStr">
+      <c r="E16" s="51" t="inlineStr">
         <is>
           <t>31/12/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F16" s="47" t="inlineStr">
+      <c r="F16" s="51" t="inlineStr">
         <is>
           <t>31/12/2026</t>
         </is>
       </c>
-      <c r="G16" s="47" t="inlineStr"/>
+      <c r="G16" s="51" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="45" t="inlineStr">
+      <c r="A17" s="49" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B17" s="45" t="inlineStr">
+      <c r="B17" s="49" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1186,30 +1366,30 @@
           <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScade il:19/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D17" s="46" t="inlineStr">
+      <c r="D17" s="50" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
         </is>
       </c>
-      <c r="E17" s="45" t="inlineStr">
+      <c r="E17" s="49" t="inlineStr">
         <is>
           <t>19/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F17" s="45" t="inlineStr">
+      <c r="F17" s="49" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G17" s="45" t="inlineStr"/>
+      <c r="G17" s="49" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="47" t="inlineStr">
+      <c r="A18" s="51" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B18" s="47" t="inlineStr">
+      <c r="B18" s="51" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1224,17 +1404,17 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-distributori-automatici-bevande-snack</t>
         </is>
       </c>
-      <c r="E18" s="47" t="inlineStr"/>
-      <c r="F18" s="47" t="inlineStr"/>
-      <c r="G18" s="47" t="inlineStr"/>
+      <c r="E18" s="51" t="inlineStr"/>
+      <c r="F18" s="51" t="inlineStr"/>
+      <c r="G18" s="51" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="45" t="inlineStr">
+      <c r="A19" s="49" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B19" s="45" t="inlineStr">
+      <c r="B19" s="49" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1244,30 +1424,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D19" s="46" t="inlineStr">
+      <c r="D19" s="50" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo</t>
         </is>
       </c>
-      <c r="E19" s="45" t="inlineStr">
+      <c r="E19" s="49" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F19" s="45" t="inlineStr">
+      <c r="F19" s="49" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G19" s="45" t="inlineStr"/>
+      <c r="G19" s="49" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="47" t="inlineStr">
+      <c r="A20" s="51" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B20" s="47" t="inlineStr">
+      <c r="B20" s="51" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1282,25 +1462,25 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo-0</t>
         </is>
       </c>
-      <c r="E20" s="47" t="inlineStr">
+      <c r="E20" s="51" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F20" s="47" t="inlineStr">
+      <c r="F20" s="51" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G20" s="47" t="inlineStr"/>
+      <c r="G20" s="51" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="45" t="inlineStr">
+      <c r="A21" s="49" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B21" s="45" t="inlineStr">
+      <c r="B21" s="49" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1310,22 +1490,22 @@
           <t>Manifestazioni di interesseST SIRACUSA - AVVISO DI MANIFESTAZIONE DI INTERESSE - Fornitura applicativo extracontabile per la gestione progetti, ecc. e</t>
         </is>
       </c>
-      <c r="D21" s="46" t="inlineStr">
+      <c r="D21" s="50" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-siracusa-avviso-manifestazione-interesse-fornitura-applicativo-extracontabile-gestione-progetti-ecc-applicativo-gestione-ed-elaborazione-informatizzata-paghe</t>
         </is>
       </c>
-      <c r="E21" s="45" t="inlineStr"/>
-      <c r="F21" s="45" t="inlineStr"/>
-      <c r="G21" s="45" t="inlineStr"/>
+      <c r="E21" s="49" t="inlineStr"/>
+      <c r="F21" s="49" t="inlineStr"/>
+      <c r="G21" s="49" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="47" t="inlineStr">
+      <c r="A22" s="51" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B22" s="47" t="inlineStr">
+      <c r="B22" s="51" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1340,25 +1520,25 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-sito-nel-comune-capo-d-orlando-trazzera-marina</t>
         </is>
       </c>
-      <c r="E22" s="47" t="inlineStr">
+      <c r="E22" s="51" t="inlineStr">
         <is>
           <t>25/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F22" s="47" t="inlineStr">
+      <c r="F22" s="51" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="G22" s="47" t="inlineStr"/>
+      <c r="G22" s="51" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="45" t="inlineStr">
+      <c r="A23" s="49" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B23" s="45" t="inlineStr">
+      <c r="B23" s="49" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1368,22 +1548,22 @@
           <t xml:space="preserve">Avvisi pubbliciST CATANIA - Programma Regionale FESR Sicilia 2021-2027 - Azione 2.4.4 - “Interventi per la riduzione del rischio incendi” - AVVISO DI </t>
         </is>
       </c>
-      <c r="D23" s="46" t="inlineStr">
+      <c r="D23" s="50" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-catania-programma-regionale-fesr-sicilia-2021-2027-azione-244-interventi-riduzione-rischio-incendi-avviso-indagine-mercato</t>
         </is>
       </c>
-      <c r="E23" s="45" t="inlineStr"/>
-      <c r="F23" s="45" t="inlineStr"/>
-      <c r="G23" s="45" t="inlineStr"/>
+      <c r="E23" s="49" t="inlineStr"/>
+      <c r="F23" s="49" t="inlineStr"/>
+      <c r="G23" s="49" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="47" t="inlineStr">
+      <c r="A24" s="51" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B24" s="47" t="inlineStr">
+      <c r="B24" s="51" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1398,17 +1578,17 @@
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-romics-primavera-2026/</t>
         </is>
       </c>
-      <c r="E24" s="47" t="inlineStr"/>
-      <c r="F24" s="47" t="inlineStr"/>
-      <c r="G24" s="47" t="inlineStr"/>
+      <c r="E24" s="51" t="inlineStr"/>
+      <c r="F24" s="51" t="inlineStr"/>
+      <c r="G24" s="51" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="45" t="inlineStr">
+      <c r="A25" s="49" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B25" s="45" t="inlineStr">
+      <c r="B25" s="49" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1418,22 +1598,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Cinema International 2026 – I edizioneApertoFESR</t>
         </is>
       </c>
-      <c r="D25" s="46" t="inlineStr">
+      <c r="D25" s="50" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lazio-cinema-international-2026-i-edizione/</t>
         </is>
       </c>
-      <c r="E25" s="45" t="inlineStr"/>
-      <c r="F25" s="45" t="inlineStr"/>
-      <c r="G25" s="45" t="inlineStr"/>
+      <c r="E25" s="49" t="inlineStr"/>
+      <c r="F25" s="49" t="inlineStr"/>
+      <c r="G25" s="49" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="47" t="inlineStr">
+      <c r="A26" s="51" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B26" s="47" t="inlineStr">
+      <c r="B26" s="51" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1448,17 +1628,17 @@
           <t>https://www.lazioeuropa.it/bandi/manifestazioni-di-interesse-alla-costituzione-di-due-nuove-fondazioni-i-t-s-academy/</t>
         </is>
       </c>
-      <c r="E26" s="47" t="inlineStr"/>
-      <c r="F26" s="47" t="inlineStr"/>
-      <c r="G26" s="47" t="inlineStr"/>
+      <c r="E26" s="51" t="inlineStr"/>
+      <c r="F26" s="51" t="inlineStr"/>
+      <c r="G26" s="51" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="45" t="inlineStr">
+      <c r="A27" s="49" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B27" s="45" t="inlineStr">
+      <c r="B27" s="49" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1468,22 +1648,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURAContributi per sostenere la ripresa del settore della pescaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D27" s="46" t="inlineStr">
+      <c r="D27" s="50" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributi-per-sostenere-la-ripresa-del-settore-della-pesca/</t>
         </is>
       </c>
-      <c r="E27" s="45" t="inlineStr"/>
-      <c r="F27" s="45" t="inlineStr"/>
-      <c r="G27" s="45" t="inlineStr"/>
+      <c r="E27" s="49" t="inlineStr"/>
+      <c r="F27" s="49" t="inlineStr"/>
+      <c r="G27" s="49" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="47" t="inlineStr">
+      <c r="A28" s="51" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B28" s="47" t="inlineStr">
+      <c r="B28" s="51" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1498,25 +1678,25 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-storytelling-aziendale-expo-wild-natura-caccia-pesca-misterbianco-ct-10-12-aprile-2026</t>
         </is>
       </c>
-      <c r="E28" s="47" t="inlineStr">
+      <c r="E28" s="51" t="inlineStr">
         <is>
           <t>30/03/2026 - 13:00</t>
         </is>
       </c>
-      <c r="F28" s="47" t="inlineStr">
+      <c r="F28" s="51" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G28" s="47" t="inlineStr"/>
+      <c r="G28" s="51" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="45" t="inlineStr">
+      <c r="A29" s="49" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B29" s="45" t="inlineStr">
+      <c r="B29" s="49" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1526,30 +1706,30 @@
           <t>Manifestazioni di interesseInvaso Lentini - Interventi di ripristino delle pareti esterne in cls della Torre di presa Sud e della trave d’appoggio del</t>
         </is>
       </c>
-      <c r="D29" s="46" t="inlineStr">
+      <c r="D29" s="50" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/invaso-lentini-interventi-ripristino-pareti-esterne-cls-torre-presa-sud-trave-d-appoggio-cavalcavia-collegamento-alla-stessa-torre</t>
         </is>
       </c>
-      <c r="E29" s="45" t="inlineStr">
+      <c r="E29" s="49" t="inlineStr">
         <is>
           <t>19/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F29" s="45" t="inlineStr">
+      <c r="F29" s="49" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G29" s="45" t="inlineStr"/>
+      <c r="G29" s="49" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="47" t="inlineStr">
+      <c r="A30" s="51" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="B30" s="47" t="inlineStr">
+      <c r="B30" s="51" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1564,17 +1744,17 @@
           <t>https://www.lazioeuropa.it/bandi/ristrutturazione-e-riconversione-vigneti-campagna-2026-2027/</t>
         </is>
       </c>
-      <c r="E30" s="47" t="inlineStr"/>
-      <c r="F30" s="47" t="inlineStr"/>
-      <c r="G30" s="47" t="inlineStr"/>
+      <c r="E30" s="51" t="inlineStr"/>
+      <c r="F30" s="51" t="inlineStr"/>
+      <c r="G30" s="51" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="45" t="inlineStr">
+      <c r="A31" s="49" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="B31" s="45" t="inlineStr">
+      <c r="B31" s="49" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1584,30 +1764,30 @@
           <t>Manifestazioni di interessePR FESR 2021/27 Azione 1.3.3 e del POC 2014/20 - Azione 1.3.1  - Avviso a manifestazione d’interesse eventi fieristici inte</t>
         </is>
       </c>
-      <c r="D31" s="46" t="inlineStr">
+      <c r="D31" s="50" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-d-interesse-eventi-fieristici-internazionali-marzo-dicembre-2026</t>
         </is>
       </c>
-      <c r="E31" s="45" t="inlineStr">
+      <c r="E31" s="49" t="inlineStr">
         <is>
           <t>30/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F31" s="45" t="inlineStr">
+      <c r="F31" s="49" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="G31" s="45" t="inlineStr"/>
+      <c r="G31" s="49" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="47" t="inlineStr">
+      <c r="A32" s="51" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="B32" s="47" t="inlineStr">
+      <c r="B32" s="51" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1622,17 +1802,17 @@
           <t>https://www.lazioeuropa.it/bandi/lecosistema-dellinnovazione-a-innovit-focus-s3/</t>
         </is>
       </c>
-      <c r="E32" s="47" t="inlineStr"/>
-      <c r="F32" s="47" t="inlineStr"/>
-      <c r="G32" s="47" t="inlineStr"/>
+      <c r="E32" s="51" t="inlineStr"/>
+      <c r="F32" s="51" t="inlineStr"/>
+      <c r="G32" s="51" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="45" t="inlineStr">
+      <c r="A33" s="49" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="B33" s="45" t="inlineStr">
+      <c r="B33" s="49" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1642,22 +1822,22 @@
           <t>Manifestazioni di interessePR FESR SICILIA 2021/27 - NUOVO Avviso a manifestazione d’interesse per esperti valutatoriScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D33" s="46" t="inlineStr">
+      <c r="D33" s="50" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/pr-fesr-sicilia-202127-nuovo-avviso-manifestazione-d-interesse-esperti-valutatori</t>
         </is>
       </c>
-      <c r="E33" s="45" t="inlineStr"/>
-      <c r="F33" s="45" t="inlineStr"/>
-      <c r="G33" s="45" t="inlineStr"/>
+      <c r="E33" s="49" t="inlineStr"/>
+      <c r="F33" s="49" t="inlineStr"/>
+      <c r="G33" s="49" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="47" t="inlineStr">
+      <c r="A34" s="51" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="B34" s="47" t="inlineStr">
+      <c r="B34" s="51" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -1672,17 +1852,17 @@
           <t>https://ambiente.regione.emilia-romagna.it/it/parchi-natura2000/bandi/bando-2026-per-contributi-dedicati-alla-manutenzione-della-rete-dei-percorsi-escursionistici</t>
         </is>
       </c>
-      <c r="E34" s="47" t="inlineStr"/>
-      <c r="F34" s="47" t="inlineStr"/>
-      <c r="G34" s="47" t="inlineStr"/>
+      <c r="E34" s="51" t="inlineStr"/>
+      <c r="F34" s="51" t="inlineStr"/>
+      <c r="G34" s="51" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="45" t="inlineStr">
+      <c r="A35" s="49" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="B35" s="45" t="inlineStr">
+      <c r="B35" s="49" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1692,22 +1872,22 @@
           <t>Programma regionale in favore delle tradizioni storiche, artistiche, religiose e popolari (2026) – manifestazioni d’interesseApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D35" s="46" t="inlineStr">
+      <c r="D35" s="50" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/programma-regionale-in-favore-delle-tradizioni-storiche-artistiche-religiose-e-popolari-2026-manifestazioni-dinteresse/</t>
         </is>
       </c>
-      <c r="E35" s="45" t="inlineStr"/>
-      <c r="F35" s="45" t="inlineStr"/>
-      <c r="G35" s="45" t="inlineStr"/>
+      <c r="E35" s="49" t="inlineStr"/>
+      <c r="F35" s="49" t="inlineStr"/>
+      <c r="G35" s="49" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="47" t="inlineStr">
+      <c r="A36" s="51" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B36" s="47" t="inlineStr">
+      <c r="B36" s="51" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1722,17 +1902,17 @@
           <t>https://www.lazioeuropa.it/bandi/buoni-servizio-per-le-persone-non-autosufficienti-nel-territorio-del-lazio/</t>
         </is>
       </c>
-      <c r="E36" s="47" t="inlineStr"/>
-      <c r="F36" s="47" t="inlineStr"/>
-      <c r="G36" s="47" t="inlineStr"/>
+      <c r="E36" s="51" t="inlineStr"/>
+      <c r="F36" s="51" t="inlineStr"/>
+      <c r="G36" s="51" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="45" t="inlineStr">
+      <c r="A37" s="49" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B37" s="45" t="inlineStr">
+      <c r="B37" s="49" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1742,22 +1922,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONERimborso delle rette dei servizi educativi nel territorio del LazioProssima AperturaFSE / FSE+</t>
         </is>
       </c>
-      <c r="D37" s="46" t="inlineStr">
+      <c r="D37" s="50" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/rimborso-delle-rette-dei-servizi-educativi-nel-territorio-del-lazio/</t>
         </is>
       </c>
-      <c r="E37" s="45" t="inlineStr"/>
-      <c r="F37" s="45" t="inlineStr"/>
-      <c r="G37" s="45" t="inlineStr"/>
+      <c r="E37" s="49" t="inlineStr"/>
+      <c r="F37" s="49" t="inlineStr"/>
+      <c r="G37" s="49" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="47" t="inlineStr">
+      <c r="A38" s="51" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B38" s="47" t="inlineStr">
+      <c r="B38" s="51" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1772,25 +1952,25 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/atto-interpello-l-affidamento-incarico-collaudo-statico-strutture-diga-pietrarossa-progetto-ex-casmez-303219</t>
         </is>
       </c>
-      <c r="E38" s="47" t="inlineStr">
+      <c r="E38" s="51" t="inlineStr">
         <is>
           <t>27/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F38" s="47" t="inlineStr">
+      <c r="F38" s="51" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="G38" s="47" t="inlineStr"/>
+      <c r="G38" s="51" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="45" t="inlineStr">
+      <c r="A39" s="49" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B39" s="45" t="inlineStr">
+      <c r="B39" s="49" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1800,30 +1980,30 @@
           <t>Manifestazioni di interesseAvviso alle Case  Editrici della Regione siciliana per la partecipazione al Salone del Libro di Torino, 14-18  maggio 2026.</t>
         </is>
       </c>
-      <c r="D39" s="46" t="inlineStr">
+      <c r="D39" s="50" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/manifestazione-d-interesse-partecipare-al-xxxviii-salone-libro-torino-14-al-18-maggio-2026-attraverso-l-esposizione-pubblicazioni-presso-stand-assessorato-beni</t>
         </is>
       </c>
-      <c r="E39" s="45" t="inlineStr">
+      <c r="E39" s="49" t="inlineStr">
         <is>
           <t>30/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F39" s="45" t="inlineStr">
+      <c r="F39" s="49" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="G39" s="45" t="inlineStr"/>
+      <c r="G39" s="49" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="47" t="inlineStr">
+      <c r="A40" s="51" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B40" s="47" t="inlineStr">
+      <c r="B40" s="51" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1838,25 +2018,25 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/pr-fesr-sicilia-202127-nuovo-avviso-manifestazione-d-interesse-esperti-valutatori</t>
         </is>
       </c>
-      <c r="E40" s="47" t="inlineStr">
+      <c r="E40" s="51" t="inlineStr">
         <is>
           <t>06/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F40" s="47" t="inlineStr">
+      <c r="F40" s="51" t="inlineStr">
         <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="G40" s="47" t="inlineStr"/>
+      <c r="G40" s="51" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="45" t="inlineStr">
+      <c r="A41" s="49" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B41" s="45" t="inlineStr">
+      <c r="B41" s="49" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1866,22 +2046,22 @@
           <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D41" s="46" t="inlineStr">
+      <c r="D41" s="50" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
         </is>
       </c>
-      <c r="E41" s="45" t="inlineStr"/>
-      <c r="F41" s="45" t="inlineStr"/>
-      <c r="G41" s="45" t="inlineStr"/>
+      <c r="E41" s="49" t="inlineStr"/>
+      <c r="F41" s="49" t="inlineStr"/>
+      <c r="G41" s="49" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="47" t="inlineStr">
+      <c r="A42" s="51" t="inlineStr">
         <is>
           <t>24/03/2026</t>
         </is>
       </c>
-      <c r="B42" s="47" t="inlineStr">
+      <c r="B42" s="51" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -1896,17 +2076,17 @@
           <t>https://agricoltura.regione.emilia-romagna.it/sviluppo-rurale-23-27/opportunita/bandi-gal/2026/du_as05b-promozione-di-fiere-agroalimentari-e-delle-filiere-del-cibo-bando-per-enti-pubblici</t>
         </is>
       </c>
-      <c r="E42" s="47" t="inlineStr"/>
-      <c r="F42" s="47" t="inlineStr"/>
-      <c r="G42" s="47" t="inlineStr"/>
+      <c r="E42" s="51" t="inlineStr"/>
+      <c r="F42" s="51" t="inlineStr"/>
+      <c r="G42" s="51" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="45" t="inlineStr">
+      <c r="A43" s="49" t="inlineStr">
         <is>
           <t>24/03/2026</t>
         </is>
       </c>
-      <c r="B43" s="45" t="inlineStr">
+      <c r="B43" s="49" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1916,30 +2096,30 @@
           <t>Manifestazioni di interesseAVVISO PUBBLICO PER MANIFESTAZIONE DI INTERESSE FINALIZZATA ALL'ASSEGNAZIONE DI SPAZI ESPOSITIVI (CORNER GRATUITI) ALL'INTE</t>
         </is>
       </c>
-      <c r="D43" s="46" t="inlineStr">
+      <c r="D43" s="50" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-manifestazione-interesse-finalizzata-all-assegnazione-spazi-espositivi-corner-gratuiti-all-interno-stand-istituzionale-dsrt-manifestazione</t>
         </is>
       </c>
-      <c r="E43" s="45" t="inlineStr">
+      <c r="E43" s="49" t="inlineStr">
         <is>
           <t>30/03/2026 - 13:00</t>
         </is>
       </c>
-      <c r="F43" s="45" t="inlineStr">
+      <c r="F43" s="49" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G43" s="45" t="inlineStr"/>
+      <c r="G43" s="49" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="47" t="inlineStr">
+      <c r="A44" s="51" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B44" s="47" t="inlineStr">
+      <c r="B44" s="51" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -1954,17 +2134,17 @@
           <t>https://www.regione.emilia-romagna.it/sport/bandi/2026/bando-2026</t>
         </is>
       </c>
-      <c r="E44" s="47" t="inlineStr"/>
-      <c r="F44" s="47" t="inlineStr"/>
-      <c r="G44" s="47" t="inlineStr"/>
+      <c r="E44" s="51" t="inlineStr"/>
+      <c r="F44" s="51" t="inlineStr"/>
+      <c r="G44" s="51" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="45" t="inlineStr">
+      <c r="A45" s="49" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B45" s="45" t="inlineStr">
+      <c r="B45" s="49" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1974,22 +2154,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Street art 2026Prossima AperturaBandi Regionali</t>
         </is>
       </c>
-      <c r="D45" s="46" t="inlineStr">
+      <c r="D45" s="50" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lazio-street-art-2026/</t>
         </is>
       </c>
-      <c r="E45" s="45" t="inlineStr"/>
-      <c r="F45" s="45" t="inlineStr"/>
-      <c r="G45" s="45" t="inlineStr"/>
+      <c r="E45" s="49" t="inlineStr"/>
+      <c r="F45" s="49" t="inlineStr"/>
+      <c r="G45" s="49" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="47" t="inlineStr">
+      <c r="A46" s="51" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B46" s="47" t="inlineStr">
+      <c r="B46" s="51" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2004,25 +2184,25 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/manifestazione-interesse-partecipazione-all-evento-r2i-italy-2026-bologna-12-13052026</t>
         </is>
       </c>
-      <c r="E46" s="47" t="inlineStr">
+      <c r="E46" s="51" t="inlineStr">
         <is>
           <t>03/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F46" s="47" t="inlineStr">
+      <c r="F46" s="51" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="G46" s="47" t="inlineStr"/>
+      <c r="G46" s="51" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="45" t="inlineStr">
+      <c r="A47" s="49" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B47" s="45" t="inlineStr">
+      <c r="B47" s="49" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2032,30 +2212,30 @@
           <t>Manifestazioni di interesseST SIRACUSA - AVVISO PER MANIFESTAZIONE DI INTERESSE - Selezione di n. 5 unità di personale internoScade il:20/04/2026 - 12</t>
         </is>
       </c>
-      <c r="D47" s="46" t="inlineStr">
+      <c r="D47" s="50" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/24-marzo-2026-st-siracusa-avviso-manifestazione-interesse-selezione-n-5-unita-personale-interno</t>
         </is>
       </c>
-      <c r="E47" s="45" t="inlineStr">
+      <c r="E47" s="49" t="inlineStr">
         <is>
           <t>20/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F47" s="45" t="inlineStr">
+      <c r="F47" s="49" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="G47" s="45" t="inlineStr"/>
+      <c r="G47" s="49" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="47" t="inlineStr">
+      <c r="A48" s="51" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B48" s="47" t="inlineStr">
+      <c r="B48" s="51" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2070,25 +2250,25 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/revoca-avviso-concessione-titolo-gratuito-16122025-inerente-all-immobile-seguito-identificato-contestuale-nuovo-avviso-concessione-titolo-oneroso-stesso-sito-nel</t>
         </is>
       </c>
-      <c r="E48" s="47" t="inlineStr">
+      <c r="E48" s="51" t="inlineStr">
         <is>
           <t>08/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F48" s="47" t="inlineStr">
+      <c r="F48" s="51" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="G48" s="47" t="inlineStr"/>
+      <c r="G48" s="51" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="45" t="inlineStr">
+      <c r="A49" s="49" t="inlineStr">
         <is>
           <t>26/03/2026</t>
         </is>
       </c>
-      <c r="B49" s="45" t="inlineStr">
+      <c r="B49" s="49" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2098,22 +2278,22 @@
           <t>Bando studi di fattibilità per fusioni di Comuni</t>
         </is>
       </c>
-      <c r="D49" s="46" t="inlineStr">
+      <c r="D49" s="50" t="inlineStr">
         <is>
           <t>https://www.regione.emilia-romagna.it/autonomie-locali/bandi/bando_studi_fattibilita_fusioni_comuni</t>
         </is>
       </c>
-      <c r="E49" s="45" t="inlineStr"/>
-      <c r="F49" s="45" t="inlineStr"/>
-      <c r="G49" s="45" t="inlineStr"/>
+      <c r="E49" s="49" t="inlineStr"/>
+      <c r="F49" s="49" t="inlineStr"/>
+      <c r="G49" s="49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="47" t="inlineStr">
+      <c r="A50" s="51" t="inlineStr">
         <is>
           <t>26/03/2026</t>
         </is>
       </c>
-      <c r="B50" s="47" t="inlineStr">
+      <c r="B50" s="51" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2128,17 +2308,17 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-selezione-interna-titoli-conferimento-po-professionali-ai-sensi-artt-19-20-21-ccrl-20222024-comparto-non-dirigenziale</t>
         </is>
       </c>
-      <c r="E50" s="47" t="inlineStr">
+      <c r="E50" s="51" t="inlineStr">
         <is>
           <t>30/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F50" s="47" t="inlineStr">
+      <c r="F50" s="51" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G50" s="47" t="inlineStr"/>
+      <c r="G50" s="51" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="49" t="inlineStr">
@@ -2164,6 +2344,204 @@
       <c r="E51" s="49" t="inlineStr"/>
       <c r="F51" s="49" t="inlineStr"/>
       <c r="G51" s="49" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="54" t="inlineStr">
+        <is>
+          <t>28/03/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="54" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “So</t>
+        </is>
+      </c>
+      <c r="D52" s="55" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-termini-imerese-locta-piazza-marina</t>
+        </is>
+      </c>
+      <c r="E52" s="54" t="inlineStr">
+        <is>
+          <t>26/04/2026 - 12:00</t>
+        </is>
+      </c>
+      <c r="F52" s="54" t="inlineStr">
+        <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="G52" s="54" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="52" t="inlineStr">
+        <is>
+          <t>28/03/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="52" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, Sig</t>
+        </is>
+      </c>
+      <c r="D53" s="53" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-porto-empedocle-locta-punta-piccola</t>
+        </is>
+      </c>
+      <c r="E53" s="52" t="inlineStr">
+        <is>
+          <t>26/04/2026 - 12:00</t>
+        </is>
+      </c>
+      <c r="F53" s="52" t="inlineStr">
+        <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="G53" s="52" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="54" t="inlineStr">
+        <is>
+          <t>28/03/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="54" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “Società </t>
+        </is>
+      </c>
+      <c r="D54" s="55" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-messina-locta-torrente-bordonaro</t>
+        </is>
+      </c>
+      <c r="E54" s="54" t="inlineStr">
+        <is>
+          <t>26/04/2026 - 12:00</t>
+        </is>
+      </c>
+      <c r="F54" s="54" t="inlineStr">
+        <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="G54" s="54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="52" t="inlineStr">
+        <is>
+          <t>28/03/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="52" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “Condomin</t>
+        </is>
+      </c>
+      <c r="D55" s="53" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-mascali-spiaggia-n-144150</t>
+        </is>
+      </c>
+      <c r="E55" s="52" t="inlineStr">
+        <is>
+          <t>26/04/2026 - 12:00</t>
+        </is>
+      </c>
+      <c r="F55" s="52" t="inlineStr">
+        <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="G55" s="52" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="54" t="inlineStr">
+        <is>
+          <t>28/03/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="54" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione sito nel Comune di Lipari, isola di Stromboli, </t>
+        </is>
+      </c>
+      <c r="D56" s="55" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-lipari-isola-stromboli-locta-fico-grande</t>
+        </is>
+      </c>
+      <c r="E56" s="54" t="inlineStr">
+        <is>
+          <t>26/04/2026 - 12:00</t>
+        </is>
+      </c>
+      <c r="F56" s="54" t="inlineStr">
+        <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="G56" s="54" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="52" t="inlineStr">
+        <is>
+          <t>28/03/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="52" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione sito nel Comune di Favignana, isola di Le</t>
+        </is>
+      </c>
+      <c r="D57" s="53" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-favignana-isola-levanzo</t>
+        </is>
+      </c>
+      <c r="E57" s="52" t="inlineStr">
+        <is>
+          <t>26/04/2026 - 12:00</t>
+        </is>
+      </c>
+      <c r="F57" s="52" t="inlineStr">
+        <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="G57" s="52" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2217,6 +2595,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId56"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2261,7 +2645,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="49" t="inlineStr">
+      <c r="A3" s="52" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2274,7 +2658,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="51" t="inlineStr">
+      <c r="A4" s="54" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2283,20 +2667,20 @@
         <v>23</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="49" t="inlineStr">
+      <c r="A5" s="52" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">

--- a/data/bandi_export.xlsx
+++ b/data/bandi_export.xlsx
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -267,6 +267,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -646,7 +658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -661,7 +673,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏛️  Nuovi Bandi — 28/03/2026 07:40</t>
+          <t>🏛️  Nuovi Bandi — 31/03/2026 08:04</t>
         </is>
       </c>
     </row>
@@ -706,29 +718,29 @@
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="52" t="inlineStr">
+      <c r="B3" s="56" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “So</t>
-        </is>
-      </c>
-      <c r="D3" s="53" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-termini-imerese-locta-piazza-marina</t>
-        </is>
-      </c>
-      <c r="E3" s="52" t="inlineStr">
-        <is>
-          <t>26/04/2026 - 12:00</t>
-        </is>
-      </c>
-      <c r="F3" s="52" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
+          <t>Manifestazioni di interesseAVVISO - Manifestazione d’interesse finalizzata alla selezione di organismi attuatori di piani di gestione locale della pic</t>
+        </is>
+      </c>
+      <c r="D3" s="57" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-d-interesse-finalizzata-alla-selezione-organismi-attuatori-piani-gestione-locale-piccola-pesca-costiera-nelle-gsa-regione-siciliana</t>
+        </is>
+      </c>
+      <c r="E3" s="56" t="inlineStr">
+        <is>
+          <t>29/04/2026 - 23:59</t>
+        </is>
+      </c>
+      <c r="F3" s="56" t="inlineStr">
+        <is>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr"/>
@@ -737,156 +749,32 @@
       <c r="A4" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="54" t="inlineStr">
+      <c r="B4" s="58" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, Sig</t>
-        </is>
-      </c>
-      <c r="D4" s="55" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-porto-empedocle-locta-punta-piccola</t>
-        </is>
-      </c>
-      <c r="E4" s="54" t="inlineStr">
-        <is>
-          <t>26/04/2026 - 12:00</t>
-        </is>
-      </c>
-      <c r="F4" s="54" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
+          <t>Avvisi pubbliciLeggi e scarica l'avvisoScade il:02/04/2026 - 12:00Leggi di più</t>
+        </is>
+      </c>
+      <c r="D4" s="59" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/proroga-termini-presentazione-candidature-po</t>
+        </is>
+      </c>
+      <c r="E4" s="58" t="inlineStr">
+        <is>
+          <t>02/04/2026 - 12:00</t>
+        </is>
+      </c>
+      <c r="F4" s="58" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="G4" s="9" t="inlineStr"/>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" s="52" t="inlineStr">
-        <is>
-          <t>Sicilia</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “Società </t>
-        </is>
-      </c>
-      <c r="D5" s="53" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-messina-locta-torrente-bordonaro</t>
-        </is>
-      </c>
-      <c r="E5" s="52" t="inlineStr">
-        <is>
-          <t>26/04/2026 - 12:00</t>
-        </is>
-      </c>
-      <c r="F5" s="52" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="54" t="inlineStr">
-        <is>
-          <t>Sicilia</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “Condomin</t>
-        </is>
-      </c>
-      <c r="D6" s="55" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-mascali-spiaggia-n-144150</t>
-        </is>
-      </c>
-      <c r="E6" s="54" t="inlineStr">
-        <is>
-          <t>26/04/2026 - 12:00</t>
-        </is>
-      </c>
-      <c r="F6" s="54" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr"/>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" s="52" t="inlineStr">
-        <is>
-          <t>Sicilia</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione sito nel Comune di Lipari, isola di Stromboli, </t>
-        </is>
-      </c>
-      <c r="D7" s="53" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-lipari-isola-stromboli-locta-fico-grande</t>
-        </is>
-      </c>
-      <c r="E7" s="52" t="inlineStr">
-        <is>
-          <t>26/04/2026 - 12:00</t>
-        </is>
-      </c>
-      <c r="F7" s="52" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" s="54" t="inlineStr">
-        <is>
-          <t>Sicilia</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione sito nel Comune di Favignana, isola di Le</t>
-        </is>
-      </c>
-      <c r="D8" s="55" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-favignana-isola-levanzo</t>
-        </is>
-      </c>
-      <c r="E8" s="54" t="inlineStr">
-        <is>
-          <t>26/04/2026 - 12:00</t>
-        </is>
-      </c>
-      <c r="F8" s="54" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="G8" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -895,10 +783,6 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -910,7 +794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -960,12 +844,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="51" t="inlineStr">
+      <c r="A2" s="54" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B2" s="51" t="inlineStr">
+      <c r="B2" s="54" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -975,22 +859,22 @@
           <t>FLAG GALPA Costa E-R. Sostituzione del motore principale e dei motori secondari. Secondo bando</t>
         </is>
       </c>
-      <c r="D2" s="48" t="inlineStr">
+      <c r="D2" s="55" t="inlineStr">
         <is>
           <t>https://agricoltura.regione.emilia-romagna.it/feampa-2021-2027/bandi-galpa/2026/galpa-sostituzione-motori-secondo-bando</t>
         </is>
       </c>
-      <c r="E2" s="51" t="inlineStr"/>
-      <c r="F2" s="51" t="inlineStr"/>
-      <c r="G2" s="51" t="inlineStr"/>
+      <c r="E2" s="54" t="inlineStr"/>
+      <c r="F2" s="54" t="inlineStr"/>
+      <c r="G2" s="54" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="49" t="inlineStr">
+      <c r="A3" s="52" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B3" s="49" t="inlineStr">
+      <c r="B3" s="52" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1000,22 +884,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0PRE-SEED 3.0Prossima AperturaFESR</t>
         </is>
       </c>
-      <c r="D3" s="50" t="inlineStr">
+      <c r="D3" s="53" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/pre-seed-3-0/</t>
         </is>
       </c>
-      <c r="E3" s="49" t="inlineStr"/>
-      <c r="F3" s="49" t="inlineStr"/>
-      <c r="G3" s="49" t="inlineStr"/>
+      <c r="E3" s="52" t="inlineStr"/>
+      <c r="F3" s="52" t="inlineStr"/>
+      <c r="G3" s="52" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="51" t="inlineStr">
+      <c r="A4" s="54" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B4" s="51" t="inlineStr">
+      <c r="B4" s="54" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1025,22 +909,22 @@
           <t>ACCESSO AL CREDITO E ALLE GARANZIE PER LE IMPRESEContributo su finanziamenti alle imprese del Lazio erogati su provvista BEIProssima AperturaFESR</t>
         </is>
       </c>
-      <c r="D4" s="48" t="inlineStr">
+      <c r="D4" s="55" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-su-finanziamenti-alle-imprese-del-lazio-erogati-su-provvista-bei/</t>
         </is>
       </c>
-      <c r="E4" s="51" t="inlineStr"/>
-      <c r="F4" s="51" t="inlineStr"/>
-      <c r="G4" s="51" t="inlineStr"/>
+      <c r="E4" s="54" t="inlineStr"/>
+      <c r="F4" s="54" t="inlineStr"/>
+      <c r="G4" s="54" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="49" t="inlineStr">
+      <c r="A5" s="52" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B5" s="49" t="inlineStr">
+      <c r="B5" s="52" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1050,22 +934,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEIndividuazione degli enti iscritti al Registro unico nazionale del Terzo settoreApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D5" s="50" t="inlineStr">
+      <c r="D5" s="53" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/individuazione-degli-enti-iscritti-al-registro-unico-nazionale-del-terzo-settore/</t>
         </is>
       </c>
-      <c r="E5" s="49" t="inlineStr"/>
-      <c r="F5" s="49" t="inlineStr"/>
-      <c r="G5" s="49" t="inlineStr"/>
+      <c r="E5" s="52" t="inlineStr"/>
+      <c r="F5" s="52" t="inlineStr"/>
+      <c r="G5" s="52" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="51" t="inlineStr">
+      <c r="A6" s="54" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B6" s="51" t="inlineStr">
+      <c r="B6" s="54" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1075,22 +959,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Technology Transfer LazioApertoFESR</t>
         </is>
       </c>
-      <c r="D6" s="48" t="inlineStr">
+      <c r="D6" s="55" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/technology-transfer-lazio/</t>
         </is>
       </c>
-      <c r="E6" s="51" t="inlineStr"/>
-      <c r="F6" s="51" t="inlineStr"/>
-      <c r="G6" s="51" t="inlineStr"/>
+      <c r="E6" s="54" t="inlineStr"/>
+      <c r="F6" s="54" t="inlineStr"/>
+      <c r="G6" s="54" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="49" t="inlineStr">
+      <c r="A7" s="52" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B7" s="49" t="inlineStr">
+      <c r="B7" s="52" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1100,22 +984,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Percorso di tutoraggio per le impreseApertoFESR</t>
         </is>
       </c>
-      <c r="D7" s="50" t="inlineStr">
+      <c r="D7" s="53" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/percorso-di-tutoraggio-per-le-imprese/</t>
         </is>
       </c>
-      <c r="E7" s="49" t="inlineStr"/>
-      <c r="F7" s="49" t="inlineStr"/>
-      <c r="G7" s="49" t="inlineStr"/>
+      <c r="E7" s="52" t="inlineStr"/>
+      <c r="F7" s="52" t="inlineStr"/>
+      <c r="G7" s="52" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="51" t="inlineStr">
+      <c r="A8" s="54" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B8" s="51" t="inlineStr">
+      <c r="B8" s="54" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1125,22 +1009,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per partecipare a SMAU Parigi 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D8" s="48" t="inlineStr">
+      <c r="D8" s="55" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-partecipare-a-smau-parigi-2026/</t>
         </is>
       </c>
-      <c r="E8" s="51" t="inlineStr"/>
-      <c r="F8" s="51" t="inlineStr"/>
-      <c r="G8" s="51" t="inlineStr"/>
+      <c r="E8" s="54" t="inlineStr"/>
+      <c r="F8" s="54" t="inlineStr"/>
+      <c r="G8" s="54" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="49" t="inlineStr">
+      <c r="A9" s="52" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B9" s="49" t="inlineStr">
+      <c r="B9" s="52" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1150,22 +1034,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONERiconoscimento della funzione sociale ed educativa degli oratoriApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D9" s="50" t="inlineStr">
+      <c r="D9" s="53" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/riconoscimento-della-funzione-sociale-ed-educativa-degli-oratori/</t>
         </is>
       </c>
-      <c r="E9" s="49" t="inlineStr"/>
-      <c r="F9" s="49" t="inlineStr"/>
-      <c r="G9" s="49" t="inlineStr"/>
+      <c r="E9" s="52" t="inlineStr"/>
+      <c r="F9" s="52" t="inlineStr"/>
+      <c r="G9" s="52" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="51" t="inlineStr">
+      <c r="A10" s="54" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B10" s="51" t="inlineStr">
+      <c r="B10" s="54" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1175,22 +1059,22 @@
           <t>GovernanceIscrizione nell’elenco regionale degli idonei all’esercizio dell’attività di direttore dell’Istituto JemoloApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D10" s="48" t="inlineStr">
+      <c r="D10" s="55" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/iscrizione-nellelenco-regionale-degli-idonei-allesercizio-dellattivita-di-direttore-dellistituto-jemolo/</t>
         </is>
       </c>
-      <c r="E10" s="51" t="inlineStr"/>
-      <c r="F10" s="51" t="inlineStr"/>
-      <c r="G10" s="51" t="inlineStr"/>
+      <c r="E10" s="54" t="inlineStr"/>
+      <c r="F10" s="54" t="inlineStr"/>
+      <c r="G10" s="54" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="49" t="inlineStr">
+      <c r="A11" s="52" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B11" s="49" t="inlineStr">
+      <c r="B11" s="52" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1200,22 +1084,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEVoucher per lo sport – seconda annualitàApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D11" s="50" t="inlineStr">
+      <c r="D11" s="53" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/voucher-per-lo-sport-seconda-annualita/</t>
         </is>
       </c>
-      <c r="E11" s="49" t="inlineStr"/>
-      <c r="F11" s="49" t="inlineStr"/>
-      <c r="G11" s="49" t="inlineStr"/>
+      <c r="E11" s="52" t="inlineStr"/>
+      <c r="F11" s="52" t="inlineStr"/>
+      <c r="G11" s="52" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="51" t="inlineStr">
+      <c r="A12" s="54" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B12" s="51" t="inlineStr">
+      <c r="B12" s="54" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1225,22 +1109,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEBonus occupazionale SALGOApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D12" s="48" t="inlineStr">
+      <c r="D12" s="55" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/bonus-occupazionale-salgo/</t>
         </is>
       </c>
-      <c r="E12" s="51" t="inlineStr"/>
-      <c r="F12" s="51" t="inlineStr"/>
-      <c r="G12" s="51" t="inlineStr"/>
+      <c r="E12" s="54" t="inlineStr"/>
+      <c r="F12" s="54" t="inlineStr"/>
+      <c r="G12" s="54" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="49" t="inlineStr">
+      <c r="A13" s="52" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B13" s="49" t="inlineStr">
+      <c r="B13" s="52" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1250,22 +1134,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEContributo di Libertà per le donne che hanno subito violenzaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D13" s="50" t="inlineStr">
+      <c r="D13" s="53" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-di-liberta-per-le-donne-che-hanno-subito-violenza/</t>
         </is>
       </c>
-      <c r="E13" s="49" t="inlineStr"/>
-      <c r="F13" s="49" t="inlineStr"/>
-      <c r="G13" s="49" t="inlineStr"/>
+      <c r="E13" s="52" t="inlineStr"/>
+      <c r="F13" s="52" t="inlineStr"/>
+      <c r="G13" s="52" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="51" t="inlineStr">
+      <c r="A14" s="54" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B14" s="51" t="inlineStr">
+      <c r="B14" s="54" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1275,22 +1159,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURAInterventi straordinari di valorizzazione del patrimonio culturale del LazioApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D14" s="48" t="inlineStr">
+      <c r="D14" s="55" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/interventi-straordinari-di-valorizzazione-del-patrimonio-culturale-del-lazio/</t>
         </is>
       </c>
-      <c r="E14" s="51" t="inlineStr"/>
-      <c r="F14" s="51" t="inlineStr"/>
-      <c r="G14" s="51" t="inlineStr"/>
+      <c r="E14" s="54" t="inlineStr"/>
+      <c r="F14" s="54" t="inlineStr"/>
+      <c r="G14" s="54" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="49" t="inlineStr">
+      <c r="A15" s="52" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B15" s="49" t="inlineStr">
+      <c r="B15" s="52" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1300,30 +1184,30 @@
           <t>Bandi di garaBANDO ATTUAZIONE Ob. 1.1 Azione 1 codice 111102 _DIV - "SOSTEGNO ALLA DIVERSIFICAZIONE E NUOVE FORME DI REDDITO PER LA PICCOLA PESCA COST</t>
         </is>
       </c>
-      <c r="D15" s="50" t="inlineStr">
+      <c r="D15" s="53" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/bando-avviso-regia-ob-11-azione-1-codice-111102-div-sostegno-alla-diversificazione-nuove-forme-reddito-piccola-pesca-costiera</t>
         </is>
       </c>
-      <c r="E15" s="49" t="inlineStr">
+      <c r="E15" s="52" t="inlineStr">
         <is>
           <t>07/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F15" s="49" t="inlineStr">
+      <c r="F15" s="52" t="inlineStr">
         <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="G15" s="49" t="inlineStr"/>
+      <c r="G15" s="52" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="51" t="inlineStr">
+      <c r="A16" s="54" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B16" s="51" t="inlineStr">
+      <c r="B16" s="54" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1333,30 +1217,30 @@
           <t>Avvisi pubblici09 marzo 2026 - ST SIRACUSA - AVVISO PUBBLICO PER LA COSTITUZIONE DI ELENCHI DI OPERATORI ECONOMICI PER L’ACQUISIZIONE DI BENI E SERVIZ</t>
         </is>
       </c>
-      <c r="D16" s="48" t="inlineStr">
+      <c r="D16" s="55" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/09-marzo-2026-st-siracusa-avviso-pubblico-costituzione-elenchi-operatori-economici-l-acquisizione-beni-servizi</t>
         </is>
       </c>
-      <c r="E16" s="51" t="inlineStr">
+      <c r="E16" s="54" t="inlineStr">
         <is>
           <t>31/12/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F16" s="51" t="inlineStr">
+      <c r="F16" s="54" t="inlineStr">
         <is>
           <t>31/12/2026</t>
         </is>
       </c>
-      <c r="G16" s="51" t="inlineStr"/>
+      <c r="G16" s="54" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="49" t="inlineStr">
+      <c r="A17" s="52" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B17" s="49" t="inlineStr">
+      <c r="B17" s="52" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1366,30 +1250,30 @@
           <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScade il:19/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D17" s="50" t="inlineStr">
+      <c r="D17" s="53" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
         </is>
       </c>
-      <c r="E17" s="49" t="inlineStr">
+      <c r="E17" s="52" t="inlineStr">
         <is>
           <t>19/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F17" s="49" t="inlineStr">
+      <c r="F17" s="52" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G17" s="49" t="inlineStr"/>
+      <c r="G17" s="52" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="51" t="inlineStr">
+      <c r="A18" s="54" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B18" s="51" t="inlineStr">
+      <c r="B18" s="54" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1399,22 +1283,22 @@
           <t>Manifestazioni di interesseAvviso Manifestazione Interesse DISTRIBUTORI AUTOMATICI di bevande e snackScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D18" s="48" t="inlineStr">
+      <c r="D18" s="55" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-distributori-automatici-bevande-snack</t>
         </is>
       </c>
-      <c r="E18" s="51" t="inlineStr"/>
-      <c r="F18" s="51" t="inlineStr"/>
-      <c r="G18" s="51" t="inlineStr"/>
+      <c r="E18" s="54" t="inlineStr"/>
+      <c r="F18" s="54" t="inlineStr"/>
+      <c r="G18" s="54" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="49" t="inlineStr">
+      <c r="A19" s="52" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B19" s="49" t="inlineStr">
+      <c r="B19" s="52" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1424,30 +1308,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D19" s="50" t="inlineStr">
+      <c r="D19" s="53" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo</t>
         </is>
       </c>
-      <c r="E19" s="49" t="inlineStr">
+      <c r="E19" s="52" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F19" s="49" t="inlineStr">
+      <c r="F19" s="52" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G19" s="49" t="inlineStr"/>
+      <c r="G19" s="52" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="51" t="inlineStr">
+      <c r="A20" s="54" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B20" s="51" t="inlineStr">
+      <c r="B20" s="54" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1457,30 +1341,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D20" s="48" t="inlineStr">
+      <c r="D20" s="55" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo-0</t>
         </is>
       </c>
-      <c r="E20" s="51" t="inlineStr">
+      <c r="E20" s="54" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F20" s="51" t="inlineStr">
+      <c r="F20" s="54" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G20" s="51" t="inlineStr"/>
+      <c r="G20" s="54" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="49" t="inlineStr">
+      <c r="A21" s="52" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B21" s="49" t="inlineStr">
+      <c r="B21" s="52" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1490,22 +1374,22 @@
           <t>Manifestazioni di interesseST SIRACUSA - AVVISO DI MANIFESTAZIONE DI INTERESSE - Fornitura applicativo extracontabile per la gestione progetti, ecc. e</t>
         </is>
       </c>
-      <c r="D21" s="50" t="inlineStr">
+      <c r="D21" s="53" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-siracusa-avviso-manifestazione-interesse-fornitura-applicativo-extracontabile-gestione-progetti-ecc-applicativo-gestione-ed-elaborazione-informatizzata-paghe</t>
         </is>
       </c>
-      <c r="E21" s="49" t="inlineStr"/>
-      <c r="F21" s="49" t="inlineStr"/>
-      <c r="G21" s="49" t="inlineStr"/>
+      <c r="E21" s="52" t="inlineStr"/>
+      <c r="F21" s="52" t="inlineStr"/>
+      <c r="G21" s="52" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="51" t="inlineStr">
+      <c r="A22" s="54" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B22" s="51" t="inlineStr">
+      <c r="B22" s="54" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1515,30 +1399,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile sito nel Comune di Capo D'Orlando, Via Trazzera MarinaScade il:25/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D22" s="48" t="inlineStr">
+      <c r="D22" s="55" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-sito-nel-comune-capo-d-orlando-trazzera-marina</t>
         </is>
       </c>
-      <c r="E22" s="51" t="inlineStr">
+      <c r="E22" s="54" t="inlineStr">
         <is>
           <t>25/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F22" s="51" t="inlineStr">
+      <c r="F22" s="54" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="G22" s="51" t="inlineStr"/>
+      <c r="G22" s="54" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="49" t="inlineStr">
+      <c r="A23" s="52" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B23" s="49" t="inlineStr">
+      <c r="B23" s="52" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1548,22 +1432,22 @@
           <t xml:space="preserve">Avvisi pubbliciST CATANIA - Programma Regionale FESR Sicilia 2021-2027 - Azione 2.4.4 - “Interventi per la riduzione del rischio incendi” - AVVISO DI </t>
         </is>
       </c>
-      <c r="D23" s="50" t="inlineStr">
+      <c r="D23" s="53" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-catania-programma-regionale-fesr-sicilia-2021-2027-azione-244-interventi-riduzione-rischio-incendi-avviso-indagine-mercato</t>
         </is>
       </c>
-      <c r="E23" s="49" t="inlineStr"/>
-      <c r="F23" s="49" t="inlineStr"/>
-      <c r="G23" s="49" t="inlineStr"/>
+      <c r="E23" s="52" t="inlineStr"/>
+      <c r="F23" s="52" t="inlineStr"/>
+      <c r="G23" s="52" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="51" t="inlineStr">
+      <c r="A24" s="54" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B24" s="51" t="inlineStr">
+      <c r="B24" s="54" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1573,22 +1457,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per ROMICS – Primavera 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D24" s="48" t="inlineStr">
+      <c r="D24" s="55" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-romics-primavera-2026/</t>
         </is>
       </c>
-      <c r="E24" s="51" t="inlineStr"/>
-      <c r="F24" s="51" t="inlineStr"/>
-      <c r="G24" s="51" t="inlineStr"/>
+      <c r="E24" s="54" t="inlineStr"/>
+      <c r="F24" s="54" t="inlineStr"/>
+      <c r="G24" s="54" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="49" t="inlineStr">
+      <c r="A25" s="52" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B25" s="49" t="inlineStr">
+      <c r="B25" s="52" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1598,22 +1482,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Cinema International 2026 – I edizioneApertoFESR</t>
         </is>
       </c>
-      <c r="D25" s="50" t="inlineStr">
+      <c r="D25" s="53" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lazio-cinema-international-2026-i-edizione/</t>
         </is>
       </c>
-      <c r="E25" s="49" t="inlineStr"/>
-      <c r="F25" s="49" t="inlineStr"/>
-      <c r="G25" s="49" t="inlineStr"/>
+      <c r="E25" s="52" t="inlineStr"/>
+      <c r="F25" s="52" t="inlineStr"/>
+      <c r="G25" s="52" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="51" t="inlineStr">
+      <c r="A26" s="54" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B26" s="51" t="inlineStr">
+      <c r="B26" s="54" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1623,22 +1507,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEManifestazioni di interesse alla costituzione di due nuove Fondazioni I.T.S. AcademyApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D26" s="48" t="inlineStr">
+      <c r="D26" s="55" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazioni-di-interesse-alla-costituzione-di-due-nuove-fondazioni-i-t-s-academy/</t>
         </is>
       </c>
-      <c r="E26" s="51" t="inlineStr"/>
-      <c r="F26" s="51" t="inlineStr"/>
-      <c r="G26" s="51" t="inlineStr"/>
+      <c r="E26" s="54" t="inlineStr"/>
+      <c r="F26" s="54" t="inlineStr"/>
+      <c r="G26" s="54" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="49" t="inlineStr">
+      <c r="A27" s="52" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B27" s="49" t="inlineStr">
+      <c r="B27" s="52" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1648,22 +1532,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURAContributi per sostenere la ripresa del settore della pescaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D27" s="50" t="inlineStr">
+      <c r="D27" s="53" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributi-per-sostenere-la-ripresa-del-settore-della-pesca/</t>
         </is>
       </c>
-      <c r="E27" s="49" t="inlineStr"/>
-      <c r="F27" s="49" t="inlineStr"/>
-      <c r="G27" s="49" t="inlineStr"/>
+      <c r="E27" s="52" t="inlineStr"/>
+      <c r="F27" s="52" t="inlineStr"/>
+      <c r="G27" s="52" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="51" t="inlineStr">
+      <c r="A28" s="54" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B28" s="51" t="inlineStr">
+      <c r="B28" s="54" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1673,30 +1557,30 @@
           <t>Manifestazioni di interesseAVVISO - Manifestazione Interesse “Storytelling aziendale” Expo Wild Natura - Caccia - Pesca. Misterbianco (CT), 10-12 apri</t>
         </is>
       </c>
-      <c r="D28" s="48" t="inlineStr">
+      <c r="D28" s="55" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-storytelling-aziendale-expo-wild-natura-caccia-pesca-misterbianco-ct-10-12-aprile-2026</t>
         </is>
       </c>
-      <c r="E28" s="51" t="inlineStr">
+      <c r="E28" s="54" t="inlineStr">
         <is>
           <t>30/03/2026 - 13:00</t>
         </is>
       </c>
-      <c r="F28" s="51" t="inlineStr">
+      <c r="F28" s="54" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G28" s="51" t="inlineStr"/>
+      <c r="G28" s="54" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="49" t="inlineStr">
+      <c r="A29" s="52" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B29" s="49" t="inlineStr">
+      <c r="B29" s="52" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1706,30 +1590,30 @@
           <t>Manifestazioni di interesseInvaso Lentini - Interventi di ripristino delle pareti esterne in cls della Torre di presa Sud e della trave d’appoggio del</t>
         </is>
       </c>
-      <c r="D29" s="50" t="inlineStr">
+      <c r="D29" s="53" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/invaso-lentini-interventi-ripristino-pareti-esterne-cls-torre-presa-sud-trave-d-appoggio-cavalcavia-collegamento-alla-stessa-torre</t>
         </is>
       </c>
-      <c r="E29" s="49" t="inlineStr">
+      <c r="E29" s="52" t="inlineStr">
         <is>
           <t>19/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F29" s="49" t="inlineStr">
+      <c r="F29" s="52" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G29" s="49" t="inlineStr"/>
+      <c r="G29" s="52" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="51" t="inlineStr">
+      <c r="A30" s="54" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="B30" s="51" t="inlineStr">
+      <c r="B30" s="54" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1739,22 +1623,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURARistrutturazione e riconversione vigneti – campagna 2026-2027ApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D30" s="48" t="inlineStr">
+      <c r="D30" s="55" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/ristrutturazione-e-riconversione-vigneti-campagna-2026-2027/</t>
         </is>
       </c>
-      <c r="E30" s="51" t="inlineStr"/>
-      <c r="F30" s="51" t="inlineStr"/>
-      <c r="G30" s="51" t="inlineStr"/>
+      <c r="E30" s="54" t="inlineStr"/>
+      <c r="F30" s="54" t="inlineStr"/>
+      <c r="G30" s="54" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="49" t="inlineStr">
+      <c r="A31" s="52" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="B31" s="49" t="inlineStr">
+      <c r="B31" s="52" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1764,30 +1648,30 @@
           <t>Manifestazioni di interessePR FESR 2021/27 Azione 1.3.3 e del POC 2014/20 - Azione 1.3.1  - Avviso a manifestazione d’interesse eventi fieristici inte</t>
         </is>
       </c>
-      <c r="D31" s="50" t="inlineStr">
+      <c r="D31" s="53" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-d-interesse-eventi-fieristici-internazionali-marzo-dicembre-2026</t>
         </is>
       </c>
-      <c r="E31" s="49" t="inlineStr">
+      <c r="E31" s="52" t="inlineStr">
         <is>
           <t>30/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F31" s="49" t="inlineStr">
+      <c r="F31" s="52" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="G31" s="49" t="inlineStr"/>
+      <c r="G31" s="52" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="51" t="inlineStr">
+      <c r="A32" s="54" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="B32" s="51" t="inlineStr">
+      <c r="B32" s="54" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1797,22 +1681,22 @@
           <t>INTERNAZIONALIZZAZIONEL’Ecosistema dell’Innovazione a INNOVIT – Focus S3ApertoFESR</t>
         </is>
       </c>
-      <c r="D32" s="48" t="inlineStr">
+      <c r="D32" s="55" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lecosistema-dellinnovazione-a-innovit-focus-s3/</t>
         </is>
       </c>
-      <c r="E32" s="51" t="inlineStr"/>
-      <c r="F32" s="51" t="inlineStr"/>
-      <c r="G32" s="51" t="inlineStr"/>
+      <c r="E32" s="54" t="inlineStr"/>
+      <c r="F32" s="54" t="inlineStr"/>
+      <c r="G32" s="54" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="49" t="inlineStr">
+      <c r="A33" s="52" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="B33" s="49" t="inlineStr">
+      <c r="B33" s="52" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1822,22 +1706,22 @@
           <t>Manifestazioni di interessePR FESR SICILIA 2021/27 - NUOVO Avviso a manifestazione d’interesse per esperti valutatoriScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D33" s="50" t="inlineStr">
+      <c r="D33" s="53" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/pr-fesr-sicilia-202127-nuovo-avviso-manifestazione-d-interesse-esperti-valutatori</t>
         </is>
       </c>
-      <c r="E33" s="49" t="inlineStr"/>
-      <c r="F33" s="49" t="inlineStr"/>
-      <c r="G33" s="49" t="inlineStr"/>
+      <c r="E33" s="52" t="inlineStr"/>
+      <c r="F33" s="52" t="inlineStr"/>
+      <c r="G33" s="52" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="51" t="inlineStr">
+      <c r="A34" s="54" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="B34" s="51" t="inlineStr">
+      <c r="B34" s="54" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -1847,22 +1731,22 @@
           <t>Bando 2026 per contributi dedicati alla manutenzione della rete dei percorsi escursionistici</t>
         </is>
       </c>
-      <c r="D34" s="48" t="inlineStr">
+      <c r="D34" s="55" t="inlineStr">
         <is>
           <t>https://ambiente.regione.emilia-romagna.it/it/parchi-natura2000/bandi/bando-2026-per-contributi-dedicati-alla-manutenzione-della-rete-dei-percorsi-escursionistici</t>
         </is>
       </c>
-      <c r="E34" s="51" t="inlineStr"/>
-      <c r="F34" s="51" t="inlineStr"/>
-      <c r="G34" s="51" t="inlineStr"/>
+      <c r="E34" s="54" t="inlineStr"/>
+      <c r="F34" s="54" t="inlineStr"/>
+      <c r="G34" s="54" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="49" t="inlineStr">
+      <c r="A35" s="52" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="B35" s="49" t="inlineStr">
+      <c r="B35" s="52" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1872,22 +1756,22 @@
           <t>Programma regionale in favore delle tradizioni storiche, artistiche, religiose e popolari (2026) – manifestazioni d’interesseApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D35" s="50" t="inlineStr">
+      <c r="D35" s="53" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/programma-regionale-in-favore-delle-tradizioni-storiche-artistiche-religiose-e-popolari-2026-manifestazioni-dinteresse/</t>
         </is>
       </c>
-      <c r="E35" s="49" t="inlineStr"/>
-      <c r="F35" s="49" t="inlineStr"/>
-      <c r="G35" s="49" t="inlineStr"/>
+      <c r="E35" s="52" t="inlineStr"/>
+      <c r="F35" s="52" t="inlineStr"/>
+      <c r="G35" s="52" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="51" t="inlineStr">
+      <c r="A36" s="54" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B36" s="51" t="inlineStr">
+      <c r="B36" s="54" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1897,22 +1781,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEBuoni servizio per le persone non autosufficienti nel territorio del LazioProssima AperturaFSE / FSE+</t>
         </is>
       </c>
-      <c r="D36" s="48" t="inlineStr">
+      <c r="D36" s="55" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/buoni-servizio-per-le-persone-non-autosufficienti-nel-territorio-del-lazio/</t>
         </is>
       </c>
-      <c r="E36" s="51" t="inlineStr"/>
-      <c r="F36" s="51" t="inlineStr"/>
-      <c r="G36" s="51" t="inlineStr"/>
+      <c r="E36" s="54" t="inlineStr"/>
+      <c r="F36" s="54" t="inlineStr"/>
+      <c r="G36" s="54" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="49" t="inlineStr">
+      <c r="A37" s="52" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B37" s="49" t="inlineStr">
+      <c r="B37" s="52" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1922,22 +1806,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONERimborso delle rette dei servizi educativi nel territorio del LazioProssima AperturaFSE / FSE+</t>
         </is>
       </c>
-      <c r="D37" s="50" t="inlineStr">
+      <c r="D37" s="53" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/rimborso-delle-rette-dei-servizi-educativi-nel-territorio-del-lazio/</t>
         </is>
       </c>
-      <c r="E37" s="49" t="inlineStr"/>
-      <c r="F37" s="49" t="inlineStr"/>
-      <c r="G37" s="49" t="inlineStr"/>
+      <c r="E37" s="52" t="inlineStr"/>
+      <c r="F37" s="52" t="inlineStr"/>
+      <c r="G37" s="52" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="51" t="inlineStr">
+      <c r="A38" s="54" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B38" s="51" t="inlineStr">
+      <c r="B38" s="54" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1947,30 +1831,30 @@
           <t>Manifestazioni di interesseATTO DI INTERPELLO PER L’AFFIDAMENTO DELL’INCARICO DI COLLAUDO STATICO DELLE STRUTTURE - Diga di Pietrarossa (Progetto ex C</t>
         </is>
       </c>
-      <c r="D38" s="48" t="inlineStr">
+      <c r="D38" s="55" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/atto-interpello-l-affidamento-incarico-collaudo-statico-strutture-diga-pietrarossa-progetto-ex-casmez-303219</t>
         </is>
       </c>
-      <c r="E38" s="51" t="inlineStr">
+      <c r="E38" s="54" t="inlineStr">
         <is>
           <t>27/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F38" s="51" t="inlineStr">
+      <c r="F38" s="54" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="G38" s="51" t="inlineStr"/>
+      <c r="G38" s="54" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="49" t="inlineStr">
+      <c r="A39" s="52" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B39" s="49" t="inlineStr">
+      <c r="B39" s="52" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1980,30 +1864,30 @@
           <t>Manifestazioni di interesseAvviso alle Case  Editrici della Regione siciliana per la partecipazione al Salone del Libro di Torino, 14-18  maggio 2026.</t>
         </is>
       </c>
-      <c r="D39" s="50" t="inlineStr">
+      <c r="D39" s="53" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/manifestazione-d-interesse-partecipare-al-xxxviii-salone-libro-torino-14-al-18-maggio-2026-attraverso-l-esposizione-pubblicazioni-presso-stand-assessorato-beni</t>
         </is>
       </c>
-      <c r="E39" s="49" t="inlineStr">
+      <c r="E39" s="52" t="inlineStr">
         <is>
           <t>30/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F39" s="49" t="inlineStr">
+      <c r="F39" s="52" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="G39" s="49" t="inlineStr"/>
+      <c r="G39" s="52" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="51" t="inlineStr">
+      <c r="A40" s="54" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B40" s="51" t="inlineStr">
+      <c r="B40" s="54" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2013,30 +1897,30 @@
           <t xml:space="preserve">Manifestazioni di interessePR FESR SICILIA 2021/27 - NUOVO Avviso a manifestazione d’interesse per esperti valutatoriScade il:06/04/2026 - 23:59Leggi </t>
         </is>
       </c>
-      <c r="D40" s="48" t="inlineStr">
+      <c r="D40" s="55" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/pr-fesr-sicilia-202127-nuovo-avviso-manifestazione-d-interesse-esperti-valutatori</t>
         </is>
       </c>
-      <c r="E40" s="51" t="inlineStr">
+      <c r="E40" s="54" t="inlineStr">
         <is>
           <t>06/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F40" s="51" t="inlineStr">
+      <c r="F40" s="54" t="inlineStr">
         <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="G40" s="51" t="inlineStr"/>
+      <c r="G40" s="54" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="49" t="inlineStr">
+      <c r="A41" s="52" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B41" s="49" t="inlineStr">
+      <c r="B41" s="52" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2046,22 +1930,22 @@
           <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D41" s="50" t="inlineStr">
+      <c r="D41" s="53" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
         </is>
       </c>
-      <c r="E41" s="49" t="inlineStr"/>
-      <c r="F41" s="49" t="inlineStr"/>
-      <c r="G41" s="49" t="inlineStr"/>
+      <c r="E41" s="52" t="inlineStr"/>
+      <c r="F41" s="52" t="inlineStr"/>
+      <c r="G41" s="52" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="51" t="inlineStr">
+      <c r="A42" s="54" t="inlineStr">
         <is>
           <t>24/03/2026</t>
         </is>
       </c>
-      <c r="B42" s="51" t="inlineStr">
+      <c r="B42" s="54" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2071,22 +1955,22 @@
           <t>GAL del Ducato - Promozione di fiere agroalimentari e delle filiere del cibo – Bando per Enti pubblici (DU AS 05B)</t>
         </is>
       </c>
-      <c r="D42" s="48" t="inlineStr">
+      <c r="D42" s="55" t="inlineStr">
         <is>
           <t>https://agricoltura.regione.emilia-romagna.it/sviluppo-rurale-23-27/opportunita/bandi-gal/2026/du_as05b-promozione-di-fiere-agroalimentari-e-delle-filiere-del-cibo-bando-per-enti-pubblici</t>
         </is>
       </c>
-      <c r="E42" s="51" t="inlineStr"/>
-      <c r="F42" s="51" t="inlineStr"/>
-      <c r="G42" s="51" t="inlineStr"/>
+      <c r="E42" s="54" t="inlineStr"/>
+      <c r="F42" s="54" t="inlineStr"/>
+      <c r="G42" s="54" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="49" t="inlineStr">
+      <c r="A43" s="52" t="inlineStr">
         <is>
           <t>24/03/2026</t>
         </is>
       </c>
-      <c r="B43" s="49" t="inlineStr">
+      <c r="B43" s="52" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2096,30 +1980,30 @@
           <t>Manifestazioni di interesseAVVISO PUBBLICO PER MANIFESTAZIONE DI INTERESSE FINALIZZATA ALL'ASSEGNAZIONE DI SPAZI ESPOSITIVI (CORNER GRATUITI) ALL'INTE</t>
         </is>
       </c>
-      <c r="D43" s="50" t="inlineStr">
+      <c r="D43" s="53" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-manifestazione-interesse-finalizzata-all-assegnazione-spazi-espositivi-corner-gratuiti-all-interno-stand-istituzionale-dsrt-manifestazione</t>
         </is>
       </c>
-      <c r="E43" s="49" t="inlineStr">
+      <c r="E43" s="52" t="inlineStr">
         <is>
           <t>30/03/2026 - 13:00</t>
         </is>
       </c>
-      <c r="F43" s="49" t="inlineStr">
+      <c r="F43" s="52" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G43" s="49" t="inlineStr"/>
+      <c r="G43" s="52" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="51" t="inlineStr">
+      <c r="A44" s="54" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B44" s="51" t="inlineStr">
+      <c r="B44" s="54" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2129,22 +2013,22 @@
           <t>Avviso per la concessione di contributi per eventi sportivi realizzati in Emilia-Romagna - Anno 2026</t>
         </is>
       </c>
-      <c r="D44" s="48" t="inlineStr">
+      <c r="D44" s="55" t="inlineStr">
         <is>
           <t>https://www.regione.emilia-romagna.it/sport/bandi/2026/bando-2026</t>
         </is>
       </c>
-      <c r="E44" s="51" t="inlineStr"/>
-      <c r="F44" s="51" t="inlineStr"/>
-      <c r="G44" s="51" t="inlineStr"/>
+      <c r="E44" s="54" t="inlineStr"/>
+      <c r="F44" s="54" t="inlineStr"/>
+      <c r="G44" s="54" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="49" t="inlineStr">
+      <c r="A45" s="52" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B45" s="49" t="inlineStr">
+      <c r="B45" s="52" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2154,22 +2038,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Street art 2026Prossima AperturaBandi Regionali</t>
         </is>
       </c>
-      <c r="D45" s="50" t="inlineStr">
+      <c r="D45" s="53" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lazio-street-art-2026/</t>
         </is>
       </c>
-      <c r="E45" s="49" t="inlineStr"/>
-      <c r="F45" s="49" t="inlineStr"/>
-      <c r="G45" s="49" t="inlineStr"/>
+      <c r="E45" s="52" t="inlineStr"/>
+      <c r="F45" s="52" t="inlineStr"/>
+      <c r="G45" s="52" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="51" t="inlineStr">
+      <c r="A46" s="54" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B46" s="51" t="inlineStr">
+      <c r="B46" s="54" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2179,30 +2063,30 @@
           <t>Manifestazioni di interesseManifestazione di interesse per la partecipazione all’evento “R2I Italy 2026” – Bologna, 12-13/05/2026Scade il:03/04/2026 -</t>
         </is>
       </c>
-      <c r="D46" s="48" t="inlineStr">
+      <c r="D46" s="55" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/manifestazione-interesse-partecipazione-all-evento-r2i-italy-2026-bologna-12-13052026</t>
         </is>
       </c>
-      <c r="E46" s="51" t="inlineStr">
+      <c r="E46" s="54" t="inlineStr">
         <is>
           <t>03/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F46" s="51" t="inlineStr">
+      <c r="F46" s="54" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="G46" s="51" t="inlineStr"/>
+      <c r="G46" s="54" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="49" t="inlineStr">
+      <c r="A47" s="52" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B47" s="49" t="inlineStr">
+      <c r="B47" s="52" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2212,30 +2096,30 @@
           <t>Manifestazioni di interesseST SIRACUSA - AVVISO PER MANIFESTAZIONE DI INTERESSE - Selezione di n. 5 unità di personale internoScade il:20/04/2026 - 12</t>
         </is>
       </c>
-      <c r="D47" s="50" t="inlineStr">
+      <c r="D47" s="53" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/24-marzo-2026-st-siracusa-avviso-manifestazione-interesse-selezione-n-5-unita-personale-interno</t>
         </is>
       </c>
-      <c r="E47" s="49" t="inlineStr">
+      <c r="E47" s="52" t="inlineStr">
         <is>
           <t>20/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F47" s="49" t="inlineStr">
+      <c r="F47" s="52" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="G47" s="49" t="inlineStr"/>
+      <c r="G47" s="52" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="51" t="inlineStr">
+      <c r="A48" s="54" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B48" s="51" t="inlineStr">
+      <c r="B48" s="54" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2245,30 +2129,30 @@
           <t>Avvisi pubbliciRevoca dell’avviso di concessione a titolo gratuito del 16.12.2025 inerente all’immobile di seguito identificato e contestuale nuovo av</t>
         </is>
       </c>
-      <c r="D48" s="48" t="inlineStr">
+      <c r="D48" s="55" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/revoca-avviso-concessione-titolo-gratuito-16122025-inerente-all-immobile-seguito-identificato-contestuale-nuovo-avviso-concessione-titolo-oneroso-stesso-sito-nel</t>
         </is>
       </c>
-      <c r="E48" s="51" t="inlineStr">
+      <c r="E48" s="54" t="inlineStr">
         <is>
           <t>08/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F48" s="51" t="inlineStr">
+      <c r="F48" s="54" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="G48" s="51" t="inlineStr"/>
+      <c r="G48" s="54" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="49" t="inlineStr">
+      <c r="A49" s="52" t="inlineStr">
         <is>
           <t>26/03/2026</t>
         </is>
       </c>
-      <c r="B49" s="49" t="inlineStr">
+      <c r="B49" s="52" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2278,22 +2162,22 @@
           <t>Bando studi di fattibilità per fusioni di Comuni</t>
         </is>
       </c>
-      <c r="D49" s="50" t="inlineStr">
+      <c r="D49" s="53" t="inlineStr">
         <is>
           <t>https://www.regione.emilia-romagna.it/autonomie-locali/bandi/bando_studi_fattibilita_fusioni_comuni</t>
         </is>
       </c>
-      <c r="E49" s="49" t="inlineStr"/>
-      <c r="F49" s="49" t="inlineStr"/>
-      <c r="G49" s="49" t="inlineStr"/>
+      <c r="E49" s="52" t="inlineStr"/>
+      <c r="F49" s="52" t="inlineStr"/>
+      <c r="G49" s="52" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="51" t="inlineStr">
+      <c r="A50" s="54" t="inlineStr">
         <is>
           <t>26/03/2026</t>
         </is>
       </c>
-      <c r="B50" s="51" t="inlineStr">
+      <c r="B50" s="54" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2303,30 +2187,30 @@
           <t xml:space="preserve">Manifestazioni di interesseAvviso pubblico di selezione interna, per titoli, per il conferimento di PO e professionali, ai sensi degli artt. 19, 20 e </t>
         </is>
       </c>
-      <c r="D50" s="48" t="inlineStr">
+      <c r="D50" s="55" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-selezione-interna-titoli-conferimento-po-professionali-ai-sensi-artt-19-20-21-ccrl-20222024-comparto-non-dirigenziale</t>
         </is>
       </c>
-      <c r="E50" s="51" t="inlineStr">
+      <c r="E50" s="54" t="inlineStr">
         <is>
           <t>30/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F50" s="51" t="inlineStr">
+      <c r="F50" s="54" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G50" s="51" t="inlineStr"/>
+      <c r="G50" s="54" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="49" t="inlineStr">
+      <c r="A51" s="52" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="B51" s="49" t="inlineStr">
+      <c r="B51" s="52" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2336,14 +2220,14 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0PRE-SEED 3.0ApertoFESR</t>
         </is>
       </c>
-      <c r="D51" s="50" t="inlineStr">
+      <c r="D51" s="53" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/pre-seed-3-0/</t>
         </is>
       </c>
-      <c r="E51" s="49" t="inlineStr"/>
-      <c r="F51" s="49" t="inlineStr"/>
-      <c r="G51" s="49" t="inlineStr"/>
+      <c r="E51" s="52" t="inlineStr"/>
+      <c r="F51" s="52" t="inlineStr"/>
+      <c r="G51" s="52" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="54" t="inlineStr">
@@ -2542,6 +2426,72 @@
         </is>
       </c>
       <c r="G57" s="52" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="58" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="58" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>Manifestazioni di interesseAVVISO - Manifestazione d’interesse finalizzata alla selezione di organismi attuatori di piani di gestione locale della pic</t>
+        </is>
+      </c>
+      <c r="D58" s="59" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-d-interesse-finalizzata-alla-selezione-organismi-attuatori-piani-gestione-locale-piccola-pesca-costiera-nelle-gsa-regione-siciliana</t>
+        </is>
+      </c>
+      <c r="E58" s="58" t="inlineStr">
+        <is>
+          <t>29/04/2026 - 23:59</t>
+        </is>
+      </c>
+      <c r="F58" s="58" t="inlineStr">
+        <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="G58" s="58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="56" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="56" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>Avvisi pubbliciLeggi e scarica l'avvisoScade il:02/04/2026 - 12:00Leggi di più</t>
+        </is>
+      </c>
+      <c r="D59" s="57" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/proroga-termini-presentazione-candidature-po</t>
+        </is>
+      </c>
+      <c r="E59" s="56" t="inlineStr">
+        <is>
+          <t>02/04/2026 - 12:00</t>
+        </is>
+      </c>
+      <c r="F59" s="56" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="G59" s="56" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2601,6 +2551,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D59" r:id="rId58"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2645,7 +2597,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="52" t="inlineStr">
+      <c r="A3" s="56" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2658,7 +2610,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="54" t="inlineStr">
+      <c r="A4" s="58" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2671,16 +2623,16 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="52" t="inlineStr">
+      <c r="A5" s="56" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">

--- a/data/bandi_export.xlsx
+++ b/data/bandi_export.xlsx
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -267,6 +267,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -658,7 +670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -673,7 +685,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏛️  Nuovi Bandi — 31/03/2026 08:04</t>
+          <t>🏛️  Nuovi Bandi — 01/04/2026 08:11</t>
         </is>
       </c>
     </row>
@@ -718,63 +730,78 @@
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="56" t="inlineStr">
-        <is>
-          <t>Sicilia</t>
+      <c r="B3" s="60" t="inlineStr">
+        <is>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Manifestazioni di interesseAVVISO - Manifestazione d’interesse finalizzata alla selezione di organismi attuatori di piani di gestione locale della pic</t>
-        </is>
-      </c>
-      <c r="D3" s="57" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-d-interesse-finalizzata-alla-selezione-organismi-attuatori-piani-gestione-locale-piccola-pesca-costiera-nelle-gsa-regione-siciliana</t>
-        </is>
-      </c>
-      <c r="E3" s="56" t="inlineStr">
-        <is>
-          <t>29/04/2026 - 23:59</t>
-        </is>
-      </c>
-      <c r="F3" s="56" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
+          <t>INTERNAZIONALIZZAZIONESMAU – Italy RestartsUp in STOCCOLMAApertoFESR</t>
+        </is>
+      </c>
+      <c r="D3" s="61" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/smau-italy-restartsup-in-stoccolma/</t>
+        </is>
+      </c>
+      <c r="E3" s="60" t="inlineStr"/>
+      <c r="F3" s="60" t="inlineStr"/>
       <c r="G3" s="5" t="inlineStr"/>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="58" t="inlineStr">
-        <is>
-          <t>Sicilia</t>
+      <c r="B4" s="62" t="inlineStr">
+        <is>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>Avvisi pubbliciLeggi e scarica l'avvisoScade il:02/04/2026 - 12:00Leggi di più</t>
-        </is>
-      </c>
-      <c r="D4" s="59" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/proroga-termini-presentazione-candidature-po</t>
-        </is>
-      </c>
-      <c r="E4" s="58" t="inlineStr">
-        <is>
-          <t>02/04/2026 - 12:00</t>
-        </is>
-      </c>
-      <c r="F4" s="58" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
+          <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per Farnborough International AirshowApertoFESR</t>
+        </is>
+      </c>
+      <c r="D4" s="63" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-farnborough-international-airshow-2/</t>
+        </is>
+      </c>
+      <c r="E4" s="62" t="inlineStr"/>
+      <c r="F4" s="62" t="inlineStr"/>
       <c r="G4" s="9" t="inlineStr"/>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="60" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA - alienazione lotto di terreno sito nel comune di Termini Imerese, via LibertàScade il:30/04/2026 - 12:00Leg</t>
+        </is>
+      </c>
+      <c r="D5" s="61" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proprieta-regionale-sito-nel-comune-termini-imerese-favore-ares-fabiola</t>
+        </is>
+      </c>
+      <c r="E5" s="60" t="inlineStr">
+        <is>
+          <t>30/04/2026 - 12:00</t>
+        </is>
+      </c>
+      <c r="F5" s="60" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -783,6 +810,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -794,7 +822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -844,12 +872,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="54" t="inlineStr">
+      <c r="A2" s="58" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B2" s="54" t="inlineStr">
+      <c r="B2" s="58" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -859,22 +887,22 @@
           <t>FLAG GALPA Costa E-R. Sostituzione del motore principale e dei motori secondari. Secondo bando</t>
         </is>
       </c>
-      <c r="D2" s="55" t="inlineStr">
+      <c r="D2" s="59" t="inlineStr">
         <is>
           <t>https://agricoltura.regione.emilia-romagna.it/feampa-2021-2027/bandi-galpa/2026/galpa-sostituzione-motori-secondo-bando</t>
         </is>
       </c>
-      <c r="E2" s="54" t="inlineStr"/>
-      <c r="F2" s="54" t="inlineStr"/>
-      <c r="G2" s="54" t="inlineStr"/>
+      <c r="E2" s="58" t="inlineStr"/>
+      <c r="F2" s="58" t="inlineStr"/>
+      <c r="G2" s="58" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="52" t="inlineStr">
+      <c r="A3" s="56" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B3" s="52" t="inlineStr">
+      <c r="B3" s="56" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -884,22 +912,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0PRE-SEED 3.0Prossima AperturaFESR</t>
         </is>
       </c>
-      <c r="D3" s="53" t="inlineStr">
+      <c r="D3" s="57" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/pre-seed-3-0/</t>
         </is>
       </c>
-      <c r="E3" s="52" t="inlineStr"/>
-      <c r="F3" s="52" t="inlineStr"/>
-      <c r="G3" s="52" t="inlineStr"/>
+      <c r="E3" s="56" t="inlineStr"/>
+      <c r="F3" s="56" t="inlineStr"/>
+      <c r="G3" s="56" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="54" t="inlineStr">
+      <c r="A4" s="58" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B4" s="54" t="inlineStr">
+      <c r="B4" s="58" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -909,22 +937,22 @@
           <t>ACCESSO AL CREDITO E ALLE GARANZIE PER LE IMPRESEContributo su finanziamenti alle imprese del Lazio erogati su provvista BEIProssima AperturaFESR</t>
         </is>
       </c>
-      <c r="D4" s="55" t="inlineStr">
+      <c r="D4" s="59" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-su-finanziamenti-alle-imprese-del-lazio-erogati-su-provvista-bei/</t>
         </is>
       </c>
-      <c r="E4" s="54" t="inlineStr"/>
-      <c r="F4" s="54" t="inlineStr"/>
-      <c r="G4" s="54" t="inlineStr"/>
+      <c r="E4" s="58" t="inlineStr"/>
+      <c r="F4" s="58" t="inlineStr"/>
+      <c r="G4" s="58" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="52" t="inlineStr">
+      <c r="A5" s="56" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B5" s="52" t="inlineStr">
+      <c r="B5" s="56" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -934,22 +962,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEIndividuazione degli enti iscritti al Registro unico nazionale del Terzo settoreApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D5" s="53" t="inlineStr">
+      <c r="D5" s="57" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/individuazione-degli-enti-iscritti-al-registro-unico-nazionale-del-terzo-settore/</t>
         </is>
       </c>
-      <c r="E5" s="52" t="inlineStr"/>
-      <c r="F5" s="52" t="inlineStr"/>
-      <c r="G5" s="52" t="inlineStr"/>
+      <c r="E5" s="56" t="inlineStr"/>
+      <c r="F5" s="56" t="inlineStr"/>
+      <c r="G5" s="56" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="54" t="inlineStr">
+      <c r="A6" s="58" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B6" s="54" t="inlineStr">
+      <c r="B6" s="58" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -959,22 +987,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Technology Transfer LazioApertoFESR</t>
         </is>
       </c>
-      <c r="D6" s="55" t="inlineStr">
+      <c r="D6" s="59" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/technology-transfer-lazio/</t>
         </is>
       </c>
-      <c r="E6" s="54" t="inlineStr"/>
-      <c r="F6" s="54" t="inlineStr"/>
-      <c r="G6" s="54" t="inlineStr"/>
+      <c r="E6" s="58" t="inlineStr"/>
+      <c r="F6" s="58" t="inlineStr"/>
+      <c r="G6" s="58" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="52" t="inlineStr">
+      <c r="A7" s="56" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B7" s="52" t="inlineStr">
+      <c r="B7" s="56" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -984,22 +1012,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Percorso di tutoraggio per le impreseApertoFESR</t>
         </is>
       </c>
-      <c r="D7" s="53" t="inlineStr">
+      <c r="D7" s="57" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/percorso-di-tutoraggio-per-le-imprese/</t>
         </is>
       </c>
-      <c r="E7" s="52" t="inlineStr"/>
-      <c r="F7" s="52" t="inlineStr"/>
-      <c r="G7" s="52" t="inlineStr"/>
+      <c r="E7" s="56" t="inlineStr"/>
+      <c r="F7" s="56" t="inlineStr"/>
+      <c r="G7" s="56" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="54" t="inlineStr">
+      <c r="A8" s="58" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B8" s="54" t="inlineStr">
+      <c r="B8" s="58" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1009,22 +1037,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per partecipare a SMAU Parigi 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D8" s="55" t="inlineStr">
+      <c r="D8" s="59" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-partecipare-a-smau-parigi-2026/</t>
         </is>
       </c>
-      <c r="E8" s="54" t="inlineStr"/>
-      <c r="F8" s="54" t="inlineStr"/>
-      <c r="G8" s="54" t="inlineStr"/>
+      <c r="E8" s="58" t="inlineStr"/>
+      <c r="F8" s="58" t="inlineStr"/>
+      <c r="G8" s="58" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="52" t="inlineStr">
+      <c r="A9" s="56" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B9" s="52" t="inlineStr">
+      <c r="B9" s="56" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1034,22 +1062,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONERiconoscimento della funzione sociale ed educativa degli oratoriApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D9" s="53" t="inlineStr">
+      <c r="D9" s="57" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/riconoscimento-della-funzione-sociale-ed-educativa-degli-oratori/</t>
         </is>
       </c>
-      <c r="E9" s="52" t="inlineStr"/>
-      <c r="F9" s="52" t="inlineStr"/>
-      <c r="G9" s="52" t="inlineStr"/>
+      <c r="E9" s="56" t="inlineStr"/>
+      <c r="F9" s="56" t="inlineStr"/>
+      <c r="G9" s="56" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="54" t="inlineStr">
+      <c r="A10" s="58" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B10" s="54" t="inlineStr">
+      <c r="B10" s="58" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1059,22 +1087,22 @@
           <t>GovernanceIscrizione nell’elenco regionale degli idonei all’esercizio dell’attività di direttore dell’Istituto JemoloApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D10" s="55" t="inlineStr">
+      <c r="D10" s="59" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/iscrizione-nellelenco-regionale-degli-idonei-allesercizio-dellattivita-di-direttore-dellistituto-jemolo/</t>
         </is>
       </c>
-      <c r="E10" s="54" t="inlineStr"/>
-      <c r="F10" s="54" t="inlineStr"/>
-      <c r="G10" s="54" t="inlineStr"/>
+      <c r="E10" s="58" t="inlineStr"/>
+      <c r="F10" s="58" t="inlineStr"/>
+      <c r="G10" s="58" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="52" t="inlineStr">
+      <c r="A11" s="56" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B11" s="52" t="inlineStr">
+      <c r="B11" s="56" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1084,22 +1112,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEVoucher per lo sport – seconda annualitàApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D11" s="53" t="inlineStr">
+      <c r="D11" s="57" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/voucher-per-lo-sport-seconda-annualita/</t>
         </is>
       </c>
-      <c r="E11" s="52" t="inlineStr"/>
-      <c r="F11" s="52" t="inlineStr"/>
-      <c r="G11" s="52" t="inlineStr"/>
+      <c r="E11" s="56" t="inlineStr"/>
+      <c r="F11" s="56" t="inlineStr"/>
+      <c r="G11" s="56" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="54" t="inlineStr">
+      <c r="A12" s="58" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B12" s="54" t="inlineStr">
+      <c r="B12" s="58" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1109,22 +1137,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEBonus occupazionale SALGOApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D12" s="55" t="inlineStr">
+      <c r="D12" s="59" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/bonus-occupazionale-salgo/</t>
         </is>
       </c>
-      <c r="E12" s="54" t="inlineStr"/>
-      <c r="F12" s="54" t="inlineStr"/>
-      <c r="G12" s="54" t="inlineStr"/>
+      <c r="E12" s="58" t="inlineStr"/>
+      <c r="F12" s="58" t="inlineStr"/>
+      <c r="G12" s="58" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="52" t="inlineStr">
+      <c r="A13" s="56" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B13" s="52" t="inlineStr">
+      <c r="B13" s="56" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1134,22 +1162,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEContributo di Libertà per le donne che hanno subito violenzaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D13" s="53" t="inlineStr">
+      <c r="D13" s="57" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-di-liberta-per-le-donne-che-hanno-subito-violenza/</t>
         </is>
       </c>
-      <c r="E13" s="52" t="inlineStr"/>
-      <c r="F13" s="52" t="inlineStr"/>
-      <c r="G13" s="52" t="inlineStr"/>
+      <c r="E13" s="56" t="inlineStr"/>
+      <c r="F13" s="56" t="inlineStr"/>
+      <c r="G13" s="56" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="54" t="inlineStr">
+      <c r="A14" s="58" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B14" s="54" t="inlineStr">
+      <c r="B14" s="58" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1159,22 +1187,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURAInterventi straordinari di valorizzazione del patrimonio culturale del LazioApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D14" s="55" t="inlineStr">
+      <c r="D14" s="59" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/interventi-straordinari-di-valorizzazione-del-patrimonio-culturale-del-lazio/</t>
         </is>
       </c>
-      <c r="E14" s="54" t="inlineStr"/>
-      <c r="F14" s="54" t="inlineStr"/>
-      <c r="G14" s="54" t="inlineStr"/>
+      <c r="E14" s="58" t="inlineStr"/>
+      <c r="F14" s="58" t="inlineStr"/>
+      <c r="G14" s="58" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="52" t="inlineStr">
+      <c r="A15" s="56" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B15" s="52" t="inlineStr">
+      <c r="B15" s="56" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1184,30 +1212,30 @@
           <t>Bandi di garaBANDO ATTUAZIONE Ob. 1.1 Azione 1 codice 111102 _DIV - "SOSTEGNO ALLA DIVERSIFICAZIONE E NUOVE FORME DI REDDITO PER LA PICCOLA PESCA COST</t>
         </is>
       </c>
-      <c r="D15" s="53" t="inlineStr">
+      <c r="D15" s="57" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/bando-avviso-regia-ob-11-azione-1-codice-111102-div-sostegno-alla-diversificazione-nuove-forme-reddito-piccola-pesca-costiera</t>
         </is>
       </c>
-      <c r="E15" s="52" t="inlineStr">
+      <c r="E15" s="56" t="inlineStr">
         <is>
           <t>07/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F15" s="52" t="inlineStr">
+      <c r="F15" s="56" t="inlineStr">
         <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="G15" s="52" t="inlineStr"/>
+      <c r="G15" s="56" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="54" t="inlineStr">
+      <c r="A16" s="58" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B16" s="54" t="inlineStr">
+      <c r="B16" s="58" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1217,30 +1245,30 @@
           <t>Avvisi pubblici09 marzo 2026 - ST SIRACUSA - AVVISO PUBBLICO PER LA COSTITUZIONE DI ELENCHI DI OPERATORI ECONOMICI PER L’ACQUISIZIONE DI BENI E SERVIZ</t>
         </is>
       </c>
-      <c r="D16" s="55" t="inlineStr">
+      <c r="D16" s="59" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/09-marzo-2026-st-siracusa-avviso-pubblico-costituzione-elenchi-operatori-economici-l-acquisizione-beni-servizi</t>
         </is>
       </c>
-      <c r="E16" s="54" t="inlineStr">
+      <c r="E16" s="58" t="inlineStr">
         <is>
           <t>31/12/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F16" s="54" t="inlineStr">
+      <c r="F16" s="58" t="inlineStr">
         <is>
           <t>31/12/2026</t>
         </is>
       </c>
-      <c r="G16" s="54" t="inlineStr"/>
+      <c r="G16" s="58" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="52" t="inlineStr">
+      <c r="A17" s="56" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B17" s="52" t="inlineStr">
+      <c r="B17" s="56" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1250,30 +1278,30 @@
           <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScade il:19/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D17" s="53" t="inlineStr">
+      <c r="D17" s="57" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
         </is>
       </c>
-      <c r="E17" s="52" t="inlineStr">
+      <c r="E17" s="56" t="inlineStr">
         <is>
           <t>19/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F17" s="52" t="inlineStr">
+      <c r="F17" s="56" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G17" s="52" t="inlineStr"/>
+      <c r="G17" s="56" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="54" t="inlineStr">
+      <c r="A18" s="58" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B18" s="54" t="inlineStr">
+      <c r="B18" s="58" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1283,22 +1311,22 @@
           <t>Manifestazioni di interesseAvviso Manifestazione Interesse DISTRIBUTORI AUTOMATICI di bevande e snackScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D18" s="55" t="inlineStr">
+      <c r="D18" s="59" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-distributori-automatici-bevande-snack</t>
         </is>
       </c>
-      <c r="E18" s="54" t="inlineStr"/>
-      <c r="F18" s="54" t="inlineStr"/>
-      <c r="G18" s="54" t="inlineStr"/>
+      <c r="E18" s="58" t="inlineStr"/>
+      <c r="F18" s="58" t="inlineStr"/>
+      <c r="G18" s="58" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="52" t="inlineStr">
+      <c r="A19" s="56" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B19" s="52" t="inlineStr">
+      <c r="B19" s="56" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1308,30 +1336,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D19" s="53" t="inlineStr">
+      <c r="D19" s="57" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo</t>
         </is>
       </c>
-      <c r="E19" s="52" t="inlineStr">
+      <c r="E19" s="56" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F19" s="52" t="inlineStr">
+      <c r="F19" s="56" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G19" s="52" t="inlineStr"/>
+      <c r="G19" s="56" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="54" t="inlineStr">
+      <c r="A20" s="58" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B20" s="54" t="inlineStr">
+      <c r="B20" s="58" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1341,30 +1369,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D20" s="55" t="inlineStr">
+      <c r="D20" s="59" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo-0</t>
         </is>
       </c>
-      <c r="E20" s="54" t="inlineStr">
+      <c r="E20" s="58" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F20" s="54" t="inlineStr">
+      <c r="F20" s="58" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G20" s="54" t="inlineStr"/>
+      <c r="G20" s="58" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="52" t="inlineStr">
+      <c r="A21" s="56" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B21" s="52" t="inlineStr">
+      <c r="B21" s="56" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1374,22 +1402,22 @@
           <t>Manifestazioni di interesseST SIRACUSA - AVVISO DI MANIFESTAZIONE DI INTERESSE - Fornitura applicativo extracontabile per la gestione progetti, ecc. e</t>
         </is>
       </c>
-      <c r="D21" s="53" t="inlineStr">
+      <c r="D21" s="57" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-siracusa-avviso-manifestazione-interesse-fornitura-applicativo-extracontabile-gestione-progetti-ecc-applicativo-gestione-ed-elaborazione-informatizzata-paghe</t>
         </is>
       </c>
-      <c r="E21" s="52" t="inlineStr"/>
-      <c r="F21" s="52" t="inlineStr"/>
-      <c r="G21" s="52" t="inlineStr"/>
+      <c r="E21" s="56" t="inlineStr"/>
+      <c r="F21" s="56" t="inlineStr"/>
+      <c r="G21" s="56" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="54" t="inlineStr">
+      <c r="A22" s="58" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B22" s="54" t="inlineStr">
+      <c r="B22" s="58" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1399,30 +1427,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile sito nel Comune di Capo D'Orlando, Via Trazzera MarinaScade il:25/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D22" s="55" t="inlineStr">
+      <c r="D22" s="59" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-sito-nel-comune-capo-d-orlando-trazzera-marina</t>
         </is>
       </c>
-      <c r="E22" s="54" t="inlineStr">
+      <c r="E22" s="58" t="inlineStr">
         <is>
           <t>25/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F22" s="54" t="inlineStr">
+      <c r="F22" s="58" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="G22" s="54" t="inlineStr"/>
+      <c r="G22" s="58" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="52" t="inlineStr">
+      <c r="A23" s="56" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B23" s="52" t="inlineStr">
+      <c r="B23" s="56" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1432,22 +1460,22 @@
           <t xml:space="preserve">Avvisi pubbliciST CATANIA - Programma Regionale FESR Sicilia 2021-2027 - Azione 2.4.4 - “Interventi per la riduzione del rischio incendi” - AVVISO DI </t>
         </is>
       </c>
-      <c r="D23" s="53" t="inlineStr">
+      <c r="D23" s="57" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-catania-programma-regionale-fesr-sicilia-2021-2027-azione-244-interventi-riduzione-rischio-incendi-avviso-indagine-mercato</t>
         </is>
       </c>
-      <c r="E23" s="52" t="inlineStr"/>
-      <c r="F23" s="52" t="inlineStr"/>
-      <c r="G23" s="52" t="inlineStr"/>
+      <c r="E23" s="56" t="inlineStr"/>
+      <c r="F23" s="56" t="inlineStr"/>
+      <c r="G23" s="56" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="54" t="inlineStr">
+      <c r="A24" s="58" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B24" s="54" t="inlineStr">
+      <c r="B24" s="58" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1457,22 +1485,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per ROMICS – Primavera 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D24" s="55" t="inlineStr">
+      <c r="D24" s="59" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-romics-primavera-2026/</t>
         </is>
       </c>
-      <c r="E24" s="54" t="inlineStr"/>
-      <c r="F24" s="54" t="inlineStr"/>
-      <c r="G24" s="54" t="inlineStr"/>
+      <c r="E24" s="58" t="inlineStr"/>
+      <c r="F24" s="58" t="inlineStr"/>
+      <c r="G24" s="58" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="52" t="inlineStr">
+      <c r="A25" s="56" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B25" s="52" t="inlineStr">
+      <c r="B25" s="56" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1482,22 +1510,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Cinema International 2026 – I edizioneApertoFESR</t>
         </is>
       </c>
-      <c r="D25" s="53" t="inlineStr">
+      <c r="D25" s="57" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lazio-cinema-international-2026-i-edizione/</t>
         </is>
       </c>
-      <c r="E25" s="52" t="inlineStr"/>
-      <c r="F25" s="52" t="inlineStr"/>
-      <c r="G25" s="52" t="inlineStr"/>
+      <c r="E25" s="56" t="inlineStr"/>
+      <c r="F25" s="56" t="inlineStr"/>
+      <c r="G25" s="56" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="54" t="inlineStr">
+      <c r="A26" s="58" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B26" s="54" t="inlineStr">
+      <c r="B26" s="58" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1507,22 +1535,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEManifestazioni di interesse alla costituzione di due nuove Fondazioni I.T.S. AcademyApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D26" s="55" t="inlineStr">
+      <c r="D26" s="59" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazioni-di-interesse-alla-costituzione-di-due-nuove-fondazioni-i-t-s-academy/</t>
         </is>
       </c>
-      <c r="E26" s="54" t="inlineStr"/>
-      <c r="F26" s="54" t="inlineStr"/>
-      <c r="G26" s="54" t="inlineStr"/>
+      <c r="E26" s="58" t="inlineStr"/>
+      <c r="F26" s="58" t="inlineStr"/>
+      <c r="G26" s="58" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="52" t="inlineStr">
+      <c r="A27" s="56" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B27" s="52" t="inlineStr">
+      <c r="B27" s="56" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1532,22 +1560,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURAContributi per sostenere la ripresa del settore della pescaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D27" s="53" t="inlineStr">
+      <c r="D27" s="57" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributi-per-sostenere-la-ripresa-del-settore-della-pesca/</t>
         </is>
       </c>
-      <c r="E27" s="52" t="inlineStr"/>
-      <c r="F27" s="52" t="inlineStr"/>
-      <c r="G27" s="52" t="inlineStr"/>
+      <c r="E27" s="56" t="inlineStr"/>
+      <c r="F27" s="56" t="inlineStr"/>
+      <c r="G27" s="56" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="54" t="inlineStr">
+      <c r="A28" s="58" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B28" s="54" t="inlineStr">
+      <c r="B28" s="58" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1557,30 +1585,30 @@
           <t>Manifestazioni di interesseAVVISO - Manifestazione Interesse “Storytelling aziendale” Expo Wild Natura - Caccia - Pesca. Misterbianco (CT), 10-12 apri</t>
         </is>
       </c>
-      <c r="D28" s="55" t="inlineStr">
+      <c r="D28" s="59" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-storytelling-aziendale-expo-wild-natura-caccia-pesca-misterbianco-ct-10-12-aprile-2026</t>
         </is>
       </c>
-      <c r="E28" s="54" t="inlineStr">
+      <c r="E28" s="58" t="inlineStr">
         <is>
           <t>30/03/2026 - 13:00</t>
         </is>
       </c>
-      <c r="F28" s="54" t="inlineStr">
+      <c r="F28" s="58" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G28" s="54" t="inlineStr"/>
+      <c r="G28" s="58" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="52" t="inlineStr">
+      <c r="A29" s="56" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B29" s="52" t="inlineStr">
+      <c r="B29" s="56" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1590,30 +1618,30 @@
           <t>Manifestazioni di interesseInvaso Lentini - Interventi di ripristino delle pareti esterne in cls della Torre di presa Sud e della trave d’appoggio del</t>
         </is>
       </c>
-      <c r="D29" s="53" t="inlineStr">
+      <c r="D29" s="57" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/invaso-lentini-interventi-ripristino-pareti-esterne-cls-torre-presa-sud-trave-d-appoggio-cavalcavia-collegamento-alla-stessa-torre</t>
         </is>
       </c>
-      <c r="E29" s="52" t="inlineStr">
+      <c r="E29" s="56" t="inlineStr">
         <is>
           <t>19/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F29" s="52" t="inlineStr">
+      <c r="F29" s="56" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G29" s="52" t="inlineStr"/>
+      <c r="G29" s="56" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="54" t="inlineStr">
+      <c r="A30" s="58" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="B30" s="54" t="inlineStr">
+      <c r="B30" s="58" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1623,22 +1651,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURARistrutturazione e riconversione vigneti – campagna 2026-2027ApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D30" s="55" t="inlineStr">
+      <c r="D30" s="59" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/ristrutturazione-e-riconversione-vigneti-campagna-2026-2027/</t>
         </is>
       </c>
-      <c r="E30" s="54" t="inlineStr"/>
-      <c r="F30" s="54" t="inlineStr"/>
-      <c r="G30" s="54" t="inlineStr"/>
+      <c r="E30" s="58" t="inlineStr"/>
+      <c r="F30" s="58" t="inlineStr"/>
+      <c r="G30" s="58" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="52" t="inlineStr">
+      <c r="A31" s="56" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="B31" s="52" t="inlineStr">
+      <c r="B31" s="56" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1648,30 +1676,30 @@
           <t>Manifestazioni di interessePR FESR 2021/27 Azione 1.3.3 e del POC 2014/20 - Azione 1.3.1  - Avviso a manifestazione d’interesse eventi fieristici inte</t>
         </is>
       </c>
-      <c r="D31" s="53" t="inlineStr">
+      <c r="D31" s="57" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-d-interesse-eventi-fieristici-internazionali-marzo-dicembre-2026</t>
         </is>
       </c>
-      <c r="E31" s="52" t="inlineStr">
+      <c r="E31" s="56" t="inlineStr">
         <is>
           <t>30/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F31" s="52" t="inlineStr">
+      <c r="F31" s="56" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="G31" s="52" t="inlineStr"/>
+      <c r="G31" s="56" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="54" t="inlineStr">
+      <c r="A32" s="58" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="B32" s="54" t="inlineStr">
+      <c r="B32" s="58" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1681,22 +1709,22 @@
           <t>INTERNAZIONALIZZAZIONEL’Ecosistema dell’Innovazione a INNOVIT – Focus S3ApertoFESR</t>
         </is>
       </c>
-      <c r="D32" s="55" t="inlineStr">
+      <c r="D32" s="59" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lecosistema-dellinnovazione-a-innovit-focus-s3/</t>
         </is>
       </c>
-      <c r="E32" s="54" t="inlineStr"/>
-      <c r="F32" s="54" t="inlineStr"/>
-      <c r="G32" s="54" t="inlineStr"/>
+      <c r="E32" s="58" t="inlineStr"/>
+      <c r="F32" s="58" t="inlineStr"/>
+      <c r="G32" s="58" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="52" t="inlineStr">
+      <c r="A33" s="56" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="B33" s="52" t="inlineStr">
+      <c r="B33" s="56" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1706,22 +1734,22 @@
           <t>Manifestazioni di interessePR FESR SICILIA 2021/27 - NUOVO Avviso a manifestazione d’interesse per esperti valutatoriScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D33" s="53" t="inlineStr">
+      <c r="D33" s="57" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/pr-fesr-sicilia-202127-nuovo-avviso-manifestazione-d-interesse-esperti-valutatori</t>
         </is>
       </c>
-      <c r="E33" s="52" t="inlineStr"/>
-      <c r="F33" s="52" t="inlineStr"/>
-      <c r="G33" s="52" t="inlineStr"/>
+      <c r="E33" s="56" t="inlineStr"/>
+      <c r="F33" s="56" t="inlineStr"/>
+      <c r="G33" s="56" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="54" t="inlineStr">
+      <c r="A34" s="58" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="B34" s="54" t="inlineStr">
+      <c r="B34" s="58" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -1731,22 +1759,22 @@
           <t>Bando 2026 per contributi dedicati alla manutenzione della rete dei percorsi escursionistici</t>
         </is>
       </c>
-      <c r="D34" s="55" t="inlineStr">
+      <c r="D34" s="59" t="inlineStr">
         <is>
           <t>https://ambiente.regione.emilia-romagna.it/it/parchi-natura2000/bandi/bando-2026-per-contributi-dedicati-alla-manutenzione-della-rete-dei-percorsi-escursionistici</t>
         </is>
       </c>
-      <c r="E34" s="54" t="inlineStr"/>
-      <c r="F34" s="54" t="inlineStr"/>
-      <c r="G34" s="54" t="inlineStr"/>
+      <c r="E34" s="58" t="inlineStr"/>
+      <c r="F34" s="58" t="inlineStr"/>
+      <c r="G34" s="58" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="52" t="inlineStr">
+      <c r="A35" s="56" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="B35" s="52" t="inlineStr">
+      <c r="B35" s="56" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1756,22 +1784,22 @@
           <t>Programma regionale in favore delle tradizioni storiche, artistiche, religiose e popolari (2026) – manifestazioni d’interesseApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D35" s="53" t="inlineStr">
+      <c r="D35" s="57" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/programma-regionale-in-favore-delle-tradizioni-storiche-artistiche-religiose-e-popolari-2026-manifestazioni-dinteresse/</t>
         </is>
       </c>
-      <c r="E35" s="52" t="inlineStr"/>
-      <c r="F35" s="52" t="inlineStr"/>
-      <c r="G35" s="52" t="inlineStr"/>
+      <c r="E35" s="56" t="inlineStr"/>
+      <c r="F35" s="56" t="inlineStr"/>
+      <c r="G35" s="56" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="54" t="inlineStr">
+      <c r="A36" s="58" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B36" s="54" t="inlineStr">
+      <c r="B36" s="58" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1781,22 +1809,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEBuoni servizio per le persone non autosufficienti nel territorio del LazioProssima AperturaFSE / FSE+</t>
         </is>
       </c>
-      <c r="D36" s="55" t="inlineStr">
+      <c r="D36" s="59" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/buoni-servizio-per-le-persone-non-autosufficienti-nel-territorio-del-lazio/</t>
         </is>
       </c>
-      <c r="E36" s="54" t="inlineStr"/>
-      <c r="F36" s="54" t="inlineStr"/>
-      <c r="G36" s="54" t="inlineStr"/>
+      <c r="E36" s="58" t="inlineStr"/>
+      <c r="F36" s="58" t="inlineStr"/>
+      <c r="G36" s="58" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="52" t="inlineStr">
+      <c r="A37" s="56" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B37" s="52" t="inlineStr">
+      <c r="B37" s="56" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1806,22 +1834,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONERimborso delle rette dei servizi educativi nel territorio del LazioProssima AperturaFSE / FSE+</t>
         </is>
       </c>
-      <c r="D37" s="53" t="inlineStr">
+      <c r="D37" s="57" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/rimborso-delle-rette-dei-servizi-educativi-nel-territorio-del-lazio/</t>
         </is>
       </c>
-      <c r="E37" s="52" t="inlineStr"/>
-      <c r="F37" s="52" t="inlineStr"/>
-      <c r="G37" s="52" t="inlineStr"/>
+      <c r="E37" s="56" t="inlineStr"/>
+      <c r="F37" s="56" t="inlineStr"/>
+      <c r="G37" s="56" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="54" t="inlineStr">
+      <c r="A38" s="58" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B38" s="54" t="inlineStr">
+      <c r="B38" s="58" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1831,30 +1859,30 @@
           <t>Manifestazioni di interesseATTO DI INTERPELLO PER L’AFFIDAMENTO DELL’INCARICO DI COLLAUDO STATICO DELLE STRUTTURE - Diga di Pietrarossa (Progetto ex C</t>
         </is>
       </c>
-      <c r="D38" s="55" t="inlineStr">
+      <c r="D38" s="59" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/atto-interpello-l-affidamento-incarico-collaudo-statico-strutture-diga-pietrarossa-progetto-ex-casmez-303219</t>
         </is>
       </c>
-      <c r="E38" s="54" t="inlineStr">
+      <c r="E38" s="58" t="inlineStr">
         <is>
           <t>27/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F38" s="54" t="inlineStr">
+      <c r="F38" s="58" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="G38" s="54" t="inlineStr"/>
+      <c r="G38" s="58" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="52" t="inlineStr">
+      <c r="A39" s="56" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B39" s="52" t="inlineStr">
+      <c r="B39" s="56" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1864,30 +1892,30 @@
           <t>Manifestazioni di interesseAvviso alle Case  Editrici della Regione siciliana per la partecipazione al Salone del Libro di Torino, 14-18  maggio 2026.</t>
         </is>
       </c>
-      <c r="D39" s="53" t="inlineStr">
+      <c r="D39" s="57" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/manifestazione-d-interesse-partecipare-al-xxxviii-salone-libro-torino-14-al-18-maggio-2026-attraverso-l-esposizione-pubblicazioni-presso-stand-assessorato-beni</t>
         </is>
       </c>
-      <c r="E39" s="52" t="inlineStr">
+      <c r="E39" s="56" t="inlineStr">
         <is>
           <t>30/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F39" s="52" t="inlineStr">
+      <c r="F39" s="56" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="G39" s="52" t="inlineStr"/>
+      <c r="G39" s="56" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="54" t="inlineStr">
+      <c r="A40" s="58" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B40" s="54" t="inlineStr">
+      <c r="B40" s="58" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1897,30 +1925,30 @@
           <t xml:space="preserve">Manifestazioni di interessePR FESR SICILIA 2021/27 - NUOVO Avviso a manifestazione d’interesse per esperti valutatoriScade il:06/04/2026 - 23:59Leggi </t>
         </is>
       </c>
-      <c r="D40" s="55" t="inlineStr">
+      <c r="D40" s="59" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/pr-fesr-sicilia-202127-nuovo-avviso-manifestazione-d-interesse-esperti-valutatori</t>
         </is>
       </c>
-      <c r="E40" s="54" t="inlineStr">
+      <c r="E40" s="58" t="inlineStr">
         <is>
           <t>06/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F40" s="54" t="inlineStr">
+      <c r="F40" s="58" t="inlineStr">
         <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="G40" s="54" t="inlineStr"/>
+      <c r="G40" s="58" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="52" t="inlineStr">
+      <c r="A41" s="56" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B41" s="52" t="inlineStr">
+      <c r="B41" s="56" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1930,22 +1958,22 @@
           <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D41" s="53" t="inlineStr">
+      <c r="D41" s="57" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
         </is>
       </c>
-      <c r="E41" s="52" t="inlineStr"/>
-      <c r="F41" s="52" t="inlineStr"/>
-      <c r="G41" s="52" t="inlineStr"/>
+      <c r="E41" s="56" t="inlineStr"/>
+      <c r="F41" s="56" t="inlineStr"/>
+      <c r="G41" s="56" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="54" t="inlineStr">
+      <c r="A42" s="58" t="inlineStr">
         <is>
           <t>24/03/2026</t>
         </is>
       </c>
-      <c r="B42" s="54" t="inlineStr">
+      <c r="B42" s="58" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -1955,22 +1983,22 @@
           <t>GAL del Ducato - Promozione di fiere agroalimentari e delle filiere del cibo – Bando per Enti pubblici (DU AS 05B)</t>
         </is>
       </c>
-      <c r="D42" s="55" t="inlineStr">
+      <c r="D42" s="59" t="inlineStr">
         <is>
           <t>https://agricoltura.regione.emilia-romagna.it/sviluppo-rurale-23-27/opportunita/bandi-gal/2026/du_as05b-promozione-di-fiere-agroalimentari-e-delle-filiere-del-cibo-bando-per-enti-pubblici</t>
         </is>
       </c>
-      <c r="E42" s="54" t="inlineStr"/>
-      <c r="F42" s="54" t="inlineStr"/>
-      <c r="G42" s="54" t="inlineStr"/>
+      <c r="E42" s="58" t="inlineStr"/>
+      <c r="F42" s="58" t="inlineStr"/>
+      <c r="G42" s="58" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="52" t="inlineStr">
+      <c r="A43" s="56" t="inlineStr">
         <is>
           <t>24/03/2026</t>
         </is>
       </c>
-      <c r="B43" s="52" t="inlineStr">
+      <c r="B43" s="56" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1980,30 +2008,30 @@
           <t>Manifestazioni di interesseAVVISO PUBBLICO PER MANIFESTAZIONE DI INTERESSE FINALIZZATA ALL'ASSEGNAZIONE DI SPAZI ESPOSITIVI (CORNER GRATUITI) ALL'INTE</t>
         </is>
       </c>
-      <c r="D43" s="53" t="inlineStr">
+      <c r="D43" s="57" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-manifestazione-interesse-finalizzata-all-assegnazione-spazi-espositivi-corner-gratuiti-all-interno-stand-istituzionale-dsrt-manifestazione</t>
         </is>
       </c>
-      <c r="E43" s="52" t="inlineStr">
+      <c r="E43" s="56" t="inlineStr">
         <is>
           <t>30/03/2026 - 13:00</t>
         </is>
       </c>
-      <c r="F43" s="52" t="inlineStr">
+      <c r="F43" s="56" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G43" s="52" t="inlineStr"/>
+      <c r="G43" s="56" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="54" t="inlineStr">
+      <c r="A44" s="58" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B44" s="54" t="inlineStr">
+      <c r="B44" s="58" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2013,22 +2041,22 @@
           <t>Avviso per la concessione di contributi per eventi sportivi realizzati in Emilia-Romagna - Anno 2026</t>
         </is>
       </c>
-      <c r="D44" s="55" t="inlineStr">
+      <c r="D44" s="59" t="inlineStr">
         <is>
           <t>https://www.regione.emilia-romagna.it/sport/bandi/2026/bando-2026</t>
         </is>
       </c>
-      <c r="E44" s="54" t="inlineStr"/>
-      <c r="F44" s="54" t="inlineStr"/>
-      <c r="G44" s="54" t="inlineStr"/>
+      <c r="E44" s="58" t="inlineStr"/>
+      <c r="F44" s="58" t="inlineStr"/>
+      <c r="G44" s="58" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="52" t="inlineStr">
+      <c r="A45" s="56" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B45" s="52" t="inlineStr">
+      <c r="B45" s="56" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2038,22 +2066,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Street art 2026Prossima AperturaBandi Regionali</t>
         </is>
       </c>
-      <c r="D45" s="53" t="inlineStr">
+      <c r="D45" s="57" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lazio-street-art-2026/</t>
         </is>
       </c>
-      <c r="E45" s="52" t="inlineStr"/>
-      <c r="F45" s="52" t="inlineStr"/>
-      <c r="G45" s="52" t="inlineStr"/>
+      <c r="E45" s="56" t="inlineStr"/>
+      <c r="F45" s="56" t="inlineStr"/>
+      <c r="G45" s="56" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="54" t="inlineStr">
+      <c r="A46" s="58" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B46" s="54" t="inlineStr">
+      <c r="B46" s="58" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2063,30 +2091,30 @@
           <t>Manifestazioni di interesseManifestazione di interesse per la partecipazione all’evento “R2I Italy 2026” – Bologna, 12-13/05/2026Scade il:03/04/2026 -</t>
         </is>
       </c>
-      <c r="D46" s="55" t="inlineStr">
+      <c r="D46" s="59" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/manifestazione-interesse-partecipazione-all-evento-r2i-italy-2026-bologna-12-13052026</t>
         </is>
       </c>
-      <c r="E46" s="54" t="inlineStr">
+      <c r="E46" s="58" t="inlineStr">
         <is>
           <t>03/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F46" s="54" t="inlineStr">
+      <c r="F46" s="58" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="G46" s="54" t="inlineStr"/>
+      <c r="G46" s="58" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="52" t="inlineStr">
+      <c r="A47" s="56" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B47" s="52" t="inlineStr">
+      <c r="B47" s="56" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2096,30 +2124,30 @@
           <t>Manifestazioni di interesseST SIRACUSA - AVVISO PER MANIFESTAZIONE DI INTERESSE - Selezione di n. 5 unità di personale internoScade il:20/04/2026 - 12</t>
         </is>
       </c>
-      <c r="D47" s="53" t="inlineStr">
+      <c r="D47" s="57" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/24-marzo-2026-st-siracusa-avviso-manifestazione-interesse-selezione-n-5-unita-personale-interno</t>
         </is>
       </c>
-      <c r="E47" s="52" t="inlineStr">
+      <c r="E47" s="56" t="inlineStr">
         <is>
           <t>20/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F47" s="52" t="inlineStr">
+      <c r="F47" s="56" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="G47" s="52" t="inlineStr"/>
+      <c r="G47" s="56" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="54" t="inlineStr">
+      <c r="A48" s="58" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B48" s="54" t="inlineStr">
+      <c r="B48" s="58" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2129,30 +2157,30 @@
           <t>Avvisi pubbliciRevoca dell’avviso di concessione a titolo gratuito del 16.12.2025 inerente all’immobile di seguito identificato e contestuale nuovo av</t>
         </is>
       </c>
-      <c r="D48" s="55" t="inlineStr">
+      <c r="D48" s="59" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/revoca-avviso-concessione-titolo-gratuito-16122025-inerente-all-immobile-seguito-identificato-contestuale-nuovo-avviso-concessione-titolo-oneroso-stesso-sito-nel</t>
         </is>
       </c>
-      <c r="E48" s="54" t="inlineStr">
+      <c r="E48" s="58" t="inlineStr">
         <is>
           <t>08/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F48" s="54" t="inlineStr">
+      <c r="F48" s="58" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="G48" s="54" t="inlineStr"/>
+      <c r="G48" s="58" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="52" t="inlineStr">
+      <c r="A49" s="56" t="inlineStr">
         <is>
           <t>26/03/2026</t>
         </is>
       </c>
-      <c r="B49" s="52" t="inlineStr">
+      <c r="B49" s="56" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2162,22 +2190,22 @@
           <t>Bando studi di fattibilità per fusioni di Comuni</t>
         </is>
       </c>
-      <c r="D49" s="53" t="inlineStr">
+      <c r="D49" s="57" t="inlineStr">
         <is>
           <t>https://www.regione.emilia-romagna.it/autonomie-locali/bandi/bando_studi_fattibilita_fusioni_comuni</t>
         </is>
       </c>
-      <c r="E49" s="52" t="inlineStr"/>
-      <c r="F49" s="52" t="inlineStr"/>
-      <c r="G49" s="52" t="inlineStr"/>
+      <c r="E49" s="56" t="inlineStr"/>
+      <c r="F49" s="56" t="inlineStr"/>
+      <c r="G49" s="56" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="54" t="inlineStr">
+      <c r="A50" s="58" t="inlineStr">
         <is>
           <t>26/03/2026</t>
         </is>
       </c>
-      <c r="B50" s="54" t="inlineStr">
+      <c r="B50" s="58" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2187,30 +2215,30 @@
           <t xml:space="preserve">Manifestazioni di interesseAvviso pubblico di selezione interna, per titoli, per il conferimento di PO e professionali, ai sensi degli artt. 19, 20 e </t>
         </is>
       </c>
-      <c r="D50" s="55" t="inlineStr">
+      <c r="D50" s="59" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-selezione-interna-titoli-conferimento-po-professionali-ai-sensi-artt-19-20-21-ccrl-20222024-comparto-non-dirigenziale</t>
         </is>
       </c>
-      <c r="E50" s="54" t="inlineStr">
+      <c r="E50" s="58" t="inlineStr">
         <is>
           <t>30/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F50" s="54" t="inlineStr">
+      <c r="F50" s="58" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G50" s="54" t="inlineStr"/>
+      <c r="G50" s="58" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="52" t="inlineStr">
+      <c r="A51" s="56" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="B51" s="52" t="inlineStr">
+      <c r="B51" s="56" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2220,22 +2248,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0PRE-SEED 3.0ApertoFESR</t>
         </is>
       </c>
-      <c r="D51" s="53" t="inlineStr">
+      <c r="D51" s="57" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/pre-seed-3-0/</t>
         </is>
       </c>
-      <c r="E51" s="52" t="inlineStr"/>
-      <c r="F51" s="52" t="inlineStr"/>
-      <c r="G51" s="52" t="inlineStr"/>
+      <c r="E51" s="56" t="inlineStr"/>
+      <c r="F51" s="56" t="inlineStr"/>
+      <c r="G51" s="56" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="54" t="inlineStr">
+      <c r="A52" s="58" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B52" s="54" t="inlineStr">
+      <c r="B52" s="58" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2245,30 +2273,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “So</t>
         </is>
       </c>
-      <c r="D52" s="55" t="inlineStr">
+      <c r="D52" s="59" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-termini-imerese-locta-piazza-marina</t>
         </is>
       </c>
-      <c r="E52" s="54" t="inlineStr">
+      <c r="E52" s="58" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F52" s="54" t="inlineStr">
+      <c r="F52" s="58" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G52" s="54" t="inlineStr"/>
+      <c r="G52" s="58" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="52" t="inlineStr">
+      <c r="A53" s="56" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B53" s="52" t="inlineStr">
+      <c r="B53" s="56" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2278,30 +2306,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, Sig</t>
         </is>
       </c>
-      <c r="D53" s="53" t="inlineStr">
+      <c r="D53" s="57" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-porto-empedocle-locta-punta-piccola</t>
         </is>
       </c>
-      <c r="E53" s="52" t="inlineStr">
+      <c r="E53" s="56" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F53" s="52" t="inlineStr">
+      <c r="F53" s="56" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G53" s="52" t="inlineStr"/>
+      <c r="G53" s="56" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="54" t="inlineStr">
+      <c r="A54" s="58" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B54" s="54" t="inlineStr">
+      <c r="B54" s="58" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2311,30 +2339,30 @@
           <t xml:space="preserve">Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “Società </t>
         </is>
       </c>
-      <c r="D54" s="55" t="inlineStr">
+      <c r="D54" s="59" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-messina-locta-torrente-bordonaro</t>
         </is>
       </c>
-      <c r="E54" s="54" t="inlineStr">
+      <c r="E54" s="58" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F54" s="54" t="inlineStr">
+      <c r="F54" s="58" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G54" s="54" t="inlineStr"/>
+      <c r="G54" s="58" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="52" t="inlineStr">
+      <c r="A55" s="56" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B55" s="52" t="inlineStr">
+      <c r="B55" s="56" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2344,30 +2372,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “Condomin</t>
         </is>
       </c>
-      <c r="D55" s="53" t="inlineStr">
+      <c r="D55" s="57" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-mascali-spiaggia-n-144150</t>
         </is>
       </c>
-      <c r="E55" s="52" t="inlineStr">
+      <c r="E55" s="56" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F55" s="52" t="inlineStr">
+      <c r="F55" s="56" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G55" s="52" t="inlineStr"/>
+      <c r="G55" s="56" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="54" t="inlineStr">
+      <c r="A56" s="58" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B56" s="54" t="inlineStr">
+      <c r="B56" s="58" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2377,30 +2405,30 @@
           <t xml:space="preserve">Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione sito nel Comune di Lipari, isola di Stromboli, </t>
         </is>
       </c>
-      <c r="D56" s="55" t="inlineStr">
+      <c r="D56" s="59" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-lipari-isola-stromboli-locta-fico-grande</t>
         </is>
       </c>
-      <c r="E56" s="54" t="inlineStr">
+      <c r="E56" s="58" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F56" s="54" t="inlineStr">
+      <c r="F56" s="58" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G56" s="54" t="inlineStr"/>
+      <c r="G56" s="58" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="52" t="inlineStr">
+      <c r="A57" s="56" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B57" s="52" t="inlineStr">
+      <c r="B57" s="56" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2410,22 +2438,22 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione sito nel Comune di Favignana, isola di Le</t>
         </is>
       </c>
-      <c r="D57" s="53" t="inlineStr">
+      <c r="D57" s="57" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-favignana-isola-levanzo</t>
         </is>
       </c>
-      <c r="E57" s="52" t="inlineStr">
+      <c r="E57" s="56" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F57" s="52" t="inlineStr">
+      <c r="F57" s="56" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G57" s="52" t="inlineStr"/>
+      <c r="G57" s="56" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="58" t="inlineStr">
@@ -2492,6 +2520,89 @@
         </is>
       </c>
       <c r="G59" s="56" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="62" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="62" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>INTERNAZIONALIZZAZIONESMAU – Italy RestartsUp in STOCCOLMAApertoFESR</t>
+        </is>
+      </c>
+      <c r="D60" s="63" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/smau-italy-restartsup-in-stoccolma/</t>
+        </is>
+      </c>
+      <c r="E60" s="62" t="inlineStr"/>
+      <c r="F60" s="62" t="inlineStr"/>
+      <c r="G60" s="62" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="60" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="60" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per Farnborough International AirshowApertoFESR</t>
+        </is>
+      </c>
+      <c r="D61" s="61" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-farnborough-international-airshow-2/</t>
+        </is>
+      </c>
+      <c r="E61" s="60" t="inlineStr"/>
+      <c r="F61" s="60" t="inlineStr"/>
+      <c r="G61" s="60" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="62" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="62" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA - alienazione lotto di terreno sito nel comune di Termini Imerese, via LibertàScade il:30/04/2026 - 12:00Leg</t>
+        </is>
+      </c>
+      <c r="D62" s="63" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proprieta-regionale-sito-nel-comune-termini-imerese-favore-ares-fabiola</t>
+        </is>
+      </c>
+      <c r="E62" s="62" t="inlineStr">
+        <is>
+          <t>30/04/2026 - 12:00</t>
+        </is>
+      </c>
+      <c r="F62" s="62" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="G62" s="62" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2553,6 +2664,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId61"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2597,7 +2711,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="56" t="inlineStr">
+      <c r="A3" s="60" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2610,29 +2724,29 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="58" t="inlineStr">
+      <c r="A4" s="62" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="56" t="inlineStr">
+      <c r="A5" s="60" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">

--- a/data/bandi_export.xlsx
+++ b/data/bandi_export.xlsx
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -267,6 +267,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -670,7 +682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -685,7 +697,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏛️  Nuovi Bandi — 01/04/2026 08:11</t>
+          <t>🏛️  Nuovi Bandi — 02/04/2026 08:01</t>
         </is>
       </c>
     </row>
@@ -730,78 +742,117 @@
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="60" t="inlineStr">
-        <is>
-          <t>Lazio</t>
+      <c r="B3" s="64" t="inlineStr">
+        <is>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>INTERNAZIONALIZZAZIONESMAU – Italy RestartsUp in STOCCOLMAApertoFESR</t>
-        </is>
-      </c>
-      <c r="D3" s="61" t="inlineStr">
-        <is>
-          <t>https://www.lazioeuropa.it/bandi/smau-italy-restartsup-in-stoccolma/</t>
-        </is>
-      </c>
-      <c r="E3" s="60" t="inlineStr"/>
-      <c r="F3" s="60" t="inlineStr"/>
+          <t>Avviso per la concessione di contributi per progetti di contrasto all'abbandono sportivo giovanile (2026)</t>
+        </is>
+      </c>
+      <c r="D3" s="65" t="inlineStr">
+        <is>
+          <t>https://www.regione.emilia-romagna.it/sport/bandi/2026/contrasto-abbandono-2026</t>
+        </is>
+      </c>
+      <c r="E3" s="64" t="inlineStr"/>
+      <c r="F3" s="64" t="inlineStr"/>
       <c r="G3" s="5" t="inlineStr"/>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="62" t="inlineStr">
-        <is>
-          <t>Lazio</t>
+      <c r="B4" s="66" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per Farnborough International AirshowApertoFESR</t>
-        </is>
-      </c>
-      <c r="D4" s="63" t="inlineStr">
-        <is>
-          <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-farnborough-international-airshow-2/</t>
-        </is>
-      </c>
-      <c r="E4" s="62" t="inlineStr"/>
-      <c r="F4" s="62" t="inlineStr"/>
+          <t>Avvisi pubbliciAvviso si procede alla riassegnazione della posizione organizzativa a supporto delle attività del Servizio 2 “Investimenti in Agricoltu</t>
+        </is>
+      </c>
+      <c r="D4" s="67" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-selezione-interna-conferimento-1-posizione-organizzativa-ai-sensi-artt-19-20-ccrl-2022-2024-comparto-non-dirigenziale</t>
+        </is>
+      </c>
+      <c r="E4" s="66" t="inlineStr">
+        <is>
+          <t>09/04/2026 - 12:00</t>
+        </is>
+      </c>
+      <c r="F4" s="66" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
       <c r="G4" s="9" t="inlineStr"/>
     </row>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="60" t="inlineStr">
+      <c r="B5" s="64" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA - alienazione lotto di terreno sito nel comune di Termini Imerese, via LibertàScade il:30/04/2026 - 12:00Leg</t>
-        </is>
-      </c>
-      <c r="D5" s="61" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proprieta-regionale-sito-nel-comune-termini-imerese-favore-ares-fabiola</t>
-        </is>
-      </c>
-      <c r="E5" s="60" t="inlineStr">
-        <is>
-          <t>30/04/2026 - 12:00</t>
-        </is>
-      </c>
-      <c r="F5" s="60" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
+          <t>Avvisi pubbliciST-MESSINA - AVVISO di INDAGINE DI MERCATO per affidamento "Interventi manutenzione straordinaria della strada/pista forestale "Annunzi</t>
+        </is>
+      </c>
+      <c r="D5" s="65" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-indagine-mercato-affidamento-interventi-manutenzione-straordinaria-stradapista-forestale-annunziata-comune-messina</t>
+        </is>
+      </c>
+      <c r="E5" s="64" t="inlineStr">
+        <is>
+          <t>16/04/2026 - 12:00</t>
+        </is>
+      </c>
+      <c r="F5" s="64" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="66" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Avvisi pubbliciST-MESSINA - AVVISO DI INDAGINE DI MERCATO per affidamento "Interventi manutenzione straordinaria della strada/pista forestale "San Riz</t>
+        </is>
+      </c>
+      <c r="D6" s="67" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-indagine-mercato-affidamento-interventi-manutenzione-straordinaria-stradapista-forestale-san-rizzo-san-leone-crupi-madonuzza-comune-messina</t>
+        </is>
+      </c>
+      <c r="E6" s="66" t="inlineStr">
+        <is>
+          <t>16/04/2026 - 12:00</t>
+        </is>
+      </c>
+      <c r="F6" s="66" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -811,6 +862,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -822,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -872,12 +924,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="58" t="inlineStr">
+      <c r="A2" s="62" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B2" s="58" t="inlineStr">
+      <c r="B2" s="62" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -887,22 +939,22 @@
           <t>FLAG GALPA Costa E-R. Sostituzione del motore principale e dei motori secondari. Secondo bando</t>
         </is>
       </c>
-      <c r="D2" s="59" t="inlineStr">
+      <c r="D2" s="63" t="inlineStr">
         <is>
           <t>https://agricoltura.regione.emilia-romagna.it/feampa-2021-2027/bandi-galpa/2026/galpa-sostituzione-motori-secondo-bando</t>
         </is>
       </c>
-      <c r="E2" s="58" t="inlineStr"/>
-      <c r="F2" s="58" t="inlineStr"/>
-      <c r="G2" s="58" t="inlineStr"/>
+      <c r="E2" s="62" t="inlineStr"/>
+      <c r="F2" s="62" t="inlineStr"/>
+      <c r="G2" s="62" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="56" t="inlineStr">
+      <c r="A3" s="60" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B3" s="56" t="inlineStr">
+      <c r="B3" s="60" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -912,22 +964,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0PRE-SEED 3.0Prossima AperturaFESR</t>
         </is>
       </c>
-      <c r="D3" s="57" t="inlineStr">
+      <c r="D3" s="61" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/pre-seed-3-0/</t>
         </is>
       </c>
-      <c r="E3" s="56" t="inlineStr"/>
-      <c r="F3" s="56" t="inlineStr"/>
-      <c r="G3" s="56" t="inlineStr"/>
+      <c r="E3" s="60" t="inlineStr"/>
+      <c r="F3" s="60" t="inlineStr"/>
+      <c r="G3" s="60" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="58" t="inlineStr">
+      <c r="A4" s="62" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B4" s="58" t="inlineStr">
+      <c r="B4" s="62" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -937,22 +989,22 @@
           <t>ACCESSO AL CREDITO E ALLE GARANZIE PER LE IMPRESEContributo su finanziamenti alle imprese del Lazio erogati su provvista BEIProssima AperturaFESR</t>
         </is>
       </c>
-      <c r="D4" s="59" t="inlineStr">
+      <c r="D4" s="63" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-su-finanziamenti-alle-imprese-del-lazio-erogati-su-provvista-bei/</t>
         </is>
       </c>
-      <c r="E4" s="58" t="inlineStr"/>
-      <c r="F4" s="58" t="inlineStr"/>
-      <c r="G4" s="58" t="inlineStr"/>
+      <c r="E4" s="62" t="inlineStr"/>
+      <c r="F4" s="62" t="inlineStr"/>
+      <c r="G4" s="62" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="56" t="inlineStr">
+      <c r="A5" s="60" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B5" s="56" t="inlineStr">
+      <c r="B5" s="60" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -962,22 +1014,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEIndividuazione degli enti iscritti al Registro unico nazionale del Terzo settoreApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D5" s="57" t="inlineStr">
+      <c r="D5" s="61" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/individuazione-degli-enti-iscritti-al-registro-unico-nazionale-del-terzo-settore/</t>
         </is>
       </c>
-      <c r="E5" s="56" t="inlineStr"/>
-      <c r="F5" s="56" t="inlineStr"/>
-      <c r="G5" s="56" t="inlineStr"/>
+      <c r="E5" s="60" t="inlineStr"/>
+      <c r="F5" s="60" t="inlineStr"/>
+      <c r="G5" s="60" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="58" t="inlineStr">
+      <c r="A6" s="62" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B6" s="58" t="inlineStr">
+      <c r="B6" s="62" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -987,22 +1039,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Technology Transfer LazioApertoFESR</t>
         </is>
       </c>
-      <c r="D6" s="59" t="inlineStr">
+      <c r="D6" s="63" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/technology-transfer-lazio/</t>
         </is>
       </c>
-      <c r="E6" s="58" t="inlineStr"/>
-      <c r="F6" s="58" t="inlineStr"/>
-      <c r="G6" s="58" t="inlineStr"/>
+      <c r="E6" s="62" t="inlineStr"/>
+      <c r="F6" s="62" t="inlineStr"/>
+      <c r="G6" s="62" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="56" t="inlineStr">
+      <c r="A7" s="60" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B7" s="56" t="inlineStr">
+      <c r="B7" s="60" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1012,22 +1064,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Percorso di tutoraggio per le impreseApertoFESR</t>
         </is>
       </c>
-      <c r="D7" s="57" t="inlineStr">
+      <c r="D7" s="61" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/percorso-di-tutoraggio-per-le-imprese/</t>
         </is>
       </c>
-      <c r="E7" s="56" t="inlineStr"/>
-      <c r="F7" s="56" t="inlineStr"/>
-      <c r="G7" s="56" t="inlineStr"/>
+      <c r="E7" s="60" t="inlineStr"/>
+      <c r="F7" s="60" t="inlineStr"/>
+      <c r="G7" s="60" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="58" t="inlineStr">
+      <c r="A8" s="62" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B8" s="58" t="inlineStr">
+      <c r="B8" s="62" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1037,22 +1089,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per partecipare a SMAU Parigi 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D8" s="59" t="inlineStr">
+      <c r="D8" s="63" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-partecipare-a-smau-parigi-2026/</t>
         </is>
       </c>
-      <c r="E8" s="58" t="inlineStr"/>
-      <c r="F8" s="58" t="inlineStr"/>
-      <c r="G8" s="58" t="inlineStr"/>
+      <c r="E8" s="62" t="inlineStr"/>
+      <c r="F8" s="62" t="inlineStr"/>
+      <c r="G8" s="62" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="56" t="inlineStr">
+      <c r="A9" s="60" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B9" s="56" t="inlineStr">
+      <c r="B9" s="60" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1062,22 +1114,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONERiconoscimento della funzione sociale ed educativa degli oratoriApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D9" s="57" t="inlineStr">
+      <c r="D9" s="61" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/riconoscimento-della-funzione-sociale-ed-educativa-degli-oratori/</t>
         </is>
       </c>
-      <c r="E9" s="56" t="inlineStr"/>
-      <c r="F9" s="56" t="inlineStr"/>
-      <c r="G9" s="56" t="inlineStr"/>
+      <c r="E9" s="60" t="inlineStr"/>
+      <c r="F9" s="60" t="inlineStr"/>
+      <c r="G9" s="60" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="58" t="inlineStr">
+      <c r="A10" s="62" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B10" s="58" t="inlineStr">
+      <c r="B10" s="62" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1087,22 +1139,22 @@
           <t>GovernanceIscrizione nell’elenco regionale degli idonei all’esercizio dell’attività di direttore dell’Istituto JemoloApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D10" s="59" t="inlineStr">
+      <c r="D10" s="63" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/iscrizione-nellelenco-regionale-degli-idonei-allesercizio-dellattivita-di-direttore-dellistituto-jemolo/</t>
         </is>
       </c>
-      <c r="E10" s="58" t="inlineStr"/>
-      <c r="F10" s="58" t="inlineStr"/>
-      <c r="G10" s="58" t="inlineStr"/>
+      <c r="E10" s="62" t="inlineStr"/>
+      <c r="F10" s="62" t="inlineStr"/>
+      <c r="G10" s="62" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="56" t="inlineStr">
+      <c r="A11" s="60" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B11" s="56" t="inlineStr">
+      <c r="B11" s="60" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1112,22 +1164,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEVoucher per lo sport – seconda annualitàApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D11" s="57" t="inlineStr">
+      <c r="D11" s="61" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/voucher-per-lo-sport-seconda-annualita/</t>
         </is>
       </c>
-      <c r="E11" s="56" t="inlineStr"/>
-      <c r="F11" s="56" t="inlineStr"/>
-      <c r="G11" s="56" t="inlineStr"/>
+      <c r="E11" s="60" t="inlineStr"/>
+      <c r="F11" s="60" t="inlineStr"/>
+      <c r="G11" s="60" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="58" t="inlineStr">
+      <c r="A12" s="62" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B12" s="58" t="inlineStr">
+      <c r="B12" s="62" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1137,22 +1189,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEBonus occupazionale SALGOApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D12" s="59" t="inlineStr">
+      <c r="D12" s="63" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/bonus-occupazionale-salgo/</t>
         </is>
       </c>
-      <c r="E12" s="58" t="inlineStr"/>
-      <c r="F12" s="58" t="inlineStr"/>
-      <c r="G12" s="58" t="inlineStr"/>
+      <c r="E12" s="62" t="inlineStr"/>
+      <c r="F12" s="62" t="inlineStr"/>
+      <c r="G12" s="62" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="56" t="inlineStr">
+      <c r="A13" s="60" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B13" s="56" t="inlineStr">
+      <c r="B13" s="60" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1162,22 +1214,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEContributo di Libertà per le donne che hanno subito violenzaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D13" s="57" t="inlineStr">
+      <c r="D13" s="61" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-di-liberta-per-le-donne-che-hanno-subito-violenza/</t>
         </is>
       </c>
-      <c r="E13" s="56" t="inlineStr"/>
-      <c r="F13" s="56" t="inlineStr"/>
-      <c r="G13" s="56" t="inlineStr"/>
+      <c r="E13" s="60" t="inlineStr"/>
+      <c r="F13" s="60" t="inlineStr"/>
+      <c r="G13" s="60" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="58" t="inlineStr">
+      <c r="A14" s="62" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B14" s="58" t="inlineStr">
+      <c r="B14" s="62" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1187,22 +1239,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURAInterventi straordinari di valorizzazione del patrimonio culturale del LazioApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D14" s="59" t="inlineStr">
+      <c r="D14" s="63" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/interventi-straordinari-di-valorizzazione-del-patrimonio-culturale-del-lazio/</t>
         </is>
       </c>
-      <c r="E14" s="58" t="inlineStr"/>
-      <c r="F14" s="58" t="inlineStr"/>
-      <c r="G14" s="58" t="inlineStr"/>
+      <c r="E14" s="62" t="inlineStr"/>
+      <c r="F14" s="62" t="inlineStr"/>
+      <c r="G14" s="62" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="56" t="inlineStr">
+      <c r="A15" s="60" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B15" s="56" t="inlineStr">
+      <c r="B15" s="60" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1212,30 +1264,30 @@
           <t>Bandi di garaBANDO ATTUAZIONE Ob. 1.1 Azione 1 codice 111102 _DIV - "SOSTEGNO ALLA DIVERSIFICAZIONE E NUOVE FORME DI REDDITO PER LA PICCOLA PESCA COST</t>
         </is>
       </c>
-      <c r="D15" s="57" t="inlineStr">
+      <c r="D15" s="61" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/bando-avviso-regia-ob-11-azione-1-codice-111102-div-sostegno-alla-diversificazione-nuove-forme-reddito-piccola-pesca-costiera</t>
         </is>
       </c>
-      <c r="E15" s="56" t="inlineStr">
+      <c r="E15" s="60" t="inlineStr">
         <is>
           <t>07/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F15" s="56" t="inlineStr">
+      <c r="F15" s="60" t="inlineStr">
         <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="G15" s="56" t="inlineStr"/>
+      <c r="G15" s="60" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="58" t="inlineStr">
+      <c r="A16" s="62" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B16" s="58" t="inlineStr">
+      <c r="B16" s="62" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1245,30 +1297,30 @@
           <t>Avvisi pubblici09 marzo 2026 - ST SIRACUSA - AVVISO PUBBLICO PER LA COSTITUZIONE DI ELENCHI DI OPERATORI ECONOMICI PER L’ACQUISIZIONE DI BENI E SERVIZ</t>
         </is>
       </c>
-      <c r="D16" s="59" t="inlineStr">
+      <c r="D16" s="63" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/09-marzo-2026-st-siracusa-avviso-pubblico-costituzione-elenchi-operatori-economici-l-acquisizione-beni-servizi</t>
         </is>
       </c>
-      <c r="E16" s="58" t="inlineStr">
+      <c r="E16" s="62" t="inlineStr">
         <is>
           <t>31/12/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F16" s="58" t="inlineStr">
+      <c r="F16" s="62" t="inlineStr">
         <is>
           <t>31/12/2026</t>
         </is>
       </c>
-      <c r="G16" s="58" t="inlineStr"/>
+      <c r="G16" s="62" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="56" t="inlineStr">
+      <c r="A17" s="60" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B17" s="56" t="inlineStr">
+      <c r="B17" s="60" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1278,30 +1330,30 @@
           <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScade il:19/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D17" s="57" t="inlineStr">
+      <c r="D17" s="61" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
         </is>
       </c>
-      <c r="E17" s="56" t="inlineStr">
+      <c r="E17" s="60" t="inlineStr">
         <is>
           <t>19/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F17" s="56" t="inlineStr">
+      <c r="F17" s="60" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G17" s="56" t="inlineStr"/>
+      <c r="G17" s="60" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="58" t="inlineStr">
+      <c r="A18" s="62" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B18" s="58" t="inlineStr">
+      <c r="B18" s="62" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1311,22 +1363,22 @@
           <t>Manifestazioni di interesseAvviso Manifestazione Interesse DISTRIBUTORI AUTOMATICI di bevande e snackScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D18" s="59" t="inlineStr">
+      <c r="D18" s="63" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-distributori-automatici-bevande-snack</t>
         </is>
       </c>
-      <c r="E18" s="58" t="inlineStr"/>
-      <c r="F18" s="58" t="inlineStr"/>
-      <c r="G18" s="58" t="inlineStr"/>
+      <c r="E18" s="62" t="inlineStr"/>
+      <c r="F18" s="62" t="inlineStr"/>
+      <c r="G18" s="62" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="56" t="inlineStr">
+      <c r="A19" s="60" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B19" s="56" t="inlineStr">
+      <c r="B19" s="60" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1336,30 +1388,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D19" s="57" t="inlineStr">
+      <c r="D19" s="61" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo</t>
         </is>
       </c>
-      <c r="E19" s="56" t="inlineStr">
+      <c r="E19" s="60" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F19" s="56" t="inlineStr">
+      <c r="F19" s="60" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G19" s="56" t="inlineStr"/>
+      <c r="G19" s="60" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="58" t="inlineStr">
+      <c r="A20" s="62" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B20" s="58" t="inlineStr">
+      <c r="B20" s="62" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1369,30 +1421,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D20" s="59" t="inlineStr">
+      <c r="D20" s="63" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo-0</t>
         </is>
       </c>
-      <c r="E20" s="58" t="inlineStr">
+      <c r="E20" s="62" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F20" s="58" t="inlineStr">
+      <c r="F20" s="62" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G20" s="58" t="inlineStr"/>
+      <c r="G20" s="62" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="56" t="inlineStr">
+      <c r="A21" s="60" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B21" s="56" t="inlineStr">
+      <c r="B21" s="60" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1402,22 +1454,22 @@
           <t>Manifestazioni di interesseST SIRACUSA - AVVISO DI MANIFESTAZIONE DI INTERESSE - Fornitura applicativo extracontabile per la gestione progetti, ecc. e</t>
         </is>
       </c>
-      <c r="D21" s="57" t="inlineStr">
+      <c r="D21" s="61" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-siracusa-avviso-manifestazione-interesse-fornitura-applicativo-extracontabile-gestione-progetti-ecc-applicativo-gestione-ed-elaborazione-informatizzata-paghe</t>
         </is>
       </c>
-      <c r="E21" s="56" t="inlineStr"/>
-      <c r="F21" s="56" t="inlineStr"/>
-      <c r="G21" s="56" t="inlineStr"/>
+      <c r="E21" s="60" t="inlineStr"/>
+      <c r="F21" s="60" t="inlineStr"/>
+      <c r="G21" s="60" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="58" t="inlineStr">
+      <c r="A22" s="62" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B22" s="58" t="inlineStr">
+      <c r="B22" s="62" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1427,30 +1479,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile sito nel Comune di Capo D'Orlando, Via Trazzera MarinaScade il:25/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D22" s="59" t="inlineStr">
+      <c r="D22" s="63" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-sito-nel-comune-capo-d-orlando-trazzera-marina</t>
         </is>
       </c>
-      <c r="E22" s="58" t="inlineStr">
+      <c r="E22" s="62" t="inlineStr">
         <is>
           <t>25/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F22" s="58" t="inlineStr">
+      <c r="F22" s="62" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="G22" s="58" t="inlineStr"/>
+      <c r="G22" s="62" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="56" t="inlineStr">
+      <c r="A23" s="60" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B23" s="56" t="inlineStr">
+      <c r="B23" s="60" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1460,22 +1512,22 @@
           <t xml:space="preserve">Avvisi pubbliciST CATANIA - Programma Regionale FESR Sicilia 2021-2027 - Azione 2.4.4 - “Interventi per la riduzione del rischio incendi” - AVVISO DI </t>
         </is>
       </c>
-      <c r="D23" s="57" t="inlineStr">
+      <c r="D23" s="61" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-catania-programma-regionale-fesr-sicilia-2021-2027-azione-244-interventi-riduzione-rischio-incendi-avviso-indagine-mercato</t>
         </is>
       </c>
-      <c r="E23" s="56" t="inlineStr"/>
-      <c r="F23" s="56" t="inlineStr"/>
-      <c r="G23" s="56" t="inlineStr"/>
+      <c r="E23" s="60" t="inlineStr"/>
+      <c r="F23" s="60" t="inlineStr"/>
+      <c r="G23" s="60" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="58" t="inlineStr">
+      <c r="A24" s="62" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B24" s="58" t="inlineStr">
+      <c r="B24" s="62" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1485,22 +1537,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per ROMICS – Primavera 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D24" s="59" t="inlineStr">
+      <c r="D24" s="63" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-romics-primavera-2026/</t>
         </is>
       </c>
-      <c r="E24" s="58" t="inlineStr"/>
-      <c r="F24" s="58" t="inlineStr"/>
-      <c r="G24" s="58" t="inlineStr"/>
+      <c r="E24" s="62" t="inlineStr"/>
+      <c r="F24" s="62" t="inlineStr"/>
+      <c r="G24" s="62" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="56" t="inlineStr">
+      <c r="A25" s="60" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B25" s="56" t="inlineStr">
+      <c r="B25" s="60" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1510,22 +1562,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Cinema International 2026 – I edizioneApertoFESR</t>
         </is>
       </c>
-      <c r="D25" s="57" t="inlineStr">
+      <c r="D25" s="61" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lazio-cinema-international-2026-i-edizione/</t>
         </is>
       </c>
-      <c r="E25" s="56" t="inlineStr"/>
-      <c r="F25" s="56" t="inlineStr"/>
-      <c r="G25" s="56" t="inlineStr"/>
+      <c r="E25" s="60" t="inlineStr"/>
+      <c r="F25" s="60" t="inlineStr"/>
+      <c r="G25" s="60" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="58" t="inlineStr">
+      <c r="A26" s="62" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B26" s="58" t="inlineStr">
+      <c r="B26" s="62" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1535,22 +1587,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEManifestazioni di interesse alla costituzione di due nuove Fondazioni I.T.S. AcademyApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D26" s="59" t="inlineStr">
+      <c r="D26" s="63" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazioni-di-interesse-alla-costituzione-di-due-nuove-fondazioni-i-t-s-academy/</t>
         </is>
       </c>
-      <c r="E26" s="58" t="inlineStr"/>
-      <c r="F26" s="58" t="inlineStr"/>
-      <c r="G26" s="58" t="inlineStr"/>
+      <c r="E26" s="62" t="inlineStr"/>
+      <c r="F26" s="62" t="inlineStr"/>
+      <c r="G26" s="62" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="56" t="inlineStr">
+      <c r="A27" s="60" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B27" s="56" t="inlineStr">
+      <c r="B27" s="60" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1560,22 +1612,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURAContributi per sostenere la ripresa del settore della pescaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D27" s="57" t="inlineStr">
+      <c r="D27" s="61" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributi-per-sostenere-la-ripresa-del-settore-della-pesca/</t>
         </is>
       </c>
-      <c r="E27" s="56" t="inlineStr"/>
-      <c r="F27" s="56" t="inlineStr"/>
-      <c r="G27" s="56" t="inlineStr"/>
+      <c r="E27" s="60" t="inlineStr"/>
+      <c r="F27" s="60" t="inlineStr"/>
+      <c r="G27" s="60" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="58" t="inlineStr">
+      <c r="A28" s="62" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B28" s="58" t="inlineStr">
+      <c r="B28" s="62" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1585,30 +1637,30 @@
           <t>Manifestazioni di interesseAVVISO - Manifestazione Interesse “Storytelling aziendale” Expo Wild Natura - Caccia - Pesca. Misterbianco (CT), 10-12 apri</t>
         </is>
       </c>
-      <c r="D28" s="59" t="inlineStr">
+      <c r="D28" s="63" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-storytelling-aziendale-expo-wild-natura-caccia-pesca-misterbianco-ct-10-12-aprile-2026</t>
         </is>
       </c>
-      <c r="E28" s="58" t="inlineStr">
+      <c r="E28" s="62" t="inlineStr">
         <is>
           <t>30/03/2026 - 13:00</t>
         </is>
       </c>
-      <c r="F28" s="58" t="inlineStr">
+      <c r="F28" s="62" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G28" s="58" t="inlineStr"/>
+      <c r="G28" s="62" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="56" t="inlineStr">
+      <c r="A29" s="60" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B29" s="56" t="inlineStr">
+      <c r="B29" s="60" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1618,30 +1670,30 @@
           <t>Manifestazioni di interesseInvaso Lentini - Interventi di ripristino delle pareti esterne in cls della Torre di presa Sud e della trave d’appoggio del</t>
         </is>
       </c>
-      <c r="D29" s="57" t="inlineStr">
+      <c r="D29" s="61" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/invaso-lentini-interventi-ripristino-pareti-esterne-cls-torre-presa-sud-trave-d-appoggio-cavalcavia-collegamento-alla-stessa-torre</t>
         </is>
       </c>
-      <c r="E29" s="56" t="inlineStr">
+      <c r="E29" s="60" t="inlineStr">
         <is>
           <t>19/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F29" s="56" t="inlineStr">
+      <c r="F29" s="60" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G29" s="56" t="inlineStr"/>
+      <c r="G29" s="60" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="58" t="inlineStr">
+      <c r="A30" s="62" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="B30" s="58" t="inlineStr">
+      <c r="B30" s="62" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1651,22 +1703,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURARistrutturazione e riconversione vigneti – campagna 2026-2027ApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D30" s="59" t="inlineStr">
+      <c r="D30" s="63" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/ristrutturazione-e-riconversione-vigneti-campagna-2026-2027/</t>
         </is>
       </c>
-      <c r="E30" s="58" t="inlineStr"/>
-      <c r="F30" s="58" t="inlineStr"/>
-      <c r="G30" s="58" t="inlineStr"/>
+      <c r="E30" s="62" t="inlineStr"/>
+      <c r="F30" s="62" t="inlineStr"/>
+      <c r="G30" s="62" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="56" t="inlineStr">
+      <c r="A31" s="60" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="B31" s="56" t="inlineStr">
+      <c r="B31" s="60" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1676,30 +1728,30 @@
           <t>Manifestazioni di interessePR FESR 2021/27 Azione 1.3.3 e del POC 2014/20 - Azione 1.3.1  - Avviso a manifestazione d’interesse eventi fieristici inte</t>
         </is>
       </c>
-      <c r="D31" s="57" t="inlineStr">
+      <c r="D31" s="61" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-d-interesse-eventi-fieristici-internazionali-marzo-dicembre-2026</t>
         </is>
       </c>
-      <c r="E31" s="56" t="inlineStr">
+      <c r="E31" s="60" t="inlineStr">
         <is>
           <t>30/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F31" s="56" t="inlineStr">
+      <c r="F31" s="60" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="G31" s="56" t="inlineStr"/>
+      <c r="G31" s="60" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="58" t="inlineStr">
+      <c r="A32" s="62" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="B32" s="58" t="inlineStr">
+      <c r="B32" s="62" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1709,22 +1761,22 @@
           <t>INTERNAZIONALIZZAZIONEL’Ecosistema dell’Innovazione a INNOVIT – Focus S3ApertoFESR</t>
         </is>
       </c>
-      <c r="D32" s="59" t="inlineStr">
+      <c r="D32" s="63" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lecosistema-dellinnovazione-a-innovit-focus-s3/</t>
         </is>
       </c>
-      <c r="E32" s="58" t="inlineStr"/>
-      <c r="F32" s="58" t="inlineStr"/>
-      <c r="G32" s="58" t="inlineStr"/>
+      <c r="E32" s="62" t="inlineStr"/>
+      <c r="F32" s="62" t="inlineStr"/>
+      <c r="G32" s="62" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="56" t="inlineStr">
+      <c r="A33" s="60" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="B33" s="56" t="inlineStr">
+      <c r="B33" s="60" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1734,22 +1786,22 @@
           <t>Manifestazioni di interessePR FESR SICILIA 2021/27 - NUOVO Avviso a manifestazione d’interesse per esperti valutatoriScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D33" s="57" t="inlineStr">
+      <c r="D33" s="61" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/pr-fesr-sicilia-202127-nuovo-avviso-manifestazione-d-interesse-esperti-valutatori</t>
         </is>
       </c>
-      <c r="E33" s="56" t="inlineStr"/>
-      <c r="F33" s="56" t="inlineStr"/>
-      <c r="G33" s="56" t="inlineStr"/>
+      <c r="E33" s="60" t="inlineStr"/>
+      <c r="F33" s="60" t="inlineStr"/>
+      <c r="G33" s="60" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="58" t="inlineStr">
+      <c r="A34" s="62" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="B34" s="58" t="inlineStr">
+      <c r="B34" s="62" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -1759,22 +1811,22 @@
           <t>Bando 2026 per contributi dedicati alla manutenzione della rete dei percorsi escursionistici</t>
         </is>
       </c>
-      <c r="D34" s="59" t="inlineStr">
+      <c r="D34" s="63" t="inlineStr">
         <is>
           <t>https://ambiente.regione.emilia-romagna.it/it/parchi-natura2000/bandi/bando-2026-per-contributi-dedicati-alla-manutenzione-della-rete-dei-percorsi-escursionistici</t>
         </is>
       </c>
-      <c r="E34" s="58" t="inlineStr"/>
-      <c r="F34" s="58" t="inlineStr"/>
-      <c r="G34" s="58" t="inlineStr"/>
+      <c r="E34" s="62" t="inlineStr"/>
+      <c r="F34" s="62" t="inlineStr"/>
+      <c r="G34" s="62" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="56" t="inlineStr">
+      <c r="A35" s="60" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="B35" s="56" t="inlineStr">
+      <c r="B35" s="60" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1784,22 +1836,22 @@
           <t>Programma regionale in favore delle tradizioni storiche, artistiche, religiose e popolari (2026) – manifestazioni d’interesseApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D35" s="57" t="inlineStr">
+      <c r="D35" s="61" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/programma-regionale-in-favore-delle-tradizioni-storiche-artistiche-religiose-e-popolari-2026-manifestazioni-dinteresse/</t>
         </is>
       </c>
-      <c r="E35" s="56" t="inlineStr"/>
-      <c r="F35" s="56" t="inlineStr"/>
-      <c r="G35" s="56" t="inlineStr"/>
+      <c r="E35" s="60" t="inlineStr"/>
+      <c r="F35" s="60" t="inlineStr"/>
+      <c r="G35" s="60" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="58" t="inlineStr">
+      <c r="A36" s="62" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B36" s="58" t="inlineStr">
+      <c r="B36" s="62" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1809,22 +1861,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEBuoni servizio per le persone non autosufficienti nel territorio del LazioProssima AperturaFSE / FSE+</t>
         </is>
       </c>
-      <c r="D36" s="59" t="inlineStr">
+      <c r="D36" s="63" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/buoni-servizio-per-le-persone-non-autosufficienti-nel-territorio-del-lazio/</t>
         </is>
       </c>
-      <c r="E36" s="58" t="inlineStr"/>
-      <c r="F36" s="58" t="inlineStr"/>
-      <c r="G36" s="58" t="inlineStr"/>
+      <c r="E36" s="62" t="inlineStr"/>
+      <c r="F36" s="62" t="inlineStr"/>
+      <c r="G36" s="62" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="56" t="inlineStr">
+      <c r="A37" s="60" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B37" s="56" t="inlineStr">
+      <c r="B37" s="60" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1834,22 +1886,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONERimborso delle rette dei servizi educativi nel territorio del LazioProssima AperturaFSE / FSE+</t>
         </is>
       </c>
-      <c r="D37" s="57" t="inlineStr">
+      <c r="D37" s="61" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/rimborso-delle-rette-dei-servizi-educativi-nel-territorio-del-lazio/</t>
         </is>
       </c>
-      <c r="E37" s="56" t="inlineStr"/>
-      <c r="F37" s="56" t="inlineStr"/>
-      <c r="G37" s="56" t="inlineStr"/>
+      <c r="E37" s="60" t="inlineStr"/>
+      <c r="F37" s="60" t="inlineStr"/>
+      <c r="G37" s="60" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="58" t="inlineStr">
+      <c r="A38" s="62" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B38" s="58" t="inlineStr">
+      <c r="B38" s="62" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1859,30 +1911,30 @@
           <t>Manifestazioni di interesseATTO DI INTERPELLO PER L’AFFIDAMENTO DELL’INCARICO DI COLLAUDO STATICO DELLE STRUTTURE - Diga di Pietrarossa (Progetto ex C</t>
         </is>
       </c>
-      <c r="D38" s="59" t="inlineStr">
+      <c r="D38" s="63" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/atto-interpello-l-affidamento-incarico-collaudo-statico-strutture-diga-pietrarossa-progetto-ex-casmez-303219</t>
         </is>
       </c>
-      <c r="E38" s="58" t="inlineStr">
+      <c r="E38" s="62" t="inlineStr">
         <is>
           <t>27/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F38" s="58" t="inlineStr">
+      <c r="F38" s="62" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="G38" s="58" t="inlineStr"/>
+      <c r="G38" s="62" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="56" t="inlineStr">
+      <c r="A39" s="60" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B39" s="56" t="inlineStr">
+      <c r="B39" s="60" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1892,30 +1944,30 @@
           <t>Manifestazioni di interesseAvviso alle Case  Editrici della Regione siciliana per la partecipazione al Salone del Libro di Torino, 14-18  maggio 2026.</t>
         </is>
       </c>
-      <c r="D39" s="57" t="inlineStr">
+      <c r="D39" s="61" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/manifestazione-d-interesse-partecipare-al-xxxviii-salone-libro-torino-14-al-18-maggio-2026-attraverso-l-esposizione-pubblicazioni-presso-stand-assessorato-beni</t>
         </is>
       </c>
-      <c r="E39" s="56" t="inlineStr">
+      <c r="E39" s="60" t="inlineStr">
         <is>
           <t>30/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F39" s="56" t="inlineStr">
+      <c r="F39" s="60" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="G39" s="56" t="inlineStr"/>
+      <c r="G39" s="60" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="58" t="inlineStr">
+      <c r="A40" s="62" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B40" s="58" t="inlineStr">
+      <c r="B40" s="62" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1925,30 +1977,30 @@
           <t xml:space="preserve">Manifestazioni di interessePR FESR SICILIA 2021/27 - NUOVO Avviso a manifestazione d’interesse per esperti valutatoriScade il:06/04/2026 - 23:59Leggi </t>
         </is>
       </c>
-      <c r="D40" s="59" t="inlineStr">
+      <c r="D40" s="63" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/pr-fesr-sicilia-202127-nuovo-avviso-manifestazione-d-interesse-esperti-valutatori</t>
         </is>
       </c>
-      <c r="E40" s="58" t="inlineStr">
+      <c r="E40" s="62" t="inlineStr">
         <is>
           <t>06/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F40" s="58" t="inlineStr">
+      <c r="F40" s="62" t="inlineStr">
         <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="G40" s="58" t="inlineStr"/>
+      <c r="G40" s="62" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="56" t="inlineStr">
+      <c r="A41" s="60" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B41" s="56" t="inlineStr">
+      <c r="B41" s="60" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1958,22 +2010,22 @@
           <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D41" s="57" t="inlineStr">
+      <c r="D41" s="61" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
         </is>
       </c>
-      <c r="E41" s="56" t="inlineStr"/>
-      <c r="F41" s="56" t="inlineStr"/>
-      <c r="G41" s="56" t="inlineStr"/>
+      <c r="E41" s="60" t="inlineStr"/>
+      <c r="F41" s="60" t="inlineStr"/>
+      <c r="G41" s="60" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="58" t="inlineStr">
+      <c r="A42" s="62" t="inlineStr">
         <is>
           <t>24/03/2026</t>
         </is>
       </c>
-      <c r="B42" s="58" t="inlineStr">
+      <c r="B42" s="62" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -1983,22 +2035,22 @@
           <t>GAL del Ducato - Promozione di fiere agroalimentari e delle filiere del cibo – Bando per Enti pubblici (DU AS 05B)</t>
         </is>
       </c>
-      <c r="D42" s="59" t="inlineStr">
+      <c r="D42" s="63" t="inlineStr">
         <is>
           <t>https://agricoltura.regione.emilia-romagna.it/sviluppo-rurale-23-27/opportunita/bandi-gal/2026/du_as05b-promozione-di-fiere-agroalimentari-e-delle-filiere-del-cibo-bando-per-enti-pubblici</t>
         </is>
       </c>
-      <c r="E42" s="58" t="inlineStr"/>
-      <c r="F42" s="58" t="inlineStr"/>
-      <c r="G42" s="58" t="inlineStr"/>
+      <c r="E42" s="62" t="inlineStr"/>
+      <c r="F42" s="62" t="inlineStr"/>
+      <c r="G42" s="62" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="56" t="inlineStr">
+      <c r="A43" s="60" t="inlineStr">
         <is>
           <t>24/03/2026</t>
         </is>
       </c>
-      <c r="B43" s="56" t="inlineStr">
+      <c r="B43" s="60" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2008,30 +2060,30 @@
           <t>Manifestazioni di interesseAVVISO PUBBLICO PER MANIFESTAZIONE DI INTERESSE FINALIZZATA ALL'ASSEGNAZIONE DI SPAZI ESPOSITIVI (CORNER GRATUITI) ALL'INTE</t>
         </is>
       </c>
-      <c r="D43" s="57" t="inlineStr">
+      <c r="D43" s="61" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-manifestazione-interesse-finalizzata-all-assegnazione-spazi-espositivi-corner-gratuiti-all-interno-stand-istituzionale-dsrt-manifestazione</t>
         </is>
       </c>
-      <c r="E43" s="56" t="inlineStr">
+      <c r="E43" s="60" t="inlineStr">
         <is>
           <t>30/03/2026 - 13:00</t>
         </is>
       </c>
-      <c r="F43" s="56" t="inlineStr">
+      <c r="F43" s="60" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G43" s="56" t="inlineStr"/>
+      <c r="G43" s="60" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="58" t="inlineStr">
+      <c r="A44" s="62" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B44" s="58" t="inlineStr">
+      <c r="B44" s="62" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2041,22 +2093,22 @@
           <t>Avviso per la concessione di contributi per eventi sportivi realizzati in Emilia-Romagna - Anno 2026</t>
         </is>
       </c>
-      <c r="D44" s="59" t="inlineStr">
+      <c r="D44" s="63" t="inlineStr">
         <is>
           <t>https://www.regione.emilia-romagna.it/sport/bandi/2026/bando-2026</t>
         </is>
       </c>
-      <c r="E44" s="58" t="inlineStr"/>
-      <c r="F44" s="58" t="inlineStr"/>
-      <c r="G44" s="58" t="inlineStr"/>
+      <c r="E44" s="62" t="inlineStr"/>
+      <c r="F44" s="62" t="inlineStr"/>
+      <c r="G44" s="62" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="56" t="inlineStr">
+      <c r="A45" s="60" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B45" s="56" t="inlineStr">
+      <c r="B45" s="60" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2066,22 +2118,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Street art 2026Prossima AperturaBandi Regionali</t>
         </is>
       </c>
-      <c r="D45" s="57" t="inlineStr">
+      <c r="D45" s="61" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lazio-street-art-2026/</t>
         </is>
       </c>
-      <c r="E45" s="56" t="inlineStr"/>
-      <c r="F45" s="56" t="inlineStr"/>
-      <c r="G45" s="56" t="inlineStr"/>
+      <c r="E45" s="60" t="inlineStr"/>
+      <c r="F45" s="60" t="inlineStr"/>
+      <c r="G45" s="60" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="58" t="inlineStr">
+      <c r="A46" s="62" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B46" s="58" t="inlineStr">
+      <c r="B46" s="62" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2091,30 +2143,30 @@
           <t>Manifestazioni di interesseManifestazione di interesse per la partecipazione all’evento “R2I Italy 2026” – Bologna, 12-13/05/2026Scade il:03/04/2026 -</t>
         </is>
       </c>
-      <c r="D46" s="59" t="inlineStr">
+      <c r="D46" s="63" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/manifestazione-interesse-partecipazione-all-evento-r2i-italy-2026-bologna-12-13052026</t>
         </is>
       </c>
-      <c r="E46" s="58" t="inlineStr">
+      <c r="E46" s="62" t="inlineStr">
         <is>
           <t>03/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F46" s="58" t="inlineStr">
+      <c r="F46" s="62" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="G46" s="58" t="inlineStr"/>
+      <c r="G46" s="62" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="56" t="inlineStr">
+      <c r="A47" s="60" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B47" s="56" t="inlineStr">
+      <c r="B47" s="60" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2124,30 +2176,30 @@
           <t>Manifestazioni di interesseST SIRACUSA - AVVISO PER MANIFESTAZIONE DI INTERESSE - Selezione di n. 5 unità di personale internoScade il:20/04/2026 - 12</t>
         </is>
       </c>
-      <c r="D47" s="57" t="inlineStr">
+      <c r="D47" s="61" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/24-marzo-2026-st-siracusa-avviso-manifestazione-interesse-selezione-n-5-unita-personale-interno</t>
         </is>
       </c>
-      <c r="E47" s="56" t="inlineStr">
+      <c r="E47" s="60" t="inlineStr">
         <is>
           <t>20/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F47" s="56" t="inlineStr">
+      <c r="F47" s="60" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="G47" s="56" t="inlineStr"/>
+      <c r="G47" s="60" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="58" t="inlineStr">
+      <c r="A48" s="62" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B48" s="58" t="inlineStr">
+      <c r="B48" s="62" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2157,30 +2209,30 @@
           <t>Avvisi pubbliciRevoca dell’avviso di concessione a titolo gratuito del 16.12.2025 inerente all’immobile di seguito identificato e contestuale nuovo av</t>
         </is>
       </c>
-      <c r="D48" s="59" t="inlineStr">
+      <c r="D48" s="63" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/revoca-avviso-concessione-titolo-gratuito-16122025-inerente-all-immobile-seguito-identificato-contestuale-nuovo-avviso-concessione-titolo-oneroso-stesso-sito-nel</t>
         </is>
       </c>
-      <c r="E48" s="58" t="inlineStr">
+      <c r="E48" s="62" t="inlineStr">
         <is>
           <t>08/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F48" s="58" t="inlineStr">
+      <c r="F48" s="62" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="G48" s="58" t="inlineStr"/>
+      <c r="G48" s="62" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="56" t="inlineStr">
+      <c r="A49" s="60" t="inlineStr">
         <is>
           <t>26/03/2026</t>
         </is>
       </c>
-      <c r="B49" s="56" t="inlineStr">
+      <c r="B49" s="60" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2190,22 +2242,22 @@
           <t>Bando studi di fattibilità per fusioni di Comuni</t>
         </is>
       </c>
-      <c r="D49" s="57" t="inlineStr">
+      <c r="D49" s="61" t="inlineStr">
         <is>
           <t>https://www.regione.emilia-romagna.it/autonomie-locali/bandi/bando_studi_fattibilita_fusioni_comuni</t>
         </is>
       </c>
-      <c r="E49" s="56" t="inlineStr"/>
-      <c r="F49" s="56" t="inlineStr"/>
-      <c r="G49" s="56" t="inlineStr"/>
+      <c r="E49" s="60" t="inlineStr"/>
+      <c r="F49" s="60" t="inlineStr"/>
+      <c r="G49" s="60" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="58" t="inlineStr">
+      <c r="A50" s="62" t="inlineStr">
         <is>
           <t>26/03/2026</t>
         </is>
       </c>
-      <c r="B50" s="58" t="inlineStr">
+      <c r="B50" s="62" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2215,30 +2267,30 @@
           <t xml:space="preserve">Manifestazioni di interesseAvviso pubblico di selezione interna, per titoli, per il conferimento di PO e professionali, ai sensi degli artt. 19, 20 e </t>
         </is>
       </c>
-      <c r="D50" s="59" t="inlineStr">
+      <c r="D50" s="63" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-selezione-interna-titoli-conferimento-po-professionali-ai-sensi-artt-19-20-21-ccrl-20222024-comparto-non-dirigenziale</t>
         </is>
       </c>
-      <c r="E50" s="58" t="inlineStr">
+      <c r="E50" s="62" t="inlineStr">
         <is>
           <t>30/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F50" s="58" t="inlineStr">
+      <c r="F50" s="62" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G50" s="58" t="inlineStr"/>
+      <c r="G50" s="62" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="56" t="inlineStr">
+      <c r="A51" s="60" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="B51" s="56" t="inlineStr">
+      <c r="B51" s="60" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2248,22 +2300,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0PRE-SEED 3.0ApertoFESR</t>
         </is>
       </c>
-      <c r="D51" s="57" t="inlineStr">
+      <c r="D51" s="61" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/pre-seed-3-0/</t>
         </is>
       </c>
-      <c r="E51" s="56" t="inlineStr"/>
-      <c r="F51" s="56" t="inlineStr"/>
-      <c r="G51" s="56" t="inlineStr"/>
+      <c r="E51" s="60" t="inlineStr"/>
+      <c r="F51" s="60" t="inlineStr"/>
+      <c r="G51" s="60" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="58" t="inlineStr">
+      <c r="A52" s="62" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B52" s="58" t="inlineStr">
+      <c r="B52" s="62" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2273,30 +2325,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “So</t>
         </is>
       </c>
-      <c r="D52" s="59" t="inlineStr">
+      <c r="D52" s="63" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-termini-imerese-locta-piazza-marina</t>
         </is>
       </c>
-      <c r="E52" s="58" t="inlineStr">
+      <c r="E52" s="62" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F52" s="58" t="inlineStr">
+      <c r="F52" s="62" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G52" s="58" t="inlineStr"/>
+      <c r="G52" s="62" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="56" t="inlineStr">
+      <c r="A53" s="60" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B53" s="56" t="inlineStr">
+      <c r="B53" s="60" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2306,30 +2358,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, Sig</t>
         </is>
       </c>
-      <c r="D53" s="57" t="inlineStr">
+      <c r="D53" s="61" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-porto-empedocle-locta-punta-piccola</t>
         </is>
       </c>
-      <c r="E53" s="56" t="inlineStr">
+      <c r="E53" s="60" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F53" s="56" t="inlineStr">
+      <c r="F53" s="60" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G53" s="56" t="inlineStr"/>
+      <c r="G53" s="60" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="58" t="inlineStr">
+      <c r="A54" s="62" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B54" s="58" t="inlineStr">
+      <c r="B54" s="62" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2339,30 +2391,30 @@
           <t xml:space="preserve">Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “Società </t>
         </is>
       </c>
-      <c r="D54" s="59" t="inlineStr">
+      <c r="D54" s="63" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-messina-locta-torrente-bordonaro</t>
         </is>
       </c>
-      <c r="E54" s="58" t="inlineStr">
+      <c r="E54" s="62" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F54" s="58" t="inlineStr">
+      <c r="F54" s="62" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G54" s="58" t="inlineStr"/>
+      <c r="G54" s="62" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="56" t="inlineStr">
+      <c r="A55" s="60" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B55" s="56" t="inlineStr">
+      <c r="B55" s="60" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2372,30 +2424,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “Condomin</t>
         </is>
       </c>
-      <c r="D55" s="57" t="inlineStr">
+      <c r="D55" s="61" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-mascali-spiaggia-n-144150</t>
         </is>
       </c>
-      <c r="E55" s="56" t="inlineStr">
+      <c r="E55" s="60" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F55" s="56" t="inlineStr">
+      <c r="F55" s="60" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G55" s="56" t="inlineStr"/>
+      <c r="G55" s="60" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="58" t="inlineStr">
+      <c r="A56" s="62" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B56" s="58" t="inlineStr">
+      <c r="B56" s="62" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2405,30 +2457,30 @@
           <t xml:space="preserve">Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione sito nel Comune di Lipari, isola di Stromboli, </t>
         </is>
       </c>
-      <c r="D56" s="59" t="inlineStr">
+      <c r="D56" s="63" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-lipari-isola-stromboli-locta-fico-grande</t>
         </is>
       </c>
-      <c r="E56" s="58" t="inlineStr">
+      <c r="E56" s="62" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F56" s="58" t="inlineStr">
+      <c r="F56" s="62" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G56" s="58" t="inlineStr"/>
+      <c r="G56" s="62" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="56" t="inlineStr">
+      <c r="A57" s="60" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B57" s="56" t="inlineStr">
+      <c r="B57" s="60" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2438,30 +2490,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione sito nel Comune di Favignana, isola di Le</t>
         </is>
       </c>
-      <c r="D57" s="57" t="inlineStr">
+      <c r="D57" s="61" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-favignana-isola-levanzo</t>
         </is>
       </c>
-      <c r="E57" s="56" t="inlineStr">
+      <c r="E57" s="60" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F57" s="56" t="inlineStr">
+      <c r="F57" s="60" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G57" s="56" t="inlineStr"/>
+      <c r="G57" s="60" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="58" t="inlineStr">
+      <c r="A58" s="62" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="B58" s="58" t="inlineStr">
+      <c r="B58" s="62" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2471,30 +2523,30 @@
           <t>Manifestazioni di interesseAVVISO - Manifestazione d’interesse finalizzata alla selezione di organismi attuatori di piani di gestione locale della pic</t>
         </is>
       </c>
-      <c r="D58" s="59" t="inlineStr">
+      <c r="D58" s="63" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-d-interesse-finalizzata-alla-selezione-organismi-attuatori-piani-gestione-locale-piccola-pesca-costiera-nelle-gsa-regione-siciliana</t>
         </is>
       </c>
-      <c r="E58" s="58" t="inlineStr">
+      <c r="E58" s="62" t="inlineStr">
         <is>
           <t>29/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F58" s="58" t="inlineStr">
+      <c r="F58" s="62" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="G58" s="58" t="inlineStr"/>
+      <c r="G58" s="62" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="56" t="inlineStr">
+      <c r="A59" s="60" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="B59" s="56" t="inlineStr">
+      <c r="B59" s="60" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2504,22 +2556,22 @@
           <t>Avvisi pubbliciLeggi e scarica l'avvisoScade il:02/04/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D59" s="57" t="inlineStr">
+      <c r="D59" s="61" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/proroga-termini-presentazione-candidature-po</t>
         </is>
       </c>
-      <c r="E59" s="56" t="inlineStr">
+      <c r="E59" s="60" t="inlineStr">
         <is>
           <t>02/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F59" s="56" t="inlineStr">
+      <c r="F59" s="60" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="G59" s="56" t="inlineStr"/>
+      <c r="G59" s="60" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="62" t="inlineStr">
@@ -2603,6 +2655,130 @@
         </is>
       </c>
       <c r="G62" s="62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="64" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="64" t="inlineStr">
+        <is>
+          <t>Emilia-Romagna</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>Avviso per la concessione di contributi per progetti di contrasto all'abbandono sportivo giovanile (2026)</t>
+        </is>
+      </c>
+      <c r="D63" s="65" t="inlineStr">
+        <is>
+          <t>https://www.regione.emilia-romagna.it/sport/bandi/2026/contrasto-abbandono-2026</t>
+        </is>
+      </c>
+      <c r="E63" s="64" t="inlineStr"/>
+      <c r="F63" s="64" t="inlineStr"/>
+      <c r="G63" s="64" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="66" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="66" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>Avvisi pubbliciAvviso si procede alla riassegnazione della posizione organizzativa a supporto delle attività del Servizio 2 “Investimenti in Agricoltu</t>
+        </is>
+      </c>
+      <c r="D64" s="67" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-selezione-interna-conferimento-1-posizione-organizzativa-ai-sensi-artt-19-20-ccrl-2022-2024-comparto-non-dirigenziale</t>
+        </is>
+      </c>
+      <c r="E64" s="66" t="inlineStr">
+        <is>
+          <t>09/04/2026 - 12:00</t>
+        </is>
+      </c>
+      <c r="F64" s="66" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="G64" s="66" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="64" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="64" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>Avvisi pubbliciST-MESSINA - AVVISO di INDAGINE DI MERCATO per affidamento "Interventi manutenzione straordinaria della strada/pista forestale "Annunzi</t>
+        </is>
+      </c>
+      <c r="D65" s="65" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-indagine-mercato-affidamento-interventi-manutenzione-straordinaria-stradapista-forestale-annunziata-comune-messina</t>
+        </is>
+      </c>
+      <c r="E65" s="64" t="inlineStr">
+        <is>
+          <t>16/04/2026 - 12:00</t>
+        </is>
+      </c>
+      <c r="F65" s="64" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="G65" s="64" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="66" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="66" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>Avvisi pubbliciST-MESSINA - AVVISO DI INDAGINE DI MERCATO per affidamento "Interventi manutenzione straordinaria della strada/pista forestale "San Riz</t>
+        </is>
+      </c>
+      <c r="D66" s="67" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-indagine-mercato-affidamento-interventi-manutenzione-straordinaria-stradapista-forestale-san-rizzo-san-leone-crupi-madonuzza-comune-messina</t>
+        </is>
+      </c>
+      <c r="E66" s="66" t="inlineStr">
+        <is>
+          <t>16/04/2026 - 12:00</t>
+        </is>
+      </c>
+      <c r="F66" s="66" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="G66" s="66" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2667,6 +2843,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D60" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D66" r:id="rId65"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2711,20 +2891,20 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="60" t="inlineStr">
+      <c r="A3" s="64" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="62" t="inlineStr">
+      <c r="A4" s="66" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2733,20 +2913,20 @@
         <v>25</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="60" t="inlineStr">
+      <c r="A5" s="64" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">

--- a/data/bandi_export.xlsx
+++ b/data/bandi_export.xlsx
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -267,6 +267,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -682,7 +694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -697,7 +709,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏛️  Nuovi Bandi — 02/04/2026 08:01</t>
+          <t>🏛️  Nuovi Bandi — 03/04/2026 07:58</t>
         </is>
       </c>
     </row>
@@ -742,83 +754,75 @@
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="64" t="inlineStr">
-        <is>
-          <t>Emilia-Romagna</t>
+      <c r="B3" s="68" t="inlineStr">
+        <is>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Avviso per la concessione di contributi per progetti di contrasto all'abbandono sportivo giovanile (2026)</t>
-        </is>
-      </c>
-      <c r="D3" s="65" t="inlineStr">
-        <is>
-          <t>https://www.regione.emilia-romagna.it/sport/bandi/2026/contrasto-abbandono-2026</t>
-        </is>
-      </c>
-      <c r="E3" s="64" t="inlineStr"/>
-      <c r="F3" s="64" t="inlineStr"/>
+          <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Manifestazione di interesse per Casaidea 2026ApertoFESR</t>
+        </is>
+      </c>
+      <c r="D3" s="69" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-casaidea-2026/</t>
+        </is>
+      </c>
+      <c r="E3" s="68" t="inlineStr"/>
+      <c r="F3" s="68" t="inlineStr"/>
       <c r="G3" s="5" t="inlineStr"/>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="66" t="inlineStr">
-        <is>
-          <t>Sicilia</t>
+      <c r="B4" s="70" t="inlineStr">
+        <is>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>Avvisi pubbliciAvviso si procede alla riassegnazione della posizione organizzativa a supporto delle attività del Servizio 2 “Investimenti in Agricoltu</t>
-        </is>
-      </c>
-      <c r="D4" s="67" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-selezione-interna-conferimento-1-posizione-organizzativa-ai-sensi-artt-19-20-ccrl-2022-2024-comparto-non-dirigenziale</t>
-        </is>
-      </c>
-      <c r="E4" s="66" t="inlineStr">
-        <is>
-          <t>09/04/2026 - 12:00</t>
-        </is>
-      </c>
-      <c r="F4" s="66" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
+          <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per il Salone Internazionale del Libro di Torino 2026ApertoFESR</t>
+        </is>
+      </c>
+      <c r="D4" s="71" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-il-salone-internazionale-del-libro-di-torino-2026/</t>
+        </is>
+      </c>
+      <c r="E4" s="70" t="inlineStr"/>
+      <c r="F4" s="70" t="inlineStr"/>
       <c r="G4" s="9" t="inlineStr"/>
     </row>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="64" t="inlineStr">
+      <c r="B5" s="68" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Avvisi pubbliciST-MESSINA - AVVISO di INDAGINE DI MERCATO per affidamento "Interventi manutenzione straordinaria della strada/pista forestale "Annunzi</t>
-        </is>
-      </c>
-      <c r="D5" s="65" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-indagine-mercato-affidamento-interventi-manutenzione-straordinaria-stradapista-forestale-annunziata-comune-messina</t>
-        </is>
-      </c>
-      <c r="E5" s="64" t="inlineStr">
-        <is>
-          <t>16/04/2026 - 12:00</t>
-        </is>
-      </c>
-      <c r="F5" s="64" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
+          <t>Avvisi pubbliciDDG 1112 del 02.04.2026 - Aggiornamento Avviso pubblico n. 4/2024 per l’attuazione del PAR GOL Sicilia da finanziare nell’ambito del Pi</t>
+        </is>
+      </c>
+      <c r="D5" s="69" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/ddg-1112-02042026-aggiornamento-avviso-pubblico-n-42024-l-attuazione-par-gol-sicilia-finanziare-nell-ambito-piano-nazionale-ripresa-resilienza-pnrr</t>
+        </is>
+      </c>
+      <c r="E5" s="68" t="inlineStr">
+        <is>
+          <t>05/04/2030 - 00:00</t>
+        </is>
+      </c>
+      <c r="F5" s="68" t="inlineStr">
+        <is>
+          <t>05/04/2030</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr"/>
@@ -827,32 +831,55 @@
       <c r="A6" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="66" t="inlineStr">
+      <c r="B6" s="70" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>Avvisi pubbliciST-MESSINA - AVVISO DI INDAGINE DI MERCATO per affidamento "Interventi manutenzione straordinaria della strada/pista forestale "San Riz</t>
-        </is>
-      </c>
-      <c r="D6" s="67" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-indagine-mercato-affidamento-interventi-manutenzione-straordinaria-stradapista-forestale-san-rizzo-san-leone-crupi-madonuzza-comune-messina</t>
-        </is>
-      </c>
-      <c r="E6" s="66" t="inlineStr">
-        <is>
-          <t>16/04/2026 - 12:00</t>
-        </is>
-      </c>
-      <c r="F6" s="66" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
+          <t>Avvisi pubbliciDDG 1113 del  02.04.2026 - Aggiornamento Avviso pubblico n. 2/2022 e s.m.i per l’attuazione del PAR GOL Sicilia da finanziare nell’ambi</t>
+        </is>
+      </c>
+      <c r="D6" s="71" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/ddg-1113-02042026-aggiornamento-avviso-pubblico-n-22022-smi-l-attuazione-par-gol-sicilia-finanziare-nell-ambito-piano-nazionale-ripresa-resilienza-pnrr</t>
+        </is>
+      </c>
+      <c r="E6" s="70" t="inlineStr">
+        <is>
+          <t>03/04/2030 - 00:00</t>
+        </is>
+      </c>
+      <c r="F6" s="70" t="inlineStr">
+        <is>
+          <t>03/04/2030</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr"/>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="68" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Avvisi pubbliciLeggi e scarica l'avvisoScadutoLeggi di più</t>
+        </is>
+      </c>
+      <c r="D7" s="69" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/proroga-termini-presentazione-candidature-po</t>
+        </is>
+      </c>
+      <c r="E7" s="68" t="inlineStr"/>
+      <c r="F7" s="68" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -863,6 +890,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -874,7 +902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -924,12 +952,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="62" t="inlineStr">
+      <c r="A2" s="66" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B2" s="62" t="inlineStr">
+      <c r="B2" s="66" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -939,22 +967,22 @@
           <t>FLAG GALPA Costa E-R. Sostituzione del motore principale e dei motori secondari. Secondo bando</t>
         </is>
       </c>
-      <c r="D2" s="63" t="inlineStr">
+      <c r="D2" s="67" t="inlineStr">
         <is>
           <t>https://agricoltura.regione.emilia-romagna.it/feampa-2021-2027/bandi-galpa/2026/galpa-sostituzione-motori-secondo-bando</t>
         </is>
       </c>
-      <c r="E2" s="62" t="inlineStr"/>
-      <c r="F2" s="62" t="inlineStr"/>
-      <c r="G2" s="62" t="inlineStr"/>
+      <c r="E2" s="66" t="inlineStr"/>
+      <c r="F2" s="66" t="inlineStr"/>
+      <c r="G2" s="66" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="60" t="inlineStr">
+      <c r="A3" s="64" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B3" s="60" t="inlineStr">
+      <c r="B3" s="64" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -964,22 +992,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0PRE-SEED 3.0Prossima AperturaFESR</t>
         </is>
       </c>
-      <c r="D3" s="61" t="inlineStr">
+      <c r="D3" s="65" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/pre-seed-3-0/</t>
         </is>
       </c>
-      <c r="E3" s="60" t="inlineStr"/>
-      <c r="F3" s="60" t="inlineStr"/>
-      <c r="G3" s="60" t="inlineStr"/>
+      <c r="E3" s="64" t="inlineStr"/>
+      <c r="F3" s="64" t="inlineStr"/>
+      <c r="G3" s="64" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="62" t="inlineStr">
+      <c r="A4" s="66" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B4" s="62" t="inlineStr">
+      <c r="B4" s="66" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -989,22 +1017,22 @@
           <t>ACCESSO AL CREDITO E ALLE GARANZIE PER LE IMPRESEContributo su finanziamenti alle imprese del Lazio erogati su provvista BEIProssima AperturaFESR</t>
         </is>
       </c>
-      <c r="D4" s="63" t="inlineStr">
+      <c r="D4" s="67" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-su-finanziamenti-alle-imprese-del-lazio-erogati-su-provvista-bei/</t>
         </is>
       </c>
-      <c r="E4" s="62" t="inlineStr"/>
-      <c r="F4" s="62" t="inlineStr"/>
-      <c r="G4" s="62" t="inlineStr"/>
+      <c r="E4" s="66" t="inlineStr"/>
+      <c r="F4" s="66" t="inlineStr"/>
+      <c r="G4" s="66" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="60" t="inlineStr">
+      <c r="A5" s="64" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B5" s="60" t="inlineStr">
+      <c r="B5" s="64" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1014,22 +1042,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEIndividuazione degli enti iscritti al Registro unico nazionale del Terzo settoreApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D5" s="61" t="inlineStr">
+      <c r="D5" s="65" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/individuazione-degli-enti-iscritti-al-registro-unico-nazionale-del-terzo-settore/</t>
         </is>
       </c>
-      <c r="E5" s="60" t="inlineStr"/>
-      <c r="F5" s="60" t="inlineStr"/>
-      <c r="G5" s="60" t="inlineStr"/>
+      <c r="E5" s="64" t="inlineStr"/>
+      <c r="F5" s="64" t="inlineStr"/>
+      <c r="G5" s="64" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="62" t="inlineStr">
+      <c r="A6" s="66" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B6" s="62" t="inlineStr">
+      <c r="B6" s="66" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1039,22 +1067,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Technology Transfer LazioApertoFESR</t>
         </is>
       </c>
-      <c r="D6" s="63" t="inlineStr">
+      <c r="D6" s="67" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/technology-transfer-lazio/</t>
         </is>
       </c>
-      <c r="E6" s="62" t="inlineStr"/>
-      <c r="F6" s="62" t="inlineStr"/>
-      <c r="G6" s="62" t="inlineStr"/>
+      <c r="E6" s="66" t="inlineStr"/>
+      <c r="F6" s="66" t="inlineStr"/>
+      <c r="G6" s="66" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="60" t="inlineStr">
+      <c r="A7" s="64" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B7" s="60" t="inlineStr">
+      <c r="B7" s="64" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1064,22 +1092,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Percorso di tutoraggio per le impreseApertoFESR</t>
         </is>
       </c>
-      <c r="D7" s="61" t="inlineStr">
+      <c r="D7" s="65" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/percorso-di-tutoraggio-per-le-imprese/</t>
         </is>
       </c>
-      <c r="E7" s="60" t="inlineStr"/>
-      <c r="F7" s="60" t="inlineStr"/>
-      <c r="G7" s="60" t="inlineStr"/>
+      <c r="E7" s="64" t="inlineStr"/>
+      <c r="F7" s="64" t="inlineStr"/>
+      <c r="G7" s="64" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="62" t="inlineStr">
+      <c r="A8" s="66" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B8" s="62" t="inlineStr">
+      <c r="B8" s="66" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1089,22 +1117,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per partecipare a SMAU Parigi 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D8" s="63" t="inlineStr">
+      <c r="D8" s="67" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-partecipare-a-smau-parigi-2026/</t>
         </is>
       </c>
-      <c r="E8" s="62" t="inlineStr"/>
-      <c r="F8" s="62" t="inlineStr"/>
-      <c r="G8" s="62" t="inlineStr"/>
+      <c r="E8" s="66" t="inlineStr"/>
+      <c r="F8" s="66" t="inlineStr"/>
+      <c r="G8" s="66" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="60" t="inlineStr">
+      <c r="A9" s="64" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B9" s="60" t="inlineStr">
+      <c r="B9" s="64" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1114,22 +1142,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONERiconoscimento della funzione sociale ed educativa degli oratoriApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D9" s="61" t="inlineStr">
+      <c r="D9" s="65" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/riconoscimento-della-funzione-sociale-ed-educativa-degli-oratori/</t>
         </is>
       </c>
-      <c r="E9" s="60" t="inlineStr"/>
-      <c r="F9" s="60" t="inlineStr"/>
-      <c r="G9" s="60" t="inlineStr"/>
+      <c r="E9" s="64" t="inlineStr"/>
+      <c r="F9" s="64" t="inlineStr"/>
+      <c r="G9" s="64" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="62" t="inlineStr">
+      <c r="A10" s="66" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B10" s="62" t="inlineStr">
+      <c r="B10" s="66" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1139,22 +1167,22 @@
           <t>GovernanceIscrizione nell’elenco regionale degli idonei all’esercizio dell’attività di direttore dell’Istituto JemoloApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D10" s="63" t="inlineStr">
+      <c r="D10" s="67" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/iscrizione-nellelenco-regionale-degli-idonei-allesercizio-dellattivita-di-direttore-dellistituto-jemolo/</t>
         </is>
       </c>
-      <c r="E10" s="62" t="inlineStr"/>
-      <c r="F10" s="62" t="inlineStr"/>
-      <c r="G10" s="62" t="inlineStr"/>
+      <c r="E10" s="66" t="inlineStr"/>
+      <c r="F10" s="66" t="inlineStr"/>
+      <c r="G10" s="66" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="60" t="inlineStr">
+      <c r="A11" s="64" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B11" s="60" t="inlineStr">
+      <c r="B11" s="64" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1164,22 +1192,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEVoucher per lo sport – seconda annualitàApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D11" s="61" t="inlineStr">
+      <c r="D11" s="65" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/voucher-per-lo-sport-seconda-annualita/</t>
         </is>
       </c>
-      <c r="E11" s="60" t="inlineStr"/>
-      <c r="F11" s="60" t="inlineStr"/>
-      <c r="G11" s="60" t="inlineStr"/>
+      <c r="E11" s="64" t="inlineStr"/>
+      <c r="F11" s="64" t="inlineStr"/>
+      <c r="G11" s="64" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="62" t="inlineStr">
+      <c r="A12" s="66" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B12" s="62" t="inlineStr">
+      <c r="B12" s="66" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1189,22 +1217,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEBonus occupazionale SALGOApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D12" s="63" t="inlineStr">
+      <c r="D12" s="67" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/bonus-occupazionale-salgo/</t>
         </is>
       </c>
-      <c r="E12" s="62" t="inlineStr"/>
-      <c r="F12" s="62" t="inlineStr"/>
-      <c r="G12" s="62" t="inlineStr"/>
+      <c r="E12" s="66" t="inlineStr"/>
+      <c r="F12" s="66" t="inlineStr"/>
+      <c r="G12" s="66" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="60" t="inlineStr">
+      <c r="A13" s="64" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B13" s="60" t="inlineStr">
+      <c r="B13" s="64" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1214,22 +1242,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEContributo di Libertà per le donne che hanno subito violenzaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D13" s="61" t="inlineStr">
+      <c r="D13" s="65" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-di-liberta-per-le-donne-che-hanno-subito-violenza/</t>
         </is>
       </c>
-      <c r="E13" s="60" t="inlineStr"/>
-      <c r="F13" s="60" t="inlineStr"/>
-      <c r="G13" s="60" t="inlineStr"/>
+      <c r="E13" s="64" t="inlineStr"/>
+      <c r="F13" s="64" t="inlineStr"/>
+      <c r="G13" s="64" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="62" t="inlineStr">
+      <c r="A14" s="66" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B14" s="62" t="inlineStr">
+      <c r="B14" s="66" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1239,22 +1267,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURAInterventi straordinari di valorizzazione del patrimonio culturale del LazioApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D14" s="63" t="inlineStr">
+      <c r="D14" s="67" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/interventi-straordinari-di-valorizzazione-del-patrimonio-culturale-del-lazio/</t>
         </is>
       </c>
-      <c r="E14" s="62" t="inlineStr"/>
-      <c r="F14" s="62" t="inlineStr"/>
-      <c r="G14" s="62" t="inlineStr"/>
+      <c r="E14" s="66" t="inlineStr"/>
+      <c r="F14" s="66" t="inlineStr"/>
+      <c r="G14" s="66" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="60" t="inlineStr">
+      <c r="A15" s="64" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B15" s="60" t="inlineStr">
+      <c r="B15" s="64" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1264,30 +1292,30 @@
           <t>Bandi di garaBANDO ATTUAZIONE Ob. 1.1 Azione 1 codice 111102 _DIV - "SOSTEGNO ALLA DIVERSIFICAZIONE E NUOVE FORME DI REDDITO PER LA PICCOLA PESCA COST</t>
         </is>
       </c>
-      <c r="D15" s="61" t="inlineStr">
+      <c r="D15" s="65" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/bando-avviso-regia-ob-11-azione-1-codice-111102-div-sostegno-alla-diversificazione-nuove-forme-reddito-piccola-pesca-costiera</t>
         </is>
       </c>
-      <c r="E15" s="60" t="inlineStr">
+      <c r="E15" s="64" t="inlineStr">
         <is>
           <t>07/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F15" s="60" t="inlineStr">
+      <c r="F15" s="64" t="inlineStr">
         <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="G15" s="60" t="inlineStr"/>
+      <c r="G15" s="64" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="62" t="inlineStr">
+      <c r="A16" s="66" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B16" s="62" t="inlineStr">
+      <c r="B16" s="66" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1297,30 +1325,30 @@
           <t>Avvisi pubblici09 marzo 2026 - ST SIRACUSA - AVVISO PUBBLICO PER LA COSTITUZIONE DI ELENCHI DI OPERATORI ECONOMICI PER L’ACQUISIZIONE DI BENI E SERVIZ</t>
         </is>
       </c>
-      <c r="D16" s="63" t="inlineStr">
+      <c r="D16" s="67" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/09-marzo-2026-st-siracusa-avviso-pubblico-costituzione-elenchi-operatori-economici-l-acquisizione-beni-servizi</t>
         </is>
       </c>
-      <c r="E16" s="62" t="inlineStr">
+      <c r="E16" s="66" t="inlineStr">
         <is>
           <t>31/12/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F16" s="62" t="inlineStr">
+      <c r="F16" s="66" t="inlineStr">
         <is>
           <t>31/12/2026</t>
         </is>
       </c>
-      <c r="G16" s="62" t="inlineStr"/>
+      <c r="G16" s="66" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="60" t="inlineStr">
+      <c r="A17" s="64" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B17" s="60" t="inlineStr">
+      <c r="B17" s="64" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1330,30 +1358,30 @@
           <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScade il:19/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D17" s="61" t="inlineStr">
+      <c r="D17" s="65" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
         </is>
       </c>
-      <c r="E17" s="60" t="inlineStr">
+      <c r="E17" s="64" t="inlineStr">
         <is>
           <t>19/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F17" s="60" t="inlineStr">
+      <c r="F17" s="64" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G17" s="60" t="inlineStr"/>
+      <c r="G17" s="64" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="62" t="inlineStr">
+      <c r="A18" s="66" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B18" s="62" t="inlineStr">
+      <c r="B18" s="66" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1363,22 +1391,22 @@
           <t>Manifestazioni di interesseAvviso Manifestazione Interesse DISTRIBUTORI AUTOMATICI di bevande e snackScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D18" s="63" t="inlineStr">
+      <c r="D18" s="67" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-distributori-automatici-bevande-snack</t>
         </is>
       </c>
-      <c r="E18" s="62" t="inlineStr"/>
-      <c r="F18" s="62" t="inlineStr"/>
-      <c r="G18" s="62" t="inlineStr"/>
+      <c r="E18" s="66" t="inlineStr"/>
+      <c r="F18" s="66" t="inlineStr"/>
+      <c r="G18" s="66" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="60" t="inlineStr">
+      <c r="A19" s="64" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B19" s="60" t="inlineStr">
+      <c r="B19" s="64" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1388,30 +1416,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D19" s="61" t="inlineStr">
+      <c r="D19" s="65" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo</t>
         </is>
       </c>
-      <c r="E19" s="60" t="inlineStr">
+      <c r="E19" s="64" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F19" s="60" t="inlineStr">
+      <c r="F19" s="64" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G19" s="60" t="inlineStr"/>
+      <c r="G19" s="64" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="62" t="inlineStr">
+      <c r="A20" s="66" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B20" s="62" t="inlineStr">
+      <c r="B20" s="66" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1421,30 +1449,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D20" s="63" t="inlineStr">
+      <c r="D20" s="67" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo-0</t>
         </is>
       </c>
-      <c r="E20" s="62" t="inlineStr">
+      <c r="E20" s="66" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F20" s="62" t="inlineStr">
+      <c r="F20" s="66" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G20" s="62" t="inlineStr"/>
+      <c r="G20" s="66" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="60" t="inlineStr">
+      <c r="A21" s="64" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B21" s="60" t="inlineStr">
+      <c r="B21" s="64" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1454,22 +1482,22 @@
           <t>Manifestazioni di interesseST SIRACUSA - AVVISO DI MANIFESTAZIONE DI INTERESSE - Fornitura applicativo extracontabile per la gestione progetti, ecc. e</t>
         </is>
       </c>
-      <c r="D21" s="61" t="inlineStr">
+      <c r="D21" s="65" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-siracusa-avviso-manifestazione-interesse-fornitura-applicativo-extracontabile-gestione-progetti-ecc-applicativo-gestione-ed-elaborazione-informatizzata-paghe</t>
         </is>
       </c>
-      <c r="E21" s="60" t="inlineStr"/>
-      <c r="F21" s="60" t="inlineStr"/>
-      <c r="G21" s="60" t="inlineStr"/>
+      <c r="E21" s="64" t="inlineStr"/>
+      <c r="F21" s="64" t="inlineStr"/>
+      <c r="G21" s="64" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="62" t="inlineStr">
+      <c r="A22" s="66" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B22" s="62" t="inlineStr">
+      <c r="B22" s="66" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1479,30 +1507,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile sito nel Comune di Capo D'Orlando, Via Trazzera MarinaScade il:25/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D22" s="63" t="inlineStr">
+      <c r="D22" s="67" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-sito-nel-comune-capo-d-orlando-trazzera-marina</t>
         </is>
       </c>
-      <c r="E22" s="62" t="inlineStr">
+      <c r="E22" s="66" t="inlineStr">
         <is>
           <t>25/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F22" s="62" t="inlineStr">
+      <c r="F22" s="66" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="G22" s="62" t="inlineStr"/>
+      <c r="G22" s="66" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="60" t="inlineStr">
+      <c r="A23" s="64" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B23" s="60" t="inlineStr">
+      <c r="B23" s="64" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1512,22 +1540,22 @@
           <t xml:space="preserve">Avvisi pubbliciST CATANIA - Programma Regionale FESR Sicilia 2021-2027 - Azione 2.4.4 - “Interventi per la riduzione del rischio incendi” - AVVISO DI </t>
         </is>
       </c>
-      <c r="D23" s="61" t="inlineStr">
+      <c r="D23" s="65" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-catania-programma-regionale-fesr-sicilia-2021-2027-azione-244-interventi-riduzione-rischio-incendi-avviso-indagine-mercato</t>
         </is>
       </c>
-      <c r="E23" s="60" t="inlineStr"/>
-      <c r="F23" s="60" t="inlineStr"/>
-      <c r="G23" s="60" t="inlineStr"/>
+      <c r="E23" s="64" t="inlineStr"/>
+      <c r="F23" s="64" t="inlineStr"/>
+      <c r="G23" s="64" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="62" t="inlineStr">
+      <c r="A24" s="66" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B24" s="62" t="inlineStr">
+      <c r="B24" s="66" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1537,22 +1565,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per ROMICS – Primavera 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D24" s="63" t="inlineStr">
+      <c r="D24" s="67" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-romics-primavera-2026/</t>
         </is>
       </c>
-      <c r="E24" s="62" t="inlineStr"/>
-      <c r="F24" s="62" t="inlineStr"/>
-      <c r="G24" s="62" t="inlineStr"/>
+      <c r="E24" s="66" t="inlineStr"/>
+      <c r="F24" s="66" t="inlineStr"/>
+      <c r="G24" s="66" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="60" t="inlineStr">
+      <c r="A25" s="64" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B25" s="60" t="inlineStr">
+      <c r="B25" s="64" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1562,22 +1590,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Cinema International 2026 – I edizioneApertoFESR</t>
         </is>
       </c>
-      <c r="D25" s="61" t="inlineStr">
+      <c r="D25" s="65" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lazio-cinema-international-2026-i-edizione/</t>
         </is>
       </c>
-      <c r="E25" s="60" t="inlineStr"/>
-      <c r="F25" s="60" t="inlineStr"/>
-      <c r="G25" s="60" t="inlineStr"/>
+      <c r="E25" s="64" t="inlineStr"/>
+      <c r="F25" s="64" t="inlineStr"/>
+      <c r="G25" s="64" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="62" t="inlineStr">
+      <c r="A26" s="66" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B26" s="62" t="inlineStr">
+      <c r="B26" s="66" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1587,22 +1615,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEManifestazioni di interesse alla costituzione di due nuove Fondazioni I.T.S. AcademyApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D26" s="63" t="inlineStr">
+      <c r="D26" s="67" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazioni-di-interesse-alla-costituzione-di-due-nuove-fondazioni-i-t-s-academy/</t>
         </is>
       </c>
-      <c r="E26" s="62" t="inlineStr"/>
-      <c r="F26" s="62" t="inlineStr"/>
-      <c r="G26" s="62" t="inlineStr"/>
+      <c r="E26" s="66" t="inlineStr"/>
+      <c r="F26" s="66" t="inlineStr"/>
+      <c r="G26" s="66" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="60" t="inlineStr">
+      <c r="A27" s="64" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B27" s="60" t="inlineStr">
+      <c r="B27" s="64" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1612,22 +1640,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURAContributi per sostenere la ripresa del settore della pescaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D27" s="61" t="inlineStr">
+      <c r="D27" s="65" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributi-per-sostenere-la-ripresa-del-settore-della-pesca/</t>
         </is>
       </c>
-      <c r="E27" s="60" t="inlineStr"/>
-      <c r="F27" s="60" t="inlineStr"/>
-      <c r="G27" s="60" t="inlineStr"/>
+      <c r="E27" s="64" t="inlineStr"/>
+      <c r="F27" s="64" t="inlineStr"/>
+      <c r="G27" s="64" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="62" t="inlineStr">
+      <c r="A28" s="66" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B28" s="62" t="inlineStr">
+      <c r="B28" s="66" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1637,30 +1665,30 @@
           <t>Manifestazioni di interesseAVVISO - Manifestazione Interesse “Storytelling aziendale” Expo Wild Natura - Caccia - Pesca. Misterbianco (CT), 10-12 apri</t>
         </is>
       </c>
-      <c r="D28" s="63" t="inlineStr">
+      <c r="D28" s="67" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-storytelling-aziendale-expo-wild-natura-caccia-pesca-misterbianco-ct-10-12-aprile-2026</t>
         </is>
       </c>
-      <c r="E28" s="62" t="inlineStr">
+      <c r="E28" s="66" t="inlineStr">
         <is>
           <t>30/03/2026 - 13:00</t>
         </is>
       </c>
-      <c r="F28" s="62" t="inlineStr">
+      <c r="F28" s="66" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G28" s="62" t="inlineStr"/>
+      <c r="G28" s="66" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="60" t="inlineStr">
+      <c r="A29" s="64" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B29" s="60" t="inlineStr">
+      <c r="B29" s="64" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1670,30 +1698,30 @@
           <t>Manifestazioni di interesseInvaso Lentini - Interventi di ripristino delle pareti esterne in cls della Torre di presa Sud e della trave d’appoggio del</t>
         </is>
       </c>
-      <c r="D29" s="61" t="inlineStr">
+      <c r="D29" s="65" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/invaso-lentini-interventi-ripristino-pareti-esterne-cls-torre-presa-sud-trave-d-appoggio-cavalcavia-collegamento-alla-stessa-torre</t>
         </is>
       </c>
-      <c r="E29" s="60" t="inlineStr">
+      <c r="E29" s="64" t="inlineStr">
         <is>
           <t>19/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F29" s="60" t="inlineStr">
+      <c r="F29" s="64" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G29" s="60" t="inlineStr"/>
+      <c r="G29" s="64" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="62" t="inlineStr">
+      <c r="A30" s="66" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="B30" s="62" t="inlineStr">
+      <c r="B30" s="66" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1703,22 +1731,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURARistrutturazione e riconversione vigneti – campagna 2026-2027ApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D30" s="63" t="inlineStr">
+      <c r="D30" s="67" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/ristrutturazione-e-riconversione-vigneti-campagna-2026-2027/</t>
         </is>
       </c>
-      <c r="E30" s="62" t="inlineStr"/>
-      <c r="F30" s="62" t="inlineStr"/>
-      <c r="G30" s="62" t="inlineStr"/>
+      <c r="E30" s="66" t="inlineStr"/>
+      <c r="F30" s="66" t="inlineStr"/>
+      <c r="G30" s="66" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="60" t="inlineStr">
+      <c r="A31" s="64" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="B31" s="60" t="inlineStr">
+      <c r="B31" s="64" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1728,30 +1756,30 @@
           <t>Manifestazioni di interessePR FESR 2021/27 Azione 1.3.3 e del POC 2014/20 - Azione 1.3.1  - Avviso a manifestazione d’interesse eventi fieristici inte</t>
         </is>
       </c>
-      <c r="D31" s="61" t="inlineStr">
+      <c r="D31" s="65" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-d-interesse-eventi-fieristici-internazionali-marzo-dicembre-2026</t>
         </is>
       </c>
-      <c r="E31" s="60" t="inlineStr">
+      <c r="E31" s="64" t="inlineStr">
         <is>
           <t>30/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F31" s="60" t="inlineStr">
+      <c r="F31" s="64" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="G31" s="60" t="inlineStr"/>
+      <c r="G31" s="64" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="62" t="inlineStr">
+      <c r="A32" s="66" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="B32" s="62" t="inlineStr">
+      <c r="B32" s="66" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1761,22 +1789,22 @@
           <t>INTERNAZIONALIZZAZIONEL’Ecosistema dell’Innovazione a INNOVIT – Focus S3ApertoFESR</t>
         </is>
       </c>
-      <c r="D32" s="63" t="inlineStr">
+      <c r="D32" s="67" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lecosistema-dellinnovazione-a-innovit-focus-s3/</t>
         </is>
       </c>
-      <c r="E32" s="62" t="inlineStr"/>
-      <c r="F32" s="62" t="inlineStr"/>
-      <c r="G32" s="62" t="inlineStr"/>
+      <c r="E32" s="66" t="inlineStr"/>
+      <c r="F32" s="66" t="inlineStr"/>
+      <c r="G32" s="66" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="60" t="inlineStr">
+      <c r="A33" s="64" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="B33" s="60" t="inlineStr">
+      <c r="B33" s="64" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1786,22 +1814,22 @@
           <t>Manifestazioni di interessePR FESR SICILIA 2021/27 - NUOVO Avviso a manifestazione d’interesse per esperti valutatoriScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D33" s="61" t="inlineStr">
+      <c r="D33" s="65" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/pr-fesr-sicilia-202127-nuovo-avviso-manifestazione-d-interesse-esperti-valutatori</t>
         </is>
       </c>
-      <c r="E33" s="60" t="inlineStr"/>
-      <c r="F33" s="60" t="inlineStr"/>
-      <c r="G33" s="60" t="inlineStr"/>
+      <c r="E33" s="64" t="inlineStr"/>
+      <c r="F33" s="64" t="inlineStr"/>
+      <c r="G33" s="64" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="62" t="inlineStr">
+      <c r="A34" s="66" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="B34" s="62" t="inlineStr">
+      <c r="B34" s="66" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -1811,22 +1839,22 @@
           <t>Bando 2026 per contributi dedicati alla manutenzione della rete dei percorsi escursionistici</t>
         </is>
       </c>
-      <c r="D34" s="63" t="inlineStr">
+      <c r="D34" s="67" t="inlineStr">
         <is>
           <t>https://ambiente.regione.emilia-romagna.it/it/parchi-natura2000/bandi/bando-2026-per-contributi-dedicati-alla-manutenzione-della-rete-dei-percorsi-escursionistici</t>
         </is>
       </c>
-      <c r="E34" s="62" t="inlineStr"/>
-      <c r="F34" s="62" t="inlineStr"/>
-      <c r="G34" s="62" t="inlineStr"/>
+      <c r="E34" s="66" t="inlineStr"/>
+      <c r="F34" s="66" t="inlineStr"/>
+      <c r="G34" s="66" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="60" t="inlineStr">
+      <c r="A35" s="64" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="B35" s="60" t="inlineStr">
+      <c r="B35" s="64" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1836,22 +1864,22 @@
           <t>Programma regionale in favore delle tradizioni storiche, artistiche, religiose e popolari (2026) – manifestazioni d’interesseApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D35" s="61" t="inlineStr">
+      <c r="D35" s="65" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/programma-regionale-in-favore-delle-tradizioni-storiche-artistiche-religiose-e-popolari-2026-manifestazioni-dinteresse/</t>
         </is>
       </c>
-      <c r="E35" s="60" t="inlineStr"/>
-      <c r="F35" s="60" t="inlineStr"/>
-      <c r="G35" s="60" t="inlineStr"/>
+      <c r="E35" s="64" t="inlineStr"/>
+      <c r="F35" s="64" t="inlineStr"/>
+      <c r="G35" s="64" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="62" t="inlineStr">
+      <c r="A36" s="66" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B36" s="62" t="inlineStr">
+      <c r="B36" s="66" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1861,22 +1889,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEBuoni servizio per le persone non autosufficienti nel territorio del LazioProssima AperturaFSE / FSE+</t>
         </is>
       </c>
-      <c r="D36" s="63" t="inlineStr">
+      <c r="D36" s="67" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/buoni-servizio-per-le-persone-non-autosufficienti-nel-territorio-del-lazio/</t>
         </is>
       </c>
-      <c r="E36" s="62" t="inlineStr"/>
-      <c r="F36" s="62" t="inlineStr"/>
-      <c r="G36" s="62" t="inlineStr"/>
+      <c r="E36" s="66" t="inlineStr"/>
+      <c r="F36" s="66" t="inlineStr"/>
+      <c r="G36" s="66" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="60" t="inlineStr">
+      <c r="A37" s="64" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B37" s="60" t="inlineStr">
+      <c r="B37" s="64" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1886,22 +1914,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONERimborso delle rette dei servizi educativi nel territorio del LazioProssima AperturaFSE / FSE+</t>
         </is>
       </c>
-      <c r="D37" s="61" t="inlineStr">
+      <c r="D37" s="65" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/rimborso-delle-rette-dei-servizi-educativi-nel-territorio-del-lazio/</t>
         </is>
       </c>
-      <c r="E37" s="60" t="inlineStr"/>
-      <c r="F37" s="60" t="inlineStr"/>
-      <c r="G37" s="60" t="inlineStr"/>
+      <c r="E37" s="64" t="inlineStr"/>
+      <c r="F37" s="64" t="inlineStr"/>
+      <c r="G37" s="64" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="62" t="inlineStr">
+      <c r="A38" s="66" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B38" s="62" t="inlineStr">
+      <c r="B38" s="66" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1911,30 +1939,30 @@
           <t>Manifestazioni di interesseATTO DI INTERPELLO PER L’AFFIDAMENTO DELL’INCARICO DI COLLAUDO STATICO DELLE STRUTTURE - Diga di Pietrarossa (Progetto ex C</t>
         </is>
       </c>
-      <c r="D38" s="63" t="inlineStr">
+      <c r="D38" s="67" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/atto-interpello-l-affidamento-incarico-collaudo-statico-strutture-diga-pietrarossa-progetto-ex-casmez-303219</t>
         </is>
       </c>
-      <c r="E38" s="62" t="inlineStr">
+      <c r="E38" s="66" t="inlineStr">
         <is>
           <t>27/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F38" s="62" t="inlineStr">
+      <c r="F38" s="66" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="G38" s="62" t="inlineStr"/>
+      <c r="G38" s="66" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="60" t="inlineStr">
+      <c r="A39" s="64" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B39" s="60" t="inlineStr">
+      <c r="B39" s="64" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1944,30 +1972,30 @@
           <t>Manifestazioni di interesseAvviso alle Case  Editrici della Regione siciliana per la partecipazione al Salone del Libro di Torino, 14-18  maggio 2026.</t>
         </is>
       </c>
-      <c r="D39" s="61" t="inlineStr">
+      <c r="D39" s="65" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/manifestazione-d-interesse-partecipare-al-xxxviii-salone-libro-torino-14-al-18-maggio-2026-attraverso-l-esposizione-pubblicazioni-presso-stand-assessorato-beni</t>
         </is>
       </c>
-      <c r="E39" s="60" t="inlineStr">
+      <c r="E39" s="64" t="inlineStr">
         <is>
           <t>30/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F39" s="60" t="inlineStr">
+      <c r="F39" s="64" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="G39" s="60" t="inlineStr"/>
+      <c r="G39" s="64" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="62" t="inlineStr">
+      <c r="A40" s="66" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B40" s="62" t="inlineStr">
+      <c r="B40" s="66" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1977,30 +2005,30 @@
           <t xml:space="preserve">Manifestazioni di interessePR FESR SICILIA 2021/27 - NUOVO Avviso a manifestazione d’interesse per esperti valutatoriScade il:06/04/2026 - 23:59Leggi </t>
         </is>
       </c>
-      <c r="D40" s="63" t="inlineStr">
+      <c r="D40" s="67" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/pr-fesr-sicilia-202127-nuovo-avviso-manifestazione-d-interesse-esperti-valutatori</t>
         </is>
       </c>
-      <c r="E40" s="62" t="inlineStr">
+      <c r="E40" s="66" t="inlineStr">
         <is>
           <t>06/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F40" s="62" t="inlineStr">
+      <c r="F40" s="66" t="inlineStr">
         <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="G40" s="62" t="inlineStr"/>
+      <c r="G40" s="66" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="60" t="inlineStr">
+      <c r="A41" s="64" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B41" s="60" t="inlineStr">
+      <c r="B41" s="64" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2010,22 +2038,22 @@
           <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D41" s="61" t="inlineStr">
+      <c r="D41" s="65" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
         </is>
       </c>
-      <c r="E41" s="60" t="inlineStr"/>
-      <c r="F41" s="60" t="inlineStr"/>
-      <c r="G41" s="60" t="inlineStr"/>
+      <c r="E41" s="64" t="inlineStr"/>
+      <c r="F41" s="64" t="inlineStr"/>
+      <c r="G41" s="64" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="62" t="inlineStr">
+      <c r="A42" s="66" t="inlineStr">
         <is>
           <t>24/03/2026</t>
         </is>
       </c>
-      <c r="B42" s="62" t="inlineStr">
+      <c r="B42" s="66" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2035,22 +2063,22 @@
           <t>GAL del Ducato - Promozione di fiere agroalimentari e delle filiere del cibo – Bando per Enti pubblici (DU AS 05B)</t>
         </is>
       </c>
-      <c r="D42" s="63" t="inlineStr">
+      <c r="D42" s="67" t="inlineStr">
         <is>
           <t>https://agricoltura.regione.emilia-romagna.it/sviluppo-rurale-23-27/opportunita/bandi-gal/2026/du_as05b-promozione-di-fiere-agroalimentari-e-delle-filiere-del-cibo-bando-per-enti-pubblici</t>
         </is>
       </c>
-      <c r="E42" s="62" t="inlineStr"/>
-      <c r="F42" s="62" t="inlineStr"/>
-      <c r="G42" s="62" t="inlineStr"/>
+      <c r="E42" s="66" t="inlineStr"/>
+      <c r="F42" s="66" t="inlineStr"/>
+      <c r="G42" s="66" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="60" t="inlineStr">
+      <c r="A43" s="64" t="inlineStr">
         <is>
           <t>24/03/2026</t>
         </is>
       </c>
-      <c r="B43" s="60" t="inlineStr">
+      <c r="B43" s="64" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2060,30 +2088,30 @@
           <t>Manifestazioni di interesseAVVISO PUBBLICO PER MANIFESTAZIONE DI INTERESSE FINALIZZATA ALL'ASSEGNAZIONE DI SPAZI ESPOSITIVI (CORNER GRATUITI) ALL'INTE</t>
         </is>
       </c>
-      <c r="D43" s="61" t="inlineStr">
+      <c r="D43" s="65" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-manifestazione-interesse-finalizzata-all-assegnazione-spazi-espositivi-corner-gratuiti-all-interno-stand-istituzionale-dsrt-manifestazione</t>
         </is>
       </c>
-      <c r="E43" s="60" t="inlineStr">
+      <c r="E43" s="64" t="inlineStr">
         <is>
           <t>30/03/2026 - 13:00</t>
         </is>
       </c>
-      <c r="F43" s="60" t="inlineStr">
+      <c r="F43" s="64" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G43" s="60" t="inlineStr"/>
+      <c r="G43" s="64" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="62" t="inlineStr">
+      <c r="A44" s="66" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B44" s="62" t="inlineStr">
+      <c r="B44" s="66" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2093,22 +2121,22 @@
           <t>Avviso per la concessione di contributi per eventi sportivi realizzati in Emilia-Romagna - Anno 2026</t>
         </is>
       </c>
-      <c r="D44" s="63" t="inlineStr">
+      <c r="D44" s="67" t="inlineStr">
         <is>
           <t>https://www.regione.emilia-romagna.it/sport/bandi/2026/bando-2026</t>
         </is>
       </c>
-      <c r="E44" s="62" t="inlineStr"/>
-      <c r="F44" s="62" t="inlineStr"/>
-      <c r="G44" s="62" t="inlineStr"/>
+      <c r="E44" s="66" t="inlineStr"/>
+      <c r="F44" s="66" t="inlineStr"/>
+      <c r="G44" s="66" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="60" t="inlineStr">
+      <c r="A45" s="64" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B45" s="60" t="inlineStr">
+      <c r="B45" s="64" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2118,22 +2146,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Street art 2026Prossima AperturaBandi Regionali</t>
         </is>
       </c>
-      <c r="D45" s="61" t="inlineStr">
+      <c r="D45" s="65" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lazio-street-art-2026/</t>
         </is>
       </c>
-      <c r="E45" s="60" t="inlineStr"/>
-      <c r="F45" s="60" t="inlineStr"/>
-      <c r="G45" s="60" t="inlineStr"/>
+      <c r="E45" s="64" t="inlineStr"/>
+      <c r="F45" s="64" t="inlineStr"/>
+      <c r="G45" s="64" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="62" t="inlineStr">
+      <c r="A46" s="66" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B46" s="62" t="inlineStr">
+      <c r="B46" s="66" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2143,30 +2171,30 @@
           <t>Manifestazioni di interesseManifestazione di interesse per la partecipazione all’evento “R2I Italy 2026” – Bologna, 12-13/05/2026Scade il:03/04/2026 -</t>
         </is>
       </c>
-      <c r="D46" s="63" t="inlineStr">
+      <c r="D46" s="67" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/manifestazione-interesse-partecipazione-all-evento-r2i-italy-2026-bologna-12-13052026</t>
         </is>
       </c>
-      <c r="E46" s="62" t="inlineStr">
+      <c r="E46" s="66" t="inlineStr">
         <is>
           <t>03/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F46" s="62" t="inlineStr">
+      <c r="F46" s="66" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="G46" s="62" t="inlineStr"/>
+      <c r="G46" s="66" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="60" t="inlineStr">
+      <c r="A47" s="64" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B47" s="60" t="inlineStr">
+      <c r="B47" s="64" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2176,30 +2204,30 @@
           <t>Manifestazioni di interesseST SIRACUSA - AVVISO PER MANIFESTAZIONE DI INTERESSE - Selezione di n. 5 unità di personale internoScade il:20/04/2026 - 12</t>
         </is>
       </c>
-      <c r="D47" s="61" t="inlineStr">
+      <c r="D47" s="65" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/24-marzo-2026-st-siracusa-avviso-manifestazione-interesse-selezione-n-5-unita-personale-interno</t>
         </is>
       </c>
-      <c r="E47" s="60" t="inlineStr">
+      <c r="E47" s="64" t="inlineStr">
         <is>
           <t>20/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F47" s="60" t="inlineStr">
+      <c r="F47" s="64" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="G47" s="60" t="inlineStr"/>
+      <c r="G47" s="64" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="62" t="inlineStr">
+      <c r="A48" s="66" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B48" s="62" t="inlineStr">
+      <c r="B48" s="66" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2209,30 +2237,30 @@
           <t>Avvisi pubbliciRevoca dell’avviso di concessione a titolo gratuito del 16.12.2025 inerente all’immobile di seguito identificato e contestuale nuovo av</t>
         </is>
       </c>
-      <c r="D48" s="63" t="inlineStr">
+      <c r="D48" s="67" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/revoca-avviso-concessione-titolo-gratuito-16122025-inerente-all-immobile-seguito-identificato-contestuale-nuovo-avviso-concessione-titolo-oneroso-stesso-sito-nel</t>
         </is>
       </c>
-      <c r="E48" s="62" t="inlineStr">
+      <c r="E48" s="66" t="inlineStr">
         <is>
           <t>08/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F48" s="62" t="inlineStr">
+      <c r="F48" s="66" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="G48" s="62" t="inlineStr"/>
+      <c r="G48" s="66" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="60" t="inlineStr">
+      <c r="A49" s="64" t="inlineStr">
         <is>
           <t>26/03/2026</t>
         </is>
       </c>
-      <c r="B49" s="60" t="inlineStr">
+      <c r="B49" s="64" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2242,22 +2270,22 @@
           <t>Bando studi di fattibilità per fusioni di Comuni</t>
         </is>
       </c>
-      <c r="D49" s="61" t="inlineStr">
+      <c r="D49" s="65" t="inlineStr">
         <is>
           <t>https://www.regione.emilia-romagna.it/autonomie-locali/bandi/bando_studi_fattibilita_fusioni_comuni</t>
         </is>
       </c>
-      <c r="E49" s="60" t="inlineStr"/>
-      <c r="F49" s="60" t="inlineStr"/>
-      <c r="G49" s="60" t="inlineStr"/>
+      <c r="E49" s="64" t="inlineStr"/>
+      <c r="F49" s="64" t="inlineStr"/>
+      <c r="G49" s="64" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="62" t="inlineStr">
+      <c r="A50" s="66" t="inlineStr">
         <is>
           <t>26/03/2026</t>
         </is>
       </c>
-      <c r="B50" s="62" t="inlineStr">
+      <c r="B50" s="66" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2267,30 +2295,30 @@
           <t xml:space="preserve">Manifestazioni di interesseAvviso pubblico di selezione interna, per titoli, per il conferimento di PO e professionali, ai sensi degli artt. 19, 20 e </t>
         </is>
       </c>
-      <c r="D50" s="63" t="inlineStr">
+      <c r="D50" s="67" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-selezione-interna-titoli-conferimento-po-professionali-ai-sensi-artt-19-20-21-ccrl-20222024-comparto-non-dirigenziale</t>
         </is>
       </c>
-      <c r="E50" s="62" t="inlineStr">
+      <c r="E50" s="66" t="inlineStr">
         <is>
           <t>30/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F50" s="62" t="inlineStr">
+      <c r="F50" s="66" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G50" s="62" t="inlineStr"/>
+      <c r="G50" s="66" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="60" t="inlineStr">
+      <c r="A51" s="64" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="B51" s="60" t="inlineStr">
+      <c r="B51" s="64" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2300,22 +2328,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0PRE-SEED 3.0ApertoFESR</t>
         </is>
       </c>
-      <c r="D51" s="61" t="inlineStr">
+      <c r="D51" s="65" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/pre-seed-3-0/</t>
         </is>
       </c>
-      <c r="E51" s="60" t="inlineStr"/>
-      <c r="F51" s="60" t="inlineStr"/>
-      <c r="G51" s="60" t="inlineStr"/>
+      <c r="E51" s="64" t="inlineStr"/>
+      <c r="F51" s="64" t="inlineStr"/>
+      <c r="G51" s="64" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="62" t="inlineStr">
+      <c r="A52" s="66" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B52" s="62" t="inlineStr">
+      <c r="B52" s="66" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2325,30 +2353,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “So</t>
         </is>
       </c>
-      <c r="D52" s="63" t="inlineStr">
+      <c r="D52" s="67" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-termini-imerese-locta-piazza-marina</t>
         </is>
       </c>
-      <c r="E52" s="62" t="inlineStr">
+      <c r="E52" s="66" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F52" s="62" t="inlineStr">
+      <c r="F52" s="66" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G52" s="62" t="inlineStr"/>
+      <c r="G52" s="66" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="60" t="inlineStr">
+      <c r="A53" s="64" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B53" s="60" t="inlineStr">
+      <c r="B53" s="64" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2358,30 +2386,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, Sig</t>
         </is>
       </c>
-      <c r="D53" s="61" t="inlineStr">
+      <c r="D53" s="65" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-porto-empedocle-locta-punta-piccola</t>
         </is>
       </c>
-      <c r="E53" s="60" t="inlineStr">
+      <c r="E53" s="64" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F53" s="60" t="inlineStr">
+      <c r="F53" s="64" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G53" s="60" t="inlineStr"/>
+      <c r="G53" s="64" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="62" t="inlineStr">
+      <c r="A54" s="66" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B54" s="62" t="inlineStr">
+      <c r="B54" s="66" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2391,30 +2419,30 @@
           <t xml:space="preserve">Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “Società </t>
         </is>
       </c>
-      <c r="D54" s="63" t="inlineStr">
+      <c r="D54" s="67" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-messina-locta-torrente-bordonaro</t>
         </is>
       </c>
-      <c r="E54" s="62" t="inlineStr">
+      <c r="E54" s="66" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F54" s="62" t="inlineStr">
+      <c r="F54" s="66" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G54" s="62" t="inlineStr"/>
+      <c r="G54" s="66" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="60" t="inlineStr">
+      <c r="A55" s="64" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B55" s="60" t="inlineStr">
+      <c r="B55" s="64" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2424,30 +2452,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “Condomin</t>
         </is>
       </c>
-      <c r="D55" s="61" t="inlineStr">
+      <c r="D55" s="65" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-mascali-spiaggia-n-144150</t>
         </is>
       </c>
-      <c r="E55" s="60" t="inlineStr">
+      <c r="E55" s="64" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F55" s="60" t="inlineStr">
+      <c r="F55" s="64" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G55" s="60" t="inlineStr"/>
+      <c r="G55" s="64" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="62" t="inlineStr">
+      <c r="A56" s="66" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B56" s="62" t="inlineStr">
+      <c r="B56" s="66" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2457,30 +2485,30 @@
           <t xml:space="preserve">Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione sito nel Comune di Lipari, isola di Stromboli, </t>
         </is>
       </c>
-      <c r="D56" s="63" t="inlineStr">
+      <c r="D56" s="67" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-lipari-isola-stromboli-locta-fico-grande</t>
         </is>
       </c>
-      <c r="E56" s="62" t="inlineStr">
+      <c r="E56" s="66" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F56" s="62" t="inlineStr">
+      <c r="F56" s="66" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G56" s="62" t="inlineStr"/>
+      <c r="G56" s="66" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="60" t="inlineStr">
+      <c r="A57" s="64" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B57" s="60" t="inlineStr">
+      <c r="B57" s="64" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2490,30 +2518,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione sito nel Comune di Favignana, isola di Le</t>
         </is>
       </c>
-      <c r="D57" s="61" t="inlineStr">
+      <c r="D57" s="65" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-favignana-isola-levanzo</t>
         </is>
       </c>
-      <c r="E57" s="60" t="inlineStr">
+      <c r="E57" s="64" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F57" s="60" t="inlineStr">
+      <c r="F57" s="64" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G57" s="60" t="inlineStr"/>
+      <c r="G57" s="64" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="62" t="inlineStr">
+      <c r="A58" s="66" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="B58" s="62" t="inlineStr">
+      <c r="B58" s="66" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2523,30 +2551,30 @@
           <t>Manifestazioni di interesseAVVISO - Manifestazione d’interesse finalizzata alla selezione di organismi attuatori di piani di gestione locale della pic</t>
         </is>
       </c>
-      <c r="D58" s="63" t="inlineStr">
+      <c r="D58" s="67" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-d-interesse-finalizzata-alla-selezione-organismi-attuatori-piani-gestione-locale-piccola-pesca-costiera-nelle-gsa-regione-siciliana</t>
         </is>
       </c>
-      <c r="E58" s="62" t="inlineStr">
+      <c r="E58" s="66" t="inlineStr">
         <is>
           <t>29/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F58" s="62" t="inlineStr">
+      <c r="F58" s="66" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="G58" s="62" t="inlineStr"/>
+      <c r="G58" s="66" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="60" t="inlineStr">
+      <c r="A59" s="64" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="B59" s="60" t="inlineStr">
+      <c r="B59" s="64" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2556,30 +2584,30 @@
           <t>Avvisi pubbliciLeggi e scarica l'avvisoScade il:02/04/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D59" s="61" t="inlineStr">
+      <c r="D59" s="65" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/proroga-termini-presentazione-candidature-po</t>
         </is>
       </c>
-      <c r="E59" s="60" t="inlineStr">
+      <c r="E59" s="64" t="inlineStr">
         <is>
           <t>02/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F59" s="60" t="inlineStr">
+      <c r="F59" s="64" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="G59" s="60" t="inlineStr"/>
+      <c r="G59" s="64" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="62" t="inlineStr">
+      <c r="A60" s="66" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="62" t="inlineStr">
+      <c r="B60" s="66" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2589,22 +2617,22 @@
           <t>INTERNAZIONALIZZAZIONESMAU – Italy RestartsUp in STOCCOLMAApertoFESR</t>
         </is>
       </c>
-      <c r="D60" s="63" t="inlineStr">
+      <c r="D60" s="67" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/smau-italy-restartsup-in-stoccolma/</t>
         </is>
       </c>
-      <c r="E60" s="62" t="inlineStr"/>
-      <c r="F60" s="62" t="inlineStr"/>
-      <c r="G60" s="62" t="inlineStr"/>
+      <c r="E60" s="66" t="inlineStr"/>
+      <c r="F60" s="66" t="inlineStr"/>
+      <c r="G60" s="66" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="60" t="inlineStr">
+      <c r="A61" s="64" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B61" s="60" t="inlineStr">
+      <c r="B61" s="64" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2614,22 +2642,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per Farnborough International AirshowApertoFESR</t>
         </is>
       </c>
-      <c r="D61" s="61" t="inlineStr">
+      <c r="D61" s="65" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-farnborough-international-airshow-2/</t>
         </is>
       </c>
-      <c r="E61" s="60" t="inlineStr"/>
-      <c r="F61" s="60" t="inlineStr"/>
-      <c r="G61" s="60" t="inlineStr"/>
+      <c r="E61" s="64" t="inlineStr"/>
+      <c r="F61" s="64" t="inlineStr"/>
+      <c r="G61" s="64" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="62" t="inlineStr">
+      <c r="A62" s="66" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="62" t="inlineStr">
+      <c r="B62" s="66" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2639,22 +2667,22 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA - alienazione lotto di terreno sito nel comune di Termini Imerese, via LibertàScade il:30/04/2026 - 12:00Leg</t>
         </is>
       </c>
-      <c r="D62" s="63" t="inlineStr">
+      <c r="D62" s="67" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proprieta-regionale-sito-nel-comune-termini-imerese-favore-ares-fabiola</t>
         </is>
       </c>
-      <c r="E62" s="62" t="inlineStr">
+      <c r="E62" s="66" t="inlineStr">
         <is>
           <t>30/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F62" s="62" t="inlineStr">
+      <c r="F62" s="66" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="G62" s="62" t="inlineStr"/>
+      <c r="G62" s="66" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="64" t="inlineStr">
@@ -2779,6 +2807,147 @@
         </is>
       </c>
       <c r="G66" s="66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="68" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="68" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Manifestazione di interesse per Casaidea 2026ApertoFESR</t>
+        </is>
+      </c>
+      <c r="D67" s="69" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-casaidea-2026/</t>
+        </is>
+      </c>
+      <c r="E67" s="68" t="inlineStr"/>
+      <c r="F67" s="68" t="inlineStr"/>
+      <c r="G67" s="68" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="70" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="70" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per il Salone Internazionale del Libro di Torino 2026ApertoFESR</t>
+        </is>
+      </c>
+      <c r="D68" s="71" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-il-salone-internazionale-del-libro-di-torino-2026/</t>
+        </is>
+      </c>
+      <c r="E68" s="70" t="inlineStr"/>
+      <c r="F68" s="70" t="inlineStr"/>
+      <c r="G68" s="70" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="68" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="68" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>Avvisi pubbliciDDG 1112 del 02.04.2026 - Aggiornamento Avviso pubblico n. 4/2024 per l’attuazione del PAR GOL Sicilia da finanziare nell’ambito del Pi</t>
+        </is>
+      </c>
+      <c r="D69" s="69" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/ddg-1112-02042026-aggiornamento-avviso-pubblico-n-42024-l-attuazione-par-gol-sicilia-finanziare-nell-ambito-piano-nazionale-ripresa-resilienza-pnrr</t>
+        </is>
+      </c>
+      <c r="E69" s="68" t="inlineStr">
+        <is>
+          <t>05/04/2030 - 00:00</t>
+        </is>
+      </c>
+      <c r="F69" s="68" t="inlineStr">
+        <is>
+          <t>05/04/2030</t>
+        </is>
+      </c>
+      <c r="G69" s="68" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="70" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="70" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>Avvisi pubbliciDDG 1113 del  02.04.2026 - Aggiornamento Avviso pubblico n. 2/2022 e s.m.i per l’attuazione del PAR GOL Sicilia da finanziare nell’ambi</t>
+        </is>
+      </c>
+      <c r="D70" s="71" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/ddg-1113-02042026-aggiornamento-avviso-pubblico-n-22022-smi-l-attuazione-par-gol-sicilia-finanziare-nell-ambito-piano-nazionale-ripresa-resilienza-pnrr</t>
+        </is>
+      </c>
+      <c r="E70" s="70" t="inlineStr">
+        <is>
+          <t>03/04/2030 - 00:00</t>
+        </is>
+      </c>
+      <c r="F70" s="70" t="inlineStr">
+        <is>
+          <t>03/04/2030</t>
+        </is>
+      </c>
+      <c r="G70" s="70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="68" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="68" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>Avvisi pubbliciLeggi e scarica l'avvisoScadutoLeggi di più</t>
+        </is>
+      </c>
+      <c r="D71" s="69" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/proroga-termini-presentazione-candidature-po</t>
+        </is>
+      </c>
+      <c r="E71" s="68" t="inlineStr"/>
+      <c r="F71" s="68" t="inlineStr"/>
+      <c r="G71" s="68" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2847,6 +3016,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId70"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2891,7 +3065,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="64" t="inlineStr">
+      <c r="A3" s="68" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2900,30 +3074,30 @@
         <v>6</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="66" t="inlineStr">
+      <c r="A4" s="70" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="64" t="inlineStr">
+      <c r="A5" s="68" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>3</v>

--- a/data/bandi_export.xlsx
+++ b/data/bandi_export.xlsx
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -267,6 +267,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -694,7 +706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -709,7 +721,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏛️  Nuovi Bandi — 03/04/2026 07:58</t>
+          <t>🏛️  Nuovi Bandi — 04/04/2026 07:44</t>
         </is>
       </c>
     </row>
@@ -754,132 +766,55 @@
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="68" t="inlineStr">
+      <c r="B3" s="72" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Manifestazione di interesse per Casaidea 2026ApertoFESR</t>
-        </is>
-      </c>
-      <c r="D3" s="69" t="inlineStr">
-        <is>
-          <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-casaidea-2026/</t>
-        </is>
-      </c>
-      <c r="E3" s="68" t="inlineStr"/>
-      <c r="F3" s="68" t="inlineStr"/>
+          <t>LAVORO, FORMAZIONE E INCLUSIONEComunicare l’inclusione – contest per le istituzioni scolastiche regionaliApertoBandi Regionali</t>
+        </is>
+      </c>
+      <c r="D3" s="73" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/comunicare-linclusione-contest-per-le-istituzioni-scolastiche-regionali/</t>
+        </is>
+      </c>
+      <c r="E3" s="72" t="inlineStr"/>
+      <c r="F3" s="72" t="inlineStr"/>
       <c r="G3" s="5" t="inlineStr"/>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="70" t="inlineStr">
-        <is>
-          <t>Lazio</t>
+      <c r="B4" s="74" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per il Salone Internazionale del Libro di Torino 2026ApertoFESR</t>
-        </is>
-      </c>
-      <c r="D4" s="71" t="inlineStr">
-        <is>
-          <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-il-salone-internazionale-del-libro-di-torino-2026/</t>
-        </is>
-      </c>
-      <c r="E4" s="70" t="inlineStr"/>
-      <c r="F4" s="70" t="inlineStr"/>
+          <t>Avvisi pubbliciAPPROVAZIONE AVVISO PUBBLICOScade il:03/04/2027 - 00:00Leggi di più</t>
+        </is>
+      </c>
+      <c r="D4" s="75" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/approvazione-avviso-pubblico</t>
+        </is>
+      </c>
+      <c r="E4" s="74" t="inlineStr">
+        <is>
+          <t>03/04/2027 - 00:00</t>
+        </is>
+      </c>
+      <c r="F4" s="74" t="inlineStr">
+        <is>
+          <t>03/04/2027</t>
+        </is>
+      </c>
       <c r="G4" s="9" t="inlineStr"/>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" s="68" t="inlineStr">
-        <is>
-          <t>Sicilia</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Avvisi pubbliciDDG 1112 del 02.04.2026 - Aggiornamento Avviso pubblico n. 4/2024 per l’attuazione del PAR GOL Sicilia da finanziare nell’ambito del Pi</t>
-        </is>
-      </c>
-      <c r="D5" s="69" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/ddg-1112-02042026-aggiornamento-avviso-pubblico-n-42024-l-attuazione-par-gol-sicilia-finanziare-nell-ambito-piano-nazionale-ripresa-resilienza-pnrr</t>
-        </is>
-      </c>
-      <c r="E5" s="68" t="inlineStr">
-        <is>
-          <t>05/04/2030 - 00:00</t>
-        </is>
-      </c>
-      <c r="F5" s="68" t="inlineStr">
-        <is>
-          <t>05/04/2030</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="70" t="inlineStr">
-        <is>
-          <t>Sicilia</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>Avvisi pubbliciDDG 1113 del  02.04.2026 - Aggiornamento Avviso pubblico n. 2/2022 e s.m.i per l’attuazione del PAR GOL Sicilia da finanziare nell’ambi</t>
-        </is>
-      </c>
-      <c r="D6" s="71" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/ddg-1113-02042026-aggiornamento-avviso-pubblico-n-22022-smi-l-attuazione-par-gol-sicilia-finanziare-nell-ambito-piano-nazionale-ripresa-resilienza-pnrr</t>
-        </is>
-      </c>
-      <c r="E6" s="70" t="inlineStr">
-        <is>
-          <t>03/04/2030 - 00:00</t>
-        </is>
-      </c>
-      <c r="F6" s="70" t="inlineStr">
-        <is>
-          <t>03/04/2030</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr"/>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" s="68" t="inlineStr">
-        <is>
-          <t>Sicilia</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Avvisi pubbliciLeggi e scarica l'avvisoScadutoLeggi di più</t>
-        </is>
-      </c>
-      <c r="D7" s="69" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/proroga-termini-presentazione-candidature-po</t>
-        </is>
-      </c>
-      <c r="E7" s="68" t="inlineStr"/>
-      <c r="F7" s="68" t="inlineStr"/>
-      <c r="G7" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -888,9 +823,6 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -902,7 +834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -952,12 +884,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="66" t="inlineStr">
+      <c r="A2" s="70" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B2" s="66" t="inlineStr">
+      <c r="B2" s="70" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -967,22 +899,22 @@
           <t>FLAG GALPA Costa E-R. Sostituzione del motore principale e dei motori secondari. Secondo bando</t>
         </is>
       </c>
-      <c r="D2" s="67" t="inlineStr">
+      <c r="D2" s="71" t="inlineStr">
         <is>
           <t>https://agricoltura.regione.emilia-romagna.it/feampa-2021-2027/bandi-galpa/2026/galpa-sostituzione-motori-secondo-bando</t>
         </is>
       </c>
-      <c r="E2" s="66" t="inlineStr"/>
-      <c r="F2" s="66" t="inlineStr"/>
-      <c r="G2" s="66" t="inlineStr"/>
+      <c r="E2" s="70" t="inlineStr"/>
+      <c r="F2" s="70" t="inlineStr"/>
+      <c r="G2" s="70" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="64" t="inlineStr">
+      <c r="A3" s="68" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B3" s="64" t="inlineStr">
+      <c r="B3" s="68" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -992,22 +924,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0PRE-SEED 3.0Prossima AperturaFESR</t>
         </is>
       </c>
-      <c r="D3" s="65" t="inlineStr">
+      <c r="D3" s="69" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/pre-seed-3-0/</t>
         </is>
       </c>
-      <c r="E3" s="64" t="inlineStr"/>
-      <c r="F3" s="64" t="inlineStr"/>
-      <c r="G3" s="64" t="inlineStr"/>
+      <c r="E3" s="68" t="inlineStr"/>
+      <c r="F3" s="68" t="inlineStr"/>
+      <c r="G3" s="68" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="66" t="inlineStr">
+      <c r="A4" s="70" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B4" s="66" t="inlineStr">
+      <c r="B4" s="70" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1017,22 +949,22 @@
           <t>ACCESSO AL CREDITO E ALLE GARANZIE PER LE IMPRESEContributo su finanziamenti alle imprese del Lazio erogati su provvista BEIProssima AperturaFESR</t>
         </is>
       </c>
-      <c r="D4" s="67" t="inlineStr">
+      <c r="D4" s="71" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-su-finanziamenti-alle-imprese-del-lazio-erogati-su-provvista-bei/</t>
         </is>
       </c>
-      <c r="E4" s="66" t="inlineStr"/>
-      <c r="F4" s="66" t="inlineStr"/>
-      <c r="G4" s="66" t="inlineStr"/>
+      <c r="E4" s="70" t="inlineStr"/>
+      <c r="F4" s="70" t="inlineStr"/>
+      <c r="G4" s="70" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="64" t="inlineStr">
+      <c r="A5" s="68" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B5" s="64" t="inlineStr">
+      <c r="B5" s="68" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1042,22 +974,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEIndividuazione degli enti iscritti al Registro unico nazionale del Terzo settoreApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D5" s="65" t="inlineStr">
+      <c r="D5" s="69" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/individuazione-degli-enti-iscritti-al-registro-unico-nazionale-del-terzo-settore/</t>
         </is>
       </c>
-      <c r="E5" s="64" t="inlineStr"/>
-      <c r="F5" s="64" t="inlineStr"/>
-      <c r="G5" s="64" t="inlineStr"/>
+      <c r="E5" s="68" t="inlineStr"/>
+      <c r="F5" s="68" t="inlineStr"/>
+      <c r="G5" s="68" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="66" t="inlineStr">
+      <c r="A6" s="70" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B6" s="66" t="inlineStr">
+      <c r="B6" s="70" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1067,22 +999,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Technology Transfer LazioApertoFESR</t>
         </is>
       </c>
-      <c r="D6" s="67" t="inlineStr">
+      <c r="D6" s="71" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/technology-transfer-lazio/</t>
         </is>
       </c>
-      <c r="E6" s="66" t="inlineStr"/>
-      <c r="F6" s="66" t="inlineStr"/>
-      <c r="G6" s="66" t="inlineStr"/>
+      <c r="E6" s="70" t="inlineStr"/>
+      <c r="F6" s="70" t="inlineStr"/>
+      <c r="G6" s="70" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="64" t="inlineStr">
+      <c r="A7" s="68" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B7" s="64" t="inlineStr">
+      <c r="B7" s="68" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1092,22 +1024,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Percorso di tutoraggio per le impreseApertoFESR</t>
         </is>
       </c>
-      <c r="D7" s="65" t="inlineStr">
+      <c r="D7" s="69" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/percorso-di-tutoraggio-per-le-imprese/</t>
         </is>
       </c>
-      <c r="E7" s="64" t="inlineStr"/>
-      <c r="F7" s="64" t="inlineStr"/>
-      <c r="G7" s="64" t="inlineStr"/>
+      <c r="E7" s="68" t="inlineStr"/>
+      <c r="F7" s="68" t="inlineStr"/>
+      <c r="G7" s="68" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="66" t="inlineStr">
+      <c r="A8" s="70" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B8" s="66" t="inlineStr">
+      <c r="B8" s="70" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1117,22 +1049,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per partecipare a SMAU Parigi 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D8" s="67" t="inlineStr">
+      <c r="D8" s="71" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-partecipare-a-smau-parigi-2026/</t>
         </is>
       </c>
-      <c r="E8" s="66" t="inlineStr"/>
-      <c r="F8" s="66" t="inlineStr"/>
-      <c r="G8" s="66" t="inlineStr"/>
+      <c r="E8" s="70" t="inlineStr"/>
+      <c r="F8" s="70" t="inlineStr"/>
+      <c r="G8" s="70" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="64" t="inlineStr">
+      <c r="A9" s="68" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B9" s="64" t="inlineStr">
+      <c r="B9" s="68" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1142,22 +1074,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONERiconoscimento della funzione sociale ed educativa degli oratoriApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D9" s="65" t="inlineStr">
+      <c r="D9" s="69" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/riconoscimento-della-funzione-sociale-ed-educativa-degli-oratori/</t>
         </is>
       </c>
-      <c r="E9" s="64" t="inlineStr"/>
-      <c r="F9" s="64" t="inlineStr"/>
-      <c r="G9" s="64" t="inlineStr"/>
+      <c r="E9" s="68" t="inlineStr"/>
+      <c r="F9" s="68" t="inlineStr"/>
+      <c r="G9" s="68" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="66" t="inlineStr">
+      <c r="A10" s="70" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B10" s="66" t="inlineStr">
+      <c r="B10" s="70" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1167,22 +1099,22 @@
           <t>GovernanceIscrizione nell’elenco regionale degli idonei all’esercizio dell’attività di direttore dell’Istituto JemoloApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D10" s="67" t="inlineStr">
+      <c r="D10" s="71" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/iscrizione-nellelenco-regionale-degli-idonei-allesercizio-dellattivita-di-direttore-dellistituto-jemolo/</t>
         </is>
       </c>
-      <c r="E10" s="66" t="inlineStr"/>
-      <c r="F10" s="66" t="inlineStr"/>
-      <c r="G10" s="66" t="inlineStr"/>
+      <c r="E10" s="70" t="inlineStr"/>
+      <c r="F10" s="70" t="inlineStr"/>
+      <c r="G10" s="70" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="64" t="inlineStr">
+      <c r="A11" s="68" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B11" s="64" t="inlineStr">
+      <c r="B11" s="68" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1192,22 +1124,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEVoucher per lo sport – seconda annualitàApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D11" s="65" t="inlineStr">
+      <c r="D11" s="69" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/voucher-per-lo-sport-seconda-annualita/</t>
         </is>
       </c>
-      <c r="E11" s="64" t="inlineStr"/>
-      <c r="F11" s="64" t="inlineStr"/>
-      <c r="G11" s="64" t="inlineStr"/>
+      <c r="E11" s="68" t="inlineStr"/>
+      <c r="F11" s="68" t="inlineStr"/>
+      <c r="G11" s="68" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="66" t="inlineStr">
+      <c r="A12" s="70" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B12" s="66" t="inlineStr">
+      <c r="B12" s="70" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1217,22 +1149,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEBonus occupazionale SALGOApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D12" s="67" t="inlineStr">
+      <c r="D12" s="71" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/bonus-occupazionale-salgo/</t>
         </is>
       </c>
-      <c r="E12" s="66" t="inlineStr"/>
-      <c r="F12" s="66" t="inlineStr"/>
-      <c r="G12" s="66" t="inlineStr"/>
+      <c r="E12" s="70" t="inlineStr"/>
+      <c r="F12" s="70" t="inlineStr"/>
+      <c r="G12" s="70" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="64" t="inlineStr">
+      <c r="A13" s="68" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B13" s="64" t="inlineStr">
+      <c r="B13" s="68" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1242,22 +1174,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEContributo di Libertà per le donne che hanno subito violenzaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D13" s="65" t="inlineStr">
+      <c r="D13" s="69" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-di-liberta-per-le-donne-che-hanno-subito-violenza/</t>
         </is>
       </c>
-      <c r="E13" s="64" t="inlineStr"/>
-      <c r="F13" s="64" t="inlineStr"/>
-      <c r="G13" s="64" t="inlineStr"/>
+      <c r="E13" s="68" t="inlineStr"/>
+      <c r="F13" s="68" t="inlineStr"/>
+      <c r="G13" s="68" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="66" t="inlineStr">
+      <c r="A14" s="70" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B14" s="66" t="inlineStr">
+      <c r="B14" s="70" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1267,22 +1199,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURAInterventi straordinari di valorizzazione del patrimonio culturale del LazioApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D14" s="67" t="inlineStr">
+      <c r="D14" s="71" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/interventi-straordinari-di-valorizzazione-del-patrimonio-culturale-del-lazio/</t>
         </is>
       </c>
-      <c r="E14" s="66" t="inlineStr"/>
-      <c r="F14" s="66" t="inlineStr"/>
-      <c r="G14" s="66" t="inlineStr"/>
+      <c r="E14" s="70" t="inlineStr"/>
+      <c r="F14" s="70" t="inlineStr"/>
+      <c r="G14" s="70" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="64" t="inlineStr">
+      <c r="A15" s="68" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B15" s="64" t="inlineStr">
+      <c r="B15" s="68" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1292,30 +1224,30 @@
           <t>Bandi di garaBANDO ATTUAZIONE Ob. 1.1 Azione 1 codice 111102 _DIV - "SOSTEGNO ALLA DIVERSIFICAZIONE E NUOVE FORME DI REDDITO PER LA PICCOLA PESCA COST</t>
         </is>
       </c>
-      <c r="D15" s="65" t="inlineStr">
+      <c r="D15" s="69" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/bando-avviso-regia-ob-11-azione-1-codice-111102-div-sostegno-alla-diversificazione-nuove-forme-reddito-piccola-pesca-costiera</t>
         </is>
       </c>
-      <c r="E15" s="64" t="inlineStr">
+      <c r="E15" s="68" t="inlineStr">
         <is>
           <t>07/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F15" s="64" t="inlineStr">
+      <c r="F15" s="68" t="inlineStr">
         <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="G15" s="64" t="inlineStr"/>
+      <c r="G15" s="68" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="66" t="inlineStr">
+      <c r="A16" s="70" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B16" s="66" t="inlineStr">
+      <c r="B16" s="70" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1325,30 +1257,30 @@
           <t>Avvisi pubblici09 marzo 2026 - ST SIRACUSA - AVVISO PUBBLICO PER LA COSTITUZIONE DI ELENCHI DI OPERATORI ECONOMICI PER L’ACQUISIZIONE DI BENI E SERVIZ</t>
         </is>
       </c>
-      <c r="D16" s="67" t="inlineStr">
+      <c r="D16" s="71" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/09-marzo-2026-st-siracusa-avviso-pubblico-costituzione-elenchi-operatori-economici-l-acquisizione-beni-servizi</t>
         </is>
       </c>
-      <c r="E16" s="66" t="inlineStr">
+      <c r="E16" s="70" t="inlineStr">
         <is>
           <t>31/12/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F16" s="66" t="inlineStr">
+      <c r="F16" s="70" t="inlineStr">
         <is>
           <t>31/12/2026</t>
         </is>
       </c>
-      <c r="G16" s="66" t="inlineStr"/>
+      <c r="G16" s="70" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="64" t="inlineStr">
+      <c r="A17" s="68" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B17" s="64" t="inlineStr">
+      <c r="B17" s="68" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1358,30 +1290,30 @@
           <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScade il:19/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D17" s="65" t="inlineStr">
+      <c r="D17" s="69" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
         </is>
       </c>
-      <c r="E17" s="64" t="inlineStr">
+      <c r="E17" s="68" t="inlineStr">
         <is>
           <t>19/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F17" s="64" t="inlineStr">
+      <c r="F17" s="68" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G17" s="64" t="inlineStr"/>
+      <c r="G17" s="68" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="66" t="inlineStr">
+      <c r="A18" s="70" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B18" s="66" t="inlineStr">
+      <c r="B18" s="70" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1391,22 +1323,22 @@
           <t>Manifestazioni di interesseAvviso Manifestazione Interesse DISTRIBUTORI AUTOMATICI di bevande e snackScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D18" s="67" t="inlineStr">
+      <c r="D18" s="71" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-distributori-automatici-bevande-snack</t>
         </is>
       </c>
-      <c r="E18" s="66" t="inlineStr"/>
-      <c r="F18" s="66" t="inlineStr"/>
-      <c r="G18" s="66" t="inlineStr"/>
+      <c r="E18" s="70" t="inlineStr"/>
+      <c r="F18" s="70" t="inlineStr"/>
+      <c r="G18" s="70" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="64" t="inlineStr">
+      <c r="A19" s="68" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B19" s="64" t="inlineStr">
+      <c r="B19" s="68" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1416,30 +1348,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D19" s="65" t="inlineStr">
+      <c r="D19" s="69" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo</t>
         </is>
       </c>
-      <c r="E19" s="64" t="inlineStr">
+      <c r="E19" s="68" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F19" s="64" t="inlineStr">
+      <c r="F19" s="68" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G19" s="64" t="inlineStr"/>
+      <c r="G19" s="68" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="66" t="inlineStr">
+      <c r="A20" s="70" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B20" s="66" t="inlineStr">
+      <c r="B20" s="70" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1449,30 +1381,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D20" s="67" t="inlineStr">
+      <c r="D20" s="71" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo-0</t>
         </is>
       </c>
-      <c r="E20" s="66" t="inlineStr">
+      <c r="E20" s="70" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F20" s="66" t="inlineStr">
+      <c r="F20" s="70" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G20" s="66" t="inlineStr"/>
+      <c r="G20" s="70" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="64" t="inlineStr">
+      <c r="A21" s="68" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B21" s="64" t="inlineStr">
+      <c r="B21" s="68" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1482,22 +1414,22 @@
           <t>Manifestazioni di interesseST SIRACUSA - AVVISO DI MANIFESTAZIONE DI INTERESSE - Fornitura applicativo extracontabile per la gestione progetti, ecc. e</t>
         </is>
       </c>
-      <c r="D21" s="65" t="inlineStr">
+      <c r="D21" s="69" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-siracusa-avviso-manifestazione-interesse-fornitura-applicativo-extracontabile-gestione-progetti-ecc-applicativo-gestione-ed-elaborazione-informatizzata-paghe</t>
         </is>
       </c>
-      <c r="E21" s="64" t="inlineStr"/>
-      <c r="F21" s="64" t="inlineStr"/>
-      <c r="G21" s="64" t="inlineStr"/>
+      <c r="E21" s="68" t="inlineStr"/>
+      <c r="F21" s="68" t="inlineStr"/>
+      <c r="G21" s="68" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="66" t="inlineStr">
+      <c r="A22" s="70" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B22" s="66" t="inlineStr">
+      <c r="B22" s="70" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1507,30 +1439,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile sito nel Comune di Capo D'Orlando, Via Trazzera MarinaScade il:25/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D22" s="67" t="inlineStr">
+      <c r="D22" s="71" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-sito-nel-comune-capo-d-orlando-trazzera-marina</t>
         </is>
       </c>
-      <c r="E22" s="66" t="inlineStr">
+      <c r="E22" s="70" t="inlineStr">
         <is>
           <t>25/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F22" s="66" t="inlineStr">
+      <c r="F22" s="70" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="G22" s="66" t="inlineStr"/>
+      <c r="G22" s="70" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="64" t="inlineStr">
+      <c r="A23" s="68" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B23" s="64" t="inlineStr">
+      <c r="B23" s="68" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1540,22 +1472,22 @@
           <t xml:space="preserve">Avvisi pubbliciST CATANIA - Programma Regionale FESR Sicilia 2021-2027 - Azione 2.4.4 - “Interventi per la riduzione del rischio incendi” - AVVISO DI </t>
         </is>
       </c>
-      <c r="D23" s="65" t="inlineStr">
+      <c r="D23" s="69" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-catania-programma-regionale-fesr-sicilia-2021-2027-azione-244-interventi-riduzione-rischio-incendi-avviso-indagine-mercato</t>
         </is>
       </c>
-      <c r="E23" s="64" t="inlineStr"/>
-      <c r="F23" s="64" t="inlineStr"/>
-      <c r="G23" s="64" t="inlineStr"/>
+      <c r="E23" s="68" t="inlineStr"/>
+      <c r="F23" s="68" t="inlineStr"/>
+      <c r="G23" s="68" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="66" t="inlineStr">
+      <c r="A24" s="70" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B24" s="66" t="inlineStr">
+      <c r="B24" s="70" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1565,22 +1497,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per ROMICS – Primavera 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D24" s="67" t="inlineStr">
+      <c r="D24" s="71" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-romics-primavera-2026/</t>
         </is>
       </c>
-      <c r="E24" s="66" t="inlineStr"/>
-      <c r="F24" s="66" t="inlineStr"/>
-      <c r="G24" s="66" t="inlineStr"/>
+      <c r="E24" s="70" t="inlineStr"/>
+      <c r="F24" s="70" t="inlineStr"/>
+      <c r="G24" s="70" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="64" t="inlineStr">
+      <c r="A25" s="68" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B25" s="64" t="inlineStr">
+      <c r="B25" s="68" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1590,22 +1522,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Cinema International 2026 – I edizioneApertoFESR</t>
         </is>
       </c>
-      <c r="D25" s="65" t="inlineStr">
+      <c r="D25" s="69" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lazio-cinema-international-2026-i-edizione/</t>
         </is>
       </c>
-      <c r="E25" s="64" t="inlineStr"/>
-      <c r="F25" s="64" t="inlineStr"/>
-      <c r="G25" s="64" t="inlineStr"/>
+      <c r="E25" s="68" t="inlineStr"/>
+      <c r="F25" s="68" t="inlineStr"/>
+      <c r="G25" s="68" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="66" t="inlineStr">
+      <c r="A26" s="70" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B26" s="66" t="inlineStr">
+      <c r="B26" s="70" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1615,22 +1547,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEManifestazioni di interesse alla costituzione di due nuove Fondazioni I.T.S. AcademyApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D26" s="67" t="inlineStr">
+      <c r="D26" s="71" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazioni-di-interesse-alla-costituzione-di-due-nuove-fondazioni-i-t-s-academy/</t>
         </is>
       </c>
-      <c r="E26" s="66" t="inlineStr"/>
-      <c r="F26" s="66" t="inlineStr"/>
-      <c r="G26" s="66" t="inlineStr"/>
+      <c r="E26" s="70" t="inlineStr"/>
+      <c r="F26" s="70" t="inlineStr"/>
+      <c r="G26" s="70" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="64" t="inlineStr">
+      <c r="A27" s="68" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B27" s="64" t="inlineStr">
+      <c r="B27" s="68" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1640,22 +1572,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURAContributi per sostenere la ripresa del settore della pescaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D27" s="65" t="inlineStr">
+      <c r="D27" s="69" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributi-per-sostenere-la-ripresa-del-settore-della-pesca/</t>
         </is>
       </c>
-      <c r="E27" s="64" t="inlineStr"/>
-      <c r="F27" s="64" t="inlineStr"/>
-      <c r="G27" s="64" t="inlineStr"/>
+      <c r="E27" s="68" t="inlineStr"/>
+      <c r="F27" s="68" t="inlineStr"/>
+      <c r="G27" s="68" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="66" t="inlineStr">
+      <c r="A28" s="70" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B28" s="66" t="inlineStr">
+      <c r="B28" s="70" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1665,30 +1597,30 @@
           <t>Manifestazioni di interesseAVVISO - Manifestazione Interesse “Storytelling aziendale” Expo Wild Natura - Caccia - Pesca. Misterbianco (CT), 10-12 apri</t>
         </is>
       </c>
-      <c r="D28" s="67" t="inlineStr">
+      <c r="D28" s="71" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-storytelling-aziendale-expo-wild-natura-caccia-pesca-misterbianco-ct-10-12-aprile-2026</t>
         </is>
       </c>
-      <c r="E28" s="66" t="inlineStr">
+      <c r="E28" s="70" t="inlineStr">
         <is>
           <t>30/03/2026 - 13:00</t>
         </is>
       </c>
-      <c r="F28" s="66" t="inlineStr">
+      <c r="F28" s="70" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G28" s="66" t="inlineStr"/>
+      <c r="G28" s="70" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="64" t="inlineStr">
+      <c r="A29" s="68" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B29" s="64" t="inlineStr">
+      <c r="B29" s="68" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1698,30 +1630,30 @@
           <t>Manifestazioni di interesseInvaso Lentini - Interventi di ripristino delle pareti esterne in cls della Torre di presa Sud e della trave d’appoggio del</t>
         </is>
       </c>
-      <c r="D29" s="65" t="inlineStr">
+      <c r="D29" s="69" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/invaso-lentini-interventi-ripristino-pareti-esterne-cls-torre-presa-sud-trave-d-appoggio-cavalcavia-collegamento-alla-stessa-torre</t>
         </is>
       </c>
-      <c r="E29" s="64" t="inlineStr">
+      <c r="E29" s="68" t="inlineStr">
         <is>
           <t>19/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F29" s="64" t="inlineStr">
+      <c r="F29" s="68" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G29" s="64" t="inlineStr"/>
+      <c r="G29" s="68" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="66" t="inlineStr">
+      <c r="A30" s="70" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="B30" s="66" t="inlineStr">
+      <c r="B30" s="70" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1731,22 +1663,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURARistrutturazione e riconversione vigneti – campagna 2026-2027ApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D30" s="67" t="inlineStr">
+      <c r="D30" s="71" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/ristrutturazione-e-riconversione-vigneti-campagna-2026-2027/</t>
         </is>
       </c>
-      <c r="E30" s="66" t="inlineStr"/>
-      <c r="F30" s="66" t="inlineStr"/>
-      <c r="G30" s="66" t="inlineStr"/>
+      <c r="E30" s="70" t="inlineStr"/>
+      <c r="F30" s="70" t="inlineStr"/>
+      <c r="G30" s="70" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="64" t="inlineStr">
+      <c r="A31" s="68" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="B31" s="64" t="inlineStr">
+      <c r="B31" s="68" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1756,30 +1688,30 @@
           <t>Manifestazioni di interessePR FESR 2021/27 Azione 1.3.3 e del POC 2014/20 - Azione 1.3.1  - Avviso a manifestazione d’interesse eventi fieristici inte</t>
         </is>
       </c>
-      <c r="D31" s="65" t="inlineStr">
+      <c r="D31" s="69" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-d-interesse-eventi-fieristici-internazionali-marzo-dicembre-2026</t>
         </is>
       </c>
-      <c r="E31" s="64" t="inlineStr">
+      <c r="E31" s="68" t="inlineStr">
         <is>
           <t>30/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F31" s="64" t="inlineStr">
+      <c r="F31" s="68" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="G31" s="64" t="inlineStr"/>
+      <c r="G31" s="68" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="66" t="inlineStr">
+      <c r="A32" s="70" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="B32" s="66" t="inlineStr">
+      <c r="B32" s="70" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1789,22 +1721,22 @@
           <t>INTERNAZIONALIZZAZIONEL’Ecosistema dell’Innovazione a INNOVIT – Focus S3ApertoFESR</t>
         </is>
       </c>
-      <c r="D32" s="67" t="inlineStr">
+      <c r="D32" s="71" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lecosistema-dellinnovazione-a-innovit-focus-s3/</t>
         </is>
       </c>
-      <c r="E32" s="66" t="inlineStr"/>
-      <c r="F32" s="66" t="inlineStr"/>
-      <c r="G32" s="66" t="inlineStr"/>
+      <c r="E32" s="70" t="inlineStr"/>
+      <c r="F32" s="70" t="inlineStr"/>
+      <c r="G32" s="70" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="64" t="inlineStr">
+      <c r="A33" s="68" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="B33" s="64" t="inlineStr">
+      <c r="B33" s="68" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1814,22 +1746,22 @@
           <t>Manifestazioni di interessePR FESR SICILIA 2021/27 - NUOVO Avviso a manifestazione d’interesse per esperti valutatoriScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D33" s="65" t="inlineStr">
+      <c r="D33" s="69" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/pr-fesr-sicilia-202127-nuovo-avviso-manifestazione-d-interesse-esperti-valutatori</t>
         </is>
       </c>
-      <c r="E33" s="64" t="inlineStr"/>
-      <c r="F33" s="64" t="inlineStr"/>
-      <c r="G33" s="64" t="inlineStr"/>
+      <c r="E33" s="68" t="inlineStr"/>
+      <c r="F33" s="68" t="inlineStr"/>
+      <c r="G33" s="68" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="66" t="inlineStr">
+      <c r="A34" s="70" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="B34" s="66" t="inlineStr">
+      <c r="B34" s="70" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -1839,22 +1771,22 @@
           <t>Bando 2026 per contributi dedicati alla manutenzione della rete dei percorsi escursionistici</t>
         </is>
       </c>
-      <c r="D34" s="67" t="inlineStr">
+      <c r="D34" s="71" t="inlineStr">
         <is>
           <t>https://ambiente.regione.emilia-romagna.it/it/parchi-natura2000/bandi/bando-2026-per-contributi-dedicati-alla-manutenzione-della-rete-dei-percorsi-escursionistici</t>
         </is>
       </c>
-      <c r="E34" s="66" t="inlineStr"/>
-      <c r="F34" s="66" t="inlineStr"/>
-      <c r="G34" s="66" t="inlineStr"/>
+      <c r="E34" s="70" t="inlineStr"/>
+      <c r="F34" s="70" t="inlineStr"/>
+      <c r="G34" s="70" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="64" t="inlineStr">
+      <c r="A35" s="68" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="B35" s="64" t="inlineStr">
+      <c r="B35" s="68" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1864,22 +1796,22 @@
           <t>Programma regionale in favore delle tradizioni storiche, artistiche, religiose e popolari (2026) – manifestazioni d’interesseApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D35" s="65" t="inlineStr">
+      <c r="D35" s="69" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/programma-regionale-in-favore-delle-tradizioni-storiche-artistiche-religiose-e-popolari-2026-manifestazioni-dinteresse/</t>
         </is>
       </c>
-      <c r="E35" s="64" t="inlineStr"/>
-      <c r="F35" s="64" t="inlineStr"/>
-      <c r="G35" s="64" t="inlineStr"/>
+      <c r="E35" s="68" t="inlineStr"/>
+      <c r="F35" s="68" t="inlineStr"/>
+      <c r="G35" s="68" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="66" t="inlineStr">
+      <c r="A36" s="70" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B36" s="66" t="inlineStr">
+      <c r="B36" s="70" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1889,22 +1821,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEBuoni servizio per le persone non autosufficienti nel territorio del LazioProssima AperturaFSE / FSE+</t>
         </is>
       </c>
-      <c r="D36" s="67" t="inlineStr">
+      <c r="D36" s="71" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/buoni-servizio-per-le-persone-non-autosufficienti-nel-territorio-del-lazio/</t>
         </is>
       </c>
-      <c r="E36" s="66" t="inlineStr"/>
-      <c r="F36" s="66" t="inlineStr"/>
-      <c r="G36" s="66" t="inlineStr"/>
+      <c r="E36" s="70" t="inlineStr"/>
+      <c r="F36" s="70" t="inlineStr"/>
+      <c r="G36" s="70" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="64" t="inlineStr">
+      <c r="A37" s="68" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B37" s="64" t="inlineStr">
+      <c r="B37" s="68" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1914,22 +1846,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONERimborso delle rette dei servizi educativi nel territorio del LazioProssima AperturaFSE / FSE+</t>
         </is>
       </c>
-      <c r="D37" s="65" t="inlineStr">
+      <c r="D37" s="69" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/rimborso-delle-rette-dei-servizi-educativi-nel-territorio-del-lazio/</t>
         </is>
       </c>
-      <c r="E37" s="64" t="inlineStr"/>
-      <c r="F37" s="64" t="inlineStr"/>
-      <c r="G37" s="64" t="inlineStr"/>
+      <c r="E37" s="68" t="inlineStr"/>
+      <c r="F37" s="68" t="inlineStr"/>
+      <c r="G37" s="68" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="66" t="inlineStr">
+      <c r="A38" s="70" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B38" s="66" t="inlineStr">
+      <c r="B38" s="70" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1939,30 +1871,30 @@
           <t>Manifestazioni di interesseATTO DI INTERPELLO PER L’AFFIDAMENTO DELL’INCARICO DI COLLAUDO STATICO DELLE STRUTTURE - Diga di Pietrarossa (Progetto ex C</t>
         </is>
       </c>
-      <c r="D38" s="67" t="inlineStr">
+      <c r="D38" s="71" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/atto-interpello-l-affidamento-incarico-collaudo-statico-strutture-diga-pietrarossa-progetto-ex-casmez-303219</t>
         </is>
       </c>
-      <c r="E38" s="66" t="inlineStr">
+      <c r="E38" s="70" t="inlineStr">
         <is>
           <t>27/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F38" s="66" t="inlineStr">
+      <c r="F38" s="70" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="G38" s="66" t="inlineStr"/>
+      <c r="G38" s="70" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="64" t="inlineStr">
+      <c r="A39" s="68" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B39" s="64" t="inlineStr">
+      <c r="B39" s="68" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1972,30 +1904,30 @@
           <t>Manifestazioni di interesseAvviso alle Case  Editrici della Regione siciliana per la partecipazione al Salone del Libro di Torino, 14-18  maggio 2026.</t>
         </is>
       </c>
-      <c r="D39" s="65" t="inlineStr">
+      <c r="D39" s="69" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/manifestazione-d-interesse-partecipare-al-xxxviii-salone-libro-torino-14-al-18-maggio-2026-attraverso-l-esposizione-pubblicazioni-presso-stand-assessorato-beni</t>
         </is>
       </c>
-      <c r="E39" s="64" t="inlineStr">
+      <c r="E39" s="68" t="inlineStr">
         <is>
           <t>30/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F39" s="64" t="inlineStr">
+      <c r="F39" s="68" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="G39" s="64" t="inlineStr"/>
+      <c r="G39" s="68" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="66" t="inlineStr">
+      <c r="A40" s="70" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B40" s="66" t="inlineStr">
+      <c r="B40" s="70" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2005,30 +1937,30 @@
           <t xml:space="preserve">Manifestazioni di interessePR FESR SICILIA 2021/27 - NUOVO Avviso a manifestazione d’interesse per esperti valutatoriScade il:06/04/2026 - 23:59Leggi </t>
         </is>
       </c>
-      <c r="D40" s="67" t="inlineStr">
+      <c r="D40" s="71" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/pr-fesr-sicilia-202127-nuovo-avviso-manifestazione-d-interesse-esperti-valutatori</t>
         </is>
       </c>
-      <c r="E40" s="66" t="inlineStr">
+      <c r="E40" s="70" t="inlineStr">
         <is>
           <t>06/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F40" s="66" t="inlineStr">
+      <c r="F40" s="70" t="inlineStr">
         <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="G40" s="66" t="inlineStr"/>
+      <c r="G40" s="70" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="64" t="inlineStr">
+      <c r="A41" s="68" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B41" s="64" t="inlineStr">
+      <c r="B41" s="68" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2038,22 +1970,22 @@
           <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D41" s="65" t="inlineStr">
+      <c r="D41" s="69" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
         </is>
       </c>
-      <c r="E41" s="64" t="inlineStr"/>
-      <c r="F41" s="64" t="inlineStr"/>
-      <c r="G41" s="64" t="inlineStr"/>
+      <c r="E41" s="68" t="inlineStr"/>
+      <c r="F41" s="68" t="inlineStr"/>
+      <c r="G41" s="68" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="66" t="inlineStr">
+      <c r="A42" s="70" t="inlineStr">
         <is>
           <t>24/03/2026</t>
         </is>
       </c>
-      <c r="B42" s="66" t="inlineStr">
+      <c r="B42" s="70" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2063,22 +1995,22 @@
           <t>GAL del Ducato - Promozione di fiere agroalimentari e delle filiere del cibo – Bando per Enti pubblici (DU AS 05B)</t>
         </is>
       </c>
-      <c r="D42" s="67" t="inlineStr">
+      <c r="D42" s="71" t="inlineStr">
         <is>
           <t>https://agricoltura.regione.emilia-romagna.it/sviluppo-rurale-23-27/opportunita/bandi-gal/2026/du_as05b-promozione-di-fiere-agroalimentari-e-delle-filiere-del-cibo-bando-per-enti-pubblici</t>
         </is>
       </c>
-      <c r="E42" s="66" t="inlineStr"/>
-      <c r="F42" s="66" t="inlineStr"/>
-      <c r="G42" s="66" t="inlineStr"/>
+      <c r="E42" s="70" t="inlineStr"/>
+      <c r="F42" s="70" t="inlineStr"/>
+      <c r="G42" s="70" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="64" t="inlineStr">
+      <c r="A43" s="68" t="inlineStr">
         <is>
           <t>24/03/2026</t>
         </is>
       </c>
-      <c r="B43" s="64" t="inlineStr">
+      <c r="B43" s="68" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2088,30 +2020,30 @@
           <t>Manifestazioni di interesseAVVISO PUBBLICO PER MANIFESTAZIONE DI INTERESSE FINALIZZATA ALL'ASSEGNAZIONE DI SPAZI ESPOSITIVI (CORNER GRATUITI) ALL'INTE</t>
         </is>
       </c>
-      <c r="D43" s="65" t="inlineStr">
+      <c r="D43" s="69" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-manifestazione-interesse-finalizzata-all-assegnazione-spazi-espositivi-corner-gratuiti-all-interno-stand-istituzionale-dsrt-manifestazione</t>
         </is>
       </c>
-      <c r="E43" s="64" t="inlineStr">
+      <c r="E43" s="68" t="inlineStr">
         <is>
           <t>30/03/2026 - 13:00</t>
         </is>
       </c>
-      <c r="F43" s="64" t="inlineStr">
+      <c r="F43" s="68" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G43" s="64" t="inlineStr"/>
+      <c r="G43" s="68" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="66" t="inlineStr">
+      <c r="A44" s="70" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B44" s="66" t="inlineStr">
+      <c r="B44" s="70" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2121,22 +2053,22 @@
           <t>Avviso per la concessione di contributi per eventi sportivi realizzati in Emilia-Romagna - Anno 2026</t>
         </is>
       </c>
-      <c r="D44" s="67" t="inlineStr">
+      <c r="D44" s="71" t="inlineStr">
         <is>
           <t>https://www.regione.emilia-romagna.it/sport/bandi/2026/bando-2026</t>
         </is>
       </c>
-      <c r="E44" s="66" t="inlineStr"/>
-      <c r="F44" s="66" t="inlineStr"/>
-      <c r="G44" s="66" t="inlineStr"/>
+      <c r="E44" s="70" t="inlineStr"/>
+      <c r="F44" s="70" t="inlineStr"/>
+      <c r="G44" s="70" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="64" t="inlineStr">
+      <c r="A45" s="68" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B45" s="64" t="inlineStr">
+      <c r="B45" s="68" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2146,22 +2078,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Street art 2026Prossima AperturaBandi Regionali</t>
         </is>
       </c>
-      <c r="D45" s="65" t="inlineStr">
+      <c r="D45" s="69" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lazio-street-art-2026/</t>
         </is>
       </c>
-      <c r="E45" s="64" t="inlineStr"/>
-      <c r="F45" s="64" t="inlineStr"/>
-      <c r="G45" s="64" t="inlineStr"/>
+      <c r="E45" s="68" t="inlineStr"/>
+      <c r="F45" s="68" t="inlineStr"/>
+      <c r="G45" s="68" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="66" t="inlineStr">
+      <c r="A46" s="70" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B46" s="66" t="inlineStr">
+      <c r="B46" s="70" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2171,30 +2103,30 @@
           <t>Manifestazioni di interesseManifestazione di interesse per la partecipazione all’evento “R2I Italy 2026” – Bologna, 12-13/05/2026Scade il:03/04/2026 -</t>
         </is>
       </c>
-      <c r="D46" s="67" t="inlineStr">
+      <c r="D46" s="71" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/manifestazione-interesse-partecipazione-all-evento-r2i-italy-2026-bologna-12-13052026</t>
         </is>
       </c>
-      <c r="E46" s="66" t="inlineStr">
+      <c r="E46" s="70" t="inlineStr">
         <is>
           <t>03/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F46" s="66" t="inlineStr">
+      <c r="F46" s="70" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="G46" s="66" t="inlineStr"/>
+      <c r="G46" s="70" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="64" t="inlineStr">
+      <c r="A47" s="68" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B47" s="64" t="inlineStr">
+      <c r="B47" s="68" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2204,30 +2136,30 @@
           <t>Manifestazioni di interesseST SIRACUSA - AVVISO PER MANIFESTAZIONE DI INTERESSE - Selezione di n. 5 unità di personale internoScade il:20/04/2026 - 12</t>
         </is>
       </c>
-      <c r="D47" s="65" t="inlineStr">
+      <c r="D47" s="69" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/24-marzo-2026-st-siracusa-avviso-manifestazione-interesse-selezione-n-5-unita-personale-interno</t>
         </is>
       </c>
-      <c r="E47" s="64" t="inlineStr">
+      <c r="E47" s="68" t="inlineStr">
         <is>
           <t>20/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F47" s="64" t="inlineStr">
+      <c r="F47" s="68" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="G47" s="64" t="inlineStr"/>
+      <c r="G47" s="68" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="66" t="inlineStr">
+      <c r="A48" s="70" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B48" s="66" t="inlineStr">
+      <c r="B48" s="70" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2237,30 +2169,30 @@
           <t>Avvisi pubbliciRevoca dell’avviso di concessione a titolo gratuito del 16.12.2025 inerente all’immobile di seguito identificato e contestuale nuovo av</t>
         </is>
       </c>
-      <c r="D48" s="67" t="inlineStr">
+      <c r="D48" s="71" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/revoca-avviso-concessione-titolo-gratuito-16122025-inerente-all-immobile-seguito-identificato-contestuale-nuovo-avviso-concessione-titolo-oneroso-stesso-sito-nel</t>
         </is>
       </c>
-      <c r="E48" s="66" t="inlineStr">
+      <c r="E48" s="70" t="inlineStr">
         <is>
           <t>08/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F48" s="66" t="inlineStr">
+      <c r="F48" s="70" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="G48" s="66" t="inlineStr"/>
+      <c r="G48" s="70" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="64" t="inlineStr">
+      <c r="A49" s="68" t="inlineStr">
         <is>
           <t>26/03/2026</t>
         </is>
       </c>
-      <c r="B49" s="64" t="inlineStr">
+      <c r="B49" s="68" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2270,22 +2202,22 @@
           <t>Bando studi di fattibilità per fusioni di Comuni</t>
         </is>
       </c>
-      <c r="D49" s="65" t="inlineStr">
+      <c r="D49" s="69" t="inlineStr">
         <is>
           <t>https://www.regione.emilia-romagna.it/autonomie-locali/bandi/bando_studi_fattibilita_fusioni_comuni</t>
         </is>
       </c>
-      <c r="E49" s="64" t="inlineStr"/>
-      <c r="F49" s="64" t="inlineStr"/>
-      <c r="G49" s="64" t="inlineStr"/>
+      <c r="E49" s="68" t="inlineStr"/>
+      <c r="F49" s="68" t="inlineStr"/>
+      <c r="G49" s="68" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="66" t="inlineStr">
+      <c r="A50" s="70" t="inlineStr">
         <is>
           <t>26/03/2026</t>
         </is>
       </c>
-      <c r="B50" s="66" t="inlineStr">
+      <c r="B50" s="70" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2295,30 +2227,30 @@
           <t xml:space="preserve">Manifestazioni di interesseAvviso pubblico di selezione interna, per titoli, per il conferimento di PO e professionali, ai sensi degli artt. 19, 20 e </t>
         </is>
       </c>
-      <c r="D50" s="67" t="inlineStr">
+      <c r="D50" s="71" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-selezione-interna-titoli-conferimento-po-professionali-ai-sensi-artt-19-20-21-ccrl-20222024-comparto-non-dirigenziale</t>
         </is>
       </c>
-      <c r="E50" s="66" t="inlineStr">
+      <c r="E50" s="70" t="inlineStr">
         <is>
           <t>30/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F50" s="66" t="inlineStr">
+      <c r="F50" s="70" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G50" s="66" t="inlineStr"/>
+      <c r="G50" s="70" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="64" t="inlineStr">
+      <c r="A51" s="68" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="B51" s="64" t="inlineStr">
+      <c r="B51" s="68" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2328,22 +2260,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0PRE-SEED 3.0ApertoFESR</t>
         </is>
       </c>
-      <c r="D51" s="65" t="inlineStr">
+      <c r="D51" s="69" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/pre-seed-3-0/</t>
         </is>
       </c>
-      <c r="E51" s="64" t="inlineStr"/>
-      <c r="F51" s="64" t="inlineStr"/>
-      <c r="G51" s="64" t="inlineStr"/>
+      <c r="E51" s="68" t="inlineStr"/>
+      <c r="F51" s="68" t="inlineStr"/>
+      <c r="G51" s="68" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="66" t="inlineStr">
+      <c r="A52" s="70" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B52" s="66" t="inlineStr">
+      <c r="B52" s="70" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2353,30 +2285,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “So</t>
         </is>
       </c>
-      <c r="D52" s="67" t="inlineStr">
+      <c r="D52" s="71" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-termini-imerese-locta-piazza-marina</t>
         </is>
       </c>
-      <c r="E52" s="66" t="inlineStr">
+      <c r="E52" s="70" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F52" s="66" t="inlineStr">
+      <c r="F52" s="70" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G52" s="66" t="inlineStr"/>
+      <c r="G52" s="70" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="64" t="inlineStr">
+      <c r="A53" s="68" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B53" s="64" t="inlineStr">
+      <c r="B53" s="68" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2386,30 +2318,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, Sig</t>
         </is>
       </c>
-      <c r="D53" s="65" t="inlineStr">
+      <c r="D53" s="69" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-porto-empedocle-locta-punta-piccola</t>
         </is>
       </c>
-      <c r="E53" s="64" t="inlineStr">
+      <c r="E53" s="68" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F53" s="64" t="inlineStr">
+      <c r="F53" s="68" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G53" s="64" t="inlineStr"/>
+      <c r="G53" s="68" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="66" t="inlineStr">
+      <c r="A54" s="70" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B54" s="66" t="inlineStr">
+      <c r="B54" s="70" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2419,30 +2351,30 @@
           <t xml:space="preserve">Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “Società </t>
         </is>
       </c>
-      <c r="D54" s="67" t="inlineStr">
+      <c r="D54" s="71" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-messina-locta-torrente-bordonaro</t>
         </is>
       </c>
-      <c r="E54" s="66" t="inlineStr">
+      <c r="E54" s="70" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F54" s="66" t="inlineStr">
+      <c r="F54" s="70" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G54" s="66" t="inlineStr"/>
+      <c r="G54" s="70" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="64" t="inlineStr">
+      <c r="A55" s="68" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B55" s="64" t="inlineStr">
+      <c r="B55" s="68" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2452,30 +2384,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “Condomin</t>
         </is>
       </c>
-      <c r="D55" s="65" t="inlineStr">
+      <c r="D55" s="69" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-mascali-spiaggia-n-144150</t>
         </is>
       </c>
-      <c r="E55" s="64" t="inlineStr">
+      <c r="E55" s="68" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F55" s="64" t="inlineStr">
+      <c r="F55" s="68" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G55" s="64" t="inlineStr"/>
+      <c r="G55" s="68" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="66" t="inlineStr">
+      <c r="A56" s="70" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B56" s="66" t="inlineStr">
+      <c r="B56" s="70" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2485,30 +2417,30 @@
           <t xml:space="preserve">Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione sito nel Comune di Lipari, isola di Stromboli, </t>
         </is>
       </c>
-      <c r="D56" s="67" t="inlineStr">
+      <c r="D56" s="71" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-lipari-isola-stromboli-locta-fico-grande</t>
         </is>
       </c>
-      <c r="E56" s="66" t="inlineStr">
+      <c r="E56" s="70" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F56" s="66" t="inlineStr">
+      <c r="F56" s="70" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G56" s="66" t="inlineStr"/>
+      <c r="G56" s="70" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="64" t="inlineStr">
+      <c r="A57" s="68" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B57" s="64" t="inlineStr">
+      <c r="B57" s="68" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2518,30 +2450,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione sito nel Comune di Favignana, isola di Le</t>
         </is>
       </c>
-      <c r="D57" s="65" t="inlineStr">
+      <c r="D57" s="69" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-favignana-isola-levanzo</t>
         </is>
       </c>
-      <c r="E57" s="64" t="inlineStr">
+      <c r="E57" s="68" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F57" s="64" t="inlineStr">
+      <c r="F57" s="68" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G57" s="64" t="inlineStr"/>
+      <c r="G57" s="68" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="66" t="inlineStr">
+      <c r="A58" s="70" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="B58" s="66" t="inlineStr">
+      <c r="B58" s="70" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2551,30 +2483,30 @@
           <t>Manifestazioni di interesseAVVISO - Manifestazione d’interesse finalizzata alla selezione di organismi attuatori di piani di gestione locale della pic</t>
         </is>
       </c>
-      <c r="D58" s="67" t="inlineStr">
+      <c r="D58" s="71" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-d-interesse-finalizzata-alla-selezione-organismi-attuatori-piani-gestione-locale-piccola-pesca-costiera-nelle-gsa-regione-siciliana</t>
         </is>
       </c>
-      <c r="E58" s="66" t="inlineStr">
+      <c r="E58" s="70" t="inlineStr">
         <is>
           <t>29/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F58" s="66" t="inlineStr">
+      <c r="F58" s="70" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="G58" s="66" t="inlineStr"/>
+      <c r="G58" s="70" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="64" t="inlineStr">
+      <c r="A59" s="68" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="B59" s="64" t="inlineStr">
+      <c r="B59" s="68" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2584,30 +2516,30 @@
           <t>Avvisi pubbliciLeggi e scarica l'avvisoScade il:02/04/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D59" s="65" t="inlineStr">
+      <c r="D59" s="69" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/proroga-termini-presentazione-candidature-po</t>
         </is>
       </c>
-      <c r="E59" s="64" t="inlineStr">
+      <c r="E59" s="68" t="inlineStr">
         <is>
           <t>02/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F59" s="64" t="inlineStr">
+      <c r="F59" s="68" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="G59" s="64" t="inlineStr"/>
+      <c r="G59" s="68" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="66" t="inlineStr">
+      <c r="A60" s="70" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="66" t="inlineStr">
+      <c r="B60" s="70" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2617,22 +2549,22 @@
           <t>INTERNAZIONALIZZAZIONESMAU – Italy RestartsUp in STOCCOLMAApertoFESR</t>
         </is>
       </c>
-      <c r="D60" s="67" t="inlineStr">
+      <c r="D60" s="71" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/smau-italy-restartsup-in-stoccolma/</t>
         </is>
       </c>
-      <c r="E60" s="66" t="inlineStr"/>
-      <c r="F60" s="66" t="inlineStr"/>
-      <c r="G60" s="66" t="inlineStr"/>
+      <c r="E60" s="70" t="inlineStr"/>
+      <c r="F60" s="70" t="inlineStr"/>
+      <c r="G60" s="70" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="64" t="inlineStr">
+      <c r="A61" s="68" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B61" s="64" t="inlineStr">
+      <c r="B61" s="68" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2642,22 +2574,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per Farnborough International AirshowApertoFESR</t>
         </is>
       </c>
-      <c r="D61" s="65" t="inlineStr">
+      <c r="D61" s="69" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-farnborough-international-airshow-2/</t>
         </is>
       </c>
-      <c r="E61" s="64" t="inlineStr"/>
-      <c r="F61" s="64" t="inlineStr"/>
-      <c r="G61" s="64" t="inlineStr"/>
+      <c r="E61" s="68" t="inlineStr"/>
+      <c r="F61" s="68" t="inlineStr"/>
+      <c r="G61" s="68" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="66" t="inlineStr">
+      <c r="A62" s="70" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="66" t="inlineStr">
+      <c r="B62" s="70" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2667,30 +2599,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA - alienazione lotto di terreno sito nel comune di Termini Imerese, via LibertàScade il:30/04/2026 - 12:00Leg</t>
         </is>
       </c>
-      <c r="D62" s="67" t="inlineStr">
+      <c r="D62" s="71" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proprieta-regionale-sito-nel-comune-termini-imerese-favore-ares-fabiola</t>
         </is>
       </c>
-      <c r="E62" s="66" t="inlineStr">
+      <c r="E62" s="70" t="inlineStr">
         <is>
           <t>30/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F62" s="66" t="inlineStr">
+      <c r="F62" s="70" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="G62" s="66" t="inlineStr"/>
+      <c r="G62" s="70" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="64" t="inlineStr">
+      <c r="A63" s="68" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B63" s="64" t="inlineStr">
+      <c r="B63" s="68" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2700,22 +2632,22 @@
           <t>Avviso per la concessione di contributi per progetti di contrasto all'abbandono sportivo giovanile (2026)</t>
         </is>
       </c>
-      <c r="D63" s="65" t="inlineStr">
+      <c r="D63" s="69" t="inlineStr">
         <is>
           <t>https://www.regione.emilia-romagna.it/sport/bandi/2026/contrasto-abbandono-2026</t>
         </is>
       </c>
-      <c r="E63" s="64" t="inlineStr"/>
-      <c r="F63" s="64" t="inlineStr"/>
-      <c r="G63" s="64" t="inlineStr"/>
+      <c r="E63" s="68" t="inlineStr"/>
+      <c r="F63" s="68" t="inlineStr"/>
+      <c r="G63" s="68" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="66" t="inlineStr">
+      <c r="A64" s="70" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="66" t="inlineStr">
+      <c r="B64" s="70" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2725,30 +2657,30 @@
           <t>Avvisi pubbliciAvviso si procede alla riassegnazione della posizione organizzativa a supporto delle attività del Servizio 2 “Investimenti in Agricoltu</t>
         </is>
       </c>
-      <c r="D64" s="67" t="inlineStr">
+      <c r="D64" s="71" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-selezione-interna-conferimento-1-posizione-organizzativa-ai-sensi-artt-19-20-ccrl-2022-2024-comparto-non-dirigenziale</t>
         </is>
       </c>
-      <c r="E64" s="66" t="inlineStr">
+      <c r="E64" s="70" t="inlineStr">
         <is>
           <t>09/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F64" s="66" t="inlineStr">
+      <c r="F64" s="70" t="inlineStr">
         <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="G64" s="66" t="inlineStr"/>
+      <c r="G64" s="70" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="64" t="inlineStr">
+      <c r="A65" s="68" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B65" s="64" t="inlineStr">
+      <c r="B65" s="68" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2758,30 +2690,30 @@
           <t>Avvisi pubbliciST-MESSINA - AVVISO di INDAGINE DI MERCATO per affidamento "Interventi manutenzione straordinaria della strada/pista forestale "Annunzi</t>
         </is>
       </c>
-      <c r="D65" s="65" t="inlineStr">
+      <c r="D65" s="69" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-indagine-mercato-affidamento-interventi-manutenzione-straordinaria-stradapista-forestale-annunziata-comune-messina</t>
         </is>
       </c>
-      <c r="E65" s="64" t="inlineStr">
+      <c r="E65" s="68" t="inlineStr">
         <is>
           <t>16/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F65" s="64" t="inlineStr">
+      <c r="F65" s="68" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="G65" s="64" t="inlineStr"/>
+      <c r="G65" s="68" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="66" t="inlineStr">
+      <c r="A66" s="70" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="66" t="inlineStr">
+      <c r="B66" s="70" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2791,22 +2723,22 @@
           <t>Avvisi pubbliciST-MESSINA - AVVISO DI INDAGINE DI MERCATO per affidamento "Interventi manutenzione straordinaria della strada/pista forestale "San Riz</t>
         </is>
       </c>
-      <c r="D66" s="67" t="inlineStr">
+      <c r="D66" s="71" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-indagine-mercato-affidamento-interventi-manutenzione-straordinaria-stradapista-forestale-san-rizzo-san-leone-crupi-madonuzza-comune-messina</t>
         </is>
       </c>
-      <c r="E66" s="66" t="inlineStr">
+      <c r="E66" s="70" t="inlineStr">
         <is>
           <t>16/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F66" s="66" t="inlineStr">
+      <c r="F66" s="70" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="G66" s="66" t="inlineStr"/>
+      <c r="G66" s="70" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="68" t="inlineStr">
@@ -2948,6 +2880,64 @@
       <c r="E71" s="68" t="inlineStr"/>
       <c r="F71" s="68" t="inlineStr"/>
       <c r="G71" s="68" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="74" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="74" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>LAVORO, FORMAZIONE E INCLUSIONEComunicare l’inclusione – contest per le istituzioni scolastiche regionaliApertoBandi Regionali</t>
+        </is>
+      </c>
+      <c r="D72" s="75" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/comunicare-linclusione-contest-per-le-istituzioni-scolastiche-regionali/</t>
+        </is>
+      </c>
+      <c r="E72" s="74" t="inlineStr"/>
+      <c r="F72" s="74" t="inlineStr"/>
+      <c r="G72" s="74" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="72" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="72" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>Avvisi pubbliciAPPROVAZIONE AVVISO PUBBLICOScade il:03/04/2027 - 00:00Leggi di più</t>
+        </is>
+      </c>
+      <c r="D73" s="73" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/approvazione-avviso-pubblico</t>
+        </is>
+      </c>
+      <c r="E73" s="72" t="inlineStr">
+        <is>
+          <t>03/04/2027 - 00:00</t>
+        </is>
+      </c>
+      <c r="F73" s="72" t="inlineStr">
+        <is>
+          <t>03/04/2027</t>
+        </is>
+      </c>
+      <c r="G73" s="72" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -3021,6 +3011,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId69"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId72"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3065,7 +3057,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="68" t="inlineStr">
+      <c r="A3" s="72" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -3078,29 +3070,29 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="70" t="inlineStr">
+      <c r="A4" s="74" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="68" t="inlineStr">
+      <c r="A5" s="72" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">

--- a/data/bandi_export.xlsx
+++ b/data/bandi_export.xlsx
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -267,6 +267,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -721,7 +733,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏛️  Nuovi Bandi — 04/04/2026 07:44</t>
+          <t>🏛️  Nuovi Bandi — 08/04/2026 08:08</t>
         </is>
       </c>
     </row>
@@ -766,52 +778,52 @@
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="72" t="inlineStr">
+      <c r="B3" s="76" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>LAVORO, FORMAZIONE E INCLUSIONEComunicare l’inclusione – contest per le istituzioni scolastiche regionaliApertoBandi Regionali</t>
-        </is>
-      </c>
-      <c r="D3" s="73" t="inlineStr">
-        <is>
-          <t>https://www.lazioeuropa.it/bandi/comunicare-linclusione-contest-per-le-istituzioni-scolastiche-regionali/</t>
-        </is>
-      </c>
-      <c r="E3" s="72" t="inlineStr"/>
-      <c r="F3" s="72" t="inlineStr"/>
+          <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Donne e Impresa 2026Prossima AperturaFESR</t>
+        </is>
+      </c>
+      <c r="D3" s="77" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/donne-e-impresa-2026/</t>
+        </is>
+      </c>
+      <c r="E3" s="76" t="inlineStr"/>
+      <c r="F3" s="76" t="inlineStr"/>
       <c r="G3" s="5" t="inlineStr"/>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="74" t="inlineStr">
+      <c r="B4" s="78" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>Avvisi pubbliciAPPROVAZIONE AVVISO PUBBLICOScade il:03/04/2027 - 00:00Leggi di più</t>
-        </is>
-      </c>
-      <c r="D4" s="75" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/approvazione-avviso-pubblico</t>
-        </is>
-      </c>
-      <c r="E4" s="74" t="inlineStr">
-        <is>
-          <t>03/04/2027 - 00:00</t>
-        </is>
-      </c>
-      <c r="F4" s="74" t="inlineStr">
-        <is>
-          <t>03/04/2027</t>
+          <t>Bandi di garaCodice Intervento 111302_FELUCHE - Investimenti a bordo e nei porti per incrementare la qualità delle produzioni e migliorare le condizio</t>
+        </is>
+      </c>
+      <c r="D4" s="79" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/bandoavviso-regia-ob-11-azione-3-codice-111302feluche-investimenti-bordo-valorizzazione-feluche-miglioramento-condizioni-lavoro-salute-sicurezza-operatori-l</t>
+        </is>
+      </c>
+      <c r="E4" s="78" t="inlineStr">
+        <is>
+          <t>02/07/2026 - 23:59</t>
+        </is>
+      </c>
+      <c r="F4" s="78" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="G4" s="9" t="inlineStr"/>
@@ -834,7 +846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -884,12 +896,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="70" t="inlineStr">
+      <c r="A2" s="74" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B2" s="70" t="inlineStr">
+      <c r="B2" s="74" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -899,22 +911,22 @@
           <t>FLAG GALPA Costa E-R. Sostituzione del motore principale e dei motori secondari. Secondo bando</t>
         </is>
       </c>
-      <c r="D2" s="71" t="inlineStr">
+      <c r="D2" s="75" t="inlineStr">
         <is>
           <t>https://agricoltura.regione.emilia-romagna.it/feampa-2021-2027/bandi-galpa/2026/galpa-sostituzione-motori-secondo-bando</t>
         </is>
       </c>
-      <c r="E2" s="70" t="inlineStr"/>
-      <c r="F2" s="70" t="inlineStr"/>
-      <c r="G2" s="70" t="inlineStr"/>
+      <c r="E2" s="74" t="inlineStr"/>
+      <c r="F2" s="74" t="inlineStr"/>
+      <c r="G2" s="74" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="68" t="inlineStr">
+      <c r="A3" s="72" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B3" s="68" t="inlineStr">
+      <c r="B3" s="72" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -924,22 +936,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0PRE-SEED 3.0Prossima AperturaFESR</t>
         </is>
       </c>
-      <c r="D3" s="69" t="inlineStr">
+      <c r="D3" s="73" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/pre-seed-3-0/</t>
         </is>
       </c>
-      <c r="E3" s="68" t="inlineStr"/>
-      <c r="F3" s="68" t="inlineStr"/>
-      <c r="G3" s="68" t="inlineStr"/>
+      <c r="E3" s="72" t="inlineStr"/>
+      <c r="F3" s="72" t="inlineStr"/>
+      <c r="G3" s="72" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="70" t="inlineStr">
+      <c r="A4" s="74" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B4" s="70" t="inlineStr">
+      <c r="B4" s="74" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -949,22 +961,22 @@
           <t>ACCESSO AL CREDITO E ALLE GARANZIE PER LE IMPRESEContributo su finanziamenti alle imprese del Lazio erogati su provvista BEIProssima AperturaFESR</t>
         </is>
       </c>
-      <c r="D4" s="71" t="inlineStr">
+      <c r="D4" s="75" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-su-finanziamenti-alle-imprese-del-lazio-erogati-su-provvista-bei/</t>
         </is>
       </c>
-      <c r="E4" s="70" t="inlineStr"/>
-      <c r="F4" s="70" t="inlineStr"/>
-      <c r="G4" s="70" t="inlineStr"/>
+      <c r="E4" s="74" t="inlineStr"/>
+      <c r="F4" s="74" t="inlineStr"/>
+      <c r="G4" s="74" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="68" t="inlineStr">
+      <c r="A5" s="72" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B5" s="68" t="inlineStr">
+      <c r="B5" s="72" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -974,22 +986,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEIndividuazione degli enti iscritti al Registro unico nazionale del Terzo settoreApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D5" s="69" t="inlineStr">
+      <c r="D5" s="73" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/individuazione-degli-enti-iscritti-al-registro-unico-nazionale-del-terzo-settore/</t>
         </is>
       </c>
-      <c r="E5" s="68" t="inlineStr"/>
-      <c r="F5" s="68" t="inlineStr"/>
-      <c r="G5" s="68" t="inlineStr"/>
+      <c r="E5" s="72" t="inlineStr"/>
+      <c r="F5" s="72" t="inlineStr"/>
+      <c r="G5" s="72" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="70" t="inlineStr">
+      <c r="A6" s="74" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B6" s="70" t="inlineStr">
+      <c r="B6" s="74" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -999,22 +1011,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Technology Transfer LazioApertoFESR</t>
         </is>
       </c>
-      <c r="D6" s="71" t="inlineStr">
+      <c r="D6" s="75" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/technology-transfer-lazio/</t>
         </is>
       </c>
-      <c r="E6" s="70" t="inlineStr"/>
-      <c r="F6" s="70" t="inlineStr"/>
-      <c r="G6" s="70" t="inlineStr"/>
+      <c r="E6" s="74" t="inlineStr"/>
+      <c r="F6" s="74" t="inlineStr"/>
+      <c r="G6" s="74" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="68" t="inlineStr">
+      <c r="A7" s="72" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B7" s="68" t="inlineStr">
+      <c r="B7" s="72" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1024,22 +1036,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Percorso di tutoraggio per le impreseApertoFESR</t>
         </is>
       </c>
-      <c r="D7" s="69" t="inlineStr">
+      <c r="D7" s="73" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/percorso-di-tutoraggio-per-le-imprese/</t>
         </is>
       </c>
-      <c r="E7" s="68" t="inlineStr"/>
-      <c r="F7" s="68" t="inlineStr"/>
-      <c r="G7" s="68" t="inlineStr"/>
+      <c r="E7" s="72" t="inlineStr"/>
+      <c r="F7" s="72" t="inlineStr"/>
+      <c r="G7" s="72" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="70" t="inlineStr">
+      <c r="A8" s="74" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B8" s="70" t="inlineStr">
+      <c r="B8" s="74" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1049,22 +1061,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per partecipare a SMAU Parigi 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D8" s="71" t="inlineStr">
+      <c r="D8" s="75" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-partecipare-a-smau-parigi-2026/</t>
         </is>
       </c>
-      <c r="E8" s="70" t="inlineStr"/>
-      <c r="F8" s="70" t="inlineStr"/>
-      <c r="G8" s="70" t="inlineStr"/>
+      <c r="E8" s="74" t="inlineStr"/>
+      <c r="F8" s="74" t="inlineStr"/>
+      <c r="G8" s="74" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="68" t="inlineStr">
+      <c r="A9" s="72" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B9" s="68" t="inlineStr">
+      <c r="B9" s="72" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1074,22 +1086,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONERiconoscimento della funzione sociale ed educativa degli oratoriApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D9" s="69" t="inlineStr">
+      <c r="D9" s="73" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/riconoscimento-della-funzione-sociale-ed-educativa-degli-oratori/</t>
         </is>
       </c>
-      <c r="E9" s="68" t="inlineStr"/>
-      <c r="F9" s="68" t="inlineStr"/>
-      <c r="G9" s="68" t="inlineStr"/>
+      <c r="E9" s="72" t="inlineStr"/>
+      <c r="F9" s="72" t="inlineStr"/>
+      <c r="G9" s="72" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="70" t="inlineStr">
+      <c r="A10" s="74" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B10" s="70" t="inlineStr">
+      <c r="B10" s="74" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1099,22 +1111,22 @@
           <t>GovernanceIscrizione nell’elenco regionale degli idonei all’esercizio dell’attività di direttore dell’Istituto JemoloApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D10" s="71" t="inlineStr">
+      <c r="D10" s="75" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/iscrizione-nellelenco-regionale-degli-idonei-allesercizio-dellattivita-di-direttore-dellistituto-jemolo/</t>
         </is>
       </c>
-      <c r="E10" s="70" t="inlineStr"/>
-      <c r="F10" s="70" t="inlineStr"/>
-      <c r="G10" s="70" t="inlineStr"/>
+      <c r="E10" s="74" t="inlineStr"/>
+      <c r="F10" s="74" t="inlineStr"/>
+      <c r="G10" s="74" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="68" t="inlineStr">
+      <c r="A11" s="72" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B11" s="68" t="inlineStr">
+      <c r="B11" s="72" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1124,22 +1136,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEVoucher per lo sport – seconda annualitàApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D11" s="69" t="inlineStr">
+      <c r="D11" s="73" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/voucher-per-lo-sport-seconda-annualita/</t>
         </is>
       </c>
-      <c r="E11" s="68" t="inlineStr"/>
-      <c r="F11" s="68" t="inlineStr"/>
-      <c r="G11" s="68" t="inlineStr"/>
+      <c r="E11" s="72" t="inlineStr"/>
+      <c r="F11" s="72" t="inlineStr"/>
+      <c r="G11" s="72" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="70" t="inlineStr">
+      <c r="A12" s="74" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B12" s="70" t="inlineStr">
+      <c r="B12" s="74" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1149,22 +1161,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEBonus occupazionale SALGOApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D12" s="71" t="inlineStr">
+      <c r="D12" s="75" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/bonus-occupazionale-salgo/</t>
         </is>
       </c>
-      <c r="E12" s="70" t="inlineStr"/>
-      <c r="F12" s="70" t="inlineStr"/>
-      <c r="G12" s="70" t="inlineStr"/>
+      <c r="E12" s="74" t="inlineStr"/>
+      <c r="F12" s="74" t="inlineStr"/>
+      <c r="G12" s="74" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="68" t="inlineStr">
+      <c r="A13" s="72" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B13" s="68" t="inlineStr">
+      <c r="B13" s="72" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1174,22 +1186,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEContributo di Libertà per le donne che hanno subito violenzaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D13" s="69" t="inlineStr">
+      <c r="D13" s="73" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-di-liberta-per-le-donne-che-hanno-subito-violenza/</t>
         </is>
       </c>
-      <c r="E13" s="68" t="inlineStr"/>
-      <c r="F13" s="68" t="inlineStr"/>
-      <c r="G13" s="68" t="inlineStr"/>
+      <c r="E13" s="72" t="inlineStr"/>
+      <c r="F13" s="72" t="inlineStr"/>
+      <c r="G13" s="72" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="70" t="inlineStr">
+      <c r="A14" s="74" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B14" s="70" t="inlineStr">
+      <c r="B14" s="74" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1199,22 +1211,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURAInterventi straordinari di valorizzazione del patrimonio culturale del LazioApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D14" s="71" t="inlineStr">
+      <c r="D14" s="75" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/interventi-straordinari-di-valorizzazione-del-patrimonio-culturale-del-lazio/</t>
         </is>
       </c>
-      <c r="E14" s="70" t="inlineStr"/>
-      <c r="F14" s="70" t="inlineStr"/>
-      <c r="G14" s="70" t="inlineStr"/>
+      <c r="E14" s="74" t="inlineStr"/>
+      <c r="F14" s="74" t="inlineStr"/>
+      <c r="G14" s="74" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="68" t="inlineStr">
+      <c r="A15" s="72" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B15" s="68" t="inlineStr">
+      <c r="B15" s="72" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1224,30 +1236,30 @@
           <t>Bandi di garaBANDO ATTUAZIONE Ob. 1.1 Azione 1 codice 111102 _DIV - "SOSTEGNO ALLA DIVERSIFICAZIONE E NUOVE FORME DI REDDITO PER LA PICCOLA PESCA COST</t>
         </is>
       </c>
-      <c r="D15" s="69" t="inlineStr">
+      <c r="D15" s="73" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/bando-avviso-regia-ob-11-azione-1-codice-111102-div-sostegno-alla-diversificazione-nuove-forme-reddito-piccola-pesca-costiera</t>
         </is>
       </c>
-      <c r="E15" s="68" t="inlineStr">
+      <c r="E15" s="72" t="inlineStr">
         <is>
           <t>07/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F15" s="68" t="inlineStr">
+      <c r="F15" s="72" t="inlineStr">
         <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="G15" s="68" t="inlineStr"/>
+      <c r="G15" s="72" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="70" t="inlineStr">
+      <c r="A16" s="74" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B16" s="70" t="inlineStr">
+      <c r="B16" s="74" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1257,30 +1269,30 @@
           <t>Avvisi pubblici09 marzo 2026 - ST SIRACUSA - AVVISO PUBBLICO PER LA COSTITUZIONE DI ELENCHI DI OPERATORI ECONOMICI PER L’ACQUISIZIONE DI BENI E SERVIZ</t>
         </is>
       </c>
-      <c r="D16" s="71" t="inlineStr">
+      <c r="D16" s="75" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/09-marzo-2026-st-siracusa-avviso-pubblico-costituzione-elenchi-operatori-economici-l-acquisizione-beni-servizi</t>
         </is>
       </c>
-      <c r="E16" s="70" t="inlineStr">
+      <c r="E16" s="74" t="inlineStr">
         <is>
           <t>31/12/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F16" s="70" t="inlineStr">
+      <c r="F16" s="74" t="inlineStr">
         <is>
           <t>31/12/2026</t>
         </is>
       </c>
-      <c r="G16" s="70" t="inlineStr"/>
+      <c r="G16" s="74" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="68" t="inlineStr">
+      <c r="A17" s="72" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B17" s="68" t="inlineStr">
+      <c r="B17" s="72" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1290,30 +1302,30 @@
           <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScade il:19/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D17" s="69" t="inlineStr">
+      <c r="D17" s="73" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
         </is>
       </c>
-      <c r="E17" s="68" t="inlineStr">
+      <c r="E17" s="72" t="inlineStr">
         <is>
           <t>19/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F17" s="68" t="inlineStr">
+      <c r="F17" s="72" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G17" s="68" t="inlineStr"/>
+      <c r="G17" s="72" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="70" t="inlineStr">
+      <c r="A18" s="74" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B18" s="70" t="inlineStr">
+      <c r="B18" s="74" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1323,22 +1335,22 @@
           <t>Manifestazioni di interesseAvviso Manifestazione Interesse DISTRIBUTORI AUTOMATICI di bevande e snackScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D18" s="71" t="inlineStr">
+      <c r="D18" s="75" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-distributori-automatici-bevande-snack</t>
         </is>
       </c>
-      <c r="E18" s="70" t="inlineStr"/>
-      <c r="F18" s="70" t="inlineStr"/>
-      <c r="G18" s="70" t="inlineStr"/>
+      <c r="E18" s="74" t="inlineStr"/>
+      <c r="F18" s="74" t="inlineStr"/>
+      <c r="G18" s="74" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="68" t="inlineStr">
+      <c r="A19" s="72" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B19" s="68" t="inlineStr">
+      <c r="B19" s="72" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1348,30 +1360,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D19" s="69" t="inlineStr">
+      <c r="D19" s="73" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo</t>
         </is>
       </c>
-      <c r="E19" s="68" t="inlineStr">
+      <c r="E19" s="72" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F19" s="68" t="inlineStr">
+      <c r="F19" s="72" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G19" s="68" t="inlineStr"/>
+      <c r="G19" s="72" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="70" t="inlineStr">
+      <c r="A20" s="74" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B20" s="70" t="inlineStr">
+      <c r="B20" s="74" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1381,30 +1393,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D20" s="71" t="inlineStr">
+      <c r="D20" s="75" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo-0</t>
         </is>
       </c>
-      <c r="E20" s="70" t="inlineStr">
+      <c r="E20" s="74" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F20" s="70" t="inlineStr">
+      <c r="F20" s="74" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G20" s="70" t="inlineStr"/>
+      <c r="G20" s="74" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="68" t="inlineStr">
+      <c r="A21" s="72" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B21" s="68" t="inlineStr">
+      <c r="B21" s="72" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1414,22 +1426,22 @@
           <t>Manifestazioni di interesseST SIRACUSA - AVVISO DI MANIFESTAZIONE DI INTERESSE - Fornitura applicativo extracontabile per la gestione progetti, ecc. e</t>
         </is>
       </c>
-      <c r="D21" s="69" t="inlineStr">
+      <c r="D21" s="73" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-siracusa-avviso-manifestazione-interesse-fornitura-applicativo-extracontabile-gestione-progetti-ecc-applicativo-gestione-ed-elaborazione-informatizzata-paghe</t>
         </is>
       </c>
-      <c r="E21" s="68" t="inlineStr"/>
-      <c r="F21" s="68" t="inlineStr"/>
-      <c r="G21" s="68" t="inlineStr"/>
+      <c r="E21" s="72" t="inlineStr"/>
+      <c r="F21" s="72" t="inlineStr"/>
+      <c r="G21" s="72" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="70" t="inlineStr">
+      <c r="A22" s="74" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B22" s="70" t="inlineStr">
+      <c r="B22" s="74" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1439,30 +1451,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile sito nel Comune di Capo D'Orlando, Via Trazzera MarinaScade il:25/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D22" s="71" t="inlineStr">
+      <c r="D22" s="75" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-sito-nel-comune-capo-d-orlando-trazzera-marina</t>
         </is>
       </c>
-      <c r="E22" s="70" t="inlineStr">
+      <c r="E22" s="74" t="inlineStr">
         <is>
           <t>25/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F22" s="70" t="inlineStr">
+      <c r="F22" s="74" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="G22" s="70" t="inlineStr"/>
+      <c r="G22" s="74" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="68" t="inlineStr">
+      <c r="A23" s="72" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B23" s="68" t="inlineStr">
+      <c r="B23" s="72" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1472,22 +1484,22 @@
           <t xml:space="preserve">Avvisi pubbliciST CATANIA - Programma Regionale FESR Sicilia 2021-2027 - Azione 2.4.4 - “Interventi per la riduzione del rischio incendi” - AVVISO DI </t>
         </is>
       </c>
-      <c r="D23" s="69" t="inlineStr">
+      <c r="D23" s="73" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-catania-programma-regionale-fesr-sicilia-2021-2027-azione-244-interventi-riduzione-rischio-incendi-avviso-indagine-mercato</t>
         </is>
       </c>
-      <c r="E23" s="68" t="inlineStr"/>
-      <c r="F23" s="68" t="inlineStr"/>
-      <c r="G23" s="68" t="inlineStr"/>
+      <c r="E23" s="72" t="inlineStr"/>
+      <c r="F23" s="72" t="inlineStr"/>
+      <c r="G23" s="72" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="70" t="inlineStr">
+      <c r="A24" s="74" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B24" s="70" t="inlineStr">
+      <c r="B24" s="74" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1497,22 +1509,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per ROMICS – Primavera 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D24" s="71" t="inlineStr">
+      <c r="D24" s="75" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-romics-primavera-2026/</t>
         </is>
       </c>
-      <c r="E24" s="70" t="inlineStr"/>
-      <c r="F24" s="70" t="inlineStr"/>
-      <c r="G24" s="70" t="inlineStr"/>
+      <c r="E24" s="74" t="inlineStr"/>
+      <c r="F24" s="74" t="inlineStr"/>
+      <c r="G24" s="74" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="68" t="inlineStr">
+      <c r="A25" s="72" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B25" s="68" t="inlineStr">
+      <c r="B25" s="72" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1522,22 +1534,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Cinema International 2026 – I edizioneApertoFESR</t>
         </is>
       </c>
-      <c r="D25" s="69" t="inlineStr">
+      <c r="D25" s="73" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lazio-cinema-international-2026-i-edizione/</t>
         </is>
       </c>
-      <c r="E25" s="68" t="inlineStr"/>
-      <c r="F25" s="68" t="inlineStr"/>
-      <c r="G25" s="68" t="inlineStr"/>
+      <c r="E25" s="72" t="inlineStr"/>
+      <c r="F25" s="72" t="inlineStr"/>
+      <c r="G25" s="72" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="70" t="inlineStr">
+      <c r="A26" s="74" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B26" s="70" t="inlineStr">
+      <c r="B26" s="74" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1547,22 +1559,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEManifestazioni di interesse alla costituzione di due nuove Fondazioni I.T.S. AcademyApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D26" s="71" t="inlineStr">
+      <c r="D26" s="75" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazioni-di-interesse-alla-costituzione-di-due-nuove-fondazioni-i-t-s-academy/</t>
         </is>
       </c>
-      <c r="E26" s="70" t="inlineStr"/>
-      <c r="F26" s="70" t="inlineStr"/>
-      <c r="G26" s="70" t="inlineStr"/>
+      <c r="E26" s="74" t="inlineStr"/>
+      <c r="F26" s="74" t="inlineStr"/>
+      <c r="G26" s="74" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="68" t="inlineStr">
+      <c r="A27" s="72" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B27" s="68" t="inlineStr">
+      <c r="B27" s="72" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1572,22 +1584,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURAContributi per sostenere la ripresa del settore della pescaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D27" s="69" t="inlineStr">
+      <c r="D27" s="73" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributi-per-sostenere-la-ripresa-del-settore-della-pesca/</t>
         </is>
       </c>
-      <c r="E27" s="68" t="inlineStr"/>
-      <c r="F27" s="68" t="inlineStr"/>
-      <c r="G27" s="68" t="inlineStr"/>
+      <c r="E27" s="72" t="inlineStr"/>
+      <c r="F27" s="72" t="inlineStr"/>
+      <c r="G27" s="72" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="70" t="inlineStr">
+      <c r="A28" s="74" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B28" s="70" t="inlineStr">
+      <c r="B28" s="74" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1597,30 +1609,30 @@
           <t>Manifestazioni di interesseAVVISO - Manifestazione Interesse “Storytelling aziendale” Expo Wild Natura - Caccia - Pesca. Misterbianco (CT), 10-12 apri</t>
         </is>
       </c>
-      <c r="D28" s="71" t="inlineStr">
+      <c r="D28" s="75" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-storytelling-aziendale-expo-wild-natura-caccia-pesca-misterbianco-ct-10-12-aprile-2026</t>
         </is>
       </c>
-      <c r="E28" s="70" t="inlineStr">
+      <c r="E28" s="74" t="inlineStr">
         <is>
           <t>30/03/2026 - 13:00</t>
         </is>
       </c>
-      <c r="F28" s="70" t="inlineStr">
+      <c r="F28" s="74" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G28" s="70" t="inlineStr"/>
+      <c r="G28" s="74" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="68" t="inlineStr">
+      <c r="A29" s="72" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B29" s="68" t="inlineStr">
+      <c r="B29" s="72" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1630,30 +1642,30 @@
           <t>Manifestazioni di interesseInvaso Lentini - Interventi di ripristino delle pareti esterne in cls della Torre di presa Sud e della trave d’appoggio del</t>
         </is>
       </c>
-      <c r="D29" s="69" t="inlineStr">
+      <c r="D29" s="73" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/invaso-lentini-interventi-ripristino-pareti-esterne-cls-torre-presa-sud-trave-d-appoggio-cavalcavia-collegamento-alla-stessa-torre</t>
         </is>
       </c>
-      <c r="E29" s="68" t="inlineStr">
+      <c r="E29" s="72" t="inlineStr">
         <is>
           <t>19/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F29" s="68" t="inlineStr">
+      <c r="F29" s="72" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G29" s="68" t="inlineStr"/>
+      <c r="G29" s="72" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="70" t="inlineStr">
+      <c r="A30" s="74" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="B30" s="70" t="inlineStr">
+      <c r="B30" s="74" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1663,22 +1675,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURARistrutturazione e riconversione vigneti – campagna 2026-2027ApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D30" s="71" t="inlineStr">
+      <c r="D30" s="75" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/ristrutturazione-e-riconversione-vigneti-campagna-2026-2027/</t>
         </is>
       </c>
-      <c r="E30" s="70" t="inlineStr"/>
-      <c r="F30" s="70" t="inlineStr"/>
-      <c r="G30" s="70" t="inlineStr"/>
+      <c r="E30" s="74" t="inlineStr"/>
+      <c r="F30" s="74" t="inlineStr"/>
+      <c r="G30" s="74" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="68" t="inlineStr">
+      <c r="A31" s="72" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="B31" s="68" t="inlineStr">
+      <c r="B31" s="72" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1688,30 +1700,30 @@
           <t>Manifestazioni di interessePR FESR 2021/27 Azione 1.3.3 e del POC 2014/20 - Azione 1.3.1  - Avviso a manifestazione d’interesse eventi fieristici inte</t>
         </is>
       </c>
-      <c r="D31" s="69" t="inlineStr">
+      <c r="D31" s="73" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-d-interesse-eventi-fieristici-internazionali-marzo-dicembre-2026</t>
         </is>
       </c>
-      <c r="E31" s="68" t="inlineStr">
+      <c r="E31" s="72" t="inlineStr">
         <is>
           <t>30/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F31" s="68" t="inlineStr">
+      <c r="F31" s="72" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="G31" s="68" t="inlineStr"/>
+      <c r="G31" s="72" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="70" t="inlineStr">
+      <c r="A32" s="74" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="B32" s="70" t="inlineStr">
+      <c r="B32" s="74" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1721,22 +1733,22 @@
           <t>INTERNAZIONALIZZAZIONEL’Ecosistema dell’Innovazione a INNOVIT – Focus S3ApertoFESR</t>
         </is>
       </c>
-      <c r="D32" s="71" t="inlineStr">
+      <c r="D32" s="75" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lecosistema-dellinnovazione-a-innovit-focus-s3/</t>
         </is>
       </c>
-      <c r="E32" s="70" t="inlineStr"/>
-      <c r="F32" s="70" t="inlineStr"/>
-      <c r="G32" s="70" t="inlineStr"/>
+      <c r="E32" s="74" t="inlineStr"/>
+      <c r="F32" s="74" t="inlineStr"/>
+      <c r="G32" s="74" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="68" t="inlineStr">
+      <c r="A33" s="72" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="B33" s="68" t="inlineStr">
+      <c r="B33" s="72" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1746,22 +1758,22 @@
           <t>Manifestazioni di interessePR FESR SICILIA 2021/27 - NUOVO Avviso a manifestazione d’interesse per esperti valutatoriScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D33" s="69" t="inlineStr">
+      <c r="D33" s="73" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/pr-fesr-sicilia-202127-nuovo-avviso-manifestazione-d-interesse-esperti-valutatori</t>
         </is>
       </c>
-      <c r="E33" s="68" t="inlineStr"/>
-      <c r="F33" s="68" t="inlineStr"/>
-      <c r="G33" s="68" t="inlineStr"/>
+      <c r="E33" s="72" t="inlineStr"/>
+      <c r="F33" s="72" t="inlineStr"/>
+      <c r="G33" s="72" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="70" t="inlineStr">
+      <c r="A34" s="74" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="B34" s="70" t="inlineStr">
+      <c r="B34" s="74" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -1771,22 +1783,22 @@
           <t>Bando 2026 per contributi dedicati alla manutenzione della rete dei percorsi escursionistici</t>
         </is>
       </c>
-      <c r="D34" s="71" t="inlineStr">
+      <c r="D34" s="75" t="inlineStr">
         <is>
           <t>https://ambiente.regione.emilia-romagna.it/it/parchi-natura2000/bandi/bando-2026-per-contributi-dedicati-alla-manutenzione-della-rete-dei-percorsi-escursionistici</t>
         </is>
       </c>
-      <c r="E34" s="70" t="inlineStr"/>
-      <c r="F34" s="70" t="inlineStr"/>
-      <c r="G34" s="70" t="inlineStr"/>
+      <c r="E34" s="74" t="inlineStr"/>
+      <c r="F34" s="74" t="inlineStr"/>
+      <c r="G34" s="74" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="68" t="inlineStr">
+      <c r="A35" s="72" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="B35" s="68" t="inlineStr">
+      <c r="B35" s="72" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1796,22 +1808,22 @@
           <t>Programma regionale in favore delle tradizioni storiche, artistiche, religiose e popolari (2026) – manifestazioni d’interesseApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D35" s="69" t="inlineStr">
+      <c r="D35" s="73" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/programma-regionale-in-favore-delle-tradizioni-storiche-artistiche-religiose-e-popolari-2026-manifestazioni-dinteresse/</t>
         </is>
       </c>
-      <c r="E35" s="68" t="inlineStr"/>
-      <c r="F35" s="68" t="inlineStr"/>
-      <c r="G35" s="68" t="inlineStr"/>
+      <c r="E35" s="72" t="inlineStr"/>
+      <c r="F35" s="72" t="inlineStr"/>
+      <c r="G35" s="72" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="70" t="inlineStr">
+      <c r="A36" s="74" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B36" s="70" t="inlineStr">
+      <c r="B36" s="74" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1821,22 +1833,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEBuoni servizio per le persone non autosufficienti nel territorio del LazioProssima AperturaFSE / FSE+</t>
         </is>
       </c>
-      <c r="D36" s="71" t="inlineStr">
+      <c r="D36" s="75" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/buoni-servizio-per-le-persone-non-autosufficienti-nel-territorio-del-lazio/</t>
         </is>
       </c>
-      <c r="E36" s="70" t="inlineStr"/>
-      <c r="F36" s="70" t="inlineStr"/>
-      <c r="G36" s="70" t="inlineStr"/>
+      <c r="E36" s="74" t="inlineStr"/>
+      <c r="F36" s="74" t="inlineStr"/>
+      <c r="G36" s="74" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="68" t="inlineStr">
+      <c r="A37" s="72" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B37" s="68" t="inlineStr">
+      <c r="B37" s="72" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1846,22 +1858,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONERimborso delle rette dei servizi educativi nel territorio del LazioProssima AperturaFSE / FSE+</t>
         </is>
       </c>
-      <c r="D37" s="69" t="inlineStr">
+      <c r="D37" s="73" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/rimborso-delle-rette-dei-servizi-educativi-nel-territorio-del-lazio/</t>
         </is>
       </c>
-      <c r="E37" s="68" t="inlineStr"/>
-      <c r="F37" s="68" t="inlineStr"/>
-      <c r="G37" s="68" t="inlineStr"/>
+      <c r="E37" s="72" t="inlineStr"/>
+      <c r="F37" s="72" t="inlineStr"/>
+      <c r="G37" s="72" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="70" t="inlineStr">
+      <c r="A38" s="74" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B38" s="70" t="inlineStr">
+      <c r="B38" s="74" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1871,30 +1883,30 @@
           <t>Manifestazioni di interesseATTO DI INTERPELLO PER L’AFFIDAMENTO DELL’INCARICO DI COLLAUDO STATICO DELLE STRUTTURE - Diga di Pietrarossa (Progetto ex C</t>
         </is>
       </c>
-      <c r="D38" s="71" t="inlineStr">
+      <c r="D38" s="75" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/atto-interpello-l-affidamento-incarico-collaudo-statico-strutture-diga-pietrarossa-progetto-ex-casmez-303219</t>
         </is>
       </c>
-      <c r="E38" s="70" t="inlineStr">
+      <c r="E38" s="74" t="inlineStr">
         <is>
           <t>27/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F38" s="70" t="inlineStr">
+      <c r="F38" s="74" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="G38" s="70" t="inlineStr"/>
+      <c r="G38" s="74" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="68" t="inlineStr">
+      <c r="A39" s="72" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B39" s="68" t="inlineStr">
+      <c r="B39" s="72" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1904,30 +1916,30 @@
           <t>Manifestazioni di interesseAvviso alle Case  Editrici della Regione siciliana per la partecipazione al Salone del Libro di Torino, 14-18  maggio 2026.</t>
         </is>
       </c>
-      <c r="D39" s="69" t="inlineStr">
+      <c r="D39" s="73" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/manifestazione-d-interesse-partecipare-al-xxxviii-salone-libro-torino-14-al-18-maggio-2026-attraverso-l-esposizione-pubblicazioni-presso-stand-assessorato-beni</t>
         </is>
       </c>
-      <c r="E39" s="68" t="inlineStr">
+      <c r="E39" s="72" t="inlineStr">
         <is>
           <t>30/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F39" s="68" t="inlineStr">
+      <c r="F39" s="72" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="G39" s="68" t="inlineStr"/>
+      <c r="G39" s="72" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="70" t="inlineStr">
+      <c r="A40" s="74" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B40" s="70" t="inlineStr">
+      <c r="B40" s="74" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1937,30 +1949,30 @@
           <t xml:space="preserve">Manifestazioni di interessePR FESR SICILIA 2021/27 - NUOVO Avviso a manifestazione d’interesse per esperti valutatoriScade il:06/04/2026 - 23:59Leggi </t>
         </is>
       </c>
-      <c r="D40" s="71" t="inlineStr">
+      <c r="D40" s="75" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/pr-fesr-sicilia-202127-nuovo-avviso-manifestazione-d-interesse-esperti-valutatori</t>
         </is>
       </c>
-      <c r="E40" s="70" t="inlineStr">
+      <c r="E40" s="74" t="inlineStr">
         <is>
           <t>06/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F40" s="70" t="inlineStr">
+      <c r="F40" s="74" t="inlineStr">
         <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="G40" s="70" t="inlineStr"/>
+      <c r="G40" s="74" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="68" t="inlineStr">
+      <c r="A41" s="72" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B41" s="68" t="inlineStr">
+      <c r="B41" s="72" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1970,22 +1982,22 @@
           <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D41" s="69" t="inlineStr">
+      <c r="D41" s="73" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
         </is>
       </c>
-      <c r="E41" s="68" t="inlineStr"/>
-      <c r="F41" s="68" t="inlineStr"/>
-      <c r="G41" s="68" t="inlineStr"/>
+      <c r="E41" s="72" t="inlineStr"/>
+      <c r="F41" s="72" t="inlineStr"/>
+      <c r="G41" s="72" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="70" t="inlineStr">
+      <c r="A42" s="74" t="inlineStr">
         <is>
           <t>24/03/2026</t>
         </is>
       </c>
-      <c r="B42" s="70" t="inlineStr">
+      <c r="B42" s="74" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -1995,22 +2007,22 @@
           <t>GAL del Ducato - Promozione di fiere agroalimentari e delle filiere del cibo – Bando per Enti pubblici (DU AS 05B)</t>
         </is>
       </c>
-      <c r="D42" s="71" t="inlineStr">
+      <c r="D42" s="75" t="inlineStr">
         <is>
           <t>https://agricoltura.regione.emilia-romagna.it/sviluppo-rurale-23-27/opportunita/bandi-gal/2026/du_as05b-promozione-di-fiere-agroalimentari-e-delle-filiere-del-cibo-bando-per-enti-pubblici</t>
         </is>
       </c>
-      <c r="E42" s="70" t="inlineStr"/>
-      <c r="F42" s="70" t="inlineStr"/>
-      <c r="G42" s="70" t="inlineStr"/>
+      <c r="E42" s="74" t="inlineStr"/>
+      <c r="F42" s="74" t="inlineStr"/>
+      <c r="G42" s="74" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="68" t="inlineStr">
+      <c r="A43" s="72" t="inlineStr">
         <is>
           <t>24/03/2026</t>
         </is>
       </c>
-      <c r="B43" s="68" t="inlineStr">
+      <c r="B43" s="72" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2020,30 +2032,30 @@
           <t>Manifestazioni di interesseAVVISO PUBBLICO PER MANIFESTAZIONE DI INTERESSE FINALIZZATA ALL'ASSEGNAZIONE DI SPAZI ESPOSITIVI (CORNER GRATUITI) ALL'INTE</t>
         </is>
       </c>
-      <c r="D43" s="69" t="inlineStr">
+      <c r="D43" s="73" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-manifestazione-interesse-finalizzata-all-assegnazione-spazi-espositivi-corner-gratuiti-all-interno-stand-istituzionale-dsrt-manifestazione</t>
         </is>
       </c>
-      <c r="E43" s="68" t="inlineStr">
+      <c r="E43" s="72" t="inlineStr">
         <is>
           <t>30/03/2026 - 13:00</t>
         </is>
       </c>
-      <c r="F43" s="68" t="inlineStr">
+      <c r="F43" s="72" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G43" s="68" t="inlineStr"/>
+      <c r="G43" s="72" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="70" t="inlineStr">
+      <c r="A44" s="74" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B44" s="70" t="inlineStr">
+      <c r="B44" s="74" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2053,22 +2065,22 @@
           <t>Avviso per la concessione di contributi per eventi sportivi realizzati in Emilia-Romagna - Anno 2026</t>
         </is>
       </c>
-      <c r="D44" s="71" t="inlineStr">
+      <c r="D44" s="75" t="inlineStr">
         <is>
           <t>https://www.regione.emilia-romagna.it/sport/bandi/2026/bando-2026</t>
         </is>
       </c>
-      <c r="E44" s="70" t="inlineStr"/>
-      <c r="F44" s="70" t="inlineStr"/>
-      <c r="G44" s="70" t="inlineStr"/>
+      <c r="E44" s="74" t="inlineStr"/>
+      <c r="F44" s="74" t="inlineStr"/>
+      <c r="G44" s="74" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="68" t="inlineStr">
+      <c r="A45" s="72" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B45" s="68" t="inlineStr">
+      <c r="B45" s="72" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2078,22 +2090,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Street art 2026Prossima AperturaBandi Regionali</t>
         </is>
       </c>
-      <c r="D45" s="69" t="inlineStr">
+      <c r="D45" s="73" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lazio-street-art-2026/</t>
         </is>
       </c>
-      <c r="E45" s="68" t="inlineStr"/>
-      <c r="F45" s="68" t="inlineStr"/>
-      <c r="G45" s="68" t="inlineStr"/>
+      <c r="E45" s="72" t="inlineStr"/>
+      <c r="F45" s="72" t="inlineStr"/>
+      <c r="G45" s="72" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="70" t="inlineStr">
+      <c r="A46" s="74" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B46" s="70" t="inlineStr">
+      <c r="B46" s="74" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2103,30 +2115,30 @@
           <t>Manifestazioni di interesseManifestazione di interesse per la partecipazione all’evento “R2I Italy 2026” – Bologna, 12-13/05/2026Scade il:03/04/2026 -</t>
         </is>
       </c>
-      <c r="D46" s="71" t="inlineStr">
+      <c r="D46" s="75" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/manifestazione-interesse-partecipazione-all-evento-r2i-italy-2026-bologna-12-13052026</t>
         </is>
       </c>
-      <c r="E46" s="70" t="inlineStr">
+      <c r="E46" s="74" t="inlineStr">
         <is>
           <t>03/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F46" s="70" t="inlineStr">
+      <c r="F46" s="74" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="G46" s="70" t="inlineStr"/>
+      <c r="G46" s="74" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="68" t="inlineStr">
+      <c r="A47" s="72" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B47" s="68" t="inlineStr">
+      <c r="B47" s="72" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2136,30 +2148,30 @@
           <t>Manifestazioni di interesseST SIRACUSA - AVVISO PER MANIFESTAZIONE DI INTERESSE - Selezione di n. 5 unità di personale internoScade il:20/04/2026 - 12</t>
         </is>
       </c>
-      <c r="D47" s="69" t="inlineStr">
+      <c r="D47" s="73" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/24-marzo-2026-st-siracusa-avviso-manifestazione-interesse-selezione-n-5-unita-personale-interno</t>
         </is>
       </c>
-      <c r="E47" s="68" t="inlineStr">
+      <c r="E47" s="72" t="inlineStr">
         <is>
           <t>20/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F47" s="68" t="inlineStr">
+      <c r="F47" s="72" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="G47" s="68" t="inlineStr"/>
+      <c r="G47" s="72" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="70" t="inlineStr">
+      <c r="A48" s="74" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B48" s="70" t="inlineStr">
+      <c r="B48" s="74" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2169,30 +2181,30 @@
           <t>Avvisi pubbliciRevoca dell’avviso di concessione a titolo gratuito del 16.12.2025 inerente all’immobile di seguito identificato e contestuale nuovo av</t>
         </is>
       </c>
-      <c r="D48" s="71" t="inlineStr">
+      <c r="D48" s="75" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/revoca-avviso-concessione-titolo-gratuito-16122025-inerente-all-immobile-seguito-identificato-contestuale-nuovo-avviso-concessione-titolo-oneroso-stesso-sito-nel</t>
         </is>
       </c>
-      <c r="E48" s="70" t="inlineStr">
+      <c r="E48" s="74" t="inlineStr">
         <is>
           <t>08/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F48" s="70" t="inlineStr">
+      <c r="F48" s="74" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="G48" s="70" t="inlineStr"/>
+      <c r="G48" s="74" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="68" t="inlineStr">
+      <c r="A49" s="72" t="inlineStr">
         <is>
           <t>26/03/2026</t>
         </is>
       </c>
-      <c r="B49" s="68" t="inlineStr">
+      <c r="B49" s="72" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2202,22 +2214,22 @@
           <t>Bando studi di fattibilità per fusioni di Comuni</t>
         </is>
       </c>
-      <c r="D49" s="69" t="inlineStr">
+      <c r="D49" s="73" t="inlineStr">
         <is>
           <t>https://www.regione.emilia-romagna.it/autonomie-locali/bandi/bando_studi_fattibilita_fusioni_comuni</t>
         </is>
       </c>
-      <c r="E49" s="68" t="inlineStr"/>
-      <c r="F49" s="68" t="inlineStr"/>
-      <c r="G49" s="68" t="inlineStr"/>
+      <c r="E49" s="72" t="inlineStr"/>
+      <c r="F49" s="72" t="inlineStr"/>
+      <c r="G49" s="72" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="70" t="inlineStr">
+      <c r="A50" s="74" t="inlineStr">
         <is>
           <t>26/03/2026</t>
         </is>
       </c>
-      <c r="B50" s="70" t="inlineStr">
+      <c r="B50" s="74" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2227,30 +2239,30 @@
           <t xml:space="preserve">Manifestazioni di interesseAvviso pubblico di selezione interna, per titoli, per il conferimento di PO e professionali, ai sensi degli artt. 19, 20 e </t>
         </is>
       </c>
-      <c r="D50" s="71" t="inlineStr">
+      <c r="D50" s="75" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-selezione-interna-titoli-conferimento-po-professionali-ai-sensi-artt-19-20-21-ccrl-20222024-comparto-non-dirigenziale</t>
         </is>
       </c>
-      <c r="E50" s="70" t="inlineStr">
+      <c r="E50" s="74" t="inlineStr">
         <is>
           <t>30/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F50" s="70" t="inlineStr">
+      <c r="F50" s="74" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G50" s="70" t="inlineStr"/>
+      <c r="G50" s="74" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="68" t="inlineStr">
+      <c r="A51" s="72" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="B51" s="68" t="inlineStr">
+      <c r="B51" s="72" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2260,22 +2272,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0PRE-SEED 3.0ApertoFESR</t>
         </is>
       </c>
-      <c r="D51" s="69" t="inlineStr">
+      <c r="D51" s="73" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/pre-seed-3-0/</t>
         </is>
       </c>
-      <c r="E51" s="68" t="inlineStr"/>
-      <c r="F51" s="68" t="inlineStr"/>
-      <c r="G51" s="68" t="inlineStr"/>
+      <c r="E51" s="72" t="inlineStr"/>
+      <c r="F51" s="72" t="inlineStr"/>
+      <c r="G51" s="72" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="70" t="inlineStr">
+      <c r="A52" s="74" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B52" s="70" t="inlineStr">
+      <c r="B52" s="74" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2285,30 +2297,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “So</t>
         </is>
       </c>
-      <c r="D52" s="71" t="inlineStr">
+      <c r="D52" s="75" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-termini-imerese-locta-piazza-marina</t>
         </is>
       </c>
-      <c r="E52" s="70" t="inlineStr">
+      <c r="E52" s="74" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F52" s="70" t="inlineStr">
+      <c r="F52" s="74" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G52" s="70" t="inlineStr"/>
+      <c r="G52" s="74" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="68" t="inlineStr">
+      <c r="A53" s="72" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B53" s="68" t="inlineStr">
+      <c r="B53" s="72" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2318,30 +2330,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, Sig</t>
         </is>
       </c>
-      <c r="D53" s="69" t="inlineStr">
+      <c r="D53" s="73" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-porto-empedocle-locta-punta-piccola</t>
         </is>
       </c>
-      <c r="E53" s="68" t="inlineStr">
+      <c r="E53" s="72" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F53" s="68" t="inlineStr">
+      <c r="F53" s="72" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G53" s="68" t="inlineStr"/>
+      <c r="G53" s="72" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="70" t="inlineStr">
+      <c r="A54" s="74" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B54" s="70" t="inlineStr">
+      <c r="B54" s="74" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2351,30 +2363,30 @@
           <t xml:space="preserve">Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “Società </t>
         </is>
       </c>
-      <c r="D54" s="71" t="inlineStr">
+      <c r="D54" s="75" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-messina-locta-torrente-bordonaro</t>
         </is>
       </c>
-      <c r="E54" s="70" t="inlineStr">
+      <c r="E54" s="74" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F54" s="70" t="inlineStr">
+      <c r="F54" s="74" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G54" s="70" t="inlineStr"/>
+      <c r="G54" s="74" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="68" t="inlineStr">
+      <c r="A55" s="72" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B55" s="68" t="inlineStr">
+      <c r="B55" s="72" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2384,30 +2396,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “Condomin</t>
         </is>
       </c>
-      <c r="D55" s="69" t="inlineStr">
+      <c r="D55" s="73" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-mascali-spiaggia-n-144150</t>
         </is>
       </c>
-      <c r="E55" s="68" t="inlineStr">
+      <c r="E55" s="72" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F55" s="68" t="inlineStr">
+      <c r="F55" s="72" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G55" s="68" t="inlineStr"/>
+      <c r="G55" s="72" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="70" t="inlineStr">
+      <c r="A56" s="74" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B56" s="70" t="inlineStr">
+      <c r="B56" s="74" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2417,30 +2429,30 @@
           <t xml:space="preserve">Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione sito nel Comune di Lipari, isola di Stromboli, </t>
         </is>
       </c>
-      <c r="D56" s="71" t="inlineStr">
+      <c r="D56" s="75" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-lipari-isola-stromboli-locta-fico-grande</t>
         </is>
       </c>
-      <c r="E56" s="70" t="inlineStr">
+      <c r="E56" s="74" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F56" s="70" t="inlineStr">
+      <c r="F56" s="74" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G56" s="70" t="inlineStr"/>
+      <c r="G56" s="74" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="68" t="inlineStr">
+      <c r="A57" s="72" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B57" s="68" t="inlineStr">
+      <c r="B57" s="72" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2450,30 +2462,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione sito nel Comune di Favignana, isola di Le</t>
         </is>
       </c>
-      <c r="D57" s="69" t="inlineStr">
+      <c r="D57" s="73" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-favignana-isola-levanzo</t>
         </is>
       </c>
-      <c r="E57" s="68" t="inlineStr">
+      <c r="E57" s="72" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F57" s="68" t="inlineStr">
+      <c r="F57" s="72" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G57" s="68" t="inlineStr"/>
+      <c r="G57" s="72" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="70" t="inlineStr">
+      <c r="A58" s="74" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="B58" s="70" t="inlineStr">
+      <c r="B58" s="74" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2483,30 +2495,30 @@
           <t>Manifestazioni di interesseAVVISO - Manifestazione d’interesse finalizzata alla selezione di organismi attuatori di piani di gestione locale della pic</t>
         </is>
       </c>
-      <c r="D58" s="71" t="inlineStr">
+      <c r="D58" s="75" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-d-interesse-finalizzata-alla-selezione-organismi-attuatori-piani-gestione-locale-piccola-pesca-costiera-nelle-gsa-regione-siciliana</t>
         </is>
       </c>
-      <c r="E58" s="70" t="inlineStr">
+      <c r="E58" s="74" t="inlineStr">
         <is>
           <t>29/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F58" s="70" t="inlineStr">
+      <c r="F58" s="74" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="G58" s="70" t="inlineStr"/>
+      <c r="G58" s="74" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="68" t="inlineStr">
+      <c r="A59" s="72" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="B59" s="68" t="inlineStr">
+      <c r="B59" s="72" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2516,30 +2528,30 @@
           <t>Avvisi pubbliciLeggi e scarica l'avvisoScade il:02/04/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D59" s="69" t="inlineStr">
+      <c r="D59" s="73" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/proroga-termini-presentazione-candidature-po</t>
         </is>
       </c>
-      <c r="E59" s="68" t="inlineStr">
+      <c r="E59" s="72" t="inlineStr">
         <is>
           <t>02/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F59" s="68" t="inlineStr">
+      <c r="F59" s="72" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="G59" s="68" t="inlineStr"/>
+      <c r="G59" s="72" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="70" t="inlineStr">
+      <c r="A60" s="74" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="70" t="inlineStr">
+      <c r="B60" s="74" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2549,22 +2561,22 @@
           <t>INTERNAZIONALIZZAZIONESMAU – Italy RestartsUp in STOCCOLMAApertoFESR</t>
         </is>
       </c>
-      <c r="D60" s="71" t="inlineStr">
+      <c r="D60" s="75" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/smau-italy-restartsup-in-stoccolma/</t>
         </is>
       </c>
-      <c r="E60" s="70" t="inlineStr"/>
-      <c r="F60" s="70" t="inlineStr"/>
-      <c r="G60" s="70" t="inlineStr"/>
+      <c r="E60" s="74" t="inlineStr"/>
+      <c r="F60" s="74" t="inlineStr"/>
+      <c r="G60" s="74" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="68" t="inlineStr">
+      <c r="A61" s="72" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B61" s="68" t="inlineStr">
+      <c r="B61" s="72" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2574,22 +2586,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per Farnborough International AirshowApertoFESR</t>
         </is>
       </c>
-      <c r="D61" s="69" t="inlineStr">
+      <c r="D61" s="73" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-farnborough-international-airshow-2/</t>
         </is>
       </c>
-      <c r="E61" s="68" t="inlineStr"/>
-      <c r="F61" s="68" t="inlineStr"/>
-      <c r="G61" s="68" t="inlineStr"/>
+      <c r="E61" s="72" t="inlineStr"/>
+      <c r="F61" s="72" t="inlineStr"/>
+      <c r="G61" s="72" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="70" t="inlineStr">
+      <c r="A62" s="74" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="70" t="inlineStr">
+      <c r="B62" s="74" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2599,30 +2611,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA - alienazione lotto di terreno sito nel comune di Termini Imerese, via LibertàScade il:30/04/2026 - 12:00Leg</t>
         </is>
       </c>
-      <c r="D62" s="71" t="inlineStr">
+      <c r="D62" s="75" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proprieta-regionale-sito-nel-comune-termini-imerese-favore-ares-fabiola</t>
         </is>
       </c>
-      <c r="E62" s="70" t="inlineStr">
+      <c r="E62" s="74" t="inlineStr">
         <is>
           <t>30/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F62" s="70" t="inlineStr">
+      <c r="F62" s="74" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="G62" s="70" t="inlineStr"/>
+      <c r="G62" s="74" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="68" t="inlineStr">
+      <c r="A63" s="72" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B63" s="68" t="inlineStr">
+      <c r="B63" s="72" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2632,22 +2644,22 @@
           <t>Avviso per la concessione di contributi per progetti di contrasto all'abbandono sportivo giovanile (2026)</t>
         </is>
       </c>
-      <c r="D63" s="69" t="inlineStr">
+      <c r="D63" s="73" t="inlineStr">
         <is>
           <t>https://www.regione.emilia-romagna.it/sport/bandi/2026/contrasto-abbandono-2026</t>
         </is>
       </c>
-      <c r="E63" s="68" t="inlineStr"/>
-      <c r="F63" s="68" t="inlineStr"/>
-      <c r="G63" s="68" t="inlineStr"/>
+      <c r="E63" s="72" t="inlineStr"/>
+      <c r="F63" s="72" t="inlineStr"/>
+      <c r="G63" s="72" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="70" t="inlineStr">
+      <c r="A64" s="74" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="70" t="inlineStr">
+      <c r="B64" s="74" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2657,30 +2669,30 @@
           <t>Avvisi pubbliciAvviso si procede alla riassegnazione della posizione organizzativa a supporto delle attività del Servizio 2 “Investimenti in Agricoltu</t>
         </is>
       </c>
-      <c r="D64" s="71" t="inlineStr">
+      <c r="D64" s="75" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-selezione-interna-conferimento-1-posizione-organizzativa-ai-sensi-artt-19-20-ccrl-2022-2024-comparto-non-dirigenziale</t>
         </is>
       </c>
-      <c r="E64" s="70" t="inlineStr">
+      <c r="E64" s="74" t="inlineStr">
         <is>
           <t>09/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F64" s="70" t="inlineStr">
+      <c r="F64" s="74" t="inlineStr">
         <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="G64" s="70" t="inlineStr"/>
+      <c r="G64" s="74" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="68" t="inlineStr">
+      <c r="A65" s="72" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B65" s="68" t="inlineStr">
+      <c r="B65" s="72" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2690,30 +2702,30 @@
           <t>Avvisi pubbliciST-MESSINA - AVVISO di INDAGINE DI MERCATO per affidamento "Interventi manutenzione straordinaria della strada/pista forestale "Annunzi</t>
         </is>
       </c>
-      <c r="D65" s="69" t="inlineStr">
+      <c r="D65" s="73" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-indagine-mercato-affidamento-interventi-manutenzione-straordinaria-stradapista-forestale-annunziata-comune-messina</t>
         </is>
       </c>
-      <c r="E65" s="68" t="inlineStr">
+      <c r="E65" s="72" t="inlineStr">
         <is>
           <t>16/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F65" s="68" t="inlineStr">
+      <c r="F65" s="72" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="G65" s="68" t="inlineStr"/>
+      <c r="G65" s="72" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="70" t="inlineStr">
+      <c r="A66" s="74" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="70" t="inlineStr">
+      <c r="B66" s="74" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2723,30 +2735,30 @@
           <t>Avvisi pubbliciST-MESSINA - AVVISO DI INDAGINE DI MERCATO per affidamento "Interventi manutenzione straordinaria della strada/pista forestale "San Riz</t>
         </is>
       </c>
-      <c r="D66" s="71" t="inlineStr">
+      <c r="D66" s="75" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-indagine-mercato-affidamento-interventi-manutenzione-straordinaria-stradapista-forestale-san-rizzo-san-leone-crupi-madonuzza-comune-messina</t>
         </is>
       </c>
-      <c r="E66" s="70" t="inlineStr">
+      <c r="E66" s="74" t="inlineStr">
         <is>
           <t>16/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F66" s="70" t="inlineStr">
+      <c r="F66" s="74" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="G66" s="70" t="inlineStr"/>
+      <c r="G66" s="74" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="68" t="inlineStr">
+      <c r="A67" s="72" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="68" t="inlineStr">
+      <c r="B67" s="72" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2756,22 +2768,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Manifestazione di interesse per Casaidea 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D67" s="69" t="inlineStr">
+      <c r="D67" s="73" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-casaidea-2026/</t>
         </is>
       </c>
-      <c r="E67" s="68" t="inlineStr"/>
-      <c r="F67" s="68" t="inlineStr"/>
-      <c r="G67" s="68" t="inlineStr"/>
+      <c r="E67" s="72" t="inlineStr"/>
+      <c r="F67" s="72" t="inlineStr"/>
+      <c r="G67" s="72" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="70" t="inlineStr">
+      <c r="A68" s="74" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="70" t="inlineStr">
+      <c r="B68" s="74" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2781,22 +2793,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per il Salone Internazionale del Libro di Torino 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D68" s="71" t="inlineStr">
+      <c r="D68" s="75" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-il-salone-internazionale-del-libro-di-torino-2026/</t>
         </is>
       </c>
-      <c r="E68" s="70" t="inlineStr"/>
-      <c r="F68" s="70" t="inlineStr"/>
-      <c r="G68" s="70" t="inlineStr"/>
+      <c r="E68" s="74" t="inlineStr"/>
+      <c r="F68" s="74" t="inlineStr"/>
+      <c r="G68" s="74" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="68" t="inlineStr">
+      <c r="A69" s="72" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="68" t="inlineStr">
+      <c r="B69" s="72" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2806,30 +2818,30 @@
           <t>Avvisi pubbliciDDG 1112 del 02.04.2026 - Aggiornamento Avviso pubblico n. 4/2024 per l’attuazione del PAR GOL Sicilia da finanziare nell’ambito del Pi</t>
         </is>
       </c>
-      <c r="D69" s="69" t="inlineStr">
+      <c r="D69" s="73" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/ddg-1112-02042026-aggiornamento-avviso-pubblico-n-42024-l-attuazione-par-gol-sicilia-finanziare-nell-ambito-piano-nazionale-ripresa-resilienza-pnrr</t>
         </is>
       </c>
-      <c r="E69" s="68" t="inlineStr">
+      <c r="E69" s="72" t="inlineStr">
         <is>
           <t>05/04/2030 - 00:00</t>
         </is>
       </c>
-      <c r="F69" s="68" t="inlineStr">
+      <c r="F69" s="72" t="inlineStr">
         <is>
           <t>05/04/2030</t>
         </is>
       </c>
-      <c r="G69" s="68" t="inlineStr"/>
+      <c r="G69" s="72" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="70" t="inlineStr">
+      <c r="A70" s="74" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="70" t="inlineStr">
+      <c r="B70" s="74" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2839,30 +2851,30 @@
           <t>Avvisi pubbliciDDG 1113 del  02.04.2026 - Aggiornamento Avviso pubblico n. 2/2022 e s.m.i per l’attuazione del PAR GOL Sicilia da finanziare nell’ambi</t>
         </is>
       </c>
-      <c r="D70" s="71" t="inlineStr">
+      <c r="D70" s="75" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/ddg-1113-02042026-aggiornamento-avviso-pubblico-n-22022-smi-l-attuazione-par-gol-sicilia-finanziare-nell-ambito-piano-nazionale-ripresa-resilienza-pnrr</t>
         </is>
       </c>
-      <c r="E70" s="70" t="inlineStr">
+      <c r="E70" s="74" t="inlineStr">
         <is>
           <t>03/04/2030 - 00:00</t>
         </is>
       </c>
-      <c r="F70" s="70" t="inlineStr">
+      <c r="F70" s="74" t="inlineStr">
         <is>
           <t>03/04/2030</t>
         </is>
       </c>
-      <c r="G70" s="70" t="inlineStr"/>
+      <c r="G70" s="74" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="68" t="inlineStr">
+      <c r="A71" s="72" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B71" s="68" t="inlineStr">
+      <c r="B71" s="72" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2872,14 +2884,14 @@
           <t>Avvisi pubbliciLeggi e scarica l'avvisoScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D71" s="69" t="inlineStr">
+      <c r="D71" s="73" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/proroga-termini-presentazione-candidature-po</t>
         </is>
       </c>
-      <c r="E71" s="68" t="inlineStr"/>
-      <c r="F71" s="68" t="inlineStr"/>
-      <c r="G71" s="68" t="inlineStr"/>
+      <c r="E71" s="72" t="inlineStr"/>
+      <c r="F71" s="72" t="inlineStr"/>
+      <c r="G71" s="72" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="74" t="inlineStr">
@@ -2938,6 +2950,64 @@
         </is>
       </c>
       <c r="G73" s="72" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="78" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="78" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Donne e Impresa 2026Prossima AperturaFESR</t>
+        </is>
+      </c>
+      <c r="D74" s="79" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/donne-e-impresa-2026/</t>
+        </is>
+      </c>
+      <c r="E74" s="78" t="inlineStr"/>
+      <c r="F74" s="78" t="inlineStr"/>
+      <c r="G74" s="78" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="76" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="76" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>Bandi di garaCodice Intervento 111302_FELUCHE - Investimenti a bordo e nei porti per incrementare la qualità delle produzioni e migliorare le condizio</t>
+        </is>
+      </c>
+      <c r="D75" s="77" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/bandoavviso-regia-ob-11-azione-3-codice-111302feluche-investimenti-bordo-valorizzazione-feluche-miglioramento-condizioni-lavoro-salute-sicurezza-operatori-l</t>
+        </is>
+      </c>
+      <c r="E75" s="76" t="inlineStr">
+        <is>
+          <t>02/07/2026 - 23:59</t>
+        </is>
+      </c>
+      <c r="F75" s="76" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="G75" s="76" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -3013,6 +3083,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D72" r:id="rId71"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId74"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3057,7 +3129,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="72" t="inlineStr">
+      <c r="A3" s="76" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -3070,26 +3142,26 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="74" t="inlineStr">
+      <c r="A4" s="78" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="72" t="inlineStr">
+      <c r="A5" s="76" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>1</v>

--- a/data/bandi_export.xlsx
+++ b/data/bandi_export.xlsx
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -267,6 +267,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -718,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -733,7 +745,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏛️  Nuovi Bandi — 08/04/2026 08:08</t>
+          <t>🏛️  Nuovi Bandi — 10/04/2026 08:18</t>
         </is>
       </c>
     </row>
@@ -778,55 +790,117 @@
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="76" t="inlineStr">
+      <c r="B3" s="80" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Donne e Impresa 2026Prossima AperturaFESR</t>
-        </is>
-      </c>
-      <c r="D3" s="77" t="inlineStr">
-        <is>
-          <t>https://www.lazioeuropa.it/bandi/donne-e-impresa-2026/</t>
-        </is>
-      </c>
-      <c r="E3" s="76" t="inlineStr"/>
-      <c r="F3" s="76" t="inlineStr"/>
+          <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURASostegno agli investimenti nel settore vitivinicolo – campagna 2026/2027ApertoBandi Regionali</t>
+        </is>
+      </c>
+      <c r="D3" s="81" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/sostegno-agli-investimenti-nel-settore-vitivinicolo-campagna-2026-2027/</t>
+        </is>
+      </c>
+      <c r="E3" s="80" t="inlineStr"/>
+      <c r="F3" s="80" t="inlineStr"/>
       <c r="G3" s="5" t="inlineStr"/>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="78" t="inlineStr">
+      <c r="B4" s="82" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>Bandi di garaCodice Intervento 111302_FELUCHE - Investimenti a bordo e nei porti per incrementare la qualità delle produzioni e migliorare le condizio</t>
-        </is>
-      </c>
-      <c r="D4" s="79" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/bandoavviso-regia-ob-11-azione-3-codice-111302feluche-investimenti-bordo-valorizzazione-feluche-miglioramento-condizioni-lavoro-salute-sicurezza-operatori-l</t>
-        </is>
-      </c>
-      <c r="E4" s="78" t="inlineStr">
-        <is>
-          <t>02/07/2026 - 23:59</t>
-        </is>
-      </c>
-      <c r="F4" s="78" t="inlineStr">
-        <is>
-          <t>02/07/2026</t>
+          <t>Manifestazioni di interesse9 aprile 2026 -ST PALERMO- Manifestazione di interesse - “Interventi di manutenzione straordinaria della strada-pista fores</t>
+        </is>
+      </c>
+      <c r="D4" s="83" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/9-aprile-2026-st-palermo-manifestazione-interesse-interventi-manutenzione-straordinaria-strada-pista-forestale-monte-cane-comune-caccamo-pa-distretto-forestale</t>
+        </is>
+      </c>
+      <c r="E4" s="82" t="inlineStr">
+        <is>
+          <t>24/04/2026 - 12:00</t>
+        </is>
+      </c>
+      <c r="F4" s="82" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="G4" s="9" t="inlineStr"/>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="80" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Avvisi pubbliciST-MESSINA - AVVISO DI INDAGINE DI MERCATO per affidamento "Interventi manutenzione straordinaria della strada/pista forestale "Faggita</t>
+        </is>
+      </c>
+      <c r="D5" s="81" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-indagine-mercato-affidamento-interventi-manutenzione-straordinaria-stradapista-forestale-faggita-comune-tripi-me</t>
+        </is>
+      </c>
+      <c r="E5" s="80" t="inlineStr">
+        <is>
+          <t>23/04/2026 - 12:00</t>
+        </is>
+      </c>
+      <c r="F5" s="80" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="82" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Avvisi pubbliciST-MESSINA - AVVISO DI INDAGINE DI MERCATO per affidamento "Interventi manutenzione straordinaria della strada/pista forestale "Ferraro</t>
+        </is>
+      </c>
+      <c r="D6" s="83" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-indagine-mercato-affidamento-interventi-manutenzione-straordinaria-stradapista-forestale-ferraro-sanrizzo-badiazza-comune-messina</t>
+        </is>
+      </c>
+      <c r="E6" s="82" t="inlineStr">
+        <is>
+          <t>23/04/2026 - 12:00</t>
+        </is>
+      </c>
+      <c r="F6" s="82" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -835,6 +909,8 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -846,7 +922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -896,12 +972,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="74" t="inlineStr">
+      <c r="A2" s="78" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B2" s="74" t="inlineStr">
+      <c r="B2" s="78" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -911,22 +987,22 @@
           <t>FLAG GALPA Costa E-R. Sostituzione del motore principale e dei motori secondari. Secondo bando</t>
         </is>
       </c>
-      <c r="D2" s="75" t="inlineStr">
+      <c r="D2" s="79" t="inlineStr">
         <is>
           <t>https://agricoltura.regione.emilia-romagna.it/feampa-2021-2027/bandi-galpa/2026/galpa-sostituzione-motori-secondo-bando</t>
         </is>
       </c>
-      <c r="E2" s="74" t="inlineStr"/>
-      <c r="F2" s="74" t="inlineStr"/>
-      <c r="G2" s="74" t="inlineStr"/>
+      <c r="E2" s="78" t="inlineStr"/>
+      <c r="F2" s="78" t="inlineStr"/>
+      <c r="G2" s="78" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="72" t="inlineStr">
+      <c r="A3" s="76" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B3" s="72" t="inlineStr">
+      <c r="B3" s="76" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -936,22 +1012,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0PRE-SEED 3.0Prossima AperturaFESR</t>
         </is>
       </c>
-      <c r="D3" s="73" t="inlineStr">
+      <c r="D3" s="77" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/pre-seed-3-0/</t>
         </is>
       </c>
-      <c r="E3" s="72" t="inlineStr"/>
-      <c r="F3" s="72" t="inlineStr"/>
-      <c r="G3" s="72" t="inlineStr"/>
+      <c r="E3" s="76" t="inlineStr"/>
+      <c r="F3" s="76" t="inlineStr"/>
+      <c r="G3" s="76" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="74" t="inlineStr">
+      <c r="A4" s="78" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B4" s="74" t="inlineStr">
+      <c r="B4" s="78" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -961,22 +1037,22 @@
           <t>ACCESSO AL CREDITO E ALLE GARANZIE PER LE IMPRESEContributo su finanziamenti alle imprese del Lazio erogati su provvista BEIProssima AperturaFESR</t>
         </is>
       </c>
-      <c r="D4" s="75" t="inlineStr">
+      <c r="D4" s="79" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-su-finanziamenti-alle-imprese-del-lazio-erogati-su-provvista-bei/</t>
         </is>
       </c>
-      <c r="E4" s="74" t="inlineStr"/>
-      <c r="F4" s="74" t="inlineStr"/>
-      <c r="G4" s="74" t="inlineStr"/>
+      <c r="E4" s="78" t="inlineStr"/>
+      <c r="F4" s="78" t="inlineStr"/>
+      <c r="G4" s="78" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="72" t="inlineStr">
+      <c r="A5" s="76" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B5" s="72" t="inlineStr">
+      <c r="B5" s="76" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -986,22 +1062,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEIndividuazione degli enti iscritti al Registro unico nazionale del Terzo settoreApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D5" s="73" t="inlineStr">
+      <c r="D5" s="77" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/individuazione-degli-enti-iscritti-al-registro-unico-nazionale-del-terzo-settore/</t>
         </is>
       </c>
-      <c r="E5" s="72" t="inlineStr"/>
-      <c r="F5" s="72" t="inlineStr"/>
-      <c r="G5" s="72" t="inlineStr"/>
+      <c r="E5" s="76" t="inlineStr"/>
+      <c r="F5" s="76" t="inlineStr"/>
+      <c r="G5" s="76" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="74" t="inlineStr">
+      <c r="A6" s="78" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B6" s="74" t="inlineStr">
+      <c r="B6" s="78" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1011,22 +1087,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Technology Transfer LazioApertoFESR</t>
         </is>
       </c>
-      <c r="D6" s="75" t="inlineStr">
+      <c r="D6" s="79" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/technology-transfer-lazio/</t>
         </is>
       </c>
-      <c r="E6" s="74" t="inlineStr"/>
-      <c r="F6" s="74" t="inlineStr"/>
-      <c r="G6" s="74" t="inlineStr"/>
+      <c r="E6" s="78" t="inlineStr"/>
+      <c r="F6" s="78" t="inlineStr"/>
+      <c r="G6" s="78" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="72" t="inlineStr">
+      <c r="A7" s="76" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B7" s="72" t="inlineStr">
+      <c r="B7" s="76" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1036,22 +1112,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Percorso di tutoraggio per le impreseApertoFESR</t>
         </is>
       </c>
-      <c r="D7" s="73" t="inlineStr">
+      <c r="D7" s="77" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/percorso-di-tutoraggio-per-le-imprese/</t>
         </is>
       </c>
-      <c r="E7" s="72" t="inlineStr"/>
-      <c r="F7" s="72" t="inlineStr"/>
-      <c r="G7" s="72" t="inlineStr"/>
+      <c r="E7" s="76" t="inlineStr"/>
+      <c r="F7" s="76" t="inlineStr"/>
+      <c r="G7" s="76" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="74" t="inlineStr">
+      <c r="A8" s="78" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B8" s="74" t="inlineStr">
+      <c r="B8" s="78" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1061,22 +1137,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per partecipare a SMAU Parigi 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D8" s="75" t="inlineStr">
+      <c r="D8" s="79" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-partecipare-a-smau-parigi-2026/</t>
         </is>
       </c>
-      <c r="E8" s="74" t="inlineStr"/>
-      <c r="F8" s="74" t="inlineStr"/>
-      <c r="G8" s="74" t="inlineStr"/>
+      <c r="E8" s="78" t="inlineStr"/>
+      <c r="F8" s="78" t="inlineStr"/>
+      <c r="G8" s="78" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="72" t="inlineStr">
+      <c r="A9" s="76" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B9" s="72" t="inlineStr">
+      <c r="B9" s="76" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1086,22 +1162,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONERiconoscimento della funzione sociale ed educativa degli oratoriApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D9" s="73" t="inlineStr">
+      <c r="D9" s="77" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/riconoscimento-della-funzione-sociale-ed-educativa-degli-oratori/</t>
         </is>
       </c>
-      <c r="E9" s="72" t="inlineStr"/>
-      <c r="F9" s="72" t="inlineStr"/>
-      <c r="G9" s="72" t="inlineStr"/>
+      <c r="E9" s="76" t="inlineStr"/>
+      <c r="F9" s="76" t="inlineStr"/>
+      <c r="G9" s="76" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="74" t="inlineStr">
+      <c r="A10" s="78" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B10" s="74" t="inlineStr">
+      <c r="B10" s="78" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1111,22 +1187,22 @@
           <t>GovernanceIscrizione nell’elenco regionale degli idonei all’esercizio dell’attività di direttore dell’Istituto JemoloApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D10" s="75" t="inlineStr">
+      <c r="D10" s="79" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/iscrizione-nellelenco-regionale-degli-idonei-allesercizio-dellattivita-di-direttore-dellistituto-jemolo/</t>
         </is>
       </c>
-      <c r="E10" s="74" t="inlineStr"/>
-      <c r="F10" s="74" t="inlineStr"/>
-      <c r="G10" s="74" t="inlineStr"/>
+      <c r="E10" s="78" t="inlineStr"/>
+      <c r="F10" s="78" t="inlineStr"/>
+      <c r="G10" s="78" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="72" t="inlineStr">
+      <c r="A11" s="76" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B11" s="72" t="inlineStr">
+      <c r="B11" s="76" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1136,22 +1212,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEVoucher per lo sport – seconda annualitàApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D11" s="73" t="inlineStr">
+      <c r="D11" s="77" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/voucher-per-lo-sport-seconda-annualita/</t>
         </is>
       </c>
-      <c r="E11" s="72" t="inlineStr"/>
-      <c r="F11" s="72" t="inlineStr"/>
-      <c r="G11" s="72" t="inlineStr"/>
+      <c r="E11" s="76" t="inlineStr"/>
+      <c r="F11" s="76" t="inlineStr"/>
+      <c r="G11" s="76" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="74" t="inlineStr">
+      <c r="A12" s="78" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B12" s="74" t="inlineStr">
+      <c r="B12" s="78" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1161,22 +1237,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEBonus occupazionale SALGOApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D12" s="75" t="inlineStr">
+      <c r="D12" s="79" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/bonus-occupazionale-salgo/</t>
         </is>
       </c>
-      <c r="E12" s="74" t="inlineStr"/>
-      <c r="F12" s="74" t="inlineStr"/>
-      <c r="G12" s="74" t="inlineStr"/>
+      <c r="E12" s="78" t="inlineStr"/>
+      <c r="F12" s="78" t="inlineStr"/>
+      <c r="G12" s="78" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="72" t="inlineStr">
+      <c r="A13" s="76" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B13" s="72" t="inlineStr">
+      <c r="B13" s="76" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1186,22 +1262,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEContributo di Libertà per le donne che hanno subito violenzaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D13" s="73" t="inlineStr">
+      <c r="D13" s="77" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-di-liberta-per-le-donne-che-hanno-subito-violenza/</t>
         </is>
       </c>
-      <c r="E13" s="72" t="inlineStr"/>
-      <c r="F13" s="72" t="inlineStr"/>
-      <c r="G13" s="72" t="inlineStr"/>
+      <c r="E13" s="76" t="inlineStr"/>
+      <c r="F13" s="76" t="inlineStr"/>
+      <c r="G13" s="76" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="74" t="inlineStr">
+      <c r="A14" s="78" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B14" s="74" t="inlineStr">
+      <c r="B14" s="78" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1211,22 +1287,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURAInterventi straordinari di valorizzazione del patrimonio culturale del LazioApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D14" s="75" t="inlineStr">
+      <c r="D14" s="79" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/interventi-straordinari-di-valorizzazione-del-patrimonio-culturale-del-lazio/</t>
         </is>
       </c>
-      <c r="E14" s="74" t="inlineStr"/>
-      <c r="F14" s="74" t="inlineStr"/>
-      <c r="G14" s="74" t="inlineStr"/>
+      <c r="E14" s="78" t="inlineStr"/>
+      <c r="F14" s="78" t="inlineStr"/>
+      <c r="G14" s="78" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="72" t="inlineStr">
+      <c r="A15" s="76" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B15" s="72" t="inlineStr">
+      <c r="B15" s="76" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1236,30 +1312,30 @@
           <t>Bandi di garaBANDO ATTUAZIONE Ob. 1.1 Azione 1 codice 111102 _DIV - "SOSTEGNO ALLA DIVERSIFICAZIONE E NUOVE FORME DI REDDITO PER LA PICCOLA PESCA COST</t>
         </is>
       </c>
-      <c r="D15" s="73" t="inlineStr">
+      <c r="D15" s="77" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/bando-avviso-regia-ob-11-azione-1-codice-111102-div-sostegno-alla-diversificazione-nuove-forme-reddito-piccola-pesca-costiera</t>
         </is>
       </c>
-      <c r="E15" s="72" t="inlineStr">
+      <c r="E15" s="76" t="inlineStr">
         <is>
           <t>07/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F15" s="72" t="inlineStr">
+      <c r="F15" s="76" t="inlineStr">
         <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="G15" s="72" t="inlineStr"/>
+      <c r="G15" s="76" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="74" t="inlineStr">
+      <c r="A16" s="78" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B16" s="74" t="inlineStr">
+      <c r="B16" s="78" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1269,30 +1345,30 @@
           <t>Avvisi pubblici09 marzo 2026 - ST SIRACUSA - AVVISO PUBBLICO PER LA COSTITUZIONE DI ELENCHI DI OPERATORI ECONOMICI PER L’ACQUISIZIONE DI BENI E SERVIZ</t>
         </is>
       </c>
-      <c r="D16" s="75" t="inlineStr">
+      <c r="D16" s="79" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/09-marzo-2026-st-siracusa-avviso-pubblico-costituzione-elenchi-operatori-economici-l-acquisizione-beni-servizi</t>
         </is>
       </c>
-      <c r="E16" s="74" t="inlineStr">
+      <c r="E16" s="78" t="inlineStr">
         <is>
           <t>31/12/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F16" s="74" t="inlineStr">
+      <c r="F16" s="78" t="inlineStr">
         <is>
           <t>31/12/2026</t>
         </is>
       </c>
-      <c r="G16" s="74" t="inlineStr"/>
+      <c r="G16" s="78" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="72" t="inlineStr">
+      <c r="A17" s="76" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B17" s="72" t="inlineStr">
+      <c r="B17" s="76" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1302,30 +1378,30 @@
           <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScade il:19/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D17" s="73" t="inlineStr">
+      <c r="D17" s="77" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
         </is>
       </c>
-      <c r="E17" s="72" t="inlineStr">
+      <c r="E17" s="76" t="inlineStr">
         <is>
           <t>19/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F17" s="72" t="inlineStr">
+      <c r="F17" s="76" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G17" s="72" t="inlineStr"/>
+      <c r="G17" s="76" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="74" t="inlineStr">
+      <c r="A18" s="78" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B18" s="74" t="inlineStr">
+      <c r="B18" s="78" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1335,22 +1411,22 @@
           <t>Manifestazioni di interesseAvviso Manifestazione Interesse DISTRIBUTORI AUTOMATICI di bevande e snackScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D18" s="75" t="inlineStr">
+      <c r="D18" s="79" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-distributori-automatici-bevande-snack</t>
         </is>
       </c>
-      <c r="E18" s="74" t="inlineStr"/>
-      <c r="F18" s="74" t="inlineStr"/>
-      <c r="G18" s="74" t="inlineStr"/>
+      <c r="E18" s="78" t="inlineStr"/>
+      <c r="F18" s="78" t="inlineStr"/>
+      <c r="G18" s="78" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="72" t="inlineStr">
+      <c r="A19" s="76" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B19" s="72" t="inlineStr">
+      <c r="B19" s="76" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1360,30 +1436,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D19" s="73" t="inlineStr">
+      <c r="D19" s="77" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo</t>
         </is>
       </c>
-      <c r="E19" s="72" t="inlineStr">
+      <c r="E19" s="76" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F19" s="72" t="inlineStr">
+      <c r="F19" s="76" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G19" s="72" t="inlineStr"/>
+      <c r="G19" s="76" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="74" t="inlineStr">
+      <c r="A20" s="78" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B20" s="74" t="inlineStr">
+      <c r="B20" s="78" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1393,30 +1469,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D20" s="75" t="inlineStr">
+      <c r="D20" s="79" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo-0</t>
         </is>
       </c>
-      <c r="E20" s="74" t="inlineStr">
+      <c r="E20" s="78" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F20" s="74" t="inlineStr">
+      <c r="F20" s="78" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G20" s="74" t="inlineStr"/>
+      <c r="G20" s="78" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="72" t="inlineStr">
+      <c r="A21" s="76" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B21" s="72" t="inlineStr">
+      <c r="B21" s="76" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1426,22 +1502,22 @@
           <t>Manifestazioni di interesseST SIRACUSA - AVVISO DI MANIFESTAZIONE DI INTERESSE - Fornitura applicativo extracontabile per la gestione progetti, ecc. e</t>
         </is>
       </c>
-      <c r="D21" s="73" t="inlineStr">
+      <c r="D21" s="77" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-siracusa-avviso-manifestazione-interesse-fornitura-applicativo-extracontabile-gestione-progetti-ecc-applicativo-gestione-ed-elaborazione-informatizzata-paghe</t>
         </is>
       </c>
-      <c r="E21" s="72" t="inlineStr"/>
-      <c r="F21" s="72" t="inlineStr"/>
-      <c r="G21" s="72" t="inlineStr"/>
+      <c r="E21" s="76" t="inlineStr"/>
+      <c r="F21" s="76" t="inlineStr"/>
+      <c r="G21" s="76" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="74" t="inlineStr">
+      <c r="A22" s="78" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B22" s="74" t="inlineStr">
+      <c r="B22" s="78" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1451,30 +1527,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile sito nel Comune di Capo D'Orlando, Via Trazzera MarinaScade il:25/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D22" s="75" t="inlineStr">
+      <c r="D22" s="79" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-sito-nel-comune-capo-d-orlando-trazzera-marina</t>
         </is>
       </c>
-      <c r="E22" s="74" t="inlineStr">
+      <c r="E22" s="78" t="inlineStr">
         <is>
           <t>25/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F22" s="74" t="inlineStr">
+      <c r="F22" s="78" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="G22" s="74" t="inlineStr"/>
+      <c r="G22" s="78" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="72" t="inlineStr">
+      <c r="A23" s="76" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B23" s="72" t="inlineStr">
+      <c r="B23" s="76" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1484,22 +1560,22 @@
           <t xml:space="preserve">Avvisi pubbliciST CATANIA - Programma Regionale FESR Sicilia 2021-2027 - Azione 2.4.4 - “Interventi per la riduzione del rischio incendi” - AVVISO DI </t>
         </is>
       </c>
-      <c r="D23" s="73" t="inlineStr">
+      <c r="D23" s="77" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-catania-programma-regionale-fesr-sicilia-2021-2027-azione-244-interventi-riduzione-rischio-incendi-avviso-indagine-mercato</t>
         </is>
       </c>
-      <c r="E23" s="72" t="inlineStr"/>
-      <c r="F23" s="72" t="inlineStr"/>
-      <c r="G23" s="72" t="inlineStr"/>
+      <c r="E23" s="76" t="inlineStr"/>
+      <c r="F23" s="76" t="inlineStr"/>
+      <c r="G23" s="76" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="74" t="inlineStr">
+      <c r="A24" s="78" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B24" s="74" t="inlineStr">
+      <c r="B24" s="78" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1509,22 +1585,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per ROMICS – Primavera 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D24" s="75" t="inlineStr">
+      <c r="D24" s="79" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-romics-primavera-2026/</t>
         </is>
       </c>
-      <c r="E24" s="74" t="inlineStr"/>
-      <c r="F24" s="74" t="inlineStr"/>
-      <c r="G24" s="74" t="inlineStr"/>
+      <c r="E24" s="78" t="inlineStr"/>
+      <c r="F24" s="78" t="inlineStr"/>
+      <c r="G24" s="78" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="72" t="inlineStr">
+      <c r="A25" s="76" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B25" s="72" t="inlineStr">
+      <c r="B25" s="76" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1534,22 +1610,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Cinema International 2026 – I edizioneApertoFESR</t>
         </is>
       </c>
-      <c r="D25" s="73" t="inlineStr">
+      <c r="D25" s="77" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lazio-cinema-international-2026-i-edizione/</t>
         </is>
       </c>
-      <c r="E25" s="72" t="inlineStr"/>
-      <c r="F25" s="72" t="inlineStr"/>
-      <c r="G25" s="72" t="inlineStr"/>
+      <c r="E25" s="76" t="inlineStr"/>
+      <c r="F25" s="76" t="inlineStr"/>
+      <c r="G25" s="76" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="74" t="inlineStr">
+      <c r="A26" s="78" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B26" s="74" t="inlineStr">
+      <c r="B26" s="78" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1559,22 +1635,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEManifestazioni di interesse alla costituzione di due nuove Fondazioni I.T.S. AcademyApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D26" s="75" t="inlineStr">
+      <c r="D26" s="79" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazioni-di-interesse-alla-costituzione-di-due-nuove-fondazioni-i-t-s-academy/</t>
         </is>
       </c>
-      <c r="E26" s="74" t="inlineStr"/>
-      <c r="F26" s="74" t="inlineStr"/>
-      <c r="G26" s="74" t="inlineStr"/>
+      <c r="E26" s="78" t="inlineStr"/>
+      <c r="F26" s="78" t="inlineStr"/>
+      <c r="G26" s="78" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="72" t="inlineStr">
+      <c r="A27" s="76" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B27" s="72" t="inlineStr">
+      <c r="B27" s="76" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1584,22 +1660,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURAContributi per sostenere la ripresa del settore della pescaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D27" s="73" t="inlineStr">
+      <c r="D27" s="77" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributi-per-sostenere-la-ripresa-del-settore-della-pesca/</t>
         </is>
       </c>
-      <c r="E27" s="72" t="inlineStr"/>
-      <c r="F27" s="72" t="inlineStr"/>
-      <c r="G27" s="72" t="inlineStr"/>
+      <c r="E27" s="76" t="inlineStr"/>
+      <c r="F27" s="76" t="inlineStr"/>
+      <c r="G27" s="76" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="74" t="inlineStr">
+      <c r="A28" s="78" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B28" s="74" t="inlineStr">
+      <c r="B28" s="78" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1609,30 +1685,30 @@
           <t>Manifestazioni di interesseAVVISO - Manifestazione Interesse “Storytelling aziendale” Expo Wild Natura - Caccia - Pesca. Misterbianco (CT), 10-12 apri</t>
         </is>
       </c>
-      <c r="D28" s="75" t="inlineStr">
+      <c r="D28" s="79" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-storytelling-aziendale-expo-wild-natura-caccia-pesca-misterbianco-ct-10-12-aprile-2026</t>
         </is>
       </c>
-      <c r="E28" s="74" t="inlineStr">
+      <c r="E28" s="78" t="inlineStr">
         <is>
           <t>30/03/2026 - 13:00</t>
         </is>
       </c>
-      <c r="F28" s="74" t="inlineStr">
+      <c r="F28" s="78" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G28" s="74" t="inlineStr"/>
+      <c r="G28" s="78" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="72" t="inlineStr">
+      <c r="A29" s="76" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B29" s="72" t="inlineStr">
+      <c r="B29" s="76" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1642,30 +1718,30 @@
           <t>Manifestazioni di interesseInvaso Lentini - Interventi di ripristino delle pareti esterne in cls della Torre di presa Sud e della trave d’appoggio del</t>
         </is>
       </c>
-      <c r="D29" s="73" t="inlineStr">
+      <c r="D29" s="77" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/invaso-lentini-interventi-ripristino-pareti-esterne-cls-torre-presa-sud-trave-d-appoggio-cavalcavia-collegamento-alla-stessa-torre</t>
         </is>
       </c>
-      <c r="E29" s="72" t="inlineStr">
+      <c r="E29" s="76" t="inlineStr">
         <is>
           <t>19/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F29" s="72" t="inlineStr">
+      <c r="F29" s="76" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G29" s="72" t="inlineStr"/>
+      <c r="G29" s="76" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="74" t="inlineStr">
+      <c r="A30" s="78" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="B30" s="74" t="inlineStr">
+      <c r="B30" s="78" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1675,22 +1751,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURARistrutturazione e riconversione vigneti – campagna 2026-2027ApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D30" s="75" t="inlineStr">
+      <c r="D30" s="79" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/ristrutturazione-e-riconversione-vigneti-campagna-2026-2027/</t>
         </is>
       </c>
-      <c r="E30" s="74" t="inlineStr"/>
-      <c r="F30" s="74" t="inlineStr"/>
-      <c r="G30" s="74" t="inlineStr"/>
+      <c r="E30" s="78" t="inlineStr"/>
+      <c r="F30" s="78" t="inlineStr"/>
+      <c r="G30" s="78" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="72" t="inlineStr">
+      <c r="A31" s="76" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="B31" s="72" t="inlineStr">
+      <c r="B31" s="76" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1700,30 +1776,30 @@
           <t>Manifestazioni di interessePR FESR 2021/27 Azione 1.3.3 e del POC 2014/20 - Azione 1.3.1  - Avviso a manifestazione d’interesse eventi fieristici inte</t>
         </is>
       </c>
-      <c r="D31" s="73" t="inlineStr">
+      <c r="D31" s="77" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-d-interesse-eventi-fieristici-internazionali-marzo-dicembre-2026</t>
         </is>
       </c>
-      <c r="E31" s="72" t="inlineStr">
+      <c r="E31" s="76" t="inlineStr">
         <is>
           <t>30/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F31" s="72" t="inlineStr">
+      <c r="F31" s="76" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="G31" s="72" t="inlineStr"/>
+      <c r="G31" s="76" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="74" t="inlineStr">
+      <c r="A32" s="78" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="B32" s="74" t="inlineStr">
+      <c r="B32" s="78" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1733,22 +1809,22 @@
           <t>INTERNAZIONALIZZAZIONEL’Ecosistema dell’Innovazione a INNOVIT – Focus S3ApertoFESR</t>
         </is>
       </c>
-      <c r="D32" s="75" t="inlineStr">
+      <c r="D32" s="79" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lecosistema-dellinnovazione-a-innovit-focus-s3/</t>
         </is>
       </c>
-      <c r="E32" s="74" t="inlineStr"/>
-      <c r="F32" s="74" t="inlineStr"/>
-      <c r="G32" s="74" t="inlineStr"/>
+      <c r="E32" s="78" t="inlineStr"/>
+      <c r="F32" s="78" t="inlineStr"/>
+      <c r="G32" s="78" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="72" t="inlineStr">
+      <c r="A33" s="76" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="B33" s="72" t="inlineStr">
+      <c r="B33" s="76" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1758,22 +1834,22 @@
           <t>Manifestazioni di interessePR FESR SICILIA 2021/27 - NUOVO Avviso a manifestazione d’interesse per esperti valutatoriScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D33" s="73" t="inlineStr">
+      <c r="D33" s="77" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/pr-fesr-sicilia-202127-nuovo-avviso-manifestazione-d-interesse-esperti-valutatori</t>
         </is>
       </c>
-      <c r="E33" s="72" t="inlineStr"/>
-      <c r="F33" s="72" t="inlineStr"/>
-      <c r="G33" s="72" t="inlineStr"/>
+      <c r="E33" s="76" t="inlineStr"/>
+      <c r="F33" s="76" t="inlineStr"/>
+      <c r="G33" s="76" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="74" t="inlineStr">
+      <c r="A34" s="78" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="B34" s="74" t="inlineStr">
+      <c r="B34" s="78" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -1783,22 +1859,22 @@
           <t>Bando 2026 per contributi dedicati alla manutenzione della rete dei percorsi escursionistici</t>
         </is>
       </c>
-      <c r="D34" s="75" t="inlineStr">
+      <c r="D34" s="79" t="inlineStr">
         <is>
           <t>https://ambiente.regione.emilia-romagna.it/it/parchi-natura2000/bandi/bando-2026-per-contributi-dedicati-alla-manutenzione-della-rete-dei-percorsi-escursionistici</t>
         </is>
       </c>
-      <c r="E34" s="74" t="inlineStr"/>
-      <c r="F34" s="74" t="inlineStr"/>
-      <c r="G34" s="74" t="inlineStr"/>
+      <c r="E34" s="78" t="inlineStr"/>
+      <c r="F34" s="78" t="inlineStr"/>
+      <c r="G34" s="78" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="72" t="inlineStr">
+      <c r="A35" s="76" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="B35" s="72" t="inlineStr">
+      <c r="B35" s="76" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1808,22 +1884,22 @@
           <t>Programma regionale in favore delle tradizioni storiche, artistiche, religiose e popolari (2026) – manifestazioni d’interesseApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D35" s="73" t="inlineStr">
+      <c r="D35" s="77" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/programma-regionale-in-favore-delle-tradizioni-storiche-artistiche-religiose-e-popolari-2026-manifestazioni-dinteresse/</t>
         </is>
       </c>
-      <c r="E35" s="72" t="inlineStr"/>
-      <c r="F35" s="72" t="inlineStr"/>
-      <c r="G35" s="72" t="inlineStr"/>
+      <c r="E35" s="76" t="inlineStr"/>
+      <c r="F35" s="76" t="inlineStr"/>
+      <c r="G35" s="76" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="74" t="inlineStr">
+      <c r="A36" s="78" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B36" s="74" t="inlineStr">
+      <c r="B36" s="78" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1833,22 +1909,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEBuoni servizio per le persone non autosufficienti nel territorio del LazioProssima AperturaFSE / FSE+</t>
         </is>
       </c>
-      <c r="D36" s="75" t="inlineStr">
+      <c r="D36" s="79" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/buoni-servizio-per-le-persone-non-autosufficienti-nel-territorio-del-lazio/</t>
         </is>
       </c>
-      <c r="E36" s="74" t="inlineStr"/>
-      <c r="F36" s="74" t="inlineStr"/>
-      <c r="G36" s="74" t="inlineStr"/>
+      <c r="E36" s="78" t="inlineStr"/>
+      <c r="F36" s="78" t="inlineStr"/>
+      <c r="G36" s="78" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="72" t="inlineStr">
+      <c r="A37" s="76" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B37" s="72" t="inlineStr">
+      <c r="B37" s="76" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1858,22 +1934,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONERimborso delle rette dei servizi educativi nel territorio del LazioProssima AperturaFSE / FSE+</t>
         </is>
       </c>
-      <c r="D37" s="73" t="inlineStr">
+      <c r="D37" s="77" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/rimborso-delle-rette-dei-servizi-educativi-nel-territorio-del-lazio/</t>
         </is>
       </c>
-      <c r="E37" s="72" t="inlineStr"/>
-      <c r="F37" s="72" t="inlineStr"/>
-      <c r="G37" s="72" t="inlineStr"/>
+      <c r="E37" s="76" t="inlineStr"/>
+      <c r="F37" s="76" t="inlineStr"/>
+      <c r="G37" s="76" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="74" t="inlineStr">
+      <c r="A38" s="78" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B38" s="74" t="inlineStr">
+      <c r="B38" s="78" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1883,30 +1959,30 @@
           <t>Manifestazioni di interesseATTO DI INTERPELLO PER L’AFFIDAMENTO DELL’INCARICO DI COLLAUDO STATICO DELLE STRUTTURE - Diga di Pietrarossa (Progetto ex C</t>
         </is>
       </c>
-      <c r="D38" s="75" t="inlineStr">
+      <c r="D38" s="79" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/atto-interpello-l-affidamento-incarico-collaudo-statico-strutture-diga-pietrarossa-progetto-ex-casmez-303219</t>
         </is>
       </c>
-      <c r="E38" s="74" t="inlineStr">
+      <c r="E38" s="78" t="inlineStr">
         <is>
           <t>27/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F38" s="74" t="inlineStr">
+      <c r="F38" s="78" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="G38" s="74" t="inlineStr"/>
+      <c r="G38" s="78" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="72" t="inlineStr">
+      <c r="A39" s="76" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B39" s="72" t="inlineStr">
+      <c r="B39" s="76" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1916,30 +1992,30 @@
           <t>Manifestazioni di interesseAvviso alle Case  Editrici della Regione siciliana per la partecipazione al Salone del Libro di Torino, 14-18  maggio 2026.</t>
         </is>
       </c>
-      <c r="D39" s="73" t="inlineStr">
+      <c r="D39" s="77" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/manifestazione-d-interesse-partecipare-al-xxxviii-salone-libro-torino-14-al-18-maggio-2026-attraverso-l-esposizione-pubblicazioni-presso-stand-assessorato-beni</t>
         </is>
       </c>
-      <c r="E39" s="72" t="inlineStr">
+      <c r="E39" s="76" t="inlineStr">
         <is>
           <t>30/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F39" s="72" t="inlineStr">
+      <c r="F39" s="76" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="G39" s="72" t="inlineStr"/>
+      <c r="G39" s="76" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="74" t="inlineStr">
+      <c r="A40" s="78" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B40" s="74" t="inlineStr">
+      <c r="B40" s="78" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1949,30 +2025,30 @@
           <t xml:space="preserve">Manifestazioni di interessePR FESR SICILIA 2021/27 - NUOVO Avviso a manifestazione d’interesse per esperti valutatoriScade il:06/04/2026 - 23:59Leggi </t>
         </is>
       </c>
-      <c r="D40" s="75" t="inlineStr">
+      <c r="D40" s="79" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/pr-fesr-sicilia-202127-nuovo-avviso-manifestazione-d-interesse-esperti-valutatori</t>
         </is>
       </c>
-      <c r="E40" s="74" t="inlineStr">
+      <c r="E40" s="78" t="inlineStr">
         <is>
           <t>06/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F40" s="74" t="inlineStr">
+      <c r="F40" s="78" t="inlineStr">
         <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="G40" s="74" t="inlineStr"/>
+      <c r="G40" s="78" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="72" t="inlineStr">
+      <c r="A41" s="76" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B41" s="72" t="inlineStr">
+      <c r="B41" s="76" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1982,22 +2058,22 @@
           <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D41" s="73" t="inlineStr">
+      <c r="D41" s="77" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
         </is>
       </c>
-      <c r="E41" s="72" t="inlineStr"/>
-      <c r="F41" s="72" t="inlineStr"/>
-      <c r="G41" s="72" t="inlineStr"/>
+      <c r="E41" s="76" t="inlineStr"/>
+      <c r="F41" s="76" t="inlineStr"/>
+      <c r="G41" s="76" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="74" t="inlineStr">
+      <c r="A42" s="78" t="inlineStr">
         <is>
           <t>24/03/2026</t>
         </is>
       </c>
-      <c r="B42" s="74" t="inlineStr">
+      <c r="B42" s="78" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2007,22 +2083,22 @@
           <t>GAL del Ducato - Promozione di fiere agroalimentari e delle filiere del cibo – Bando per Enti pubblici (DU AS 05B)</t>
         </is>
       </c>
-      <c r="D42" s="75" t="inlineStr">
+      <c r="D42" s="79" t="inlineStr">
         <is>
           <t>https://agricoltura.regione.emilia-romagna.it/sviluppo-rurale-23-27/opportunita/bandi-gal/2026/du_as05b-promozione-di-fiere-agroalimentari-e-delle-filiere-del-cibo-bando-per-enti-pubblici</t>
         </is>
       </c>
-      <c r="E42" s="74" t="inlineStr"/>
-      <c r="F42" s="74" t="inlineStr"/>
-      <c r="G42" s="74" t="inlineStr"/>
+      <c r="E42" s="78" t="inlineStr"/>
+      <c r="F42" s="78" t="inlineStr"/>
+      <c r="G42" s="78" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="72" t="inlineStr">
+      <c r="A43" s="76" t="inlineStr">
         <is>
           <t>24/03/2026</t>
         </is>
       </c>
-      <c r="B43" s="72" t="inlineStr">
+      <c r="B43" s="76" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2032,30 +2108,30 @@
           <t>Manifestazioni di interesseAVVISO PUBBLICO PER MANIFESTAZIONE DI INTERESSE FINALIZZATA ALL'ASSEGNAZIONE DI SPAZI ESPOSITIVI (CORNER GRATUITI) ALL'INTE</t>
         </is>
       </c>
-      <c r="D43" s="73" t="inlineStr">
+      <c r="D43" s="77" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-manifestazione-interesse-finalizzata-all-assegnazione-spazi-espositivi-corner-gratuiti-all-interno-stand-istituzionale-dsrt-manifestazione</t>
         </is>
       </c>
-      <c r="E43" s="72" t="inlineStr">
+      <c r="E43" s="76" t="inlineStr">
         <is>
           <t>30/03/2026 - 13:00</t>
         </is>
       </c>
-      <c r="F43" s="72" t="inlineStr">
+      <c r="F43" s="76" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G43" s="72" t="inlineStr"/>
+      <c r="G43" s="76" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="74" t="inlineStr">
+      <c r="A44" s="78" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B44" s="74" t="inlineStr">
+      <c r="B44" s="78" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2065,22 +2141,22 @@
           <t>Avviso per la concessione di contributi per eventi sportivi realizzati in Emilia-Romagna - Anno 2026</t>
         </is>
       </c>
-      <c r="D44" s="75" t="inlineStr">
+      <c r="D44" s="79" t="inlineStr">
         <is>
           <t>https://www.regione.emilia-romagna.it/sport/bandi/2026/bando-2026</t>
         </is>
       </c>
-      <c r="E44" s="74" t="inlineStr"/>
-      <c r="F44" s="74" t="inlineStr"/>
-      <c r="G44" s="74" t="inlineStr"/>
+      <c r="E44" s="78" t="inlineStr"/>
+      <c r="F44" s="78" t="inlineStr"/>
+      <c r="G44" s="78" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="72" t="inlineStr">
+      <c r="A45" s="76" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B45" s="72" t="inlineStr">
+      <c r="B45" s="76" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2090,22 +2166,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Street art 2026Prossima AperturaBandi Regionali</t>
         </is>
       </c>
-      <c r="D45" s="73" t="inlineStr">
+      <c r="D45" s="77" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lazio-street-art-2026/</t>
         </is>
       </c>
-      <c r="E45" s="72" t="inlineStr"/>
-      <c r="F45" s="72" t="inlineStr"/>
-      <c r="G45" s="72" t="inlineStr"/>
+      <c r="E45" s="76" t="inlineStr"/>
+      <c r="F45" s="76" t="inlineStr"/>
+      <c r="G45" s="76" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="74" t="inlineStr">
+      <c r="A46" s="78" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B46" s="74" t="inlineStr">
+      <c r="B46" s="78" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2115,30 +2191,30 @@
           <t>Manifestazioni di interesseManifestazione di interesse per la partecipazione all’evento “R2I Italy 2026” – Bologna, 12-13/05/2026Scade il:03/04/2026 -</t>
         </is>
       </c>
-      <c r="D46" s="75" t="inlineStr">
+      <c r="D46" s="79" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/manifestazione-interesse-partecipazione-all-evento-r2i-italy-2026-bologna-12-13052026</t>
         </is>
       </c>
-      <c r="E46" s="74" t="inlineStr">
+      <c r="E46" s="78" t="inlineStr">
         <is>
           <t>03/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F46" s="74" t="inlineStr">
+      <c r="F46" s="78" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="G46" s="74" t="inlineStr"/>
+      <c r="G46" s="78" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="72" t="inlineStr">
+      <c r="A47" s="76" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B47" s="72" t="inlineStr">
+      <c r="B47" s="76" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2148,30 +2224,30 @@
           <t>Manifestazioni di interesseST SIRACUSA - AVVISO PER MANIFESTAZIONE DI INTERESSE - Selezione di n. 5 unità di personale internoScade il:20/04/2026 - 12</t>
         </is>
       </c>
-      <c r="D47" s="73" t="inlineStr">
+      <c r="D47" s="77" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/24-marzo-2026-st-siracusa-avviso-manifestazione-interesse-selezione-n-5-unita-personale-interno</t>
         </is>
       </c>
-      <c r="E47" s="72" t="inlineStr">
+      <c r="E47" s="76" t="inlineStr">
         <is>
           <t>20/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F47" s="72" t="inlineStr">
+      <c r="F47" s="76" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="G47" s="72" t="inlineStr"/>
+      <c r="G47" s="76" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="74" t="inlineStr">
+      <c r="A48" s="78" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B48" s="74" t="inlineStr">
+      <c r="B48" s="78" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2181,30 +2257,30 @@
           <t>Avvisi pubbliciRevoca dell’avviso di concessione a titolo gratuito del 16.12.2025 inerente all’immobile di seguito identificato e contestuale nuovo av</t>
         </is>
       </c>
-      <c r="D48" s="75" t="inlineStr">
+      <c r="D48" s="79" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/revoca-avviso-concessione-titolo-gratuito-16122025-inerente-all-immobile-seguito-identificato-contestuale-nuovo-avviso-concessione-titolo-oneroso-stesso-sito-nel</t>
         </is>
       </c>
-      <c r="E48" s="74" t="inlineStr">
+      <c r="E48" s="78" t="inlineStr">
         <is>
           <t>08/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F48" s="74" t="inlineStr">
+      <c r="F48" s="78" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="G48" s="74" t="inlineStr"/>
+      <c r="G48" s="78" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="72" t="inlineStr">
+      <c r="A49" s="76" t="inlineStr">
         <is>
           <t>26/03/2026</t>
         </is>
       </c>
-      <c r="B49" s="72" t="inlineStr">
+      <c r="B49" s="76" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2214,22 +2290,22 @@
           <t>Bando studi di fattibilità per fusioni di Comuni</t>
         </is>
       </c>
-      <c r="D49" s="73" t="inlineStr">
+      <c r="D49" s="77" t="inlineStr">
         <is>
           <t>https://www.regione.emilia-romagna.it/autonomie-locali/bandi/bando_studi_fattibilita_fusioni_comuni</t>
         </is>
       </c>
-      <c r="E49" s="72" t="inlineStr"/>
-      <c r="F49" s="72" t="inlineStr"/>
-      <c r="G49" s="72" t="inlineStr"/>
+      <c r="E49" s="76" t="inlineStr"/>
+      <c r="F49" s="76" t="inlineStr"/>
+      <c r="G49" s="76" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="74" t="inlineStr">
+      <c r="A50" s="78" t="inlineStr">
         <is>
           <t>26/03/2026</t>
         </is>
       </c>
-      <c r="B50" s="74" t="inlineStr">
+      <c r="B50" s="78" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2239,30 +2315,30 @@
           <t xml:space="preserve">Manifestazioni di interesseAvviso pubblico di selezione interna, per titoli, per il conferimento di PO e professionali, ai sensi degli artt. 19, 20 e </t>
         </is>
       </c>
-      <c r="D50" s="75" t="inlineStr">
+      <c r="D50" s="79" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-selezione-interna-titoli-conferimento-po-professionali-ai-sensi-artt-19-20-21-ccrl-20222024-comparto-non-dirigenziale</t>
         </is>
       </c>
-      <c r="E50" s="74" t="inlineStr">
+      <c r="E50" s="78" t="inlineStr">
         <is>
           <t>30/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F50" s="74" t="inlineStr">
+      <c r="F50" s="78" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G50" s="74" t="inlineStr"/>
+      <c r="G50" s="78" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="72" t="inlineStr">
+      <c r="A51" s="76" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="B51" s="72" t="inlineStr">
+      <c r="B51" s="76" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2272,22 +2348,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0PRE-SEED 3.0ApertoFESR</t>
         </is>
       </c>
-      <c r="D51" s="73" t="inlineStr">
+      <c r="D51" s="77" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/pre-seed-3-0/</t>
         </is>
       </c>
-      <c r="E51" s="72" t="inlineStr"/>
-      <c r="F51" s="72" t="inlineStr"/>
-      <c r="G51" s="72" t="inlineStr"/>
+      <c r="E51" s="76" t="inlineStr"/>
+      <c r="F51" s="76" t="inlineStr"/>
+      <c r="G51" s="76" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="74" t="inlineStr">
+      <c r="A52" s="78" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B52" s="74" t="inlineStr">
+      <c r="B52" s="78" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2297,30 +2373,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “So</t>
         </is>
       </c>
-      <c r="D52" s="75" t="inlineStr">
+      <c r="D52" s="79" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-termini-imerese-locta-piazza-marina</t>
         </is>
       </c>
-      <c r="E52" s="74" t="inlineStr">
+      <c r="E52" s="78" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F52" s="74" t="inlineStr">
+      <c r="F52" s="78" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G52" s="74" t="inlineStr"/>
+      <c r="G52" s="78" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="72" t="inlineStr">
+      <c r="A53" s="76" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B53" s="72" t="inlineStr">
+      <c r="B53" s="76" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2330,30 +2406,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, Sig</t>
         </is>
       </c>
-      <c r="D53" s="73" t="inlineStr">
+      <c r="D53" s="77" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-porto-empedocle-locta-punta-piccola</t>
         </is>
       </c>
-      <c r="E53" s="72" t="inlineStr">
+      <c r="E53" s="76" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F53" s="72" t="inlineStr">
+      <c r="F53" s="76" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G53" s="72" t="inlineStr"/>
+      <c r="G53" s="76" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="74" t="inlineStr">
+      <c r="A54" s="78" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B54" s="74" t="inlineStr">
+      <c r="B54" s="78" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2363,30 +2439,30 @@
           <t xml:space="preserve">Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “Società </t>
         </is>
       </c>
-      <c r="D54" s="75" t="inlineStr">
+      <c r="D54" s="79" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-messina-locta-torrente-bordonaro</t>
         </is>
       </c>
-      <c r="E54" s="74" t="inlineStr">
+      <c r="E54" s="78" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F54" s="74" t="inlineStr">
+      <c r="F54" s="78" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G54" s="74" t="inlineStr"/>
+      <c r="G54" s="78" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="72" t="inlineStr">
+      <c r="A55" s="76" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B55" s="72" t="inlineStr">
+      <c r="B55" s="76" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2396,30 +2472,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “Condomin</t>
         </is>
       </c>
-      <c r="D55" s="73" t="inlineStr">
+      <c r="D55" s="77" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-mascali-spiaggia-n-144150</t>
         </is>
       </c>
-      <c r="E55" s="72" t="inlineStr">
+      <c r="E55" s="76" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F55" s="72" t="inlineStr">
+      <c r="F55" s="76" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G55" s="72" t="inlineStr"/>
+      <c r="G55" s="76" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="74" t="inlineStr">
+      <c r="A56" s="78" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B56" s="74" t="inlineStr">
+      <c r="B56" s="78" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2429,30 +2505,30 @@
           <t xml:space="preserve">Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione sito nel Comune di Lipari, isola di Stromboli, </t>
         </is>
       </c>
-      <c r="D56" s="75" t="inlineStr">
+      <c r="D56" s="79" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-lipari-isola-stromboli-locta-fico-grande</t>
         </is>
       </c>
-      <c r="E56" s="74" t="inlineStr">
+      <c r="E56" s="78" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F56" s="74" t="inlineStr">
+      <c r="F56" s="78" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G56" s="74" t="inlineStr"/>
+      <c r="G56" s="78" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="72" t="inlineStr">
+      <c r="A57" s="76" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B57" s="72" t="inlineStr">
+      <c r="B57" s="76" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2462,30 +2538,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione sito nel Comune di Favignana, isola di Le</t>
         </is>
       </c>
-      <c r="D57" s="73" t="inlineStr">
+      <c r="D57" s="77" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-favignana-isola-levanzo</t>
         </is>
       </c>
-      <c r="E57" s="72" t="inlineStr">
+      <c r="E57" s="76" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F57" s="72" t="inlineStr">
+      <c r="F57" s="76" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G57" s="72" t="inlineStr"/>
+      <c r="G57" s="76" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="74" t="inlineStr">
+      <c r="A58" s="78" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="B58" s="74" t="inlineStr">
+      <c r="B58" s="78" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2495,30 +2571,30 @@
           <t>Manifestazioni di interesseAVVISO - Manifestazione d’interesse finalizzata alla selezione di organismi attuatori di piani di gestione locale della pic</t>
         </is>
       </c>
-      <c r="D58" s="75" t="inlineStr">
+      <c r="D58" s="79" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-d-interesse-finalizzata-alla-selezione-organismi-attuatori-piani-gestione-locale-piccola-pesca-costiera-nelle-gsa-regione-siciliana</t>
         </is>
       </c>
-      <c r="E58" s="74" t="inlineStr">
+      <c r="E58" s="78" t="inlineStr">
         <is>
           <t>29/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F58" s="74" t="inlineStr">
+      <c r="F58" s="78" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="G58" s="74" t="inlineStr"/>
+      <c r="G58" s="78" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="72" t="inlineStr">
+      <c r="A59" s="76" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="B59" s="72" t="inlineStr">
+      <c r="B59" s="76" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2528,30 +2604,30 @@
           <t>Avvisi pubbliciLeggi e scarica l'avvisoScade il:02/04/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D59" s="73" t="inlineStr">
+      <c r="D59" s="77" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/proroga-termini-presentazione-candidature-po</t>
         </is>
       </c>
-      <c r="E59" s="72" t="inlineStr">
+      <c r="E59" s="76" t="inlineStr">
         <is>
           <t>02/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F59" s="72" t="inlineStr">
+      <c r="F59" s="76" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="G59" s="72" t="inlineStr"/>
+      <c r="G59" s="76" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="74" t="inlineStr">
+      <c r="A60" s="78" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="74" t="inlineStr">
+      <c r="B60" s="78" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2561,22 +2637,22 @@
           <t>INTERNAZIONALIZZAZIONESMAU – Italy RestartsUp in STOCCOLMAApertoFESR</t>
         </is>
       </c>
-      <c r="D60" s="75" t="inlineStr">
+      <c r="D60" s="79" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/smau-italy-restartsup-in-stoccolma/</t>
         </is>
       </c>
-      <c r="E60" s="74" t="inlineStr"/>
-      <c r="F60" s="74" t="inlineStr"/>
-      <c r="G60" s="74" t="inlineStr"/>
+      <c r="E60" s="78" t="inlineStr"/>
+      <c r="F60" s="78" t="inlineStr"/>
+      <c r="G60" s="78" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="72" t="inlineStr">
+      <c r="A61" s="76" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B61" s="72" t="inlineStr">
+      <c r="B61" s="76" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2586,22 +2662,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per Farnborough International AirshowApertoFESR</t>
         </is>
       </c>
-      <c r="D61" s="73" t="inlineStr">
+      <c r="D61" s="77" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-farnborough-international-airshow-2/</t>
         </is>
       </c>
-      <c r="E61" s="72" t="inlineStr"/>
-      <c r="F61" s="72" t="inlineStr"/>
-      <c r="G61" s="72" t="inlineStr"/>
+      <c r="E61" s="76" t="inlineStr"/>
+      <c r="F61" s="76" t="inlineStr"/>
+      <c r="G61" s="76" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="74" t="inlineStr">
+      <c r="A62" s="78" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="74" t="inlineStr">
+      <c r="B62" s="78" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2611,30 +2687,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA - alienazione lotto di terreno sito nel comune di Termini Imerese, via LibertàScade il:30/04/2026 - 12:00Leg</t>
         </is>
       </c>
-      <c r="D62" s="75" t="inlineStr">
+      <c r="D62" s="79" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proprieta-regionale-sito-nel-comune-termini-imerese-favore-ares-fabiola</t>
         </is>
       </c>
-      <c r="E62" s="74" t="inlineStr">
+      <c r="E62" s="78" t="inlineStr">
         <is>
           <t>30/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F62" s="74" t="inlineStr">
+      <c r="F62" s="78" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="G62" s="74" t="inlineStr"/>
+      <c r="G62" s="78" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="72" t="inlineStr">
+      <c r="A63" s="76" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B63" s="72" t="inlineStr">
+      <c r="B63" s="76" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2644,22 +2720,22 @@
           <t>Avviso per la concessione di contributi per progetti di contrasto all'abbandono sportivo giovanile (2026)</t>
         </is>
       </c>
-      <c r="D63" s="73" t="inlineStr">
+      <c r="D63" s="77" t="inlineStr">
         <is>
           <t>https://www.regione.emilia-romagna.it/sport/bandi/2026/contrasto-abbandono-2026</t>
         </is>
       </c>
-      <c r="E63" s="72" t="inlineStr"/>
-      <c r="F63" s="72" t="inlineStr"/>
-      <c r="G63" s="72" t="inlineStr"/>
+      <c r="E63" s="76" t="inlineStr"/>
+      <c r="F63" s="76" t="inlineStr"/>
+      <c r="G63" s="76" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="74" t="inlineStr">
+      <c r="A64" s="78" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="74" t="inlineStr">
+      <c r="B64" s="78" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2669,30 +2745,30 @@
           <t>Avvisi pubbliciAvviso si procede alla riassegnazione della posizione organizzativa a supporto delle attività del Servizio 2 “Investimenti in Agricoltu</t>
         </is>
       </c>
-      <c r="D64" s="75" t="inlineStr">
+      <c r="D64" s="79" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-selezione-interna-conferimento-1-posizione-organizzativa-ai-sensi-artt-19-20-ccrl-2022-2024-comparto-non-dirigenziale</t>
         </is>
       </c>
-      <c r="E64" s="74" t="inlineStr">
+      <c r="E64" s="78" t="inlineStr">
         <is>
           <t>09/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F64" s="74" t="inlineStr">
+      <c r="F64" s="78" t="inlineStr">
         <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="G64" s="74" t="inlineStr"/>
+      <c r="G64" s="78" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="72" t="inlineStr">
+      <c r="A65" s="76" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B65" s="72" t="inlineStr">
+      <c r="B65" s="76" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2702,30 +2778,30 @@
           <t>Avvisi pubbliciST-MESSINA - AVVISO di INDAGINE DI MERCATO per affidamento "Interventi manutenzione straordinaria della strada/pista forestale "Annunzi</t>
         </is>
       </c>
-      <c r="D65" s="73" t="inlineStr">
+      <c r="D65" s="77" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-indagine-mercato-affidamento-interventi-manutenzione-straordinaria-stradapista-forestale-annunziata-comune-messina</t>
         </is>
       </c>
-      <c r="E65" s="72" t="inlineStr">
+      <c r="E65" s="76" t="inlineStr">
         <is>
           <t>16/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F65" s="72" t="inlineStr">
+      <c r="F65" s="76" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="G65" s="72" t="inlineStr"/>
+      <c r="G65" s="76" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="74" t="inlineStr">
+      <c r="A66" s="78" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="74" t="inlineStr">
+      <c r="B66" s="78" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2735,30 +2811,30 @@
           <t>Avvisi pubbliciST-MESSINA - AVVISO DI INDAGINE DI MERCATO per affidamento "Interventi manutenzione straordinaria della strada/pista forestale "San Riz</t>
         </is>
       </c>
-      <c r="D66" s="75" t="inlineStr">
+      <c r="D66" s="79" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-indagine-mercato-affidamento-interventi-manutenzione-straordinaria-stradapista-forestale-san-rizzo-san-leone-crupi-madonuzza-comune-messina</t>
         </is>
       </c>
-      <c r="E66" s="74" t="inlineStr">
+      <c r="E66" s="78" t="inlineStr">
         <is>
           <t>16/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F66" s="74" t="inlineStr">
+      <c r="F66" s="78" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="G66" s="74" t="inlineStr"/>
+      <c r="G66" s="78" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="72" t="inlineStr">
+      <c r="A67" s="76" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="72" t="inlineStr">
+      <c r="B67" s="76" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2768,22 +2844,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Manifestazione di interesse per Casaidea 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D67" s="73" t="inlineStr">
+      <c r="D67" s="77" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-casaidea-2026/</t>
         </is>
       </c>
-      <c r="E67" s="72" t="inlineStr"/>
-      <c r="F67" s="72" t="inlineStr"/>
-      <c r="G67" s="72" t="inlineStr"/>
+      <c r="E67" s="76" t="inlineStr"/>
+      <c r="F67" s="76" t="inlineStr"/>
+      <c r="G67" s="76" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="74" t="inlineStr">
+      <c r="A68" s="78" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="74" t="inlineStr">
+      <c r="B68" s="78" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2793,22 +2869,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per il Salone Internazionale del Libro di Torino 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D68" s="75" t="inlineStr">
+      <c r="D68" s="79" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-il-salone-internazionale-del-libro-di-torino-2026/</t>
         </is>
       </c>
-      <c r="E68" s="74" t="inlineStr"/>
-      <c r="F68" s="74" t="inlineStr"/>
-      <c r="G68" s="74" t="inlineStr"/>
+      <c r="E68" s="78" t="inlineStr"/>
+      <c r="F68" s="78" t="inlineStr"/>
+      <c r="G68" s="78" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="72" t="inlineStr">
+      <c r="A69" s="76" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="72" t="inlineStr">
+      <c r="B69" s="76" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2818,30 +2894,30 @@
           <t>Avvisi pubbliciDDG 1112 del 02.04.2026 - Aggiornamento Avviso pubblico n. 4/2024 per l’attuazione del PAR GOL Sicilia da finanziare nell’ambito del Pi</t>
         </is>
       </c>
-      <c r="D69" s="73" t="inlineStr">
+      <c r="D69" s="77" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/ddg-1112-02042026-aggiornamento-avviso-pubblico-n-42024-l-attuazione-par-gol-sicilia-finanziare-nell-ambito-piano-nazionale-ripresa-resilienza-pnrr</t>
         </is>
       </c>
-      <c r="E69" s="72" t="inlineStr">
+      <c r="E69" s="76" t="inlineStr">
         <is>
           <t>05/04/2030 - 00:00</t>
         </is>
       </c>
-      <c r="F69" s="72" t="inlineStr">
+      <c r="F69" s="76" t="inlineStr">
         <is>
           <t>05/04/2030</t>
         </is>
       </c>
-      <c r="G69" s="72" t="inlineStr"/>
+      <c r="G69" s="76" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="74" t="inlineStr">
+      <c r="A70" s="78" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="74" t="inlineStr">
+      <c r="B70" s="78" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2851,30 +2927,30 @@
           <t>Avvisi pubbliciDDG 1113 del  02.04.2026 - Aggiornamento Avviso pubblico n. 2/2022 e s.m.i per l’attuazione del PAR GOL Sicilia da finanziare nell’ambi</t>
         </is>
       </c>
-      <c r="D70" s="75" t="inlineStr">
+      <c r="D70" s="79" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/ddg-1113-02042026-aggiornamento-avviso-pubblico-n-22022-smi-l-attuazione-par-gol-sicilia-finanziare-nell-ambito-piano-nazionale-ripresa-resilienza-pnrr</t>
         </is>
       </c>
-      <c r="E70" s="74" t="inlineStr">
+      <c r="E70" s="78" t="inlineStr">
         <is>
           <t>03/04/2030 - 00:00</t>
         </is>
       </c>
-      <c r="F70" s="74" t="inlineStr">
+      <c r="F70" s="78" t="inlineStr">
         <is>
           <t>03/04/2030</t>
         </is>
       </c>
-      <c r="G70" s="74" t="inlineStr"/>
+      <c r="G70" s="78" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="72" t="inlineStr">
+      <c r="A71" s="76" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B71" s="72" t="inlineStr">
+      <c r="B71" s="76" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2884,22 +2960,22 @@
           <t>Avvisi pubbliciLeggi e scarica l'avvisoScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D71" s="73" t="inlineStr">
+      <c r="D71" s="77" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/proroga-termini-presentazione-candidature-po</t>
         </is>
       </c>
-      <c r="E71" s="72" t="inlineStr"/>
-      <c r="F71" s="72" t="inlineStr"/>
-      <c r="G71" s="72" t="inlineStr"/>
+      <c r="E71" s="76" t="inlineStr"/>
+      <c r="F71" s="76" t="inlineStr"/>
+      <c r="G71" s="76" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="74" t="inlineStr">
+      <c r="A72" s="78" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="74" t="inlineStr">
+      <c r="B72" s="78" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2909,22 +2985,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEComunicare l’inclusione – contest per le istituzioni scolastiche regionaliApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D72" s="75" t="inlineStr">
+      <c r="D72" s="79" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/comunicare-linclusione-contest-per-le-istituzioni-scolastiche-regionali/</t>
         </is>
       </c>
-      <c r="E72" s="74" t="inlineStr"/>
-      <c r="F72" s="74" t="inlineStr"/>
-      <c r="G72" s="74" t="inlineStr"/>
+      <c r="E72" s="78" t="inlineStr"/>
+      <c r="F72" s="78" t="inlineStr"/>
+      <c r="G72" s="78" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="72" t="inlineStr">
+      <c r="A73" s="76" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B73" s="72" t="inlineStr">
+      <c r="B73" s="76" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2934,22 +3010,22 @@
           <t>Avvisi pubbliciAPPROVAZIONE AVVISO PUBBLICOScade il:03/04/2027 - 00:00Leggi di più</t>
         </is>
       </c>
-      <c r="D73" s="73" t="inlineStr">
+      <c r="D73" s="77" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/approvazione-avviso-pubblico</t>
         </is>
       </c>
-      <c r="E73" s="72" t="inlineStr">
+      <c r="E73" s="76" t="inlineStr">
         <is>
           <t>03/04/2027 - 00:00</t>
         </is>
       </c>
-      <c r="F73" s="72" t="inlineStr">
+      <c r="F73" s="76" t="inlineStr">
         <is>
           <t>03/04/2027</t>
         </is>
       </c>
-      <c r="G73" s="72" t="inlineStr"/>
+      <c r="G73" s="76" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="78" t="inlineStr">
@@ -3008,6 +3084,130 @@
         </is>
       </c>
       <c r="G75" s="76" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="82" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="82" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURASostegno agli investimenti nel settore vitivinicolo – campagna 2026/2027ApertoBandi Regionali</t>
+        </is>
+      </c>
+      <c r="D76" s="83" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/sostegno-agli-investimenti-nel-settore-vitivinicolo-campagna-2026-2027/</t>
+        </is>
+      </c>
+      <c r="E76" s="82" t="inlineStr"/>
+      <c r="F76" s="82" t="inlineStr"/>
+      <c r="G76" s="82" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="80" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="80" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>Manifestazioni di interesse9 aprile 2026 -ST PALERMO- Manifestazione di interesse - “Interventi di manutenzione straordinaria della strada-pista fores</t>
+        </is>
+      </c>
+      <c r="D77" s="81" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/9-aprile-2026-st-palermo-manifestazione-interesse-interventi-manutenzione-straordinaria-strada-pista-forestale-monte-cane-comune-caccamo-pa-distretto-forestale</t>
+        </is>
+      </c>
+      <c r="E77" s="80" t="inlineStr">
+        <is>
+          <t>24/04/2026 - 12:00</t>
+        </is>
+      </c>
+      <c r="F77" s="80" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="G77" s="80" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="82" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="82" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>Avvisi pubbliciST-MESSINA - AVVISO DI INDAGINE DI MERCATO per affidamento "Interventi manutenzione straordinaria della strada/pista forestale "Faggita</t>
+        </is>
+      </c>
+      <c r="D78" s="83" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-indagine-mercato-affidamento-interventi-manutenzione-straordinaria-stradapista-forestale-faggita-comune-tripi-me</t>
+        </is>
+      </c>
+      <c r="E78" s="82" t="inlineStr">
+        <is>
+          <t>23/04/2026 - 12:00</t>
+        </is>
+      </c>
+      <c r="F78" s="82" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="G78" s="82" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="80" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="80" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>Avvisi pubbliciST-MESSINA - AVVISO DI INDAGINE DI MERCATO per affidamento "Interventi manutenzione straordinaria della strada/pista forestale "Ferraro</t>
+        </is>
+      </c>
+      <c r="D79" s="81" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-indagine-mercato-affidamento-interventi-manutenzione-straordinaria-stradapista-forestale-ferraro-sanrizzo-badiazza-comune-messina</t>
+        </is>
+      </c>
+      <c r="E79" s="80" t="inlineStr">
+        <is>
+          <t>23/04/2026 - 12:00</t>
+        </is>
+      </c>
+      <c r="F79" s="80" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="G79" s="80" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -3085,6 +3285,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId73"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId78"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3129,7 +3333,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="76" t="inlineStr">
+      <c r="A3" s="80" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -3142,29 +3346,29 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="78" t="inlineStr">
+      <c r="A4" s="82" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="76" t="inlineStr">
+      <c r="A5" s="80" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">

--- a/data/bandi_export.xlsx
+++ b/data/bandi_export.xlsx
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -267,6 +267,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -730,7 +742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -745,7 +757,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏛️  Nuovi Bandi — 10/04/2026 08:18</t>
+          <t>🏛️  Nuovi Bandi — 11/04/2026 07:45</t>
         </is>
       </c>
     </row>
@@ -790,117 +802,55 @@
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="80" t="inlineStr">
+      <c r="B3" s="84" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURASostegno agli investimenti nel settore vitivinicolo – campagna 2026/2027ApertoBandi Regionali</t>
-        </is>
-      </c>
-      <c r="D3" s="81" t="inlineStr">
-        <is>
-          <t>https://www.lazioeuropa.it/bandi/sostegno-agli-investimenti-nel-settore-vitivinicolo-campagna-2026-2027/</t>
-        </is>
-      </c>
-      <c r="E3" s="80" t="inlineStr"/>
-      <c r="F3" s="80" t="inlineStr"/>
+          <t>Comunicazione e informazioneAcquisizione di servizi di comunicazione e informazione – PR Lazio FESR, PR Lazio FSE+ e comunicazione unitariaApertoBandi</t>
+        </is>
+      </c>
+      <c r="D3" s="85" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/acquisizione-di-servizi-di-comunicazione-e-informazione-pr-lazio-fesr-pr-lazio-fse-e-comunicazione-unitaria/</t>
+        </is>
+      </c>
+      <c r="E3" s="84" t="inlineStr"/>
+      <c r="F3" s="84" t="inlineStr"/>
       <c r="G3" s="5" t="inlineStr"/>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="82" t="inlineStr">
+      <c r="B4" s="86" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>Manifestazioni di interesse9 aprile 2026 -ST PALERMO- Manifestazione di interesse - “Interventi di manutenzione straordinaria della strada-pista fores</t>
-        </is>
-      </c>
-      <c r="D4" s="83" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/9-aprile-2026-st-palermo-manifestazione-interesse-interventi-manutenzione-straordinaria-strada-pista-forestale-monte-cane-comune-caccamo-pa-distretto-forestale</t>
-        </is>
-      </c>
-      <c r="E4" s="82" t="inlineStr">
-        <is>
-          <t>24/04/2026 - 12:00</t>
-        </is>
-      </c>
-      <c r="F4" s="82" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
+          <t>Avvisi pubbliciAvviso pubblico di selezione interna, per titoli, per il conferimento, ai sensi degli artt. 21 del CCRL 2022-2024 del comparto non diri</t>
+        </is>
+      </c>
+      <c r="D4" s="87" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-selezione-interna-titoli-conferimento-ai-sensi-artt-21-ccrl-2022-2024-comparto-non-dirigenziale-una-posizione-organizzativa-dipartimento</t>
+        </is>
+      </c>
+      <c r="E4" s="86" t="inlineStr">
+        <is>
+          <t>16/04/2026 - 12:00</t>
+        </is>
+      </c>
+      <c r="F4" s="86" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="G4" s="9" t="inlineStr"/>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" s="80" t="inlineStr">
-        <is>
-          <t>Sicilia</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Avvisi pubbliciST-MESSINA - AVVISO DI INDAGINE DI MERCATO per affidamento "Interventi manutenzione straordinaria della strada/pista forestale "Faggita</t>
-        </is>
-      </c>
-      <c r="D5" s="81" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-indagine-mercato-affidamento-interventi-manutenzione-straordinaria-stradapista-forestale-faggita-comune-tripi-me</t>
-        </is>
-      </c>
-      <c r="E5" s="80" t="inlineStr">
-        <is>
-          <t>23/04/2026 - 12:00</t>
-        </is>
-      </c>
-      <c r="F5" s="80" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="82" t="inlineStr">
-        <is>
-          <t>Sicilia</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>Avvisi pubbliciST-MESSINA - AVVISO DI INDAGINE DI MERCATO per affidamento "Interventi manutenzione straordinaria della strada/pista forestale "Ferraro</t>
-        </is>
-      </c>
-      <c r="D6" s="83" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-indagine-mercato-affidamento-interventi-manutenzione-straordinaria-stradapista-forestale-ferraro-sanrizzo-badiazza-comune-messina</t>
-        </is>
-      </c>
-      <c r="E6" s="82" t="inlineStr">
-        <is>
-          <t>23/04/2026 - 12:00</t>
-        </is>
-      </c>
-      <c r="F6" s="82" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -909,8 +859,6 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -922,7 +870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -972,12 +920,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="78" t="inlineStr">
+      <c r="A2" s="82" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B2" s="78" t="inlineStr">
+      <c r="B2" s="82" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -987,22 +935,22 @@
           <t>FLAG GALPA Costa E-R. Sostituzione del motore principale e dei motori secondari. Secondo bando</t>
         </is>
       </c>
-      <c r="D2" s="79" t="inlineStr">
+      <c r="D2" s="83" t="inlineStr">
         <is>
           <t>https://agricoltura.regione.emilia-romagna.it/feampa-2021-2027/bandi-galpa/2026/galpa-sostituzione-motori-secondo-bando</t>
         </is>
       </c>
-      <c r="E2" s="78" t="inlineStr"/>
-      <c r="F2" s="78" t="inlineStr"/>
-      <c r="G2" s="78" t="inlineStr"/>
+      <c r="E2" s="82" t="inlineStr"/>
+      <c r="F2" s="82" t="inlineStr"/>
+      <c r="G2" s="82" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="76" t="inlineStr">
+      <c r="A3" s="80" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B3" s="76" t="inlineStr">
+      <c r="B3" s="80" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1012,22 +960,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0PRE-SEED 3.0Prossima AperturaFESR</t>
         </is>
       </c>
-      <c r="D3" s="77" t="inlineStr">
+      <c r="D3" s="81" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/pre-seed-3-0/</t>
         </is>
       </c>
-      <c r="E3" s="76" t="inlineStr"/>
-      <c r="F3" s="76" t="inlineStr"/>
-      <c r="G3" s="76" t="inlineStr"/>
+      <c r="E3" s="80" t="inlineStr"/>
+      <c r="F3" s="80" t="inlineStr"/>
+      <c r="G3" s="80" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="78" t="inlineStr">
+      <c r="A4" s="82" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B4" s="78" t="inlineStr">
+      <c r="B4" s="82" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1037,22 +985,22 @@
           <t>ACCESSO AL CREDITO E ALLE GARANZIE PER LE IMPRESEContributo su finanziamenti alle imprese del Lazio erogati su provvista BEIProssima AperturaFESR</t>
         </is>
       </c>
-      <c r="D4" s="79" t="inlineStr">
+      <c r="D4" s="83" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-su-finanziamenti-alle-imprese-del-lazio-erogati-su-provvista-bei/</t>
         </is>
       </c>
-      <c r="E4" s="78" t="inlineStr"/>
-      <c r="F4" s="78" t="inlineStr"/>
-      <c r="G4" s="78" t="inlineStr"/>
+      <c r="E4" s="82" t="inlineStr"/>
+      <c r="F4" s="82" t="inlineStr"/>
+      <c r="G4" s="82" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="76" t="inlineStr">
+      <c r="A5" s="80" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B5" s="76" t="inlineStr">
+      <c r="B5" s="80" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1062,22 +1010,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEIndividuazione degli enti iscritti al Registro unico nazionale del Terzo settoreApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D5" s="77" t="inlineStr">
+      <c r="D5" s="81" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/individuazione-degli-enti-iscritti-al-registro-unico-nazionale-del-terzo-settore/</t>
         </is>
       </c>
-      <c r="E5" s="76" t="inlineStr"/>
-      <c r="F5" s="76" t="inlineStr"/>
-      <c r="G5" s="76" t="inlineStr"/>
+      <c r="E5" s="80" t="inlineStr"/>
+      <c r="F5" s="80" t="inlineStr"/>
+      <c r="G5" s="80" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="78" t="inlineStr">
+      <c r="A6" s="82" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B6" s="78" t="inlineStr">
+      <c r="B6" s="82" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1087,22 +1035,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Technology Transfer LazioApertoFESR</t>
         </is>
       </c>
-      <c r="D6" s="79" t="inlineStr">
+      <c r="D6" s="83" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/technology-transfer-lazio/</t>
         </is>
       </c>
-      <c r="E6" s="78" t="inlineStr"/>
-      <c r="F6" s="78" t="inlineStr"/>
-      <c r="G6" s="78" t="inlineStr"/>
+      <c r="E6" s="82" t="inlineStr"/>
+      <c r="F6" s="82" t="inlineStr"/>
+      <c r="G6" s="82" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="76" t="inlineStr">
+      <c r="A7" s="80" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B7" s="76" t="inlineStr">
+      <c r="B7" s="80" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1112,22 +1060,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Percorso di tutoraggio per le impreseApertoFESR</t>
         </is>
       </c>
-      <c r="D7" s="77" t="inlineStr">
+      <c r="D7" s="81" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/percorso-di-tutoraggio-per-le-imprese/</t>
         </is>
       </c>
-      <c r="E7" s="76" t="inlineStr"/>
-      <c r="F7" s="76" t="inlineStr"/>
-      <c r="G7" s="76" t="inlineStr"/>
+      <c r="E7" s="80" t="inlineStr"/>
+      <c r="F7" s="80" t="inlineStr"/>
+      <c r="G7" s="80" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="78" t="inlineStr">
+      <c r="A8" s="82" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B8" s="78" t="inlineStr">
+      <c r="B8" s="82" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1137,22 +1085,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per partecipare a SMAU Parigi 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D8" s="79" t="inlineStr">
+      <c r="D8" s="83" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-partecipare-a-smau-parigi-2026/</t>
         </is>
       </c>
-      <c r="E8" s="78" t="inlineStr"/>
-      <c r="F8" s="78" t="inlineStr"/>
-      <c r="G8" s="78" t="inlineStr"/>
+      <c r="E8" s="82" t="inlineStr"/>
+      <c r="F8" s="82" t="inlineStr"/>
+      <c r="G8" s="82" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="76" t="inlineStr">
+      <c r="A9" s="80" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B9" s="76" t="inlineStr">
+      <c r="B9" s="80" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1162,22 +1110,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONERiconoscimento della funzione sociale ed educativa degli oratoriApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D9" s="77" t="inlineStr">
+      <c r="D9" s="81" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/riconoscimento-della-funzione-sociale-ed-educativa-degli-oratori/</t>
         </is>
       </c>
-      <c r="E9" s="76" t="inlineStr"/>
-      <c r="F9" s="76" t="inlineStr"/>
-      <c r="G9" s="76" t="inlineStr"/>
+      <c r="E9" s="80" t="inlineStr"/>
+      <c r="F9" s="80" t="inlineStr"/>
+      <c r="G9" s="80" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="78" t="inlineStr">
+      <c r="A10" s="82" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B10" s="78" t="inlineStr">
+      <c r="B10" s="82" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1187,22 +1135,22 @@
           <t>GovernanceIscrizione nell’elenco regionale degli idonei all’esercizio dell’attività di direttore dell’Istituto JemoloApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D10" s="79" t="inlineStr">
+      <c r="D10" s="83" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/iscrizione-nellelenco-regionale-degli-idonei-allesercizio-dellattivita-di-direttore-dellistituto-jemolo/</t>
         </is>
       </c>
-      <c r="E10" s="78" t="inlineStr"/>
-      <c r="F10" s="78" t="inlineStr"/>
-      <c r="G10" s="78" t="inlineStr"/>
+      <c r="E10" s="82" t="inlineStr"/>
+      <c r="F10" s="82" t="inlineStr"/>
+      <c r="G10" s="82" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="76" t="inlineStr">
+      <c r="A11" s="80" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B11" s="76" t="inlineStr">
+      <c r="B11" s="80" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1212,22 +1160,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEVoucher per lo sport – seconda annualitàApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D11" s="77" t="inlineStr">
+      <c r="D11" s="81" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/voucher-per-lo-sport-seconda-annualita/</t>
         </is>
       </c>
-      <c r="E11" s="76" t="inlineStr"/>
-      <c r="F11" s="76" t="inlineStr"/>
-      <c r="G11" s="76" t="inlineStr"/>
+      <c r="E11" s="80" t="inlineStr"/>
+      <c r="F11" s="80" t="inlineStr"/>
+      <c r="G11" s="80" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="78" t="inlineStr">
+      <c r="A12" s="82" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B12" s="78" t="inlineStr">
+      <c r="B12" s="82" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1237,22 +1185,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEBonus occupazionale SALGOApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D12" s="79" t="inlineStr">
+      <c r="D12" s="83" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/bonus-occupazionale-salgo/</t>
         </is>
       </c>
-      <c r="E12" s="78" t="inlineStr"/>
-      <c r="F12" s="78" t="inlineStr"/>
-      <c r="G12" s="78" t="inlineStr"/>
+      <c r="E12" s="82" t="inlineStr"/>
+      <c r="F12" s="82" t="inlineStr"/>
+      <c r="G12" s="82" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="76" t="inlineStr">
+      <c r="A13" s="80" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B13" s="76" t="inlineStr">
+      <c r="B13" s="80" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1262,22 +1210,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEContributo di Libertà per le donne che hanno subito violenzaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D13" s="77" t="inlineStr">
+      <c r="D13" s="81" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-di-liberta-per-le-donne-che-hanno-subito-violenza/</t>
         </is>
       </c>
-      <c r="E13" s="76" t="inlineStr"/>
-      <c r="F13" s="76" t="inlineStr"/>
-      <c r="G13" s="76" t="inlineStr"/>
+      <c r="E13" s="80" t="inlineStr"/>
+      <c r="F13" s="80" t="inlineStr"/>
+      <c r="G13" s="80" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="78" t="inlineStr">
+      <c r="A14" s="82" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B14" s="78" t="inlineStr">
+      <c r="B14" s="82" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1287,22 +1235,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURAInterventi straordinari di valorizzazione del patrimonio culturale del LazioApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D14" s="79" t="inlineStr">
+      <c r="D14" s="83" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/interventi-straordinari-di-valorizzazione-del-patrimonio-culturale-del-lazio/</t>
         </is>
       </c>
-      <c r="E14" s="78" t="inlineStr"/>
-      <c r="F14" s="78" t="inlineStr"/>
-      <c r="G14" s="78" t="inlineStr"/>
+      <c r="E14" s="82" t="inlineStr"/>
+      <c r="F14" s="82" t="inlineStr"/>
+      <c r="G14" s="82" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="76" t="inlineStr">
+      <c r="A15" s="80" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B15" s="76" t="inlineStr">
+      <c r="B15" s="80" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1312,30 +1260,30 @@
           <t>Bandi di garaBANDO ATTUAZIONE Ob. 1.1 Azione 1 codice 111102 _DIV - "SOSTEGNO ALLA DIVERSIFICAZIONE E NUOVE FORME DI REDDITO PER LA PICCOLA PESCA COST</t>
         </is>
       </c>
-      <c r="D15" s="77" t="inlineStr">
+      <c r="D15" s="81" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/bando-avviso-regia-ob-11-azione-1-codice-111102-div-sostegno-alla-diversificazione-nuove-forme-reddito-piccola-pesca-costiera</t>
         </is>
       </c>
-      <c r="E15" s="76" t="inlineStr">
+      <c r="E15" s="80" t="inlineStr">
         <is>
           <t>07/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F15" s="76" t="inlineStr">
+      <c r="F15" s="80" t="inlineStr">
         <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="G15" s="76" t="inlineStr"/>
+      <c r="G15" s="80" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="78" t="inlineStr">
+      <c r="A16" s="82" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B16" s="78" t="inlineStr">
+      <c r="B16" s="82" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1345,30 +1293,30 @@
           <t>Avvisi pubblici09 marzo 2026 - ST SIRACUSA - AVVISO PUBBLICO PER LA COSTITUZIONE DI ELENCHI DI OPERATORI ECONOMICI PER L’ACQUISIZIONE DI BENI E SERVIZ</t>
         </is>
       </c>
-      <c r="D16" s="79" t="inlineStr">
+      <c r="D16" s="83" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/09-marzo-2026-st-siracusa-avviso-pubblico-costituzione-elenchi-operatori-economici-l-acquisizione-beni-servizi</t>
         </is>
       </c>
-      <c r="E16" s="78" t="inlineStr">
+      <c r="E16" s="82" t="inlineStr">
         <is>
           <t>31/12/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F16" s="78" t="inlineStr">
+      <c r="F16" s="82" t="inlineStr">
         <is>
           <t>31/12/2026</t>
         </is>
       </c>
-      <c r="G16" s="78" t="inlineStr"/>
+      <c r="G16" s="82" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="76" t="inlineStr">
+      <c r="A17" s="80" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B17" s="76" t="inlineStr">
+      <c r="B17" s="80" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1378,30 +1326,30 @@
           <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScade il:19/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D17" s="77" t="inlineStr">
+      <c r="D17" s="81" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
         </is>
       </c>
-      <c r="E17" s="76" t="inlineStr">
+      <c r="E17" s="80" t="inlineStr">
         <is>
           <t>19/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F17" s="76" t="inlineStr">
+      <c r="F17" s="80" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G17" s="76" t="inlineStr"/>
+      <c r="G17" s="80" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="78" t="inlineStr">
+      <c r="A18" s="82" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B18" s="78" t="inlineStr">
+      <c r="B18" s="82" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1411,22 +1359,22 @@
           <t>Manifestazioni di interesseAvviso Manifestazione Interesse DISTRIBUTORI AUTOMATICI di bevande e snackScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D18" s="79" t="inlineStr">
+      <c r="D18" s="83" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-distributori-automatici-bevande-snack</t>
         </is>
       </c>
-      <c r="E18" s="78" t="inlineStr"/>
-      <c r="F18" s="78" t="inlineStr"/>
-      <c r="G18" s="78" t="inlineStr"/>
+      <c r="E18" s="82" t="inlineStr"/>
+      <c r="F18" s="82" t="inlineStr"/>
+      <c r="G18" s="82" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="76" t="inlineStr">
+      <c r="A19" s="80" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B19" s="76" t="inlineStr">
+      <c r="B19" s="80" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1436,30 +1384,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D19" s="77" t="inlineStr">
+      <c r="D19" s="81" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo</t>
         </is>
       </c>
-      <c r="E19" s="76" t="inlineStr">
+      <c r="E19" s="80" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F19" s="76" t="inlineStr">
+      <c r="F19" s="80" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G19" s="76" t="inlineStr"/>
+      <c r="G19" s="80" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="78" t="inlineStr">
+      <c r="A20" s="82" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B20" s="78" t="inlineStr">
+      <c r="B20" s="82" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1469,30 +1417,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D20" s="79" t="inlineStr">
+      <c r="D20" s="83" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo-0</t>
         </is>
       </c>
-      <c r="E20" s="78" t="inlineStr">
+      <c r="E20" s="82" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F20" s="78" t="inlineStr">
+      <c r="F20" s="82" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G20" s="78" t="inlineStr"/>
+      <c r="G20" s="82" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="76" t="inlineStr">
+      <c r="A21" s="80" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B21" s="76" t="inlineStr">
+      <c r="B21" s="80" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1502,22 +1450,22 @@
           <t>Manifestazioni di interesseST SIRACUSA - AVVISO DI MANIFESTAZIONE DI INTERESSE - Fornitura applicativo extracontabile per la gestione progetti, ecc. e</t>
         </is>
       </c>
-      <c r="D21" s="77" t="inlineStr">
+      <c r="D21" s="81" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-siracusa-avviso-manifestazione-interesse-fornitura-applicativo-extracontabile-gestione-progetti-ecc-applicativo-gestione-ed-elaborazione-informatizzata-paghe</t>
         </is>
       </c>
-      <c r="E21" s="76" t="inlineStr"/>
-      <c r="F21" s="76" t="inlineStr"/>
-      <c r="G21" s="76" t="inlineStr"/>
+      <c r="E21" s="80" t="inlineStr"/>
+      <c r="F21" s="80" t="inlineStr"/>
+      <c r="G21" s="80" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="78" t="inlineStr">
+      <c r="A22" s="82" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B22" s="78" t="inlineStr">
+      <c r="B22" s="82" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1527,30 +1475,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile sito nel Comune di Capo D'Orlando, Via Trazzera MarinaScade il:25/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D22" s="79" t="inlineStr">
+      <c r="D22" s="83" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-sito-nel-comune-capo-d-orlando-trazzera-marina</t>
         </is>
       </c>
-      <c r="E22" s="78" t="inlineStr">
+      <c r="E22" s="82" t="inlineStr">
         <is>
           <t>25/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F22" s="78" t="inlineStr">
+      <c r="F22" s="82" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="G22" s="78" t="inlineStr"/>
+      <c r="G22" s="82" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="76" t="inlineStr">
+      <c r="A23" s="80" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B23" s="76" t="inlineStr">
+      <c r="B23" s="80" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1560,22 +1508,22 @@
           <t xml:space="preserve">Avvisi pubbliciST CATANIA - Programma Regionale FESR Sicilia 2021-2027 - Azione 2.4.4 - “Interventi per la riduzione del rischio incendi” - AVVISO DI </t>
         </is>
       </c>
-      <c r="D23" s="77" t="inlineStr">
+      <c r="D23" s="81" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-catania-programma-regionale-fesr-sicilia-2021-2027-azione-244-interventi-riduzione-rischio-incendi-avviso-indagine-mercato</t>
         </is>
       </c>
-      <c r="E23" s="76" t="inlineStr"/>
-      <c r="F23" s="76" t="inlineStr"/>
-      <c r="G23" s="76" t="inlineStr"/>
+      <c r="E23" s="80" t="inlineStr"/>
+      <c r="F23" s="80" t="inlineStr"/>
+      <c r="G23" s="80" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="78" t="inlineStr">
+      <c r="A24" s="82" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B24" s="78" t="inlineStr">
+      <c r="B24" s="82" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1585,22 +1533,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per ROMICS – Primavera 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D24" s="79" t="inlineStr">
+      <c r="D24" s="83" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-romics-primavera-2026/</t>
         </is>
       </c>
-      <c r="E24" s="78" t="inlineStr"/>
-      <c r="F24" s="78" t="inlineStr"/>
-      <c r="G24" s="78" t="inlineStr"/>
+      <c r="E24" s="82" t="inlineStr"/>
+      <c r="F24" s="82" t="inlineStr"/>
+      <c r="G24" s="82" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="76" t="inlineStr">
+      <c r="A25" s="80" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B25" s="76" t="inlineStr">
+      <c r="B25" s="80" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1610,22 +1558,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Cinema International 2026 – I edizioneApertoFESR</t>
         </is>
       </c>
-      <c r="D25" s="77" t="inlineStr">
+      <c r="D25" s="81" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lazio-cinema-international-2026-i-edizione/</t>
         </is>
       </c>
-      <c r="E25" s="76" t="inlineStr"/>
-      <c r="F25" s="76" t="inlineStr"/>
-      <c r="G25" s="76" t="inlineStr"/>
+      <c r="E25" s="80" t="inlineStr"/>
+      <c r="F25" s="80" t="inlineStr"/>
+      <c r="G25" s="80" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="78" t="inlineStr">
+      <c r="A26" s="82" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B26" s="78" t="inlineStr">
+      <c r="B26" s="82" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1635,22 +1583,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEManifestazioni di interesse alla costituzione di due nuove Fondazioni I.T.S. AcademyApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D26" s="79" t="inlineStr">
+      <c r="D26" s="83" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazioni-di-interesse-alla-costituzione-di-due-nuove-fondazioni-i-t-s-academy/</t>
         </is>
       </c>
-      <c r="E26" s="78" t="inlineStr"/>
-      <c r="F26" s="78" t="inlineStr"/>
-      <c r="G26" s="78" t="inlineStr"/>
+      <c r="E26" s="82" t="inlineStr"/>
+      <c r="F26" s="82" t="inlineStr"/>
+      <c r="G26" s="82" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="76" t="inlineStr">
+      <c r="A27" s="80" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B27" s="76" t="inlineStr">
+      <c r="B27" s="80" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1660,22 +1608,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURAContributi per sostenere la ripresa del settore della pescaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D27" s="77" t="inlineStr">
+      <c r="D27" s="81" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributi-per-sostenere-la-ripresa-del-settore-della-pesca/</t>
         </is>
       </c>
-      <c r="E27" s="76" t="inlineStr"/>
-      <c r="F27" s="76" t="inlineStr"/>
-      <c r="G27" s="76" t="inlineStr"/>
+      <c r="E27" s="80" t="inlineStr"/>
+      <c r="F27" s="80" t="inlineStr"/>
+      <c r="G27" s="80" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="78" t="inlineStr">
+      <c r="A28" s="82" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B28" s="78" t="inlineStr">
+      <c r="B28" s="82" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1685,30 +1633,30 @@
           <t>Manifestazioni di interesseAVVISO - Manifestazione Interesse “Storytelling aziendale” Expo Wild Natura - Caccia - Pesca. Misterbianco (CT), 10-12 apri</t>
         </is>
       </c>
-      <c r="D28" s="79" t="inlineStr">
+      <c r="D28" s="83" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-storytelling-aziendale-expo-wild-natura-caccia-pesca-misterbianco-ct-10-12-aprile-2026</t>
         </is>
       </c>
-      <c r="E28" s="78" t="inlineStr">
+      <c r="E28" s="82" t="inlineStr">
         <is>
           <t>30/03/2026 - 13:00</t>
         </is>
       </c>
-      <c r="F28" s="78" t="inlineStr">
+      <c r="F28" s="82" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G28" s="78" t="inlineStr"/>
+      <c r="G28" s="82" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="76" t="inlineStr">
+      <c r="A29" s="80" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B29" s="76" t="inlineStr">
+      <c r="B29" s="80" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1718,30 +1666,30 @@
           <t>Manifestazioni di interesseInvaso Lentini - Interventi di ripristino delle pareti esterne in cls della Torre di presa Sud e della trave d’appoggio del</t>
         </is>
       </c>
-      <c r="D29" s="77" t="inlineStr">
+      <c r="D29" s="81" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/invaso-lentini-interventi-ripristino-pareti-esterne-cls-torre-presa-sud-trave-d-appoggio-cavalcavia-collegamento-alla-stessa-torre</t>
         </is>
       </c>
-      <c r="E29" s="76" t="inlineStr">
+      <c r="E29" s="80" t="inlineStr">
         <is>
           <t>19/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F29" s="76" t="inlineStr">
+      <c r="F29" s="80" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G29" s="76" t="inlineStr"/>
+      <c r="G29" s="80" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="78" t="inlineStr">
+      <c r="A30" s="82" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="B30" s="78" t="inlineStr">
+      <c r="B30" s="82" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1751,22 +1699,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURARistrutturazione e riconversione vigneti – campagna 2026-2027ApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D30" s="79" t="inlineStr">
+      <c r="D30" s="83" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/ristrutturazione-e-riconversione-vigneti-campagna-2026-2027/</t>
         </is>
       </c>
-      <c r="E30" s="78" t="inlineStr"/>
-      <c r="F30" s="78" t="inlineStr"/>
-      <c r="G30" s="78" t="inlineStr"/>
+      <c r="E30" s="82" t="inlineStr"/>
+      <c r="F30" s="82" t="inlineStr"/>
+      <c r="G30" s="82" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="76" t="inlineStr">
+      <c r="A31" s="80" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="B31" s="76" t="inlineStr">
+      <c r="B31" s="80" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1776,30 +1724,30 @@
           <t>Manifestazioni di interessePR FESR 2021/27 Azione 1.3.3 e del POC 2014/20 - Azione 1.3.1  - Avviso a manifestazione d’interesse eventi fieristici inte</t>
         </is>
       </c>
-      <c r="D31" s="77" t="inlineStr">
+      <c r="D31" s="81" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-d-interesse-eventi-fieristici-internazionali-marzo-dicembre-2026</t>
         </is>
       </c>
-      <c r="E31" s="76" t="inlineStr">
+      <c r="E31" s="80" t="inlineStr">
         <is>
           <t>30/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F31" s="76" t="inlineStr">
+      <c r="F31" s="80" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="G31" s="76" t="inlineStr"/>
+      <c r="G31" s="80" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="78" t="inlineStr">
+      <c r="A32" s="82" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="B32" s="78" t="inlineStr">
+      <c r="B32" s="82" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1809,22 +1757,22 @@
           <t>INTERNAZIONALIZZAZIONEL’Ecosistema dell’Innovazione a INNOVIT – Focus S3ApertoFESR</t>
         </is>
       </c>
-      <c r="D32" s="79" t="inlineStr">
+      <c r="D32" s="83" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lecosistema-dellinnovazione-a-innovit-focus-s3/</t>
         </is>
       </c>
-      <c r="E32" s="78" t="inlineStr"/>
-      <c r="F32" s="78" t="inlineStr"/>
-      <c r="G32" s="78" t="inlineStr"/>
+      <c r="E32" s="82" t="inlineStr"/>
+      <c r="F32" s="82" t="inlineStr"/>
+      <c r="G32" s="82" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="76" t="inlineStr">
+      <c r="A33" s="80" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="B33" s="76" t="inlineStr">
+      <c r="B33" s="80" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1834,22 +1782,22 @@
           <t>Manifestazioni di interessePR FESR SICILIA 2021/27 - NUOVO Avviso a manifestazione d’interesse per esperti valutatoriScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D33" s="77" t="inlineStr">
+      <c r="D33" s="81" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/pr-fesr-sicilia-202127-nuovo-avviso-manifestazione-d-interesse-esperti-valutatori</t>
         </is>
       </c>
-      <c r="E33" s="76" t="inlineStr"/>
-      <c r="F33" s="76" t="inlineStr"/>
-      <c r="G33" s="76" t="inlineStr"/>
+      <c r="E33" s="80" t="inlineStr"/>
+      <c r="F33" s="80" t="inlineStr"/>
+      <c r="G33" s="80" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="78" t="inlineStr">
+      <c r="A34" s="82" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="B34" s="78" t="inlineStr">
+      <c r="B34" s="82" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -1859,22 +1807,22 @@
           <t>Bando 2026 per contributi dedicati alla manutenzione della rete dei percorsi escursionistici</t>
         </is>
       </c>
-      <c r="D34" s="79" t="inlineStr">
+      <c r="D34" s="83" t="inlineStr">
         <is>
           <t>https://ambiente.regione.emilia-romagna.it/it/parchi-natura2000/bandi/bando-2026-per-contributi-dedicati-alla-manutenzione-della-rete-dei-percorsi-escursionistici</t>
         </is>
       </c>
-      <c r="E34" s="78" t="inlineStr"/>
-      <c r="F34" s="78" t="inlineStr"/>
-      <c r="G34" s="78" t="inlineStr"/>
+      <c r="E34" s="82" t="inlineStr"/>
+      <c r="F34" s="82" t="inlineStr"/>
+      <c r="G34" s="82" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="76" t="inlineStr">
+      <c r="A35" s="80" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="B35" s="76" t="inlineStr">
+      <c r="B35" s="80" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1884,22 +1832,22 @@
           <t>Programma regionale in favore delle tradizioni storiche, artistiche, religiose e popolari (2026) – manifestazioni d’interesseApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D35" s="77" t="inlineStr">
+      <c r="D35" s="81" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/programma-regionale-in-favore-delle-tradizioni-storiche-artistiche-religiose-e-popolari-2026-manifestazioni-dinteresse/</t>
         </is>
       </c>
-      <c r="E35" s="76" t="inlineStr"/>
-      <c r="F35" s="76" t="inlineStr"/>
-      <c r="G35" s="76" t="inlineStr"/>
+      <c r="E35" s="80" t="inlineStr"/>
+      <c r="F35" s="80" t="inlineStr"/>
+      <c r="G35" s="80" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="78" t="inlineStr">
+      <c r="A36" s="82" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B36" s="78" t="inlineStr">
+      <c r="B36" s="82" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1909,22 +1857,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEBuoni servizio per le persone non autosufficienti nel territorio del LazioProssima AperturaFSE / FSE+</t>
         </is>
       </c>
-      <c r="D36" s="79" t="inlineStr">
+      <c r="D36" s="83" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/buoni-servizio-per-le-persone-non-autosufficienti-nel-territorio-del-lazio/</t>
         </is>
       </c>
-      <c r="E36" s="78" t="inlineStr"/>
-      <c r="F36" s="78" t="inlineStr"/>
-      <c r="G36" s="78" t="inlineStr"/>
+      <c r="E36" s="82" t="inlineStr"/>
+      <c r="F36" s="82" t="inlineStr"/>
+      <c r="G36" s="82" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="76" t="inlineStr">
+      <c r="A37" s="80" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B37" s="76" t="inlineStr">
+      <c r="B37" s="80" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1934,22 +1882,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONERimborso delle rette dei servizi educativi nel territorio del LazioProssima AperturaFSE / FSE+</t>
         </is>
       </c>
-      <c r="D37" s="77" t="inlineStr">
+      <c r="D37" s="81" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/rimborso-delle-rette-dei-servizi-educativi-nel-territorio-del-lazio/</t>
         </is>
       </c>
-      <c r="E37" s="76" t="inlineStr"/>
-      <c r="F37" s="76" t="inlineStr"/>
-      <c r="G37" s="76" t="inlineStr"/>
+      <c r="E37" s="80" t="inlineStr"/>
+      <c r="F37" s="80" t="inlineStr"/>
+      <c r="G37" s="80" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="78" t="inlineStr">
+      <c r="A38" s="82" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B38" s="78" t="inlineStr">
+      <c r="B38" s="82" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1959,30 +1907,30 @@
           <t>Manifestazioni di interesseATTO DI INTERPELLO PER L’AFFIDAMENTO DELL’INCARICO DI COLLAUDO STATICO DELLE STRUTTURE - Diga di Pietrarossa (Progetto ex C</t>
         </is>
       </c>
-      <c r="D38" s="79" t="inlineStr">
+      <c r="D38" s="83" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/atto-interpello-l-affidamento-incarico-collaudo-statico-strutture-diga-pietrarossa-progetto-ex-casmez-303219</t>
         </is>
       </c>
-      <c r="E38" s="78" t="inlineStr">
+      <c r="E38" s="82" t="inlineStr">
         <is>
           <t>27/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F38" s="78" t="inlineStr">
+      <c r="F38" s="82" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="G38" s="78" t="inlineStr"/>
+      <c r="G38" s="82" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="76" t="inlineStr">
+      <c r="A39" s="80" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B39" s="76" t="inlineStr">
+      <c r="B39" s="80" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1992,30 +1940,30 @@
           <t>Manifestazioni di interesseAvviso alle Case  Editrici della Regione siciliana per la partecipazione al Salone del Libro di Torino, 14-18  maggio 2026.</t>
         </is>
       </c>
-      <c r="D39" s="77" t="inlineStr">
+      <c r="D39" s="81" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/manifestazione-d-interesse-partecipare-al-xxxviii-salone-libro-torino-14-al-18-maggio-2026-attraverso-l-esposizione-pubblicazioni-presso-stand-assessorato-beni</t>
         </is>
       </c>
-      <c r="E39" s="76" t="inlineStr">
+      <c r="E39" s="80" t="inlineStr">
         <is>
           <t>30/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F39" s="76" t="inlineStr">
+      <c r="F39" s="80" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="G39" s="76" t="inlineStr"/>
+      <c r="G39" s="80" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="78" t="inlineStr">
+      <c r="A40" s="82" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B40" s="78" t="inlineStr">
+      <c r="B40" s="82" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2025,30 +1973,30 @@
           <t xml:space="preserve">Manifestazioni di interessePR FESR SICILIA 2021/27 - NUOVO Avviso a manifestazione d’interesse per esperti valutatoriScade il:06/04/2026 - 23:59Leggi </t>
         </is>
       </c>
-      <c r="D40" s="79" t="inlineStr">
+      <c r="D40" s="83" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/pr-fesr-sicilia-202127-nuovo-avviso-manifestazione-d-interesse-esperti-valutatori</t>
         </is>
       </c>
-      <c r="E40" s="78" t="inlineStr">
+      <c r="E40" s="82" t="inlineStr">
         <is>
           <t>06/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F40" s="78" t="inlineStr">
+      <c r="F40" s="82" t="inlineStr">
         <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="G40" s="78" t="inlineStr"/>
+      <c r="G40" s="82" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="76" t="inlineStr">
+      <c r="A41" s="80" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B41" s="76" t="inlineStr">
+      <c r="B41" s="80" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2058,22 +2006,22 @@
           <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D41" s="77" t="inlineStr">
+      <c r="D41" s="81" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
         </is>
       </c>
-      <c r="E41" s="76" t="inlineStr"/>
-      <c r="F41" s="76" t="inlineStr"/>
-      <c r="G41" s="76" t="inlineStr"/>
+      <c r="E41" s="80" t="inlineStr"/>
+      <c r="F41" s="80" t="inlineStr"/>
+      <c r="G41" s="80" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="78" t="inlineStr">
+      <c r="A42" s="82" t="inlineStr">
         <is>
           <t>24/03/2026</t>
         </is>
       </c>
-      <c r="B42" s="78" t="inlineStr">
+      <c r="B42" s="82" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2083,22 +2031,22 @@
           <t>GAL del Ducato - Promozione di fiere agroalimentari e delle filiere del cibo – Bando per Enti pubblici (DU AS 05B)</t>
         </is>
       </c>
-      <c r="D42" s="79" t="inlineStr">
+      <c r="D42" s="83" t="inlineStr">
         <is>
           <t>https://agricoltura.regione.emilia-romagna.it/sviluppo-rurale-23-27/opportunita/bandi-gal/2026/du_as05b-promozione-di-fiere-agroalimentari-e-delle-filiere-del-cibo-bando-per-enti-pubblici</t>
         </is>
       </c>
-      <c r="E42" s="78" t="inlineStr"/>
-      <c r="F42" s="78" t="inlineStr"/>
-      <c r="G42" s="78" t="inlineStr"/>
+      <c r="E42" s="82" t="inlineStr"/>
+      <c r="F42" s="82" t="inlineStr"/>
+      <c r="G42" s="82" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="76" t="inlineStr">
+      <c r="A43" s="80" t="inlineStr">
         <is>
           <t>24/03/2026</t>
         </is>
       </c>
-      <c r="B43" s="76" t="inlineStr">
+      <c r="B43" s="80" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2108,30 +2056,30 @@
           <t>Manifestazioni di interesseAVVISO PUBBLICO PER MANIFESTAZIONE DI INTERESSE FINALIZZATA ALL'ASSEGNAZIONE DI SPAZI ESPOSITIVI (CORNER GRATUITI) ALL'INTE</t>
         </is>
       </c>
-      <c r="D43" s="77" t="inlineStr">
+      <c r="D43" s="81" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-manifestazione-interesse-finalizzata-all-assegnazione-spazi-espositivi-corner-gratuiti-all-interno-stand-istituzionale-dsrt-manifestazione</t>
         </is>
       </c>
-      <c r="E43" s="76" t="inlineStr">
+      <c r="E43" s="80" t="inlineStr">
         <is>
           <t>30/03/2026 - 13:00</t>
         </is>
       </c>
-      <c r="F43" s="76" t="inlineStr">
+      <c r="F43" s="80" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G43" s="76" t="inlineStr"/>
+      <c r="G43" s="80" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="78" t="inlineStr">
+      <c r="A44" s="82" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B44" s="78" t="inlineStr">
+      <c r="B44" s="82" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2141,22 +2089,22 @@
           <t>Avviso per la concessione di contributi per eventi sportivi realizzati in Emilia-Romagna - Anno 2026</t>
         </is>
       </c>
-      <c r="D44" s="79" t="inlineStr">
+      <c r="D44" s="83" t="inlineStr">
         <is>
           <t>https://www.regione.emilia-romagna.it/sport/bandi/2026/bando-2026</t>
         </is>
       </c>
-      <c r="E44" s="78" t="inlineStr"/>
-      <c r="F44" s="78" t="inlineStr"/>
-      <c r="G44" s="78" t="inlineStr"/>
+      <c r="E44" s="82" t="inlineStr"/>
+      <c r="F44" s="82" t="inlineStr"/>
+      <c r="G44" s="82" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="76" t="inlineStr">
+      <c r="A45" s="80" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B45" s="76" t="inlineStr">
+      <c r="B45" s="80" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2166,22 +2114,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Street art 2026Prossima AperturaBandi Regionali</t>
         </is>
       </c>
-      <c r="D45" s="77" t="inlineStr">
+      <c r="D45" s="81" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lazio-street-art-2026/</t>
         </is>
       </c>
-      <c r="E45" s="76" t="inlineStr"/>
-      <c r="F45" s="76" t="inlineStr"/>
-      <c r="G45" s="76" t="inlineStr"/>
+      <c r="E45" s="80" t="inlineStr"/>
+      <c r="F45" s="80" t="inlineStr"/>
+      <c r="G45" s="80" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="78" t="inlineStr">
+      <c r="A46" s="82" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B46" s="78" t="inlineStr">
+      <c r="B46" s="82" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2191,30 +2139,30 @@
           <t>Manifestazioni di interesseManifestazione di interesse per la partecipazione all’evento “R2I Italy 2026” – Bologna, 12-13/05/2026Scade il:03/04/2026 -</t>
         </is>
       </c>
-      <c r="D46" s="79" t="inlineStr">
+      <c r="D46" s="83" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/manifestazione-interesse-partecipazione-all-evento-r2i-italy-2026-bologna-12-13052026</t>
         </is>
       </c>
-      <c r="E46" s="78" t="inlineStr">
+      <c r="E46" s="82" t="inlineStr">
         <is>
           <t>03/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F46" s="78" t="inlineStr">
+      <c r="F46" s="82" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="G46" s="78" t="inlineStr"/>
+      <c r="G46" s="82" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="76" t="inlineStr">
+      <c r="A47" s="80" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B47" s="76" t="inlineStr">
+      <c r="B47" s="80" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2224,30 +2172,30 @@
           <t>Manifestazioni di interesseST SIRACUSA - AVVISO PER MANIFESTAZIONE DI INTERESSE - Selezione di n. 5 unità di personale internoScade il:20/04/2026 - 12</t>
         </is>
       </c>
-      <c r="D47" s="77" t="inlineStr">
+      <c r="D47" s="81" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/24-marzo-2026-st-siracusa-avviso-manifestazione-interesse-selezione-n-5-unita-personale-interno</t>
         </is>
       </c>
-      <c r="E47" s="76" t="inlineStr">
+      <c r="E47" s="80" t="inlineStr">
         <is>
           <t>20/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F47" s="76" t="inlineStr">
+      <c r="F47" s="80" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="G47" s="76" t="inlineStr"/>
+      <c r="G47" s="80" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="78" t="inlineStr">
+      <c r="A48" s="82" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B48" s="78" t="inlineStr">
+      <c r="B48" s="82" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2257,30 +2205,30 @@
           <t>Avvisi pubbliciRevoca dell’avviso di concessione a titolo gratuito del 16.12.2025 inerente all’immobile di seguito identificato e contestuale nuovo av</t>
         </is>
       </c>
-      <c r="D48" s="79" t="inlineStr">
+      <c r="D48" s="83" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/revoca-avviso-concessione-titolo-gratuito-16122025-inerente-all-immobile-seguito-identificato-contestuale-nuovo-avviso-concessione-titolo-oneroso-stesso-sito-nel</t>
         </is>
       </c>
-      <c r="E48" s="78" t="inlineStr">
+      <c r="E48" s="82" t="inlineStr">
         <is>
           <t>08/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F48" s="78" t="inlineStr">
+      <c r="F48" s="82" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="G48" s="78" t="inlineStr"/>
+      <c r="G48" s="82" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="76" t="inlineStr">
+      <c r="A49" s="80" t="inlineStr">
         <is>
           <t>26/03/2026</t>
         </is>
       </c>
-      <c r="B49" s="76" t="inlineStr">
+      <c r="B49" s="80" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2290,22 +2238,22 @@
           <t>Bando studi di fattibilità per fusioni di Comuni</t>
         </is>
       </c>
-      <c r="D49" s="77" t="inlineStr">
+      <c r="D49" s="81" t="inlineStr">
         <is>
           <t>https://www.regione.emilia-romagna.it/autonomie-locali/bandi/bando_studi_fattibilita_fusioni_comuni</t>
         </is>
       </c>
-      <c r="E49" s="76" t="inlineStr"/>
-      <c r="F49" s="76" t="inlineStr"/>
-      <c r="G49" s="76" t="inlineStr"/>
+      <c r="E49" s="80" t="inlineStr"/>
+      <c r="F49" s="80" t="inlineStr"/>
+      <c r="G49" s="80" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="78" t="inlineStr">
+      <c r="A50" s="82" t="inlineStr">
         <is>
           <t>26/03/2026</t>
         </is>
       </c>
-      <c r="B50" s="78" t="inlineStr">
+      <c r="B50" s="82" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2315,30 +2263,30 @@
           <t xml:space="preserve">Manifestazioni di interesseAvviso pubblico di selezione interna, per titoli, per il conferimento di PO e professionali, ai sensi degli artt. 19, 20 e </t>
         </is>
       </c>
-      <c r="D50" s="79" t="inlineStr">
+      <c r="D50" s="83" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-selezione-interna-titoli-conferimento-po-professionali-ai-sensi-artt-19-20-21-ccrl-20222024-comparto-non-dirigenziale</t>
         </is>
       </c>
-      <c r="E50" s="78" t="inlineStr">
+      <c r="E50" s="82" t="inlineStr">
         <is>
           <t>30/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F50" s="78" t="inlineStr">
+      <c r="F50" s="82" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G50" s="78" t="inlineStr"/>
+      <c r="G50" s="82" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="76" t="inlineStr">
+      <c r="A51" s="80" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="B51" s="76" t="inlineStr">
+      <c r="B51" s="80" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2348,22 +2296,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0PRE-SEED 3.0ApertoFESR</t>
         </is>
       </c>
-      <c r="D51" s="77" t="inlineStr">
+      <c r="D51" s="81" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/pre-seed-3-0/</t>
         </is>
       </c>
-      <c r="E51" s="76" t="inlineStr"/>
-      <c r="F51" s="76" t="inlineStr"/>
-      <c r="G51" s="76" t="inlineStr"/>
+      <c r="E51" s="80" t="inlineStr"/>
+      <c r="F51" s="80" t="inlineStr"/>
+      <c r="G51" s="80" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="78" t="inlineStr">
+      <c r="A52" s="82" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B52" s="78" t="inlineStr">
+      <c r="B52" s="82" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2373,30 +2321,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “So</t>
         </is>
       </c>
-      <c r="D52" s="79" t="inlineStr">
+      <c r="D52" s="83" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-termini-imerese-locta-piazza-marina</t>
         </is>
       </c>
-      <c r="E52" s="78" t="inlineStr">
+      <c r="E52" s="82" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F52" s="78" t="inlineStr">
+      <c r="F52" s="82" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G52" s="78" t="inlineStr"/>
+      <c r="G52" s="82" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="76" t="inlineStr">
+      <c r="A53" s="80" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B53" s="76" t="inlineStr">
+      <c r="B53" s="80" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2406,30 +2354,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, Sig</t>
         </is>
       </c>
-      <c r="D53" s="77" t="inlineStr">
+      <c r="D53" s="81" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-porto-empedocle-locta-punta-piccola</t>
         </is>
       </c>
-      <c r="E53" s="76" t="inlineStr">
+      <c r="E53" s="80" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F53" s="76" t="inlineStr">
+      <c r="F53" s="80" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G53" s="76" t="inlineStr"/>
+      <c r="G53" s="80" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="78" t="inlineStr">
+      <c r="A54" s="82" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B54" s="78" t="inlineStr">
+      <c r="B54" s="82" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2439,30 +2387,30 @@
           <t xml:space="preserve">Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “Società </t>
         </is>
       </c>
-      <c r="D54" s="79" t="inlineStr">
+      <c r="D54" s="83" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-messina-locta-torrente-bordonaro</t>
         </is>
       </c>
-      <c r="E54" s="78" t="inlineStr">
+      <c r="E54" s="82" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F54" s="78" t="inlineStr">
+      <c r="F54" s="82" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G54" s="78" t="inlineStr"/>
+      <c r="G54" s="82" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="76" t="inlineStr">
+      <c r="A55" s="80" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B55" s="76" t="inlineStr">
+      <c r="B55" s="80" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2472,30 +2420,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “Condomin</t>
         </is>
       </c>
-      <c r="D55" s="77" t="inlineStr">
+      <c r="D55" s="81" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-mascali-spiaggia-n-144150</t>
         </is>
       </c>
-      <c r="E55" s="76" t="inlineStr">
+      <c r="E55" s="80" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F55" s="76" t="inlineStr">
+      <c r="F55" s="80" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G55" s="76" t="inlineStr"/>
+      <c r="G55" s="80" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="78" t="inlineStr">
+      <c r="A56" s="82" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B56" s="78" t="inlineStr">
+      <c r="B56" s="82" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2505,30 +2453,30 @@
           <t xml:space="preserve">Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione sito nel Comune di Lipari, isola di Stromboli, </t>
         </is>
       </c>
-      <c r="D56" s="79" t="inlineStr">
+      <c r="D56" s="83" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-lipari-isola-stromboli-locta-fico-grande</t>
         </is>
       </c>
-      <c r="E56" s="78" t="inlineStr">
+      <c r="E56" s="82" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F56" s="78" t="inlineStr">
+      <c r="F56" s="82" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G56" s="78" t="inlineStr"/>
+      <c r="G56" s="82" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="76" t="inlineStr">
+      <c r="A57" s="80" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B57" s="76" t="inlineStr">
+      <c r="B57" s="80" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2538,30 +2486,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione sito nel Comune di Favignana, isola di Le</t>
         </is>
       </c>
-      <c r="D57" s="77" t="inlineStr">
+      <c r="D57" s="81" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-favignana-isola-levanzo</t>
         </is>
       </c>
-      <c r="E57" s="76" t="inlineStr">
+      <c r="E57" s="80" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F57" s="76" t="inlineStr">
+      <c r="F57" s="80" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G57" s="76" t="inlineStr"/>
+      <c r="G57" s="80" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="78" t="inlineStr">
+      <c r="A58" s="82" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="B58" s="78" t="inlineStr">
+      <c r="B58" s="82" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2571,30 +2519,30 @@
           <t>Manifestazioni di interesseAVVISO - Manifestazione d’interesse finalizzata alla selezione di organismi attuatori di piani di gestione locale della pic</t>
         </is>
       </c>
-      <c r="D58" s="79" t="inlineStr">
+      <c r="D58" s="83" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-d-interesse-finalizzata-alla-selezione-organismi-attuatori-piani-gestione-locale-piccola-pesca-costiera-nelle-gsa-regione-siciliana</t>
         </is>
       </c>
-      <c r="E58" s="78" t="inlineStr">
+      <c r="E58" s="82" t="inlineStr">
         <is>
           <t>29/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F58" s="78" t="inlineStr">
+      <c r="F58" s="82" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="G58" s="78" t="inlineStr"/>
+      <c r="G58" s="82" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="76" t="inlineStr">
+      <c r="A59" s="80" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="B59" s="76" t="inlineStr">
+      <c r="B59" s="80" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2604,30 +2552,30 @@
           <t>Avvisi pubbliciLeggi e scarica l'avvisoScade il:02/04/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D59" s="77" t="inlineStr">
+      <c r="D59" s="81" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/proroga-termini-presentazione-candidature-po</t>
         </is>
       </c>
-      <c r="E59" s="76" t="inlineStr">
+      <c r="E59" s="80" t="inlineStr">
         <is>
           <t>02/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F59" s="76" t="inlineStr">
+      <c r="F59" s="80" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="G59" s="76" t="inlineStr"/>
+      <c r="G59" s="80" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="78" t="inlineStr">
+      <c r="A60" s="82" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="78" t="inlineStr">
+      <c r="B60" s="82" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2637,22 +2585,22 @@
           <t>INTERNAZIONALIZZAZIONESMAU – Italy RestartsUp in STOCCOLMAApertoFESR</t>
         </is>
       </c>
-      <c r="D60" s="79" t="inlineStr">
+      <c r="D60" s="83" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/smau-italy-restartsup-in-stoccolma/</t>
         </is>
       </c>
-      <c r="E60" s="78" t="inlineStr"/>
-      <c r="F60" s="78" t="inlineStr"/>
-      <c r="G60" s="78" t="inlineStr"/>
+      <c r="E60" s="82" t="inlineStr"/>
+      <c r="F60" s="82" t="inlineStr"/>
+      <c r="G60" s="82" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="76" t="inlineStr">
+      <c r="A61" s="80" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B61" s="76" t="inlineStr">
+      <c r="B61" s="80" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2662,22 +2610,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per Farnborough International AirshowApertoFESR</t>
         </is>
       </c>
-      <c r="D61" s="77" t="inlineStr">
+      <c r="D61" s="81" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-farnborough-international-airshow-2/</t>
         </is>
       </c>
-      <c r="E61" s="76" t="inlineStr"/>
-      <c r="F61" s="76" t="inlineStr"/>
-      <c r="G61" s="76" t="inlineStr"/>
+      <c r="E61" s="80" t="inlineStr"/>
+      <c r="F61" s="80" t="inlineStr"/>
+      <c r="G61" s="80" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="78" t="inlineStr">
+      <c r="A62" s="82" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="78" t="inlineStr">
+      <c r="B62" s="82" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2687,30 +2635,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA - alienazione lotto di terreno sito nel comune di Termini Imerese, via LibertàScade il:30/04/2026 - 12:00Leg</t>
         </is>
       </c>
-      <c r="D62" s="79" t="inlineStr">
+      <c r="D62" s="83" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proprieta-regionale-sito-nel-comune-termini-imerese-favore-ares-fabiola</t>
         </is>
       </c>
-      <c r="E62" s="78" t="inlineStr">
+      <c r="E62" s="82" t="inlineStr">
         <is>
           <t>30/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F62" s="78" t="inlineStr">
+      <c r="F62" s="82" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="G62" s="78" t="inlineStr"/>
+      <c r="G62" s="82" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="76" t="inlineStr">
+      <c r="A63" s="80" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B63" s="76" t="inlineStr">
+      <c r="B63" s="80" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2720,22 +2668,22 @@
           <t>Avviso per la concessione di contributi per progetti di contrasto all'abbandono sportivo giovanile (2026)</t>
         </is>
       </c>
-      <c r="D63" s="77" t="inlineStr">
+      <c r="D63" s="81" t="inlineStr">
         <is>
           <t>https://www.regione.emilia-romagna.it/sport/bandi/2026/contrasto-abbandono-2026</t>
         </is>
       </c>
-      <c r="E63" s="76" t="inlineStr"/>
-      <c r="F63" s="76" t="inlineStr"/>
-      <c r="G63" s="76" t="inlineStr"/>
+      <c r="E63" s="80" t="inlineStr"/>
+      <c r="F63" s="80" t="inlineStr"/>
+      <c r="G63" s="80" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="78" t="inlineStr">
+      <c r="A64" s="82" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="78" t="inlineStr">
+      <c r="B64" s="82" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2745,30 +2693,30 @@
           <t>Avvisi pubbliciAvviso si procede alla riassegnazione della posizione organizzativa a supporto delle attività del Servizio 2 “Investimenti in Agricoltu</t>
         </is>
       </c>
-      <c r="D64" s="79" t="inlineStr">
+      <c r="D64" s="83" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-selezione-interna-conferimento-1-posizione-organizzativa-ai-sensi-artt-19-20-ccrl-2022-2024-comparto-non-dirigenziale</t>
         </is>
       </c>
-      <c r="E64" s="78" t="inlineStr">
+      <c r="E64" s="82" t="inlineStr">
         <is>
           <t>09/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F64" s="78" t="inlineStr">
+      <c r="F64" s="82" t="inlineStr">
         <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="G64" s="78" t="inlineStr"/>
+      <c r="G64" s="82" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="76" t="inlineStr">
+      <c r="A65" s="80" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B65" s="76" t="inlineStr">
+      <c r="B65" s="80" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2778,30 +2726,30 @@
           <t>Avvisi pubbliciST-MESSINA - AVVISO di INDAGINE DI MERCATO per affidamento "Interventi manutenzione straordinaria della strada/pista forestale "Annunzi</t>
         </is>
       </c>
-      <c r="D65" s="77" t="inlineStr">
+      <c r="D65" s="81" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-indagine-mercato-affidamento-interventi-manutenzione-straordinaria-stradapista-forestale-annunziata-comune-messina</t>
         </is>
       </c>
-      <c r="E65" s="76" t="inlineStr">
+      <c r="E65" s="80" t="inlineStr">
         <is>
           <t>16/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F65" s="76" t="inlineStr">
+      <c r="F65" s="80" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="G65" s="76" t="inlineStr"/>
+      <c r="G65" s="80" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="78" t="inlineStr">
+      <c r="A66" s="82" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="78" t="inlineStr">
+      <c r="B66" s="82" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2811,30 +2759,30 @@
           <t>Avvisi pubbliciST-MESSINA - AVVISO DI INDAGINE DI MERCATO per affidamento "Interventi manutenzione straordinaria della strada/pista forestale "San Riz</t>
         </is>
       </c>
-      <c r="D66" s="79" t="inlineStr">
+      <c r="D66" s="83" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-indagine-mercato-affidamento-interventi-manutenzione-straordinaria-stradapista-forestale-san-rizzo-san-leone-crupi-madonuzza-comune-messina</t>
         </is>
       </c>
-      <c r="E66" s="78" t="inlineStr">
+      <c r="E66" s="82" t="inlineStr">
         <is>
           <t>16/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F66" s="78" t="inlineStr">
+      <c r="F66" s="82" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="G66" s="78" t="inlineStr"/>
+      <c r="G66" s="82" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="76" t="inlineStr">
+      <c r="A67" s="80" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="76" t="inlineStr">
+      <c r="B67" s="80" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2844,22 +2792,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Manifestazione di interesse per Casaidea 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D67" s="77" t="inlineStr">
+      <c r="D67" s="81" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-casaidea-2026/</t>
         </is>
       </c>
-      <c r="E67" s="76" t="inlineStr"/>
-      <c r="F67" s="76" t="inlineStr"/>
-      <c r="G67" s="76" t="inlineStr"/>
+      <c r="E67" s="80" t="inlineStr"/>
+      <c r="F67" s="80" t="inlineStr"/>
+      <c r="G67" s="80" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="78" t="inlineStr">
+      <c r="A68" s="82" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="78" t="inlineStr">
+      <c r="B68" s="82" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2869,22 +2817,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per il Salone Internazionale del Libro di Torino 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D68" s="79" t="inlineStr">
+      <c r="D68" s="83" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-il-salone-internazionale-del-libro-di-torino-2026/</t>
         </is>
       </c>
-      <c r="E68" s="78" t="inlineStr"/>
-      <c r="F68" s="78" t="inlineStr"/>
-      <c r="G68" s="78" t="inlineStr"/>
+      <c r="E68" s="82" t="inlineStr"/>
+      <c r="F68" s="82" t="inlineStr"/>
+      <c r="G68" s="82" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="76" t="inlineStr">
+      <c r="A69" s="80" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="76" t="inlineStr">
+      <c r="B69" s="80" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2894,30 +2842,30 @@
           <t>Avvisi pubbliciDDG 1112 del 02.04.2026 - Aggiornamento Avviso pubblico n. 4/2024 per l’attuazione del PAR GOL Sicilia da finanziare nell’ambito del Pi</t>
         </is>
       </c>
-      <c r="D69" s="77" t="inlineStr">
+      <c r="D69" s="81" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/ddg-1112-02042026-aggiornamento-avviso-pubblico-n-42024-l-attuazione-par-gol-sicilia-finanziare-nell-ambito-piano-nazionale-ripresa-resilienza-pnrr</t>
         </is>
       </c>
-      <c r="E69" s="76" t="inlineStr">
+      <c r="E69" s="80" t="inlineStr">
         <is>
           <t>05/04/2030 - 00:00</t>
         </is>
       </c>
-      <c r="F69" s="76" t="inlineStr">
+      <c r="F69" s="80" t="inlineStr">
         <is>
           <t>05/04/2030</t>
         </is>
       </c>
-      <c r="G69" s="76" t="inlineStr"/>
+      <c r="G69" s="80" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="78" t="inlineStr">
+      <c r="A70" s="82" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="78" t="inlineStr">
+      <c r="B70" s="82" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2927,30 +2875,30 @@
           <t>Avvisi pubbliciDDG 1113 del  02.04.2026 - Aggiornamento Avviso pubblico n. 2/2022 e s.m.i per l’attuazione del PAR GOL Sicilia da finanziare nell’ambi</t>
         </is>
       </c>
-      <c r="D70" s="79" t="inlineStr">
+      <c r="D70" s="83" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/ddg-1113-02042026-aggiornamento-avviso-pubblico-n-22022-smi-l-attuazione-par-gol-sicilia-finanziare-nell-ambito-piano-nazionale-ripresa-resilienza-pnrr</t>
         </is>
       </c>
-      <c r="E70" s="78" t="inlineStr">
+      <c r="E70" s="82" t="inlineStr">
         <is>
           <t>03/04/2030 - 00:00</t>
         </is>
       </c>
-      <c r="F70" s="78" t="inlineStr">
+      <c r="F70" s="82" t="inlineStr">
         <is>
           <t>03/04/2030</t>
         </is>
       </c>
-      <c r="G70" s="78" t="inlineStr"/>
+      <c r="G70" s="82" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="76" t="inlineStr">
+      <c r="A71" s="80" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B71" s="76" t="inlineStr">
+      <c r="B71" s="80" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2960,22 +2908,22 @@
           <t>Avvisi pubbliciLeggi e scarica l'avvisoScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D71" s="77" t="inlineStr">
+      <c r="D71" s="81" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/proroga-termini-presentazione-candidature-po</t>
         </is>
       </c>
-      <c r="E71" s="76" t="inlineStr"/>
-      <c r="F71" s="76" t="inlineStr"/>
-      <c r="G71" s="76" t="inlineStr"/>
+      <c r="E71" s="80" t="inlineStr"/>
+      <c r="F71" s="80" t="inlineStr"/>
+      <c r="G71" s="80" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="78" t="inlineStr">
+      <c r="A72" s="82" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="78" t="inlineStr">
+      <c r="B72" s="82" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2985,22 +2933,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEComunicare l’inclusione – contest per le istituzioni scolastiche regionaliApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D72" s="79" t="inlineStr">
+      <c r="D72" s="83" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/comunicare-linclusione-contest-per-le-istituzioni-scolastiche-regionali/</t>
         </is>
       </c>
-      <c r="E72" s="78" t="inlineStr"/>
-      <c r="F72" s="78" t="inlineStr"/>
-      <c r="G72" s="78" t="inlineStr"/>
+      <c r="E72" s="82" t="inlineStr"/>
+      <c r="F72" s="82" t="inlineStr"/>
+      <c r="G72" s="82" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="76" t="inlineStr">
+      <c r="A73" s="80" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B73" s="76" t="inlineStr">
+      <c r="B73" s="80" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3010,30 +2958,30 @@
           <t>Avvisi pubbliciAPPROVAZIONE AVVISO PUBBLICOScade il:03/04/2027 - 00:00Leggi di più</t>
         </is>
       </c>
-      <c r="D73" s="77" t="inlineStr">
+      <c r="D73" s="81" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/approvazione-avviso-pubblico</t>
         </is>
       </c>
-      <c r="E73" s="76" t="inlineStr">
+      <c r="E73" s="80" t="inlineStr">
         <is>
           <t>03/04/2027 - 00:00</t>
         </is>
       </c>
-      <c r="F73" s="76" t="inlineStr">
+      <c r="F73" s="80" t="inlineStr">
         <is>
           <t>03/04/2027</t>
         </is>
       </c>
-      <c r="G73" s="76" t="inlineStr"/>
+      <c r="G73" s="80" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="78" t="inlineStr">
+      <c r="A74" s="82" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="78" t="inlineStr">
+      <c r="B74" s="82" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -3043,22 +2991,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Donne e Impresa 2026Prossima AperturaFESR</t>
         </is>
       </c>
-      <c r="D74" s="79" t="inlineStr">
+      <c r="D74" s="83" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/donne-e-impresa-2026/</t>
         </is>
       </c>
-      <c r="E74" s="78" t="inlineStr"/>
-      <c r="F74" s="78" t="inlineStr"/>
-      <c r="G74" s="78" t="inlineStr"/>
+      <c r="E74" s="82" t="inlineStr"/>
+      <c r="F74" s="82" t="inlineStr"/>
+      <c r="G74" s="82" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="76" t="inlineStr">
+      <c r="A75" s="80" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B75" s="76" t="inlineStr">
+      <c r="B75" s="80" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3068,22 +3016,22 @@
           <t>Bandi di garaCodice Intervento 111302_FELUCHE - Investimenti a bordo e nei porti per incrementare la qualità delle produzioni e migliorare le condizio</t>
         </is>
       </c>
-      <c r="D75" s="77" t="inlineStr">
+      <c r="D75" s="81" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/bandoavviso-regia-ob-11-azione-3-codice-111302feluche-investimenti-bordo-valorizzazione-feluche-miglioramento-condizioni-lavoro-salute-sicurezza-operatori-l</t>
         </is>
       </c>
-      <c r="E75" s="76" t="inlineStr">
+      <c r="E75" s="80" t="inlineStr">
         <is>
           <t>02/07/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F75" s="76" t="inlineStr">
+      <c r="F75" s="80" t="inlineStr">
         <is>
           <t>02/07/2026</t>
         </is>
       </c>
-      <c r="G75" s="76" t="inlineStr"/>
+      <c r="G75" s="80" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="82" t="inlineStr">
@@ -3208,6 +3156,64 @@
         </is>
       </c>
       <c r="G79" s="80" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="86" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="86" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>Comunicazione e informazioneAcquisizione di servizi di comunicazione e informazione – PR Lazio FESR, PR Lazio FSE+ e comunicazione unitariaApertoBandi</t>
+        </is>
+      </c>
+      <c r="D80" s="87" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/acquisizione-di-servizi-di-comunicazione-e-informazione-pr-lazio-fesr-pr-lazio-fse-e-comunicazione-unitaria/</t>
+        </is>
+      </c>
+      <c r="E80" s="86" t="inlineStr"/>
+      <c r="F80" s="86" t="inlineStr"/>
+      <c r="G80" s="86" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="84" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="84" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>Avvisi pubbliciAvviso pubblico di selezione interna, per titoli, per il conferimento, ai sensi degli artt. 21 del CCRL 2022-2024 del comparto non diri</t>
+        </is>
+      </c>
+      <c r="D81" s="85" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-selezione-interna-titoli-conferimento-ai-sensi-artt-21-ccrl-2022-2024-comparto-non-dirigenziale-una-posizione-organizzativa-dipartimento</t>
+        </is>
+      </c>
+      <c r="E81" s="84" t="inlineStr">
+        <is>
+          <t>16/04/2026 - 12:00</t>
+        </is>
+      </c>
+      <c r="F81" s="84" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="G81" s="84" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -3289,6 +3295,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId77"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId80"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3333,7 +3341,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="80" t="inlineStr">
+      <c r="A3" s="84" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -3346,29 +3354,29 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="82" t="inlineStr">
+      <c r="A4" s="86" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="80" t="inlineStr">
+      <c r="A5" s="84" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">

--- a/data/bandi_export.xlsx
+++ b/data/bandi_export.xlsx
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -267,6 +267,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -742,7 +754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -757,7 +769,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏛️  Nuovi Bandi — 11/04/2026 07:45</t>
+          <t>🏛️  Nuovi Bandi — 14/04/2026 08:23</t>
         </is>
       </c>
     </row>
@@ -802,55 +814,32 @@
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="84" t="inlineStr">
-        <is>
-          <t>Lazio</t>
+      <c r="B3" s="88" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Comunicazione e informazioneAcquisizione di servizi di comunicazione e informazione – PR Lazio FESR, PR Lazio FSE+ e comunicazione unitariaApertoBandi</t>
-        </is>
-      </c>
-      <c r="D3" s="85" t="inlineStr">
-        <is>
-          <t>https://www.lazioeuropa.it/bandi/acquisizione-di-servizi-di-comunicazione-e-informazione-pr-lazio-fesr-pr-lazio-fse-e-comunicazione-unitaria/</t>
-        </is>
-      </c>
-      <c r="E3" s="84" t="inlineStr"/>
-      <c r="F3" s="84" t="inlineStr"/>
+          <t xml:space="preserve">Avvisi pubbliciAVVISO DI INDAGINE DI MERCATO  per la partecipazione alla successiva procedura negoziata a norma dell'art. 50, comma 1, lettera c) del </t>
+        </is>
+      </c>
+      <c r="D3" s="89" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-indagine-mercato-partecipazione-alla-successiva-procedura-negoziata-norma-art-50-comma-1-lettera-c-dlgs-31-marzo-2023-n-36-ssmmii-finalizzata-all</t>
+        </is>
+      </c>
+      <c r="E3" s="88" t="inlineStr">
+        <is>
+          <t>30/04/2026 - 12:00</t>
+        </is>
+      </c>
+      <c r="F3" s="88" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
       <c r="G3" s="5" t="inlineStr"/>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="86" t="inlineStr">
-        <is>
-          <t>Sicilia</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>Avvisi pubbliciAvviso pubblico di selezione interna, per titoli, per il conferimento, ai sensi degli artt. 21 del CCRL 2022-2024 del comparto non diri</t>
-        </is>
-      </c>
-      <c r="D4" s="87" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-selezione-interna-titoli-conferimento-ai-sensi-artt-21-ccrl-2022-2024-comparto-non-dirigenziale-una-posizione-organizzativa-dipartimento</t>
-        </is>
-      </c>
-      <c r="E4" s="86" t="inlineStr">
-        <is>
-          <t>16/04/2026 - 12:00</t>
-        </is>
-      </c>
-      <c r="F4" s="86" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="G4" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -858,7 +847,6 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -870,7 +858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -920,12 +908,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="82" t="inlineStr">
+      <c r="A2" s="86" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B2" s="82" t="inlineStr">
+      <c r="B2" s="86" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -935,22 +923,22 @@
           <t>FLAG GALPA Costa E-R. Sostituzione del motore principale e dei motori secondari. Secondo bando</t>
         </is>
       </c>
-      <c r="D2" s="83" t="inlineStr">
+      <c r="D2" s="87" t="inlineStr">
         <is>
           <t>https://agricoltura.regione.emilia-romagna.it/feampa-2021-2027/bandi-galpa/2026/galpa-sostituzione-motori-secondo-bando</t>
         </is>
       </c>
-      <c r="E2" s="82" t="inlineStr"/>
-      <c r="F2" s="82" t="inlineStr"/>
-      <c r="G2" s="82" t="inlineStr"/>
+      <c r="E2" s="86" t="inlineStr"/>
+      <c r="F2" s="86" t="inlineStr"/>
+      <c r="G2" s="86" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="80" t="inlineStr">
+      <c r="A3" s="84" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B3" s="80" t="inlineStr">
+      <c r="B3" s="84" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -960,22 +948,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0PRE-SEED 3.0Prossima AperturaFESR</t>
         </is>
       </c>
-      <c r="D3" s="81" t="inlineStr">
+      <c r="D3" s="85" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/pre-seed-3-0/</t>
         </is>
       </c>
-      <c r="E3" s="80" t="inlineStr"/>
-      <c r="F3" s="80" t="inlineStr"/>
-      <c r="G3" s="80" t="inlineStr"/>
+      <c r="E3" s="84" t="inlineStr"/>
+      <c r="F3" s="84" t="inlineStr"/>
+      <c r="G3" s="84" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="82" t="inlineStr">
+      <c r="A4" s="86" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B4" s="82" t="inlineStr">
+      <c r="B4" s="86" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -985,22 +973,22 @@
           <t>ACCESSO AL CREDITO E ALLE GARANZIE PER LE IMPRESEContributo su finanziamenti alle imprese del Lazio erogati su provvista BEIProssima AperturaFESR</t>
         </is>
       </c>
-      <c r="D4" s="83" t="inlineStr">
+      <c r="D4" s="87" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-su-finanziamenti-alle-imprese-del-lazio-erogati-su-provvista-bei/</t>
         </is>
       </c>
-      <c r="E4" s="82" t="inlineStr"/>
-      <c r="F4" s="82" t="inlineStr"/>
-      <c r="G4" s="82" t="inlineStr"/>
+      <c r="E4" s="86" t="inlineStr"/>
+      <c r="F4" s="86" t="inlineStr"/>
+      <c r="G4" s="86" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="80" t="inlineStr">
+      <c r="A5" s="84" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B5" s="80" t="inlineStr">
+      <c r="B5" s="84" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1010,22 +998,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEIndividuazione degli enti iscritti al Registro unico nazionale del Terzo settoreApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D5" s="81" t="inlineStr">
+      <c r="D5" s="85" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/individuazione-degli-enti-iscritti-al-registro-unico-nazionale-del-terzo-settore/</t>
         </is>
       </c>
-      <c r="E5" s="80" t="inlineStr"/>
-      <c r="F5" s="80" t="inlineStr"/>
-      <c r="G5" s="80" t="inlineStr"/>
+      <c r="E5" s="84" t="inlineStr"/>
+      <c r="F5" s="84" t="inlineStr"/>
+      <c r="G5" s="84" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="82" t="inlineStr">
+      <c r="A6" s="86" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B6" s="82" t="inlineStr">
+      <c r="B6" s="86" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1035,22 +1023,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Technology Transfer LazioApertoFESR</t>
         </is>
       </c>
-      <c r="D6" s="83" t="inlineStr">
+      <c r="D6" s="87" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/technology-transfer-lazio/</t>
         </is>
       </c>
-      <c r="E6" s="82" t="inlineStr"/>
-      <c r="F6" s="82" t="inlineStr"/>
-      <c r="G6" s="82" t="inlineStr"/>
+      <c r="E6" s="86" t="inlineStr"/>
+      <c r="F6" s="86" t="inlineStr"/>
+      <c r="G6" s="86" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="80" t="inlineStr">
+      <c r="A7" s="84" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B7" s="80" t="inlineStr">
+      <c r="B7" s="84" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1060,22 +1048,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Percorso di tutoraggio per le impreseApertoFESR</t>
         </is>
       </c>
-      <c r="D7" s="81" t="inlineStr">
+      <c r="D7" s="85" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/percorso-di-tutoraggio-per-le-imprese/</t>
         </is>
       </c>
-      <c r="E7" s="80" t="inlineStr"/>
-      <c r="F7" s="80" t="inlineStr"/>
-      <c r="G7" s="80" t="inlineStr"/>
+      <c r="E7" s="84" t="inlineStr"/>
+      <c r="F7" s="84" t="inlineStr"/>
+      <c r="G7" s="84" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="82" t="inlineStr">
+      <c r="A8" s="86" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B8" s="82" t="inlineStr">
+      <c r="B8" s="86" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1085,22 +1073,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per partecipare a SMAU Parigi 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D8" s="83" t="inlineStr">
+      <c r="D8" s="87" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-partecipare-a-smau-parigi-2026/</t>
         </is>
       </c>
-      <c r="E8" s="82" t="inlineStr"/>
-      <c r="F8" s="82" t="inlineStr"/>
-      <c r="G8" s="82" t="inlineStr"/>
+      <c r="E8" s="86" t="inlineStr"/>
+      <c r="F8" s="86" t="inlineStr"/>
+      <c r="G8" s="86" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="80" t="inlineStr">
+      <c r="A9" s="84" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B9" s="80" t="inlineStr">
+      <c r="B9" s="84" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1110,22 +1098,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONERiconoscimento della funzione sociale ed educativa degli oratoriApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D9" s="81" t="inlineStr">
+      <c r="D9" s="85" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/riconoscimento-della-funzione-sociale-ed-educativa-degli-oratori/</t>
         </is>
       </c>
-      <c r="E9" s="80" t="inlineStr"/>
-      <c r="F9" s="80" t="inlineStr"/>
-      <c r="G9" s="80" t="inlineStr"/>
+      <c r="E9" s="84" t="inlineStr"/>
+      <c r="F9" s="84" t="inlineStr"/>
+      <c r="G9" s="84" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="82" t="inlineStr">
+      <c r="A10" s="86" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B10" s="82" t="inlineStr">
+      <c r="B10" s="86" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1135,22 +1123,22 @@
           <t>GovernanceIscrizione nell’elenco regionale degli idonei all’esercizio dell’attività di direttore dell’Istituto JemoloApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D10" s="83" t="inlineStr">
+      <c r="D10" s="87" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/iscrizione-nellelenco-regionale-degli-idonei-allesercizio-dellattivita-di-direttore-dellistituto-jemolo/</t>
         </is>
       </c>
-      <c r="E10" s="82" t="inlineStr"/>
-      <c r="F10" s="82" t="inlineStr"/>
-      <c r="G10" s="82" t="inlineStr"/>
+      <c r="E10" s="86" t="inlineStr"/>
+      <c r="F10" s="86" t="inlineStr"/>
+      <c r="G10" s="86" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="80" t="inlineStr">
+      <c r="A11" s="84" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B11" s="80" t="inlineStr">
+      <c r="B11" s="84" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1160,22 +1148,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEVoucher per lo sport – seconda annualitàApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D11" s="81" t="inlineStr">
+      <c r="D11" s="85" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/voucher-per-lo-sport-seconda-annualita/</t>
         </is>
       </c>
-      <c r="E11" s="80" t="inlineStr"/>
-      <c r="F11" s="80" t="inlineStr"/>
-      <c r="G11" s="80" t="inlineStr"/>
+      <c r="E11" s="84" t="inlineStr"/>
+      <c r="F11" s="84" t="inlineStr"/>
+      <c r="G11" s="84" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="82" t="inlineStr">
+      <c r="A12" s="86" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B12" s="82" t="inlineStr">
+      <c r="B12" s="86" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1185,22 +1173,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEBonus occupazionale SALGOApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D12" s="83" t="inlineStr">
+      <c r="D12" s="87" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/bonus-occupazionale-salgo/</t>
         </is>
       </c>
-      <c r="E12" s="82" t="inlineStr"/>
-      <c r="F12" s="82" t="inlineStr"/>
-      <c r="G12" s="82" t="inlineStr"/>
+      <c r="E12" s="86" t="inlineStr"/>
+      <c r="F12" s="86" t="inlineStr"/>
+      <c r="G12" s="86" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="80" t="inlineStr">
+      <c r="A13" s="84" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B13" s="80" t="inlineStr">
+      <c r="B13" s="84" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1210,22 +1198,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEContributo di Libertà per le donne che hanno subito violenzaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D13" s="81" t="inlineStr">
+      <c r="D13" s="85" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-di-liberta-per-le-donne-che-hanno-subito-violenza/</t>
         </is>
       </c>
-      <c r="E13" s="80" t="inlineStr"/>
-      <c r="F13" s="80" t="inlineStr"/>
-      <c r="G13" s="80" t="inlineStr"/>
+      <c r="E13" s="84" t="inlineStr"/>
+      <c r="F13" s="84" t="inlineStr"/>
+      <c r="G13" s="84" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="82" t="inlineStr">
+      <c r="A14" s="86" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B14" s="82" t="inlineStr">
+      <c r="B14" s="86" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1235,22 +1223,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURAInterventi straordinari di valorizzazione del patrimonio culturale del LazioApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D14" s="83" t="inlineStr">
+      <c r="D14" s="87" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/interventi-straordinari-di-valorizzazione-del-patrimonio-culturale-del-lazio/</t>
         </is>
       </c>
-      <c r="E14" s="82" t="inlineStr"/>
-      <c r="F14" s="82" t="inlineStr"/>
-      <c r="G14" s="82" t="inlineStr"/>
+      <c r="E14" s="86" t="inlineStr"/>
+      <c r="F14" s="86" t="inlineStr"/>
+      <c r="G14" s="86" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="80" t="inlineStr">
+      <c r="A15" s="84" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B15" s="80" t="inlineStr">
+      <c r="B15" s="84" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1260,30 +1248,30 @@
           <t>Bandi di garaBANDO ATTUAZIONE Ob. 1.1 Azione 1 codice 111102 _DIV - "SOSTEGNO ALLA DIVERSIFICAZIONE E NUOVE FORME DI REDDITO PER LA PICCOLA PESCA COST</t>
         </is>
       </c>
-      <c r="D15" s="81" t="inlineStr">
+      <c r="D15" s="85" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/bando-avviso-regia-ob-11-azione-1-codice-111102-div-sostegno-alla-diversificazione-nuove-forme-reddito-piccola-pesca-costiera</t>
         </is>
       </c>
-      <c r="E15" s="80" t="inlineStr">
+      <c r="E15" s="84" t="inlineStr">
         <is>
           <t>07/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F15" s="80" t="inlineStr">
+      <c r="F15" s="84" t="inlineStr">
         <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="G15" s="80" t="inlineStr"/>
+      <c r="G15" s="84" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="82" t="inlineStr">
+      <c r="A16" s="86" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B16" s="82" t="inlineStr">
+      <c r="B16" s="86" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1293,30 +1281,30 @@
           <t>Avvisi pubblici09 marzo 2026 - ST SIRACUSA - AVVISO PUBBLICO PER LA COSTITUZIONE DI ELENCHI DI OPERATORI ECONOMICI PER L’ACQUISIZIONE DI BENI E SERVIZ</t>
         </is>
       </c>
-      <c r="D16" s="83" t="inlineStr">
+      <c r="D16" s="87" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/09-marzo-2026-st-siracusa-avviso-pubblico-costituzione-elenchi-operatori-economici-l-acquisizione-beni-servizi</t>
         </is>
       </c>
-      <c r="E16" s="82" t="inlineStr">
+      <c r="E16" s="86" t="inlineStr">
         <is>
           <t>31/12/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F16" s="82" t="inlineStr">
+      <c r="F16" s="86" t="inlineStr">
         <is>
           <t>31/12/2026</t>
         </is>
       </c>
-      <c r="G16" s="82" t="inlineStr"/>
+      <c r="G16" s="86" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="80" t="inlineStr">
+      <c r="A17" s="84" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B17" s="80" t="inlineStr">
+      <c r="B17" s="84" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1326,30 +1314,30 @@
           <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScade il:19/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D17" s="81" t="inlineStr">
+      <c r="D17" s="85" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
         </is>
       </c>
-      <c r="E17" s="80" t="inlineStr">
+      <c r="E17" s="84" t="inlineStr">
         <is>
           <t>19/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F17" s="80" t="inlineStr">
+      <c r="F17" s="84" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G17" s="80" t="inlineStr"/>
+      <c r="G17" s="84" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="82" t="inlineStr">
+      <c r="A18" s="86" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B18" s="82" t="inlineStr">
+      <c r="B18" s="86" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1359,22 +1347,22 @@
           <t>Manifestazioni di interesseAvviso Manifestazione Interesse DISTRIBUTORI AUTOMATICI di bevande e snackScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D18" s="83" t="inlineStr">
+      <c r="D18" s="87" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-distributori-automatici-bevande-snack</t>
         </is>
       </c>
-      <c r="E18" s="82" t="inlineStr"/>
-      <c r="F18" s="82" t="inlineStr"/>
-      <c r="G18" s="82" t="inlineStr"/>
+      <c r="E18" s="86" t="inlineStr"/>
+      <c r="F18" s="86" t="inlineStr"/>
+      <c r="G18" s="86" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="80" t="inlineStr">
+      <c r="A19" s="84" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B19" s="80" t="inlineStr">
+      <c r="B19" s="84" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1384,30 +1372,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D19" s="81" t="inlineStr">
+      <c r="D19" s="85" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo</t>
         </is>
       </c>
-      <c r="E19" s="80" t="inlineStr">
+      <c r="E19" s="84" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F19" s="80" t="inlineStr">
+      <c r="F19" s="84" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G19" s="80" t="inlineStr"/>
+      <c r="G19" s="84" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="82" t="inlineStr">
+      <c r="A20" s="86" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B20" s="82" t="inlineStr">
+      <c r="B20" s="86" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1417,30 +1405,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D20" s="83" t="inlineStr">
+      <c r="D20" s="87" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo-0</t>
         </is>
       </c>
-      <c r="E20" s="82" t="inlineStr">
+      <c r="E20" s="86" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F20" s="82" t="inlineStr">
+      <c r="F20" s="86" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G20" s="82" t="inlineStr"/>
+      <c r="G20" s="86" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="80" t="inlineStr">
+      <c r="A21" s="84" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B21" s="80" t="inlineStr">
+      <c r="B21" s="84" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1450,22 +1438,22 @@
           <t>Manifestazioni di interesseST SIRACUSA - AVVISO DI MANIFESTAZIONE DI INTERESSE - Fornitura applicativo extracontabile per la gestione progetti, ecc. e</t>
         </is>
       </c>
-      <c r="D21" s="81" t="inlineStr">
+      <c r="D21" s="85" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-siracusa-avviso-manifestazione-interesse-fornitura-applicativo-extracontabile-gestione-progetti-ecc-applicativo-gestione-ed-elaborazione-informatizzata-paghe</t>
         </is>
       </c>
-      <c r="E21" s="80" t="inlineStr"/>
-      <c r="F21" s="80" t="inlineStr"/>
-      <c r="G21" s="80" t="inlineStr"/>
+      <c r="E21" s="84" t="inlineStr"/>
+      <c r="F21" s="84" t="inlineStr"/>
+      <c r="G21" s="84" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="82" t="inlineStr">
+      <c r="A22" s="86" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B22" s="82" t="inlineStr">
+      <c r="B22" s="86" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1475,30 +1463,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile sito nel Comune di Capo D'Orlando, Via Trazzera MarinaScade il:25/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D22" s="83" t="inlineStr">
+      <c r="D22" s="87" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-sito-nel-comune-capo-d-orlando-trazzera-marina</t>
         </is>
       </c>
-      <c r="E22" s="82" t="inlineStr">
+      <c r="E22" s="86" t="inlineStr">
         <is>
           <t>25/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F22" s="82" t="inlineStr">
+      <c r="F22" s="86" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="G22" s="82" t="inlineStr"/>
+      <c r="G22" s="86" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="80" t="inlineStr">
+      <c r="A23" s="84" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B23" s="80" t="inlineStr">
+      <c r="B23" s="84" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1508,22 +1496,22 @@
           <t xml:space="preserve">Avvisi pubbliciST CATANIA - Programma Regionale FESR Sicilia 2021-2027 - Azione 2.4.4 - “Interventi per la riduzione del rischio incendi” - AVVISO DI </t>
         </is>
       </c>
-      <c r="D23" s="81" t="inlineStr">
+      <c r="D23" s="85" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-catania-programma-regionale-fesr-sicilia-2021-2027-azione-244-interventi-riduzione-rischio-incendi-avviso-indagine-mercato</t>
         </is>
       </c>
-      <c r="E23" s="80" t="inlineStr"/>
-      <c r="F23" s="80" t="inlineStr"/>
-      <c r="G23" s="80" t="inlineStr"/>
+      <c r="E23" s="84" t="inlineStr"/>
+      <c r="F23" s="84" t="inlineStr"/>
+      <c r="G23" s="84" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="82" t="inlineStr">
+      <c r="A24" s="86" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B24" s="82" t="inlineStr">
+      <c r="B24" s="86" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1533,22 +1521,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per ROMICS – Primavera 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D24" s="83" t="inlineStr">
+      <c r="D24" s="87" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-romics-primavera-2026/</t>
         </is>
       </c>
-      <c r="E24" s="82" t="inlineStr"/>
-      <c r="F24" s="82" t="inlineStr"/>
-      <c r="G24" s="82" t="inlineStr"/>
+      <c r="E24" s="86" t="inlineStr"/>
+      <c r="F24" s="86" t="inlineStr"/>
+      <c r="G24" s="86" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="80" t="inlineStr">
+      <c r="A25" s="84" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B25" s="80" t="inlineStr">
+      <c r="B25" s="84" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1558,22 +1546,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Cinema International 2026 – I edizioneApertoFESR</t>
         </is>
       </c>
-      <c r="D25" s="81" t="inlineStr">
+      <c r="D25" s="85" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lazio-cinema-international-2026-i-edizione/</t>
         </is>
       </c>
-      <c r="E25" s="80" t="inlineStr"/>
-      <c r="F25" s="80" t="inlineStr"/>
-      <c r="G25" s="80" t="inlineStr"/>
+      <c r="E25" s="84" t="inlineStr"/>
+      <c r="F25" s="84" t="inlineStr"/>
+      <c r="G25" s="84" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="82" t="inlineStr">
+      <c r="A26" s="86" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B26" s="82" t="inlineStr">
+      <c r="B26" s="86" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1583,22 +1571,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEManifestazioni di interesse alla costituzione di due nuove Fondazioni I.T.S. AcademyApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D26" s="83" t="inlineStr">
+      <c r="D26" s="87" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazioni-di-interesse-alla-costituzione-di-due-nuove-fondazioni-i-t-s-academy/</t>
         </is>
       </c>
-      <c r="E26" s="82" t="inlineStr"/>
-      <c r="F26" s="82" t="inlineStr"/>
-      <c r="G26" s="82" t="inlineStr"/>
+      <c r="E26" s="86" t="inlineStr"/>
+      <c r="F26" s="86" t="inlineStr"/>
+      <c r="G26" s="86" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="80" t="inlineStr">
+      <c r="A27" s="84" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B27" s="80" t="inlineStr">
+      <c r="B27" s="84" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1608,22 +1596,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURAContributi per sostenere la ripresa del settore della pescaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D27" s="81" t="inlineStr">
+      <c r="D27" s="85" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributi-per-sostenere-la-ripresa-del-settore-della-pesca/</t>
         </is>
       </c>
-      <c r="E27" s="80" t="inlineStr"/>
-      <c r="F27" s="80" t="inlineStr"/>
-      <c r="G27" s="80" t="inlineStr"/>
+      <c r="E27" s="84" t="inlineStr"/>
+      <c r="F27" s="84" t="inlineStr"/>
+      <c r="G27" s="84" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="82" t="inlineStr">
+      <c r="A28" s="86" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B28" s="82" t="inlineStr">
+      <c r="B28" s="86" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1633,30 +1621,30 @@
           <t>Manifestazioni di interesseAVVISO - Manifestazione Interesse “Storytelling aziendale” Expo Wild Natura - Caccia - Pesca. Misterbianco (CT), 10-12 apri</t>
         </is>
       </c>
-      <c r="D28" s="83" t="inlineStr">
+      <c r="D28" s="87" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-storytelling-aziendale-expo-wild-natura-caccia-pesca-misterbianco-ct-10-12-aprile-2026</t>
         </is>
       </c>
-      <c r="E28" s="82" t="inlineStr">
+      <c r="E28" s="86" t="inlineStr">
         <is>
           <t>30/03/2026 - 13:00</t>
         </is>
       </c>
-      <c r="F28" s="82" t="inlineStr">
+      <c r="F28" s="86" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G28" s="82" t="inlineStr"/>
+      <c r="G28" s="86" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="80" t="inlineStr">
+      <c r="A29" s="84" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B29" s="80" t="inlineStr">
+      <c r="B29" s="84" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1666,30 +1654,30 @@
           <t>Manifestazioni di interesseInvaso Lentini - Interventi di ripristino delle pareti esterne in cls della Torre di presa Sud e della trave d’appoggio del</t>
         </is>
       </c>
-      <c r="D29" s="81" t="inlineStr">
+      <c r="D29" s="85" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/invaso-lentini-interventi-ripristino-pareti-esterne-cls-torre-presa-sud-trave-d-appoggio-cavalcavia-collegamento-alla-stessa-torre</t>
         </is>
       </c>
-      <c r="E29" s="80" t="inlineStr">
+      <c r="E29" s="84" t="inlineStr">
         <is>
           <t>19/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F29" s="80" t="inlineStr">
+      <c r="F29" s="84" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G29" s="80" t="inlineStr"/>
+      <c r="G29" s="84" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="82" t="inlineStr">
+      <c r="A30" s="86" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="B30" s="82" t="inlineStr">
+      <c r="B30" s="86" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1699,22 +1687,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURARistrutturazione e riconversione vigneti – campagna 2026-2027ApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D30" s="83" t="inlineStr">
+      <c r="D30" s="87" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/ristrutturazione-e-riconversione-vigneti-campagna-2026-2027/</t>
         </is>
       </c>
-      <c r="E30" s="82" t="inlineStr"/>
-      <c r="F30" s="82" t="inlineStr"/>
-      <c r="G30" s="82" t="inlineStr"/>
+      <c r="E30" s="86" t="inlineStr"/>
+      <c r="F30" s="86" t="inlineStr"/>
+      <c r="G30" s="86" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="80" t="inlineStr">
+      <c r="A31" s="84" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="B31" s="80" t="inlineStr">
+      <c r="B31" s="84" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1724,30 +1712,30 @@
           <t>Manifestazioni di interessePR FESR 2021/27 Azione 1.3.3 e del POC 2014/20 - Azione 1.3.1  - Avviso a manifestazione d’interesse eventi fieristici inte</t>
         </is>
       </c>
-      <c r="D31" s="81" t="inlineStr">
+      <c r="D31" s="85" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-d-interesse-eventi-fieristici-internazionali-marzo-dicembre-2026</t>
         </is>
       </c>
-      <c r="E31" s="80" t="inlineStr">
+      <c r="E31" s="84" t="inlineStr">
         <is>
           <t>30/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F31" s="80" t="inlineStr">
+      <c r="F31" s="84" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="G31" s="80" t="inlineStr"/>
+      <c r="G31" s="84" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="82" t="inlineStr">
+      <c r="A32" s="86" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="B32" s="82" t="inlineStr">
+      <c r="B32" s="86" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1757,22 +1745,22 @@
           <t>INTERNAZIONALIZZAZIONEL’Ecosistema dell’Innovazione a INNOVIT – Focus S3ApertoFESR</t>
         </is>
       </c>
-      <c r="D32" s="83" t="inlineStr">
+      <c r="D32" s="87" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lecosistema-dellinnovazione-a-innovit-focus-s3/</t>
         </is>
       </c>
-      <c r="E32" s="82" t="inlineStr"/>
-      <c r="F32" s="82" t="inlineStr"/>
-      <c r="G32" s="82" t="inlineStr"/>
+      <c r="E32" s="86" t="inlineStr"/>
+      <c r="F32" s="86" t="inlineStr"/>
+      <c r="G32" s="86" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="80" t="inlineStr">
+      <c r="A33" s="84" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="B33" s="80" t="inlineStr">
+      <c r="B33" s="84" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1782,22 +1770,22 @@
           <t>Manifestazioni di interessePR FESR SICILIA 2021/27 - NUOVO Avviso a manifestazione d’interesse per esperti valutatoriScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D33" s="81" t="inlineStr">
+      <c r="D33" s="85" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/pr-fesr-sicilia-202127-nuovo-avviso-manifestazione-d-interesse-esperti-valutatori</t>
         </is>
       </c>
-      <c r="E33" s="80" t="inlineStr"/>
-      <c r="F33" s="80" t="inlineStr"/>
-      <c r="G33" s="80" t="inlineStr"/>
+      <c r="E33" s="84" t="inlineStr"/>
+      <c r="F33" s="84" t="inlineStr"/>
+      <c r="G33" s="84" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="82" t="inlineStr">
+      <c r="A34" s="86" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="B34" s="82" t="inlineStr">
+      <c r="B34" s="86" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -1807,22 +1795,22 @@
           <t>Bando 2026 per contributi dedicati alla manutenzione della rete dei percorsi escursionistici</t>
         </is>
       </c>
-      <c r="D34" s="83" t="inlineStr">
+      <c r="D34" s="87" t="inlineStr">
         <is>
           <t>https://ambiente.regione.emilia-romagna.it/it/parchi-natura2000/bandi/bando-2026-per-contributi-dedicati-alla-manutenzione-della-rete-dei-percorsi-escursionistici</t>
         </is>
       </c>
-      <c r="E34" s="82" t="inlineStr"/>
-      <c r="F34" s="82" t="inlineStr"/>
-      <c r="G34" s="82" t="inlineStr"/>
+      <c r="E34" s="86" t="inlineStr"/>
+      <c r="F34" s="86" t="inlineStr"/>
+      <c r="G34" s="86" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="80" t="inlineStr">
+      <c r="A35" s="84" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="B35" s="80" t="inlineStr">
+      <c r="B35" s="84" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1832,22 +1820,22 @@
           <t>Programma regionale in favore delle tradizioni storiche, artistiche, religiose e popolari (2026) – manifestazioni d’interesseApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D35" s="81" t="inlineStr">
+      <c r="D35" s="85" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/programma-regionale-in-favore-delle-tradizioni-storiche-artistiche-religiose-e-popolari-2026-manifestazioni-dinteresse/</t>
         </is>
       </c>
-      <c r="E35" s="80" t="inlineStr"/>
-      <c r="F35" s="80" t="inlineStr"/>
-      <c r="G35" s="80" t="inlineStr"/>
+      <c r="E35" s="84" t="inlineStr"/>
+      <c r="F35" s="84" t="inlineStr"/>
+      <c r="G35" s="84" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="82" t="inlineStr">
+      <c r="A36" s="86" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B36" s="82" t="inlineStr">
+      <c r="B36" s="86" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1857,22 +1845,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEBuoni servizio per le persone non autosufficienti nel territorio del LazioProssima AperturaFSE / FSE+</t>
         </is>
       </c>
-      <c r="D36" s="83" t="inlineStr">
+      <c r="D36" s="87" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/buoni-servizio-per-le-persone-non-autosufficienti-nel-territorio-del-lazio/</t>
         </is>
       </c>
-      <c r="E36" s="82" t="inlineStr"/>
-      <c r="F36" s="82" t="inlineStr"/>
-      <c r="G36" s="82" t="inlineStr"/>
+      <c r="E36" s="86" t="inlineStr"/>
+      <c r="F36" s="86" t="inlineStr"/>
+      <c r="G36" s="86" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="80" t="inlineStr">
+      <c r="A37" s="84" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B37" s="80" t="inlineStr">
+      <c r="B37" s="84" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1882,22 +1870,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONERimborso delle rette dei servizi educativi nel territorio del LazioProssima AperturaFSE / FSE+</t>
         </is>
       </c>
-      <c r="D37" s="81" t="inlineStr">
+      <c r="D37" s="85" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/rimborso-delle-rette-dei-servizi-educativi-nel-territorio-del-lazio/</t>
         </is>
       </c>
-      <c r="E37" s="80" t="inlineStr"/>
-      <c r="F37" s="80" t="inlineStr"/>
-      <c r="G37" s="80" t="inlineStr"/>
+      <c r="E37" s="84" t="inlineStr"/>
+      <c r="F37" s="84" t="inlineStr"/>
+      <c r="G37" s="84" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="82" t="inlineStr">
+      <c r="A38" s="86" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B38" s="82" t="inlineStr">
+      <c r="B38" s="86" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1907,30 +1895,30 @@
           <t>Manifestazioni di interesseATTO DI INTERPELLO PER L’AFFIDAMENTO DELL’INCARICO DI COLLAUDO STATICO DELLE STRUTTURE - Diga di Pietrarossa (Progetto ex C</t>
         </is>
       </c>
-      <c r="D38" s="83" t="inlineStr">
+      <c r="D38" s="87" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/atto-interpello-l-affidamento-incarico-collaudo-statico-strutture-diga-pietrarossa-progetto-ex-casmez-303219</t>
         </is>
       </c>
-      <c r="E38" s="82" t="inlineStr">
+      <c r="E38" s="86" t="inlineStr">
         <is>
           <t>27/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F38" s="82" t="inlineStr">
+      <c r="F38" s="86" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="G38" s="82" t="inlineStr"/>
+      <c r="G38" s="86" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="80" t="inlineStr">
+      <c r="A39" s="84" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B39" s="80" t="inlineStr">
+      <c r="B39" s="84" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1940,30 +1928,30 @@
           <t>Manifestazioni di interesseAvviso alle Case  Editrici della Regione siciliana per la partecipazione al Salone del Libro di Torino, 14-18  maggio 2026.</t>
         </is>
       </c>
-      <c r="D39" s="81" t="inlineStr">
+      <c r="D39" s="85" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/manifestazione-d-interesse-partecipare-al-xxxviii-salone-libro-torino-14-al-18-maggio-2026-attraverso-l-esposizione-pubblicazioni-presso-stand-assessorato-beni</t>
         </is>
       </c>
-      <c r="E39" s="80" t="inlineStr">
+      <c r="E39" s="84" t="inlineStr">
         <is>
           <t>30/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F39" s="80" t="inlineStr">
+      <c r="F39" s="84" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="G39" s="80" t="inlineStr"/>
+      <c r="G39" s="84" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="82" t="inlineStr">
+      <c r="A40" s="86" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B40" s="82" t="inlineStr">
+      <c r="B40" s="86" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1973,30 +1961,30 @@
           <t xml:space="preserve">Manifestazioni di interessePR FESR SICILIA 2021/27 - NUOVO Avviso a manifestazione d’interesse per esperti valutatoriScade il:06/04/2026 - 23:59Leggi </t>
         </is>
       </c>
-      <c r="D40" s="83" t="inlineStr">
+      <c r="D40" s="87" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/pr-fesr-sicilia-202127-nuovo-avviso-manifestazione-d-interesse-esperti-valutatori</t>
         </is>
       </c>
-      <c r="E40" s="82" t="inlineStr">
+      <c r="E40" s="86" t="inlineStr">
         <is>
           <t>06/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F40" s="82" t="inlineStr">
+      <c r="F40" s="86" t="inlineStr">
         <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="G40" s="82" t="inlineStr"/>
+      <c r="G40" s="86" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="80" t="inlineStr">
+      <c r="A41" s="84" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B41" s="80" t="inlineStr">
+      <c r="B41" s="84" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2006,22 +1994,22 @@
           <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D41" s="81" t="inlineStr">
+      <c r="D41" s="85" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
         </is>
       </c>
-      <c r="E41" s="80" t="inlineStr"/>
-      <c r="F41" s="80" t="inlineStr"/>
-      <c r="G41" s="80" t="inlineStr"/>
+      <c r="E41" s="84" t="inlineStr"/>
+      <c r="F41" s="84" t="inlineStr"/>
+      <c r="G41" s="84" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="82" t="inlineStr">
+      <c r="A42" s="86" t="inlineStr">
         <is>
           <t>24/03/2026</t>
         </is>
       </c>
-      <c r="B42" s="82" t="inlineStr">
+      <c r="B42" s="86" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2031,22 +2019,22 @@
           <t>GAL del Ducato - Promozione di fiere agroalimentari e delle filiere del cibo – Bando per Enti pubblici (DU AS 05B)</t>
         </is>
       </c>
-      <c r="D42" s="83" t="inlineStr">
+      <c r="D42" s="87" t="inlineStr">
         <is>
           <t>https://agricoltura.regione.emilia-romagna.it/sviluppo-rurale-23-27/opportunita/bandi-gal/2026/du_as05b-promozione-di-fiere-agroalimentari-e-delle-filiere-del-cibo-bando-per-enti-pubblici</t>
         </is>
       </c>
-      <c r="E42" s="82" t="inlineStr"/>
-      <c r="F42" s="82" t="inlineStr"/>
-      <c r="G42" s="82" t="inlineStr"/>
+      <c r="E42" s="86" t="inlineStr"/>
+      <c r="F42" s="86" t="inlineStr"/>
+      <c r="G42" s="86" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="80" t="inlineStr">
+      <c r="A43" s="84" t="inlineStr">
         <is>
           <t>24/03/2026</t>
         </is>
       </c>
-      <c r="B43" s="80" t="inlineStr">
+      <c r="B43" s="84" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2056,30 +2044,30 @@
           <t>Manifestazioni di interesseAVVISO PUBBLICO PER MANIFESTAZIONE DI INTERESSE FINALIZZATA ALL'ASSEGNAZIONE DI SPAZI ESPOSITIVI (CORNER GRATUITI) ALL'INTE</t>
         </is>
       </c>
-      <c r="D43" s="81" t="inlineStr">
+      <c r="D43" s="85" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-manifestazione-interesse-finalizzata-all-assegnazione-spazi-espositivi-corner-gratuiti-all-interno-stand-istituzionale-dsrt-manifestazione</t>
         </is>
       </c>
-      <c r="E43" s="80" t="inlineStr">
+      <c r="E43" s="84" t="inlineStr">
         <is>
           <t>30/03/2026 - 13:00</t>
         </is>
       </c>
-      <c r="F43" s="80" t="inlineStr">
+      <c r="F43" s="84" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G43" s="80" t="inlineStr"/>
+      <c r="G43" s="84" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="82" t="inlineStr">
+      <c r="A44" s="86" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B44" s="82" t="inlineStr">
+      <c r="B44" s="86" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2089,22 +2077,22 @@
           <t>Avviso per la concessione di contributi per eventi sportivi realizzati in Emilia-Romagna - Anno 2026</t>
         </is>
       </c>
-      <c r="D44" s="83" t="inlineStr">
+      <c r="D44" s="87" t="inlineStr">
         <is>
           <t>https://www.regione.emilia-romagna.it/sport/bandi/2026/bando-2026</t>
         </is>
       </c>
-      <c r="E44" s="82" t="inlineStr"/>
-      <c r="F44" s="82" t="inlineStr"/>
-      <c r="G44" s="82" t="inlineStr"/>
+      <c r="E44" s="86" t="inlineStr"/>
+      <c r="F44" s="86" t="inlineStr"/>
+      <c r="G44" s="86" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="80" t="inlineStr">
+      <c r="A45" s="84" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B45" s="80" t="inlineStr">
+      <c r="B45" s="84" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2114,22 +2102,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Street art 2026Prossima AperturaBandi Regionali</t>
         </is>
       </c>
-      <c r="D45" s="81" t="inlineStr">
+      <c r="D45" s="85" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lazio-street-art-2026/</t>
         </is>
       </c>
-      <c r="E45" s="80" t="inlineStr"/>
-      <c r="F45" s="80" t="inlineStr"/>
-      <c r="G45" s="80" t="inlineStr"/>
+      <c r="E45" s="84" t="inlineStr"/>
+      <c r="F45" s="84" t="inlineStr"/>
+      <c r="G45" s="84" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="82" t="inlineStr">
+      <c r="A46" s="86" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B46" s="82" t="inlineStr">
+      <c r="B46" s="86" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2139,30 +2127,30 @@
           <t>Manifestazioni di interesseManifestazione di interesse per la partecipazione all’evento “R2I Italy 2026” – Bologna, 12-13/05/2026Scade il:03/04/2026 -</t>
         </is>
       </c>
-      <c r="D46" s="83" t="inlineStr">
+      <c r="D46" s="87" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/manifestazione-interesse-partecipazione-all-evento-r2i-italy-2026-bologna-12-13052026</t>
         </is>
       </c>
-      <c r="E46" s="82" t="inlineStr">
+      <c r="E46" s="86" t="inlineStr">
         <is>
           <t>03/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F46" s="82" t="inlineStr">
+      <c r="F46" s="86" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="G46" s="82" t="inlineStr"/>
+      <c r="G46" s="86" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="80" t="inlineStr">
+      <c r="A47" s="84" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B47" s="80" t="inlineStr">
+      <c r="B47" s="84" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2172,30 +2160,30 @@
           <t>Manifestazioni di interesseST SIRACUSA - AVVISO PER MANIFESTAZIONE DI INTERESSE - Selezione di n. 5 unità di personale internoScade il:20/04/2026 - 12</t>
         </is>
       </c>
-      <c r="D47" s="81" t="inlineStr">
+      <c r="D47" s="85" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/24-marzo-2026-st-siracusa-avviso-manifestazione-interesse-selezione-n-5-unita-personale-interno</t>
         </is>
       </c>
-      <c r="E47" s="80" t="inlineStr">
+      <c r="E47" s="84" t="inlineStr">
         <is>
           <t>20/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F47" s="80" t="inlineStr">
+      <c r="F47" s="84" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="G47" s="80" t="inlineStr"/>
+      <c r="G47" s="84" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="82" t="inlineStr">
+      <c r="A48" s="86" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B48" s="82" t="inlineStr">
+      <c r="B48" s="86" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2205,30 +2193,30 @@
           <t>Avvisi pubbliciRevoca dell’avviso di concessione a titolo gratuito del 16.12.2025 inerente all’immobile di seguito identificato e contestuale nuovo av</t>
         </is>
       </c>
-      <c r="D48" s="83" t="inlineStr">
+      <c r="D48" s="87" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/revoca-avviso-concessione-titolo-gratuito-16122025-inerente-all-immobile-seguito-identificato-contestuale-nuovo-avviso-concessione-titolo-oneroso-stesso-sito-nel</t>
         </is>
       </c>
-      <c r="E48" s="82" t="inlineStr">
+      <c r="E48" s="86" t="inlineStr">
         <is>
           <t>08/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F48" s="82" t="inlineStr">
+      <c r="F48" s="86" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="G48" s="82" t="inlineStr"/>
+      <c r="G48" s="86" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="80" t="inlineStr">
+      <c r="A49" s="84" t="inlineStr">
         <is>
           <t>26/03/2026</t>
         </is>
       </c>
-      <c r="B49" s="80" t="inlineStr">
+      <c r="B49" s="84" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2238,22 +2226,22 @@
           <t>Bando studi di fattibilità per fusioni di Comuni</t>
         </is>
       </c>
-      <c r="D49" s="81" t="inlineStr">
+      <c r="D49" s="85" t="inlineStr">
         <is>
           <t>https://www.regione.emilia-romagna.it/autonomie-locali/bandi/bando_studi_fattibilita_fusioni_comuni</t>
         </is>
       </c>
-      <c r="E49" s="80" t="inlineStr"/>
-      <c r="F49" s="80" t="inlineStr"/>
-      <c r="G49" s="80" t="inlineStr"/>
+      <c r="E49" s="84" t="inlineStr"/>
+      <c r="F49" s="84" t="inlineStr"/>
+      <c r="G49" s="84" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="82" t="inlineStr">
+      <c r="A50" s="86" t="inlineStr">
         <is>
           <t>26/03/2026</t>
         </is>
       </c>
-      <c r="B50" s="82" t="inlineStr">
+      <c r="B50" s="86" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2263,30 +2251,30 @@
           <t xml:space="preserve">Manifestazioni di interesseAvviso pubblico di selezione interna, per titoli, per il conferimento di PO e professionali, ai sensi degli artt. 19, 20 e </t>
         </is>
       </c>
-      <c r="D50" s="83" t="inlineStr">
+      <c r="D50" s="87" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-selezione-interna-titoli-conferimento-po-professionali-ai-sensi-artt-19-20-21-ccrl-20222024-comparto-non-dirigenziale</t>
         </is>
       </c>
-      <c r="E50" s="82" t="inlineStr">
+      <c r="E50" s="86" t="inlineStr">
         <is>
           <t>30/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F50" s="82" t="inlineStr">
+      <c r="F50" s="86" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G50" s="82" t="inlineStr"/>
+      <c r="G50" s="86" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="80" t="inlineStr">
+      <c r="A51" s="84" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="B51" s="80" t="inlineStr">
+      <c r="B51" s="84" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2296,22 +2284,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0PRE-SEED 3.0ApertoFESR</t>
         </is>
       </c>
-      <c r="D51" s="81" t="inlineStr">
+      <c r="D51" s="85" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/pre-seed-3-0/</t>
         </is>
       </c>
-      <c r="E51" s="80" t="inlineStr"/>
-      <c r="F51" s="80" t="inlineStr"/>
-      <c r="G51" s="80" t="inlineStr"/>
+      <c r="E51" s="84" t="inlineStr"/>
+      <c r="F51" s="84" t="inlineStr"/>
+      <c r="G51" s="84" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="82" t="inlineStr">
+      <c r="A52" s="86" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B52" s="82" t="inlineStr">
+      <c r="B52" s="86" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2321,30 +2309,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “So</t>
         </is>
       </c>
-      <c r="D52" s="83" t="inlineStr">
+      <c r="D52" s="87" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-termini-imerese-locta-piazza-marina</t>
         </is>
       </c>
-      <c r="E52" s="82" t="inlineStr">
+      <c r="E52" s="86" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F52" s="82" t="inlineStr">
+      <c r="F52" s="86" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G52" s="82" t="inlineStr"/>
+      <c r="G52" s="86" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="80" t="inlineStr">
+      <c r="A53" s="84" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B53" s="80" t="inlineStr">
+      <c r="B53" s="84" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2354,30 +2342,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, Sig</t>
         </is>
       </c>
-      <c r="D53" s="81" t="inlineStr">
+      <c r="D53" s="85" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-porto-empedocle-locta-punta-piccola</t>
         </is>
       </c>
-      <c r="E53" s="80" t="inlineStr">
+      <c r="E53" s="84" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F53" s="80" t="inlineStr">
+      <c r="F53" s="84" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G53" s="80" t="inlineStr"/>
+      <c r="G53" s="84" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="82" t="inlineStr">
+      <c r="A54" s="86" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B54" s="82" t="inlineStr">
+      <c r="B54" s="86" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2387,30 +2375,30 @@
           <t xml:space="preserve">Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “Società </t>
         </is>
       </c>
-      <c r="D54" s="83" t="inlineStr">
+      <c r="D54" s="87" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-messina-locta-torrente-bordonaro</t>
         </is>
       </c>
-      <c r="E54" s="82" t="inlineStr">
+      <c r="E54" s="86" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F54" s="82" t="inlineStr">
+      <c r="F54" s="86" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G54" s="82" t="inlineStr"/>
+      <c r="G54" s="86" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="80" t="inlineStr">
+      <c r="A55" s="84" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B55" s="80" t="inlineStr">
+      <c r="B55" s="84" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2420,30 +2408,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “Condomin</t>
         </is>
       </c>
-      <c r="D55" s="81" t="inlineStr">
+      <c r="D55" s="85" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-mascali-spiaggia-n-144150</t>
         </is>
       </c>
-      <c r="E55" s="80" t="inlineStr">
+      <c r="E55" s="84" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F55" s="80" t="inlineStr">
+      <c r="F55" s="84" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G55" s="80" t="inlineStr"/>
+      <c r="G55" s="84" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="82" t="inlineStr">
+      <c r="A56" s="86" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B56" s="82" t="inlineStr">
+      <c r="B56" s="86" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2453,30 +2441,30 @@
           <t xml:space="preserve">Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione sito nel Comune di Lipari, isola di Stromboli, </t>
         </is>
       </c>
-      <c r="D56" s="83" t="inlineStr">
+      <c r="D56" s="87" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-lipari-isola-stromboli-locta-fico-grande</t>
         </is>
       </c>
-      <c r="E56" s="82" t="inlineStr">
+      <c r="E56" s="86" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F56" s="82" t="inlineStr">
+      <c r="F56" s="86" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G56" s="82" t="inlineStr"/>
+      <c r="G56" s="86" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="80" t="inlineStr">
+      <c r="A57" s="84" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B57" s="80" t="inlineStr">
+      <c r="B57" s="84" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2486,30 +2474,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione sito nel Comune di Favignana, isola di Le</t>
         </is>
       </c>
-      <c r="D57" s="81" t="inlineStr">
+      <c r="D57" s="85" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-favignana-isola-levanzo</t>
         </is>
       </c>
-      <c r="E57" s="80" t="inlineStr">
+      <c r="E57" s="84" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F57" s="80" t="inlineStr">
+      <c r="F57" s="84" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G57" s="80" t="inlineStr"/>
+      <c r="G57" s="84" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="82" t="inlineStr">
+      <c r="A58" s="86" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="B58" s="82" t="inlineStr">
+      <c r="B58" s="86" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2519,30 +2507,30 @@
           <t>Manifestazioni di interesseAVVISO - Manifestazione d’interesse finalizzata alla selezione di organismi attuatori di piani di gestione locale della pic</t>
         </is>
       </c>
-      <c r="D58" s="83" t="inlineStr">
+      <c r="D58" s="87" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-d-interesse-finalizzata-alla-selezione-organismi-attuatori-piani-gestione-locale-piccola-pesca-costiera-nelle-gsa-regione-siciliana</t>
         </is>
       </c>
-      <c r="E58" s="82" t="inlineStr">
+      <c r="E58" s="86" t="inlineStr">
         <is>
           <t>29/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F58" s="82" t="inlineStr">
+      <c r="F58" s="86" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="G58" s="82" t="inlineStr"/>
+      <c r="G58" s="86" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="80" t="inlineStr">
+      <c r="A59" s="84" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="B59" s="80" t="inlineStr">
+      <c r="B59" s="84" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2552,30 +2540,30 @@
           <t>Avvisi pubbliciLeggi e scarica l'avvisoScade il:02/04/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D59" s="81" t="inlineStr">
+      <c r="D59" s="85" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/proroga-termini-presentazione-candidature-po</t>
         </is>
       </c>
-      <c r="E59" s="80" t="inlineStr">
+      <c r="E59" s="84" t="inlineStr">
         <is>
           <t>02/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F59" s="80" t="inlineStr">
+      <c r="F59" s="84" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="G59" s="80" t="inlineStr"/>
+      <c r="G59" s="84" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="82" t="inlineStr">
+      <c r="A60" s="86" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="82" t="inlineStr">
+      <c r="B60" s="86" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2585,22 +2573,22 @@
           <t>INTERNAZIONALIZZAZIONESMAU – Italy RestartsUp in STOCCOLMAApertoFESR</t>
         </is>
       </c>
-      <c r="D60" s="83" t="inlineStr">
+      <c r="D60" s="87" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/smau-italy-restartsup-in-stoccolma/</t>
         </is>
       </c>
-      <c r="E60" s="82" t="inlineStr"/>
-      <c r="F60" s="82" t="inlineStr"/>
-      <c r="G60" s="82" t="inlineStr"/>
+      <c r="E60" s="86" t="inlineStr"/>
+      <c r="F60" s="86" t="inlineStr"/>
+      <c r="G60" s="86" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="80" t="inlineStr">
+      <c r="A61" s="84" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B61" s="80" t="inlineStr">
+      <c r="B61" s="84" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2610,22 +2598,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per Farnborough International AirshowApertoFESR</t>
         </is>
       </c>
-      <c r="D61" s="81" t="inlineStr">
+      <c r="D61" s="85" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-farnborough-international-airshow-2/</t>
         </is>
       </c>
-      <c r="E61" s="80" t="inlineStr"/>
-      <c r="F61" s="80" t="inlineStr"/>
-      <c r="G61" s="80" t="inlineStr"/>
+      <c r="E61" s="84" t="inlineStr"/>
+      <c r="F61" s="84" t="inlineStr"/>
+      <c r="G61" s="84" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="82" t="inlineStr">
+      <c r="A62" s="86" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="82" t="inlineStr">
+      <c r="B62" s="86" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2635,30 +2623,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA - alienazione lotto di terreno sito nel comune di Termini Imerese, via LibertàScade il:30/04/2026 - 12:00Leg</t>
         </is>
       </c>
-      <c r="D62" s="83" t="inlineStr">
+      <c r="D62" s="87" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proprieta-regionale-sito-nel-comune-termini-imerese-favore-ares-fabiola</t>
         </is>
       </c>
-      <c r="E62" s="82" t="inlineStr">
+      <c r="E62" s="86" t="inlineStr">
         <is>
           <t>30/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F62" s="82" t="inlineStr">
+      <c r="F62" s="86" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="G62" s="82" t="inlineStr"/>
+      <c r="G62" s="86" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="80" t="inlineStr">
+      <c r="A63" s="84" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B63" s="80" t="inlineStr">
+      <c r="B63" s="84" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2668,22 +2656,22 @@
           <t>Avviso per la concessione di contributi per progetti di contrasto all'abbandono sportivo giovanile (2026)</t>
         </is>
       </c>
-      <c r="D63" s="81" t="inlineStr">
+      <c r="D63" s="85" t="inlineStr">
         <is>
           <t>https://www.regione.emilia-romagna.it/sport/bandi/2026/contrasto-abbandono-2026</t>
         </is>
       </c>
-      <c r="E63" s="80" t="inlineStr"/>
-      <c r="F63" s="80" t="inlineStr"/>
-      <c r="G63" s="80" t="inlineStr"/>
+      <c r="E63" s="84" t="inlineStr"/>
+      <c r="F63" s="84" t="inlineStr"/>
+      <c r="G63" s="84" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="82" t="inlineStr">
+      <c r="A64" s="86" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="82" t="inlineStr">
+      <c r="B64" s="86" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2693,30 +2681,30 @@
           <t>Avvisi pubbliciAvviso si procede alla riassegnazione della posizione organizzativa a supporto delle attività del Servizio 2 “Investimenti in Agricoltu</t>
         </is>
       </c>
-      <c r="D64" s="83" t="inlineStr">
+      <c r="D64" s="87" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-selezione-interna-conferimento-1-posizione-organizzativa-ai-sensi-artt-19-20-ccrl-2022-2024-comparto-non-dirigenziale</t>
         </is>
       </c>
-      <c r="E64" s="82" t="inlineStr">
+      <c r="E64" s="86" t="inlineStr">
         <is>
           <t>09/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F64" s="82" t="inlineStr">
+      <c r="F64" s="86" t="inlineStr">
         <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="G64" s="82" t="inlineStr"/>
+      <c r="G64" s="86" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="80" t="inlineStr">
+      <c r="A65" s="84" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B65" s="80" t="inlineStr">
+      <c r="B65" s="84" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2726,30 +2714,30 @@
           <t>Avvisi pubbliciST-MESSINA - AVVISO di INDAGINE DI MERCATO per affidamento "Interventi manutenzione straordinaria della strada/pista forestale "Annunzi</t>
         </is>
       </c>
-      <c r="D65" s="81" t="inlineStr">
+      <c r="D65" s="85" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-indagine-mercato-affidamento-interventi-manutenzione-straordinaria-stradapista-forestale-annunziata-comune-messina</t>
         </is>
       </c>
-      <c r="E65" s="80" t="inlineStr">
+      <c r="E65" s="84" t="inlineStr">
         <is>
           <t>16/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F65" s="80" t="inlineStr">
+      <c r="F65" s="84" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="G65" s="80" t="inlineStr"/>
+      <c r="G65" s="84" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="82" t="inlineStr">
+      <c r="A66" s="86" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="82" t="inlineStr">
+      <c r="B66" s="86" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2759,30 +2747,30 @@
           <t>Avvisi pubbliciST-MESSINA - AVVISO DI INDAGINE DI MERCATO per affidamento "Interventi manutenzione straordinaria della strada/pista forestale "San Riz</t>
         </is>
       </c>
-      <c r="D66" s="83" t="inlineStr">
+      <c r="D66" s="87" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-indagine-mercato-affidamento-interventi-manutenzione-straordinaria-stradapista-forestale-san-rizzo-san-leone-crupi-madonuzza-comune-messina</t>
         </is>
       </c>
-      <c r="E66" s="82" t="inlineStr">
+      <c r="E66" s="86" t="inlineStr">
         <is>
           <t>16/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F66" s="82" t="inlineStr">
+      <c r="F66" s="86" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="G66" s="82" t="inlineStr"/>
+      <c r="G66" s="86" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="80" t="inlineStr">
+      <c r="A67" s="84" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="80" t="inlineStr">
+      <c r="B67" s="84" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2792,22 +2780,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Manifestazione di interesse per Casaidea 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D67" s="81" t="inlineStr">
+      <c r="D67" s="85" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-casaidea-2026/</t>
         </is>
       </c>
-      <c r="E67" s="80" t="inlineStr"/>
-      <c r="F67" s="80" t="inlineStr"/>
-      <c r="G67" s="80" t="inlineStr"/>
+      <c r="E67" s="84" t="inlineStr"/>
+      <c r="F67" s="84" t="inlineStr"/>
+      <c r="G67" s="84" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="82" t="inlineStr">
+      <c r="A68" s="86" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="82" t="inlineStr">
+      <c r="B68" s="86" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2817,22 +2805,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per il Salone Internazionale del Libro di Torino 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D68" s="83" t="inlineStr">
+      <c r="D68" s="87" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-il-salone-internazionale-del-libro-di-torino-2026/</t>
         </is>
       </c>
-      <c r="E68" s="82" t="inlineStr"/>
-      <c r="F68" s="82" t="inlineStr"/>
-      <c r="G68" s="82" t="inlineStr"/>
+      <c r="E68" s="86" t="inlineStr"/>
+      <c r="F68" s="86" t="inlineStr"/>
+      <c r="G68" s="86" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="80" t="inlineStr">
+      <c r="A69" s="84" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="80" t="inlineStr">
+      <c r="B69" s="84" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2842,30 +2830,30 @@
           <t>Avvisi pubbliciDDG 1112 del 02.04.2026 - Aggiornamento Avviso pubblico n. 4/2024 per l’attuazione del PAR GOL Sicilia da finanziare nell’ambito del Pi</t>
         </is>
       </c>
-      <c r="D69" s="81" t="inlineStr">
+      <c r="D69" s="85" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/ddg-1112-02042026-aggiornamento-avviso-pubblico-n-42024-l-attuazione-par-gol-sicilia-finanziare-nell-ambito-piano-nazionale-ripresa-resilienza-pnrr</t>
         </is>
       </c>
-      <c r="E69" s="80" t="inlineStr">
+      <c r="E69" s="84" t="inlineStr">
         <is>
           <t>05/04/2030 - 00:00</t>
         </is>
       </c>
-      <c r="F69" s="80" t="inlineStr">
+      <c r="F69" s="84" t="inlineStr">
         <is>
           <t>05/04/2030</t>
         </is>
       </c>
-      <c r="G69" s="80" t="inlineStr"/>
+      <c r="G69" s="84" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="82" t="inlineStr">
+      <c r="A70" s="86" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="82" t="inlineStr">
+      <c r="B70" s="86" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2875,30 +2863,30 @@
           <t>Avvisi pubbliciDDG 1113 del  02.04.2026 - Aggiornamento Avviso pubblico n. 2/2022 e s.m.i per l’attuazione del PAR GOL Sicilia da finanziare nell’ambi</t>
         </is>
       </c>
-      <c r="D70" s="83" t="inlineStr">
+      <c r="D70" s="87" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/ddg-1113-02042026-aggiornamento-avviso-pubblico-n-22022-smi-l-attuazione-par-gol-sicilia-finanziare-nell-ambito-piano-nazionale-ripresa-resilienza-pnrr</t>
         </is>
       </c>
-      <c r="E70" s="82" t="inlineStr">
+      <c r="E70" s="86" t="inlineStr">
         <is>
           <t>03/04/2030 - 00:00</t>
         </is>
       </c>
-      <c r="F70" s="82" t="inlineStr">
+      <c r="F70" s="86" t="inlineStr">
         <is>
           <t>03/04/2030</t>
         </is>
       </c>
-      <c r="G70" s="82" t="inlineStr"/>
+      <c r="G70" s="86" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="80" t="inlineStr">
+      <c r="A71" s="84" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B71" s="80" t="inlineStr">
+      <c r="B71" s="84" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2908,22 +2896,22 @@
           <t>Avvisi pubbliciLeggi e scarica l'avvisoScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D71" s="81" t="inlineStr">
+      <c r="D71" s="85" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/proroga-termini-presentazione-candidature-po</t>
         </is>
       </c>
-      <c r="E71" s="80" t="inlineStr"/>
-      <c r="F71" s="80" t="inlineStr"/>
-      <c r="G71" s="80" t="inlineStr"/>
+      <c r="E71" s="84" t="inlineStr"/>
+      <c r="F71" s="84" t="inlineStr"/>
+      <c r="G71" s="84" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="82" t="inlineStr">
+      <c r="A72" s="86" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="82" t="inlineStr">
+      <c r="B72" s="86" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2933,22 +2921,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEComunicare l’inclusione – contest per le istituzioni scolastiche regionaliApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D72" s="83" t="inlineStr">
+      <c r="D72" s="87" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/comunicare-linclusione-contest-per-le-istituzioni-scolastiche-regionali/</t>
         </is>
       </c>
-      <c r="E72" s="82" t="inlineStr"/>
-      <c r="F72" s="82" t="inlineStr"/>
-      <c r="G72" s="82" t="inlineStr"/>
+      <c r="E72" s="86" t="inlineStr"/>
+      <c r="F72" s="86" t="inlineStr"/>
+      <c r="G72" s="86" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="80" t="inlineStr">
+      <c r="A73" s="84" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B73" s="80" t="inlineStr">
+      <c r="B73" s="84" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2958,30 +2946,30 @@
           <t>Avvisi pubbliciAPPROVAZIONE AVVISO PUBBLICOScade il:03/04/2027 - 00:00Leggi di più</t>
         </is>
       </c>
-      <c r="D73" s="81" t="inlineStr">
+      <c r="D73" s="85" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/approvazione-avviso-pubblico</t>
         </is>
       </c>
-      <c r="E73" s="80" t="inlineStr">
+      <c r="E73" s="84" t="inlineStr">
         <is>
           <t>03/04/2027 - 00:00</t>
         </is>
       </c>
-      <c r="F73" s="80" t="inlineStr">
+      <c r="F73" s="84" t="inlineStr">
         <is>
           <t>03/04/2027</t>
         </is>
       </c>
-      <c r="G73" s="80" t="inlineStr"/>
+      <c r="G73" s="84" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="82" t="inlineStr">
+      <c r="A74" s="86" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="82" t="inlineStr">
+      <c r="B74" s="86" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2991,22 +2979,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Donne e Impresa 2026Prossima AperturaFESR</t>
         </is>
       </c>
-      <c r="D74" s="83" t="inlineStr">
+      <c r="D74" s="87" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/donne-e-impresa-2026/</t>
         </is>
       </c>
-      <c r="E74" s="82" t="inlineStr"/>
-      <c r="F74" s="82" t="inlineStr"/>
-      <c r="G74" s="82" t="inlineStr"/>
+      <c r="E74" s="86" t="inlineStr"/>
+      <c r="F74" s="86" t="inlineStr"/>
+      <c r="G74" s="86" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="80" t="inlineStr">
+      <c r="A75" s="84" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B75" s="80" t="inlineStr">
+      <c r="B75" s="84" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3016,30 +3004,30 @@
           <t>Bandi di garaCodice Intervento 111302_FELUCHE - Investimenti a bordo e nei porti per incrementare la qualità delle produzioni e migliorare le condizio</t>
         </is>
       </c>
-      <c r="D75" s="81" t="inlineStr">
+      <c r="D75" s="85" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/bandoavviso-regia-ob-11-azione-3-codice-111302feluche-investimenti-bordo-valorizzazione-feluche-miglioramento-condizioni-lavoro-salute-sicurezza-operatori-l</t>
         </is>
       </c>
-      <c r="E75" s="80" t="inlineStr">
+      <c r="E75" s="84" t="inlineStr">
         <is>
           <t>02/07/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F75" s="80" t="inlineStr">
+      <c r="F75" s="84" t="inlineStr">
         <is>
           <t>02/07/2026</t>
         </is>
       </c>
-      <c r="G75" s="80" t="inlineStr"/>
+      <c r="G75" s="84" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="82" t="inlineStr">
+      <c r="A76" s="86" t="inlineStr">
         <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="82" t="inlineStr">
+      <c r="B76" s="86" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -3049,22 +3037,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURASostegno agli investimenti nel settore vitivinicolo – campagna 2026/2027ApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D76" s="83" t="inlineStr">
+      <c r="D76" s="87" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/sostegno-agli-investimenti-nel-settore-vitivinicolo-campagna-2026-2027/</t>
         </is>
       </c>
-      <c r="E76" s="82" t="inlineStr"/>
-      <c r="F76" s="82" t="inlineStr"/>
-      <c r="G76" s="82" t="inlineStr"/>
+      <c r="E76" s="86" t="inlineStr"/>
+      <c r="F76" s="86" t="inlineStr"/>
+      <c r="G76" s="86" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="80" t="inlineStr">
+      <c r="A77" s="84" t="inlineStr">
         <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="80" t="inlineStr">
+      <c r="B77" s="84" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3074,30 +3062,30 @@
           <t>Manifestazioni di interesse9 aprile 2026 -ST PALERMO- Manifestazione di interesse - “Interventi di manutenzione straordinaria della strada-pista fores</t>
         </is>
       </c>
-      <c r="D77" s="81" t="inlineStr">
+      <c r="D77" s="85" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/9-aprile-2026-st-palermo-manifestazione-interesse-interventi-manutenzione-straordinaria-strada-pista-forestale-monte-cane-comune-caccamo-pa-distretto-forestale</t>
         </is>
       </c>
-      <c r="E77" s="80" t="inlineStr">
+      <c r="E77" s="84" t="inlineStr">
         <is>
           <t>24/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F77" s="80" t="inlineStr">
+      <c r="F77" s="84" t="inlineStr">
         <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="G77" s="80" t="inlineStr"/>
+      <c r="G77" s="84" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="82" t="inlineStr">
+      <c r="A78" s="86" t="inlineStr">
         <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="82" t="inlineStr">
+      <c r="B78" s="86" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3107,30 +3095,30 @@
           <t>Avvisi pubbliciST-MESSINA - AVVISO DI INDAGINE DI MERCATO per affidamento "Interventi manutenzione straordinaria della strada/pista forestale "Faggita</t>
         </is>
       </c>
-      <c r="D78" s="83" t="inlineStr">
+      <c r="D78" s="87" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-indagine-mercato-affidamento-interventi-manutenzione-straordinaria-stradapista-forestale-faggita-comune-tripi-me</t>
         </is>
       </c>
-      <c r="E78" s="82" t="inlineStr">
+      <c r="E78" s="86" t="inlineStr">
         <is>
           <t>23/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F78" s="82" t="inlineStr">
+      <c r="F78" s="86" t="inlineStr">
         <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="G78" s="82" t="inlineStr"/>
+      <c r="G78" s="86" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="80" t="inlineStr">
+      <c r="A79" s="84" t="inlineStr">
         <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B79" s="80" t="inlineStr">
+      <c r="B79" s="84" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3140,22 +3128,22 @@
           <t>Avvisi pubbliciST-MESSINA - AVVISO DI INDAGINE DI MERCATO per affidamento "Interventi manutenzione straordinaria della strada/pista forestale "Ferraro</t>
         </is>
       </c>
-      <c r="D79" s="81" t="inlineStr">
+      <c r="D79" s="85" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-indagine-mercato-affidamento-interventi-manutenzione-straordinaria-stradapista-forestale-ferraro-sanrizzo-badiazza-comune-messina</t>
         </is>
       </c>
-      <c r="E79" s="80" t="inlineStr">
+      <c r="E79" s="84" t="inlineStr">
         <is>
           <t>23/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F79" s="80" t="inlineStr">
+      <c r="F79" s="84" t="inlineStr">
         <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="G79" s="80" t="inlineStr"/>
+      <c r="G79" s="84" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="86" t="inlineStr">
@@ -3214,6 +3202,39 @@
         </is>
       </c>
       <c r="G81" s="84" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="90" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="90" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Avvisi pubbliciAVVISO DI INDAGINE DI MERCATO  per la partecipazione alla successiva procedura negoziata a norma dell'art. 50, comma 1, lettera c) del </t>
+        </is>
+      </c>
+      <c r="D82" s="91" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-indagine-mercato-partecipazione-alla-successiva-procedura-negoziata-norma-art-50-comma-1-lettera-c-dlgs-31-marzo-2023-n-36-ssmmii-finalizzata-all</t>
+        </is>
+      </c>
+      <c r="E82" s="90" t="inlineStr">
+        <is>
+          <t>30/04/2026 - 12:00</t>
+        </is>
+      </c>
+      <c r="F82" s="90" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="G82" s="90" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -3297,6 +3318,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D82" r:id="rId81"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3341,7 +3363,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="84" t="inlineStr">
+      <c r="A3" s="88" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -3354,7 +3376,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="86" t="inlineStr">
+      <c r="A4" s="90" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -3363,17 +3385,17 @@
         <v>31</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="84" t="inlineStr">
+      <c r="A5" s="88" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>1</v>

--- a/data/bandi_export.xlsx
+++ b/data/bandi_export.xlsx
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -387,6 +387,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -769,7 +778,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏛️  Nuovi Bandi — 14/04/2026 08:23</t>
+          <t>🏛️  Nuovi Bandi — 15/04/2026 08:24</t>
         </is>
       </c>
     </row>
@@ -814,31 +823,23 @@
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="88" t="inlineStr">
-        <is>
-          <t>Sicilia</t>
+      <c r="B3" s="92" t="inlineStr">
+        <is>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avvisi pubbliciAVVISO DI INDAGINE DI MERCATO  per la partecipazione alla successiva procedura negoziata a norma dell'art. 50, comma 1, lettera c) del </t>
-        </is>
-      </c>
-      <c r="D3" s="89" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-indagine-mercato-partecipazione-alla-successiva-procedura-negoziata-norma-art-50-comma-1-lettera-c-dlgs-31-marzo-2023-n-36-ssmmii-finalizzata-all</t>
-        </is>
-      </c>
-      <c r="E3" s="88" t="inlineStr">
-        <is>
-          <t>30/04/2026 - 12:00</t>
-        </is>
-      </c>
-      <c r="F3" s="88" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
+          <t>LAVORO, FORMAZIONE E INCLUSIONEVoucher per lo Sport – individuazione dei destinatari (II edizione)ApertoFSE / FSE+</t>
+        </is>
+      </c>
+      <c r="D3" s="93" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/voucher-per-lo-sport-individuazione-dei-destinatari-ii-edizione/</t>
+        </is>
+      </c>
+      <c r="E3" s="92" t="inlineStr"/>
+      <c r="F3" s="92" t="inlineStr"/>
       <c r="G3" s="5" t="inlineStr"/>
     </row>
   </sheetData>
@@ -858,7 +859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -908,12 +909,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="86" t="inlineStr">
+      <c r="A2" s="90" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B2" s="86" t="inlineStr">
+      <c r="B2" s="90" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -923,22 +924,22 @@
           <t>FLAG GALPA Costa E-R. Sostituzione del motore principale e dei motori secondari. Secondo bando</t>
         </is>
       </c>
-      <c r="D2" s="87" t="inlineStr">
+      <c r="D2" s="91" t="inlineStr">
         <is>
           <t>https://agricoltura.regione.emilia-romagna.it/feampa-2021-2027/bandi-galpa/2026/galpa-sostituzione-motori-secondo-bando</t>
         </is>
       </c>
-      <c r="E2" s="86" t="inlineStr"/>
-      <c r="F2" s="86" t="inlineStr"/>
-      <c r="G2" s="86" t="inlineStr"/>
+      <c r="E2" s="90" t="inlineStr"/>
+      <c r="F2" s="90" t="inlineStr"/>
+      <c r="G2" s="90" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="84" t="inlineStr">
+      <c r="A3" s="88" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B3" s="84" t="inlineStr">
+      <c r="B3" s="88" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -948,22 +949,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0PRE-SEED 3.0Prossima AperturaFESR</t>
         </is>
       </c>
-      <c r="D3" s="85" t="inlineStr">
+      <c r="D3" s="89" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/pre-seed-3-0/</t>
         </is>
       </c>
-      <c r="E3" s="84" t="inlineStr"/>
-      <c r="F3" s="84" t="inlineStr"/>
-      <c r="G3" s="84" t="inlineStr"/>
+      <c r="E3" s="88" t="inlineStr"/>
+      <c r="F3" s="88" t="inlineStr"/>
+      <c r="G3" s="88" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="86" t="inlineStr">
+      <c r="A4" s="90" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B4" s="86" t="inlineStr">
+      <c r="B4" s="90" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -973,22 +974,22 @@
           <t>ACCESSO AL CREDITO E ALLE GARANZIE PER LE IMPRESEContributo su finanziamenti alle imprese del Lazio erogati su provvista BEIProssima AperturaFESR</t>
         </is>
       </c>
-      <c r="D4" s="87" t="inlineStr">
+      <c r="D4" s="91" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-su-finanziamenti-alle-imprese-del-lazio-erogati-su-provvista-bei/</t>
         </is>
       </c>
-      <c r="E4" s="86" t="inlineStr"/>
-      <c r="F4" s="86" t="inlineStr"/>
-      <c r="G4" s="86" t="inlineStr"/>
+      <c r="E4" s="90" t="inlineStr"/>
+      <c r="F4" s="90" t="inlineStr"/>
+      <c r="G4" s="90" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="84" t="inlineStr">
+      <c r="A5" s="88" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B5" s="84" t="inlineStr">
+      <c r="B5" s="88" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -998,22 +999,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEIndividuazione degli enti iscritti al Registro unico nazionale del Terzo settoreApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D5" s="85" t="inlineStr">
+      <c r="D5" s="89" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/individuazione-degli-enti-iscritti-al-registro-unico-nazionale-del-terzo-settore/</t>
         </is>
       </c>
-      <c r="E5" s="84" t="inlineStr"/>
-      <c r="F5" s="84" t="inlineStr"/>
-      <c r="G5" s="84" t="inlineStr"/>
+      <c r="E5" s="88" t="inlineStr"/>
+      <c r="F5" s="88" t="inlineStr"/>
+      <c r="G5" s="88" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="86" t="inlineStr">
+      <c r="A6" s="90" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B6" s="86" t="inlineStr">
+      <c r="B6" s="90" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1023,22 +1024,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Technology Transfer LazioApertoFESR</t>
         </is>
       </c>
-      <c r="D6" s="87" t="inlineStr">
+      <c r="D6" s="91" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/technology-transfer-lazio/</t>
         </is>
       </c>
-      <c r="E6" s="86" t="inlineStr"/>
-      <c r="F6" s="86" t="inlineStr"/>
-      <c r="G6" s="86" t="inlineStr"/>
+      <c r="E6" s="90" t="inlineStr"/>
+      <c r="F6" s="90" t="inlineStr"/>
+      <c r="G6" s="90" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="84" t="inlineStr">
+      <c r="A7" s="88" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B7" s="84" t="inlineStr">
+      <c r="B7" s="88" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1048,22 +1049,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Percorso di tutoraggio per le impreseApertoFESR</t>
         </is>
       </c>
-      <c r="D7" s="85" t="inlineStr">
+      <c r="D7" s="89" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/percorso-di-tutoraggio-per-le-imprese/</t>
         </is>
       </c>
-      <c r="E7" s="84" t="inlineStr"/>
-      <c r="F7" s="84" t="inlineStr"/>
-      <c r="G7" s="84" t="inlineStr"/>
+      <c r="E7" s="88" t="inlineStr"/>
+      <c r="F7" s="88" t="inlineStr"/>
+      <c r="G7" s="88" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="86" t="inlineStr">
+      <c r="A8" s="90" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B8" s="86" t="inlineStr">
+      <c r="B8" s="90" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1073,22 +1074,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per partecipare a SMAU Parigi 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D8" s="87" t="inlineStr">
+      <c r="D8" s="91" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-partecipare-a-smau-parigi-2026/</t>
         </is>
       </c>
-      <c r="E8" s="86" t="inlineStr"/>
-      <c r="F8" s="86" t="inlineStr"/>
-      <c r="G8" s="86" t="inlineStr"/>
+      <c r="E8" s="90" t="inlineStr"/>
+      <c r="F8" s="90" t="inlineStr"/>
+      <c r="G8" s="90" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="84" t="inlineStr">
+      <c r="A9" s="88" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B9" s="84" t="inlineStr">
+      <c r="B9" s="88" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1098,22 +1099,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONERiconoscimento della funzione sociale ed educativa degli oratoriApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D9" s="85" t="inlineStr">
+      <c r="D9" s="89" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/riconoscimento-della-funzione-sociale-ed-educativa-degli-oratori/</t>
         </is>
       </c>
-      <c r="E9" s="84" t="inlineStr"/>
-      <c r="F9" s="84" t="inlineStr"/>
-      <c r="G9" s="84" t="inlineStr"/>
+      <c r="E9" s="88" t="inlineStr"/>
+      <c r="F9" s="88" t="inlineStr"/>
+      <c r="G9" s="88" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="86" t="inlineStr">
+      <c r="A10" s="90" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B10" s="86" t="inlineStr">
+      <c r="B10" s="90" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1123,22 +1124,22 @@
           <t>GovernanceIscrizione nell’elenco regionale degli idonei all’esercizio dell’attività di direttore dell’Istituto JemoloApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D10" s="87" t="inlineStr">
+      <c r="D10" s="91" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/iscrizione-nellelenco-regionale-degli-idonei-allesercizio-dellattivita-di-direttore-dellistituto-jemolo/</t>
         </is>
       </c>
-      <c r="E10" s="86" t="inlineStr"/>
-      <c r="F10" s="86" t="inlineStr"/>
-      <c r="G10" s="86" t="inlineStr"/>
+      <c r="E10" s="90" t="inlineStr"/>
+      <c r="F10" s="90" t="inlineStr"/>
+      <c r="G10" s="90" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="84" t="inlineStr">
+      <c r="A11" s="88" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B11" s="84" t="inlineStr">
+      <c r="B11" s="88" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1148,22 +1149,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEVoucher per lo sport – seconda annualitàApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D11" s="85" t="inlineStr">
+      <c r="D11" s="89" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/voucher-per-lo-sport-seconda-annualita/</t>
         </is>
       </c>
-      <c r="E11" s="84" t="inlineStr"/>
-      <c r="F11" s="84" t="inlineStr"/>
-      <c r="G11" s="84" t="inlineStr"/>
+      <c r="E11" s="88" t="inlineStr"/>
+      <c r="F11" s="88" t="inlineStr"/>
+      <c r="G11" s="88" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="86" t="inlineStr">
+      <c r="A12" s="90" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B12" s="86" t="inlineStr">
+      <c r="B12" s="90" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1173,22 +1174,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEBonus occupazionale SALGOApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D12" s="87" t="inlineStr">
+      <c r="D12" s="91" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/bonus-occupazionale-salgo/</t>
         </is>
       </c>
-      <c r="E12" s="86" t="inlineStr"/>
-      <c r="F12" s="86" t="inlineStr"/>
-      <c r="G12" s="86" t="inlineStr"/>
+      <c r="E12" s="90" t="inlineStr"/>
+      <c r="F12" s="90" t="inlineStr"/>
+      <c r="G12" s="90" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="84" t="inlineStr">
+      <c r="A13" s="88" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B13" s="84" t="inlineStr">
+      <c r="B13" s="88" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1198,22 +1199,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEContributo di Libertà per le donne che hanno subito violenzaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D13" s="85" t="inlineStr">
+      <c r="D13" s="89" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-di-liberta-per-le-donne-che-hanno-subito-violenza/</t>
         </is>
       </c>
-      <c r="E13" s="84" t="inlineStr"/>
-      <c r="F13" s="84" t="inlineStr"/>
-      <c r="G13" s="84" t="inlineStr"/>
+      <c r="E13" s="88" t="inlineStr"/>
+      <c r="F13" s="88" t="inlineStr"/>
+      <c r="G13" s="88" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="86" t="inlineStr">
+      <c r="A14" s="90" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B14" s="86" t="inlineStr">
+      <c r="B14" s="90" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1223,22 +1224,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURAInterventi straordinari di valorizzazione del patrimonio culturale del LazioApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D14" s="87" t="inlineStr">
+      <c r="D14" s="91" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/interventi-straordinari-di-valorizzazione-del-patrimonio-culturale-del-lazio/</t>
         </is>
       </c>
-      <c r="E14" s="86" t="inlineStr"/>
-      <c r="F14" s="86" t="inlineStr"/>
-      <c r="G14" s="86" t="inlineStr"/>
+      <c r="E14" s="90" t="inlineStr"/>
+      <c r="F14" s="90" t="inlineStr"/>
+      <c r="G14" s="90" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="84" t="inlineStr">
+      <c r="A15" s="88" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B15" s="84" t="inlineStr">
+      <c r="B15" s="88" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1248,30 +1249,30 @@
           <t>Bandi di garaBANDO ATTUAZIONE Ob. 1.1 Azione 1 codice 111102 _DIV - "SOSTEGNO ALLA DIVERSIFICAZIONE E NUOVE FORME DI REDDITO PER LA PICCOLA PESCA COST</t>
         </is>
       </c>
-      <c r="D15" s="85" t="inlineStr">
+      <c r="D15" s="89" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/bando-avviso-regia-ob-11-azione-1-codice-111102-div-sostegno-alla-diversificazione-nuove-forme-reddito-piccola-pesca-costiera</t>
         </is>
       </c>
-      <c r="E15" s="84" t="inlineStr">
+      <c r="E15" s="88" t="inlineStr">
         <is>
           <t>07/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F15" s="84" t="inlineStr">
+      <c r="F15" s="88" t="inlineStr">
         <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="G15" s="84" t="inlineStr"/>
+      <c r="G15" s="88" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="86" t="inlineStr">
+      <c r="A16" s="90" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B16" s="86" t="inlineStr">
+      <c r="B16" s="90" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1281,30 +1282,30 @@
           <t>Avvisi pubblici09 marzo 2026 - ST SIRACUSA - AVVISO PUBBLICO PER LA COSTITUZIONE DI ELENCHI DI OPERATORI ECONOMICI PER L’ACQUISIZIONE DI BENI E SERVIZ</t>
         </is>
       </c>
-      <c r="D16" s="87" t="inlineStr">
+      <c r="D16" s="91" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/09-marzo-2026-st-siracusa-avviso-pubblico-costituzione-elenchi-operatori-economici-l-acquisizione-beni-servizi</t>
         </is>
       </c>
-      <c r="E16" s="86" t="inlineStr">
+      <c r="E16" s="90" t="inlineStr">
         <is>
           <t>31/12/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F16" s="86" t="inlineStr">
+      <c r="F16" s="90" t="inlineStr">
         <is>
           <t>31/12/2026</t>
         </is>
       </c>
-      <c r="G16" s="86" t="inlineStr"/>
+      <c r="G16" s="90" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="84" t="inlineStr">
+      <c r="A17" s="88" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B17" s="84" t="inlineStr">
+      <c r="B17" s="88" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1314,30 +1315,30 @@
           <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScade il:19/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D17" s="85" t="inlineStr">
+      <c r="D17" s="89" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
         </is>
       </c>
-      <c r="E17" s="84" t="inlineStr">
+      <c r="E17" s="88" t="inlineStr">
         <is>
           <t>19/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F17" s="84" t="inlineStr">
+      <c r="F17" s="88" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G17" s="84" t="inlineStr"/>
+      <c r="G17" s="88" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="86" t="inlineStr">
+      <c r="A18" s="90" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B18" s="86" t="inlineStr">
+      <c r="B18" s="90" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1347,22 +1348,22 @@
           <t>Manifestazioni di interesseAvviso Manifestazione Interesse DISTRIBUTORI AUTOMATICI di bevande e snackScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D18" s="87" t="inlineStr">
+      <c r="D18" s="91" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-distributori-automatici-bevande-snack</t>
         </is>
       </c>
-      <c r="E18" s="86" t="inlineStr"/>
-      <c r="F18" s="86" t="inlineStr"/>
-      <c r="G18" s="86" t="inlineStr"/>
+      <c r="E18" s="90" t="inlineStr"/>
+      <c r="F18" s="90" t="inlineStr"/>
+      <c r="G18" s="90" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="84" t="inlineStr">
+      <c r="A19" s="88" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B19" s="84" t="inlineStr">
+      <c r="B19" s="88" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1372,30 +1373,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D19" s="85" t="inlineStr">
+      <c r="D19" s="89" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo</t>
         </is>
       </c>
-      <c r="E19" s="84" t="inlineStr">
+      <c r="E19" s="88" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F19" s="84" t="inlineStr">
+      <c r="F19" s="88" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G19" s="84" t="inlineStr"/>
+      <c r="G19" s="88" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="86" t="inlineStr">
+      <c r="A20" s="90" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B20" s="86" t="inlineStr">
+      <c r="B20" s="90" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1405,30 +1406,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D20" s="87" t="inlineStr">
+      <c r="D20" s="91" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo-0</t>
         </is>
       </c>
-      <c r="E20" s="86" t="inlineStr">
+      <c r="E20" s="90" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F20" s="86" t="inlineStr">
+      <c r="F20" s="90" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G20" s="86" t="inlineStr"/>
+      <c r="G20" s="90" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="84" t="inlineStr">
+      <c r="A21" s="88" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B21" s="84" t="inlineStr">
+      <c r="B21" s="88" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1438,22 +1439,22 @@
           <t>Manifestazioni di interesseST SIRACUSA - AVVISO DI MANIFESTAZIONE DI INTERESSE - Fornitura applicativo extracontabile per la gestione progetti, ecc. e</t>
         </is>
       </c>
-      <c r="D21" s="85" t="inlineStr">
+      <c r="D21" s="89" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-siracusa-avviso-manifestazione-interesse-fornitura-applicativo-extracontabile-gestione-progetti-ecc-applicativo-gestione-ed-elaborazione-informatizzata-paghe</t>
         </is>
       </c>
-      <c r="E21" s="84" t="inlineStr"/>
-      <c r="F21" s="84" t="inlineStr"/>
-      <c r="G21" s="84" t="inlineStr"/>
+      <c r="E21" s="88" t="inlineStr"/>
+      <c r="F21" s="88" t="inlineStr"/>
+      <c r="G21" s="88" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="86" t="inlineStr">
+      <c r="A22" s="90" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B22" s="86" t="inlineStr">
+      <c r="B22" s="90" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1463,30 +1464,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile sito nel Comune di Capo D'Orlando, Via Trazzera MarinaScade il:25/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D22" s="87" t="inlineStr">
+      <c r="D22" s="91" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-sito-nel-comune-capo-d-orlando-trazzera-marina</t>
         </is>
       </c>
-      <c r="E22" s="86" t="inlineStr">
+      <c r="E22" s="90" t="inlineStr">
         <is>
           <t>25/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F22" s="86" t="inlineStr">
+      <c r="F22" s="90" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="G22" s="86" t="inlineStr"/>
+      <c r="G22" s="90" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="84" t="inlineStr">
+      <c r="A23" s="88" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B23" s="84" t="inlineStr">
+      <c r="B23" s="88" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1496,22 +1497,22 @@
           <t xml:space="preserve">Avvisi pubbliciST CATANIA - Programma Regionale FESR Sicilia 2021-2027 - Azione 2.4.4 - “Interventi per la riduzione del rischio incendi” - AVVISO DI </t>
         </is>
       </c>
-      <c r="D23" s="85" t="inlineStr">
+      <c r="D23" s="89" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-catania-programma-regionale-fesr-sicilia-2021-2027-azione-244-interventi-riduzione-rischio-incendi-avviso-indagine-mercato</t>
         </is>
       </c>
-      <c r="E23" s="84" t="inlineStr"/>
-      <c r="F23" s="84" t="inlineStr"/>
-      <c r="G23" s="84" t="inlineStr"/>
+      <c r="E23" s="88" t="inlineStr"/>
+      <c r="F23" s="88" t="inlineStr"/>
+      <c r="G23" s="88" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="86" t="inlineStr">
+      <c r="A24" s="90" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B24" s="86" t="inlineStr">
+      <c r="B24" s="90" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1521,22 +1522,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per ROMICS – Primavera 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D24" s="87" t="inlineStr">
+      <c r="D24" s="91" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-romics-primavera-2026/</t>
         </is>
       </c>
-      <c r="E24" s="86" t="inlineStr"/>
-      <c r="F24" s="86" t="inlineStr"/>
-      <c r="G24" s="86" t="inlineStr"/>
+      <c r="E24" s="90" t="inlineStr"/>
+      <c r="F24" s="90" t="inlineStr"/>
+      <c r="G24" s="90" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="84" t="inlineStr">
+      <c r="A25" s="88" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B25" s="84" t="inlineStr">
+      <c r="B25" s="88" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1546,22 +1547,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Cinema International 2026 – I edizioneApertoFESR</t>
         </is>
       </c>
-      <c r="D25" s="85" t="inlineStr">
+      <c r="D25" s="89" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lazio-cinema-international-2026-i-edizione/</t>
         </is>
       </c>
-      <c r="E25" s="84" t="inlineStr"/>
-      <c r="F25" s="84" t="inlineStr"/>
-      <c r="G25" s="84" t="inlineStr"/>
+      <c r="E25" s="88" t="inlineStr"/>
+      <c r="F25" s="88" t="inlineStr"/>
+      <c r="G25" s="88" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="86" t="inlineStr">
+      <c r="A26" s="90" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B26" s="86" t="inlineStr">
+      <c r="B26" s="90" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1571,22 +1572,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEManifestazioni di interesse alla costituzione di due nuove Fondazioni I.T.S. AcademyApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D26" s="87" t="inlineStr">
+      <c r="D26" s="91" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazioni-di-interesse-alla-costituzione-di-due-nuove-fondazioni-i-t-s-academy/</t>
         </is>
       </c>
-      <c r="E26" s="86" t="inlineStr"/>
-      <c r="F26" s="86" t="inlineStr"/>
-      <c r="G26" s="86" t="inlineStr"/>
+      <c r="E26" s="90" t="inlineStr"/>
+      <c r="F26" s="90" t="inlineStr"/>
+      <c r="G26" s="90" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="84" t="inlineStr">
+      <c r="A27" s="88" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B27" s="84" t="inlineStr">
+      <c r="B27" s="88" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1596,22 +1597,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURAContributi per sostenere la ripresa del settore della pescaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D27" s="85" t="inlineStr">
+      <c r="D27" s="89" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributi-per-sostenere-la-ripresa-del-settore-della-pesca/</t>
         </is>
       </c>
-      <c r="E27" s="84" t="inlineStr"/>
-      <c r="F27" s="84" t="inlineStr"/>
-      <c r="G27" s="84" t="inlineStr"/>
+      <c r="E27" s="88" t="inlineStr"/>
+      <c r="F27" s="88" t="inlineStr"/>
+      <c r="G27" s="88" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="86" t="inlineStr">
+      <c r="A28" s="90" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B28" s="86" t="inlineStr">
+      <c r="B28" s="90" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1621,30 +1622,30 @@
           <t>Manifestazioni di interesseAVVISO - Manifestazione Interesse “Storytelling aziendale” Expo Wild Natura - Caccia - Pesca. Misterbianco (CT), 10-12 apri</t>
         </is>
       </c>
-      <c r="D28" s="87" t="inlineStr">
+      <c r="D28" s="91" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-storytelling-aziendale-expo-wild-natura-caccia-pesca-misterbianco-ct-10-12-aprile-2026</t>
         </is>
       </c>
-      <c r="E28" s="86" t="inlineStr">
+      <c r="E28" s="90" t="inlineStr">
         <is>
           <t>30/03/2026 - 13:00</t>
         </is>
       </c>
-      <c r="F28" s="86" t="inlineStr">
+      <c r="F28" s="90" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G28" s="86" t="inlineStr"/>
+      <c r="G28" s="90" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="84" t="inlineStr">
+      <c r="A29" s="88" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B29" s="84" t="inlineStr">
+      <c r="B29" s="88" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1654,30 +1655,30 @@
           <t>Manifestazioni di interesseInvaso Lentini - Interventi di ripristino delle pareti esterne in cls della Torre di presa Sud e della trave d’appoggio del</t>
         </is>
       </c>
-      <c r="D29" s="85" t="inlineStr">
+      <c r="D29" s="89" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/invaso-lentini-interventi-ripristino-pareti-esterne-cls-torre-presa-sud-trave-d-appoggio-cavalcavia-collegamento-alla-stessa-torre</t>
         </is>
       </c>
-      <c r="E29" s="84" t="inlineStr">
+      <c r="E29" s="88" t="inlineStr">
         <is>
           <t>19/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F29" s="84" t="inlineStr">
+      <c r="F29" s="88" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G29" s="84" t="inlineStr"/>
+      <c r="G29" s="88" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="86" t="inlineStr">
+      <c r="A30" s="90" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="B30" s="86" t="inlineStr">
+      <c r="B30" s="90" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1687,22 +1688,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURARistrutturazione e riconversione vigneti – campagna 2026-2027ApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D30" s="87" t="inlineStr">
+      <c r="D30" s="91" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/ristrutturazione-e-riconversione-vigneti-campagna-2026-2027/</t>
         </is>
       </c>
-      <c r="E30" s="86" t="inlineStr"/>
-      <c r="F30" s="86" t="inlineStr"/>
-      <c r="G30" s="86" t="inlineStr"/>
+      <c r="E30" s="90" t="inlineStr"/>
+      <c r="F30" s="90" t="inlineStr"/>
+      <c r="G30" s="90" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="84" t="inlineStr">
+      <c r="A31" s="88" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="B31" s="84" t="inlineStr">
+      <c r="B31" s="88" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1712,30 +1713,30 @@
           <t>Manifestazioni di interessePR FESR 2021/27 Azione 1.3.3 e del POC 2014/20 - Azione 1.3.1  - Avviso a manifestazione d’interesse eventi fieristici inte</t>
         </is>
       </c>
-      <c r="D31" s="85" t="inlineStr">
+      <c r="D31" s="89" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-d-interesse-eventi-fieristici-internazionali-marzo-dicembre-2026</t>
         </is>
       </c>
-      <c r="E31" s="84" t="inlineStr">
+      <c r="E31" s="88" t="inlineStr">
         <is>
           <t>30/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F31" s="84" t="inlineStr">
+      <c r="F31" s="88" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="G31" s="84" t="inlineStr"/>
+      <c r="G31" s="88" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="86" t="inlineStr">
+      <c r="A32" s="90" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="B32" s="86" t="inlineStr">
+      <c r="B32" s="90" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1745,22 +1746,22 @@
           <t>INTERNAZIONALIZZAZIONEL’Ecosistema dell’Innovazione a INNOVIT – Focus S3ApertoFESR</t>
         </is>
       </c>
-      <c r="D32" s="87" t="inlineStr">
+      <c r="D32" s="91" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lecosistema-dellinnovazione-a-innovit-focus-s3/</t>
         </is>
       </c>
-      <c r="E32" s="86" t="inlineStr"/>
-      <c r="F32" s="86" t="inlineStr"/>
-      <c r="G32" s="86" t="inlineStr"/>
+      <c r="E32" s="90" t="inlineStr"/>
+      <c r="F32" s="90" t="inlineStr"/>
+      <c r="G32" s="90" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="84" t="inlineStr">
+      <c r="A33" s="88" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="B33" s="84" t="inlineStr">
+      <c r="B33" s="88" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1770,22 +1771,22 @@
           <t>Manifestazioni di interessePR FESR SICILIA 2021/27 - NUOVO Avviso a manifestazione d’interesse per esperti valutatoriScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D33" s="85" t="inlineStr">
+      <c r="D33" s="89" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/pr-fesr-sicilia-202127-nuovo-avviso-manifestazione-d-interesse-esperti-valutatori</t>
         </is>
       </c>
-      <c r="E33" s="84" t="inlineStr"/>
-      <c r="F33" s="84" t="inlineStr"/>
-      <c r="G33" s="84" t="inlineStr"/>
+      <c r="E33" s="88" t="inlineStr"/>
+      <c r="F33" s="88" t="inlineStr"/>
+      <c r="G33" s="88" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="86" t="inlineStr">
+      <c r="A34" s="90" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="B34" s="86" t="inlineStr">
+      <c r="B34" s="90" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -1795,22 +1796,22 @@
           <t>Bando 2026 per contributi dedicati alla manutenzione della rete dei percorsi escursionistici</t>
         </is>
       </c>
-      <c r="D34" s="87" t="inlineStr">
+      <c r="D34" s="91" t="inlineStr">
         <is>
           <t>https://ambiente.regione.emilia-romagna.it/it/parchi-natura2000/bandi/bando-2026-per-contributi-dedicati-alla-manutenzione-della-rete-dei-percorsi-escursionistici</t>
         </is>
       </c>
-      <c r="E34" s="86" t="inlineStr"/>
-      <c r="F34" s="86" t="inlineStr"/>
-      <c r="G34" s="86" t="inlineStr"/>
+      <c r="E34" s="90" t="inlineStr"/>
+      <c r="F34" s="90" t="inlineStr"/>
+      <c r="G34" s="90" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="84" t="inlineStr">
+      <c r="A35" s="88" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="B35" s="84" t="inlineStr">
+      <c r="B35" s="88" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1820,22 +1821,22 @@
           <t>Programma regionale in favore delle tradizioni storiche, artistiche, religiose e popolari (2026) – manifestazioni d’interesseApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D35" s="85" t="inlineStr">
+      <c r="D35" s="89" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/programma-regionale-in-favore-delle-tradizioni-storiche-artistiche-religiose-e-popolari-2026-manifestazioni-dinteresse/</t>
         </is>
       </c>
-      <c r="E35" s="84" t="inlineStr"/>
-      <c r="F35" s="84" t="inlineStr"/>
-      <c r="G35" s="84" t="inlineStr"/>
+      <c r="E35" s="88" t="inlineStr"/>
+      <c r="F35" s="88" t="inlineStr"/>
+      <c r="G35" s="88" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="86" t="inlineStr">
+      <c r="A36" s="90" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B36" s="86" t="inlineStr">
+      <c r="B36" s="90" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1845,22 +1846,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEBuoni servizio per le persone non autosufficienti nel territorio del LazioProssima AperturaFSE / FSE+</t>
         </is>
       </c>
-      <c r="D36" s="87" t="inlineStr">
+      <c r="D36" s="91" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/buoni-servizio-per-le-persone-non-autosufficienti-nel-territorio-del-lazio/</t>
         </is>
       </c>
-      <c r="E36" s="86" t="inlineStr"/>
-      <c r="F36" s="86" t="inlineStr"/>
-      <c r="G36" s="86" t="inlineStr"/>
+      <c r="E36" s="90" t="inlineStr"/>
+      <c r="F36" s="90" t="inlineStr"/>
+      <c r="G36" s="90" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="84" t="inlineStr">
+      <c r="A37" s="88" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B37" s="84" t="inlineStr">
+      <c r="B37" s="88" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1870,22 +1871,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONERimborso delle rette dei servizi educativi nel territorio del LazioProssima AperturaFSE / FSE+</t>
         </is>
       </c>
-      <c r="D37" s="85" t="inlineStr">
+      <c r="D37" s="89" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/rimborso-delle-rette-dei-servizi-educativi-nel-territorio-del-lazio/</t>
         </is>
       </c>
-      <c r="E37" s="84" t="inlineStr"/>
-      <c r="F37" s="84" t="inlineStr"/>
-      <c r="G37" s="84" t="inlineStr"/>
+      <c r="E37" s="88" t="inlineStr"/>
+      <c r="F37" s="88" t="inlineStr"/>
+      <c r="G37" s="88" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="86" t="inlineStr">
+      <c r="A38" s="90" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B38" s="86" t="inlineStr">
+      <c r="B38" s="90" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1895,30 +1896,30 @@
           <t>Manifestazioni di interesseATTO DI INTERPELLO PER L’AFFIDAMENTO DELL’INCARICO DI COLLAUDO STATICO DELLE STRUTTURE - Diga di Pietrarossa (Progetto ex C</t>
         </is>
       </c>
-      <c r="D38" s="87" t="inlineStr">
+      <c r="D38" s="91" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/atto-interpello-l-affidamento-incarico-collaudo-statico-strutture-diga-pietrarossa-progetto-ex-casmez-303219</t>
         </is>
       </c>
-      <c r="E38" s="86" t="inlineStr">
+      <c r="E38" s="90" t="inlineStr">
         <is>
           <t>27/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F38" s="86" t="inlineStr">
+      <c r="F38" s="90" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="G38" s="86" t="inlineStr"/>
+      <c r="G38" s="90" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="84" t="inlineStr">
+      <c r="A39" s="88" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B39" s="84" t="inlineStr">
+      <c r="B39" s="88" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1928,30 +1929,30 @@
           <t>Manifestazioni di interesseAvviso alle Case  Editrici della Regione siciliana per la partecipazione al Salone del Libro di Torino, 14-18  maggio 2026.</t>
         </is>
       </c>
-      <c r="D39" s="85" t="inlineStr">
+      <c r="D39" s="89" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/manifestazione-d-interesse-partecipare-al-xxxviii-salone-libro-torino-14-al-18-maggio-2026-attraverso-l-esposizione-pubblicazioni-presso-stand-assessorato-beni</t>
         </is>
       </c>
-      <c r="E39" s="84" t="inlineStr">
+      <c r="E39" s="88" t="inlineStr">
         <is>
           <t>30/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F39" s="84" t="inlineStr">
+      <c r="F39" s="88" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="G39" s="84" t="inlineStr"/>
+      <c r="G39" s="88" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="86" t="inlineStr">
+      <c r="A40" s="90" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B40" s="86" t="inlineStr">
+      <c r="B40" s="90" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1961,30 +1962,30 @@
           <t xml:space="preserve">Manifestazioni di interessePR FESR SICILIA 2021/27 - NUOVO Avviso a manifestazione d’interesse per esperti valutatoriScade il:06/04/2026 - 23:59Leggi </t>
         </is>
       </c>
-      <c r="D40" s="87" t="inlineStr">
+      <c r="D40" s="91" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/pr-fesr-sicilia-202127-nuovo-avviso-manifestazione-d-interesse-esperti-valutatori</t>
         </is>
       </c>
-      <c r="E40" s="86" t="inlineStr">
+      <c r="E40" s="90" t="inlineStr">
         <is>
           <t>06/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F40" s="86" t="inlineStr">
+      <c r="F40" s="90" t="inlineStr">
         <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="G40" s="86" t="inlineStr"/>
+      <c r="G40" s="90" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="84" t="inlineStr">
+      <c r="A41" s="88" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B41" s="84" t="inlineStr">
+      <c r="B41" s="88" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1994,22 +1995,22 @@
           <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D41" s="85" t="inlineStr">
+      <c r="D41" s="89" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
         </is>
       </c>
-      <c r="E41" s="84" t="inlineStr"/>
-      <c r="F41" s="84" t="inlineStr"/>
-      <c r="G41" s="84" t="inlineStr"/>
+      <c r="E41" s="88" t="inlineStr"/>
+      <c r="F41" s="88" t="inlineStr"/>
+      <c r="G41" s="88" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="86" t="inlineStr">
+      <c r="A42" s="90" t="inlineStr">
         <is>
           <t>24/03/2026</t>
         </is>
       </c>
-      <c r="B42" s="86" t="inlineStr">
+      <c r="B42" s="90" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2019,22 +2020,22 @@
           <t>GAL del Ducato - Promozione di fiere agroalimentari e delle filiere del cibo – Bando per Enti pubblici (DU AS 05B)</t>
         </is>
       </c>
-      <c r="D42" s="87" t="inlineStr">
+      <c r="D42" s="91" t="inlineStr">
         <is>
           <t>https://agricoltura.regione.emilia-romagna.it/sviluppo-rurale-23-27/opportunita/bandi-gal/2026/du_as05b-promozione-di-fiere-agroalimentari-e-delle-filiere-del-cibo-bando-per-enti-pubblici</t>
         </is>
       </c>
-      <c r="E42" s="86" t="inlineStr"/>
-      <c r="F42" s="86" t="inlineStr"/>
-      <c r="G42" s="86" t="inlineStr"/>
+      <c r="E42" s="90" t="inlineStr"/>
+      <c r="F42" s="90" t="inlineStr"/>
+      <c r="G42" s="90" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="84" t="inlineStr">
+      <c r="A43" s="88" t="inlineStr">
         <is>
           <t>24/03/2026</t>
         </is>
       </c>
-      <c r="B43" s="84" t="inlineStr">
+      <c r="B43" s="88" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2044,30 +2045,30 @@
           <t>Manifestazioni di interesseAVVISO PUBBLICO PER MANIFESTAZIONE DI INTERESSE FINALIZZATA ALL'ASSEGNAZIONE DI SPAZI ESPOSITIVI (CORNER GRATUITI) ALL'INTE</t>
         </is>
       </c>
-      <c r="D43" s="85" t="inlineStr">
+      <c r="D43" s="89" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-manifestazione-interesse-finalizzata-all-assegnazione-spazi-espositivi-corner-gratuiti-all-interno-stand-istituzionale-dsrt-manifestazione</t>
         </is>
       </c>
-      <c r="E43" s="84" t="inlineStr">
+      <c r="E43" s="88" t="inlineStr">
         <is>
           <t>30/03/2026 - 13:00</t>
         </is>
       </c>
-      <c r="F43" s="84" t="inlineStr">
+      <c r="F43" s="88" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G43" s="84" t="inlineStr"/>
+      <c r="G43" s="88" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="86" t="inlineStr">
+      <c r="A44" s="90" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B44" s="86" t="inlineStr">
+      <c r="B44" s="90" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2077,22 +2078,22 @@
           <t>Avviso per la concessione di contributi per eventi sportivi realizzati in Emilia-Romagna - Anno 2026</t>
         </is>
       </c>
-      <c r="D44" s="87" t="inlineStr">
+      <c r="D44" s="91" t="inlineStr">
         <is>
           <t>https://www.regione.emilia-romagna.it/sport/bandi/2026/bando-2026</t>
         </is>
       </c>
-      <c r="E44" s="86" t="inlineStr"/>
-      <c r="F44" s="86" t="inlineStr"/>
-      <c r="G44" s="86" t="inlineStr"/>
+      <c r="E44" s="90" t="inlineStr"/>
+      <c r="F44" s="90" t="inlineStr"/>
+      <c r="G44" s="90" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="84" t="inlineStr">
+      <c r="A45" s="88" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B45" s="84" t="inlineStr">
+      <c r="B45" s="88" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2102,22 +2103,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Street art 2026Prossima AperturaBandi Regionali</t>
         </is>
       </c>
-      <c r="D45" s="85" t="inlineStr">
+      <c r="D45" s="89" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lazio-street-art-2026/</t>
         </is>
       </c>
-      <c r="E45" s="84" t="inlineStr"/>
-      <c r="F45" s="84" t="inlineStr"/>
-      <c r="G45" s="84" t="inlineStr"/>
+      <c r="E45" s="88" t="inlineStr"/>
+      <c r="F45" s="88" t="inlineStr"/>
+      <c r="G45" s="88" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="86" t="inlineStr">
+      <c r="A46" s="90" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B46" s="86" t="inlineStr">
+      <c r="B46" s="90" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2127,30 +2128,30 @@
           <t>Manifestazioni di interesseManifestazione di interesse per la partecipazione all’evento “R2I Italy 2026” – Bologna, 12-13/05/2026Scade il:03/04/2026 -</t>
         </is>
       </c>
-      <c r="D46" s="87" t="inlineStr">
+      <c r="D46" s="91" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/manifestazione-interesse-partecipazione-all-evento-r2i-italy-2026-bologna-12-13052026</t>
         </is>
       </c>
-      <c r="E46" s="86" t="inlineStr">
+      <c r="E46" s="90" t="inlineStr">
         <is>
           <t>03/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F46" s="86" t="inlineStr">
+      <c r="F46" s="90" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="G46" s="86" t="inlineStr"/>
+      <c r="G46" s="90" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="84" t="inlineStr">
+      <c r="A47" s="88" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B47" s="84" t="inlineStr">
+      <c r="B47" s="88" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2160,30 +2161,30 @@
           <t>Manifestazioni di interesseST SIRACUSA - AVVISO PER MANIFESTAZIONE DI INTERESSE - Selezione di n. 5 unità di personale internoScade il:20/04/2026 - 12</t>
         </is>
       </c>
-      <c r="D47" s="85" t="inlineStr">
+      <c r="D47" s="89" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/24-marzo-2026-st-siracusa-avviso-manifestazione-interesse-selezione-n-5-unita-personale-interno</t>
         </is>
       </c>
-      <c r="E47" s="84" t="inlineStr">
+      <c r="E47" s="88" t="inlineStr">
         <is>
           <t>20/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F47" s="84" t="inlineStr">
+      <c r="F47" s="88" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="G47" s="84" t="inlineStr"/>
+      <c r="G47" s="88" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="86" t="inlineStr">
+      <c r="A48" s="90" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B48" s="86" t="inlineStr">
+      <c r="B48" s="90" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2193,30 +2194,30 @@
           <t>Avvisi pubbliciRevoca dell’avviso di concessione a titolo gratuito del 16.12.2025 inerente all’immobile di seguito identificato e contestuale nuovo av</t>
         </is>
       </c>
-      <c r="D48" s="87" t="inlineStr">
+      <c r="D48" s="91" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/revoca-avviso-concessione-titolo-gratuito-16122025-inerente-all-immobile-seguito-identificato-contestuale-nuovo-avviso-concessione-titolo-oneroso-stesso-sito-nel</t>
         </is>
       </c>
-      <c r="E48" s="86" t="inlineStr">
+      <c r="E48" s="90" t="inlineStr">
         <is>
           <t>08/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F48" s="86" t="inlineStr">
+      <c r="F48" s="90" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="G48" s="86" t="inlineStr"/>
+      <c r="G48" s="90" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="84" t="inlineStr">
+      <c r="A49" s="88" t="inlineStr">
         <is>
           <t>26/03/2026</t>
         </is>
       </c>
-      <c r="B49" s="84" t="inlineStr">
+      <c r="B49" s="88" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2226,22 +2227,22 @@
           <t>Bando studi di fattibilità per fusioni di Comuni</t>
         </is>
       </c>
-      <c r="D49" s="85" t="inlineStr">
+      <c r="D49" s="89" t="inlineStr">
         <is>
           <t>https://www.regione.emilia-romagna.it/autonomie-locali/bandi/bando_studi_fattibilita_fusioni_comuni</t>
         </is>
       </c>
-      <c r="E49" s="84" t="inlineStr"/>
-      <c r="F49" s="84" t="inlineStr"/>
-      <c r="G49" s="84" t="inlineStr"/>
+      <c r="E49" s="88" t="inlineStr"/>
+      <c r="F49" s="88" t="inlineStr"/>
+      <c r="G49" s="88" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="86" t="inlineStr">
+      <c r="A50" s="90" t="inlineStr">
         <is>
           <t>26/03/2026</t>
         </is>
       </c>
-      <c r="B50" s="86" t="inlineStr">
+      <c r="B50" s="90" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2251,30 +2252,30 @@
           <t xml:space="preserve">Manifestazioni di interesseAvviso pubblico di selezione interna, per titoli, per il conferimento di PO e professionali, ai sensi degli artt. 19, 20 e </t>
         </is>
       </c>
-      <c r="D50" s="87" t="inlineStr">
+      <c r="D50" s="91" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-selezione-interna-titoli-conferimento-po-professionali-ai-sensi-artt-19-20-21-ccrl-20222024-comparto-non-dirigenziale</t>
         </is>
       </c>
-      <c r="E50" s="86" t="inlineStr">
+      <c r="E50" s="90" t="inlineStr">
         <is>
           <t>30/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F50" s="86" t="inlineStr">
+      <c r="F50" s="90" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G50" s="86" t="inlineStr"/>
+      <c r="G50" s="90" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="84" t="inlineStr">
+      <c r="A51" s="88" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="B51" s="84" t="inlineStr">
+      <c r="B51" s="88" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2284,22 +2285,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0PRE-SEED 3.0ApertoFESR</t>
         </is>
       </c>
-      <c r="D51" s="85" t="inlineStr">
+      <c r="D51" s="89" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/pre-seed-3-0/</t>
         </is>
       </c>
-      <c r="E51" s="84" t="inlineStr"/>
-      <c r="F51" s="84" t="inlineStr"/>
-      <c r="G51" s="84" t="inlineStr"/>
+      <c r="E51" s="88" t="inlineStr"/>
+      <c r="F51" s="88" t="inlineStr"/>
+      <c r="G51" s="88" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="86" t="inlineStr">
+      <c r="A52" s="90" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B52" s="86" t="inlineStr">
+      <c r="B52" s="90" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2309,30 +2310,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “So</t>
         </is>
       </c>
-      <c r="D52" s="87" t="inlineStr">
+      <c r="D52" s="91" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-termini-imerese-locta-piazza-marina</t>
         </is>
       </c>
-      <c r="E52" s="86" t="inlineStr">
+      <c r="E52" s="90" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F52" s="86" t="inlineStr">
+      <c r="F52" s="90" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G52" s="86" t="inlineStr"/>
+      <c r="G52" s="90" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="84" t="inlineStr">
+      <c r="A53" s="88" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B53" s="84" t="inlineStr">
+      <c r="B53" s="88" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2342,30 +2343,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, Sig</t>
         </is>
       </c>
-      <c r="D53" s="85" t="inlineStr">
+      <c r="D53" s="89" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-porto-empedocle-locta-punta-piccola</t>
         </is>
       </c>
-      <c r="E53" s="84" t="inlineStr">
+      <c r="E53" s="88" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F53" s="84" t="inlineStr">
+      <c r="F53" s="88" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G53" s="84" t="inlineStr"/>
+      <c r="G53" s="88" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="86" t="inlineStr">
+      <c r="A54" s="90" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B54" s="86" t="inlineStr">
+      <c r="B54" s="90" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2375,30 +2376,30 @@
           <t xml:space="preserve">Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “Società </t>
         </is>
       </c>
-      <c r="D54" s="87" t="inlineStr">
+      <c r="D54" s="91" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-messina-locta-torrente-bordonaro</t>
         </is>
       </c>
-      <c r="E54" s="86" t="inlineStr">
+      <c r="E54" s="90" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F54" s="86" t="inlineStr">
+      <c r="F54" s="90" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G54" s="86" t="inlineStr"/>
+      <c r="G54" s="90" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="84" t="inlineStr">
+      <c r="A55" s="88" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B55" s="84" t="inlineStr">
+      <c r="B55" s="88" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2408,30 +2409,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “Condomin</t>
         </is>
       </c>
-      <c r="D55" s="85" t="inlineStr">
+      <c r="D55" s="89" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-mascali-spiaggia-n-144150</t>
         </is>
       </c>
-      <c r="E55" s="84" t="inlineStr">
+      <c r="E55" s="88" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F55" s="84" t="inlineStr">
+      <c r="F55" s="88" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G55" s="84" t="inlineStr"/>
+      <c r="G55" s="88" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="86" t="inlineStr">
+      <c r="A56" s="90" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B56" s="86" t="inlineStr">
+      <c r="B56" s="90" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2441,30 +2442,30 @@
           <t xml:space="preserve">Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione sito nel Comune di Lipari, isola di Stromboli, </t>
         </is>
       </c>
-      <c r="D56" s="87" t="inlineStr">
+      <c r="D56" s="91" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-lipari-isola-stromboli-locta-fico-grande</t>
         </is>
       </c>
-      <c r="E56" s="86" t="inlineStr">
+      <c r="E56" s="90" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F56" s="86" t="inlineStr">
+      <c r="F56" s="90" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G56" s="86" t="inlineStr"/>
+      <c r="G56" s="90" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="84" t="inlineStr">
+      <c r="A57" s="88" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B57" s="84" t="inlineStr">
+      <c r="B57" s="88" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2474,30 +2475,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione sito nel Comune di Favignana, isola di Le</t>
         </is>
       </c>
-      <c r="D57" s="85" t="inlineStr">
+      <c r="D57" s="89" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-favignana-isola-levanzo</t>
         </is>
       </c>
-      <c r="E57" s="84" t="inlineStr">
+      <c r="E57" s="88" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F57" s="84" t="inlineStr">
+      <c r="F57" s="88" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G57" s="84" t="inlineStr"/>
+      <c r="G57" s="88" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="86" t="inlineStr">
+      <c r="A58" s="90" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="B58" s="86" t="inlineStr">
+      <c r="B58" s="90" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2507,30 +2508,30 @@
           <t>Manifestazioni di interesseAVVISO - Manifestazione d’interesse finalizzata alla selezione di organismi attuatori di piani di gestione locale della pic</t>
         </is>
       </c>
-      <c r="D58" s="87" t="inlineStr">
+      <c r="D58" s="91" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-d-interesse-finalizzata-alla-selezione-organismi-attuatori-piani-gestione-locale-piccola-pesca-costiera-nelle-gsa-regione-siciliana</t>
         </is>
       </c>
-      <c r="E58" s="86" t="inlineStr">
+      <c r="E58" s="90" t="inlineStr">
         <is>
           <t>29/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F58" s="86" t="inlineStr">
+      <c r="F58" s="90" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="G58" s="86" t="inlineStr"/>
+      <c r="G58" s="90" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="84" t="inlineStr">
+      <c r="A59" s="88" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="B59" s="84" t="inlineStr">
+      <c r="B59" s="88" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2540,30 +2541,30 @@
           <t>Avvisi pubbliciLeggi e scarica l'avvisoScade il:02/04/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D59" s="85" t="inlineStr">
+      <c r="D59" s="89" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/proroga-termini-presentazione-candidature-po</t>
         </is>
       </c>
-      <c r="E59" s="84" t="inlineStr">
+      <c r="E59" s="88" t="inlineStr">
         <is>
           <t>02/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F59" s="84" t="inlineStr">
+      <c r="F59" s="88" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="G59" s="84" t="inlineStr"/>
+      <c r="G59" s="88" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="86" t="inlineStr">
+      <c r="A60" s="90" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="86" t="inlineStr">
+      <c r="B60" s="90" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2573,22 +2574,22 @@
           <t>INTERNAZIONALIZZAZIONESMAU – Italy RestartsUp in STOCCOLMAApertoFESR</t>
         </is>
       </c>
-      <c r="D60" s="87" t="inlineStr">
+      <c r="D60" s="91" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/smau-italy-restartsup-in-stoccolma/</t>
         </is>
       </c>
-      <c r="E60" s="86" t="inlineStr"/>
-      <c r="F60" s="86" t="inlineStr"/>
-      <c r="G60" s="86" t="inlineStr"/>
+      <c r="E60" s="90" t="inlineStr"/>
+      <c r="F60" s="90" t="inlineStr"/>
+      <c r="G60" s="90" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="84" t="inlineStr">
+      <c r="A61" s="88" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B61" s="84" t="inlineStr">
+      <c r="B61" s="88" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2598,22 +2599,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per Farnborough International AirshowApertoFESR</t>
         </is>
       </c>
-      <c r="D61" s="85" t="inlineStr">
+      <c r="D61" s="89" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-farnborough-international-airshow-2/</t>
         </is>
       </c>
-      <c r="E61" s="84" t="inlineStr"/>
-      <c r="F61" s="84" t="inlineStr"/>
-      <c r="G61" s="84" t="inlineStr"/>
+      <c r="E61" s="88" t="inlineStr"/>
+      <c r="F61" s="88" t="inlineStr"/>
+      <c r="G61" s="88" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="86" t="inlineStr">
+      <c r="A62" s="90" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="86" t="inlineStr">
+      <c r="B62" s="90" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2623,30 +2624,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA - alienazione lotto di terreno sito nel comune di Termini Imerese, via LibertàScade il:30/04/2026 - 12:00Leg</t>
         </is>
       </c>
-      <c r="D62" s="87" t="inlineStr">
+      <c r="D62" s="91" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proprieta-regionale-sito-nel-comune-termini-imerese-favore-ares-fabiola</t>
         </is>
       </c>
-      <c r="E62" s="86" t="inlineStr">
+      <c r="E62" s="90" t="inlineStr">
         <is>
           <t>30/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F62" s="86" t="inlineStr">
+      <c r="F62" s="90" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="G62" s="86" t="inlineStr"/>
+      <c r="G62" s="90" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="84" t="inlineStr">
+      <c r="A63" s="88" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B63" s="84" t="inlineStr">
+      <c r="B63" s="88" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2656,22 +2657,22 @@
           <t>Avviso per la concessione di contributi per progetti di contrasto all'abbandono sportivo giovanile (2026)</t>
         </is>
       </c>
-      <c r="D63" s="85" t="inlineStr">
+      <c r="D63" s="89" t="inlineStr">
         <is>
           <t>https://www.regione.emilia-romagna.it/sport/bandi/2026/contrasto-abbandono-2026</t>
         </is>
       </c>
-      <c r="E63" s="84" t="inlineStr"/>
-      <c r="F63" s="84" t="inlineStr"/>
-      <c r="G63" s="84" t="inlineStr"/>
+      <c r="E63" s="88" t="inlineStr"/>
+      <c r="F63" s="88" t="inlineStr"/>
+      <c r="G63" s="88" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="86" t="inlineStr">
+      <c r="A64" s="90" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="86" t="inlineStr">
+      <c r="B64" s="90" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2681,30 +2682,30 @@
           <t>Avvisi pubbliciAvviso si procede alla riassegnazione della posizione organizzativa a supporto delle attività del Servizio 2 “Investimenti in Agricoltu</t>
         </is>
       </c>
-      <c r="D64" s="87" t="inlineStr">
+      <c r="D64" s="91" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-selezione-interna-conferimento-1-posizione-organizzativa-ai-sensi-artt-19-20-ccrl-2022-2024-comparto-non-dirigenziale</t>
         </is>
       </c>
-      <c r="E64" s="86" t="inlineStr">
+      <c r="E64" s="90" t="inlineStr">
         <is>
           <t>09/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F64" s="86" t="inlineStr">
+      <c r="F64" s="90" t="inlineStr">
         <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="G64" s="86" t="inlineStr"/>
+      <c r="G64" s="90" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="84" t="inlineStr">
+      <c r="A65" s="88" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B65" s="84" t="inlineStr">
+      <c r="B65" s="88" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2714,30 +2715,30 @@
           <t>Avvisi pubbliciST-MESSINA - AVVISO di INDAGINE DI MERCATO per affidamento "Interventi manutenzione straordinaria della strada/pista forestale "Annunzi</t>
         </is>
       </c>
-      <c r="D65" s="85" t="inlineStr">
+      <c r="D65" s="89" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-indagine-mercato-affidamento-interventi-manutenzione-straordinaria-stradapista-forestale-annunziata-comune-messina</t>
         </is>
       </c>
-      <c r="E65" s="84" t="inlineStr">
+      <c r="E65" s="88" t="inlineStr">
         <is>
           <t>16/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F65" s="84" t="inlineStr">
+      <c r="F65" s="88" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="G65" s="84" t="inlineStr"/>
+      <c r="G65" s="88" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="86" t="inlineStr">
+      <c r="A66" s="90" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="86" t="inlineStr">
+      <c r="B66" s="90" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2747,30 +2748,30 @@
           <t>Avvisi pubbliciST-MESSINA - AVVISO DI INDAGINE DI MERCATO per affidamento "Interventi manutenzione straordinaria della strada/pista forestale "San Riz</t>
         </is>
       </c>
-      <c r="D66" s="87" t="inlineStr">
+      <c r="D66" s="91" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-indagine-mercato-affidamento-interventi-manutenzione-straordinaria-stradapista-forestale-san-rizzo-san-leone-crupi-madonuzza-comune-messina</t>
         </is>
       </c>
-      <c r="E66" s="86" t="inlineStr">
+      <c r="E66" s="90" t="inlineStr">
         <is>
           <t>16/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F66" s="86" t="inlineStr">
+      <c r="F66" s="90" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="G66" s="86" t="inlineStr"/>
+      <c r="G66" s="90" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="84" t="inlineStr">
+      <c r="A67" s="88" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="84" t="inlineStr">
+      <c r="B67" s="88" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2780,22 +2781,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Manifestazione di interesse per Casaidea 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D67" s="85" t="inlineStr">
+      <c r="D67" s="89" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-casaidea-2026/</t>
         </is>
       </c>
-      <c r="E67" s="84" t="inlineStr"/>
-      <c r="F67" s="84" t="inlineStr"/>
-      <c r="G67" s="84" t="inlineStr"/>
+      <c r="E67" s="88" t="inlineStr"/>
+      <c r="F67" s="88" t="inlineStr"/>
+      <c r="G67" s="88" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="86" t="inlineStr">
+      <c r="A68" s="90" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="86" t="inlineStr">
+      <c r="B68" s="90" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2805,22 +2806,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per il Salone Internazionale del Libro di Torino 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D68" s="87" t="inlineStr">
+      <c r="D68" s="91" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-il-salone-internazionale-del-libro-di-torino-2026/</t>
         </is>
       </c>
-      <c r="E68" s="86" t="inlineStr"/>
-      <c r="F68" s="86" t="inlineStr"/>
-      <c r="G68" s="86" t="inlineStr"/>
+      <c r="E68" s="90" t="inlineStr"/>
+      <c r="F68" s="90" t="inlineStr"/>
+      <c r="G68" s="90" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="84" t="inlineStr">
+      <c r="A69" s="88" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="84" t="inlineStr">
+      <c r="B69" s="88" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2830,30 +2831,30 @@
           <t>Avvisi pubbliciDDG 1112 del 02.04.2026 - Aggiornamento Avviso pubblico n. 4/2024 per l’attuazione del PAR GOL Sicilia da finanziare nell’ambito del Pi</t>
         </is>
       </c>
-      <c r="D69" s="85" t="inlineStr">
+      <c r="D69" s="89" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/ddg-1112-02042026-aggiornamento-avviso-pubblico-n-42024-l-attuazione-par-gol-sicilia-finanziare-nell-ambito-piano-nazionale-ripresa-resilienza-pnrr</t>
         </is>
       </c>
-      <c r="E69" s="84" t="inlineStr">
+      <c r="E69" s="88" t="inlineStr">
         <is>
           <t>05/04/2030 - 00:00</t>
         </is>
       </c>
-      <c r="F69" s="84" t="inlineStr">
+      <c r="F69" s="88" t="inlineStr">
         <is>
           <t>05/04/2030</t>
         </is>
       </c>
-      <c r="G69" s="84" t="inlineStr"/>
+      <c r="G69" s="88" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="86" t="inlineStr">
+      <c r="A70" s="90" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="86" t="inlineStr">
+      <c r="B70" s="90" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2863,30 +2864,30 @@
           <t>Avvisi pubbliciDDG 1113 del  02.04.2026 - Aggiornamento Avviso pubblico n. 2/2022 e s.m.i per l’attuazione del PAR GOL Sicilia da finanziare nell’ambi</t>
         </is>
       </c>
-      <c r="D70" s="87" t="inlineStr">
+      <c r="D70" s="91" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/ddg-1113-02042026-aggiornamento-avviso-pubblico-n-22022-smi-l-attuazione-par-gol-sicilia-finanziare-nell-ambito-piano-nazionale-ripresa-resilienza-pnrr</t>
         </is>
       </c>
-      <c r="E70" s="86" t="inlineStr">
+      <c r="E70" s="90" t="inlineStr">
         <is>
           <t>03/04/2030 - 00:00</t>
         </is>
       </c>
-      <c r="F70" s="86" t="inlineStr">
+      <c r="F70" s="90" t="inlineStr">
         <is>
           <t>03/04/2030</t>
         </is>
       </c>
-      <c r="G70" s="86" t="inlineStr"/>
+      <c r="G70" s="90" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="84" t="inlineStr">
+      <c r="A71" s="88" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B71" s="84" t="inlineStr">
+      <c r="B71" s="88" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2896,22 +2897,22 @@
           <t>Avvisi pubbliciLeggi e scarica l'avvisoScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D71" s="85" t="inlineStr">
+      <c r="D71" s="89" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/proroga-termini-presentazione-candidature-po</t>
         </is>
       </c>
-      <c r="E71" s="84" t="inlineStr"/>
-      <c r="F71" s="84" t="inlineStr"/>
-      <c r="G71" s="84" t="inlineStr"/>
+      <c r="E71" s="88" t="inlineStr"/>
+      <c r="F71" s="88" t="inlineStr"/>
+      <c r="G71" s="88" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="86" t="inlineStr">
+      <c r="A72" s="90" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="86" t="inlineStr">
+      <c r="B72" s="90" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2921,22 +2922,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEComunicare l’inclusione – contest per le istituzioni scolastiche regionaliApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D72" s="87" t="inlineStr">
+      <c r="D72" s="91" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/comunicare-linclusione-contest-per-le-istituzioni-scolastiche-regionali/</t>
         </is>
       </c>
-      <c r="E72" s="86" t="inlineStr"/>
-      <c r="F72" s="86" t="inlineStr"/>
-      <c r="G72" s="86" t="inlineStr"/>
+      <c r="E72" s="90" t="inlineStr"/>
+      <c r="F72" s="90" t="inlineStr"/>
+      <c r="G72" s="90" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="84" t="inlineStr">
+      <c r="A73" s="88" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B73" s="84" t="inlineStr">
+      <c r="B73" s="88" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2946,30 +2947,30 @@
           <t>Avvisi pubbliciAPPROVAZIONE AVVISO PUBBLICOScade il:03/04/2027 - 00:00Leggi di più</t>
         </is>
       </c>
-      <c r="D73" s="85" t="inlineStr">
+      <c r="D73" s="89" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/approvazione-avviso-pubblico</t>
         </is>
       </c>
-      <c r="E73" s="84" t="inlineStr">
+      <c r="E73" s="88" t="inlineStr">
         <is>
           <t>03/04/2027 - 00:00</t>
         </is>
       </c>
-      <c r="F73" s="84" t="inlineStr">
+      <c r="F73" s="88" t="inlineStr">
         <is>
           <t>03/04/2027</t>
         </is>
       </c>
-      <c r="G73" s="84" t="inlineStr"/>
+      <c r="G73" s="88" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="86" t="inlineStr">
+      <c r="A74" s="90" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="86" t="inlineStr">
+      <c r="B74" s="90" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2979,22 +2980,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Donne e Impresa 2026Prossima AperturaFESR</t>
         </is>
       </c>
-      <c r="D74" s="87" t="inlineStr">
+      <c r="D74" s="91" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/donne-e-impresa-2026/</t>
         </is>
       </c>
-      <c r="E74" s="86" t="inlineStr"/>
-      <c r="F74" s="86" t="inlineStr"/>
-      <c r="G74" s="86" t="inlineStr"/>
+      <c r="E74" s="90" t="inlineStr"/>
+      <c r="F74" s="90" t="inlineStr"/>
+      <c r="G74" s="90" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="84" t="inlineStr">
+      <c r="A75" s="88" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B75" s="84" t="inlineStr">
+      <c r="B75" s="88" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3004,30 +3005,30 @@
           <t>Bandi di garaCodice Intervento 111302_FELUCHE - Investimenti a bordo e nei porti per incrementare la qualità delle produzioni e migliorare le condizio</t>
         </is>
       </c>
-      <c r="D75" s="85" t="inlineStr">
+      <c r="D75" s="89" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/bandoavviso-regia-ob-11-azione-3-codice-111302feluche-investimenti-bordo-valorizzazione-feluche-miglioramento-condizioni-lavoro-salute-sicurezza-operatori-l</t>
         </is>
       </c>
-      <c r="E75" s="84" t="inlineStr">
+      <c r="E75" s="88" t="inlineStr">
         <is>
           <t>02/07/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F75" s="84" t="inlineStr">
+      <c r="F75" s="88" t="inlineStr">
         <is>
           <t>02/07/2026</t>
         </is>
       </c>
-      <c r="G75" s="84" t="inlineStr"/>
+      <c r="G75" s="88" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="86" t="inlineStr">
+      <c r="A76" s="90" t="inlineStr">
         <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="86" t="inlineStr">
+      <c r="B76" s="90" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -3037,22 +3038,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURASostegno agli investimenti nel settore vitivinicolo – campagna 2026/2027ApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D76" s="87" t="inlineStr">
+      <c r="D76" s="91" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/sostegno-agli-investimenti-nel-settore-vitivinicolo-campagna-2026-2027/</t>
         </is>
       </c>
-      <c r="E76" s="86" t="inlineStr"/>
-      <c r="F76" s="86" t="inlineStr"/>
-      <c r="G76" s="86" t="inlineStr"/>
+      <c r="E76" s="90" t="inlineStr"/>
+      <c r="F76" s="90" t="inlineStr"/>
+      <c r="G76" s="90" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="84" t="inlineStr">
+      <c r="A77" s="88" t="inlineStr">
         <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="84" t="inlineStr">
+      <c r="B77" s="88" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3062,30 +3063,30 @@
           <t>Manifestazioni di interesse9 aprile 2026 -ST PALERMO- Manifestazione di interesse - “Interventi di manutenzione straordinaria della strada-pista fores</t>
         </is>
       </c>
-      <c r="D77" s="85" t="inlineStr">
+      <c r="D77" s="89" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/9-aprile-2026-st-palermo-manifestazione-interesse-interventi-manutenzione-straordinaria-strada-pista-forestale-monte-cane-comune-caccamo-pa-distretto-forestale</t>
         </is>
       </c>
-      <c r="E77" s="84" t="inlineStr">
+      <c r="E77" s="88" t="inlineStr">
         <is>
           <t>24/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F77" s="84" t="inlineStr">
+      <c r="F77" s="88" t="inlineStr">
         <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="G77" s="84" t="inlineStr"/>
+      <c r="G77" s="88" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="86" t="inlineStr">
+      <c r="A78" s="90" t="inlineStr">
         <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="86" t="inlineStr">
+      <c r="B78" s="90" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3095,30 +3096,30 @@
           <t>Avvisi pubbliciST-MESSINA - AVVISO DI INDAGINE DI MERCATO per affidamento "Interventi manutenzione straordinaria della strada/pista forestale "Faggita</t>
         </is>
       </c>
-      <c r="D78" s="87" t="inlineStr">
+      <c r="D78" s="91" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-indagine-mercato-affidamento-interventi-manutenzione-straordinaria-stradapista-forestale-faggita-comune-tripi-me</t>
         </is>
       </c>
-      <c r="E78" s="86" t="inlineStr">
+      <c r="E78" s="90" t="inlineStr">
         <is>
           <t>23/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F78" s="86" t="inlineStr">
+      <c r="F78" s="90" t="inlineStr">
         <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="G78" s="86" t="inlineStr"/>
+      <c r="G78" s="90" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="84" t="inlineStr">
+      <c r="A79" s="88" t="inlineStr">
         <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B79" s="84" t="inlineStr">
+      <c r="B79" s="88" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3128,30 +3129,30 @@
           <t>Avvisi pubbliciST-MESSINA - AVVISO DI INDAGINE DI MERCATO per affidamento "Interventi manutenzione straordinaria della strada/pista forestale "Ferraro</t>
         </is>
       </c>
-      <c r="D79" s="85" t="inlineStr">
+      <c r="D79" s="89" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-indagine-mercato-affidamento-interventi-manutenzione-straordinaria-stradapista-forestale-ferraro-sanrizzo-badiazza-comune-messina</t>
         </is>
       </c>
-      <c r="E79" s="84" t="inlineStr">
+      <c r="E79" s="88" t="inlineStr">
         <is>
           <t>23/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F79" s="84" t="inlineStr">
+      <c r="F79" s="88" t="inlineStr">
         <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="G79" s="84" t="inlineStr"/>
+      <c r="G79" s="88" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="86" t="inlineStr">
+      <c r="A80" s="90" t="inlineStr">
         <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="86" t="inlineStr">
+      <c r="B80" s="90" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -3161,22 +3162,22 @@
           <t>Comunicazione e informazioneAcquisizione di servizi di comunicazione e informazione – PR Lazio FESR, PR Lazio FSE+ e comunicazione unitariaApertoBandi</t>
         </is>
       </c>
-      <c r="D80" s="87" t="inlineStr">
+      <c r="D80" s="91" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/acquisizione-di-servizi-di-comunicazione-e-informazione-pr-lazio-fesr-pr-lazio-fse-e-comunicazione-unitaria/</t>
         </is>
       </c>
-      <c r="E80" s="86" t="inlineStr"/>
-      <c r="F80" s="86" t="inlineStr"/>
-      <c r="G80" s="86" t="inlineStr"/>
+      <c r="E80" s="90" t="inlineStr"/>
+      <c r="F80" s="90" t="inlineStr"/>
+      <c r="G80" s="90" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="84" t="inlineStr">
+      <c r="A81" s="88" t="inlineStr">
         <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B81" s="84" t="inlineStr">
+      <c r="B81" s="88" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3186,22 +3187,22 @@
           <t>Avvisi pubbliciAvviso pubblico di selezione interna, per titoli, per il conferimento, ai sensi degli artt. 21 del CCRL 2022-2024 del comparto non diri</t>
         </is>
       </c>
-      <c r="D81" s="85" t="inlineStr">
+      <c r="D81" s="89" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-selezione-interna-titoli-conferimento-ai-sensi-artt-21-ccrl-2022-2024-comparto-non-dirigenziale-una-posizione-organizzativa-dipartimento</t>
         </is>
       </c>
-      <c r="E81" s="84" t="inlineStr">
+      <c r="E81" s="88" t="inlineStr">
         <is>
           <t>16/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F81" s="84" t="inlineStr">
+      <c r="F81" s="88" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="G81" s="84" t="inlineStr"/>
+      <c r="G81" s="88" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="90" t="inlineStr">
@@ -3235,6 +3236,31 @@
         </is>
       </c>
       <c r="G82" s="90" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="92" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="92" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>LAVORO, FORMAZIONE E INCLUSIONEVoucher per lo Sport – individuazione dei destinatari (II edizione)ApertoFSE / FSE+</t>
+        </is>
+      </c>
+      <c r="D83" s="93" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/voucher-per-lo-sport-individuazione-dei-destinatari-ii-edizione/</t>
+        </is>
+      </c>
+      <c r="E83" s="92" t="inlineStr"/>
+      <c r="F83" s="92" t="inlineStr"/>
+      <c r="G83" s="92" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -3319,6 +3345,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D83" r:id="rId82"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3363,7 +3390,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="88" t="inlineStr">
+      <c r="A3" s="92" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -3376,20 +3403,20 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="90" t="inlineStr">
+      <c r="A4" s="94" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="88" t="inlineStr">
+      <c r="A5" s="92" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3398,7 +3425,7 @@
         <v>44</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">

--- a/data/bandi_export.xlsx
+++ b/data/bandi_export.xlsx
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -396,6 +396,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -763,7 +775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -778,7 +790,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏛️  Nuovi Bandi — 15/04/2026 08:24</t>
+          <t>🏛️  Nuovi Bandi — 16/04/2026 08:24</t>
         </is>
       </c>
     </row>
@@ -823,24 +835,163 @@
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="92" t="inlineStr">
+      <c r="B3" s="95" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>LAVORO, FORMAZIONE E INCLUSIONEVoucher per lo Sport – individuazione dei destinatari (II edizione)ApertoFSE / FSE+</t>
-        </is>
-      </c>
-      <c r="D3" s="93" t="inlineStr">
-        <is>
-          <t>https://www.lazioeuropa.it/bandi/voucher-per-lo-sport-individuazione-dei-destinatari-ii-edizione/</t>
-        </is>
-      </c>
-      <c r="E3" s="92" t="inlineStr"/>
-      <c r="F3" s="92" t="inlineStr"/>
+          <t>CooperazioneManifestazione di interesse per partecipare a Codeway Expo 2026ApertoAltri fondiFESR</t>
+        </is>
+      </c>
+      <c r="D3" s="96" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-partecipare-a-codeway-expo-2026/</t>
+        </is>
+      </c>
+      <c r="E3" s="95" t="inlineStr"/>
+      <c r="F3" s="95" t="inlineStr"/>
       <c r="G3" s="5" t="inlineStr"/>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="97" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Street art 2026ApertoBandi Regionali</t>
+        </is>
+      </c>
+      <c r="D4" s="98" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/lazio-street-art-2026/</t>
+        </is>
+      </c>
+      <c r="E4" s="97" t="inlineStr"/>
+      <c r="F4" s="97" t="inlineStr"/>
+      <c r="G4" s="9" t="inlineStr"/>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="95" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>LAVORO, FORMAZIONE E INCLUSIONEBuoni servizio per le persone non autosufficienti nel territorio del LazioApertoFSE / FSE+</t>
+        </is>
+      </c>
+      <c r="D5" s="96" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/buoni-servizio-per-le-persone-non-autosufficienti-nel-territorio-del-lazio/</t>
+        </is>
+      </c>
+      <c r="E5" s="95" t="inlineStr"/>
+      <c r="F5" s="95" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="97" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Avvisi pubbliciSERVIZIO 14 SERVIZIO PER IL TERRITORIO DI PALERMO AVVISO PUBBLICO PER LA CONCESSIONE AL PASCOLO NEI TERRENI DEL DEMANIO FORESTALE REGIO</t>
+        </is>
+      </c>
+      <c r="D6" s="98" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-14-servizio-territorio-palermo-avviso-pubblico-concessione-al-pascolo-nei-terreni-demanio-forestale-regionale-gestiti-dipartimento-sviluppo-rurale</t>
+        </is>
+      </c>
+      <c r="E6" s="97" t="inlineStr">
+        <is>
+          <t>05/05/2026 - 12:00</t>
+        </is>
+      </c>
+      <c r="F6" s="97" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr"/>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="95" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Avvisi pubbliciAtto di interpello rivolto al personale del Comparto non dirigenziale per la designazione del  Consegnatario e del Vice Consegnatario d</t>
+        </is>
+      </c>
+      <c r="D7" s="96" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/atto-intepello-dipartimento-turismo-sport-spettacolo</t>
+        </is>
+      </c>
+      <c r="E7" s="95" t="inlineStr">
+        <is>
+          <t>30/04/2026 - 23:59</t>
+        </is>
+      </c>
+      <c r="F7" s="95" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="97" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Avvisi pubbliciAVVISO DI INDAGINE DI MERCATO - per la partecipazione alla successiva procedura negoziata a norma dell'art. 50, comma 1, lettera c) del</t>
+        </is>
+      </c>
+      <c r="D8" s="98" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-pa-avviso-indagine-mercato-partecipazione-alla-successiva-procedura-negoziata-norma-art-50-comma-1-lettera-c-dlgs-31-marzo-2023-n-36-ssmmii-finalizzata-all</t>
+        </is>
+      </c>
+      <c r="E8" s="97" t="inlineStr">
+        <is>
+          <t>02/05/2026 - 12:00</t>
+        </is>
+      </c>
+      <c r="F8" s="97" t="inlineStr">
+        <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -848,6 +999,11 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -859,7 +1015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -909,12 +1065,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="90" t="inlineStr">
+      <c r="A2" s="94" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B2" s="90" t="inlineStr">
+      <c r="B2" s="94" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -929,17 +1085,17 @@
           <t>https://agricoltura.regione.emilia-romagna.it/feampa-2021-2027/bandi-galpa/2026/galpa-sostituzione-motori-secondo-bando</t>
         </is>
       </c>
-      <c r="E2" s="90" t="inlineStr"/>
-      <c r="F2" s="90" t="inlineStr"/>
-      <c r="G2" s="90" t="inlineStr"/>
+      <c r="E2" s="94" t="inlineStr"/>
+      <c r="F2" s="94" t="inlineStr"/>
+      <c r="G2" s="94" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="88" t="inlineStr">
+      <c r="A3" s="92" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B3" s="88" t="inlineStr">
+      <c r="B3" s="92" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -949,22 +1105,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0PRE-SEED 3.0Prossima AperturaFESR</t>
         </is>
       </c>
-      <c r="D3" s="89" t="inlineStr">
+      <c r="D3" s="93" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/pre-seed-3-0/</t>
         </is>
       </c>
-      <c r="E3" s="88" t="inlineStr"/>
-      <c r="F3" s="88" t="inlineStr"/>
-      <c r="G3" s="88" t="inlineStr"/>
+      <c r="E3" s="92" t="inlineStr"/>
+      <c r="F3" s="92" t="inlineStr"/>
+      <c r="G3" s="92" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="90" t="inlineStr">
+      <c r="A4" s="94" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B4" s="90" t="inlineStr">
+      <c r="B4" s="94" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -979,17 +1135,17 @@
           <t>https://www.lazioeuropa.it/bandi/contributo-su-finanziamenti-alle-imprese-del-lazio-erogati-su-provvista-bei/</t>
         </is>
       </c>
-      <c r="E4" s="90" t="inlineStr"/>
-      <c r="F4" s="90" t="inlineStr"/>
-      <c r="G4" s="90" t="inlineStr"/>
+      <c r="E4" s="94" t="inlineStr"/>
+      <c r="F4" s="94" t="inlineStr"/>
+      <c r="G4" s="94" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="88" t="inlineStr">
+      <c r="A5" s="92" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B5" s="88" t="inlineStr">
+      <c r="B5" s="92" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -999,22 +1155,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEIndividuazione degli enti iscritti al Registro unico nazionale del Terzo settoreApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D5" s="89" t="inlineStr">
+      <c r="D5" s="93" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/individuazione-degli-enti-iscritti-al-registro-unico-nazionale-del-terzo-settore/</t>
         </is>
       </c>
-      <c r="E5" s="88" t="inlineStr"/>
-      <c r="F5" s="88" t="inlineStr"/>
-      <c r="G5" s="88" t="inlineStr"/>
+      <c r="E5" s="92" t="inlineStr"/>
+      <c r="F5" s="92" t="inlineStr"/>
+      <c r="G5" s="92" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="90" t="inlineStr">
+      <c r="A6" s="94" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B6" s="90" t="inlineStr">
+      <c r="B6" s="94" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1029,17 +1185,17 @@
           <t>https://www.lazioeuropa.it/bandi/technology-transfer-lazio/</t>
         </is>
       </c>
-      <c r="E6" s="90" t="inlineStr"/>
-      <c r="F6" s="90" t="inlineStr"/>
-      <c r="G6" s="90" t="inlineStr"/>
+      <c r="E6" s="94" t="inlineStr"/>
+      <c r="F6" s="94" t="inlineStr"/>
+      <c r="G6" s="94" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="88" t="inlineStr">
+      <c r="A7" s="92" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B7" s="88" t="inlineStr">
+      <c r="B7" s="92" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1049,22 +1205,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Percorso di tutoraggio per le impreseApertoFESR</t>
         </is>
       </c>
-      <c r="D7" s="89" t="inlineStr">
+      <c r="D7" s="93" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/percorso-di-tutoraggio-per-le-imprese/</t>
         </is>
       </c>
-      <c r="E7" s="88" t="inlineStr"/>
-      <c r="F7" s="88" t="inlineStr"/>
-      <c r="G7" s="88" t="inlineStr"/>
+      <c r="E7" s="92" t="inlineStr"/>
+      <c r="F7" s="92" t="inlineStr"/>
+      <c r="G7" s="92" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="90" t="inlineStr">
+      <c r="A8" s="94" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B8" s="90" t="inlineStr">
+      <c r="B8" s="94" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1079,17 +1235,17 @@
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-partecipare-a-smau-parigi-2026/</t>
         </is>
       </c>
-      <c r="E8" s="90" t="inlineStr"/>
-      <c r="F8" s="90" t="inlineStr"/>
-      <c r="G8" s="90" t="inlineStr"/>
+      <c r="E8" s="94" t="inlineStr"/>
+      <c r="F8" s="94" t="inlineStr"/>
+      <c r="G8" s="94" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="88" t="inlineStr">
+      <c r="A9" s="92" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B9" s="88" t="inlineStr">
+      <c r="B9" s="92" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1099,22 +1255,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONERiconoscimento della funzione sociale ed educativa degli oratoriApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D9" s="89" t="inlineStr">
+      <c r="D9" s="93" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/riconoscimento-della-funzione-sociale-ed-educativa-degli-oratori/</t>
         </is>
       </c>
-      <c r="E9" s="88" t="inlineStr"/>
-      <c r="F9" s="88" t="inlineStr"/>
-      <c r="G9" s="88" t="inlineStr"/>
+      <c r="E9" s="92" t="inlineStr"/>
+      <c r="F9" s="92" t="inlineStr"/>
+      <c r="G9" s="92" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="90" t="inlineStr">
+      <c r="A10" s="94" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B10" s="90" t="inlineStr">
+      <c r="B10" s="94" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1129,17 +1285,17 @@
           <t>https://www.lazioeuropa.it/bandi/iscrizione-nellelenco-regionale-degli-idonei-allesercizio-dellattivita-di-direttore-dellistituto-jemolo/</t>
         </is>
       </c>
-      <c r="E10" s="90" t="inlineStr"/>
-      <c r="F10" s="90" t="inlineStr"/>
-      <c r="G10" s="90" t="inlineStr"/>
+      <c r="E10" s="94" t="inlineStr"/>
+      <c r="F10" s="94" t="inlineStr"/>
+      <c r="G10" s="94" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="88" t="inlineStr">
+      <c r="A11" s="92" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B11" s="88" t="inlineStr">
+      <c r="B11" s="92" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1149,22 +1305,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEVoucher per lo sport – seconda annualitàApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D11" s="89" t="inlineStr">
+      <c r="D11" s="93" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/voucher-per-lo-sport-seconda-annualita/</t>
         </is>
       </c>
-      <c r="E11" s="88" t="inlineStr"/>
-      <c r="F11" s="88" t="inlineStr"/>
-      <c r="G11" s="88" t="inlineStr"/>
+      <c r="E11" s="92" t="inlineStr"/>
+      <c r="F11" s="92" t="inlineStr"/>
+      <c r="G11" s="92" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="90" t="inlineStr">
+      <c r="A12" s="94" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B12" s="90" t="inlineStr">
+      <c r="B12" s="94" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1179,17 +1335,17 @@
           <t>https://www.lazioeuropa.it/bandi/bonus-occupazionale-salgo/</t>
         </is>
       </c>
-      <c r="E12" s="90" t="inlineStr"/>
-      <c r="F12" s="90" t="inlineStr"/>
-      <c r="G12" s="90" t="inlineStr"/>
+      <c r="E12" s="94" t="inlineStr"/>
+      <c r="F12" s="94" t="inlineStr"/>
+      <c r="G12" s="94" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="88" t="inlineStr">
+      <c r="A13" s="92" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B13" s="88" t="inlineStr">
+      <c r="B13" s="92" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1199,22 +1355,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEContributo di Libertà per le donne che hanno subito violenzaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D13" s="89" t="inlineStr">
+      <c r="D13" s="93" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-di-liberta-per-le-donne-che-hanno-subito-violenza/</t>
         </is>
       </c>
-      <c r="E13" s="88" t="inlineStr"/>
-      <c r="F13" s="88" t="inlineStr"/>
-      <c r="G13" s="88" t="inlineStr"/>
+      <c r="E13" s="92" t="inlineStr"/>
+      <c r="F13" s="92" t="inlineStr"/>
+      <c r="G13" s="92" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="90" t="inlineStr">
+      <c r="A14" s="94" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B14" s="90" t="inlineStr">
+      <c r="B14" s="94" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1229,17 +1385,17 @@
           <t>https://www.lazioeuropa.it/bandi/interventi-straordinari-di-valorizzazione-del-patrimonio-culturale-del-lazio/</t>
         </is>
       </c>
-      <c r="E14" s="90" t="inlineStr"/>
-      <c r="F14" s="90" t="inlineStr"/>
-      <c r="G14" s="90" t="inlineStr"/>
+      <c r="E14" s="94" t="inlineStr"/>
+      <c r="F14" s="94" t="inlineStr"/>
+      <c r="G14" s="94" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="88" t="inlineStr">
+      <c r="A15" s="92" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B15" s="88" t="inlineStr">
+      <c r="B15" s="92" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1249,30 +1405,30 @@
           <t>Bandi di garaBANDO ATTUAZIONE Ob. 1.1 Azione 1 codice 111102 _DIV - "SOSTEGNO ALLA DIVERSIFICAZIONE E NUOVE FORME DI REDDITO PER LA PICCOLA PESCA COST</t>
         </is>
       </c>
-      <c r="D15" s="89" t="inlineStr">
+      <c r="D15" s="93" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/bando-avviso-regia-ob-11-azione-1-codice-111102-div-sostegno-alla-diversificazione-nuove-forme-reddito-piccola-pesca-costiera</t>
         </is>
       </c>
-      <c r="E15" s="88" t="inlineStr">
+      <c r="E15" s="92" t="inlineStr">
         <is>
           <t>07/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F15" s="88" t="inlineStr">
+      <c r="F15" s="92" t="inlineStr">
         <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="G15" s="88" t="inlineStr"/>
+      <c r="G15" s="92" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="90" t="inlineStr">
+      <c r="A16" s="94" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B16" s="90" t="inlineStr">
+      <c r="B16" s="94" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1287,25 +1443,25 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/09-marzo-2026-st-siracusa-avviso-pubblico-costituzione-elenchi-operatori-economici-l-acquisizione-beni-servizi</t>
         </is>
       </c>
-      <c r="E16" s="90" t="inlineStr">
+      <c r="E16" s="94" t="inlineStr">
         <is>
           <t>31/12/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F16" s="90" t="inlineStr">
+      <c r="F16" s="94" t="inlineStr">
         <is>
           <t>31/12/2026</t>
         </is>
       </c>
-      <c r="G16" s="90" t="inlineStr"/>
+      <c r="G16" s="94" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="88" t="inlineStr">
+      <c r="A17" s="92" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B17" s="88" t="inlineStr">
+      <c r="B17" s="92" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1315,30 +1471,30 @@
           <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScade il:19/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D17" s="89" t="inlineStr">
+      <c r="D17" s="93" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
         </is>
       </c>
-      <c r="E17" s="88" t="inlineStr">
+      <c r="E17" s="92" t="inlineStr">
         <is>
           <t>19/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F17" s="88" t="inlineStr">
+      <c r="F17" s="92" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G17" s="88" t="inlineStr"/>
+      <c r="G17" s="92" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="90" t="inlineStr">
+      <c r="A18" s="94" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B18" s="90" t="inlineStr">
+      <c r="B18" s="94" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1353,17 +1509,17 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-distributori-automatici-bevande-snack</t>
         </is>
       </c>
-      <c r="E18" s="90" t="inlineStr"/>
-      <c r="F18" s="90" t="inlineStr"/>
-      <c r="G18" s="90" t="inlineStr"/>
+      <c r="E18" s="94" t="inlineStr"/>
+      <c r="F18" s="94" t="inlineStr"/>
+      <c r="G18" s="94" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="88" t="inlineStr">
+      <c r="A19" s="92" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B19" s="88" t="inlineStr">
+      <c r="B19" s="92" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1373,30 +1529,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D19" s="89" t="inlineStr">
+      <c r="D19" s="93" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo</t>
         </is>
       </c>
-      <c r="E19" s="88" t="inlineStr">
+      <c r="E19" s="92" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F19" s="88" t="inlineStr">
+      <c r="F19" s="92" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G19" s="88" t="inlineStr"/>
+      <c r="G19" s="92" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="90" t="inlineStr">
+      <c r="A20" s="94" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B20" s="90" t="inlineStr">
+      <c r="B20" s="94" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1411,25 +1567,25 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo-0</t>
         </is>
       </c>
-      <c r="E20" s="90" t="inlineStr">
+      <c r="E20" s="94" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F20" s="90" t="inlineStr">
+      <c r="F20" s="94" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G20" s="90" t="inlineStr"/>
+      <c r="G20" s="94" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="88" t="inlineStr">
+      <c r="A21" s="92" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B21" s="88" t="inlineStr">
+      <c r="B21" s="92" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1439,22 +1595,22 @@
           <t>Manifestazioni di interesseST SIRACUSA - AVVISO DI MANIFESTAZIONE DI INTERESSE - Fornitura applicativo extracontabile per la gestione progetti, ecc. e</t>
         </is>
       </c>
-      <c r="D21" s="89" t="inlineStr">
+      <c r="D21" s="93" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-siracusa-avviso-manifestazione-interesse-fornitura-applicativo-extracontabile-gestione-progetti-ecc-applicativo-gestione-ed-elaborazione-informatizzata-paghe</t>
         </is>
       </c>
-      <c r="E21" s="88" t="inlineStr"/>
-      <c r="F21" s="88" t="inlineStr"/>
-      <c r="G21" s="88" t="inlineStr"/>
+      <c r="E21" s="92" t="inlineStr"/>
+      <c r="F21" s="92" t="inlineStr"/>
+      <c r="G21" s="92" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="90" t="inlineStr">
+      <c r="A22" s="94" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B22" s="90" t="inlineStr">
+      <c r="B22" s="94" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1469,25 +1625,25 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-sito-nel-comune-capo-d-orlando-trazzera-marina</t>
         </is>
       </c>
-      <c r="E22" s="90" t="inlineStr">
+      <c r="E22" s="94" t="inlineStr">
         <is>
           <t>25/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F22" s="90" t="inlineStr">
+      <c r="F22" s="94" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="G22" s="90" t="inlineStr"/>
+      <c r="G22" s="94" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="88" t="inlineStr">
+      <c r="A23" s="92" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B23" s="88" t="inlineStr">
+      <c r="B23" s="92" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1497,22 +1653,22 @@
           <t xml:space="preserve">Avvisi pubbliciST CATANIA - Programma Regionale FESR Sicilia 2021-2027 - Azione 2.4.4 - “Interventi per la riduzione del rischio incendi” - AVVISO DI </t>
         </is>
       </c>
-      <c r="D23" s="89" t="inlineStr">
+      <c r="D23" s="93" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-catania-programma-regionale-fesr-sicilia-2021-2027-azione-244-interventi-riduzione-rischio-incendi-avviso-indagine-mercato</t>
         </is>
       </c>
-      <c r="E23" s="88" t="inlineStr"/>
-      <c r="F23" s="88" t="inlineStr"/>
-      <c r="G23" s="88" t="inlineStr"/>
+      <c r="E23" s="92" t="inlineStr"/>
+      <c r="F23" s="92" t="inlineStr"/>
+      <c r="G23" s="92" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="90" t="inlineStr">
+      <c r="A24" s="94" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B24" s="90" t="inlineStr">
+      <c r="B24" s="94" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1527,17 +1683,17 @@
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-romics-primavera-2026/</t>
         </is>
       </c>
-      <c r="E24" s="90" t="inlineStr"/>
-      <c r="F24" s="90" t="inlineStr"/>
-      <c r="G24" s="90" t="inlineStr"/>
+      <c r="E24" s="94" t="inlineStr"/>
+      <c r="F24" s="94" t="inlineStr"/>
+      <c r="G24" s="94" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="88" t="inlineStr">
+      <c r="A25" s="92" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B25" s="88" t="inlineStr">
+      <c r="B25" s="92" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1547,22 +1703,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Cinema International 2026 – I edizioneApertoFESR</t>
         </is>
       </c>
-      <c r="D25" s="89" t="inlineStr">
+      <c r="D25" s="93" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lazio-cinema-international-2026-i-edizione/</t>
         </is>
       </c>
-      <c r="E25" s="88" t="inlineStr"/>
-      <c r="F25" s="88" t="inlineStr"/>
-      <c r="G25" s="88" t="inlineStr"/>
+      <c r="E25" s="92" t="inlineStr"/>
+      <c r="F25" s="92" t="inlineStr"/>
+      <c r="G25" s="92" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="90" t="inlineStr">
+      <c r="A26" s="94" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B26" s="90" t="inlineStr">
+      <c r="B26" s="94" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1577,17 +1733,17 @@
           <t>https://www.lazioeuropa.it/bandi/manifestazioni-di-interesse-alla-costituzione-di-due-nuove-fondazioni-i-t-s-academy/</t>
         </is>
       </c>
-      <c r="E26" s="90" t="inlineStr"/>
-      <c r="F26" s="90" t="inlineStr"/>
-      <c r="G26" s="90" t="inlineStr"/>
+      <c r="E26" s="94" t="inlineStr"/>
+      <c r="F26" s="94" t="inlineStr"/>
+      <c r="G26" s="94" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="88" t="inlineStr">
+      <c r="A27" s="92" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B27" s="88" t="inlineStr">
+      <c r="B27" s="92" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1597,22 +1753,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURAContributi per sostenere la ripresa del settore della pescaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D27" s="89" t="inlineStr">
+      <c r="D27" s="93" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributi-per-sostenere-la-ripresa-del-settore-della-pesca/</t>
         </is>
       </c>
-      <c r="E27" s="88" t="inlineStr"/>
-      <c r="F27" s="88" t="inlineStr"/>
-      <c r="G27" s="88" t="inlineStr"/>
+      <c r="E27" s="92" t="inlineStr"/>
+      <c r="F27" s="92" t="inlineStr"/>
+      <c r="G27" s="92" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="90" t="inlineStr">
+      <c r="A28" s="94" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B28" s="90" t="inlineStr">
+      <c r="B28" s="94" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1627,25 +1783,25 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-storytelling-aziendale-expo-wild-natura-caccia-pesca-misterbianco-ct-10-12-aprile-2026</t>
         </is>
       </c>
-      <c r="E28" s="90" t="inlineStr">
+      <c r="E28" s="94" t="inlineStr">
         <is>
           <t>30/03/2026 - 13:00</t>
         </is>
       </c>
-      <c r="F28" s="90" t="inlineStr">
+      <c r="F28" s="94" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G28" s="90" t="inlineStr"/>
+      <c r="G28" s="94" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="88" t="inlineStr">
+      <c r="A29" s="92" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B29" s="88" t="inlineStr">
+      <c r="B29" s="92" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1655,30 +1811,30 @@
           <t>Manifestazioni di interesseInvaso Lentini - Interventi di ripristino delle pareti esterne in cls della Torre di presa Sud e della trave d’appoggio del</t>
         </is>
       </c>
-      <c r="D29" s="89" t="inlineStr">
+      <c r="D29" s="93" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/invaso-lentini-interventi-ripristino-pareti-esterne-cls-torre-presa-sud-trave-d-appoggio-cavalcavia-collegamento-alla-stessa-torre</t>
         </is>
       </c>
-      <c r="E29" s="88" t="inlineStr">
+      <c r="E29" s="92" t="inlineStr">
         <is>
           <t>19/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F29" s="88" t="inlineStr">
+      <c r="F29" s="92" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G29" s="88" t="inlineStr"/>
+      <c r="G29" s="92" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="90" t="inlineStr">
+      <c r="A30" s="94" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="B30" s="90" t="inlineStr">
+      <c r="B30" s="94" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1693,17 +1849,17 @@
           <t>https://www.lazioeuropa.it/bandi/ristrutturazione-e-riconversione-vigneti-campagna-2026-2027/</t>
         </is>
       </c>
-      <c r="E30" s="90" t="inlineStr"/>
-      <c r="F30" s="90" t="inlineStr"/>
-      <c r="G30" s="90" t="inlineStr"/>
+      <c r="E30" s="94" t="inlineStr"/>
+      <c r="F30" s="94" t="inlineStr"/>
+      <c r="G30" s="94" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="88" t="inlineStr">
+      <c r="A31" s="92" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="B31" s="88" t="inlineStr">
+      <c r="B31" s="92" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1713,30 +1869,30 @@
           <t>Manifestazioni di interessePR FESR 2021/27 Azione 1.3.3 e del POC 2014/20 - Azione 1.3.1  - Avviso a manifestazione d’interesse eventi fieristici inte</t>
         </is>
       </c>
-      <c r="D31" s="89" t="inlineStr">
+      <c r="D31" s="93" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-d-interesse-eventi-fieristici-internazionali-marzo-dicembre-2026</t>
         </is>
       </c>
-      <c r="E31" s="88" t="inlineStr">
+      <c r="E31" s="92" t="inlineStr">
         <is>
           <t>30/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F31" s="88" t="inlineStr">
+      <c r="F31" s="92" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="G31" s="88" t="inlineStr"/>
+      <c r="G31" s="92" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="90" t="inlineStr">
+      <c r="A32" s="94" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="B32" s="90" t="inlineStr">
+      <c r="B32" s="94" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1751,17 +1907,17 @@
           <t>https://www.lazioeuropa.it/bandi/lecosistema-dellinnovazione-a-innovit-focus-s3/</t>
         </is>
       </c>
-      <c r="E32" s="90" t="inlineStr"/>
-      <c r="F32" s="90" t="inlineStr"/>
-      <c r="G32" s="90" t="inlineStr"/>
+      <c r="E32" s="94" t="inlineStr"/>
+      <c r="F32" s="94" t="inlineStr"/>
+      <c r="G32" s="94" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="88" t="inlineStr">
+      <c r="A33" s="92" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="B33" s="88" t="inlineStr">
+      <c r="B33" s="92" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1771,22 +1927,22 @@
           <t>Manifestazioni di interessePR FESR SICILIA 2021/27 - NUOVO Avviso a manifestazione d’interesse per esperti valutatoriScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D33" s="89" t="inlineStr">
+      <c r="D33" s="93" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/pr-fesr-sicilia-202127-nuovo-avviso-manifestazione-d-interesse-esperti-valutatori</t>
         </is>
       </c>
-      <c r="E33" s="88" t="inlineStr"/>
-      <c r="F33" s="88" t="inlineStr"/>
-      <c r="G33" s="88" t="inlineStr"/>
+      <c r="E33" s="92" t="inlineStr"/>
+      <c r="F33" s="92" t="inlineStr"/>
+      <c r="G33" s="92" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="90" t="inlineStr">
+      <c r="A34" s="94" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="B34" s="90" t="inlineStr">
+      <c r="B34" s="94" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -1801,17 +1957,17 @@
           <t>https://ambiente.regione.emilia-romagna.it/it/parchi-natura2000/bandi/bando-2026-per-contributi-dedicati-alla-manutenzione-della-rete-dei-percorsi-escursionistici</t>
         </is>
       </c>
-      <c r="E34" s="90" t="inlineStr"/>
-      <c r="F34" s="90" t="inlineStr"/>
-      <c r="G34" s="90" t="inlineStr"/>
+      <c r="E34" s="94" t="inlineStr"/>
+      <c r="F34" s="94" t="inlineStr"/>
+      <c r="G34" s="94" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="88" t="inlineStr">
+      <c r="A35" s="92" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="B35" s="88" t="inlineStr">
+      <c r="B35" s="92" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1821,22 +1977,22 @@
           <t>Programma regionale in favore delle tradizioni storiche, artistiche, religiose e popolari (2026) – manifestazioni d’interesseApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D35" s="89" t="inlineStr">
+      <c r="D35" s="93" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/programma-regionale-in-favore-delle-tradizioni-storiche-artistiche-religiose-e-popolari-2026-manifestazioni-dinteresse/</t>
         </is>
       </c>
-      <c r="E35" s="88" t="inlineStr"/>
-      <c r="F35" s="88" t="inlineStr"/>
-      <c r="G35" s="88" t="inlineStr"/>
+      <c r="E35" s="92" t="inlineStr"/>
+      <c r="F35" s="92" t="inlineStr"/>
+      <c r="G35" s="92" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="90" t="inlineStr">
+      <c r="A36" s="94" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B36" s="90" t="inlineStr">
+      <c r="B36" s="94" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1851,17 +2007,17 @@
           <t>https://www.lazioeuropa.it/bandi/buoni-servizio-per-le-persone-non-autosufficienti-nel-territorio-del-lazio/</t>
         </is>
       </c>
-      <c r="E36" s="90" t="inlineStr"/>
-      <c r="F36" s="90" t="inlineStr"/>
-      <c r="G36" s="90" t="inlineStr"/>
+      <c r="E36" s="94" t="inlineStr"/>
+      <c r="F36" s="94" t="inlineStr"/>
+      <c r="G36" s="94" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="88" t="inlineStr">
+      <c r="A37" s="92" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B37" s="88" t="inlineStr">
+      <c r="B37" s="92" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1871,22 +2027,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONERimborso delle rette dei servizi educativi nel territorio del LazioProssima AperturaFSE / FSE+</t>
         </is>
       </c>
-      <c r="D37" s="89" t="inlineStr">
+      <c r="D37" s="93" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/rimborso-delle-rette-dei-servizi-educativi-nel-territorio-del-lazio/</t>
         </is>
       </c>
-      <c r="E37" s="88" t="inlineStr"/>
-      <c r="F37" s="88" t="inlineStr"/>
-      <c r="G37" s="88" t="inlineStr"/>
+      <c r="E37" s="92" t="inlineStr"/>
+      <c r="F37" s="92" t="inlineStr"/>
+      <c r="G37" s="92" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="90" t="inlineStr">
+      <c r="A38" s="94" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B38" s="90" t="inlineStr">
+      <c r="B38" s="94" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1901,25 +2057,25 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/atto-interpello-l-affidamento-incarico-collaudo-statico-strutture-diga-pietrarossa-progetto-ex-casmez-303219</t>
         </is>
       </c>
-      <c r="E38" s="90" t="inlineStr">
+      <c r="E38" s="94" t="inlineStr">
         <is>
           <t>27/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F38" s="90" t="inlineStr">
+      <c r="F38" s="94" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="G38" s="90" t="inlineStr"/>
+      <c r="G38" s="94" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="88" t="inlineStr">
+      <c r="A39" s="92" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B39" s="88" t="inlineStr">
+      <c r="B39" s="92" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1929,30 +2085,30 @@
           <t>Manifestazioni di interesseAvviso alle Case  Editrici della Regione siciliana per la partecipazione al Salone del Libro di Torino, 14-18  maggio 2026.</t>
         </is>
       </c>
-      <c r="D39" s="89" t="inlineStr">
+      <c r="D39" s="93" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/manifestazione-d-interesse-partecipare-al-xxxviii-salone-libro-torino-14-al-18-maggio-2026-attraverso-l-esposizione-pubblicazioni-presso-stand-assessorato-beni</t>
         </is>
       </c>
-      <c r="E39" s="88" t="inlineStr">
+      <c r="E39" s="92" t="inlineStr">
         <is>
           <t>30/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F39" s="88" t="inlineStr">
+      <c r="F39" s="92" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="G39" s="88" t="inlineStr"/>
+      <c r="G39" s="92" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="90" t="inlineStr">
+      <c r="A40" s="94" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B40" s="90" t="inlineStr">
+      <c r="B40" s="94" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1967,25 +2123,25 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/pr-fesr-sicilia-202127-nuovo-avviso-manifestazione-d-interesse-esperti-valutatori</t>
         </is>
       </c>
-      <c r="E40" s="90" t="inlineStr">
+      <c r="E40" s="94" t="inlineStr">
         <is>
           <t>06/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F40" s="90" t="inlineStr">
+      <c r="F40" s="94" t="inlineStr">
         <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="G40" s="90" t="inlineStr"/>
+      <c r="G40" s="94" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="88" t="inlineStr">
+      <c r="A41" s="92" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B41" s="88" t="inlineStr">
+      <c r="B41" s="92" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1995,22 +2151,22 @@
           <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D41" s="89" t="inlineStr">
+      <c r="D41" s="93" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
         </is>
       </c>
-      <c r="E41" s="88" t="inlineStr"/>
-      <c r="F41" s="88" t="inlineStr"/>
-      <c r="G41" s="88" t="inlineStr"/>
+      <c r="E41" s="92" t="inlineStr"/>
+      <c r="F41" s="92" t="inlineStr"/>
+      <c r="G41" s="92" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="90" t="inlineStr">
+      <c r="A42" s="94" t="inlineStr">
         <is>
           <t>24/03/2026</t>
         </is>
       </c>
-      <c r="B42" s="90" t="inlineStr">
+      <c r="B42" s="94" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2025,17 +2181,17 @@
           <t>https://agricoltura.regione.emilia-romagna.it/sviluppo-rurale-23-27/opportunita/bandi-gal/2026/du_as05b-promozione-di-fiere-agroalimentari-e-delle-filiere-del-cibo-bando-per-enti-pubblici</t>
         </is>
       </c>
-      <c r="E42" s="90" t="inlineStr"/>
-      <c r="F42" s="90" t="inlineStr"/>
-      <c r="G42" s="90" t="inlineStr"/>
+      <c r="E42" s="94" t="inlineStr"/>
+      <c r="F42" s="94" t="inlineStr"/>
+      <c r="G42" s="94" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="88" t="inlineStr">
+      <c r="A43" s="92" t="inlineStr">
         <is>
           <t>24/03/2026</t>
         </is>
       </c>
-      <c r="B43" s="88" t="inlineStr">
+      <c r="B43" s="92" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2045,30 +2201,30 @@
           <t>Manifestazioni di interesseAVVISO PUBBLICO PER MANIFESTAZIONE DI INTERESSE FINALIZZATA ALL'ASSEGNAZIONE DI SPAZI ESPOSITIVI (CORNER GRATUITI) ALL'INTE</t>
         </is>
       </c>
-      <c r="D43" s="89" t="inlineStr">
+      <c r="D43" s="93" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-manifestazione-interesse-finalizzata-all-assegnazione-spazi-espositivi-corner-gratuiti-all-interno-stand-istituzionale-dsrt-manifestazione</t>
         </is>
       </c>
-      <c r="E43" s="88" t="inlineStr">
+      <c r="E43" s="92" t="inlineStr">
         <is>
           <t>30/03/2026 - 13:00</t>
         </is>
       </c>
-      <c r="F43" s="88" t="inlineStr">
+      <c r="F43" s="92" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G43" s="88" t="inlineStr"/>
+      <c r="G43" s="92" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="90" t="inlineStr">
+      <c r="A44" s="94" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B44" s="90" t="inlineStr">
+      <c r="B44" s="94" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2083,17 +2239,17 @@
           <t>https://www.regione.emilia-romagna.it/sport/bandi/2026/bando-2026</t>
         </is>
       </c>
-      <c r="E44" s="90" t="inlineStr"/>
-      <c r="F44" s="90" t="inlineStr"/>
-      <c r="G44" s="90" t="inlineStr"/>
+      <c r="E44" s="94" t="inlineStr"/>
+      <c r="F44" s="94" t="inlineStr"/>
+      <c r="G44" s="94" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="88" t="inlineStr">
+      <c r="A45" s="92" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B45" s="88" t="inlineStr">
+      <c r="B45" s="92" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2103,22 +2259,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Street art 2026Prossima AperturaBandi Regionali</t>
         </is>
       </c>
-      <c r="D45" s="89" t="inlineStr">
+      <c r="D45" s="93" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lazio-street-art-2026/</t>
         </is>
       </c>
-      <c r="E45" s="88" t="inlineStr"/>
-      <c r="F45" s="88" t="inlineStr"/>
-      <c r="G45" s="88" t="inlineStr"/>
+      <c r="E45" s="92" t="inlineStr"/>
+      <c r="F45" s="92" t="inlineStr"/>
+      <c r="G45" s="92" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="90" t="inlineStr">
+      <c r="A46" s="94" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B46" s="90" t="inlineStr">
+      <c r="B46" s="94" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2133,25 +2289,25 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/manifestazione-interesse-partecipazione-all-evento-r2i-italy-2026-bologna-12-13052026</t>
         </is>
       </c>
-      <c r="E46" s="90" t="inlineStr">
+      <c r="E46" s="94" t="inlineStr">
         <is>
           <t>03/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F46" s="90" t="inlineStr">
+      <c r="F46" s="94" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="G46" s="90" t="inlineStr"/>
+      <c r="G46" s="94" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="88" t="inlineStr">
+      <c r="A47" s="92" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B47" s="88" t="inlineStr">
+      <c r="B47" s="92" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2161,30 +2317,30 @@
           <t>Manifestazioni di interesseST SIRACUSA - AVVISO PER MANIFESTAZIONE DI INTERESSE - Selezione di n. 5 unità di personale internoScade il:20/04/2026 - 12</t>
         </is>
       </c>
-      <c r="D47" s="89" t="inlineStr">
+      <c r="D47" s="93" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/24-marzo-2026-st-siracusa-avviso-manifestazione-interesse-selezione-n-5-unita-personale-interno</t>
         </is>
       </c>
-      <c r="E47" s="88" t="inlineStr">
+      <c r="E47" s="92" t="inlineStr">
         <is>
           <t>20/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F47" s="88" t="inlineStr">
+      <c r="F47" s="92" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="G47" s="88" t="inlineStr"/>
+      <c r="G47" s="92" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="90" t="inlineStr">
+      <c r="A48" s="94" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B48" s="90" t="inlineStr">
+      <c r="B48" s="94" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2199,25 +2355,25 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/revoca-avviso-concessione-titolo-gratuito-16122025-inerente-all-immobile-seguito-identificato-contestuale-nuovo-avviso-concessione-titolo-oneroso-stesso-sito-nel</t>
         </is>
       </c>
-      <c r="E48" s="90" t="inlineStr">
+      <c r="E48" s="94" t="inlineStr">
         <is>
           <t>08/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F48" s="90" t="inlineStr">
+      <c r="F48" s="94" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="G48" s="90" t="inlineStr"/>
+      <c r="G48" s="94" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="88" t="inlineStr">
+      <c r="A49" s="92" t="inlineStr">
         <is>
           <t>26/03/2026</t>
         </is>
       </c>
-      <c r="B49" s="88" t="inlineStr">
+      <c r="B49" s="92" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2227,22 +2383,22 @@
           <t>Bando studi di fattibilità per fusioni di Comuni</t>
         </is>
       </c>
-      <c r="D49" s="89" t="inlineStr">
+      <c r="D49" s="93" t="inlineStr">
         <is>
           <t>https://www.regione.emilia-romagna.it/autonomie-locali/bandi/bando_studi_fattibilita_fusioni_comuni</t>
         </is>
       </c>
-      <c r="E49" s="88" t="inlineStr"/>
-      <c r="F49" s="88" t="inlineStr"/>
-      <c r="G49" s="88" t="inlineStr"/>
+      <c r="E49" s="92" t="inlineStr"/>
+      <c r="F49" s="92" t="inlineStr"/>
+      <c r="G49" s="92" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="90" t="inlineStr">
+      <c r="A50" s="94" t="inlineStr">
         <is>
           <t>26/03/2026</t>
         </is>
       </c>
-      <c r="B50" s="90" t="inlineStr">
+      <c r="B50" s="94" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2257,25 +2413,25 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-selezione-interna-titoli-conferimento-po-professionali-ai-sensi-artt-19-20-21-ccrl-20222024-comparto-non-dirigenziale</t>
         </is>
       </c>
-      <c r="E50" s="90" t="inlineStr">
+      <c r="E50" s="94" t="inlineStr">
         <is>
           <t>30/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F50" s="90" t="inlineStr">
+      <c r="F50" s="94" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G50" s="90" t="inlineStr"/>
+      <c r="G50" s="94" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="88" t="inlineStr">
+      <c r="A51" s="92" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="B51" s="88" t="inlineStr">
+      <c r="B51" s="92" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2285,22 +2441,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0PRE-SEED 3.0ApertoFESR</t>
         </is>
       </c>
-      <c r="D51" s="89" t="inlineStr">
+      <c r="D51" s="93" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/pre-seed-3-0/</t>
         </is>
       </c>
-      <c r="E51" s="88" t="inlineStr"/>
-      <c r="F51" s="88" t="inlineStr"/>
-      <c r="G51" s="88" t="inlineStr"/>
+      <c r="E51" s="92" t="inlineStr"/>
+      <c r="F51" s="92" t="inlineStr"/>
+      <c r="G51" s="92" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="90" t="inlineStr">
+      <c r="A52" s="94" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B52" s="90" t="inlineStr">
+      <c r="B52" s="94" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2315,25 +2471,25 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-termini-imerese-locta-piazza-marina</t>
         </is>
       </c>
-      <c r="E52" s="90" t="inlineStr">
+      <c r="E52" s="94" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F52" s="90" t="inlineStr">
+      <c r="F52" s="94" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G52" s="90" t="inlineStr"/>
+      <c r="G52" s="94" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="88" t="inlineStr">
+      <c r="A53" s="92" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B53" s="88" t="inlineStr">
+      <c r="B53" s="92" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2343,30 +2499,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, Sig</t>
         </is>
       </c>
-      <c r="D53" s="89" t="inlineStr">
+      <c r="D53" s="93" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-porto-empedocle-locta-punta-piccola</t>
         </is>
       </c>
-      <c r="E53" s="88" t="inlineStr">
+      <c r="E53" s="92" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F53" s="88" t="inlineStr">
+      <c r="F53" s="92" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G53" s="88" t="inlineStr"/>
+      <c r="G53" s="92" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="90" t="inlineStr">
+      <c r="A54" s="94" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B54" s="90" t="inlineStr">
+      <c r="B54" s="94" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2381,25 +2537,25 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-messina-locta-torrente-bordonaro</t>
         </is>
       </c>
-      <c r="E54" s="90" t="inlineStr">
+      <c r="E54" s="94" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F54" s="90" t="inlineStr">
+      <c r="F54" s="94" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G54" s="90" t="inlineStr"/>
+      <c r="G54" s="94" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="88" t="inlineStr">
+      <c r="A55" s="92" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B55" s="88" t="inlineStr">
+      <c r="B55" s="92" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2409,30 +2565,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “Condomin</t>
         </is>
       </c>
-      <c r="D55" s="89" t="inlineStr">
+      <c r="D55" s="93" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-mascali-spiaggia-n-144150</t>
         </is>
       </c>
-      <c r="E55" s="88" t="inlineStr">
+      <c r="E55" s="92" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F55" s="88" t="inlineStr">
+      <c r="F55" s="92" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G55" s="88" t="inlineStr"/>
+      <c r="G55" s="92" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="90" t="inlineStr">
+      <c r="A56" s="94" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B56" s="90" t="inlineStr">
+      <c r="B56" s="94" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2447,25 +2603,25 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-lipari-isola-stromboli-locta-fico-grande</t>
         </is>
       </c>
-      <c r="E56" s="90" t="inlineStr">
+      <c r="E56" s="94" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F56" s="90" t="inlineStr">
+      <c r="F56" s="94" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G56" s="90" t="inlineStr"/>
+      <c r="G56" s="94" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="88" t="inlineStr">
+      <c r="A57" s="92" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B57" s="88" t="inlineStr">
+      <c r="B57" s="92" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2475,30 +2631,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione sito nel Comune di Favignana, isola di Le</t>
         </is>
       </c>
-      <c r="D57" s="89" t="inlineStr">
+      <c r="D57" s="93" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-favignana-isola-levanzo</t>
         </is>
       </c>
-      <c r="E57" s="88" t="inlineStr">
+      <c r="E57" s="92" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F57" s="88" t="inlineStr">
+      <c r="F57" s="92" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G57" s="88" t="inlineStr"/>
+      <c r="G57" s="92" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="90" t="inlineStr">
+      <c r="A58" s="94" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="B58" s="90" t="inlineStr">
+      <c r="B58" s="94" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2513,25 +2669,25 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-d-interesse-finalizzata-alla-selezione-organismi-attuatori-piani-gestione-locale-piccola-pesca-costiera-nelle-gsa-regione-siciliana</t>
         </is>
       </c>
-      <c r="E58" s="90" t="inlineStr">
+      <c r="E58" s="94" t="inlineStr">
         <is>
           <t>29/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F58" s="90" t="inlineStr">
+      <c r="F58" s="94" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="G58" s="90" t="inlineStr"/>
+      <c r="G58" s="94" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="88" t="inlineStr">
+      <c r="A59" s="92" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="B59" s="88" t="inlineStr">
+      <c r="B59" s="92" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2541,30 +2697,30 @@
           <t>Avvisi pubbliciLeggi e scarica l'avvisoScade il:02/04/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D59" s="89" t="inlineStr">
+      <c r="D59" s="93" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/proroga-termini-presentazione-candidature-po</t>
         </is>
       </c>
-      <c r="E59" s="88" t="inlineStr">
+      <c r="E59" s="92" t="inlineStr">
         <is>
           <t>02/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F59" s="88" t="inlineStr">
+      <c r="F59" s="92" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="G59" s="88" t="inlineStr"/>
+      <c r="G59" s="92" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="90" t="inlineStr">
+      <c r="A60" s="94" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="90" t="inlineStr">
+      <c r="B60" s="94" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2579,17 +2735,17 @@
           <t>https://www.lazioeuropa.it/bandi/smau-italy-restartsup-in-stoccolma/</t>
         </is>
       </c>
-      <c r="E60" s="90" t="inlineStr"/>
-      <c r="F60" s="90" t="inlineStr"/>
-      <c r="G60" s="90" t="inlineStr"/>
+      <c r="E60" s="94" t="inlineStr"/>
+      <c r="F60" s="94" t="inlineStr"/>
+      <c r="G60" s="94" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="88" t="inlineStr">
+      <c r="A61" s="92" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B61" s="88" t="inlineStr">
+      <c r="B61" s="92" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2599,22 +2755,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per Farnborough International AirshowApertoFESR</t>
         </is>
       </c>
-      <c r="D61" s="89" t="inlineStr">
+      <c r="D61" s="93" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-farnborough-international-airshow-2/</t>
         </is>
       </c>
-      <c r="E61" s="88" t="inlineStr"/>
-      <c r="F61" s="88" t="inlineStr"/>
-      <c r="G61" s="88" t="inlineStr"/>
+      <c r="E61" s="92" t="inlineStr"/>
+      <c r="F61" s="92" t="inlineStr"/>
+      <c r="G61" s="92" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="90" t="inlineStr">
+      <c r="A62" s="94" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="90" t="inlineStr">
+      <c r="B62" s="94" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2629,25 +2785,25 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proprieta-regionale-sito-nel-comune-termini-imerese-favore-ares-fabiola</t>
         </is>
       </c>
-      <c r="E62" s="90" t="inlineStr">
+      <c r="E62" s="94" t="inlineStr">
         <is>
           <t>30/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F62" s="90" t="inlineStr">
+      <c r="F62" s="94" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="G62" s="90" t="inlineStr"/>
+      <c r="G62" s="94" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="88" t="inlineStr">
+      <c r="A63" s="92" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B63" s="88" t="inlineStr">
+      <c r="B63" s="92" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2657,22 +2813,22 @@
           <t>Avviso per la concessione di contributi per progetti di contrasto all'abbandono sportivo giovanile (2026)</t>
         </is>
       </c>
-      <c r="D63" s="89" t="inlineStr">
+      <c r="D63" s="93" t="inlineStr">
         <is>
           <t>https://www.regione.emilia-romagna.it/sport/bandi/2026/contrasto-abbandono-2026</t>
         </is>
       </c>
-      <c r="E63" s="88" t="inlineStr"/>
-      <c r="F63" s="88" t="inlineStr"/>
-      <c r="G63" s="88" t="inlineStr"/>
+      <c r="E63" s="92" t="inlineStr"/>
+      <c r="F63" s="92" t="inlineStr"/>
+      <c r="G63" s="92" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="90" t="inlineStr">
+      <c r="A64" s="94" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="90" t="inlineStr">
+      <c r="B64" s="94" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2687,25 +2843,25 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-selezione-interna-conferimento-1-posizione-organizzativa-ai-sensi-artt-19-20-ccrl-2022-2024-comparto-non-dirigenziale</t>
         </is>
       </c>
-      <c r="E64" s="90" t="inlineStr">
+      <c r="E64" s="94" t="inlineStr">
         <is>
           <t>09/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F64" s="90" t="inlineStr">
+      <c r="F64" s="94" t="inlineStr">
         <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="G64" s="90" t="inlineStr"/>
+      <c r="G64" s="94" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="88" t="inlineStr">
+      <c r="A65" s="92" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B65" s="88" t="inlineStr">
+      <c r="B65" s="92" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2715,30 +2871,30 @@
           <t>Avvisi pubbliciST-MESSINA - AVVISO di INDAGINE DI MERCATO per affidamento "Interventi manutenzione straordinaria della strada/pista forestale "Annunzi</t>
         </is>
       </c>
-      <c r="D65" s="89" t="inlineStr">
+      <c r="D65" s="93" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-indagine-mercato-affidamento-interventi-manutenzione-straordinaria-stradapista-forestale-annunziata-comune-messina</t>
         </is>
       </c>
-      <c r="E65" s="88" t="inlineStr">
+      <c r="E65" s="92" t="inlineStr">
         <is>
           <t>16/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F65" s="88" t="inlineStr">
+      <c r="F65" s="92" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="G65" s="88" t="inlineStr"/>
+      <c r="G65" s="92" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="90" t="inlineStr">
+      <c r="A66" s="94" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="90" t="inlineStr">
+      <c r="B66" s="94" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2753,25 +2909,25 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-indagine-mercato-affidamento-interventi-manutenzione-straordinaria-stradapista-forestale-san-rizzo-san-leone-crupi-madonuzza-comune-messina</t>
         </is>
       </c>
-      <c r="E66" s="90" t="inlineStr">
+      <c r="E66" s="94" t="inlineStr">
         <is>
           <t>16/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F66" s="90" t="inlineStr">
+      <c r="F66" s="94" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="G66" s="90" t="inlineStr"/>
+      <c r="G66" s="94" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="88" t="inlineStr">
+      <c r="A67" s="92" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="88" t="inlineStr">
+      <c r="B67" s="92" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2781,22 +2937,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Manifestazione di interesse per Casaidea 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D67" s="89" t="inlineStr">
+      <c r="D67" s="93" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-casaidea-2026/</t>
         </is>
       </c>
-      <c r="E67" s="88" t="inlineStr"/>
-      <c r="F67" s="88" t="inlineStr"/>
-      <c r="G67" s="88" t="inlineStr"/>
+      <c r="E67" s="92" t="inlineStr"/>
+      <c r="F67" s="92" t="inlineStr"/>
+      <c r="G67" s="92" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="90" t="inlineStr">
+      <c r="A68" s="94" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="90" t="inlineStr">
+      <c r="B68" s="94" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2811,17 +2967,17 @@
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-il-salone-internazionale-del-libro-di-torino-2026/</t>
         </is>
       </c>
-      <c r="E68" s="90" t="inlineStr"/>
-      <c r="F68" s="90" t="inlineStr"/>
-      <c r="G68" s="90" t="inlineStr"/>
+      <c r="E68" s="94" t="inlineStr"/>
+      <c r="F68" s="94" t="inlineStr"/>
+      <c r="G68" s="94" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="88" t="inlineStr">
+      <c r="A69" s="92" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="88" t="inlineStr">
+      <c r="B69" s="92" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2831,30 +2987,30 @@
           <t>Avvisi pubbliciDDG 1112 del 02.04.2026 - Aggiornamento Avviso pubblico n. 4/2024 per l’attuazione del PAR GOL Sicilia da finanziare nell’ambito del Pi</t>
         </is>
       </c>
-      <c r="D69" s="89" t="inlineStr">
+      <c r="D69" s="93" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/ddg-1112-02042026-aggiornamento-avviso-pubblico-n-42024-l-attuazione-par-gol-sicilia-finanziare-nell-ambito-piano-nazionale-ripresa-resilienza-pnrr</t>
         </is>
       </c>
-      <c r="E69" s="88" t="inlineStr">
+      <c r="E69" s="92" t="inlineStr">
         <is>
           <t>05/04/2030 - 00:00</t>
         </is>
       </c>
-      <c r="F69" s="88" t="inlineStr">
+      <c r="F69" s="92" t="inlineStr">
         <is>
           <t>05/04/2030</t>
         </is>
       </c>
-      <c r="G69" s="88" t="inlineStr"/>
+      <c r="G69" s="92" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="90" t="inlineStr">
+      <c r="A70" s="94" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="90" t="inlineStr">
+      <c r="B70" s="94" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2869,25 +3025,25 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/ddg-1113-02042026-aggiornamento-avviso-pubblico-n-22022-smi-l-attuazione-par-gol-sicilia-finanziare-nell-ambito-piano-nazionale-ripresa-resilienza-pnrr</t>
         </is>
       </c>
-      <c r="E70" s="90" t="inlineStr">
+      <c r="E70" s="94" t="inlineStr">
         <is>
           <t>03/04/2030 - 00:00</t>
         </is>
       </c>
-      <c r="F70" s="90" t="inlineStr">
+      <c r="F70" s="94" t="inlineStr">
         <is>
           <t>03/04/2030</t>
         </is>
       </c>
-      <c r="G70" s="90" t="inlineStr"/>
+      <c r="G70" s="94" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="88" t="inlineStr">
+      <c r="A71" s="92" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B71" s="88" t="inlineStr">
+      <c r="B71" s="92" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2897,22 +3053,22 @@
           <t>Avvisi pubbliciLeggi e scarica l'avvisoScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D71" s="89" t="inlineStr">
+      <c r="D71" s="93" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/proroga-termini-presentazione-candidature-po</t>
         </is>
       </c>
-      <c r="E71" s="88" t="inlineStr"/>
-      <c r="F71" s="88" t="inlineStr"/>
-      <c r="G71" s="88" t="inlineStr"/>
+      <c r="E71" s="92" t="inlineStr"/>
+      <c r="F71" s="92" t="inlineStr"/>
+      <c r="G71" s="92" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="90" t="inlineStr">
+      <c r="A72" s="94" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="90" t="inlineStr">
+      <c r="B72" s="94" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2927,17 +3083,17 @@
           <t>https://www.lazioeuropa.it/bandi/comunicare-linclusione-contest-per-le-istituzioni-scolastiche-regionali/</t>
         </is>
       </c>
-      <c r="E72" s="90" t="inlineStr"/>
-      <c r="F72" s="90" t="inlineStr"/>
-      <c r="G72" s="90" t="inlineStr"/>
+      <c r="E72" s="94" t="inlineStr"/>
+      <c r="F72" s="94" t="inlineStr"/>
+      <c r="G72" s="94" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="88" t="inlineStr">
+      <c r="A73" s="92" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B73" s="88" t="inlineStr">
+      <c r="B73" s="92" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2947,30 +3103,30 @@
           <t>Avvisi pubbliciAPPROVAZIONE AVVISO PUBBLICOScade il:03/04/2027 - 00:00Leggi di più</t>
         </is>
       </c>
-      <c r="D73" s="89" t="inlineStr">
+      <c r="D73" s="93" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/approvazione-avviso-pubblico</t>
         </is>
       </c>
-      <c r="E73" s="88" t="inlineStr">
+      <c r="E73" s="92" t="inlineStr">
         <is>
           <t>03/04/2027 - 00:00</t>
         </is>
       </c>
-      <c r="F73" s="88" t="inlineStr">
+      <c r="F73" s="92" t="inlineStr">
         <is>
           <t>03/04/2027</t>
         </is>
       </c>
-      <c r="G73" s="88" t="inlineStr"/>
+      <c r="G73" s="92" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="90" t="inlineStr">
+      <c r="A74" s="94" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="90" t="inlineStr">
+      <c r="B74" s="94" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2985,17 +3141,17 @@
           <t>https://www.lazioeuropa.it/bandi/donne-e-impresa-2026/</t>
         </is>
       </c>
-      <c r="E74" s="90" t="inlineStr"/>
-      <c r="F74" s="90" t="inlineStr"/>
-      <c r="G74" s="90" t="inlineStr"/>
+      <c r="E74" s="94" t="inlineStr"/>
+      <c r="F74" s="94" t="inlineStr"/>
+      <c r="G74" s="94" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="88" t="inlineStr">
+      <c r="A75" s="92" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B75" s="88" t="inlineStr">
+      <c r="B75" s="92" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3005,30 +3161,30 @@
           <t>Bandi di garaCodice Intervento 111302_FELUCHE - Investimenti a bordo e nei porti per incrementare la qualità delle produzioni e migliorare le condizio</t>
         </is>
       </c>
-      <c r="D75" s="89" t="inlineStr">
+      <c r="D75" s="93" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/bandoavviso-regia-ob-11-azione-3-codice-111302feluche-investimenti-bordo-valorizzazione-feluche-miglioramento-condizioni-lavoro-salute-sicurezza-operatori-l</t>
         </is>
       </c>
-      <c r="E75" s="88" t="inlineStr">
+      <c r="E75" s="92" t="inlineStr">
         <is>
           <t>02/07/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F75" s="88" t="inlineStr">
+      <c r="F75" s="92" t="inlineStr">
         <is>
           <t>02/07/2026</t>
         </is>
       </c>
-      <c r="G75" s="88" t="inlineStr"/>
+      <c r="G75" s="92" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="90" t="inlineStr">
+      <c r="A76" s="94" t="inlineStr">
         <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="90" t="inlineStr">
+      <c r="B76" s="94" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -3043,17 +3199,17 @@
           <t>https://www.lazioeuropa.it/bandi/sostegno-agli-investimenti-nel-settore-vitivinicolo-campagna-2026-2027/</t>
         </is>
       </c>
-      <c r="E76" s="90" t="inlineStr"/>
-      <c r="F76" s="90" t="inlineStr"/>
-      <c r="G76" s="90" t="inlineStr"/>
+      <c r="E76" s="94" t="inlineStr"/>
+      <c r="F76" s="94" t="inlineStr"/>
+      <c r="G76" s="94" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="88" t="inlineStr">
+      <c r="A77" s="92" t="inlineStr">
         <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="88" t="inlineStr">
+      <c r="B77" s="92" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3063,30 +3219,30 @@
           <t>Manifestazioni di interesse9 aprile 2026 -ST PALERMO- Manifestazione di interesse - “Interventi di manutenzione straordinaria della strada-pista fores</t>
         </is>
       </c>
-      <c r="D77" s="89" t="inlineStr">
+      <c r="D77" s="93" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/9-aprile-2026-st-palermo-manifestazione-interesse-interventi-manutenzione-straordinaria-strada-pista-forestale-monte-cane-comune-caccamo-pa-distretto-forestale</t>
         </is>
       </c>
-      <c r="E77" s="88" t="inlineStr">
+      <c r="E77" s="92" t="inlineStr">
         <is>
           <t>24/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F77" s="88" t="inlineStr">
+      <c r="F77" s="92" t="inlineStr">
         <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="G77" s="88" t="inlineStr"/>
+      <c r="G77" s="92" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="90" t="inlineStr">
+      <c r="A78" s="94" t="inlineStr">
         <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="90" t="inlineStr">
+      <c r="B78" s="94" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3101,25 +3257,25 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-indagine-mercato-affidamento-interventi-manutenzione-straordinaria-stradapista-forestale-faggita-comune-tripi-me</t>
         </is>
       </c>
-      <c r="E78" s="90" t="inlineStr">
+      <c r="E78" s="94" t="inlineStr">
         <is>
           <t>23/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F78" s="90" t="inlineStr">
+      <c r="F78" s="94" t="inlineStr">
         <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="G78" s="90" t="inlineStr"/>
+      <c r="G78" s="94" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="88" t="inlineStr">
+      <c r="A79" s="92" t="inlineStr">
         <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B79" s="88" t="inlineStr">
+      <c r="B79" s="92" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3129,30 +3285,30 @@
           <t>Avvisi pubbliciST-MESSINA - AVVISO DI INDAGINE DI MERCATO per affidamento "Interventi manutenzione straordinaria della strada/pista forestale "Ferraro</t>
         </is>
       </c>
-      <c r="D79" s="89" t="inlineStr">
+      <c r="D79" s="93" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-indagine-mercato-affidamento-interventi-manutenzione-straordinaria-stradapista-forestale-ferraro-sanrizzo-badiazza-comune-messina</t>
         </is>
       </c>
-      <c r="E79" s="88" t="inlineStr">
+      <c r="E79" s="92" t="inlineStr">
         <is>
           <t>23/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F79" s="88" t="inlineStr">
+      <c r="F79" s="92" t="inlineStr">
         <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="G79" s="88" t="inlineStr"/>
+      <c r="G79" s="92" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="90" t="inlineStr">
+      <c r="A80" s="94" t="inlineStr">
         <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="90" t="inlineStr">
+      <c r="B80" s="94" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -3167,17 +3323,17 @@
           <t>https://www.lazioeuropa.it/bandi/acquisizione-di-servizi-di-comunicazione-e-informazione-pr-lazio-fesr-pr-lazio-fse-e-comunicazione-unitaria/</t>
         </is>
       </c>
-      <c r="E80" s="90" t="inlineStr"/>
-      <c r="F80" s="90" t="inlineStr"/>
-      <c r="G80" s="90" t="inlineStr"/>
+      <c r="E80" s="94" t="inlineStr"/>
+      <c r="F80" s="94" t="inlineStr"/>
+      <c r="G80" s="94" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="88" t="inlineStr">
+      <c r="A81" s="92" t="inlineStr">
         <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B81" s="88" t="inlineStr">
+      <c r="B81" s="92" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3187,30 +3343,30 @@
           <t>Avvisi pubbliciAvviso pubblico di selezione interna, per titoli, per il conferimento, ai sensi degli artt. 21 del CCRL 2022-2024 del comparto non diri</t>
         </is>
       </c>
-      <c r="D81" s="89" t="inlineStr">
+      <c r="D81" s="93" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-selezione-interna-titoli-conferimento-ai-sensi-artt-21-ccrl-2022-2024-comparto-non-dirigenziale-una-posizione-organizzativa-dipartimento</t>
         </is>
       </c>
-      <c r="E81" s="88" t="inlineStr">
+      <c r="E81" s="92" t="inlineStr">
         <is>
           <t>16/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F81" s="88" t="inlineStr">
+      <c r="F81" s="92" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="G81" s="88" t="inlineStr"/>
+      <c r="G81" s="92" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="90" t="inlineStr">
+      <c r="A82" s="94" t="inlineStr">
         <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="90" t="inlineStr">
+      <c r="B82" s="94" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3225,17 +3381,17 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-indagine-mercato-partecipazione-alla-successiva-procedura-negoziata-norma-art-50-comma-1-lettera-c-dlgs-31-marzo-2023-n-36-ssmmii-finalizzata-all</t>
         </is>
       </c>
-      <c r="E82" s="90" t="inlineStr">
+      <c r="E82" s="94" t="inlineStr">
         <is>
           <t>30/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F82" s="90" t="inlineStr">
+      <c r="F82" s="94" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="G82" s="90" t="inlineStr"/>
+      <c r="G82" s="94" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="92" t="inlineStr">
@@ -3261,6 +3417,180 @@
       <c r="E83" s="92" t="inlineStr"/>
       <c r="F83" s="92" t="inlineStr"/>
       <c r="G83" s="92" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="97" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="97" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>CooperazioneManifestazione di interesse per partecipare a Codeway Expo 2026ApertoAltri fondiFESR</t>
+        </is>
+      </c>
+      <c r="D84" s="98" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-partecipare-a-codeway-expo-2026/</t>
+        </is>
+      </c>
+      <c r="E84" s="97" t="inlineStr"/>
+      <c r="F84" s="97" t="inlineStr"/>
+      <c r="G84" s="97" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="95" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="95" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Street art 2026ApertoBandi Regionali</t>
+        </is>
+      </c>
+      <c r="D85" s="96" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/lazio-street-art-2026/</t>
+        </is>
+      </c>
+      <c r="E85" s="95" t="inlineStr"/>
+      <c r="F85" s="95" t="inlineStr"/>
+      <c r="G85" s="95" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="97" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="97" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="C86" s="9" t="inlineStr">
+        <is>
+          <t>LAVORO, FORMAZIONE E INCLUSIONEBuoni servizio per le persone non autosufficienti nel territorio del LazioApertoFSE / FSE+</t>
+        </is>
+      </c>
+      <c r="D86" s="98" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/buoni-servizio-per-le-persone-non-autosufficienti-nel-territorio-del-lazio/</t>
+        </is>
+      </c>
+      <c r="E86" s="97" t="inlineStr"/>
+      <c r="F86" s="97" t="inlineStr"/>
+      <c r="G86" s="97" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="95" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="95" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>Avvisi pubbliciSERVIZIO 14 SERVIZIO PER IL TERRITORIO DI PALERMO AVVISO PUBBLICO PER LA CONCESSIONE AL PASCOLO NEI TERRENI DEL DEMANIO FORESTALE REGIO</t>
+        </is>
+      </c>
+      <c r="D87" s="96" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-14-servizio-territorio-palermo-avviso-pubblico-concessione-al-pascolo-nei-terreni-demanio-forestale-regionale-gestiti-dipartimento-sviluppo-rurale</t>
+        </is>
+      </c>
+      <c r="E87" s="95" t="inlineStr">
+        <is>
+          <t>05/05/2026 - 12:00</t>
+        </is>
+      </c>
+      <c r="F87" s="95" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="G87" s="95" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="97" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="97" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C88" s="9" t="inlineStr">
+        <is>
+          <t>Avvisi pubbliciAtto di interpello rivolto al personale del Comparto non dirigenziale per la designazione del  Consegnatario e del Vice Consegnatario d</t>
+        </is>
+      </c>
+      <c r="D88" s="98" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/atto-intepello-dipartimento-turismo-sport-spettacolo</t>
+        </is>
+      </c>
+      <c r="E88" s="97" t="inlineStr">
+        <is>
+          <t>30/04/2026 - 23:59</t>
+        </is>
+      </c>
+      <c r="F88" s="97" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="G88" s="97" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="95" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="95" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>Avvisi pubbliciAVVISO DI INDAGINE DI MERCATO - per la partecipazione alla successiva procedura negoziata a norma dell'art. 50, comma 1, lettera c) del</t>
+        </is>
+      </c>
+      <c r="D89" s="96" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-pa-avviso-indagine-mercato-partecipazione-alla-successiva-procedura-negoziata-norma-art-50-comma-1-lettera-c-dlgs-31-marzo-2023-n-36-ssmmii-finalizzata-all</t>
+        </is>
+      </c>
+      <c r="E89" s="95" t="inlineStr">
+        <is>
+          <t>02/05/2026 - 12:00</t>
+        </is>
+      </c>
+      <c r="F89" s="95" t="inlineStr">
+        <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="G89" s="95" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -3346,6 +3676,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D82" r:id="rId81"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D89" r:id="rId88"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3390,7 +3726,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="92" t="inlineStr">
+      <c r="A3" s="95" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -3403,29 +3739,29 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="94" t="inlineStr">
+      <c r="A4" s="97" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="92" t="inlineStr">
+      <c r="A5" s="95" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">

--- a/data/bandi_export.xlsx
+++ b/data/bandi_export.xlsx
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -396,6 +396,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -775,7 +787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -790,7 +802,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏛️  Nuovi Bandi — 16/04/2026 08:24</t>
+          <t>🏛️  Nuovi Bandi — 17/04/2026 08:23</t>
         </is>
       </c>
     </row>
@@ -835,98 +847,98 @@
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="95" t="inlineStr">
+      <c r="B3" s="99" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>CooperazioneManifestazione di interesse per partecipare a Codeway Expo 2026ApertoAltri fondiFESR</t>
-        </is>
-      </c>
-      <c r="D3" s="96" t="inlineStr">
-        <is>
-          <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-partecipare-a-codeway-expo-2026/</t>
-        </is>
-      </c>
-      <c r="E3" s="95" t="inlineStr"/>
-      <c r="F3" s="95" t="inlineStr"/>
+          <t>ACCESSO AL CREDITO E ALLE GARANZIE PER LE IMPRESEFondo Patrimonializzazione Pmi 2025 – Riapertura terminiProssima AperturaFESR</t>
+        </is>
+      </c>
+      <c r="D3" s="100" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/fondo-patrimonializzazione-pmi-riapertura-termini/</t>
+        </is>
+      </c>
+      <c r="E3" s="99" t="inlineStr"/>
+      <c r="F3" s="99" t="inlineStr"/>
       <c r="G3" s="5" t="inlineStr"/>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="97" t="inlineStr">
+      <c r="B4" s="101" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Street art 2026ApertoBandi Regionali</t>
-        </is>
-      </c>
-      <c r="D4" s="98" t="inlineStr">
-        <is>
-          <t>https://www.lazioeuropa.it/bandi/lazio-street-art-2026/</t>
-        </is>
-      </c>
-      <c r="E4" s="97" t="inlineStr"/>
-      <c r="F4" s="97" t="inlineStr"/>
+          <t>ACCESSO AL CREDITO E ALLE GARANZIE PER LE IMPRESENuovo Fondo Piccolo Credito – sezione ordinaria (2026)Prossima AperturaFESRPOCRisorse regionali</t>
+        </is>
+      </c>
+      <c r="D4" s="102" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/nuovo-fondo-piccolo-credito-sezione-ordinaria-2026/</t>
+        </is>
+      </c>
+      <c r="E4" s="101" t="inlineStr"/>
+      <c r="F4" s="101" t="inlineStr"/>
       <c r="G4" s="9" t="inlineStr"/>
     </row>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="95" t="inlineStr">
+      <c r="B5" s="99" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>LAVORO, FORMAZIONE E INCLUSIONEBuoni servizio per le persone non autosufficienti nel territorio del LazioApertoFSE / FSE+</t>
-        </is>
-      </c>
-      <c r="D5" s="96" t="inlineStr">
-        <is>
-          <t>https://www.lazioeuropa.it/bandi/buoni-servizio-per-le-persone-non-autosufficienti-nel-territorio-del-lazio/</t>
-        </is>
-      </c>
-      <c r="E5" s="95" t="inlineStr"/>
-      <c r="F5" s="95" t="inlineStr"/>
+          <t>ACCESSO AL CREDITO E ALLE GARANZIE PER LE IMPRESENuovo Fondo Futuro 2026Prossima AperturaFESRPOC</t>
+        </is>
+      </c>
+      <c r="D5" s="100" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/nuovo-fondo-futuro-2026/</t>
+        </is>
+      </c>
+      <c r="E5" s="99" t="inlineStr"/>
+      <c r="F5" s="99" t="inlineStr"/>
       <c r="G5" s="5" t="inlineStr"/>
     </row>
     <row r="6" ht="32" customHeight="1">
       <c r="A6" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="97" t="inlineStr">
+      <c r="B6" s="101" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>Avvisi pubbliciSERVIZIO 14 SERVIZIO PER IL TERRITORIO DI PALERMO AVVISO PUBBLICO PER LA CONCESSIONE AL PASCOLO NEI TERRENI DEL DEMANIO FORESTALE REGIO</t>
-        </is>
-      </c>
-      <c r="D6" s="98" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-14-servizio-territorio-palermo-avviso-pubblico-concessione-al-pascolo-nei-terreni-demanio-forestale-regionale-gestiti-dipartimento-sviluppo-rurale</t>
-        </is>
-      </c>
-      <c r="E6" s="97" t="inlineStr">
-        <is>
-          <t>05/05/2026 - 12:00</t>
-        </is>
-      </c>
-      <c r="F6" s="97" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
+          <t>Avvisi pubbliciAvviso pubblico di selezione interna, per titoli, per il conferimento, ai sensi degli artt. 19 e 20 del CCRL 2022-2024 del comparto non</t>
+        </is>
+      </c>
+      <c r="D6" s="102" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-selezione-interna-titoli-conferimento-ai-sensi-artt-19-20-ccrl-2022-2024-comparto-non-dirigenziale-posizioni-organizzative-dipartimento-regionale</t>
+        </is>
+      </c>
+      <c r="E6" s="101" t="inlineStr">
+        <is>
+          <t>24/04/2026 - 12:00</t>
+        </is>
+      </c>
+      <c r="F6" s="101" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr"/>
@@ -935,63 +947,32 @@
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="95" t="inlineStr">
+      <c r="B7" s="99" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Avvisi pubbliciAtto di interpello rivolto al personale del Comparto non dirigenziale per la designazione del  Consegnatario e del Vice Consegnatario d</t>
-        </is>
-      </c>
-      <c r="D7" s="96" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/atto-intepello-dipartimento-turismo-sport-spettacolo</t>
-        </is>
-      </c>
-      <c r="E7" s="95" t="inlineStr">
-        <is>
-          <t>30/04/2026 - 23:59</t>
-        </is>
-      </c>
-      <c r="F7" s="95" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
+          <t>Avvisi pubblici16 aprile 2026 - ST CATANIA - Avviso Concessione postazioni arnie - anno 2026Scade il:27/04/2026 - 12:00Leggi di più</t>
+        </is>
+      </c>
+      <c r="D7" s="100" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/16-aprile-2026-st-catania-avviso-concessione-postazioni-arnie-anno-2026</t>
+        </is>
+      </c>
+      <c r="E7" s="99" t="inlineStr">
+        <is>
+          <t>27/04/2026 - 12:00</t>
+        </is>
+      </c>
+      <c r="F7" s="99" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" s="97" t="inlineStr">
-        <is>
-          <t>Sicilia</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>Avvisi pubbliciAVVISO DI INDAGINE DI MERCATO - per la partecipazione alla successiva procedura negoziata a norma dell'art. 50, comma 1, lettera c) del</t>
-        </is>
-      </c>
-      <c r="D8" s="98" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-pa-avviso-indagine-mercato-partecipazione-alla-successiva-procedura-negoziata-norma-art-50-comma-1-lettera-c-dlgs-31-marzo-2023-n-36-ssmmii-finalizzata-all</t>
-        </is>
-      </c>
-      <c r="E8" s="97" t="inlineStr">
-        <is>
-          <t>02/05/2026 - 12:00</t>
-        </is>
-      </c>
-      <c r="F8" s="97" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="G8" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1003,7 +984,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1015,7 +995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1065,12 +1045,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="94" t="inlineStr">
+      <c r="A2" s="97" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B2" s="94" t="inlineStr">
+      <c r="B2" s="97" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -1080,22 +1060,22 @@
           <t>FLAG GALPA Costa E-R. Sostituzione del motore principale e dei motori secondari. Secondo bando</t>
         </is>
       </c>
-      <c r="D2" s="91" t="inlineStr">
+      <c r="D2" s="98" t="inlineStr">
         <is>
           <t>https://agricoltura.regione.emilia-romagna.it/feampa-2021-2027/bandi-galpa/2026/galpa-sostituzione-motori-secondo-bando</t>
         </is>
       </c>
-      <c r="E2" s="94" t="inlineStr"/>
-      <c r="F2" s="94" t="inlineStr"/>
-      <c r="G2" s="94" t="inlineStr"/>
+      <c r="E2" s="97" t="inlineStr"/>
+      <c r="F2" s="97" t="inlineStr"/>
+      <c r="G2" s="97" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="92" t="inlineStr">
+      <c r="A3" s="95" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B3" s="92" t="inlineStr">
+      <c r="B3" s="95" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1105,22 +1085,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0PRE-SEED 3.0Prossima AperturaFESR</t>
         </is>
       </c>
-      <c r="D3" s="93" t="inlineStr">
+      <c r="D3" s="96" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/pre-seed-3-0/</t>
         </is>
       </c>
-      <c r="E3" s="92" t="inlineStr"/>
-      <c r="F3" s="92" t="inlineStr"/>
-      <c r="G3" s="92" t="inlineStr"/>
+      <c r="E3" s="95" t="inlineStr"/>
+      <c r="F3" s="95" t="inlineStr"/>
+      <c r="G3" s="95" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="94" t="inlineStr">
+      <c r="A4" s="97" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B4" s="94" t="inlineStr">
+      <c r="B4" s="97" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1130,22 +1110,22 @@
           <t>ACCESSO AL CREDITO E ALLE GARANZIE PER LE IMPRESEContributo su finanziamenti alle imprese del Lazio erogati su provvista BEIProssima AperturaFESR</t>
         </is>
       </c>
-      <c r="D4" s="91" t="inlineStr">
+      <c r="D4" s="98" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-su-finanziamenti-alle-imprese-del-lazio-erogati-su-provvista-bei/</t>
         </is>
       </c>
-      <c r="E4" s="94" t="inlineStr"/>
-      <c r="F4" s="94" t="inlineStr"/>
-      <c r="G4" s="94" t="inlineStr"/>
+      <c r="E4" s="97" t="inlineStr"/>
+      <c r="F4" s="97" t="inlineStr"/>
+      <c r="G4" s="97" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="92" t="inlineStr">
+      <c r="A5" s="95" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B5" s="92" t="inlineStr">
+      <c r="B5" s="95" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1155,22 +1135,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEIndividuazione degli enti iscritti al Registro unico nazionale del Terzo settoreApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D5" s="93" t="inlineStr">
+      <c r="D5" s="96" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/individuazione-degli-enti-iscritti-al-registro-unico-nazionale-del-terzo-settore/</t>
         </is>
       </c>
-      <c r="E5" s="92" t="inlineStr"/>
-      <c r="F5" s="92" t="inlineStr"/>
-      <c r="G5" s="92" t="inlineStr"/>
+      <c r="E5" s="95" t="inlineStr"/>
+      <c r="F5" s="95" t="inlineStr"/>
+      <c r="G5" s="95" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="94" t="inlineStr">
+      <c r="A6" s="97" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B6" s="94" t="inlineStr">
+      <c r="B6" s="97" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1180,22 +1160,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Technology Transfer LazioApertoFESR</t>
         </is>
       </c>
-      <c r="D6" s="91" t="inlineStr">
+      <c r="D6" s="98" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/technology-transfer-lazio/</t>
         </is>
       </c>
-      <c r="E6" s="94" t="inlineStr"/>
-      <c r="F6" s="94" t="inlineStr"/>
-      <c r="G6" s="94" t="inlineStr"/>
+      <c r="E6" s="97" t="inlineStr"/>
+      <c r="F6" s="97" t="inlineStr"/>
+      <c r="G6" s="97" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="92" t="inlineStr">
+      <c r="A7" s="95" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B7" s="92" t="inlineStr">
+      <c r="B7" s="95" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1205,22 +1185,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Percorso di tutoraggio per le impreseApertoFESR</t>
         </is>
       </c>
-      <c r="D7" s="93" t="inlineStr">
+      <c r="D7" s="96" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/percorso-di-tutoraggio-per-le-imprese/</t>
         </is>
       </c>
-      <c r="E7" s="92" t="inlineStr"/>
-      <c r="F7" s="92" t="inlineStr"/>
-      <c r="G7" s="92" t="inlineStr"/>
+      <c r="E7" s="95" t="inlineStr"/>
+      <c r="F7" s="95" t="inlineStr"/>
+      <c r="G7" s="95" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="94" t="inlineStr">
+      <c r="A8" s="97" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B8" s="94" t="inlineStr">
+      <c r="B8" s="97" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1230,22 +1210,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per partecipare a SMAU Parigi 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D8" s="91" t="inlineStr">
+      <c r="D8" s="98" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-partecipare-a-smau-parigi-2026/</t>
         </is>
       </c>
-      <c r="E8" s="94" t="inlineStr"/>
-      <c r="F8" s="94" t="inlineStr"/>
-      <c r="G8" s="94" t="inlineStr"/>
+      <c r="E8" s="97" t="inlineStr"/>
+      <c r="F8" s="97" t="inlineStr"/>
+      <c r="G8" s="97" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="92" t="inlineStr">
+      <c r="A9" s="95" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B9" s="92" t="inlineStr">
+      <c r="B9" s="95" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1255,22 +1235,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONERiconoscimento della funzione sociale ed educativa degli oratoriApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D9" s="93" t="inlineStr">
+      <c r="D9" s="96" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/riconoscimento-della-funzione-sociale-ed-educativa-degli-oratori/</t>
         </is>
       </c>
-      <c r="E9" s="92" t="inlineStr"/>
-      <c r="F9" s="92" t="inlineStr"/>
-      <c r="G9" s="92" t="inlineStr"/>
+      <c r="E9" s="95" t="inlineStr"/>
+      <c r="F9" s="95" t="inlineStr"/>
+      <c r="G9" s="95" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="94" t="inlineStr">
+      <c r="A10" s="97" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B10" s="94" t="inlineStr">
+      <c r="B10" s="97" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1280,22 +1260,22 @@
           <t>GovernanceIscrizione nell’elenco regionale degli idonei all’esercizio dell’attività di direttore dell’Istituto JemoloApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D10" s="91" t="inlineStr">
+      <c r="D10" s="98" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/iscrizione-nellelenco-regionale-degli-idonei-allesercizio-dellattivita-di-direttore-dellistituto-jemolo/</t>
         </is>
       </c>
-      <c r="E10" s="94" t="inlineStr"/>
-      <c r="F10" s="94" t="inlineStr"/>
-      <c r="G10" s="94" t="inlineStr"/>
+      <c r="E10" s="97" t="inlineStr"/>
+      <c r="F10" s="97" t="inlineStr"/>
+      <c r="G10" s="97" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="92" t="inlineStr">
+      <c r="A11" s="95" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B11" s="92" t="inlineStr">
+      <c r="B11" s="95" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1305,22 +1285,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEVoucher per lo sport – seconda annualitàApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D11" s="93" t="inlineStr">
+      <c r="D11" s="96" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/voucher-per-lo-sport-seconda-annualita/</t>
         </is>
       </c>
-      <c r="E11" s="92" t="inlineStr"/>
-      <c r="F11" s="92" t="inlineStr"/>
-      <c r="G11" s="92" t="inlineStr"/>
+      <c r="E11" s="95" t="inlineStr"/>
+      <c r="F11" s="95" t="inlineStr"/>
+      <c r="G11" s="95" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="94" t="inlineStr">
+      <c r="A12" s="97" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B12" s="94" t="inlineStr">
+      <c r="B12" s="97" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1330,22 +1310,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEBonus occupazionale SALGOApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D12" s="91" t="inlineStr">
+      <c r="D12" s="98" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/bonus-occupazionale-salgo/</t>
         </is>
       </c>
-      <c r="E12" s="94" t="inlineStr"/>
-      <c r="F12" s="94" t="inlineStr"/>
-      <c r="G12" s="94" t="inlineStr"/>
+      <c r="E12" s="97" t="inlineStr"/>
+      <c r="F12" s="97" t="inlineStr"/>
+      <c r="G12" s="97" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="92" t="inlineStr">
+      <c r="A13" s="95" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B13" s="92" t="inlineStr">
+      <c r="B13" s="95" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1355,22 +1335,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEContributo di Libertà per le donne che hanno subito violenzaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D13" s="93" t="inlineStr">
+      <c r="D13" s="96" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-di-liberta-per-le-donne-che-hanno-subito-violenza/</t>
         </is>
       </c>
-      <c r="E13" s="92" t="inlineStr"/>
-      <c r="F13" s="92" t="inlineStr"/>
-      <c r="G13" s="92" t="inlineStr"/>
+      <c r="E13" s="95" t="inlineStr"/>
+      <c r="F13" s="95" t="inlineStr"/>
+      <c r="G13" s="95" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="94" t="inlineStr">
+      <c r="A14" s="97" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B14" s="94" t="inlineStr">
+      <c r="B14" s="97" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1380,22 +1360,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURAInterventi straordinari di valorizzazione del patrimonio culturale del LazioApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D14" s="91" t="inlineStr">
+      <c r="D14" s="98" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/interventi-straordinari-di-valorizzazione-del-patrimonio-culturale-del-lazio/</t>
         </is>
       </c>
-      <c r="E14" s="94" t="inlineStr"/>
-      <c r="F14" s="94" t="inlineStr"/>
-      <c r="G14" s="94" t="inlineStr"/>
+      <c r="E14" s="97" t="inlineStr"/>
+      <c r="F14" s="97" t="inlineStr"/>
+      <c r="G14" s="97" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="92" t="inlineStr">
+      <c r="A15" s="95" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B15" s="92" t="inlineStr">
+      <c r="B15" s="95" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1405,30 +1385,30 @@
           <t>Bandi di garaBANDO ATTUAZIONE Ob. 1.1 Azione 1 codice 111102 _DIV - "SOSTEGNO ALLA DIVERSIFICAZIONE E NUOVE FORME DI REDDITO PER LA PICCOLA PESCA COST</t>
         </is>
       </c>
-      <c r="D15" s="93" t="inlineStr">
+      <c r="D15" s="96" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/bando-avviso-regia-ob-11-azione-1-codice-111102-div-sostegno-alla-diversificazione-nuove-forme-reddito-piccola-pesca-costiera</t>
         </is>
       </c>
-      <c r="E15" s="92" t="inlineStr">
+      <c r="E15" s="95" t="inlineStr">
         <is>
           <t>07/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F15" s="92" t="inlineStr">
+      <c r="F15" s="95" t="inlineStr">
         <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="G15" s="92" t="inlineStr"/>
+      <c r="G15" s="95" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="94" t="inlineStr">
+      <c r="A16" s="97" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B16" s="94" t="inlineStr">
+      <c r="B16" s="97" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1438,30 +1418,30 @@
           <t>Avvisi pubblici09 marzo 2026 - ST SIRACUSA - AVVISO PUBBLICO PER LA COSTITUZIONE DI ELENCHI DI OPERATORI ECONOMICI PER L’ACQUISIZIONE DI BENI E SERVIZ</t>
         </is>
       </c>
-      <c r="D16" s="91" t="inlineStr">
+      <c r="D16" s="98" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/09-marzo-2026-st-siracusa-avviso-pubblico-costituzione-elenchi-operatori-economici-l-acquisizione-beni-servizi</t>
         </is>
       </c>
-      <c r="E16" s="94" t="inlineStr">
+      <c r="E16" s="97" t="inlineStr">
         <is>
           <t>31/12/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F16" s="94" t="inlineStr">
+      <c r="F16" s="97" t="inlineStr">
         <is>
           <t>31/12/2026</t>
         </is>
       </c>
-      <c r="G16" s="94" t="inlineStr"/>
+      <c r="G16" s="97" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="92" t="inlineStr">
+      <c r="A17" s="95" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B17" s="92" t="inlineStr">
+      <c r="B17" s="95" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1471,30 +1451,30 @@
           <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScade il:19/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D17" s="93" t="inlineStr">
+      <c r="D17" s="96" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
         </is>
       </c>
-      <c r="E17" s="92" t="inlineStr">
+      <c r="E17" s="95" t="inlineStr">
         <is>
           <t>19/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F17" s="92" t="inlineStr">
+      <c r="F17" s="95" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G17" s="92" t="inlineStr"/>
+      <c r="G17" s="95" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="94" t="inlineStr">
+      <c r="A18" s="97" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B18" s="94" t="inlineStr">
+      <c r="B18" s="97" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1504,22 +1484,22 @@
           <t>Manifestazioni di interesseAvviso Manifestazione Interesse DISTRIBUTORI AUTOMATICI di bevande e snackScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D18" s="91" t="inlineStr">
+      <c r="D18" s="98" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-distributori-automatici-bevande-snack</t>
         </is>
       </c>
-      <c r="E18" s="94" t="inlineStr"/>
-      <c r="F18" s="94" t="inlineStr"/>
-      <c r="G18" s="94" t="inlineStr"/>
+      <c r="E18" s="97" t="inlineStr"/>
+      <c r="F18" s="97" t="inlineStr"/>
+      <c r="G18" s="97" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="92" t="inlineStr">
+      <c r="A19" s="95" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B19" s="92" t="inlineStr">
+      <c r="B19" s="95" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1529,30 +1509,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D19" s="93" t="inlineStr">
+      <c r="D19" s="96" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo</t>
         </is>
       </c>
-      <c r="E19" s="92" t="inlineStr">
+      <c r="E19" s="95" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F19" s="92" t="inlineStr">
+      <c r="F19" s="95" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G19" s="92" t="inlineStr"/>
+      <c r="G19" s="95" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="94" t="inlineStr">
+      <c r="A20" s="97" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B20" s="94" t="inlineStr">
+      <c r="B20" s="97" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1562,30 +1542,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D20" s="91" t="inlineStr">
+      <c r="D20" s="98" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo-0</t>
         </is>
       </c>
-      <c r="E20" s="94" t="inlineStr">
+      <c r="E20" s="97" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F20" s="94" t="inlineStr">
+      <c r="F20" s="97" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G20" s="94" t="inlineStr"/>
+      <c r="G20" s="97" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="92" t="inlineStr">
+      <c r="A21" s="95" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B21" s="92" t="inlineStr">
+      <c r="B21" s="95" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1595,22 +1575,22 @@
           <t>Manifestazioni di interesseST SIRACUSA - AVVISO DI MANIFESTAZIONE DI INTERESSE - Fornitura applicativo extracontabile per la gestione progetti, ecc. e</t>
         </is>
       </c>
-      <c r="D21" s="93" t="inlineStr">
+      <c r="D21" s="96" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-siracusa-avviso-manifestazione-interesse-fornitura-applicativo-extracontabile-gestione-progetti-ecc-applicativo-gestione-ed-elaborazione-informatizzata-paghe</t>
         </is>
       </c>
-      <c r="E21" s="92" t="inlineStr"/>
-      <c r="F21" s="92" t="inlineStr"/>
-      <c r="G21" s="92" t="inlineStr"/>
+      <c r="E21" s="95" t="inlineStr"/>
+      <c r="F21" s="95" t="inlineStr"/>
+      <c r="G21" s="95" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="94" t="inlineStr">
+      <c r="A22" s="97" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B22" s="94" t="inlineStr">
+      <c r="B22" s="97" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1620,30 +1600,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile sito nel Comune di Capo D'Orlando, Via Trazzera MarinaScade il:25/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D22" s="91" t="inlineStr">
+      <c r="D22" s="98" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-sito-nel-comune-capo-d-orlando-trazzera-marina</t>
         </is>
       </c>
-      <c r="E22" s="94" t="inlineStr">
+      <c r="E22" s="97" t="inlineStr">
         <is>
           <t>25/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F22" s="94" t="inlineStr">
+      <c r="F22" s="97" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="G22" s="94" t="inlineStr"/>
+      <c r="G22" s="97" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="92" t="inlineStr">
+      <c r="A23" s="95" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B23" s="92" t="inlineStr">
+      <c r="B23" s="95" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1653,22 +1633,22 @@
           <t xml:space="preserve">Avvisi pubbliciST CATANIA - Programma Regionale FESR Sicilia 2021-2027 - Azione 2.4.4 - “Interventi per la riduzione del rischio incendi” - AVVISO DI </t>
         </is>
       </c>
-      <c r="D23" s="93" t="inlineStr">
+      <c r="D23" s="96" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-catania-programma-regionale-fesr-sicilia-2021-2027-azione-244-interventi-riduzione-rischio-incendi-avviso-indagine-mercato</t>
         </is>
       </c>
-      <c r="E23" s="92" t="inlineStr"/>
-      <c r="F23" s="92" t="inlineStr"/>
-      <c r="G23" s="92" t="inlineStr"/>
+      <c r="E23" s="95" t="inlineStr"/>
+      <c r="F23" s="95" t="inlineStr"/>
+      <c r="G23" s="95" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="94" t="inlineStr">
+      <c r="A24" s="97" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B24" s="94" t="inlineStr">
+      <c r="B24" s="97" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1678,22 +1658,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per ROMICS – Primavera 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D24" s="91" t="inlineStr">
+      <c r="D24" s="98" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-romics-primavera-2026/</t>
         </is>
       </c>
-      <c r="E24" s="94" t="inlineStr"/>
-      <c r="F24" s="94" t="inlineStr"/>
-      <c r="G24" s="94" t="inlineStr"/>
+      <c r="E24" s="97" t="inlineStr"/>
+      <c r="F24" s="97" t="inlineStr"/>
+      <c r="G24" s="97" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="92" t="inlineStr">
+      <c r="A25" s="95" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B25" s="92" t="inlineStr">
+      <c r="B25" s="95" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1703,22 +1683,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Cinema International 2026 – I edizioneApertoFESR</t>
         </is>
       </c>
-      <c r="D25" s="93" t="inlineStr">
+      <c r="D25" s="96" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lazio-cinema-international-2026-i-edizione/</t>
         </is>
       </c>
-      <c r="E25" s="92" t="inlineStr"/>
-      <c r="F25" s="92" t="inlineStr"/>
-      <c r="G25" s="92" t="inlineStr"/>
+      <c r="E25" s="95" t="inlineStr"/>
+      <c r="F25" s="95" t="inlineStr"/>
+      <c r="G25" s="95" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="94" t="inlineStr">
+      <c r="A26" s="97" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B26" s="94" t="inlineStr">
+      <c r="B26" s="97" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1728,22 +1708,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEManifestazioni di interesse alla costituzione di due nuove Fondazioni I.T.S. AcademyApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D26" s="91" t="inlineStr">
+      <c r="D26" s="98" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazioni-di-interesse-alla-costituzione-di-due-nuove-fondazioni-i-t-s-academy/</t>
         </is>
       </c>
-      <c r="E26" s="94" t="inlineStr"/>
-      <c r="F26" s="94" t="inlineStr"/>
-      <c r="G26" s="94" t="inlineStr"/>
+      <c r="E26" s="97" t="inlineStr"/>
+      <c r="F26" s="97" t="inlineStr"/>
+      <c r="G26" s="97" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="92" t="inlineStr">
+      <c r="A27" s="95" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B27" s="92" t="inlineStr">
+      <c r="B27" s="95" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1753,22 +1733,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURAContributi per sostenere la ripresa del settore della pescaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D27" s="93" t="inlineStr">
+      <c r="D27" s="96" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributi-per-sostenere-la-ripresa-del-settore-della-pesca/</t>
         </is>
       </c>
-      <c r="E27" s="92" t="inlineStr"/>
-      <c r="F27" s="92" t="inlineStr"/>
-      <c r="G27" s="92" t="inlineStr"/>
+      <c r="E27" s="95" t="inlineStr"/>
+      <c r="F27" s="95" t="inlineStr"/>
+      <c r="G27" s="95" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="94" t="inlineStr">
+      <c r="A28" s="97" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B28" s="94" t="inlineStr">
+      <c r="B28" s="97" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1778,30 +1758,30 @@
           <t>Manifestazioni di interesseAVVISO - Manifestazione Interesse “Storytelling aziendale” Expo Wild Natura - Caccia - Pesca. Misterbianco (CT), 10-12 apri</t>
         </is>
       </c>
-      <c r="D28" s="91" t="inlineStr">
+      <c r="D28" s="98" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-storytelling-aziendale-expo-wild-natura-caccia-pesca-misterbianco-ct-10-12-aprile-2026</t>
         </is>
       </c>
-      <c r="E28" s="94" t="inlineStr">
+      <c r="E28" s="97" t="inlineStr">
         <is>
           <t>30/03/2026 - 13:00</t>
         </is>
       </c>
-      <c r="F28" s="94" t="inlineStr">
+      <c r="F28" s="97" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G28" s="94" t="inlineStr"/>
+      <c r="G28" s="97" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="92" t="inlineStr">
+      <c r="A29" s="95" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B29" s="92" t="inlineStr">
+      <c r="B29" s="95" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1811,30 +1791,30 @@
           <t>Manifestazioni di interesseInvaso Lentini - Interventi di ripristino delle pareti esterne in cls della Torre di presa Sud e della trave d’appoggio del</t>
         </is>
       </c>
-      <c r="D29" s="93" t="inlineStr">
+      <c r="D29" s="96" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/invaso-lentini-interventi-ripristino-pareti-esterne-cls-torre-presa-sud-trave-d-appoggio-cavalcavia-collegamento-alla-stessa-torre</t>
         </is>
       </c>
-      <c r="E29" s="92" t="inlineStr">
+      <c r="E29" s="95" t="inlineStr">
         <is>
           <t>19/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F29" s="92" t="inlineStr">
+      <c r="F29" s="95" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G29" s="92" t="inlineStr"/>
+      <c r="G29" s="95" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="94" t="inlineStr">
+      <c r="A30" s="97" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="B30" s="94" t="inlineStr">
+      <c r="B30" s="97" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1844,22 +1824,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURARistrutturazione e riconversione vigneti – campagna 2026-2027ApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D30" s="91" t="inlineStr">
+      <c r="D30" s="98" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/ristrutturazione-e-riconversione-vigneti-campagna-2026-2027/</t>
         </is>
       </c>
-      <c r="E30" s="94" t="inlineStr"/>
-      <c r="F30" s="94" t="inlineStr"/>
-      <c r="G30" s="94" t="inlineStr"/>
+      <c r="E30" s="97" t="inlineStr"/>
+      <c r="F30" s="97" t="inlineStr"/>
+      <c r="G30" s="97" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="92" t="inlineStr">
+      <c r="A31" s="95" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="B31" s="92" t="inlineStr">
+      <c r="B31" s="95" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1869,30 +1849,30 @@
           <t>Manifestazioni di interessePR FESR 2021/27 Azione 1.3.3 e del POC 2014/20 - Azione 1.3.1  - Avviso a manifestazione d’interesse eventi fieristici inte</t>
         </is>
       </c>
-      <c r="D31" s="93" t="inlineStr">
+      <c r="D31" s="96" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-d-interesse-eventi-fieristici-internazionali-marzo-dicembre-2026</t>
         </is>
       </c>
-      <c r="E31" s="92" t="inlineStr">
+      <c r="E31" s="95" t="inlineStr">
         <is>
           <t>30/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F31" s="92" t="inlineStr">
+      <c r="F31" s="95" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="G31" s="92" t="inlineStr"/>
+      <c r="G31" s="95" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="94" t="inlineStr">
+      <c r="A32" s="97" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="B32" s="94" t="inlineStr">
+      <c r="B32" s="97" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1902,22 +1882,22 @@
           <t>INTERNAZIONALIZZAZIONEL’Ecosistema dell’Innovazione a INNOVIT – Focus S3ApertoFESR</t>
         </is>
       </c>
-      <c r="D32" s="91" t="inlineStr">
+      <c r="D32" s="98" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lecosistema-dellinnovazione-a-innovit-focus-s3/</t>
         </is>
       </c>
-      <c r="E32" s="94" t="inlineStr"/>
-      <c r="F32" s="94" t="inlineStr"/>
-      <c r="G32" s="94" t="inlineStr"/>
+      <c r="E32" s="97" t="inlineStr"/>
+      <c r="F32" s="97" t="inlineStr"/>
+      <c r="G32" s="97" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="92" t="inlineStr">
+      <c r="A33" s="95" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="B33" s="92" t="inlineStr">
+      <c r="B33" s="95" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1927,22 +1907,22 @@
           <t>Manifestazioni di interessePR FESR SICILIA 2021/27 - NUOVO Avviso a manifestazione d’interesse per esperti valutatoriScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D33" s="93" t="inlineStr">
+      <c r="D33" s="96" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/pr-fesr-sicilia-202127-nuovo-avviso-manifestazione-d-interesse-esperti-valutatori</t>
         </is>
       </c>
-      <c r="E33" s="92" t="inlineStr"/>
-      <c r="F33" s="92" t="inlineStr"/>
-      <c r="G33" s="92" t="inlineStr"/>
+      <c r="E33" s="95" t="inlineStr"/>
+      <c r="F33" s="95" t="inlineStr"/>
+      <c r="G33" s="95" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="94" t="inlineStr">
+      <c r="A34" s="97" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="B34" s="94" t="inlineStr">
+      <c r="B34" s="97" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -1952,22 +1932,22 @@
           <t>Bando 2026 per contributi dedicati alla manutenzione della rete dei percorsi escursionistici</t>
         </is>
       </c>
-      <c r="D34" s="91" t="inlineStr">
+      <c r="D34" s="98" t="inlineStr">
         <is>
           <t>https://ambiente.regione.emilia-romagna.it/it/parchi-natura2000/bandi/bando-2026-per-contributi-dedicati-alla-manutenzione-della-rete-dei-percorsi-escursionistici</t>
         </is>
       </c>
-      <c r="E34" s="94" t="inlineStr"/>
-      <c r="F34" s="94" t="inlineStr"/>
-      <c r="G34" s="94" t="inlineStr"/>
+      <c r="E34" s="97" t="inlineStr"/>
+      <c r="F34" s="97" t="inlineStr"/>
+      <c r="G34" s="97" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="92" t="inlineStr">
+      <c r="A35" s="95" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="B35" s="92" t="inlineStr">
+      <c r="B35" s="95" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1977,22 +1957,22 @@
           <t>Programma regionale in favore delle tradizioni storiche, artistiche, religiose e popolari (2026) – manifestazioni d’interesseApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D35" s="93" t="inlineStr">
+      <c r="D35" s="96" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/programma-regionale-in-favore-delle-tradizioni-storiche-artistiche-religiose-e-popolari-2026-manifestazioni-dinteresse/</t>
         </is>
       </c>
-      <c r="E35" s="92" t="inlineStr"/>
-      <c r="F35" s="92" t="inlineStr"/>
-      <c r="G35" s="92" t="inlineStr"/>
+      <c r="E35" s="95" t="inlineStr"/>
+      <c r="F35" s="95" t="inlineStr"/>
+      <c r="G35" s="95" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="94" t="inlineStr">
+      <c r="A36" s="97" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B36" s="94" t="inlineStr">
+      <c r="B36" s="97" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2002,22 +1982,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEBuoni servizio per le persone non autosufficienti nel territorio del LazioProssima AperturaFSE / FSE+</t>
         </is>
       </c>
-      <c r="D36" s="91" t="inlineStr">
+      <c r="D36" s="98" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/buoni-servizio-per-le-persone-non-autosufficienti-nel-territorio-del-lazio/</t>
         </is>
       </c>
-      <c r="E36" s="94" t="inlineStr"/>
-      <c r="F36" s="94" t="inlineStr"/>
-      <c r="G36" s="94" t="inlineStr"/>
+      <c r="E36" s="97" t="inlineStr"/>
+      <c r="F36" s="97" t="inlineStr"/>
+      <c r="G36" s="97" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="92" t="inlineStr">
+      <c r="A37" s="95" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B37" s="92" t="inlineStr">
+      <c r="B37" s="95" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2027,22 +2007,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONERimborso delle rette dei servizi educativi nel territorio del LazioProssima AperturaFSE / FSE+</t>
         </is>
       </c>
-      <c r="D37" s="93" t="inlineStr">
+      <c r="D37" s="96" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/rimborso-delle-rette-dei-servizi-educativi-nel-territorio-del-lazio/</t>
         </is>
       </c>
-      <c r="E37" s="92" t="inlineStr"/>
-      <c r="F37" s="92" t="inlineStr"/>
-      <c r="G37" s="92" t="inlineStr"/>
+      <c r="E37" s="95" t="inlineStr"/>
+      <c r="F37" s="95" t="inlineStr"/>
+      <c r="G37" s="95" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="94" t="inlineStr">
+      <c r="A38" s="97" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B38" s="94" t="inlineStr">
+      <c r="B38" s="97" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2052,30 +2032,30 @@
           <t>Manifestazioni di interesseATTO DI INTERPELLO PER L’AFFIDAMENTO DELL’INCARICO DI COLLAUDO STATICO DELLE STRUTTURE - Diga di Pietrarossa (Progetto ex C</t>
         </is>
       </c>
-      <c r="D38" s="91" t="inlineStr">
+      <c r="D38" s="98" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/atto-interpello-l-affidamento-incarico-collaudo-statico-strutture-diga-pietrarossa-progetto-ex-casmez-303219</t>
         </is>
       </c>
-      <c r="E38" s="94" t="inlineStr">
+      <c r="E38" s="97" t="inlineStr">
         <is>
           <t>27/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F38" s="94" t="inlineStr">
+      <c r="F38" s="97" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="G38" s="94" t="inlineStr"/>
+      <c r="G38" s="97" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="92" t="inlineStr">
+      <c r="A39" s="95" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B39" s="92" t="inlineStr">
+      <c r="B39" s="95" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2085,30 +2065,30 @@
           <t>Manifestazioni di interesseAvviso alle Case  Editrici della Regione siciliana per la partecipazione al Salone del Libro di Torino, 14-18  maggio 2026.</t>
         </is>
       </c>
-      <c r="D39" s="93" t="inlineStr">
+      <c r="D39" s="96" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/manifestazione-d-interesse-partecipare-al-xxxviii-salone-libro-torino-14-al-18-maggio-2026-attraverso-l-esposizione-pubblicazioni-presso-stand-assessorato-beni</t>
         </is>
       </c>
-      <c r="E39" s="92" t="inlineStr">
+      <c r="E39" s="95" t="inlineStr">
         <is>
           <t>30/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F39" s="92" t="inlineStr">
+      <c r="F39" s="95" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="G39" s="92" t="inlineStr"/>
+      <c r="G39" s="95" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="94" t="inlineStr">
+      <c r="A40" s="97" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B40" s="94" t="inlineStr">
+      <c r="B40" s="97" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2118,30 +2098,30 @@
           <t xml:space="preserve">Manifestazioni di interessePR FESR SICILIA 2021/27 - NUOVO Avviso a manifestazione d’interesse per esperti valutatoriScade il:06/04/2026 - 23:59Leggi </t>
         </is>
       </c>
-      <c r="D40" s="91" t="inlineStr">
+      <c r="D40" s="98" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/pr-fesr-sicilia-202127-nuovo-avviso-manifestazione-d-interesse-esperti-valutatori</t>
         </is>
       </c>
-      <c r="E40" s="94" t="inlineStr">
+      <c r="E40" s="97" t="inlineStr">
         <is>
           <t>06/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F40" s="94" t="inlineStr">
+      <c r="F40" s="97" t="inlineStr">
         <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="G40" s="94" t="inlineStr"/>
+      <c r="G40" s="97" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="92" t="inlineStr">
+      <c r="A41" s="95" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B41" s="92" t="inlineStr">
+      <c r="B41" s="95" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2151,22 +2131,22 @@
           <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D41" s="93" t="inlineStr">
+      <c r="D41" s="96" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
         </is>
       </c>
-      <c r="E41" s="92" t="inlineStr"/>
-      <c r="F41" s="92" t="inlineStr"/>
-      <c r="G41" s="92" t="inlineStr"/>
+      <c r="E41" s="95" t="inlineStr"/>
+      <c r="F41" s="95" t="inlineStr"/>
+      <c r="G41" s="95" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="94" t="inlineStr">
+      <c r="A42" s="97" t="inlineStr">
         <is>
           <t>24/03/2026</t>
         </is>
       </c>
-      <c r="B42" s="94" t="inlineStr">
+      <c r="B42" s="97" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2176,22 +2156,22 @@
           <t>GAL del Ducato - Promozione di fiere agroalimentari e delle filiere del cibo – Bando per Enti pubblici (DU AS 05B)</t>
         </is>
       </c>
-      <c r="D42" s="91" t="inlineStr">
+      <c r="D42" s="98" t="inlineStr">
         <is>
           <t>https://agricoltura.regione.emilia-romagna.it/sviluppo-rurale-23-27/opportunita/bandi-gal/2026/du_as05b-promozione-di-fiere-agroalimentari-e-delle-filiere-del-cibo-bando-per-enti-pubblici</t>
         </is>
       </c>
-      <c r="E42" s="94" t="inlineStr"/>
-      <c r="F42" s="94" t="inlineStr"/>
-      <c r="G42" s="94" t="inlineStr"/>
+      <c r="E42" s="97" t="inlineStr"/>
+      <c r="F42" s="97" t="inlineStr"/>
+      <c r="G42" s="97" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="92" t="inlineStr">
+      <c r="A43" s="95" t="inlineStr">
         <is>
           <t>24/03/2026</t>
         </is>
       </c>
-      <c r="B43" s="92" t="inlineStr">
+      <c r="B43" s="95" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2201,30 +2181,30 @@
           <t>Manifestazioni di interesseAVVISO PUBBLICO PER MANIFESTAZIONE DI INTERESSE FINALIZZATA ALL'ASSEGNAZIONE DI SPAZI ESPOSITIVI (CORNER GRATUITI) ALL'INTE</t>
         </is>
       </c>
-      <c r="D43" s="93" t="inlineStr">
+      <c r="D43" s="96" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-manifestazione-interesse-finalizzata-all-assegnazione-spazi-espositivi-corner-gratuiti-all-interno-stand-istituzionale-dsrt-manifestazione</t>
         </is>
       </c>
-      <c r="E43" s="92" t="inlineStr">
+      <c r="E43" s="95" t="inlineStr">
         <is>
           <t>30/03/2026 - 13:00</t>
         </is>
       </c>
-      <c r="F43" s="92" t="inlineStr">
+      <c r="F43" s="95" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G43" s="92" t="inlineStr"/>
+      <c r="G43" s="95" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="94" t="inlineStr">
+      <c r="A44" s="97" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B44" s="94" t="inlineStr">
+      <c r="B44" s="97" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2234,22 +2214,22 @@
           <t>Avviso per la concessione di contributi per eventi sportivi realizzati in Emilia-Romagna - Anno 2026</t>
         </is>
       </c>
-      <c r="D44" s="91" t="inlineStr">
+      <c r="D44" s="98" t="inlineStr">
         <is>
           <t>https://www.regione.emilia-romagna.it/sport/bandi/2026/bando-2026</t>
         </is>
       </c>
-      <c r="E44" s="94" t="inlineStr"/>
-      <c r="F44" s="94" t="inlineStr"/>
-      <c r="G44" s="94" t="inlineStr"/>
+      <c r="E44" s="97" t="inlineStr"/>
+      <c r="F44" s="97" t="inlineStr"/>
+      <c r="G44" s="97" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="92" t="inlineStr">
+      <c r="A45" s="95" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B45" s="92" t="inlineStr">
+      <c r="B45" s="95" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2259,22 +2239,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Street art 2026Prossima AperturaBandi Regionali</t>
         </is>
       </c>
-      <c r="D45" s="93" t="inlineStr">
+      <c r="D45" s="96" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lazio-street-art-2026/</t>
         </is>
       </c>
-      <c r="E45" s="92" t="inlineStr"/>
-      <c r="F45" s="92" t="inlineStr"/>
-      <c r="G45" s="92" t="inlineStr"/>
+      <c r="E45" s="95" t="inlineStr"/>
+      <c r="F45" s="95" t="inlineStr"/>
+      <c r="G45" s="95" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="94" t="inlineStr">
+      <c r="A46" s="97" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B46" s="94" t="inlineStr">
+      <c r="B46" s="97" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2284,30 +2264,30 @@
           <t>Manifestazioni di interesseManifestazione di interesse per la partecipazione all’evento “R2I Italy 2026” – Bologna, 12-13/05/2026Scade il:03/04/2026 -</t>
         </is>
       </c>
-      <c r="D46" s="91" t="inlineStr">
+      <c r="D46" s="98" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/manifestazione-interesse-partecipazione-all-evento-r2i-italy-2026-bologna-12-13052026</t>
         </is>
       </c>
-      <c r="E46" s="94" t="inlineStr">
+      <c r="E46" s="97" t="inlineStr">
         <is>
           <t>03/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F46" s="94" t="inlineStr">
+      <c r="F46" s="97" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="G46" s="94" t="inlineStr"/>
+      <c r="G46" s="97" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="92" t="inlineStr">
+      <c r="A47" s="95" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B47" s="92" t="inlineStr">
+      <c r="B47" s="95" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2317,30 +2297,30 @@
           <t>Manifestazioni di interesseST SIRACUSA - AVVISO PER MANIFESTAZIONE DI INTERESSE - Selezione di n. 5 unità di personale internoScade il:20/04/2026 - 12</t>
         </is>
       </c>
-      <c r="D47" s="93" t="inlineStr">
+      <c r="D47" s="96" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/24-marzo-2026-st-siracusa-avviso-manifestazione-interesse-selezione-n-5-unita-personale-interno</t>
         </is>
       </c>
-      <c r="E47" s="92" t="inlineStr">
+      <c r="E47" s="95" t="inlineStr">
         <is>
           <t>20/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F47" s="92" t="inlineStr">
+      <c r="F47" s="95" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="G47" s="92" t="inlineStr"/>
+      <c r="G47" s="95" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="94" t="inlineStr">
+      <c r="A48" s="97" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B48" s="94" t="inlineStr">
+      <c r="B48" s="97" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2350,30 +2330,30 @@
           <t>Avvisi pubbliciRevoca dell’avviso di concessione a titolo gratuito del 16.12.2025 inerente all’immobile di seguito identificato e contestuale nuovo av</t>
         </is>
       </c>
-      <c r="D48" s="91" t="inlineStr">
+      <c r="D48" s="98" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/revoca-avviso-concessione-titolo-gratuito-16122025-inerente-all-immobile-seguito-identificato-contestuale-nuovo-avviso-concessione-titolo-oneroso-stesso-sito-nel</t>
         </is>
       </c>
-      <c r="E48" s="94" t="inlineStr">
+      <c r="E48" s="97" t="inlineStr">
         <is>
           <t>08/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F48" s="94" t="inlineStr">
+      <c r="F48" s="97" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="G48" s="94" t="inlineStr"/>
+      <c r="G48" s="97" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="92" t="inlineStr">
+      <c r="A49" s="95" t="inlineStr">
         <is>
           <t>26/03/2026</t>
         </is>
       </c>
-      <c r="B49" s="92" t="inlineStr">
+      <c r="B49" s="95" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2383,22 +2363,22 @@
           <t>Bando studi di fattibilità per fusioni di Comuni</t>
         </is>
       </c>
-      <c r="D49" s="93" t="inlineStr">
+      <c r="D49" s="96" t="inlineStr">
         <is>
           <t>https://www.regione.emilia-romagna.it/autonomie-locali/bandi/bando_studi_fattibilita_fusioni_comuni</t>
         </is>
       </c>
-      <c r="E49" s="92" t="inlineStr"/>
-      <c r="F49" s="92" t="inlineStr"/>
-      <c r="G49" s="92" t="inlineStr"/>
+      <c r="E49" s="95" t="inlineStr"/>
+      <c r="F49" s="95" t="inlineStr"/>
+      <c r="G49" s="95" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="94" t="inlineStr">
+      <c r="A50" s="97" t="inlineStr">
         <is>
           <t>26/03/2026</t>
         </is>
       </c>
-      <c r="B50" s="94" t="inlineStr">
+      <c r="B50" s="97" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2408,30 +2388,30 @@
           <t xml:space="preserve">Manifestazioni di interesseAvviso pubblico di selezione interna, per titoli, per il conferimento di PO e professionali, ai sensi degli artt. 19, 20 e </t>
         </is>
       </c>
-      <c r="D50" s="91" t="inlineStr">
+      <c r="D50" s="98" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-selezione-interna-titoli-conferimento-po-professionali-ai-sensi-artt-19-20-21-ccrl-20222024-comparto-non-dirigenziale</t>
         </is>
       </c>
-      <c r="E50" s="94" t="inlineStr">
+      <c r="E50" s="97" t="inlineStr">
         <is>
           <t>30/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F50" s="94" t="inlineStr">
+      <c r="F50" s="97" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G50" s="94" t="inlineStr"/>
+      <c r="G50" s="97" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="92" t="inlineStr">
+      <c r="A51" s="95" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="B51" s="92" t="inlineStr">
+      <c r="B51" s="95" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2441,22 +2421,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0PRE-SEED 3.0ApertoFESR</t>
         </is>
       </c>
-      <c r="D51" s="93" t="inlineStr">
+      <c r="D51" s="96" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/pre-seed-3-0/</t>
         </is>
       </c>
-      <c r="E51" s="92" t="inlineStr"/>
-      <c r="F51" s="92" t="inlineStr"/>
-      <c r="G51" s="92" t="inlineStr"/>
+      <c r="E51" s="95" t="inlineStr"/>
+      <c r="F51" s="95" t="inlineStr"/>
+      <c r="G51" s="95" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="94" t="inlineStr">
+      <c r="A52" s="97" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B52" s="94" t="inlineStr">
+      <c r="B52" s="97" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2466,30 +2446,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “So</t>
         </is>
       </c>
-      <c r="D52" s="91" t="inlineStr">
+      <c r="D52" s="98" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-termini-imerese-locta-piazza-marina</t>
         </is>
       </c>
-      <c r="E52" s="94" t="inlineStr">
+      <c r="E52" s="97" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F52" s="94" t="inlineStr">
+      <c r="F52" s="97" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G52" s="94" t="inlineStr"/>
+      <c r="G52" s="97" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="92" t="inlineStr">
+      <c r="A53" s="95" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B53" s="92" t="inlineStr">
+      <c r="B53" s="95" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2499,30 +2479,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, Sig</t>
         </is>
       </c>
-      <c r="D53" s="93" t="inlineStr">
+      <c r="D53" s="96" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-porto-empedocle-locta-punta-piccola</t>
         </is>
       </c>
-      <c r="E53" s="92" t="inlineStr">
+      <c r="E53" s="95" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F53" s="92" t="inlineStr">
+      <c r="F53" s="95" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G53" s="92" t="inlineStr"/>
+      <c r="G53" s="95" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="94" t="inlineStr">
+      <c r="A54" s="97" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B54" s="94" t="inlineStr">
+      <c r="B54" s="97" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2532,30 +2512,30 @@
           <t xml:space="preserve">Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “Società </t>
         </is>
       </c>
-      <c r="D54" s="91" t="inlineStr">
+      <c r="D54" s="98" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-messina-locta-torrente-bordonaro</t>
         </is>
       </c>
-      <c r="E54" s="94" t="inlineStr">
+      <c r="E54" s="97" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F54" s="94" t="inlineStr">
+      <c r="F54" s="97" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G54" s="94" t="inlineStr"/>
+      <c r="G54" s="97" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="92" t="inlineStr">
+      <c r="A55" s="95" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B55" s="92" t="inlineStr">
+      <c r="B55" s="95" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2565,30 +2545,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “Condomin</t>
         </is>
       </c>
-      <c r="D55" s="93" t="inlineStr">
+      <c r="D55" s="96" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-mascali-spiaggia-n-144150</t>
         </is>
       </c>
-      <c r="E55" s="92" t="inlineStr">
+      <c r="E55" s="95" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F55" s="92" t="inlineStr">
+      <c r="F55" s="95" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G55" s="92" t="inlineStr"/>
+      <c r="G55" s="95" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="94" t="inlineStr">
+      <c r="A56" s="97" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B56" s="94" t="inlineStr">
+      <c r="B56" s="97" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2598,30 +2578,30 @@
           <t xml:space="preserve">Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione sito nel Comune di Lipari, isola di Stromboli, </t>
         </is>
       </c>
-      <c r="D56" s="91" t="inlineStr">
+      <c r="D56" s="98" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-lipari-isola-stromboli-locta-fico-grande</t>
         </is>
       </c>
-      <c r="E56" s="94" t="inlineStr">
+      <c r="E56" s="97" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F56" s="94" t="inlineStr">
+      <c r="F56" s="97" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G56" s="94" t="inlineStr"/>
+      <c r="G56" s="97" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="92" t="inlineStr">
+      <c r="A57" s="95" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B57" s="92" t="inlineStr">
+      <c r="B57" s="95" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2631,30 +2611,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione sito nel Comune di Favignana, isola di Le</t>
         </is>
       </c>
-      <c r="D57" s="93" t="inlineStr">
+      <c r="D57" s="96" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-favignana-isola-levanzo</t>
         </is>
       </c>
-      <c r="E57" s="92" t="inlineStr">
+      <c r="E57" s="95" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F57" s="92" t="inlineStr">
+      <c r="F57" s="95" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G57" s="92" t="inlineStr"/>
+      <c r="G57" s="95" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="94" t="inlineStr">
+      <c r="A58" s="97" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="B58" s="94" t="inlineStr">
+      <c r="B58" s="97" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2664,30 +2644,30 @@
           <t>Manifestazioni di interesseAVVISO - Manifestazione d’interesse finalizzata alla selezione di organismi attuatori di piani di gestione locale della pic</t>
         </is>
       </c>
-      <c r="D58" s="91" t="inlineStr">
+      <c r="D58" s="98" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-d-interesse-finalizzata-alla-selezione-organismi-attuatori-piani-gestione-locale-piccola-pesca-costiera-nelle-gsa-regione-siciliana</t>
         </is>
       </c>
-      <c r="E58" s="94" t="inlineStr">
+      <c r="E58" s="97" t="inlineStr">
         <is>
           <t>29/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F58" s="94" t="inlineStr">
+      <c r="F58" s="97" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="G58" s="94" t="inlineStr"/>
+      <c r="G58" s="97" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="92" t="inlineStr">
+      <c r="A59" s="95" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="B59" s="92" t="inlineStr">
+      <c r="B59" s="95" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2697,30 +2677,30 @@
           <t>Avvisi pubbliciLeggi e scarica l'avvisoScade il:02/04/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D59" s="93" t="inlineStr">
+      <c r="D59" s="96" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/proroga-termini-presentazione-candidature-po</t>
         </is>
       </c>
-      <c r="E59" s="92" t="inlineStr">
+      <c r="E59" s="95" t="inlineStr">
         <is>
           <t>02/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F59" s="92" t="inlineStr">
+      <c r="F59" s="95" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="G59" s="92" t="inlineStr"/>
+      <c r="G59" s="95" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="94" t="inlineStr">
+      <c r="A60" s="97" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="94" t="inlineStr">
+      <c r="B60" s="97" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2730,22 +2710,22 @@
           <t>INTERNAZIONALIZZAZIONESMAU – Italy RestartsUp in STOCCOLMAApertoFESR</t>
         </is>
       </c>
-      <c r="D60" s="91" t="inlineStr">
+      <c r="D60" s="98" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/smau-italy-restartsup-in-stoccolma/</t>
         </is>
       </c>
-      <c r="E60" s="94" t="inlineStr"/>
-      <c r="F60" s="94" t="inlineStr"/>
-      <c r="G60" s="94" t="inlineStr"/>
+      <c r="E60" s="97" t="inlineStr"/>
+      <c r="F60" s="97" t="inlineStr"/>
+      <c r="G60" s="97" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="92" t="inlineStr">
+      <c r="A61" s="95" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B61" s="92" t="inlineStr">
+      <c r="B61" s="95" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2755,22 +2735,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per Farnborough International AirshowApertoFESR</t>
         </is>
       </c>
-      <c r="D61" s="93" t="inlineStr">
+      <c r="D61" s="96" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-farnborough-international-airshow-2/</t>
         </is>
       </c>
-      <c r="E61" s="92" t="inlineStr"/>
-      <c r="F61" s="92" t="inlineStr"/>
-      <c r="G61" s="92" t="inlineStr"/>
+      <c r="E61" s="95" t="inlineStr"/>
+      <c r="F61" s="95" t="inlineStr"/>
+      <c r="G61" s="95" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="94" t="inlineStr">
+      <c r="A62" s="97" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="94" t="inlineStr">
+      <c r="B62" s="97" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2780,30 +2760,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA - alienazione lotto di terreno sito nel comune di Termini Imerese, via LibertàScade il:30/04/2026 - 12:00Leg</t>
         </is>
       </c>
-      <c r="D62" s="91" t="inlineStr">
+      <c r="D62" s="98" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proprieta-regionale-sito-nel-comune-termini-imerese-favore-ares-fabiola</t>
         </is>
       </c>
-      <c r="E62" s="94" t="inlineStr">
+      <c r="E62" s="97" t="inlineStr">
         <is>
           <t>30/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F62" s="94" t="inlineStr">
+      <c r="F62" s="97" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="G62" s="94" t="inlineStr"/>
+      <c r="G62" s="97" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="92" t="inlineStr">
+      <c r="A63" s="95" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B63" s="92" t="inlineStr">
+      <c r="B63" s="95" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2813,22 +2793,22 @@
           <t>Avviso per la concessione di contributi per progetti di contrasto all'abbandono sportivo giovanile (2026)</t>
         </is>
       </c>
-      <c r="D63" s="93" t="inlineStr">
+      <c r="D63" s="96" t="inlineStr">
         <is>
           <t>https://www.regione.emilia-romagna.it/sport/bandi/2026/contrasto-abbandono-2026</t>
         </is>
       </c>
-      <c r="E63" s="92" t="inlineStr"/>
-      <c r="F63" s="92" t="inlineStr"/>
-      <c r="G63" s="92" t="inlineStr"/>
+      <c r="E63" s="95" t="inlineStr"/>
+      <c r="F63" s="95" t="inlineStr"/>
+      <c r="G63" s="95" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="94" t="inlineStr">
+      <c r="A64" s="97" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="94" t="inlineStr">
+      <c r="B64" s="97" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2838,30 +2818,30 @@
           <t>Avvisi pubbliciAvviso si procede alla riassegnazione della posizione organizzativa a supporto delle attività del Servizio 2 “Investimenti in Agricoltu</t>
         </is>
       </c>
-      <c r="D64" s="91" t="inlineStr">
+      <c r="D64" s="98" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-selezione-interna-conferimento-1-posizione-organizzativa-ai-sensi-artt-19-20-ccrl-2022-2024-comparto-non-dirigenziale</t>
         </is>
       </c>
-      <c r="E64" s="94" t="inlineStr">
+      <c r="E64" s="97" t="inlineStr">
         <is>
           <t>09/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F64" s="94" t="inlineStr">
+      <c r="F64" s="97" t="inlineStr">
         <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="G64" s="94" t="inlineStr"/>
+      <c r="G64" s="97" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="92" t="inlineStr">
+      <c r="A65" s="95" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B65" s="92" t="inlineStr">
+      <c r="B65" s="95" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2871,30 +2851,30 @@
           <t>Avvisi pubbliciST-MESSINA - AVVISO di INDAGINE DI MERCATO per affidamento "Interventi manutenzione straordinaria della strada/pista forestale "Annunzi</t>
         </is>
       </c>
-      <c r="D65" s="93" t="inlineStr">
+      <c r="D65" s="96" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-indagine-mercato-affidamento-interventi-manutenzione-straordinaria-stradapista-forestale-annunziata-comune-messina</t>
         </is>
       </c>
-      <c r="E65" s="92" t="inlineStr">
+      <c r="E65" s="95" t="inlineStr">
         <is>
           <t>16/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F65" s="92" t="inlineStr">
+      <c r="F65" s="95" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="G65" s="92" t="inlineStr"/>
+      <c r="G65" s="95" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="94" t="inlineStr">
+      <c r="A66" s="97" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="94" t="inlineStr">
+      <c r="B66" s="97" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2904,30 +2884,30 @@
           <t>Avvisi pubbliciST-MESSINA - AVVISO DI INDAGINE DI MERCATO per affidamento "Interventi manutenzione straordinaria della strada/pista forestale "San Riz</t>
         </is>
       </c>
-      <c r="D66" s="91" t="inlineStr">
+      <c r="D66" s="98" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-indagine-mercato-affidamento-interventi-manutenzione-straordinaria-stradapista-forestale-san-rizzo-san-leone-crupi-madonuzza-comune-messina</t>
         </is>
       </c>
-      <c r="E66" s="94" t="inlineStr">
+      <c r="E66" s="97" t="inlineStr">
         <is>
           <t>16/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F66" s="94" t="inlineStr">
+      <c r="F66" s="97" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="G66" s="94" t="inlineStr"/>
+      <c r="G66" s="97" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="92" t="inlineStr">
+      <c r="A67" s="95" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="92" t="inlineStr">
+      <c r="B67" s="95" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2937,22 +2917,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Manifestazione di interesse per Casaidea 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D67" s="93" t="inlineStr">
+      <c r="D67" s="96" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-casaidea-2026/</t>
         </is>
       </c>
-      <c r="E67" s="92" t="inlineStr"/>
-      <c r="F67" s="92" t="inlineStr"/>
-      <c r="G67" s="92" t="inlineStr"/>
+      <c r="E67" s="95" t="inlineStr"/>
+      <c r="F67" s="95" t="inlineStr"/>
+      <c r="G67" s="95" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="94" t="inlineStr">
+      <c r="A68" s="97" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="94" t="inlineStr">
+      <c r="B68" s="97" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2962,22 +2942,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per il Salone Internazionale del Libro di Torino 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D68" s="91" t="inlineStr">
+      <c r="D68" s="98" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-il-salone-internazionale-del-libro-di-torino-2026/</t>
         </is>
       </c>
-      <c r="E68" s="94" t="inlineStr"/>
-      <c r="F68" s="94" t="inlineStr"/>
-      <c r="G68" s="94" t="inlineStr"/>
+      <c r="E68" s="97" t="inlineStr"/>
+      <c r="F68" s="97" t="inlineStr"/>
+      <c r="G68" s="97" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="92" t="inlineStr">
+      <c r="A69" s="95" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="92" t="inlineStr">
+      <c r="B69" s="95" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2987,30 +2967,30 @@
           <t>Avvisi pubbliciDDG 1112 del 02.04.2026 - Aggiornamento Avviso pubblico n. 4/2024 per l’attuazione del PAR GOL Sicilia da finanziare nell’ambito del Pi</t>
         </is>
       </c>
-      <c r="D69" s="93" t="inlineStr">
+      <c r="D69" s="96" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/ddg-1112-02042026-aggiornamento-avviso-pubblico-n-42024-l-attuazione-par-gol-sicilia-finanziare-nell-ambito-piano-nazionale-ripresa-resilienza-pnrr</t>
         </is>
       </c>
-      <c r="E69" s="92" t="inlineStr">
+      <c r="E69" s="95" t="inlineStr">
         <is>
           <t>05/04/2030 - 00:00</t>
         </is>
       </c>
-      <c r="F69" s="92" t="inlineStr">
+      <c r="F69" s="95" t="inlineStr">
         <is>
           <t>05/04/2030</t>
         </is>
       </c>
-      <c r="G69" s="92" t="inlineStr"/>
+      <c r="G69" s="95" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="94" t="inlineStr">
+      <c r="A70" s="97" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="94" t="inlineStr">
+      <c r="B70" s="97" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3020,30 +3000,30 @@
           <t>Avvisi pubbliciDDG 1113 del  02.04.2026 - Aggiornamento Avviso pubblico n. 2/2022 e s.m.i per l’attuazione del PAR GOL Sicilia da finanziare nell’ambi</t>
         </is>
       </c>
-      <c r="D70" s="91" t="inlineStr">
+      <c r="D70" s="98" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/ddg-1113-02042026-aggiornamento-avviso-pubblico-n-22022-smi-l-attuazione-par-gol-sicilia-finanziare-nell-ambito-piano-nazionale-ripresa-resilienza-pnrr</t>
         </is>
       </c>
-      <c r="E70" s="94" t="inlineStr">
+      <c r="E70" s="97" t="inlineStr">
         <is>
           <t>03/04/2030 - 00:00</t>
         </is>
       </c>
-      <c r="F70" s="94" t="inlineStr">
+      <c r="F70" s="97" t="inlineStr">
         <is>
           <t>03/04/2030</t>
         </is>
       </c>
-      <c r="G70" s="94" t="inlineStr"/>
+      <c r="G70" s="97" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="92" t="inlineStr">
+      <c r="A71" s="95" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B71" s="92" t="inlineStr">
+      <c r="B71" s="95" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3053,22 +3033,22 @@
           <t>Avvisi pubbliciLeggi e scarica l'avvisoScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D71" s="93" t="inlineStr">
+      <c r="D71" s="96" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/proroga-termini-presentazione-candidature-po</t>
         </is>
       </c>
-      <c r="E71" s="92" t="inlineStr"/>
-      <c r="F71" s="92" t="inlineStr"/>
-      <c r="G71" s="92" t="inlineStr"/>
+      <c r="E71" s="95" t="inlineStr"/>
+      <c r="F71" s="95" t="inlineStr"/>
+      <c r="G71" s="95" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="94" t="inlineStr">
+      <c r="A72" s="97" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="94" t="inlineStr">
+      <c r="B72" s="97" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -3078,22 +3058,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEComunicare l’inclusione – contest per le istituzioni scolastiche regionaliApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D72" s="91" t="inlineStr">
+      <c r="D72" s="98" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/comunicare-linclusione-contest-per-le-istituzioni-scolastiche-regionali/</t>
         </is>
       </c>
-      <c r="E72" s="94" t="inlineStr"/>
-      <c r="F72" s="94" t="inlineStr"/>
-      <c r="G72" s="94" t="inlineStr"/>
+      <c r="E72" s="97" t="inlineStr"/>
+      <c r="F72" s="97" t="inlineStr"/>
+      <c r="G72" s="97" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="92" t="inlineStr">
+      <c r="A73" s="95" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B73" s="92" t="inlineStr">
+      <c r="B73" s="95" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3103,30 +3083,30 @@
           <t>Avvisi pubbliciAPPROVAZIONE AVVISO PUBBLICOScade il:03/04/2027 - 00:00Leggi di più</t>
         </is>
       </c>
-      <c r="D73" s="93" t="inlineStr">
+      <c r="D73" s="96" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/approvazione-avviso-pubblico</t>
         </is>
       </c>
-      <c r="E73" s="92" t="inlineStr">
+      <c r="E73" s="95" t="inlineStr">
         <is>
           <t>03/04/2027 - 00:00</t>
         </is>
       </c>
-      <c r="F73" s="92" t="inlineStr">
+      <c r="F73" s="95" t="inlineStr">
         <is>
           <t>03/04/2027</t>
         </is>
       </c>
-      <c r="G73" s="92" t="inlineStr"/>
+      <c r="G73" s="95" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="94" t="inlineStr">
+      <c r="A74" s="97" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="94" t="inlineStr">
+      <c r="B74" s="97" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -3136,22 +3116,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Donne e Impresa 2026Prossima AperturaFESR</t>
         </is>
       </c>
-      <c r="D74" s="91" t="inlineStr">
+      <c r="D74" s="98" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/donne-e-impresa-2026/</t>
         </is>
       </c>
-      <c r="E74" s="94" t="inlineStr"/>
-      <c r="F74" s="94" t="inlineStr"/>
-      <c r="G74" s="94" t="inlineStr"/>
+      <c r="E74" s="97" t="inlineStr"/>
+      <c r="F74" s="97" t="inlineStr"/>
+      <c r="G74" s="97" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="92" t="inlineStr">
+      <c r="A75" s="95" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B75" s="92" t="inlineStr">
+      <c r="B75" s="95" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3161,30 +3141,30 @@
           <t>Bandi di garaCodice Intervento 111302_FELUCHE - Investimenti a bordo e nei porti per incrementare la qualità delle produzioni e migliorare le condizio</t>
         </is>
       </c>
-      <c r="D75" s="93" t="inlineStr">
+      <c r="D75" s="96" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/bandoavviso-regia-ob-11-azione-3-codice-111302feluche-investimenti-bordo-valorizzazione-feluche-miglioramento-condizioni-lavoro-salute-sicurezza-operatori-l</t>
         </is>
       </c>
-      <c r="E75" s="92" t="inlineStr">
+      <c r="E75" s="95" t="inlineStr">
         <is>
           <t>02/07/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F75" s="92" t="inlineStr">
+      <c r="F75" s="95" t="inlineStr">
         <is>
           <t>02/07/2026</t>
         </is>
       </c>
-      <c r="G75" s="92" t="inlineStr"/>
+      <c r="G75" s="95" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="94" t="inlineStr">
+      <c r="A76" s="97" t="inlineStr">
         <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="94" t="inlineStr">
+      <c r="B76" s="97" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -3194,22 +3174,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURASostegno agli investimenti nel settore vitivinicolo – campagna 2026/2027ApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D76" s="91" t="inlineStr">
+      <c r="D76" s="98" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/sostegno-agli-investimenti-nel-settore-vitivinicolo-campagna-2026-2027/</t>
         </is>
       </c>
-      <c r="E76" s="94" t="inlineStr"/>
-      <c r="F76" s="94" t="inlineStr"/>
-      <c r="G76" s="94" t="inlineStr"/>
+      <c r="E76" s="97" t="inlineStr"/>
+      <c r="F76" s="97" t="inlineStr"/>
+      <c r="G76" s="97" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="92" t="inlineStr">
+      <c r="A77" s="95" t="inlineStr">
         <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="92" t="inlineStr">
+      <c r="B77" s="95" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3219,30 +3199,30 @@
           <t>Manifestazioni di interesse9 aprile 2026 -ST PALERMO- Manifestazione di interesse - “Interventi di manutenzione straordinaria della strada-pista fores</t>
         </is>
       </c>
-      <c r="D77" s="93" t="inlineStr">
+      <c r="D77" s="96" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/9-aprile-2026-st-palermo-manifestazione-interesse-interventi-manutenzione-straordinaria-strada-pista-forestale-monte-cane-comune-caccamo-pa-distretto-forestale</t>
         </is>
       </c>
-      <c r="E77" s="92" t="inlineStr">
+      <c r="E77" s="95" t="inlineStr">
         <is>
           <t>24/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F77" s="92" t="inlineStr">
+      <c r="F77" s="95" t="inlineStr">
         <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="G77" s="92" t="inlineStr"/>
+      <c r="G77" s="95" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="94" t="inlineStr">
+      <c r="A78" s="97" t="inlineStr">
         <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="94" t="inlineStr">
+      <c r="B78" s="97" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3252,30 +3232,30 @@
           <t>Avvisi pubbliciST-MESSINA - AVVISO DI INDAGINE DI MERCATO per affidamento "Interventi manutenzione straordinaria della strada/pista forestale "Faggita</t>
         </is>
       </c>
-      <c r="D78" s="91" t="inlineStr">
+      <c r="D78" s="98" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-indagine-mercato-affidamento-interventi-manutenzione-straordinaria-stradapista-forestale-faggita-comune-tripi-me</t>
         </is>
       </c>
-      <c r="E78" s="94" t="inlineStr">
+      <c r="E78" s="97" t="inlineStr">
         <is>
           <t>23/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F78" s="94" t="inlineStr">
+      <c r="F78" s="97" t="inlineStr">
         <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="G78" s="94" t="inlineStr"/>
+      <c r="G78" s="97" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="92" t="inlineStr">
+      <c r="A79" s="95" t="inlineStr">
         <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B79" s="92" t="inlineStr">
+      <c r="B79" s="95" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3285,30 +3265,30 @@
           <t>Avvisi pubbliciST-MESSINA - AVVISO DI INDAGINE DI MERCATO per affidamento "Interventi manutenzione straordinaria della strada/pista forestale "Ferraro</t>
         </is>
       </c>
-      <c r="D79" s="93" t="inlineStr">
+      <c r="D79" s="96" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-indagine-mercato-affidamento-interventi-manutenzione-straordinaria-stradapista-forestale-ferraro-sanrizzo-badiazza-comune-messina</t>
         </is>
       </c>
-      <c r="E79" s="92" t="inlineStr">
+      <c r="E79" s="95" t="inlineStr">
         <is>
           <t>23/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F79" s="92" t="inlineStr">
+      <c r="F79" s="95" t="inlineStr">
         <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="G79" s="92" t="inlineStr"/>
+      <c r="G79" s="95" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="94" t="inlineStr">
+      <c r="A80" s="97" t="inlineStr">
         <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="94" t="inlineStr">
+      <c r="B80" s="97" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -3318,22 +3298,22 @@
           <t>Comunicazione e informazioneAcquisizione di servizi di comunicazione e informazione – PR Lazio FESR, PR Lazio FSE+ e comunicazione unitariaApertoBandi</t>
         </is>
       </c>
-      <c r="D80" s="91" t="inlineStr">
+      <c r="D80" s="98" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/acquisizione-di-servizi-di-comunicazione-e-informazione-pr-lazio-fesr-pr-lazio-fse-e-comunicazione-unitaria/</t>
         </is>
       </c>
-      <c r="E80" s="94" t="inlineStr"/>
-      <c r="F80" s="94" t="inlineStr"/>
-      <c r="G80" s="94" t="inlineStr"/>
+      <c r="E80" s="97" t="inlineStr"/>
+      <c r="F80" s="97" t="inlineStr"/>
+      <c r="G80" s="97" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="92" t="inlineStr">
+      <c r="A81" s="95" t="inlineStr">
         <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B81" s="92" t="inlineStr">
+      <c r="B81" s="95" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3343,30 +3323,30 @@
           <t>Avvisi pubbliciAvviso pubblico di selezione interna, per titoli, per il conferimento, ai sensi degli artt. 21 del CCRL 2022-2024 del comparto non diri</t>
         </is>
       </c>
-      <c r="D81" s="93" t="inlineStr">
+      <c r="D81" s="96" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-selezione-interna-titoli-conferimento-ai-sensi-artt-21-ccrl-2022-2024-comparto-non-dirigenziale-una-posizione-organizzativa-dipartimento</t>
         </is>
       </c>
-      <c r="E81" s="92" t="inlineStr">
+      <c r="E81" s="95" t="inlineStr">
         <is>
           <t>16/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F81" s="92" t="inlineStr">
+      <c r="F81" s="95" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="G81" s="92" t="inlineStr"/>
+      <c r="G81" s="95" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="94" t="inlineStr">
+      <c r="A82" s="97" t="inlineStr">
         <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="94" t="inlineStr">
+      <c r="B82" s="97" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3376,30 +3356,30 @@
           <t xml:space="preserve">Avvisi pubbliciAVVISO DI INDAGINE DI MERCATO  per la partecipazione alla successiva procedura negoziata a norma dell'art. 50, comma 1, lettera c) del </t>
         </is>
       </c>
-      <c r="D82" s="91" t="inlineStr">
+      <c r="D82" s="98" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-indagine-mercato-partecipazione-alla-successiva-procedura-negoziata-norma-art-50-comma-1-lettera-c-dlgs-31-marzo-2023-n-36-ssmmii-finalizzata-all</t>
         </is>
       </c>
-      <c r="E82" s="94" t="inlineStr">
+      <c r="E82" s="97" t="inlineStr">
         <is>
           <t>30/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F82" s="94" t="inlineStr">
+      <c r="F82" s="97" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="G82" s="94" t="inlineStr"/>
+      <c r="G82" s="97" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="92" t="inlineStr">
+      <c r="A83" s="95" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="92" t="inlineStr">
+      <c r="B83" s="95" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -3409,14 +3389,14 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEVoucher per lo Sport – individuazione dei destinatari (II edizione)ApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D83" s="93" t="inlineStr">
+      <c r="D83" s="96" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/voucher-per-lo-sport-individuazione-dei-destinatari-ii-edizione/</t>
         </is>
       </c>
-      <c r="E83" s="92" t="inlineStr"/>
-      <c r="F83" s="92" t="inlineStr"/>
-      <c r="G83" s="92" t="inlineStr"/>
+      <c r="E83" s="95" t="inlineStr"/>
+      <c r="F83" s="95" t="inlineStr"/>
+      <c r="G83" s="95" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="97" t="inlineStr">
@@ -3591,6 +3571,147 @@
         </is>
       </c>
       <c r="G89" s="95" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="101" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="101" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="C90" s="9" t="inlineStr">
+        <is>
+          <t>ACCESSO AL CREDITO E ALLE GARANZIE PER LE IMPRESEFondo Patrimonializzazione Pmi 2025 – Riapertura terminiProssima AperturaFESR</t>
+        </is>
+      </c>
+      <c r="D90" s="102" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/fondo-patrimonializzazione-pmi-riapertura-termini/</t>
+        </is>
+      </c>
+      <c r="E90" s="101" t="inlineStr"/>
+      <c r="F90" s="101" t="inlineStr"/>
+      <c r="G90" s="101" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="99" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="99" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>ACCESSO AL CREDITO E ALLE GARANZIE PER LE IMPRESENuovo Fondo Piccolo Credito – sezione ordinaria (2026)Prossima AperturaFESRPOCRisorse regionali</t>
+        </is>
+      </c>
+      <c r="D91" s="100" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/nuovo-fondo-piccolo-credito-sezione-ordinaria-2026/</t>
+        </is>
+      </c>
+      <c r="E91" s="99" t="inlineStr"/>
+      <c r="F91" s="99" t="inlineStr"/>
+      <c r="G91" s="99" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="101" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="101" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="C92" s="9" t="inlineStr">
+        <is>
+          <t>ACCESSO AL CREDITO E ALLE GARANZIE PER LE IMPRESENuovo Fondo Futuro 2026Prossima AperturaFESRPOC</t>
+        </is>
+      </c>
+      <c r="D92" s="102" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/nuovo-fondo-futuro-2026/</t>
+        </is>
+      </c>
+      <c r="E92" s="101" t="inlineStr"/>
+      <c r="F92" s="101" t="inlineStr"/>
+      <c r="G92" s="101" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="99" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="99" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>Avvisi pubbliciAvviso pubblico di selezione interna, per titoli, per il conferimento, ai sensi degli artt. 19 e 20 del CCRL 2022-2024 del comparto non</t>
+        </is>
+      </c>
+      <c r="D93" s="100" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-selezione-interna-titoli-conferimento-ai-sensi-artt-19-20-ccrl-2022-2024-comparto-non-dirigenziale-posizioni-organizzative-dipartimento-regionale</t>
+        </is>
+      </c>
+      <c r="E93" s="99" t="inlineStr">
+        <is>
+          <t>24/04/2026 - 12:00</t>
+        </is>
+      </c>
+      <c r="F93" s="99" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="G93" s="99" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="101" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="101" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C94" s="9" t="inlineStr">
+        <is>
+          <t>Avvisi pubblici16 aprile 2026 - ST CATANIA - Avviso Concessione postazioni arnie - anno 2026Scade il:27/04/2026 - 12:00Leggi di più</t>
+        </is>
+      </c>
+      <c r="D94" s="102" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/16-aprile-2026-st-catania-avviso-concessione-postazioni-arnie-anno-2026</t>
+        </is>
+      </c>
+      <c r="E94" s="101" t="inlineStr">
+        <is>
+          <t>27/04/2026 - 12:00</t>
+        </is>
+      </c>
+      <c r="F94" s="101" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="G94" s="101" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -3682,6 +3803,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D87" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D88" r:id="rId87"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D94" r:id="rId93"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3726,7 +3852,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="95" t="inlineStr">
+      <c r="A3" s="99" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -3739,29 +3865,29 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="97" t="inlineStr">
+      <c r="A4" s="101" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="95" t="inlineStr">
+      <c r="A5" s="99" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">

--- a/data/bandi_export.xlsx
+++ b/data/bandi_export.xlsx
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -396,6 +396,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -787,7 +799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -802,7 +814,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏛️  Nuovi Bandi — 17/04/2026 08:23</t>
+          <t>🏛️  Nuovi Bandi — 18/04/2026 07:56</t>
         </is>
       </c>
     </row>
@@ -847,132 +859,63 @@
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="99" t="inlineStr">
-        <is>
-          <t>Lazio</t>
+      <c r="B3" s="103" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>ACCESSO AL CREDITO E ALLE GARANZIE PER LE IMPRESEFondo Patrimonializzazione Pmi 2025 – Riapertura terminiProssima AperturaFESR</t>
-        </is>
-      </c>
-      <c r="D3" s="100" t="inlineStr">
-        <is>
-          <t>https://www.lazioeuropa.it/bandi/fondo-patrimonializzazione-pmi-riapertura-termini/</t>
-        </is>
-      </c>
-      <c r="E3" s="99" t="inlineStr"/>
-      <c r="F3" s="99" t="inlineStr"/>
+          <t>Manifestazioni di interesseIndividuazione delle Compagnie di Assicurazione disponibili a emettere polizze collettive e polizze individuali multirischi</t>
+        </is>
+      </c>
+      <c r="D3" s="104" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/polizze-collettive-polizze-individuali-multirischio-agricole-integrate-fondo-agricat-favore-agricoltori-siciliani-campagna-assicurativa-2026</t>
+        </is>
+      </c>
+      <c r="E3" s="103" t="inlineStr">
+        <is>
+          <t>29/04/2026 - 23:59</t>
+        </is>
+      </c>
+      <c r="F3" s="103" t="inlineStr">
+        <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
       <c r="G3" s="5" t="inlineStr"/>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="101" t="inlineStr">
-        <is>
-          <t>Lazio</t>
+      <c r="B4" s="105" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>ACCESSO AL CREDITO E ALLE GARANZIE PER LE IMPRESENuovo Fondo Piccolo Credito – sezione ordinaria (2026)Prossima AperturaFESRPOCRisorse regionali</t>
-        </is>
-      </c>
-      <c r="D4" s="102" t="inlineStr">
-        <is>
-          <t>https://www.lazioeuropa.it/bandi/nuovo-fondo-piccolo-credito-sezione-ordinaria-2026/</t>
-        </is>
-      </c>
-      <c r="E4" s="101" t="inlineStr"/>
-      <c r="F4" s="101" t="inlineStr"/>
+          <t>Avvisi pubbliciST MESSINA - AVVISO PUBBLICO - MANIFESTAZIONE DI INTERESSE ALLA LICITAZIONE PRIVATA PER LA CONCESSIONE AL PASCOLO NEI TERRENI DEL DEMAN</t>
+        </is>
+      </c>
+      <c r="D4" s="106" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-pubblico-manifestazione-interesse-alla-licitazione-privata-concessione-al-pascolo-nei-terreni-demanio-forestale-regionale-gestiti-dipartimento</t>
+        </is>
+      </c>
+      <c r="E4" s="105" t="inlineStr">
+        <is>
+          <t>28/04/2026 - 12:00</t>
+        </is>
+      </c>
+      <c r="F4" s="105" t="inlineStr">
+        <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
       <c r="G4" s="9" t="inlineStr"/>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" s="99" t="inlineStr">
-        <is>
-          <t>Lazio</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>ACCESSO AL CREDITO E ALLE GARANZIE PER LE IMPRESENuovo Fondo Futuro 2026Prossima AperturaFESRPOC</t>
-        </is>
-      </c>
-      <c r="D5" s="100" t="inlineStr">
-        <is>
-          <t>https://www.lazioeuropa.it/bandi/nuovo-fondo-futuro-2026/</t>
-        </is>
-      </c>
-      <c r="E5" s="99" t="inlineStr"/>
-      <c r="F5" s="99" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="101" t="inlineStr">
-        <is>
-          <t>Sicilia</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>Avvisi pubbliciAvviso pubblico di selezione interna, per titoli, per il conferimento, ai sensi degli artt. 19 e 20 del CCRL 2022-2024 del comparto non</t>
-        </is>
-      </c>
-      <c r="D6" s="102" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-selezione-interna-titoli-conferimento-ai-sensi-artt-19-20-ccrl-2022-2024-comparto-non-dirigenziale-posizioni-organizzative-dipartimento-regionale</t>
-        </is>
-      </c>
-      <c r="E6" s="101" t="inlineStr">
-        <is>
-          <t>24/04/2026 - 12:00</t>
-        </is>
-      </c>
-      <c r="F6" s="101" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr"/>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" s="99" t="inlineStr">
-        <is>
-          <t>Sicilia</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Avvisi pubblici16 aprile 2026 - ST CATANIA - Avviso Concessione postazioni arnie - anno 2026Scade il:27/04/2026 - 12:00Leggi di più</t>
-        </is>
-      </c>
-      <c r="D7" s="100" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/16-aprile-2026-st-catania-avviso-concessione-postazioni-arnie-anno-2026</t>
-        </is>
-      </c>
-      <c r="E7" s="99" t="inlineStr">
-        <is>
-          <t>27/04/2026 - 12:00</t>
-        </is>
-      </c>
-      <c r="F7" s="99" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -981,9 +924,6 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -995,7 +935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1045,12 +985,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="97" t="inlineStr">
+      <c r="A2" s="101" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B2" s="97" t="inlineStr">
+      <c r="B2" s="101" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -1060,22 +1000,22 @@
           <t>FLAG GALPA Costa E-R. Sostituzione del motore principale e dei motori secondari. Secondo bando</t>
         </is>
       </c>
-      <c r="D2" s="98" t="inlineStr">
+      <c r="D2" s="102" t="inlineStr">
         <is>
           <t>https://agricoltura.regione.emilia-romagna.it/feampa-2021-2027/bandi-galpa/2026/galpa-sostituzione-motori-secondo-bando</t>
         </is>
       </c>
-      <c r="E2" s="97" t="inlineStr"/>
-      <c r="F2" s="97" t="inlineStr"/>
-      <c r="G2" s="97" t="inlineStr"/>
+      <c r="E2" s="101" t="inlineStr"/>
+      <c r="F2" s="101" t="inlineStr"/>
+      <c r="G2" s="101" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="95" t="inlineStr">
+      <c r="A3" s="99" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B3" s="95" t="inlineStr">
+      <c r="B3" s="99" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1085,22 +1025,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0PRE-SEED 3.0Prossima AperturaFESR</t>
         </is>
       </c>
-      <c r="D3" s="96" t="inlineStr">
+      <c r="D3" s="100" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/pre-seed-3-0/</t>
         </is>
       </c>
-      <c r="E3" s="95" t="inlineStr"/>
-      <c r="F3" s="95" t="inlineStr"/>
-      <c r="G3" s="95" t="inlineStr"/>
+      <c r="E3" s="99" t="inlineStr"/>
+      <c r="F3" s="99" t="inlineStr"/>
+      <c r="G3" s="99" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="97" t="inlineStr">
+      <c r="A4" s="101" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B4" s="97" t="inlineStr">
+      <c r="B4" s="101" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1110,22 +1050,22 @@
           <t>ACCESSO AL CREDITO E ALLE GARANZIE PER LE IMPRESEContributo su finanziamenti alle imprese del Lazio erogati su provvista BEIProssima AperturaFESR</t>
         </is>
       </c>
-      <c r="D4" s="98" t="inlineStr">
+      <c r="D4" s="102" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-su-finanziamenti-alle-imprese-del-lazio-erogati-su-provvista-bei/</t>
         </is>
       </c>
-      <c r="E4" s="97" t="inlineStr"/>
-      <c r="F4" s="97" t="inlineStr"/>
-      <c r="G4" s="97" t="inlineStr"/>
+      <c r="E4" s="101" t="inlineStr"/>
+      <c r="F4" s="101" t="inlineStr"/>
+      <c r="G4" s="101" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="95" t="inlineStr">
+      <c r="A5" s="99" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B5" s="95" t="inlineStr">
+      <c r="B5" s="99" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1135,22 +1075,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEIndividuazione degli enti iscritti al Registro unico nazionale del Terzo settoreApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D5" s="96" t="inlineStr">
+      <c r="D5" s="100" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/individuazione-degli-enti-iscritti-al-registro-unico-nazionale-del-terzo-settore/</t>
         </is>
       </c>
-      <c r="E5" s="95" t="inlineStr"/>
-      <c r="F5" s="95" t="inlineStr"/>
-      <c r="G5" s="95" t="inlineStr"/>
+      <c r="E5" s="99" t="inlineStr"/>
+      <c r="F5" s="99" t="inlineStr"/>
+      <c r="G5" s="99" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="97" t="inlineStr">
+      <c r="A6" s="101" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B6" s="97" t="inlineStr">
+      <c r="B6" s="101" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1160,22 +1100,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Technology Transfer LazioApertoFESR</t>
         </is>
       </c>
-      <c r="D6" s="98" t="inlineStr">
+      <c r="D6" s="102" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/technology-transfer-lazio/</t>
         </is>
       </c>
-      <c r="E6" s="97" t="inlineStr"/>
-      <c r="F6" s="97" t="inlineStr"/>
-      <c r="G6" s="97" t="inlineStr"/>
+      <c r="E6" s="101" t="inlineStr"/>
+      <c r="F6" s="101" t="inlineStr"/>
+      <c r="G6" s="101" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="95" t="inlineStr">
+      <c r="A7" s="99" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B7" s="95" t="inlineStr">
+      <c r="B7" s="99" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1185,22 +1125,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Percorso di tutoraggio per le impreseApertoFESR</t>
         </is>
       </c>
-      <c r="D7" s="96" t="inlineStr">
+      <c r="D7" s="100" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/percorso-di-tutoraggio-per-le-imprese/</t>
         </is>
       </c>
-      <c r="E7" s="95" t="inlineStr"/>
-      <c r="F7" s="95" t="inlineStr"/>
-      <c r="G7" s="95" t="inlineStr"/>
+      <c r="E7" s="99" t="inlineStr"/>
+      <c r="F7" s="99" t="inlineStr"/>
+      <c r="G7" s="99" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="97" t="inlineStr">
+      <c r="A8" s="101" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B8" s="97" t="inlineStr">
+      <c r="B8" s="101" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1210,22 +1150,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per partecipare a SMAU Parigi 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D8" s="98" t="inlineStr">
+      <c r="D8" s="102" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-partecipare-a-smau-parigi-2026/</t>
         </is>
       </c>
-      <c r="E8" s="97" t="inlineStr"/>
-      <c r="F8" s="97" t="inlineStr"/>
-      <c r="G8" s="97" t="inlineStr"/>
+      <c r="E8" s="101" t="inlineStr"/>
+      <c r="F8" s="101" t="inlineStr"/>
+      <c r="G8" s="101" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="95" t="inlineStr">
+      <c r="A9" s="99" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B9" s="95" t="inlineStr">
+      <c r="B9" s="99" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1235,22 +1175,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONERiconoscimento della funzione sociale ed educativa degli oratoriApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D9" s="96" t="inlineStr">
+      <c r="D9" s="100" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/riconoscimento-della-funzione-sociale-ed-educativa-degli-oratori/</t>
         </is>
       </c>
-      <c r="E9" s="95" t="inlineStr"/>
-      <c r="F9" s="95" t="inlineStr"/>
-      <c r="G9" s="95" t="inlineStr"/>
+      <c r="E9" s="99" t="inlineStr"/>
+      <c r="F9" s="99" t="inlineStr"/>
+      <c r="G9" s="99" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="97" t="inlineStr">
+      <c r="A10" s="101" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B10" s="97" t="inlineStr">
+      <c r="B10" s="101" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1260,22 +1200,22 @@
           <t>GovernanceIscrizione nell’elenco regionale degli idonei all’esercizio dell’attività di direttore dell’Istituto JemoloApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D10" s="98" t="inlineStr">
+      <c r="D10" s="102" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/iscrizione-nellelenco-regionale-degli-idonei-allesercizio-dellattivita-di-direttore-dellistituto-jemolo/</t>
         </is>
       </c>
-      <c r="E10" s="97" t="inlineStr"/>
-      <c r="F10" s="97" t="inlineStr"/>
-      <c r="G10" s="97" t="inlineStr"/>
+      <c r="E10" s="101" t="inlineStr"/>
+      <c r="F10" s="101" t="inlineStr"/>
+      <c r="G10" s="101" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="95" t="inlineStr">
+      <c r="A11" s="99" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B11" s="95" t="inlineStr">
+      <c r="B11" s="99" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1285,22 +1225,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEVoucher per lo sport – seconda annualitàApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D11" s="96" t="inlineStr">
+      <c r="D11" s="100" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/voucher-per-lo-sport-seconda-annualita/</t>
         </is>
       </c>
-      <c r="E11" s="95" t="inlineStr"/>
-      <c r="F11" s="95" t="inlineStr"/>
-      <c r="G11" s="95" t="inlineStr"/>
+      <c r="E11" s="99" t="inlineStr"/>
+      <c r="F11" s="99" t="inlineStr"/>
+      <c r="G11" s="99" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="97" t="inlineStr">
+      <c r="A12" s="101" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B12" s="97" t="inlineStr">
+      <c r="B12" s="101" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1310,22 +1250,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEBonus occupazionale SALGOApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D12" s="98" t="inlineStr">
+      <c r="D12" s="102" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/bonus-occupazionale-salgo/</t>
         </is>
       </c>
-      <c r="E12" s="97" t="inlineStr"/>
-      <c r="F12" s="97" t="inlineStr"/>
-      <c r="G12" s="97" t="inlineStr"/>
+      <c r="E12" s="101" t="inlineStr"/>
+      <c r="F12" s="101" t="inlineStr"/>
+      <c r="G12" s="101" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="95" t="inlineStr">
+      <c r="A13" s="99" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B13" s="95" t="inlineStr">
+      <c r="B13" s="99" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1335,22 +1275,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEContributo di Libertà per le donne che hanno subito violenzaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D13" s="96" t="inlineStr">
+      <c r="D13" s="100" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-di-liberta-per-le-donne-che-hanno-subito-violenza/</t>
         </is>
       </c>
-      <c r="E13" s="95" t="inlineStr"/>
-      <c r="F13" s="95" t="inlineStr"/>
-      <c r="G13" s="95" t="inlineStr"/>
+      <c r="E13" s="99" t="inlineStr"/>
+      <c r="F13" s="99" t="inlineStr"/>
+      <c r="G13" s="99" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="97" t="inlineStr">
+      <c r="A14" s="101" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B14" s="97" t="inlineStr">
+      <c r="B14" s="101" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1360,22 +1300,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURAInterventi straordinari di valorizzazione del patrimonio culturale del LazioApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D14" s="98" t="inlineStr">
+      <c r="D14" s="102" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/interventi-straordinari-di-valorizzazione-del-patrimonio-culturale-del-lazio/</t>
         </is>
       </c>
-      <c r="E14" s="97" t="inlineStr"/>
-      <c r="F14" s="97" t="inlineStr"/>
-      <c r="G14" s="97" t="inlineStr"/>
+      <c r="E14" s="101" t="inlineStr"/>
+      <c r="F14" s="101" t="inlineStr"/>
+      <c r="G14" s="101" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="95" t="inlineStr">
+      <c r="A15" s="99" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B15" s="95" t="inlineStr">
+      <c r="B15" s="99" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1385,30 +1325,30 @@
           <t>Bandi di garaBANDO ATTUAZIONE Ob. 1.1 Azione 1 codice 111102 _DIV - "SOSTEGNO ALLA DIVERSIFICAZIONE E NUOVE FORME DI REDDITO PER LA PICCOLA PESCA COST</t>
         </is>
       </c>
-      <c r="D15" s="96" t="inlineStr">
+      <c r="D15" s="100" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/bando-avviso-regia-ob-11-azione-1-codice-111102-div-sostegno-alla-diversificazione-nuove-forme-reddito-piccola-pesca-costiera</t>
         </is>
       </c>
-      <c r="E15" s="95" t="inlineStr">
+      <c r="E15" s="99" t="inlineStr">
         <is>
           <t>07/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F15" s="95" t="inlineStr">
+      <c r="F15" s="99" t="inlineStr">
         <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="G15" s="95" t="inlineStr"/>
+      <c r="G15" s="99" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="97" t="inlineStr">
+      <c r="A16" s="101" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B16" s="97" t="inlineStr">
+      <c r="B16" s="101" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1418,30 +1358,30 @@
           <t>Avvisi pubblici09 marzo 2026 - ST SIRACUSA - AVVISO PUBBLICO PER LA COSTITUZIONE DI ELENCHI DI OPERATORI ECONOMICI PER L’ACQUISIZIONE DI BENI E SERVIZ</t>
         </is>
       </c>
-      <c r="D16" s="98" t="inlineStr">
+      <c r="D16" s="102" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/09-marzo-2026-st-siracusa-avviso-pubblico-costituzione-elenchi-operatori-economici-l-acquisizione-beni-servizi</t>
         </is>
       </c>
-      <c r="E16" s="97" t="inlineStr">
+      <c r="E16" s="101" t="inlineStr">
         <is>
           <t>31/12/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F16" s="97" t="inlineStr">
+      <c r="F16" s="101" t="inlineStr">
         <is>
           <t>31/12/2026</t>
         </is>
       </c>
-      <c r="G16" s="97" t="inlineStr"/>
+      <c r="G16" s="101" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="95" t="inlineStr">
+      <c r="A17" s="99" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B17" s="95" t="inlineStr">
+      <c r="B17" s="99" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1451,30 +1391,30 @@
           <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScade il:19/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D17" s="96" t="inlineStr">
+      <c r="D17" s="100" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
         </is>
       </c>
-      <c r="E17" s="95" t="inlineStr">
+      <c r="E17" s="99" t="inlineStr">
         <is>
           <t>19/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F17" s="95" t="inlineStr">
+      <c r="F17" s="99" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G17" s="95" t="inlineStr"/>
+      <c r="G17" s="99" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="97" t="inlineStr">
+      <c r="A18" s="101" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B18" s="97" t="inlineStr">
+      <c r="B18" s="101" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1484,22 +1424,22 @@
           <t>Manifestazioni di interesseAvviso Manifestazione Interesse DISTRIBUTORI AUTOMATICI di bevande e snackScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D18" s="98" t="inlineStr">
+      <c r="D18" s="102" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-distributori-automatici-bevande-snack</t>
         </is>
       </c>
-      <c r="E18" s="97" t="inlineStr"/>
-      <c r="F18" s="97" t="inlineStr"/>
-      <c r="G18" s="97" t="inlineStr"/>
+      <c r="E18" s="101" t="inlineStr"/>
+      <c r="F18" s="101" t="inlineStr"/>
+      <c r="G18" s="101" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="95" t="inlineStr">
+      <c r="A19" s="99" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B19" s="95" t="inlineStr">
+      <c r="B19" s="99" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1509,30 +1449,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D19" s="96" t="inlineStr">
+      <c r="D19" s="100" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo</t>
         </is>
       </c>
-      <c r="E19" s="95" t="inlineStr">
+      <c r="E19" s="99" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F19" s="95" t="inlineStr">
+      <c r="F19" s="99" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G19" s="95" t="inlineStr"/>
+      <c r="G19" s="99" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="97" t="inlineStr">
+      <c r="A20" s="101" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B20" s="97" t="inlineStr">
+      <c r="B20" s="101" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1542,30 +1482,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D20" s="98" t="inlineStr">
+      <c r="D20" s="102" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo-0</t>
         </is>
       </c>
-      <c r="E20" s="97" t="inlineStr">
+      <c r="E20" s="101" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F20" s="97" t="inlineStr">
+      <c r="F20" s="101" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G20" s="97" t="inlineStr"/>
+      <c r="G20" s="101" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="95" t="inlineStr">
+      <c r="A21" s="99" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B21" s="95" t="inlineStr">
+      <c r="B21" s="99" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1575,22 +1515,22 @@
           <t>Manifestazioni di interesseST SIRACUSA - AVVISO DI MANIFESTAZIONE DI INTERESSE - Fornitura applicativo extracontabile per la gestione progetti, ecc. e</t>
         </is>
       </c>
-      <c r="D21" s="96" t="inlineStr">
+      <c r="D21" s="100" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-siracusa-avviso-manifestazione-interesse-fornitura-applicativo-extracontabile-gestione-progetti-ecc-applicativo-gestione-ed-elaborazione-informatizzata-paghe</t>
         </is>
       </c>
-      <c r="E21" s="95" t="inlineStr"/>
-      <c r="F21" s="95" t="inlineStr"/>
-      <c r="G21" s="95" t="inlineStr"/>
+      <c r="E21" s="99" t="inlineStr"/>
+      <c r="F21" s="99" t="inlineStr"/>
+      <c r="G21" s="99" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="97" t="inlineStr">
+      <c r="A22" s="101" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B22" s="97" t="inlineStr">
+      <c r="B22" s="101" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1600,30 +1540,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile sito nel Comune di Capo D'Orlando, Via Trazzera MarinaScade il:25/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D22" s="98" t="inlineStr">
+      <c r="D22" s="102" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-sito-nel-comune-capo-d-orlando-trazzera-marina</t>
         </is>
       </c>
-      <c r="E22" s="97" t="inlineStr">
+      <c r="E22" s="101" t="inlineStr">
         <is>
           <t>25/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F22" s="97" t="inlineStr">
+      <c r="F22" s="101" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="G22" s="97" t="inlineStr"/>
+      <c r="G22" s="101" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="95" t="inlineStr">
+      <c r="A23" s="99" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B23" s="95" t="inlineStr">
+      <c r="B23" s="99" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1633,22 +1573,22 @@
           <t xml:space="preserve">Avvisi pubbliciST CATANIA - Programma Regionale FESR Sicilia 2021-2027 - Azione 2.4.4 - “Interventi per la riduzione del rischio incendi” - AVVISO DI </t>
         </is>
       </c>
-      <c r="D23" s="96" t="inlineStr">
+      <c r="D23" s="100" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-catania-programma-regionale-fesr-sicilia-2021-2027-azione-244-interventi-riduzione-rischio-incendi-avviso-indagine-mercato</t>
         </is>
       </c>
-      <c r="E23" s="95" t="inlineStr"/>
-      <c r="F23" s="95" t="inlineStr"/>
-      <c r="G23" s="95" t="inlineStr"/>
+      <c r="E23" s="99" t="inlineStr"/>
+      <c r="F23" s="99" t="inlineStr"/>
+      <c r="G23" s="99" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="97" t="inlineStr">
+      <c r="A24" s="101" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B24" s="97" t="inlineStr">
+      <c r="B24" s="101" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1658,22 +1598,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per ROMICS – Primavera 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D24" s="98" t="inlineStr">
+      <c r="D24" s="102" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-romics-primavera-2026/</t>
         </is>
       </c>
-      <c r="E24" s="97" t="inlineStr"/>
-      <c r="F24" s="97" t="inlineStr"/>
-      <c r="G24" s="97" t="inlineStr"/>
+      <c r="E24" s="101" t="inlineStr"/>
+      <c r="F24" s="101" t="inlineStr"/>
+      <c r="G24" s="101" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="95" t="inlineStr">
+      <c r="A25" s="99" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B25" s="95" t="inlineStr">
+      <c r="B25" s="99" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1683,22 +1623,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Cinema International 2026 – I edizioneApertoFESR</t>
         </is>
       </c>
-      <c r="D25" s="96" t="inlineStr">
+      <c r="D25" s="100" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lazio-cinema-international-2026-i-edizione/</t>
         </is>
       </c>
-      <c r="E25" s="95" t="inlineStr"/>
-      <c r="F25" s="95" t="inlineStr"/>
-      <c r="G25" s="95" t="inlineStr"/>
+      <c r="E25" s="99" t="inlineStr"/>
+      <c r="F25" s="99" t="inlineStr"/>
+      <c r="G25" s="99" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="97" t="inlineStr">
+      <c r="A26" s="101" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B26" s="97" t="inlineStr">
+      <c r="B26" s="101" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1708,22 +1648,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEManifestazioni di interesse alla costituzione di due nuove Fondazioni I.T.S. AcademyApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D26" s="98" t="inlineStr">
+      <c r="D26" s="102" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazioni-di-interesse-alla-costituzione-di-due-nuove-fondazioni-i-t-s-academy/</t>
         </is>
       </c>
-      <c r="E26" s="97" t="inlineStr"/>
-      <c r="F26" s="97" t="inlineStr"/>
-      <c r="G26" s="97" t="inlineStr"/>
+      <c r="E26" s="101" t="inlineStr"/>
+      <c r="F26" s="101" t="inlineStr"/>
+      <c r="G26" s="101" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="95" t="inlineStr">
+      <c r="A27" s="99" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B27" s="95" t="inlineStr">
+      <c r="B27" s="99" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1733,22 +1673,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURAContributi per sostenere la ripresa del settore della pescaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D27" s="96" t="inlineStr">
+      <c r="D27" s="100" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributi-per-sostenere-la-ripresa-del-settore-della-pesca/</t>
         </is>
       </c>
-      <c r="E27" s="95" t="inlineStr"/>
-      <c r="F27" s="95" t="inlineStr"/>
-      <c r="G27" s="95" t="inlineStr"/>
+      <c r="E27" s="99" t="inlineStr"/>
+      <c r="F27" s="99" t="inlineStr"/>
+      <c r="G27" s="99" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="97" t="inlineStr">
+      <c r="A28" s="101" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B28" s="97" t="inlineStr">
+      <c r="B28" s="101" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1758,30 +1698,30 @@
           <t>Manifestazioni di interesseAVVISO - Manifestazione Interesse “Storytelling aziendale” Expo Wild Natura - Caccia - Pesca. Misterbianco (CT), 10-12 apri</t>
         </is>
       </c>
-      <c r="D28" s="98" t="inlineStr">
+      <c r="D28" s="102" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-storytelling-aziendale-expo-wild-natura-caccia-pesca-misterbianco-ct-10-12-aprile-2026</t>
         </is>
       </c>
-      <c r="E28" s="97" t="inlineStr">
+      <c r="E28" s="101" t="inlineStr">
         <is>
           <t>30/03/2026 - 13:00</t>
         </is>
       </c>
-      <c r="F28" s="97" t="inlineStr">
+      <c r="F28" s="101" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G28" s="97" t="inlineStr"/>
+      <c r="G28" s="101" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="95" t="inlineStr">
+      <c r="A29" s="99" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B29" s="95" t="inlineStr">
+      <c r="B29" s="99" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1791,30 +1731,30 @@
           <t>Manifestazioni di interesseInvaso Lentini - Interventi di ripristino delle pareti esterne in cls della Torre di presa Sud e della trave d’appoggio del</t>
         </is>
       </c>
-      <c r="D29" s="96" t="inlineStr">
+      <c r="D29" s="100" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/invaso-lentini-interventi-ripristino-pareti-esterne-cls-torre-presa-sud-trave-d-appoggio-cavalcavia-collegamento-alla-stessa-torre</t>
         </is>
       </c>
-      <c r="E29" s="95" t="inlineStr">
+      <c r="E29" s="99" t="inlineStr">
         <is>
           <t>19/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F29" s="95" t="inlineStr">
+      <c r="F29" s="99" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G29" s="95" t="inlineStr"/>
+      <c r="G29" s="99" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="97" t="inlineStr">
+      <c r="A30" s="101" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="B30" s="97" t="inlineStr">
+      <c r="B30" s="101" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1824,22 +1764,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURARistrutturazione e riconversione vigneti – campagna 2026-2027ApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D30" s="98" t="inlineStr">
+      <c r="D30" s="102" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/ristrutturazione-e-riconversione-vigneti-campagna-2026-2027/</t>
         </is>
       </c>
-      <c r="E30" s="97" t="inlineStr"/>
-      <c r="F30" s="97" t="inlineStr"/>
-      <c r="G30" s="97" t="inlineStr"/>
+      <c r="E30" s="101" t="inlineStr"/>
+      <c r="F30" s="101" t="inlineStr"/>
+      <c r="G30" s="101" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="95" t="inlineStr">
+      <c r="A31" s="99" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="B31" s="95" t="inlineStr">
+      <c r="B31" s="99" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1849,30 +1789,30 @@
           <t>Manifestazioni di interessePR FESR 2021/27 Azione 1.3.3 e del POC 2014/20 - Azione 1.3.1  - Avviso a manifestazione d’interesse eventi fieristici inte</t>
         </is>
       </c>
-      <c r="D31" s="96" t="inlineStr">
+      <c r="D31" s="100" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-d-interesse-eventi-fieristici-internazionali-marzo-dicembre-2026</t>
         </is>
       </c>
-      <c r="E31" s="95" t="inlineStr">
+      <c r="E31" s="99" t="inlineStr">
         <is>
           <t>30/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F31" s="95" t="inlineStr">
+      <c r="F31" s="99" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="G31" s="95" t="inlineStr"/>
+      <c r="G31" s="99" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="97" t="inlineStr">
+      <c r="A32" s="101" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="B32" s="97" t="inlineStr">
+      <c r="B32" s="101" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1882,22 +1822,22 @@
           <t>INTERNAZIONALIZZAZIONEL’Ecosistema dell’Innovazione a INNOVIT – Focus S3ApertoFESR</t>
         </is>
       </c>
-      <c r="D32" s="98" t="inlineStr">
+      <c r="D32" s="102" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lecosistema-dellinnovazione-a-innovit-focus-s3/</t>
         </is>
       </c>
-      <c r="E32" s="97" t="inlineStr"/>
-      <c r="F32" s="97" t="inlineStr"/>
-      <c r="G32" s="97" t="inlineStr"/>
+      <c r="E32" s="101" t="inlineStr"/>
+      <c r="F32" s="101" t="inlineStr"/>
+      <c r="G32" s="101" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="95" t="inlineStr">
+      <c r="A33" s="99" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="B33" s="95" t="inlineStr">
+      <c r="B33" s="99" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1907,22 +1847,22 @@
           <t>Manifestazioni di interessePR FESR SICILIA 2021/27 - NUOVO Avviso a manifestazione d’interesse per esperti valutatoriScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D33" s="96" t="inlineStr">
+      <c r="D33" s="100" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/pr-fesr-sicilia-202127-nuovo-avviso-manifestazione-d-interesse-esperti-valutatori</t>
         </is>
       </c>
-      <c r="E33" s="95" t="inlineStr"/>
-      <c r="F33" s="95" t="inlineStr"/>
-      <c r="G33" s="95" t="inlineStr"/>
+      <c r="E33" s="99" t="inlineStr"/>
+      <c r="F33" s="99" t="inlineStr"/>
+      <c r="G33" s="99" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="97" t="inlineStr">
+      <c r="A34" s="101" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="B34" s="97" t="inlineStr">
+      <c r="B34" s="101" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -1932,22 +1872,22 @@
           <t>Bando 2026 per contributi dedicati alla manutenzione della rete dei percorsi escursionistici</t>
         </is>
       </c>
-      <c r="D34" s="98" t="inlineStr">
+      <c r="D34" s="102" t="inlineStr">
         <is>
           <t>https://ambiente.regione.emilia-romagna.it/it/parchi-natura2000/bandi/bando-2026-per-contributi-dedicati-alla-manutenzione-della-rete-dei-percorsi-escursionistici</t>
         </is>
       </c>
-      <c r="E34" s="97" t="inlineStr"/>
-      <c r="F34" s="97" t="inlineStr"/>
-      <c r="G34" s="97" t="inlineStr"/>
+      <c r="E34" s="101" t="inlineStr"/>
+      <c r="F34" s="101" t="inlineStr"/>
+      <c r="G34" s="101" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="95" t="inlineStr">
+      <c r="A35" s="99" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="B35" s="95" t="inlineStr">
+      <c r="B35" s="99" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1957,22 +1897,22 @@
           <t>Programma regionale in favore delle tradizioni storiche, artistiche, religiose e popolari (2026) – manifestazioni d’interesseApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D35" s="96" t="inlineStr">
+      <c r="D35" s="100" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/programma-regionale-in-favore-delle-tradizioni-storiche-artistiche-religiose-e-popolari-2026-manifestazioni-dinteresse/</t>
         </is>
       </c>
-      <c r="E35" s="95" t="inlineStr"/>
-      <c r="F35" s="95" t="inlineStr"/>
-      <c r="G35" s="95" t="inlineStr"/>
+      <c r="E35" s="99" t="inlineStr"/>
+      <c r="F35" s="99" t="inlineStr"/>
+      <c r="G35" s="99" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="97" t="inlineStr">
+      <c r="A36" s="101" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B36" s="97" t="inlineStr">
+      <c r="B36" s="101" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1982,22 +1922,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEBuoni servizio per le persone non autosufficienti nel territorio del LazioProssima AperturaFSE / FSE+</t>
         </is>
       </c>
-      <c r="D36" s="98" t="inlineStr">
+      <c r="D36" s="102" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/buoni-servizio-per-le-persone-non-autosufficienti-nel-territorio-del-lazio/</t>
         </is>
       </c>
-      <c r="E36" s="97" t="inlineStr"/>
-      <c r="F36" s="97" t="inlineStr"/>
-      <c r="G36" s="97" t="inlineStr"/>
+      <c r="E36" s="101" t="inlineStr"/>
+      <c r="F36" s="101" t="inlineStr"/>
+      <c r="G36" s="101" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="95" t="inlineStr">
+      <c r="A37" s="99" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B37" s="95" t="inlineStr">
+      <c r="B37" s="99" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2007,22 +1947,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONERimborso delle rette dei servizi educativi nel territorio del LazioProssima AperturaFSE / FSE+</t>
         </is>
       </c>
-      <c r="D37" s="96" t="inlineStr">
+      <c r="D37" s="100" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/rimborso-delle-rette-dei-servizi-educativi-nel-territorio-del-lazio/</t>
         </is>
       </c>
-      <c r="E37" s="95" t="inlineStr"/>
-      <c r="F37" s="95" t="inlineStr"/>
-      <c r="G37" s="95" t="inlineStr"/>
+      <c r="E37" s="99" t="inlineStr"/>
+      <c r="F37" s="99" t="inlineStr"/>
+      <c r="G37" s="99" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="97" t="inlineStr">
+      <c r="A38" s="101" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B38" s="97" t="inlineStr">
+      <c r="B38" s="101" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2032,30 +1972,30 @@
           <t>Manifestazioni di interesseATTO DI INTERPELLO PER L’AFFIDAMENTO DELL’INCARICO DI COLLAUDO STATICO DELLE STRUTTURE - Diga di Pietrarossa (Progetto ex C</t>
         </is>
       </c>
-      <c r="D38" s="98" t="inlineStr">
+      <c r="D38" s="102" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/atto-interpello-l-affidamento-incarico-collaudo-statico-strutture-diga-pietrarossa-progetto-ex-casmez-303219</t>
         </is>
       </c>
-      <c r="E38" s="97" t="inlineStr">
+      <c r="E38" s="101" t="inlineStr">
         <is>
           <t>27/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F38" s="97" t="inlineStr">
+      <c r="F38" s="101" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="G38" s="97" t="inlineStr"/>
+      <c r="G38" s="101" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="95" t="inlineStr">
+      <c r="A39" s="99" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B39" s="95" t="inlineStr">
+      <c r="B39" s="99" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2065,30 +2005,30 @@
           <t>Manifestazioni di interesseAvviso alle Case  Editrici della Regione siciliana per la partecipazione al Salone del Libro di Torino, 14-18  maggio 2026.</t>
         </is>
       </c>
-      <c r="D39" s="96" t="inlineStr">
+      <c r="D39" s="100" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/manifestazione-d-interesse-partecipare-al-xxxviii-salone-libro-torino-14-al-18-maggio-2026-attraverso-l-esposizione-pubblicazioni-presso-stand-assessorato-beni</t>
         </is>
       </c>
-      <c r="E39" s="95" t="inlineStr">
+      <c r="E39" s="99" t="inlineStr">
         <is>
           <t>30/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F39" s="95" t="inlineStr">
+      <c r="F39" s="99" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="G39" s="95" t="inlineStr"/>
+      <c r="G39" s="99" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="97" t="inlineStr">
+      <c r="A40" s="101" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B40" s="97" t="inlineStr">
+      <c r="B40" s="101" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2098,30 +2038,30 @@
           <t xml:space="preserve">Manifestazioni di interessePR FESR SICILIA 2021/27 - NUOVO Avviso a manifestazione d’interesse per esperti valutatoriScade il:06/04/2026 - 23:59Leggi </t>
         </is>
       </c>
-      <c r="D40" s="98" t="inlineStr">
+      <c r="D40" s="102" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/pr-fesr-sicilia-202127-nuovo-avviso-manifestazione-d-interesse-esperti-valutatori</t>
         </is>
       </c>
-      <c r="E40" s="97" t="inlineStr">
+      <c r="E40" s="101" t="inlineStr">
         <is>
           <t>06/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F40" s="97" t="inlineStr">
+      <c r="F40" s="101" t="inlineStr">
         <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="G40" s="97" t="inlineStr"/>
+      <c r="G40" s="101" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="95" t="inlineStr">
+      <c r="A41" s="99" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B41" s="95" t="inlineStr">
+      <c r="B41" s="99" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2131,22 +2071,22 @@
           <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D41" s="96" t="inlineStr">
+      <c r="D41" s="100" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
         </is>
       </c>
-      <c r="E41" s="95" t="inlineStr"/>
-      <c r="F41" s="95" t="inlineStr"/>
-      <c r="G41" s="95" t="inlineStr"/>
+      <c r="E41" s="99" t="inlineStr"/>
+      <c r="F41" s="99" t="inlineStr"/>
+      <c r="G41" s="99" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="97" t="inlineStr">
+      <c r="A42" s="101" t="inlineStr">
         <is>
           <t>24/03/2026</t>
         </is>
       </c>
-      <c r="B42" s="97" t="inlineStr">
+      <c r="B42" s="101" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2156,22 +2096,22 @@
           <t>GAL del Ducato - Promozione di fiere agroalimentari e delle filiere del cibo – Bando per Enti pubblici (DU AS 05B)</t>
         </is>
       </c>
-      <c r="D42" s="98" t="inlineStr">
+      <c r="D42" s="102" t="inlineStr">
         <is>
           <t>https://agricoltura.regione.emilia-romagna.it/sviluppo-rurale-23-27/opportunita/bandi-gal/2026/du_as05b-promozione-di-fiere-agroalimentari-e-delle-filiere-del-cibo-bando-per-enti-pubblici</t>
         </is>
       </c>
-      <c r="E42" s="97" t="inlineStr"/>
-      <c r="F42" s="97" t="inlineStr"/>
-      <c r="G42" s="97" t="inlineStr"/>
+      <c r="E42" s="101" t="inlineStr"/>
+      <c r="F42" s="101" t="inlineStr"/>
+      <c r="G42" s="101" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="95" t="inlineStr">
+      <c r="A43" s="99" t="inlineStr">
         <is>
           <t>24/03/2026</t>
         </is>
       </c>
-      <c r="B43" s="95" t="inlineStr">
+      <c r="B43" s="99" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2181,30 +2121,30 @@
           <t>Manifestazioni di interesseAVVISO PUBBLICO PER MANIFESTAZIONE DI INTERESSE FINALIZZATA ALL'ASSEGNAZIONE DI SPAZI ESPOSITIVI (CORNER GRATUITI) ALL'INTE</t>
         </is>
       </c>
-      <c r="D43" s="96" t="inlineStr">
+      <c r="D43" s="100" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-manifestazione-interesse-finalizzata-all-assegnazione-spazi-espositivi-corner-gratuiti-all-interno-stand-istituzionale-dsrt-manifestazione</t>
         </is>
       </c>
-      <c r="E43" s="95" t="inlineStr">
+      <c r="E43" s="99" t="inlineStr">
         <is>
           <t>30/03/2026 - 13:00</t>
         </is>
       </c>
-      <c r="F43" s="95" t="inlineStr">
+      <c r="F43" s="99" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G43" s="95" t="inlineStr"/>
+      <c r="G43" s="99" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="97" t="inlineStr">
+      <c r="A44" s="101" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B44" s="97" t="inlineStr">
+      <c r="B44" s="101" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2214,22 +2154,22 @@
           <t>Avviso per la concessione di contributi per eventi sportivi realizzati in Emilia-Romagna - Anno 2026</t>
         </is>
       </c>
-      <c r="D44" s="98" t="inlineStr">
+      <c r="D44" s="102" t="inlineStr">
         <is>
           <t>https://www.regione.emilia-romagna.it/sport/bandi/2026/bando-2026</t>
         </is>
       </c>
-      <c r="E44" s="97" t="inlineStr"/>
-      <c r="F44" s="97" t="inlineStr"/>
-      <c r="G44" s="97" t="inlineStr"/>
+      <c r="E44" s="101" t="inlineStr"/>
+      <c r="F44" s="101" t="inlineStr"/>
+      <c r="G44" s="101" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="95" t="inlineStr">
+      <c r="A45" s="99" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B45" s="95" t="inlineStr">
+      <c r="B45" s="99" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2239,22 +2179,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Street art 2026Prossima AperturaBandi Regionali</t>
         </is>
       </c>
-      <c r="D45" s="96" t="inlineStr">
+      <c r="D45" s="100" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lazio-street-art-2026/</t>
         </is>
       </c>
-      <c r="E45" s="95" t="inlineStr"/>
-      <c r="F45" s="95" t="inlineStr"/>
-      <c r="G45" s="95" t="inlineStr"/>
+      <c r="E45" s="99" t="inlineStr"/>
+      <c r="F45" s="99" t="inlineStr"/>
+      <c r="G45" s="99" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="97" t="inlineStr">
+      <c r="A46" s="101" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B46" s="97" t="inlineStr">
+      <c r="B46" s="101" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2264,30 +2204,30 @@
           <t>Manifestazioni di interesseManifestazione di interesse per la partecipazione all’evento “R2I Italy 2026” – Bologna, 12-13/05/2026Scade il:03/04/2026 -</t>
         </is>
       </c>
-      <c r="D46" s="98" t="inlineStr">
+      <c r="D46" s="102" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/manifestazione-interesse-partecipazione-all-evento-r2i-italy-2026-bologna-12-13052026</t>
         </is>
       </c>
-      <c r="E46" s="97" t="inlineStr">
+      <c r="E46" s="101" t="inlineStr">
         <is>
           <t>03/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F46" s="97" t="inlineStr">
+      <c r="F46" s="101" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="G46" s="97" t="inlineStr"/>
+      <c r="G46" s="101" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="95" t="inlineStr">
+      <c r="A47" s="99" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B47" s="95" t="inlineStr">
+      <c r="B47" s="99" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2297,30 +2237,30 @@
           <t>Manifestazioni di interesseST SIRACUSA - AVVISO PER MANIFESTAZIONE DI INTERESSE - Selezione di n. 5 unità di personale internoScade il:20/04/2026 - 12</t>
         </is>
       </c>
-      <c r="D47" s="96" t="inlineStr">
+      <c r="D47" s="100" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/24-marzo-2026-st-siracusa-avviso-manifestazione-interesse-selezione-n-5-unita-personale-interno</t>
         </is>
       </c>
-      <c r="E47" s="95" t="inlineStr">
+      <c r="E47" s="99" t="inlineStr">
         <is>
           <t>20/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F47" s="95" t="inlineStr">
+      <c r="F47" s="99" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="G47" s="95" t="inlineStr"/>
+      <c r="G47" s="99" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="97" t="inlineStr">
+      <c r="A48" s="101" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B48" s="97" t="inlineStr">
+      <c r="B48" s="101" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2330,30 +2270,30 @@
           <t>Avvisi pubbliciRevoca dell’avviso di concessione a titolo gratuito del 16.12.2025 inerente all’immobile di seguito identificato e contestuale nuovo av</t>
         </is>
       </c>
-      <c r="D48" s="98" t="inlineStr">
+      <c r="D48" s="102" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/revoca-avviso-concessione-titolo-gratuito-16122025-inerente-all-immobile-seguito-identificato-contestuale-nuovo-avviso-concessione-titolo-oneroso-stesso-sito-nel</t>
         </is>
       </c>
-      <c r="E48" s="97" t="inlineStr">
+      <c r="E48" s="101" t="inlineStr">
         <is>
           <t>08/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F48" s="97" t="inlineStr">
+      <c r="F48" s="101" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="G48" s="97" t="inlineStr"/>
+      <c r="G48" s="101" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="95" t="inlineStr">
+      <c r="A49" s="99" t="inlineStr">
         <is>
           <t>26/03/2026</t>
         </is>
       </c>
-      <c r="B49" s="95" t="inlineStr">
+      <c r="B49" s="99" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2363,22 +2303,22 @@
           <t>Bando studi di fattibilità per fusioni di Comuni</t>
         </is>
       </c>
-      <c r="D49" s="96" t="inlineStr">
+      <c r="D49" s="100" t="inlineStr">
         <is>
           <t>https://www.regione.emilia-romagna.it/autonomie-locali/bandi/bando_studi_fattibilita_fusioni_comuni</t>
         </is>
       </c>
-      <c r="E49" s="95" t="inlineStr"/>
-      <c r="F49" s="95" t="inlineStr"/>
-      <c r="G49" s="95" t="inlineStr"/>
+      <c r="E49" s="99" t="inlineStr"/>
+      <c r="F49" s="99" t="inlineStr"/>
+      <c r="G49" s="99" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="97" t="inlineStr">
+      <c r="A50" s="101" t="inlineStr">
         <is>
           <t>26/03/2026</t>
         </is>
       </c>
-      <c r="B50" s="97" t="inlineStr">
+      <c r="B50" s="101" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2388,30 +2328,30 @@
           <t xml:space="preserve">Manifestazioni di interesseAvviso pubblico di selezione interna, per titoli, per il conferimento di PO e professionali, ai sensi degli artt. 19, 20 e </t>
         </is>
       </c>
-      <c r="D50" s="98" t="inlineStr">
+      <c r="D50" s="102" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-selezione-interna-titoli-conferimento-po-professionali-ai-sensi-artt-19-20-21-ccrl-20222024-comparto-non-dirigenziale</t>
         </is>
       </c>
-      <c r="E50" s="97" t="inlineStr">
+      <c r="E50" s="101" t="inlineStr">
         <is>
           <t>30/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F50" s="97" t="inlineStr">
+      <c r="F50" s="101" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G50" s="97" t="inlineStr"/>
+      <c r="G50" s="101" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="95" t="inlineStr">
+      <c r="A51" s="99" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="B51" s="95" t="inlineStr">
+      <c r="B51" s="99" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2421,22 +2361,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0PRE-SEED 3.0ApertoFESR</t>
         </is>
       </c>
-      <c r="D51" s="96" t="inlineStr">
+      <c r="D51" s="100" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/pre-seed-3-0/</t>
         </is>
       </c>
-      <c r="E51" s="95" t="inlineStr"/>
-      <c r="F51" s="95" t="inlineStr"/>
-      <c r="G51" s="95" t="inlineStr"/>
+      <c r="E51" s="99" t="inlineStr"/>
+      <c r="F51" s="99" t="inlineStr"/>
+      <c r="G51" s="99" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="97" t="inlineStr">
+      <c r="A52" s="101" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B52" s="97" t="inlineStr">
+      <c r="B52" s="101" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2446,30 +2386,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “So</t>
         </is>
       </c>
-      <c r="D52" s="98" t="inlineStr">
+      <c r="D52" s="102" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-termini-imerese-locta-piazza-marina</t>
         </is>
       </c>
-      <c r="E52" s="97" t="inlineStr">
+      <c r="E52" s="101" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F52" s="97" t="inlineStr">
+      <c r="F52" s="101" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G52" s="97" t="inlineStr"/>
+      <c r="G52" s="101" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="95" t="inlineStr">
+      <c r="A53" s="99" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B53" s="95" t="inlineStr">
+      <c r="B53" s="99" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2479,30 +2419,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, Sig</t>
         </is>
       </c>
-      <c r="D53" s="96" t="inlineStr">
+      <c r="D53" s="100" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-porto-empedocle-locta-punta-piccola</t>
         </is>
       </c>
-      <c r="E53" s="95" t="inlineStr">
+      <c r="E53" s="99" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F53" s="95" t="inlineStr">
+      <c r="F53" s="99" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G53" s="95" t="inlineStr"/>
+      <c r="G53" s="99" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="97" t="inlineStr">
+      <c r="A54" s="101" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B54" s="97" t="inlineStr">
+      <c r="B54" s="101" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2512,30 +2452,30 @@
           <t xml:space="preserve">Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “Società </t>
         </is>
       </c>
-      <c r="D54" s="98" t="inlineStr">
+      <c r="D54" s="102" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-messina-locta-torrente-bordonaro</t>
         </is>
       </c>
-      <c r="E54" s="97" t="inlineStr">
+      <c r="E54" s="101" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F54" s="97" t="inlineStr">
+      <c r="F54" s="101" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G54" s="97" t="inlineStr"/>
+      <c r="G54" s="101" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="95" t="inlineStr">
+      <c r="A55" s="99" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B55" s="95" t="inlineStr">
+      <c r="B55" s="99" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2545,30 +2485,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “Condomin</t>
         </is>
       </c>
-      <c r="D55" s="96" t="inlineStr">
+      <c r="D55" s="100" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-mascali-spiaggia-n-144150</t>
         </is>
       </c>
-      <c r="E55" s="95" t="inlineStr">
+      <c r="E55" s="99" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F55" s="95" t="inlineStr">
+      <c r="F55" s="99" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G55" s="95" t="inlineStr"/>
+      <c r="G55" s="99" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="97" t="inlineStr">
+      <c r="A56" s="101" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B56" s="97" t="inlineStr">
+      <c r="B56" s="101" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2578,30 +2518,30 @@
           <t xml:space="preserve">Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione sito nel Comune di Lipari, isola di Stromboli, </t>
         </is>
       </c>
-      <c r="D56" s="98" t="inlineStr">
+      <c r="D56" s="102" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-lipari-isola-stromboli-locta-fico-grande</t>
         </is>
       </c>
-      <c r="E56" s="97" t="inlineStr">
+      <c r="E56" s="101" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F56" s="97" t="inlineStr">
+      <c r="F56" s="101" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G56" s="97" t="inlineStr"/>
+      <c r="G56" s="101" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="95" t="inlineStr">
+      <c r="A57" s="99" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B57" s="95" t="inlineStr">
+      <c r="B57" s="99" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2611,30 +2551,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione sito nel Comune di Favignana, isola di Le</t>
         </is>
       </c>
-      <c r="D57" s="96" t="inlineStr">
+      <c r="D57" s="100" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-favignana-isola-levanzo</t>
         </is>
       </c>
-      <c r="E57" s="95" t="inlineStr">
+      <c r="E57" s="99" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F57" s="95" t="inlineStr">
+      <c r="F57" s="99" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G57" s="95" t="inlineStr"/>
+      <c r="G57" s="99" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="97" t="inlineStr">
+      <c r="A58" s="101" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="B58" s="97" t="inlineStr">
+      <c r="B58" s="101" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2644,30 +2584,30 @@
           <t>Manifestazioni di interesseAVVISO - Manifestazione d’interesse finalizzata alla selezione di organismi attuatori di piani di gestione locale della pic</t>
         </is>
       </c>
-      <c r="D58" s="98" t="inlineStr">
+      <c r="D58" s="102" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-d-interesse-finalizzata-alla-selezione-organismi-attuatori-piani-gestione-locale-piccola-pesca-costiera-nelle-gsa-regione-siciliana</t>
         </is>
       </c>
-      <c r="E58" s="97" t="inlineStr">
+      <c r="E58" s="101" t="inlineStr">
         <is>
           <t>29/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F58" s="97" t="inlineStr">
+      <c r="F58" s="101" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="G58" s="97" t="inlineStr"/>
+      <c r="G58" s="101" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="95" t="inlineStr">
+      <c r="A59" s="99" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="B59" s="95" t="inlineStr">
+      <c r="B59" s="99" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2677,30 +2617,30 @@
           <t>Avvisi pubbliciLeggi e scarica l'avvisoScade il:02/04/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D59" s="96" t="inlineStr">
+      <c r="D59" s="100" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/proroga-termini-presentazione-candidature-po</t>
         </is>
       </c>
-      <c r="E59" s="95" t="inlineStr">
+      <c r="E59" s="99" t="inlineStr">
         <is>
           <t>02/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F59" s="95" t="inlineStr">
+      <c r="F59" s="99" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="G59" s="95" t="inlineStr"/>
+      <c r="G59" s="99" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="97" t="inlineStr">
+      <c r="A60" s="101" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="97" t="inlineStr">
+      <c r="B60" s="101" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2710,22 +2650,22 @@
           <t>INTERNAZIONALIZZAZIONESMAU – Italy RestartsUp in STOCCOLMAApertoFESR</t>
         </is>
       </c>
-      <c r="D60" s="98" t="inlineStr">
+      <c r="D60" s="102" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/smau-italy-restartsup-in-stoccolma/</t>
         </is>
       </c>
-      <c r="E60" s="97" t="inlineStr"/>
-      <c r="F60" s="97" t="inlineStr"/>
-      <c r="G60" s="97" t="inlineStr"/>
+      <c r="E60" s="101" t="inlineStr"/>
+      <c r="F60" s="101" t="inlineStr"/>
+      <c r="G60" s="101" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="95" t="inlineStr">
+      <c r="A61" s="99" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B61" s="95" t="inlineStr">
+      <c r="B61" s="99" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2735,22 +2675,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per Farnborough International AirshowApertoFESR</t>
         </is>
       </c>
-      <c r="D61" s="96" t="inlineStr">
+      <c r="D61" s="100" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-farnborough-international-airshow-2/</t>
         </is>
       </c>
-      <c r="E61" s="95" t="inlineStr"/>
-      <c r="F61" s="95" t="inlineStr"/>
-      <c r="G61" s="95" t="inlineStr"/>
+      <c r="E61" s="99" t="inlineStr"/>
+      <c r="F61" s="99" t="inlineStr"/>
+      <c r="G61" s="99" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="97" t="inlineStr">
+      <c r="A62" s="101" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="97" t="inlineStr">
+      <c r="B62" s="101" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2760,30 +2700,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA - alienazione lotto di terreno sito nel comune di Termini Imerese, via LibertàScade il:30/04/2026 - 12:00Leg</t>
         </is>
       </c>
-      <c r="D62" s="98" t="inlineStr">
+      <c r="D62" s="102" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proprieta-regionale-sito-nel-comune-termini-imerese-favore-ares-fabiola</t>
         </is>
       </c>
-      <c r="E62" s="97" t="inlineStr">
+      <c r="E62" s="101" t="inlineStr">
         <is>
           <t>30/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F62" s="97" t="inlineStr">
+      <c r="F62" s="101" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="G62" s="97" t="inlineStr"/>
+      <c r="G62" s="101" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="95" t="inlineStr">
+      <c r="A63" s="99" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B63" s="95" t="inlineStr">
+      <c r="B63" s="99" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2793,22 +2733,22 @@
           <t>Avviso per la concessione di contributi per progetti di contrasto all'abbandono sportivo giovanile (2026)</t>
         </is>
       </c>
-      <c r="D63" s="96" t="inlineStr">
+      <c r="D63" s="100" t="inlineStr">
         <is>
           <t>https://www.regione.emilia-romagna.it/sport/bandi/2026/contrasto-abbandono-2026</t>
         </is>
       </c>
-      <c r="E63" s="95" t="inlineStr"/>
-      <c r="F63" s="95" t="inlineStr"/>
-      <c r="G63" s="95" t="inlineStr"/>
+      <c r="E63" s="99" t="inlineStr"/>
+      <c r="F63" s="99" t="inlineStr"/>
+      <c r="G63" s="99" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="97" t="inlineStr">
+      <c r="A64" s="101" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="97" t="inlineStr">
+      <c r="B64" s="101" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2818,30 +2758,30 @@
           <t>Avvisi pubbliciAvviso si procede alla riassegnazione della posizione organizzativa a supporto delle attività del Servizio 2 “Investimenti in Agricoltu</t>
         </is>
       </c>
-      <c r="D64" s="98" t="inlineStr">
+      <c r="D64" s="102" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-selezione-interna-conferimento-1-posizione-organizzativa-ai-sensi-artt-19-20-ccrl-2022-2024-comparto-non-dirigenziale</t>
         </is>
       </c>
-      <c r="E64" s="97" t="inlineStr">
+      <c r="E64" s="101" t="inlineStr">
         <is>
           <t>09/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F64" s="97" t="inlineStr">
+      <c r="F64" s="101" t="inlineStr">
         <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="G64" s="97" t="inlineStr"/>
+      <c r="G64" s="101" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="95" t="inlineStr">
+      <c r="A65" s="99" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B65" s="95" t="inlineStr">
+      <c r="B65" s="99" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2851,30 +2791,30 @@
           <t>Avvisi pubbliciST-MESSINA - AVVISO di INDAGINE DI MERCATO per affidamento "Interventi manutenzione straordinaria della strada/pista forestale "Annunzi</t>
         </is>
       </c>
-      <c r="D65" s="96" t="inlineStr">
+      <c r="D65" s="100" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-indagine-mercato-affidamento-interventi-manutenzione-straordinaria-stradapista-forestale-annunziata-comune-messina</t>
         </is>
       </c>
-      <c r="E65" s="95" t="inlineStr">
+      <c r="E65" s="99" t="inlineStr">
         <is>
           <t>16/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F65" s="95" t="inlineStr">
+      <c r="F65" s="99" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="G65" s="95" t="inlineStr"/>
+      <c r="G65" s="99" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="97" t="inlineStr">
+      <c r="A66" s="101" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="97" t="inlineStr">
+      <c r="B66" s="101" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2884,30 +2824,30 @@
           <t>Avvisi pubbliciST-MESSINA - AVVISO DI INDAGINE DI MERCATO per affidamento "Interventi manutenzione straordinaria della strada/pista forestale "San Riz</t>
         </is>
       </c>
-      <c r="D66" s="98" t="inlineStr">
+      <c r="D66" s="102" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-indagine-mercato-affidamento-interventi-manutenzione-straordinaria-stradapista-forestale-san-rizzo-san-leone-crupi-madonuzza-comune-messina</t>
         </is>
       </c>
-      <c r="E66" s="97" t="inlineStr">
+      <c r="E66" s="101" t="inlineStr">
         <is>
           <t>16/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F66" s="97" t="inlineStr">
+      <c r="F66" s="101" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="G66" s="97" t="inlineStr"/>
+      <c r="G66" s="101" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="95" t="inlineStr">
+      <c r="A67" s="99" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="95" t="inlineStr">
+      <c r="B67" s="99" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2917,22 +2857,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Manifestazione di interesse per Casaidea 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D67" s="96" t="inlineStr">
+      <c r="D67" s="100" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-casaidea-2026/</t>
         </is>
       </c>
-      <c r="E67" s="95" t="inlineStr"/>
-      <c r="F67" s="95" t="inlineStr"/>
-      <c r="G67" s="95" t="inlineStr"/>
+      <c r="E67" s="99" t="inlineStr"/>
+      <c r="F67" s="99" t="inlineStr"/>
+      <c r="G67" s="99" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="97" t="inlineStr">
+      <c r="A68" s="101" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="97" t="inlineStr">
+      <c r="B68" s="101" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2942,22 +2882,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per il Salone Internazionale del Libro di Torino 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D68" s="98" t="inlineStr">
+      <c r="D68" s="102" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-il-salone-internazionale-del-libro-di-torino-2026/</t>
         </is>
       </c>
-      <c r="E68" s="97" t="inlineStr"/>
-      <c r="F68" s="97" t="inlineStr"/>
-      <c r="G68" s="97" t="inlineStr"/>
+      <c r="E68" s="101" t="inlineStr"/>
+      <c r="F68" s="101" t="inlineStr"/>
+      <c r="G68" s="101" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="95" t="inlineStr">
+      <c r="A69" s="99" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="95" t="inlineStr">
+      <c r="B69" s="99" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2967,30 +2907,30 @@
           <t>Avvisi pubbliciDDG 1112 del 02.04.2026 - Aggiornamento Avviso pubblico n. 4/2024 per l’attuazione del PAR GOL Sicilia da finanziare nell’ambito del Pi</t>
         </is>
       </c>
-      <c r="D69" s="96" t="inlineStr">
+      <c r="D69" s="100" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/ddg-1112-02042026-aggiornamento-avviso-pubblico-n-42024-l-attuazione-par-gol-sicilia-finanziare-nell-ambito-piano-nazionale-ripresa-resilienza-pnrr</t>
         </is>
       </c>
-      <c r="E69" s="95" t="inlineStr">
+      <c r="E69" s="99" t="inlineStr">
         <is>
           <t>05/04/2030 - 00:00</t>
         </is>
       </c>
-      <c r="F69" s="95" t="inlineStr">
+      <c r="F69" s="99" t="inlineStr">
         <is>
           <t>05/04/2030</t>
         </is>
       </c>
-      <c r="G69" s="95" t="inlineStr"/>
+      <c r="G69" s="99" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="97" t="inlineStr">
+      <c r="A70" s="101" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="97" t="inlineStr">
+      <c r="B70" s="101" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3000,30 +2940,30 @@
           <t>Avvisi pubbliciDDG 1113 del  02.04.2026 - Aggiornamento Avviso pubblico n. 2/2022 e s.m.i per l’attuazione del PAR GOL Sicilia da finanziare nell’ambi</t>
         </is>
       </c>
-      <c r="D70" s="98" t="inlineStr">
+      <c r="D70" s="102" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/ddg-1113-02042026-aggiornamento-avviso-pubblico-n-22022-smi-l-attuazione-par-gol-sicilia-finanziare-nell-ambito-piano-nazionale-ripresa-resilienza-pnrr</t>
         </is>
       </c>
-      <c r="E70" s="97" t="inlineStr">
+      <c r="E70" s="101" t="inlineStr">
         <is>
           <t>03/04/2030 - 00:00</t>
         </is>
       </c>
-      <c r="F70" s="97" t="inlineStr">
+      <c r="F70" s="101" t="inlineStr">
         <is>
           <t>03/04/2030</t>
         </is>
       </c>
-      <c r="G70" s="97" t="inlineStr"/>
+      <c r="G70" s="101" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="95" t="inlineStr">
+      <c r="A71" s="99" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B71" s="95" t="inlineStr">
+      <c r="B71" s="99" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3033,22 +2973,22 @@
           <t>Avvisi pubbliciLeggi e scarica l'avvisoScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D71" s="96" t="inlineStr">
+      <c r="D71" s="100" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/proroga-termini-presentazione-candidature-po</t>
         </is>
       </c>
-      <c r="E71" s="95" t="inlineStr"/>
-      <c r="F71" s="95" t="inlineStr"/>
-      <c r="G71" s="95" t="inlineStr"/>
+      <c r="E71" s="99" t="inlineStr"/>
+      <c r="F71" s="99" t="inlineStr"/>
+      <c r="G71" s="99" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="97" t="inlineStr">
+      <c r="A72" s="101" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="97" t="inlineStr">
+      <c r="B72" s="101" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -3058,22 +2998,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEComunicare l’inclusione – contest per le istituzioni scolastiche regionaliApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D72" s="98" t="inlineStr">
+      <c r="D72" s="102" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/comunicare-linclusione-contest-per-le-istituzioni-scolastiche-regionali/</t>
         </is>
       </c>
-      <c r="E72" s="97" t="inlineStr"/>
-      <c r="F72" s="97" t="inlineStr"/>
-      <c r="G72" s="97" t="inlineStr"/>
+      <c r="E72" s="101" t="inlineStr"/>
+      <c r="F72" s="101" t="inlineStr"/>
+      <c r="G72" s="101" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="95" t="inlineStr">
+      <c r="A73" s="99" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B73" s="95" t="inlineStr">
+      <c r="B73" s="99" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3083,30 +3023,30 @@
           <t>Avvisi pubbliciAPPROVAZIONE AVVISO PUBBLICOScade il:03/04/2027 - 00:00Leggi di più</t>
         </is>
       </c>
-      <c r="D73" s="96" t="inlineStr">
+      <c r="D73" s="100" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/approvazione-avviso-pubblico</t>
         </is>
       </c>
-      <c r="E73" s="95" t="inlineStr">
+      <c r="E73" s="99" t="inlineStr">
         <is>
           <t>03/04/2027 - 00:00</t>
         </is>
       </c>
-      <c r="F73" s="95" t="inlineStr">
+      <c r="F73" s="99" t="inlineStr">
         <is>
           <t>03/04/2027</t>
         </is>
       </c>
-      <c r="G73" s="95" t="inlineStr"/>
+      <c r="G73" s="99" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="97" t="inlineStr">
+      <c r="A74" s="101" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="97" t="inlineStr">
+      <c r="B74" s="101" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -3116,22 +3056,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Donne e Impresa 2026Prossima AperturaFESR</t>
         </is>
       </c>
-      <c r="D74" s="98" t="inlineStr">
+      <c r="D74" s="102" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/donne-e-impresa-2026/</t>
         </is>
       </c>
-      <c r="E74" s="97" t="inlineStr"/>
-      <c r="F74" s="97" t="inlineStr"/>
-      <c r="G74" s="97" t="inlineStr"/>
+      <c r="E74" s="101" t="inlineStr"/>
+      <c r="F74" s="101" t="inlineStr"/>
+      <c r="G74" s="101" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="95" t="inlineStr">
+      <c r="A75" s="99" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B75" s="95" t="inlineStr">
+      <c r="B75" s="99" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3141,30 +3081,30 @@
           <t>Bandi di garaCodice Intervento 111302_FELUCHE - Investimenti a bordo e nei porti per incrementare la qualità delle produzioni e migliorare le condizio</t>
         </is>
       </c>
-      <c r="D75" s="96" t="inlineStr">
+      <c r="D75" s="100" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/bandoavviso-regia-ob-11-azione-3-codice-111302feluche-investimenti-bordo-valorizzazione-feluche-miglioramento-condizioni-lavoro-salute-sicurezza-operatori-l</t>
         </is>
       </c>
-      <c r="E75" s="95" t="inlineStr">
+      <c r="E75" s="99" t="inlineStr">
         <is>
           <t>02/07/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F75" s="95" t="inlineStr">
+      <c r="F75" s="99" t="inlineStr">
         <is>
           <t>02/07/2026</t>
         </is>
       </c>
-      <c r="G75" s="95" t="inlineStr"/>
+      <c r="G75" s="99" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="97" t="inlineStr">
+      <c r="A76" s="101" t="inlineStr">
         <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="97" t="inlineStr">
+      <c r="B76" s="101" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -3174,22 +3114,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURASostegno agli investimenti nel settore vitivinicolo – campagna 2026/2027ApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D76" s="98" t="inlineStr">
+      <c r="D76" s="102" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/sostegno-agli-investimenti-nel-settore-vitivinicolo-campagna-2026-2027/</t>
         </is>
       </c>
-      <c r="E76" s="97" t="inlineStr"/>
-      <c r="F76" s="97" t="inlineStr"/>
-      <c r="G76" s="97" t="inlineStr"/>
+      <c r="E76" s="101" t="inlineStr"/>
+      <c r="F76" s="101" t="inlineStr"/>
+      <c r="G76" s="101" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="95" t="inlineStr">
+      <c r="A77" s="99" t="inlineStr">
         <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="95" t="inlineStr">
+      <c r="B77" s="99" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3199,30 +3139,30 @@
           <t>Manifestazioni di interesse9 aprile 2026 -ST PALERMO- Manifestazione di interesse - “Interventi di manutenzione straordinaria della strada-pista fores</t>
         </is>
       </c>
-      <c r="D77" s="96" t="inlineStr">
+      <c r="D77" s="100" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/9-aprile-2026-st-palermo-manifestazione-interesse-interventi-manutenzione-straordinaria-strada-pista-forestale-monte-cane-comune-caccamo-pa-distretto-forestale</t>
         </is>
       </c>
-      <c r="E77" s="95" t="inlineStr">
+      <c r="E77" s="99" t="inlineStr">
         <is>
           <t>24/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F77" s="95" t="inlineStr">
+      <c r="F77" s="99" t="inlineStr">
         <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="G77" s="95" t="inlineStr"/>
+      <c r="G77" s="99" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="97" t="inlineStr">
+      <c r="A78" s="101" t="inlineStr">
         <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="97" t="inlineStr">
+      <c r="B78" s="101" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3232,30 +3172,30 @@
           <t>Avvisi pubbliciST-MESSINA - AVVISO DI INDAGINE DI MERCATO per affidamento "Interventi manutenzione straordinaria della strada/pista forestale "Faggita</t>
         </is>
       </c>
-      <c r="D78" s="98" t="inlineStr">
+      <c r="D78" s="102" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-indagine-mercato-affidamento-interventi-manutenzione-straordinaria-stradapista-forestale-faggita-comune-tripi-me</t>
         </is>
       </c>
-      <c r="E78" s="97" t="inlineStr">
+      <c r="E78" s="101" t="inlineStr">
         <is>
           <t>23/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F78" s="97" t="inlineStr">
+      <c r="F78" s="101" t="inlineStr">
         <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="G78" s="97" t="inlineStr"/>
+      <c r="G78" s="101" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="95" t="inlineStr">
+      <c r="A79" s="99" t="inlineStr">
         <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B79" s="95" t="inlineStr">
+      <c r="B79" s="99" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3265,30 +3205,30 @@
           <t>Avvisi pubbliciST-MESSINA - AVVISO DI INDAGINE DI MERCATO per affidamento "Interventi manutenzione straordinaria della strada/pista forestale "Ferraro</t>
         </is>
       </c>
-      <c r="D79" s="96" t="inlineStr">
+      <c r="D79" s="100" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-indagine-mercato-affidamento-interventi-manutenzione-straordinaria-stradapista-forestale-ferraro-sanrizzo-badiazza-comune-messina</t>
         </is>
       </c>
-      <c r="E79" s="95" t="inlineStr">
+      <c r="E79" s="99" t="inlineStr">
         <is>
           <t>23/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F79" s="95" t="inlineStr">
+      <c r="F79" s="99" t="inlineStr">
         <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="G79" s="95" t="inlineStr"/>
+      <c r="G79" s="99" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="97" t="inlineStr">
+      <c r="A80" s="101" t="inlineStr">
         <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="97" t="inlineStr">
+      <c r="B80" s="101" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -3298,22 +3238,22 @@
           <t>Comunicazione e informazioneAcquisizione di servizi di comunicazione e informazione – PR Lazio FESR, PR Lazio FSE+ e comunicazione unitariaApertoBandi</t>
         </is>
       </c>
-      <c r="D80" s="98" t="inlineStr">
+      <c r="D80" s="102" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/acquisizione-di-servizi-di-comunicazione-e-informazione-pr-lazio-fesr-pr-lazio-fse-e-comunicazione-unitaria/</t>
         </is>
       </c>
-      <c r="E80" s="97" t="inlineStr"/>
-      <c r="F80" s="97" t="inlineStr"/>
-      <c r="G80" s="97" t="inlineStr"/>
+      <c r="E80" s="101" t="inlineStr"/>
+      <c r="F80" s="101" t="inlineStr"/>
+      <c r="G80" s="101" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="95" t="inlineStr">
+      <c r="A81" s="99" t="inlineStr">
         <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B81" s="95" t="inlineStr">
+      <c r="B81" s="99" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3323,30 +3263,30 @@
           <t>Avvisi pubbliciAvviso pubblico di selezione interna, per titoli, per il conferimento, ai sensi degli artt. 21 del CCRL 2022-2024 del comparto non diri</t>
         </is>
       </c>
-      <c r="D81" s="96" t="inlineStr">
+      <c r="D81" s="100" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-selezione-interna-titoli-conferimento-ai-sensi-artt-21-ccrl-2022-2024-comparto-non-dirigenziale-una-posizione-organizzativa-dipartimento</t>
         </is>
       </c>
-      <c r="E81" s="95" t="inlineStr">
+      <c r="E81" s="99" t="inlineStr">
         <is>
           <t>16/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F81" s="95" t="inlineStr">
+      <c r="F81" s="99" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="G81" s="95" t="inlineStr"/>
+      <c r="G81" s="99" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="97" t="inlineStr">
+      <c r="A82" s="101" t="inlineStr">
         <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="97" t="inlineStr">
+      <c r="B82" s="101" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3356,30 +3296,30 @@
           <t xml:space="preserve">Avvisi pubbliciAVVISO DI INDAGINE DI MERCATO  per la partecipazione alla successiva procedura negoziata a norma dell'art. 50, comma 1, lettera c) del </t>
         </is>
       </c>
-      <c r="D82" s="98" t="inlineStr">
+      <c r="D82" s="102" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-indagine-mercato-partecipazione-alla-successiva-procedura-negoziata-norma-art-50-comma-1-lettera-c-dlgs-31-marzo-2023-n-36-ssmmii-finalizzata-all</t>
         </is>
       </c>
-      <c r="E82" s="97" t="inlineStr">
+      <c r="E82" s="101" t="inlineStr">
         <is>
           <t>30/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F82" s="97" t="inlineStr">
+      <c r="F82" s="101" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="G82" s="97" t="inlineStr"/>
+      <c r="G82" s="101" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="95" t="inlineStr">
+      <c r="A83" s="99" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="95" t="inlineStr">
+      <c r="B83" s="99" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -3389,22 +3329,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEVoucher per lo Sport – individuazione dei destinatari (II edizione)ApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D83" s="96" t="inlineStr">
+      <c r="D83" s="100" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/voucher-per-lo-sport-individuazione-dei-destinatari-ii-edizione/</t>
         </is>
       </c>
-      <c r="E83" s="95" t="inlineStr"/>
-      <c r="F83" s="95" t="inlineStr"/>
-      <c r="G83" s="95" t="inlineStr"/>
+      <c r="E83" s="99" t="inlineStr"/>
+      <c r="F83" s="99" t="inlineStr"/>
+      <c r="G83" s="99" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="97" t="inlineStr">
+      <c r="A84" s="101" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B84" s="97" t="inlineStr">
+      <c r="B84" s="101" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -3414,22 +3354,22 @@
           <t>CooperazioneManifestazione di interesse per partecipare a Codeway Expo 2026ApertoAltri fondiFESR</t>
         </is>
       </c>
-      <c r="D84" s="98" t="inlineStr">
+      <c r="D84" s="102" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-partecipare-a-codeway-expo-2026/</t>
         </is>
       </c>
-      <c r="E84" s="97" t="inlineStr"/>
-      <c r="F84" s="97" t="inlineStr"/>
-      <c r="G84" s="97" t="inlineStr"/>
+      <c r="E84" s="101" t="inlineStr"/>
+      <c r="F84" s="101" t="inlineStr"/>
+      <c r="G84" s="101" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="95" t="inlineStr">
+      <c r="A85" s="99" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B85" s="95" t="inlineStr">
+      <c r="B85" s="99" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -3439,22 +3379,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Street art 2026ApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D85" s="96" t="inlineStr">
+      <c r="D85" s="100" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lazio-street-art-2026/</t>
         </is>
       </c>
-      <c r="E85" s="95" t="inlineStr"/>
-      <c r="F85" s="95" t="inlineStr"/>
-      <c r="G85" s="95" t="inlineStr"/>
+      <c r="E85" s="99" t="inlineStr"/>
+      <c r="F85" s="99" t="inlineStr"/>
+      <c r="G85" s="99" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="97" t="inlineStr">
+      <c r="A86" s="101" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B86" s="97" t="inlineStr">
+      <c r="B86" s="101" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -3464,22 +3404,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEBuoni servizio per le persone non autosufficienti nel territorio del LazioApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D86" s="98" t="inlineStr">
+      <c r="D86" s="102" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/buoni-servizio-per-le-persone-non-autosufficienti-nel-territorio-del-lazio/</t>
         </is>
       </c>
-      <c r="E86" s="97" t="inlineStr"/>
-      <c r="F86" s="97" t="inlineStr"/>
-      <c r="G86" s="97" t="inlineStr"/>
+      <c r="E86" s="101" t="inlineStr"/>
+      <c r="F86" s="101" t="inlineStr"/>
+      <c r="G86" s="101" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="95" t="inlineStr">
+      <c r="A87" s="99" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B87" s="95" t="inlineStr">
+      <c r="B87" s="99" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3489,30 +3429,30 @@
           <t>Avvisi pubbliciSERVIZIO 14 SERVIZIO PER IL TERRITORIO DI PALERMO AVVISO PUBBLICO PER LA CONCESSIONE AL PASCOLO NEI TERRENI DEL DEMANIO FORESTALE REGIO</t>
         </is>
       </c>
-      <c r="D87" s="96" t="inlineStr">
+      <c r="D87" s="100" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-14-servizio-territorio-palermo-avviso-pubblico-concessione-al-pascolo-nei-terreni-demanio-forestale-regionale-gestiti-dipartimento-sviluppo-rurale</t>
         </is>
       </c>
-      <c r="E87" s="95" t="inlineStr">
+      <c r="E87" s="99" t="inlineStr">
         <is>
           <t>05/05/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F87" s="95" t="inlineStr">
+      <c r="F87" s="99" t="inlineStr">
         <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="G87" s="95" t="inlineStr"/>
+      <c r="G87" s="99" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="97" t="inlineStr">
+      <c r="A88" s="101" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B88" s="97" t="inlineStr">
+      <c r="B88" s="101" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3522,30 +3462,30 @@
           <t>Avvisi pubbliciAtto di interpello rivolto al personale del Comparto non dirigenziale per la designazione del  Consegnatario e del Vice Consegnatario d</t>
         </is>
       </c>
-      <c r="D88" s="98" t="inlineStr">
+      <c r="D88" s="102" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/atto-intepello-dipartimento-turismo-sport-spettacolo</t>
         </is>
       </c>
-      <c r="E88" s="97" t="inlineStr">
+      <c r="E88" s="101" t="inlineStr">
         <is>
           <t>30/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F88" s="97" t="inlineStr">
+      <c r="F88" s="101" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="G88" s="97" t="inlineStr"/>
+      <c r="G88" s="101" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="95" t="inlineStr">
+      <c r="A89" s="99" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B89" s="95" t="inlineStr">
+      <c r="B89" s="99" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3555,22 +3495,22 @@
           <t>Avvisi pubbliciAVVISO DI INDAGINE DI MERCATO - per la partecipazione alla successiva procedura negoziata a norma dell'art. 50, comma 1, lettera c) del</t>
         </is>
       </c>
-      <c r="D89" s="96" t="inlineStr">
+      <c r="D89" s="100" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-pa-avviso-indagine-mercato-partecipazione-alla-successiva-procedura-negoziata-norma-art-50-comma-1-lettera-c-dlgs-31-marzo-2023-n-36-ssmmii-finalizzata-all</t>
         </is>
       </c>
-      <c r="E89" s="95" t="inlineStr">
+      <c r="E89" s="99" t="inlineStr">
         <is>
           <t>02/05/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F89" s="95" t="inlineStr">
+      <c r="F89" s="99" t="inlineStr">
         <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="G89" s="95" t="inlineStr"/>
+      <c r="G89" s="99" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="101" t="inlineStr">
@@ -3712,6 +3652,72 @@
         </is>
       </c>
       <c r="G94" s="101" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="103" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="103" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>Manifestazioni di interesseIndividuazione delle Compagnie di Assicurazione disponibili a emettere polizze collettive e polizze individuali multirischi</t>
+        </is>
+      </c>
+      <c r="D95" s="104" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/polizze-collettive-polizze-individuali-multirischio-agricole-integrate-fondo-agricat-favore-agricoltori-siciliani-campagna-assicurativa-2026</t>
+        </is>
+      </c>
+      <c r="E95" s="103" t="inlineStr">
+        <is>
+          <t>29/04/2026 - 23:59</t>
+        </is>
+      </c>
+      <c r="F95" s="103" t="inlineStr">
+        <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="G95" s="103" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="105" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="105" t="inlineStr">
+        <is>
+          <t>Sicilia</t>
+        </is>
+      </c>
+      <c r="C96" s="9" t="inlineStr">
+        <is>
+          <t>Avvisi pubbliciST MESSINA - AVVISO PUBBLICO - MANIFESTAZIONE DI INTERESSE ALLA LICITAZIONE PRIVATA PER LA CONCESSIONE AL PASCOLO NEI TERRENI DEL DEMAN</t>
+        </is>
+      </c>
+      <c r="D96" s="106" t="inlineStr">
+        <is>
+          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-pubblico-manifestazione-interesse-alla-licitazione-privata-concessione-al-pascolo-nei-terreni-demanio-forestale-regionale-gestiti-dipartimento</t>
+        </is>
+      </c>
+      <c r="E96" s="105" t="inlineStr">
+        <is>
+          <t>28/04/2026 - 12:00</t>
+        </is>
+      </c>
+      <c r="F96" s="105" t="inlineStr">
+        <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="G96" s="105" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -3808,6 +3814,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D92" r:id="rId91"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D93" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D96" r:id="rId95"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3852,7 +3860,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="99" t="inlineStr">
+      <c r="A3" s="103" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -3865,7 +3873,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="101" t="inlineStr">
+      <c r="A4" s="105" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -3874,17 +3882,17 @@
         <v>38</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="99" t="inlineStr">
+      <c r="A5" s="103" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>2</v>

--- a/data/bandi_export.xlsx
+++ b/data/bandi_export.xlsx
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -432,6 +432,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -799,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -814,7 +823,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏛️  Nuovi Bandi — 18/04/2026 07:56</t>
+          <t>🏛️  Nuovi Bandi — 19/04/2026 08:03</t>
         </is>
       </c>
     </row>
@@ -859,63 +868,24 @@
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="103" t="inlineStr">
-        <is>
-          <t>Sicilia</t>
+      <c r="B3" s="107" t="inlineStr">
+        <is>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Manifestazioni di interesseIndividuazione delle Compagnie di Assicurazione disponibili a emettere polizze collettive e polizze individuali multirischi</t>
-        </is>
-      </c>
-      <c r="D3" s="104" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/polizze-collettive-polizze-individuali-multirischio-agricole-integrate-fondo-agricat-favore-agricoltori-siciliani-campagna-assicurativa-2026</t>
-        </is>
-      </c>
-      <c r="E3" s="103" t="inlineStr">
-        <is>
-          <t>29/04/2026 - 23:59</t>
-        </is>
-      </c>
-      <c r="F3" s="103" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
+          <t>Bando per la gestione e gli interventi di cura e salvaguardia degli alberi monumentali tutelati per l’annualità 2027</t>
+        </is>
+      </c>
+      <c r="D3" s="108" t="inlineStr">
+        <is>
+          <t>https://ambiente.regione.emilia-romagna.it/it/parchi-natura2000/bandi/bando-alberi-monumentali-annualita-2027</t>
+        </is>
+      </c>
+      <c r="E3" s="107" t="inlineStr"/>
+      <c r="F3" s="107" t="inlineStr"/>
       <c r="G3" s="5" t="inlineStr"/>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="105" t="inlineStr">
-        <is>
-          <t>Sicilia</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>Avvisi pubbliciST MESSINA - AVVISO PUBBLICO - MANIFESTAZIONE DI INTERESSE ALLA LICITAZIONE PRIVATA PER LA CONCESSIONE AL PASCOLO NEI TERRENI DEL DEMAN</t>
-        </is>
-      </c>
-      <c r="D4" s="106" t="inlineStr">
-        <is>
-          <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-pubblico-manifestazione-interesse-alla-licitazione-privata-concessione-al-pascolo-nei-terreni-demanio-forestale-regionale-gestiti-dipartimento</t>
-        </is>
-      </c>
-      <c r="E4" s="105" t="inlineStr">
-        <is>
-          <t>28/04/2026 - 12:00</t>
-        </is>
-      </c>
-      <c r="F4" s="105" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="G4" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -923,7 +893,6 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -935,7 +904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -985,12 +954,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="101" t="inlineStr">
+      <c r="A2" s="105" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B2" s="101" t="inlineStr">
+      <c r="B2" s="105" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -1000,22 +969,22 @@
           <t>FLAG GALPA Costa E-R. Sostituzione del motore principale e dei motori secondari. Secondo bando</t>
         </is>
       </c>
-      <c r="D2" s="102" t="inlineStr">
+      <c r="D2" s="106" t="inlineStr">
         <is>
           <t>https://agricoltura.regione.emilia-romagna.it/feampa-2021-2027/bandi-galpa/2026/galpa-sostituzione-motori-secondo-bando</t>
         </is>
       </c>
-      <c r="E2" s="101" t="inlineStr"/>
-      <c r="F2" s="101" t="inlineStr"/>
-      <c r="G2" s="101" t="inlineStr"/>
+      <c r="E2" s="105" t="inlineStr"/>
+      <c r="F2" s="105" t="inlineStr"/>
+      <c r="G2" s="105" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="99" t="inlineStr">
+      <c r="A3" s="103" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B3" s="99" t="inlineStr">
+      <c r="B3" s="103" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1025,22 +994,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0PRE-SEED 3.0Prossima AperturaFESR</t>
         </is>
       </c>
-      <c r="D3" s="100" t="inlineStr">
+      <c r="D3" s="104" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/pre-seed-3-0/</t>
         </is>
       </c>
-      <c r="E3" s="99" t="inlineStr"/>
-      <c r="F3" s="99" t="inlineStr"/>
-      <c r="G3" s="99" t="inlineStr"/>
+      <c r="E3" s="103" t="inlineStr"/>
+      <c r="F3" s="103" t="inlineStr"/>
+      <c r="G3" s="103" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="101" t="inlineStr">
+      <c r="A4" s="105" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B4" s="101" t="inlineStr">
+      <c r="B4" s="105" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1050,22 +1019,22 @@
           <t>ACCESSO AL CREDITO E ALLE GARANZIE PER LE IMPRESEContributo su finanziamenti alle imprese del Lazio erogati su provvista BEIProssima AperturaFESR</t>
         </is>
       </c>
-      <c r="D4" s="102" t="inlineStr">
+      <c r="D4" s="106" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-su-finanziamenti-alle-imprese-del-lazio-erogati-su-provvista-bei/</t>
         </is>
       </c>
-      <c r="E4" s="101" t="inlineStr"/>
-      <c r="F4" s="101" t="inlineStr"/>
-      <c r="G4" s="101" t="inlineStr"/>
+      <c r="E4" s="105" t="inlineStr"/>
+      <c r="F4" s="105" t="inlineStr"/>
+      <c r="G4" s="105" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="99" t="inlineStr">
+      <c r="A5" s="103" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B5" s="99" t="inlineStr">
+      <c r="B5" s="103" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1075,22 +1044,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEIndividuazione degli enti iscritti al Registro unico nazionale del Terzo settoreApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D5" s="100" t="inlineStr">
+      <c r="D5" s="104" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/individuazione-degli-enti-iscritti-al-registro-unico-nazionale-del-terzo-settore/</t>
         </is>
       </c>
-      <c r="E5" s="99" t="inlineStr"/>
-      <c r="F5" s="99" t="inlineStr"/>
-      <c r="G5" s="99" t="inlineStr"/>
+      <c r="E5" s="103" t="inlineStr"/>
+      <c r="F5" s="103" t="inlineStr"/>
+      <c r="G5" s="103" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="101" t="inlineStr">
+      <c r="A6" s="105" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B6" s="101" t="inlineStr">
+      <c r="B6" s="105" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1100,22 +1069,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Technology Transfer LazioApertoFESR</t>
         </is>
       </c>
-      <c r="D6" s="102" t="inlineStr">
+      <c r="D6" s="106" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/technology-transfer-lazio/</t>
         </is>
       </c>
-      <c r="E6" s="101" t="inlineStr"/>
-      <c r="F6" s="101" t="inlineStr"/>
-      <c r="G6" s="101" t="inlineStr"/>
+      <c r="E6" s="105" t="inlineStr"/>
+      <c r="F6" s="105" t="inlineStr"/>
+      <c r="G6" s="105" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="99" t="inlineStr">
+      <c r="A7" s="103" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B7" s="99" t="inlineStr">
+      <c r="B7" s="103" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1125,22 +1094,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Percorso di tutoraggio per le impreseApertoFESR</t>
         </is>
       </c>
-      <c r="D7" s="100" t="inlineStr">
+      <c r="D7" s="104" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/percorso-di-tutoraggio-per-le-imprese/</t>
         </is>
       </c>
-      <c r="E7" s="99" t="inlineStr"/>
-      <c r="F7" s="99" t="inlineStr"/>
-      <c r="G7" s="99" t="inlineStr"/>
+      <c r="E7" s="103" t="inlineStr"/>
+      <c r="F7" s="103" t="inlineStr"/>
+      <c r="G7" s="103" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="101" t="inlineStr">
+      <c r="A8" s="105" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B8" s="101" t="inlineStr">
+      <c r="B8" s="105" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1150,22 +1119,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per partecipare a SMAU Parigi 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D8" s="102" t="inlineStr">
+      <c r="D8" s="106" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-partecipare-a-smau-parigi-2026/</t>
         </is>
       </c>
-      <c r="E8" s="101" t="inlineStr"/>
-      <c r="F8" s="101" t="inlineStr"/>
-      <c r="G8" s="101" t="inlineStr"/>
+      <c r="E8" s="105" t="inlineStr"/>
+      <c r="F8" s="105" t="inlineStr"/>
+      <c r="G8" s="105" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="99" t="inlineStr">
+      <c r="A9" s="103" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B9" s="99" t="inlineStr">
+      <c r="B9" s="103" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1175,22 +1144,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONERiconoscimento della funzione sociale ed educativa degli oratoriApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D9" s="100" t="inlineStr">
+      <c r="D9" s="104" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/riconoscimento-della-funzione-sociale-ed-educativa-degli-oratori/</t>
         </is>
       </c>
-      <c r="E9" s="99" t="inlineStr"/>
-      <c r="F9" s="99" t="inlineStr"/>
-      <c r="G9" s="99" t="inlineStr"/>
+      <c r="E9" s="103" t="inlineStr"/>
+      <c r="F9" s="103" t="inlineStr"/>
+      <c r="G9" s="103" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="101" t="inlineStr">
+      <c r="A10" s="105" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B10" s="101" t="inlineStr">
+      <c r="B10" s="105" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1200,22 +1169,22 @@
           <t>GovernanceIscrizione nell’elenco regionale degli idonei all’esercizio dell’attività di direttore dell’Istituto JemoloApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D10" s="102" t="inlineStr">
+      <c r="D10" s="106" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/iscrizione-nellelenco-regionale-degli-idonei-allesercizio-dellattivita-di-direttore-dellistituto-jemolo/</t>
         </is>
       </c>
-      <c r="E10" s="101" t="inlineStr"/>
-      <c r="F10" s="101" t="inlineStr"/>
-      <c r="G10" s="101" t="inlineStr"/>
+      <c r="E10" s="105" t="inlineStr"/>
+      <c r="F10" s="105" t="inlineStr"/>
+      <c r="G10" s="105" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="99" t="inlineStr">
+      <c r="A11" s="103" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B11" s="99" t="inlineStr">
+      <c r="B11" s="103" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1225,22 +1194,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEVoucher per lo sport – seconda annualitàApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D11" s="100" t="inlineStr">
+      <c r="D11" s="104" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/voucher-per-lo-sport-seconda-annualita/</t>
         </is>
       </c>
-      <c r="E11" s="99" t="inlineStr"/>
-      <c r="F11" s="99" t="inlineStr"/>
-      <c r="G11" s="99" t="inlineStr"/>
+      <c r="E11" s="103" t="inlineStr"/>
+      <c r="F11" s="103" t="inlineStr"/>
+      <c r="G11" s="103" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="101" t="inlineStr">
+      <c r="A12" s="105" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B12" s="101" t="inlineStr">
+      <c r="B12" s="105" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1250,22 +1219,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEBonus occupazionale SALGOApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D12" s="102" t="inlineStr">
+      <c r="D12" s="106" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/bonus-occupazionale-salgo/</t>
         </is>
       </c>
-      <c r="E12" s="101" t="inlineStr"/>
-      <c r="F12" s="101" t="inlineStr"/>
-      <c r="G12" s="101" t="inlineStr"/>
+      <c r="E12" s="105" t="inlineStr"/>
+      <c r="F12" s="105" t="inlineStr"/>
+      <c r="G12" s="105" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="99" t="inlineStr">
+      <c r="A13" s="103" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B13" s="99" t="inlineStr">
+      <c r="B13" s="103" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1275,22 +1244,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEContributo di Libertà per le donne che hanno subito violenzaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D13" s="100" t="inlineStr">
+      <c r="D13" s="104" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-di-liberta-per-le-donne-che-hanno-subito-violenza/</t>
         </is>
       </c>
-      <c r="E13" s="99" t="inlineStr"/>
-      <c r="F13" s="99" t="inlineStr"/>
-      <c r="G13" s="99" t="inlineStr"/>
+      <c r="E13" s="103" t="inlineStr"/>
+      <c r="F13" s="103" t="inlineStr"/>
+      <c r="G13" s="103" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="101" t="inlineStr">
+      <c r="A14" s="105" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B14" s="101" t="inlineStr">
+      <c r="B14" s="105" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1300,22 +1269,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURAInterventi straordinari di valorizzazione del patrimonio culturale del LazioApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D14" s="102" t="inlineStr">
+      <c r="D14" s="106" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/interventi-straordinari-di-valorizzazione-del-patrimonio-culturale-del-lazio/</t>
         </is>
       </c>
-      <c r="E14" s="101" t="inlineStr"/>
-      <c r="F14" s="101" t="inlineStr"/>
-      <c r="G14" s="101" t="inlineStr"/>
+      <c r="E14" s="105" t="inlineStr"/>
+      <c r="F14" s="105" t="inlineStr"/>
+      <c r="G14" s="105" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="99" t="inlineStr">
+      <c r="A15" s="103" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B15" s="99" t="inlineStr">
+      <c r="B15" s="103" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1325,30 +1294,30 @@
           <t>Bandi di garaBANDO ATTUAZIONE Ob. 1.1 Azione 1 codice 111102 _DIV - "SOSTEGNO ALLA DIVERSIFICAZIONE E NUOVE FORME DI REDDITO PER LA PICCOLA PESCA COST</t>
         </is>
       </c>
-      <c r="D15" s="100" t="inlineStr">
+      <c r="D15" s="104" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/bando-avviso-regia-ob-11-azione-1-codice-111102-div-sostegno-alla-diversificazione-nuove-forme-reddito-piccola-pesca-costiera</t>
         </is>
       </c>
-      <c r="E15" s="99" t="inlineStr">
+      <c r="E15" s="103" t="inlineStr">
         <is>
           <t>07/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F15" s="99" t="inlineStr">
+      <c r="F15" s="103" t="inlineStr">
         <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="G15" s="99" t="inlineStr"/>
+      <c r="G15" s="103" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="101" t="inlineStr">
+      <c r="A16" s="105" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B16" s="101" t="inlineStr">
+      <c r="B16" s="105" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1358,30 +1327,30 @@
           <t>Avvisi pubblici09 marzo 2026 - ST SIRACUSA - AVVISO PUBBLICO PER LA COSTITUZIONE DI ELENCHI DI OPERATORI ECONOMICI PER L’ACQUISIZIONE DI BENI E SERVIZ</t>
         </is>
       </c>
-      <c r="D16" s="102" t="inlineStr">
+      <c r="D16" s="106" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/09-marzo-2026-st-siracusa-avviso-pubblico-costituzione-elenchi-operatori-economici-l-acquisizione-beni-servizi</t>
         </is>
       </c>
-      <c r="E16" s="101" t="inlineStr">
+      <c r="E16" s="105" t="inlineStr">
         <is>
           <t>31/12/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F16" s="101" t="inlineStr">
+      <c r="F16" s="105" t="inlineStr">
         <is>
           <t>31/12/2026</t>
         </is>
       </c>
-      <c r="G16" s="101" t="inlineStr"/>
+      <c r="G16" s="105" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="99" t="inlineStr">
+      <c r="A17" s="103" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B17" s="99" t="inlineStr">
+      <c r="B17" s="103" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1391,30 +1360,30 @@
           <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScade il:19/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D17" s="100" t="inlineStr">
+      <c r="D17" s="104" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
         </is>
       </c>
-      <c r="E17" s="99" t="inlineStr">
+      <c r="E17" s="103" t="inlineStr">
         <is>
           <t>19/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F17" s="99" t="inlineStr">
+      <c r="F17" s="103" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G17" s="99" t="inlineStr"/>
+      <c r="G17" s="103" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="101" t="inlineStr">
+      <c r="A18" s="105" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B18" s="101" t="inlineStr">
+      <c r="B18" s="105" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1424,22 +1393,22 @@
           <t>Manifestazioni di interesseAvviso Manifestazione Interesse DISTRIBUTORI AUTOMATICI di bevande e snackScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D18" s="102" t="inlineStr">
+      <c r="D18" s="106" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-distributori-automatici-bevande-snack</t>
         </is>
       </c>
-      <c r="E18" s="101" t="inlineStr"/>
-      <c r="F18" s="101" t="inlineStr"/>
-      <c r="G18" s="101" t="inlineStr"/>
+      <c r="E18" s="105" t="inlineStr"/>
+      <c r="F18" s="105" t="inlineStr"/>
+      <c r="G18" s="105" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="99" t="inlineStr">
+      <c r="A19" s="103" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B19" s="99" t="inlineStr">
+      <c r="B19" s="103" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1449,30 +1418,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D19" s="100" t="inlineStr">
+      <c r="D19" s="104" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo</t>
         </is>
       </c>
-      <c r="E19" s="99" t="inlineStr">
+      <c r="E19" s="103" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F19" s="99" t="inlineStr">
+      <c r="F19" s="103" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G19" s="99" t="inlineStr"/>
+      <c r="G19" s="103" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="101" t="inlineStr">
+      <c r="A20" s="105" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B20" s="101" t="inlineStr">
+      <c r="B20" s="105" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1482,30 +1451,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D20" s="102" t="inlineStr">
+      <c r="D20" s="106" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo-0</t>
         </is>
       </c>
-      <c r="E20" s="101" t="inlineStr">
+      <c r="E20" s="105" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F20" s="101" t="inlineStr">
+      <c r="F20" s="105" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G20" s="101" t="inlineStr"/>
+      <c r="G20" s="105" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="99" t="inlineStr">
+      <c r="A21" s="103" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B21" s="99" t="inlineStr">
+      <c r="B21" s="103" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1515,22 +1484,22 @@
           <t>Manifestazioni di interesseST SIRACUSA - AVVISO DI MANIFESTAZIONE DI INTERESSE - Fornitura applicativo extracontabile per la gestione progetti, ecc. e</t>
         </is>
       </c>
-      <c r="D21" s="100" t="inlineStr">
+      <c r="D21" s="104" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-siracusa-avviso-manifestazione-interesse-fornitura-applicativo-extracontabile-gestione-progetti-ecc-applicativo-gestione-ed-elaborazione-informatizzata-paghe</t>
         </is>
       </c>
-      <c r="E21" s="99" t="inlineStr"/>
-      <c r="F21" s="99" t="inlineStr"/>
-      <c r="G21" s="99" t="inlineStr"/>
+      <c r="E21" s="103" t="inlineStr"/>
+      <c r="F21" s="103" t="inlineStr"/>
+      <c r="G21" s="103" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="101" t="inlineStr">
+      <c r="A22" s="105" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B22" s="101" t="inlineStr">
+      <c r="B22" s="105" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1540,30 +1509,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile sito nel Comune di Capo D'Orlando, Via Trazzera MarinaScade il:25/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D22" s="102" t="inlineStr">
+      <c r="D22" s="106" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-sito-nel-comune-capo-d-orlando-trazzera-marina</t>
         </is>
       </c>
-      <c r="E22" s="101" t="inlineStr">
+      <c r="E22" s="105" t="inlineStr">
         <is>
           <t>25/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F22" s="101" t="inlineStr">
+      <c r="F22" s="105" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="G22" s="101" t="inlineStr"/>
+      <c r="G22" s="105" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="99" t="inlineStr">
+      <c r="A23" s="103" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B23" s="99" t="inlineStr">
+      <c r="B23" s="103" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1573,22 +1542,22 @@
           <t xml:space="preserve">Avvisi pubbliciST CATANIA - Programma Regionale FESR Sicilia 2021-2027 - Azione 2.4.4 - “Interventi per la riduzione del rischio incendi” - AVVISO DI </t>
         </is>
       </c>
-      <c r="D23" s="100" t="inlineStr">
+      <c r="D23" s="104" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-catania-programma-regionale-fesr-sicilia-2021-2027-azione-244-interventi-riduzione-rischio-incendi-avviso-indagine-mercato</t>
         </is>
       </c>
-      <c r="E23" s="99" t="inlineStr"/>
-      <c r="F23" s="99" t="inlineStr"/>
-      <c r="G23" s="99" t="inlineStr"/>
+      <c r="E23" s="103" t="inlineStr"/>
+      <c r="F23" s="103" t="inlineStr"/>
+      <c r="G23" s="103" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="101" t="inlineStr">
+      <c r="A24" s="105" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B24" s="101" t="inlineStr">
+      <c r="B24" s="105" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1598,22 +1567,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per ROMICS – Primavera 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D24" s="102" t="inlineStr">
+      <c r="D24" s="106" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-romics-primavera-2026/</t>
         </is>
       </c>
-      <c r="E24" s="101" t="inlineStr"/>
-      <c r="F24" s="101" t="inlineStr"/>
-      <c r="G24" s="101" t="inlineStr"/>
+      <c r="E24" s="105" t="inlineStr"/>
+      <c r="F24" s="105" t="inlineStr"/>
+      <c r="G24" s="105" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="99" t="inlineStr">
+      <c r="A25" s="103" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B25" s="99" t="inlineStr">
+      <c r="B25" s="103" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1623,22 +1592,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Cinema International 2026 – I edizioneApertoFESR</t>
         </is>
       </c>
-      <c r="D25" s="100" t="inlineStr">
+      <c r="D25" s="104" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lazio-cinema-international-2026-i-edizione/</t>
         </is>
       </c>
-      <c r="E25" s="99" t="inlineStr"/>
-      <c r="F25" s="99" t="inlineStr"/>
-      <c r="G25" s="99" t="inlineStr"/>
+      <c r="E25" s="103" t="inlineStr"/>
+      <c r="F25" s="103" t="inlineStr"/>
+      <c r="G25" s="103" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="101" t="inlineStr">
+      <c r="A26" s="105" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B26" s="101" t="inlineStr">
+      <c r="B26" s="105" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1648,22 +1617,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEManifestazioni di interesse alla costituzione di due nuove Fondazioni I.T.S. AcademyApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D26" s="102" t="inlineStr">
+      <c r="D26" s="106" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazioni-di-interesse-alla-costituzione-di-due-nuove-fondazioni-i-t-s-academy/</t>
         </is>
       </c>
-      <c r="E26" s="101" t="inlineStr"/>
-      <c r="F26" s="101" t="inlineStr"/>
-      <c r="G26" s="101" t="inlineStr"/>
+      <c r="E26" s="105" t="inlineStr"/>
+      <c r="F26" s="105" t="inlineStr"/>
+      <c r="G26" s="105" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="99" t="inlineStr">
+      <c r="A27" s="103" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B27" s="99" t="inlineStr">
+      <c r="B27" s="103" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1673,22 +1642,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURAContributi per sostenere la ripresa del settore della pescaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D27" s="100" t="inlineStr">
+      <c r="D27" s="104" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributi-per-sostenere-la-ripresa-del-settore-della-pesca/</t>
         </is>
       </c>
-      <c r="E27" s="99" t="inlineStr"/>
-      <c r="F27" s="99" t="inlineStr"/>
-      <c r="G27" s="99" t="inlineStr"/>
+      <c r="E27" s="103" t="inlineStr"/>
+      <c r="F27" s="103" t="inlineStr"/>
+      <c r="G27" s="103" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="101" t="inlineStr">
+      <c r="A28" s="105" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B28" s="101" t="inlineStr">
+      <c r="B28" s="105" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1698,30 +1667,30 @@
           <t>Manifestazioni di interesseAVVISO - Manifestazione Interesse “Storytelling aziendale” Expo Wild Natura - Caccia - Pesca. Misterbianco (CT), 10-12 apri</t>
         </is>
       </c>
-      <c r="D28" s="102" t="inlineStr">
+      <c r="D28" s="106" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-storytelling-aziendale-expo-wild-natura-caccia-pesca-misterbianco-ct-10-12-aprile-2026</t>
         </is>
       </c>
-      <c r="E28" s="101" t="inlineStr">
+      <c r="E28" s="105" t="inlineStr">
         <is>
           <t>30/03/2026 - 13:00</t>
         </is>
       </c>
-      <c r="F28" s="101" t="inlineStr">
+      <c r="F28" s="105" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G28" s="101" t="inlineStr"/>
+      <c r="G28" s="105" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="99" t="inlineStr">
+      <c r="A29" s="103" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B29" s="99" t="inlineStr">
+      <c r="B29" s="103" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1731,30 +1700,30 @@
           <t>Manifestazioni di interesseInvaso Lentini - Interventi di ripristino delle pareti esterne in cls della Torre di presa Sud e della trave d’appoggio del</t>
         </is>
       </c>
-      <c r="D29" s="100" t="inlineStr">
+      <c r="D29" s="104" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/invaso-lentini-interventi-ripristino-pareti-esterne-cls-torre-presa-sud-trave-d-appoggio-cavalcavia-collegamento-alla-stessa-torre</t>
         </is>
       </c>
-      <c r="E29" s="99" t="inlineStr">
+      <c r="E29" s="103" t="inlineStr">
         <is>
           <t>19/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F29" s="99" t="inlineStr">
+      <c r="F29" s="103" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G29" s="99" t="inlineStr"/>
+      <c r="G29" s="103" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="101" t="inlineStr">
+      <c r="A30" s="105" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="B30" s="101" t="inlineStr">
+      <c r="B30" s="105" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1764,22 +1733,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURARistrutturazione e riconversione vigneti – campagna 2026-2027ApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D30" s="102" t="inlineStr">
+      <c r="D30" s="106" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/ristrutturazione-e-riconversione-vigneti-campagna-2026-2027/</t>
         </is>
       </c>
-      <c r="E30" s="101" t="inlineStr"/>
-      <c r="F30" s="101" t="inlineStr"/>
-      <c r="G30" s="101" t="inlineStr"/>
+      <c r="E30" s="105" t="inlineStr"/>
+      <c r="F30" s="105" t="inlineStr"/>
+      <c r="G30" s="105" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="99" t="inlineStr">
+      <c r="A31" s="103" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="B31" s="99" t="inlineStr">
+      <c r="B31" s="103" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1789,30 +1758,30 @@
           <t>Manifestazioni di interessePR FESR 2021/27 Azione 1.3.3 e del POC 2014/20 - Azione 1.3.1  - Avviso a manifestazione d’interesse eventi fieristici inte</t>
         </is>
       </c>
-      <c r="D31" s="100" t="inlineStr">
+      <c r="D31" s="104" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-d-interesse-eventi-fieristici-internazionali-marzo-dicembre-2026</t>
         </is>
       </c>
-      <c r="E31" s="99" t="inlineStr">
+      <c r="E31" s="103" t="inlineStr">
         <is>
           <t>30/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F31" s="99" t="inlineStr">
+      <c r="F31" s="103" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="G31" s="99" t="inlineStr"/>
+      <c r="G31" s="103" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="101" t="inlineStr">
+      <c r="A32" s="105" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="B32" s="101" t="inlineStr">
+      <c r="B32" s="105" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1822,22 +1791,22 @@
           <t>INTERNAZIONALIZZAZIONEL’Ecosistema dell’Innovazione a INNOVIT – Focus S3ApertoFESR</t>
         </is>
       </c>
-      <c r="D32" s="102" t="inlineStr">
+      <c r="D32" s="106" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lecosistema-dellinnovazione-a-innovit-focus-s3/</t>
         </is>
       </c>
-      <c r="E32" s="101" t="inlineStr"/>
-      <c r="F32" s="101" t="inlineStr"/>
-      <c r="G32" s="101" t="inlineStr"/>
+      <c r="E32" s="105" t="inlineStr"/>
+      <c r="F32" s="105" t="inlineStr"/>
+      <c r="G32" s="105" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="99" t="inlineStr">
+      <c r="A33" s="103" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="B33" s="99" t="inlineStr">
+      <c r="B33" s="103" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1847,22 +1816,22 @@
           <t>Manifestazioni di interessePR FESR SICILIA 2021/27 - NUOVO Avviso a manifestazione d’interesse per esperti valutatoriScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D33" s="100" t="inlineStr">
+      <c r="D33" s="104" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/pr-fesr-sicilia-202127-nuovo-avviso-manifestazione-d-interesse-esperti-valutatori</t>
         </is>
       </c>
-      <c r="E33" s="99" t="inlineStr"/>
-      <c r="F33" s="99" t="inlineStr"/>
-      <c r="G33" s="99" t="inlineStr"/>
+      <c r="E33" s="103" t="inlineStr"/>
+      <c r="F33" s="103" t="inlineStr"/>
+      <c r="G33" s="103" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="101" t="inlineStr">
+      <c r="A34" s="105" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="B34" s="101" t="inlineStr">
+      <c r="B34" s="105" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -1872,22 +1841,22 @@
           <t>Bando 2026 per contributi dedicati alla manutenzione della rete dei percorsi escursionistici</t>
         </is>
       </c>
-      <c r="D34" s="102" t="inlineStr">
+      <c r="D34" s="106" t="inlineStr">
         <is>
           <t>https://ambiente.regione.emilia-romagna.it/it/parchi-natura2000/bandi/bando-2026-per-contributi-dedicati-alla-manutenzione-della-rete-dei-percorsi-escursionistici</t>
         </is>
       </c>
-      <c r="E34" s="101" t="inlineStr"/>
-      <c r="F34" s="101" t="inlineStr"/>
-      <c r="G34" s="101" t="inlineStr"/>
+      <c r="E34" s="105" t="inlineStr"/>
+      <c r="F34" s="105" t="inlineStr"/>
+      <c r="G34" s="105" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="99" t="inlineStr">
+      <c r="A35" s="103" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="B35" s="99" t="inlineStr">
+      <c r="B35" s="103" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1897,22 +1866,22 @@
           <t>Programma regionale in favore delle tradizioni storiche, artistiche, religiose e popolari (2026) – manifestazioni d’interesseApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D35" s="100" t="inlineStr">
+      <c r="D35" s="104" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/programma-regionale-in-favore-delle-tradizioni-storiche-artistiche-religiose-e-popolari-2026-manifestazioni-dinteresse/</t>
         </is>
       </c>
-      <c r="E35" s="99" t="inlineStr"/>
-      <c r="F35" s="99" t="inlineStr"/>
-      <c r="G35" s="99" t="inlineStr"/>
+      <c r="E35" s="103" t="inlineStr"/>
+      <c r="F35" s="103" t="inlineStr"/>
+      <c r="G35" s="103" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="101" t="inlineStr">
+      <c r="A36" s="105" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B36" s="101" t="inlineStr">
+      <c r="B36" s="105" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1922,22 +1891,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEBuoni servizio per le persone non autosufficienti nel territorio del LazioProssima AperturaFSE / FSE+</t>
         </is>
       </c>
-      <c r="D36" s="102" t="inlineStr">
+      <c r="D36" s="106" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/buoni-servizio-per-le-persone-non-autosufficienti-nel-territorio-del-lazio/</t>
         </is>
       </c>
-      <c r="E36" s="101" t="inlineStr"/>
-      <c r="F36" s="101" t="inlineStr"/>
-      <c r="G36" s="101" t="inlineStr"/>
+      <c r="E36" s="105" t="inlineStr"/>
+      <c r="F36" s="105" t="inlineStr"/>
+      <c r="G36" s="105" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="99" t="inlineStr">
+      <c r="A37" s="103" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B37" s="99" t="inlineStr">
+      <c r="B37" s="103" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1947,22 +1916,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONERimborso delle rette dei servizi educativi nel territorio del LazioProssima AperturaFSE / FSE+</t>
         </is>
       </c>
-      <c r="D37" s="100" t="inlineStr">
+      <c r="D37" s="104" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/rimborso-delle-rette-dei-servizi-educativi-nel-territorio-del-lazio/</t>
         </is>
       </c>
-      <c r="E37" s="99" t="inlineStr"/>
-      <c r="F37" s="99" t="inlineStr"/>
-      <c r="G37" s="99" t="inlineStr"/>
+      <c r="E37" s="103" t="inlineStr"/>
+      <c r="F37" s="103" t="inlineStr"/>
+      <c r="G37" s="103" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="101" t="inlineStr">
+      <c r="A38" s="105" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B38" s="101" t="inlineStr">
+      <c r="B38" s="105" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1972,30 +1941,30 @@
           <t>Manifestazioni di interesseATTO DI INTERPELLO PER L’AFFIDAMENTO DELL’INCARICO DI COLLAUDO STATICO DELLE STRUTTURE - Diga di Pietrarossa (Progetto ex C</t>
         </is>
       </c>
-      <c r="D38" s="102" t="inlineStr">
+      <c r="D38" s="106" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/atto-interpello-l-affidamento-incarico-collaudo-statico-strutture-diga-pietrarossa-progetto-ex-casmez-303219</t>
         </is>
       </c>
-      <c r="E38" s="101" t="inlineStr">
+      <c r="E38" s="105" t="inlineStr">
         <is>
           <t>27/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F38" s="101" t="inlineStr">
+      <c r="F38" s="105" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="G38" s="101" t="inlineStr"/>
+      <c r="G38" s="105" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="99" t="inlineStr">
+      <c r="A39" s="103" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B39" s="99" t="inlineStr">
+      <c r="B39" s="103" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2005,30 +1974,30 @@
           <t>Manifestazioni di interesseAvviso alle Case  Editrici della Regione siciliana per la partecipazione al Salone del Libro di Torino, 14-18  maggio 2026.</t>
         </is>
       </c>
-      <c r="D39" s="100" t="inlineStr">
+      <c r="D39" s="104" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/manifestazione-d-interesse-partecipare-al-xxxviii-salone-libro-torino-14-al-18-maggio-2026-attraverso-l-esposizione-pubblicazioni-presso-stand-assessorato-beni</t>
         </is>
       </c>
-      <c r="E39" s="99" t="inlineStr">
+      <c r="E39" s="103" t="inlineStr">
         <is>
           <t>30/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F39" s="99" t="inlineStr">
+      <c r="F39" s="103" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="G39" s="99" t="inlineStr"/>
+      <c r="G39" s="103" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="101" t="inlineStr">
+      <c r="A40" s="105" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B40" s="101" t="inlineStr">
+      <c r="B40" s="105" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2038,30 +2007,30 @@
           <t xml:space="preserve">Manifestazioni di interessePR FESR SICILIA 2021/27 - NUOVO Avviso a manifestazione d’interesse per esperti valutatoriScade il:06/04/2026 - 23:59Leggi </t>
         </is>
       </c>
-      <c r="D40" s="102" t="inlineStr">
+      <c r="D40" s="106" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/pr-fesr-sicilia-202127-nuovo-avviso-manifestazione-d-interesse-esperti-valutatori</t>
         </is>
       </c>
-      <c r="E40" s="101" t="inlineStr">
+      <c r="E40" s="105" t="inlineStr">
         <is>
           <t>06/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F40" s="101" t="inlineStr">
+      <c r="F40" s="105" t="inlineStr">
         <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="G40" s="101" t="inlineStr"/>
+      <c r="G40" s="105" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="99" t="inlineStr">
+      <c r="A41" s="103" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B41" s="99" t="inlineStr">
+      <c r="B41" s="103" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2071,22 +2040,22 @@
           <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D41" s="100" t="inlineStr">
+      <c r="D41" s="104" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
         </is>
       </c>
-      <c r="E41" s="99" t="inlineStr"/>
-      <c r="F41" s="99" t="inlineStr"/>
-      <c r="G41" s="99" t="inlineStr"/>
+      <c r="E41" s="103" t="inlineStr"/>
+      <c r="F41" s="103" t="inlineStr"/>
+      <c r="G41" s="103" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="101" t="inlineStr">
+      <c r="A42" s="105" t="inlineStr">
         <is>
           <t>24/03/2026</t>
         </is>
       </c>
-      <c r="B42" s="101" t="inlineStr">
+      <c r="B42" s="105" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2096,22 +2065,22 @@
           <t>GAL del Ducato - Promozione di fiere agroalimentari e delle filiere del cibo – Bando per Enti pubblici (DU AS 05B)</t>
         </is>
       </c>
-      <c r="D42" s="102" t="inlineStr">
+      <c r="D42" s="106" t="inlineStr">
         <is>
           <t>https://agricoltura.regione.emilia-romagna.it/sviluppo-rurale-23-27/opportunita/bandi-gal/2026/du_as05b-promozione-di-fiere-agroalimentari-e-delle-filiere-del-cibo-bando-per-enti-pubblici</t>
         </is>
       </c>
-      <c r="E42" s="101" t="inlineStr"/>
-      <c r="F42" s="101" t="inlineStr"/>
-      <c r="G42" s="101" t="inlineStr"/>
+      <c r="E42" s="105" t="inlineStr"/>
+      <c r="F42" s="105" t="inlineStr"/>
+      <c r="G42" s="105" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="99" t="inlineStr">
+      <c r="A43" s="103" t="inlineStr">
         <is>
           <t>24/03/2026</t>
         </is>
       </c>
-      <c r="B43" s="99" t="inlineStr">
+      <c r="B43" s="103" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2121,30 +2090,30 @@
           <t>Manifestazioni di interesseAVVISO PUBBLICO PER MANIFESTAZIONE DI INTERESSE FINALIZZATA ALL'ASSEGNAZIONE DI SPAZI ESPOSITIVI (CORNER GRATUITI) ALL'INTE</t>
         </is>
       </c>
-      <c r="D43" s="100" t="inlineStr">
+      <c r="D43" s="104" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-manifestazione-interesse-finalizzata-all-assegnazione-spazi-espositivi-corner-gratuiti-all-interno-stand-istituzionale-dsrt-manifestazione</t>
         </is>
       </c>
-      <c r="E43" s="99" t="inlineStr">
+      <c r="E43" s="103" t="inlineStr">
         <is>
           <t>30/03/2026 - 13:00</t>
         </is>
       </c>
-      <c r="F43" s="99" t="inlineStr">
+      <c r="F43" s="103" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G43" s="99" t="inlineStr"/>
+      <c r="G43" s="103" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="101" t="inlineStr">
+      <c r="A44" s="105" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B44" s="101" t="inlineStr">
+      <c r="B44" s="105" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2154,22 +2123,22 @@
           <t>Avviso per la concessione di contributi per eventi sportivi realizzati in Emilia-Romagna - Anno 2026</t>
         </is>
       </c>
-      <c r="D44" s="102" t="inlineStr">
+      <c r="D44" s="106" t="inlineStr">
         <is>
           <t>https://www.regione.emilia-romagna.it/sport/bandi/2026/bando-2026</t>
         </is>
       </c>
-      <c r="E44" s="101" t="inlineStr"/>
-      <c r="F44" s="101" t="inlineStr"/>
-      <c r="G44" s="101" t="inlineStr"/>
+      <c r="E44" s="105" t="inlineStr"/>
+      <c r="F44" s="105" t="inlineStr"/>
+      <c r="G44" s="105" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="99" t="inlineStr">
+      <c r="A45" s="103" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B45" s="99" t="inlineStr">
+      <c r="B45" s="103" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2179,22 +2148,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Street art 2026Prossima AperturaBandi Regionali</t>
         </is>
       </c>
-      <c r="D45" s="100" t="inlineStr">
+      <c r="D45" s="104" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lazio-street-art-2026/</t>
         </is>
       </c>
-      <c r="E45" s="99" t="inlineStr"/>
-      <c r="F45" s="99" t="inlineStr"/>
-      <c r="G45" s="99" t="inlineStr"/>
+      <c r="E45" s="103" t="inlineStr"/>
+      <c r="F45" s="103" t="inlineStr"/>
+      <c r="G45" s="103" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="101" t="inlineStr">
+      <c r="A46" s="105" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B46" s="101" t="inlineStr">
+      <c r="B46" s="105" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2204,30 +2173,30 @@
           <t>Manifestazioni di interesseManifestazione di interesse per la partecipazione all’evento “R2I Italy 2026” – Bologna, 12-13/05/2026Scade il:03/04/2026 -</t>
         </is>
       </c>
-      <c r="D46" s="102" t="inlineStr">
+      <c r="D46" s="106" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/manifestazione-interesse-partecipazione-all-evento-r2i-italy-2026-bologna-12-13052026</t>
         </is>
       </c>
-      <c r="E46" s="101" t="inlineStr">
+      <c r="E46" s="105" t="inlineStr">
         <is>
           <t>03/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F46" s="101" t="inlineStr">
+      <c r="F46" s="105" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="G46" s="101" t="inlineStr"/>
+      <c r="G46" s="105" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="99" t="inlineStr">
+      <c r="A47" s="103" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B47" s="99" t="inlineStr">
+      <c r="B47" s="103" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2237,30 +2206,30 @@
           <t>Manifestazioni di interesseST SIRACUSA - AVVISO PER MANIFESTAZIONE DI INTERESSE - Selezione di n. 5 unità di personale internoScade il:20/04/2026 - 12</t>
         </is>
       </c>
-      <c r="D47" s="100" t="inlineStr">
+      <c r="D47" s="104" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/24-marzo-2026-st-siracusa-avviso-manifestazione-interesse-selezione-n-5-unita-personale-interno</t>
         </is>
       </c>
-      <c r="E47" s="99" t="inlineStr">
+      <c r="E47" s="103" t="inlineStr">
         <is>
           <t>20/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F47" s="99" t="inlineStr">
+      <c r="F47" s="103" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="G47" s="99" t="inlineStr"/>
+      <c r="G47" s="103" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="101" t="inlineStr">
+      <c r="A48" s="105" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B48" s="101" t="inlineStr">
+      <c r="B48" s="105" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2270,30 +2239,30 @@
           <t>Avvisi pubbliciRevoca dell’avviso di concessione a titolo gratuito del 16.12.2025 inerente all’immobile di seguito identificato e contestuale nuovo av</t>
         </is>
       </c>
-      <c r="D48" s="102" t="inlineStr">
+      <c r="D48" s="106" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/revoca-avviso-concessione-titolo-gratuito-16122025-inerente-all-immobile-seguito-identificato-contestuale-nuovo-avviso-concessione-titolo-oneroso-stesso-sito-nel</t>
         </is>
       </c>
-      <c r="E48" s="101" t="inlineStr">
+      <c r="E48" s="105" t="inlineStr">
         <is>
           <t>08/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F48" s="101" t="inlineStr">
+      <c r="F48" s="105" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="G48" s="101" t="inlineStr"/>
+      <c r="G48" s="105" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="99" t="inlineStr">
+      <c r="A49" s="103" t="inlineStr">
         <is>
           <t>26/03/2026</t>
         </is>
       </c>
-      <c r="B49" s="99" t="inlineStr">
+      <c r="B49" s="103" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2303,22 +2272,22 @@
           <t>Bando studi di fattibilità per fusioni di Comuni</t>
         </is>
       </c>
-      <c r="D49" s="100" t="inlineStr">
+      <c r="D49" s="104" t="inlineStr">
         <is>
           <t>https://www.regione.emilia-romagna.it/autonomie-locali/bandi/bando_studi_fattibilita_fusioni_comuni</t>
         </is>
       </c>
-      <c r="E49" s="99" t="inlineStr"/>
-      <c r="F49" s="99" t="inlineStr"/>
-      <c r="G49" s="99" t="inlineStr"/>
+      <c r="E49" s="103" t="inlineStr"/>
+      <c r="F49" s="103" t="inlineStr"/>
+      <c r="G49" s="103" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="101" t="inlineStr">
+      <c r="A50" s="105" t="inlineStr">
         <is>
           <t>26/03/2026</t>
         </is>
       </c>
-      <c r="B50" s="101" t="inlineStr">
+      <c r="B50" s="105" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2328,30 +2297,30 @@
           <t xml:space="preserve">Manifestazioni di interesseAvviso pubblico di selezione interna, per titoli, per il conferimento di PO e professionali, ai sensi degli artt. 19, 20 e </t>
         </is>
       </c>
-      <c r="D50" s="102" t="inlineStr">
+      <c r="D50" s="106" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-selezione-interna-titoli-conferimento-po-professionali-ai-sensi-artt-19-20-21-ccrl-20222024-comparto-non-dirigenziale</t>
         </is>
       </c>
-      <c r="E50" s="101" t="inlineStr">
+      <c r="E50" s="105" t="inlineStr">
         <is>
           <t>30/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F50" s="101" t="inlineStr">
+      <c r="F50" s="105" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G50" s="101" t="inlineStr"/>
+      <c r="G50" s="105" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="99" t="inlineStr">
+      <c r="A51" s="103" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="B51" s="99" t="inlineStr">
+      <c r="B51" s="103" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2361,22 +2330,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0PRE-SEED 3.0ApertoFESR</t>
         </is>
       </c>
-      <c r="D51" s="100" t="inlineStr">
+      <c r="D51" s="104" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/pre-seed-3-0/</t>
         </is>
       </c>
-      <c r="E51" s="99" t="inlineStr"/>
-      <c r="F51" s="99" t="inlineStr"/>
-      <c r="G51" s="99" t="inlineStr"/>
+      <c r="E51" s="103" t="inlineStr"/>
+      <c r="F51" s="103" t="inlineStr"/>
+      <c r="G51" s="103" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="101" t="inlineStr">
+      <c r="A52" s="105" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B52" s="101" t="inlineStr">
+      <c r="B52" s="105" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2386,30 +2355,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “So</t>
         </is>
       </c>
-      <c r="D52" s="102" t="inlineStr">
+      <c r="D52" s="106" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-termini-imerese-locta-piazza-marina</t>
         </is>
       </c>
-      <c r="E52" s="101" t="inlineStr">
+      <c r="E52" s="105" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F52" s="101" t="inlineStr">
+      <c r="F52" s="105" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G52" s="101" t="inlineStr"/>
+      <c r="G52" s="105" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="99" t="inlineStr">
+      <c r="A53" s="103" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B53" s="99" t="inlineStr">
+      <c r="B53" s="103" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2419,30 +2388,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, Sig</t>
         </is>
       </c>
-      <c r="D53" s="100" t="inlineStr">
+      <c r="D53" s="104" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-porto-empedocle-locta-punta-piccola</t>
         </is>
       </c>
-      <c r="E53" s="99" t="inlineStr">
+      <c r="E53" s="103" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F53" s="99" t="inlineStr">
+      <c r="F53" s="103" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G53" s="99" t="inlineStr"/>
+      <c r="G53" s="103" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="101" t="inlineStr">
+      <c r="A54" s="105" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B54" s="101" t="inlineStr">
+      <c r="B54" s="105" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2452,30 +2421,30 @@
           <t xml:space="preserve">Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “Società </t>
         </is>
       </c>
-      <c r="D54" s="102" t="inlineStr">
+      <c r="D54" s="106" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-messina-locta-torrente-bordonaro</t>
         </is>
       </c>
-      <c r="E54" s="101" t="inlineStr">
+      <c r="E54" s="105" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F54" s="101" t="inlineStr">
+      <c r="F54" s="105" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G54" s="101" t="inlineStr"/>
+      <c r="G54" s="105" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="99" t="inlineStr">
+      <c r="A55" s="103" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B55" s="99" t="inlineStr">
+      <c r="B55" s="103" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2485,30 +2454,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “Condomin</t>
         </is>
       </c>
-      <c r="D55" s="100" t="inlineStr">
+      <c r="D55" s="104" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-mascali-spiaggia-n-144150</t>
         </is>
       </c>
-      <c r="E55" s="99" t="inlineStr">
+      <c r="E55" s="103" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F55" s="99" t="inlineStr">
+      <c r="F55" s="103" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G55" s="99" t="inlineStr"/>
+      <c r="G55" s="103" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="101" t="inlineStr">
+      <c r="A56" s="105" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B56" s="101" t="inlineStr">
+      <c r="B56" s="105" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2518,30 +2487,30 @@
           <t xml:space="preserve">Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione sito nel Comune di Lipari, isola di Stromboli, </t>
         </is>
       </c>
-      <c r="D56" s="102" t="inlineStr">
+      <c r="D56" s="106" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-lipari-isola-stromboli-locta-fico-grande</t>
         </is>
       </c>
-      <c r="E56" s="101" t="inlineStr">
+      <c r="E56" s="105" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F56" s="101" t="inlineStr">
+      <c r="F56" s="105" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G56" s="101" t="inlineStr"/>
+      <c r="G56" s="105" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="99" t="inlineStr">
+      <c r="A57" s="103" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B57" s="99" t="inlineStr">
+      <c r="B57" s="103" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2551,30 +2520,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione sito nel Comune di Favignana, isola di Le</t>
         </is>
       </c>
-      <c r="D57" s="100" t="inlineStr">
+      <c r="D57" s="104" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-favignana-isola-levanzo</t>
         </is>
       </c>
-      <c r="E57" s="99" t="inlineStr">
+      <c r="E57" s="103" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F57" s="99" t="inlineStr">
+      <c r="F57" s="103" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G57" s="99" t="inlineStr"/>
+      <c r="G57" s="103" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="101" t="inlineStr">
+      <c r="A58" s="105" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="B58" s="101" t="inlineStr">
+      <c r="B58" s="105" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2584,30 +2553,30 @@
           <t>Manifestazioni di interesseAVVISO - Manifestazione d’interesse finalizzata alla selezione di organismi attuatori di piani di gestione locale della pic</t>
         </is>
       </c>
-      <c r="D58" s="102" t="inlineStr">
+      <c r="D58" s="106" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-d-interesse-finalizzata-alla-selezione-organismi-attuatori-piani-gestione-locale-piccola-pesca-costiera-nelle-gsa-regione-siciliana</t>
         </is>
       </c>
-      <c r="E58" s="101" t="inlineStr">
+      <c r="E58" s="105" t="inlineStr">
         <is>
           <t>29/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F58" s="101" t="inlineStr">
+      <c r="F58" s="105" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="G58" s="101" t="inlineStr"/>
+      <c r="G58" s="105" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="99" t="inlineStr">
+      <c r="A59" s="103" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="B59" s="99" t="inlineStr">
+      <c r="B59" s="103" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2617,30 +2586,30 @@
           <t>Avvisi pubbliciLeggi e scarica l'avvisoScade il:02/04/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D59" s="100" t="inlineStr">
+      <c r="D59" s="104" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/proroga-termini-presentazione-candidature-po</t>
         </is>
       </c>
-      <c r="E59" s="99" t="inlineStr">
+      <c r="E59" s="103" t="inlineStr">
         <is>
           <t>02/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F59" s="99" t="inlineStr">
+      <c r="F59" s="103" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="G59" s="99" t="inlineStr"/>
+      <c r="G59" s="103" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="101" t="inlineStr">
+      <c r="A60" s="105" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="101" t="inlineStr">
+      <c r="B60" s="105" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2650,22 +2619,22 @@
           <t>INTERNAZIONALIZZAZIONESMAU – Italy RestartsUp in STOCCOLMAApertoFESR</t>
         </is>
       </c>
-      <c r="D60" s="102" t="inlineStr">
+      <c r="D60" s="106" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/smau-italy-restartsup-in-stoccolma/</t>
         </is>
       </c>
-      <c r="E60" s="101" t="inlineStr"/>
-      <c r="F60" s="101" t="inlineStr"/>
-      <c r="G60" s="101" t="inlineStr"/>
+      <c r="E60" s="105" t="inlineStr"/>
+      <c r="F60" s="105" t="inlineStr"/>
+      <c r="G60" s="105" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="99" t="inlineStr">
+      <c r="A61" s="103" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B61" s="99" t="inlineStr">
+      <c r="B61" s="103" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2675,22 +2644,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per Farnborough International AirshowApertoFESR</t>
         </is>
       </c>
-      <c r="D61" s="100" t="inlineStr">
+      <c r="D61" s="104" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-farnborough-international-airshow-2/</t>
         </is>
       </c>
-      <c r="E61" s="99" t="inlineStr"/>
-      <c r="F61" s="99" t="inlineStr"/>
-      <c r="G61" s="99" t="inlineStr"/>
+      <c r="E61" s="103" t="inlineStr"/>
+      <c r="F61" s="103" t="inlineStr"/>
+      <c r="G61" s="103" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="101" t="inlineStr">
+      <c r="A62" s="105" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="101" t="inlineStr">
+      <c r="B62" s="105" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2700,30 +2669,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA - alienazione lotto di terreno sito nel comune di Termini Imerese, via LibertàScade il:30/04/2026 - 12:00Leg</t>
         </is>
       </c>
-      <c r="D62" s="102" t="inlineStr">
+      <c r="D62" s="106" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proprieta-regionale-sito-nel-comune-termini-imerese-favore-ares-fabiola</t>
         </is>
       </c>
-      <c r="E62" s="101" t="inlineStr">
+      <c r="E62" s="105" t="inlineStr">
         <is>
           <t>30/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F62" s="101" t="inlineStr">
+      <c r="F62" s="105" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="G62" s="101" t="inlineStr"/>
+      <c r="G62" s="105" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="99" t="inlineStr">
+      <c r="A63" s="103" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B63" s="99" t="inlineStr">
+      <c r="B63" s="103" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2733,22 +2702,22 @@
           <t>Avviso per la concessione di contributi per progetti di contrasto all'abbandono sportivo giovanile (2026)</t>
         </is>
       </c>
-      <c r="D63" s="100" t="inlineStr">
+      <c r="D63" s="104" t="inlineStr">
         <is>
           <t>https://www.regione.emilia-romagna.it/sport/bandi/2026/contrasto-abbandono-2026</t>
         </is>
       </c>
-      <c r="E63" s="99" t="inlineStr"/>
-      <c r="F63" s="99" t="inlineStr"/>
-      <c r="G63" s="99" t="inlineStr"/>
+      <c r="E63" s="103" t="inlineStr"/>
+      <c r="F63" s="103" t="inlineStr"/>
+      <c r="G63" s="103" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="101" t="inlineStr">
+      <c r="A64" s="105" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="101" t="inlineStr">
+      <c r="B64" s="105" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2758,30 +2727,30 @@
           <t>Avvisi pubbliciAvviso si procede alla riassegnazione della posizione organizzativa a supporto delle attività del Servizio 2 “Investimenti in Agricoltu</t>
         </is>
       </c>
-      <c r="D64" s="102" t="inlineStr">
+      <c r="D64" s="106" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-selezione-interna-conferimento-1-posizione-organizzativa-ai-sensi-artt-19-20-ccrl-2022-2024-comparto-non-dirigenziale</t>
         </is>
       </c>
-      <c r="E64" s="101" t="inlineStr">
+      <c r="E64" s="105" t="inlineStr">
         <is>
           <t>09/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F64" s="101" t="inlineStr">
+      <c r="F64" s="105" t="inlineStr">
         <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="G64" s="101" t="inlineStr"/>
+      <c r="G64" s="105" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="99" t="inlineStr">
+      <c r="A65" s="103" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B65" s="99" t="inlineStr">
+      <c r="B65" s="103" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2791,30 +2760,30 @@
           <t>Avvisi pubbliciST-MESSINA - AVVISO di INDAGINE DI MERCATO per affidamento "Interventi manutenzione straordinaria della strada/pista forestale "Annunzi</t>
         </is>
       </c>
-      <c r="D65" s="100" t="inlineStr">
+      <c r="D65" s="104" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-indagine-mercato-affidamento-interventi-manutenzione-straordinaria-stradapista-forestale-annunziata-comune-messina</t>
         </is>
       </c>
-      <c r="E65" s="99" t="inlineStr">
+      <c r="E65" s="103" t="inlineStr">
         <is>
           <t>16/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F65" s="99" t="inlineStr">
+      <c r="F65" s="103" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="G65" s="99" t="inlineStr"/>
+      <c r="G65" s="103" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="101" t="inlineStr">
+      <c r="A66" s="105" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="101" t="inlineStr">
+      <c r="B66" s="105" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2824,30 +2793,30 @@
           <t>Avvisi pubbliciST-MESSINA - AVVISO DI INDAGINE DI MERCATO per affidamento "Interventi manutenzione straordinaria della strada/pista forestale "San Riz</t>
         </is>
       </c>
-      <c r="D66" s="102" t="inlineStr">
+      <c r="D66" s="106" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-indagine-mercato-affidamento-interventi-manutenzione-straordinaria-stradapista-forestale-san-rizzo-san-leone-crupi-madonuzza-comune-messina</t>
         </is>
       </c>
-      <c r="E66" s="101" t="inlineStr">
+      <c r="E66" s="105" t="inlineStr">
         <is>
           <t>16/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F66" s="101" t="inlineStr">
+      <c r="F66" s="105" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="G66" s="101" t="inlineStr"/>
+      <c r="G66" s="105" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="99" t="inlineStr">
+      <c r="A67" s="103" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="99" t="inlineStr">
+      <c r="B67" s="103" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2857,22 +2826,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Manifestazione di interesse per Casaidea 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D67" s="100" t="inlineStr">
+      <c r="D67" s="104" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-casaidea-2026/</t>
         </is>
       </c>
-      <c r="E67" s="99" t="inlineStr"/>
-      <c r="F67" s="99" t="inlineStr"/>
-      <c r="G67" s="99" t="inlineStr"/>
+      <c r="E67" s="103" t="inlineStr"/>
+      <c r="F67" s="103" t="inlineStr"/>
+      <c r="G67" s="103" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="101" t="inlineStr">
+      <c r="A68" s="105" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="101" t="inlineStr">
+      <c r="B68" s="105" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2882,22 +2851,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per il Salone Internazionale del Libro di Torino 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D68" s="102" t="inlineStr">
+      <c r="D68" s="106" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-il-salone-internazionale-del-libro-di-torino-2026/</t>
         </is>
       </c>
-      <c r="E68" s="101" t="inlineStr"/>
-      <c r="F68" s="101" t="inlineStr"/>
-      <c r="G68" s="101" t="inlineStr"/>
+      <c r="E68" s="105" t="inlineStr"/>
+      <c r="F68" s="105" t="inlineStr"/>
+      <c r="G68" s="105" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="99" t="inlineStr">
+      <c r="A69" s="103" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="99" t="inlineStr">
+      <c r="B69" s="103" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2907,30 +2876,30 @@
           <t>Avvisi pubbliciDDG 1112 del 02.04.2026 - Aggiornamento Avviso pubblico n. 4/2024 per l’attuazione del PAR GOL Sicilia da finanziare nell’ambito del Pi</t>
         </is>
       </c>
-      <c r="D69" s="100" t="inlineStr">
+      <c r="D69" s="104" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/ddg-1112-02042026-aggiornamento-avviso-pubblico-n-42024-l-attuazione-par-gol-sicilia-finanziare-nell-ambito-piano-nazionale-ripresa-resilienza-pnrr</t>
         </is>
       </c>
-      <c r="E69" s="99" t="inlineStr">
+      <c r="E69" s="103" t="inlineStr">
         <is>
           <t>05/04/2030 - 00:00</t>
         </is>
       </c>
-      <c r="F69" s="99" t="inlineStr">
+      <c r="F69" s="103" t="inlineStr">
         <is>
           <t>05/04/2030</t>
         </is>
       </c>
-      <c r="G69" s="99" t="inlineStr"/>
+      <c r="G69" s="103" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="101" t="inlineStr">
+      <c r="A70" s="105" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="101" t="inlineStr">
+      <c r="B70" s="105" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2940,30 +2909,30 @@
           <t>Avvisi pubbliciDDG 1113 del  02.04.2026 - Aggiornamento Avviso pubblico n. 2/2022 e s.m.i per l’attuazione del PAR GOL Sicilia da finanziare nell’ambi</t>
         </is>
       </c>
-      <c r="D70" s="102" t="inlineStr">
+      <c r="D70" s="106" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/ddg-1113-02042026-aggiornamento-avviso-pubblico-n-22022-smi-l-attuazione-par-gol-sicilia-finanziare-nell-ambito-piano-nazionale-ripresa-resilienza-pnrr</t>
         </is>
       </c>
-      <c r="E70" s="101" t="inlineStr">
+      <c r="E70" s="105" t="inlineStr">
         <is>
           <t>03/04/2030 - 00:00</t>
         </is>
       </c>
-      <c r="F70" s="101" t="inlineStr">
+      <c r="F70" s="105" t="inlineStr">
         <is>
           <t>03/04/2030</t>
         </is>
       </c>
-      <c r="G70" s="101" t="inlineStr"/>
+      <c r="G70" s="105" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="99" t="inlineStr">
+      <c r="A71" s="103" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B71" s="99" t="inlineStr">
+      <c r="B71" s="103" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2973,22 +2942,22 @@
           <t>Avvisi pubbliciLeggi e scarica l'avvisoScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D71" s="100" t="inlineStr">
+      <c r="D71" s="104" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/proroga-termini-presentazione-candidature-po</t>
         </is>
       </c>
-      <c r="E71" s="99" t="inlineStr"/>
-      <c r="F71" s="99" t="inlineStr"/>
-      <c r="G71" s="99" t="inlineStr"/>
+      <c r="E71" s="103" t="inlineStr"/>
+      <c r="F71" s="103" t="inlineStr"/>
+      <c r="G71" s="103" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="101" t="inlineStr">
+      <c r="A72" s="105" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="101" t="inlineStr">
+      <c r="B72" s="105" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2998,22 +2967,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEComunicare l’inclusione – contest per le istituzioni scolastiche regionaliApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D72" s="102" t="inlineStr">
+      <c r="D72" s="106" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/comunicare-linclusione-contest-per-le-istituzioni-scolastiche-regionali/</t>
         </is>
       </c>
-      <c r="E72" s="101" t="inlineStr"/>
-      <c r="F72" s="101" t="inlineStr"/>
-      <c r="G72" s="101" t="inlineStr"/>
+      <c r="E72" s="105" t="inlineStr"/>
+      <c r="F72" s="105" t="inlineStr"/>
+      <c r="G72" s="105" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="99" t="inlineStr">
+      <c r="A73" s="103" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B73" s="99" t="inlineStr">
+      <c r="B73" s="103" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3023,30 +2992,30 @@
           <t>Avvisi pubbliciAPPROVAZIONE AVVISO PUBBLICOScade il:03/04/2027 - 00:00Leggi di più</t>
         </is>
       </c>
-      <c r="D73" s="100" t="inlineStr">
+      <c r="D73" s="104" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/approvazione-avviso-pubblico</t>
         </is>
       </c>
-      <c r="E73" s="99" t="inlineStr">
+      <c r="E73" s="103" t="inlineStr">
         <is>
           <t>03/04/2027 - 00:00</t>
         </is>
       </c>
-      <c r="F73" s="99" t="inlineStr">
+      <c r="F73" s="103" t="inlineStr">
         <is>
           <t>03/04/2027</t>
         </is>
       </c>
-      <c r="G73" s="99" t="inlineStr"/>
+      <c r="G73" s="103" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="101" t="inlineStr">
+      <c r="A74" s="105" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="101" t="inlineStr">
+      <c r="B74" s="105" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -3056,22 +3025,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Donne e Impresa 2026Prossima AperturaFESR</t>
         </is>
       </c>
-      <c r="D74" s="102" t="inlineStr">
+      <c r="D74" s="106" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/donne-e-impresa-2026/</t>
         </is>
       </c>
-      <c r="E74" s="101" t="inlineStr"/>
-      <c r="F74" s="101" t="inlineStr"/>
-      <c r="G74" s="101" t="inlineStr"/>
+      <c r="E74" s="105" t="inlineStr"/>
+      <c r="F74" s="105" t="inlineStr"/>
+      <c r="G74" s="105" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="99" t="inlineStr">
+      <c r="A75" s="103" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B75" s="99" t="inlineStr">
+      <c r="B75" s="103" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3081,30 +3050,30 @@
           <t>Bandi di garaCodice Intervento 111302_FELUCHE - Investimenti a bordo e nei porti per incrementare la qualità delle produzioni e migliorare le condizio</t>
         </is>
       </c>
-      <c r="D75" s="100" t="inlineStr">
+      <c r="D75" s="104" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/bandoavviso-regia-ob-11-azione-3-codice-111302feluche-investimenti-bordo-valorizzazione-feluche-miglioramento-condizioni-lavoro-salute-sicurezza-operatori-l</t>
         </is>
       </c>
-      <c r="E75" s="99" t="inlineStr">
+      <c r="E75" s="103" t="inlineStr">
         <is>
           <t>02/07/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F75" s="99" t="inlineStr">
+      <c r="F75" s="103" t="inlineStr">
         <is>
           <t>02/07/2026</t>
         </is>
       </c>
-      <c r="G75" s="99" t="inlineStr"/>
+      <c r="G75" s="103" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="101" t="inlineStr">
+      <c r="A76" s="105" t="inlineStr">
         <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="101" t="inlineStr">
+      <c r="B76" s="105" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -3114,22 +3083,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURASostegno agli investimenti nel settore vitivinicolo – campagna 2026/2027ApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D76" s="102" t="inlineStr">
+      <c r="D76" s="106" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/sostegno-agli-investimenti-nel-settore-vitivinicolo-campagna-2026-2027/</t>
         </is>
       </c>
-      <c r="E76" s="101" t="inlineStr"/>
-      <c r="F76" s="101" t="inlineStr"/>
-      <c r="G76" s="101" t="inlineStr"/>
+      <c r="E76" s="105" t="inlineStr"/>
+      <c r="F76" s="105" t="inlineStr"/>
+      <c r="G76" s="105" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="99" t="inlineStr">
+      <c r="A77" s="103" t="inlineStr">
         <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="99" t="inlineStr">
+      <c r="B77" s="103" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3139,30 +3108,30 @@
           <t>Manifestazioni di interesse9 aprile 2026 -ST PALERMO- Manifestazione di interesse - “Interventi di manutenzione straordinaria della strada-pista fores</t>
         </is>
       </c>
-      <c r="D77" s="100" t="inlineStr">
+      <c r="D77" s="104" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/9-aprile-2026-st-palermo-manifestazione-interesse-interventi-manutenzione-straordinaria-strada-pista-forestale-monte-cane-comune-caccamo-pa-distretto-forestale</t>
         </is>
       </c>
-      <c r="E77" s="99" t="inlineStr">
+      <c r="E77" s="103" t="inlineStr">
         <is>
           <t>24/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F77" s="99" t="inlineStr">
+      <c r="F77" s="103" t="inlineStr">
         <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="G77" s="99" t="inlineStr"/>
+      <c r="G77" s="103" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="101" t="inlineStr">
+      <c r="A78" s="105" t="inlineStr">
         <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="101" t="inlineStr">
+      <c r="B78" s="105" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3172,30 +3141,30 @@
           <t>Avvisi pubbliciST-MESSINA - AVVISO DI INDAGINE DI MERCATO per affidamento "Interventi manutenzione straordinaria della strada/pista forestale "Faggita</t>
         </is>
       </c>
-      <c r="D78" s="102" t="inlineStr">
+      <c r="D78" s="106" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-indagine-mercato-affidamento-interventi-manutenzione-straordinaria-stradapista-forestale-faggita-comune-tripi-me</t>
         </is>
       </c>
-      <c r="E78" s="101" t="inlineStr">
+      <c r="E78" s="105" t="inlineStr">
         <is>
           <t>23/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F78" s="101" t="inlineStr">
+      <c r="F78" s="105" t="inlineStr">
         <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="G78" s="101" t="inlineStr"/>
+      <c r="G78" s="105" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="99" t="inlineStr">
+      <c r="A79" s="103" t="inlineStr">
         <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B79" s="99" t="inlineStr">
+      <c r="B79" s="103" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3205,30 +3174,30 @@
           <t>Avvisi pubbliciST-MESSINA - AVVISO DI INDAGINE DI MERCATO per affidamento "Interventi manutenzione straordinaria della strada/pista forestale "Ferraro</t>
         </is>
       </c>
-      <c r="D79" s="100" t="inlineStr">
+      <c r="D79" s="104" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-indagine-mercato-affidamento-interventi-manutenzione-straordinaria-stradapista-forestale-ferraro-sanrizzo-badiazza-comune-messina</t>
         </is>
       </c>
-      <c r="E79" s="99" t="inlineStr">
+      <c r="E79" s="103" t="inlineStr">
         <is>
           <t>23/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F79" s="99" t="inlineStr">
+      <c r="F79" s="103" t="inlineStr">
         <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="G79" s="99" t="inlineStr"/>
+      <c r="G79" s="103" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="101" t="inlineStr">
+      <c r="A80" s="105" t="inlineStr">
         <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="101" t="inlineStr">
+      <c r="B80" s="105" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -3238,22 +3207,22 @@
           <t>Comunicazione e informazioneAcquisizione di servizi di comunicazione e informazione – PR Lazio FESR, PR Lazio FSE+ e comunicazione unitariaApertoBandi</t>
         </is>
       </c>
-      <c r="D80" s="102" t="inlineStr">
+      <c r="D80" s="106" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/acquisizione-di-servizi-di-comunicazione-e-informazione-pr-lazio-fesr-pr-lazio-fse-e-comunicazione-unitaria/</t>
         </is>
       </c>
-      <c r="E80" s="101" t="inlineStr"/>
-      <c r="F80" s="101" t="inlineStr"/>
-      <c r="G80" s="101" t="inlineStr"/>
+      <c r="E80" s="105" t="inlineStr"/>
+      <c r="F80" s="105" t="inlineStr"/>
+      <c r="G80" s="105" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="99" t="inlineStr">
+      <c r="A81" s="103" t="inlineStr">
         <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B81" s="99" t="inlineStr">
+      <c r="B81" s="103" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3263,30 +3232,30 @@
           <t>Avvisi pubbliciAvviso pubblico di selezione interna, per titoli, per il conferimento, ai sensi degli artt. 21 del CCRL 2022-2024 del comparto non diri</t>
         </is>
       </c>
-      <c r="D81" s="100" t="inlineStr">
+      <c r="D81" s="104" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-selezione-interna-titoli-conferimento-ai-sensi-artt-21-ccrl-2022-2024-comparto-non-dirigenziale-una-posizione-organizzativa-dipartimento</t>
         </is>
       </c>
-      <c r="E81" s="99" t="inlineStr">
+      <c r="E81" s="103" t="inlineStr">
         <is>
           <t>16/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F81" s="99" t="inlineStr">
+      <c r="F81" s="103" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="G81" s="99" t="inlineStr"/>
+      <c r="G81" s="103" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="101" t="inlineStr">
+      <c r="A82" s="105" t="inlineStr">
         <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="101" t="inlineStr">
+      <c r="B82" s="105" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3296,30 +3265,30 @@
           <t xml:space="preserve">Avvisi pubbliciAVVISO DI INDAGINE DI MERCATO  per la partecipazione alla successiva procedura negoziata a norma dell'art. 50, comma 1, lettera c) del </t>
         </is>
       </c>
-      <c r="D82" s="102" t="inlineStr">
+      <c r="D82" s="106" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-indagine-mercato-partecipazione-alla-successiva-procedura-negoziata-norma-art-50-comma-1-lettera-c-dlgs-31-marzo-2023-n-36-ssmmii-finalizzata-all</t>
         </is>
       </c>
-      <c r="E82" s="101" t="inlineStr">
+      <c r="E82" s="105" t="inlineStr">
         <is>
           <t>30/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F82" s="101" t="inlineStr">
+      <c r="F82" s="105" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="G82" s="101" t="inlineStr"/>
+      <c r="G82" s="105" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="99" t="inlineStr">
+      <c r="A83" s="103" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="99" t="inlineStr">
+      <c r="B83" s="103" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -3329,22 +3298,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEVoucher per lo Sport – individuazione dei destinatari (II edizione)ApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D83" s="100" t="inlineStr">
+      <c r="D83" s="104" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/voucher-per-lo-sport-individuazione-dei-destinatari-ii-edizione/</t>
         </is>
       </c>
-      <c r="E83" s="99" t="inlineStr"/>
-      <c r="F83" s="99" t="inlineStr"/>
-      <c r="G83" s="99" t="inlineStr"/>
+      <c r="E83" s="103" t="inlineStr"/>
+      <c r="F83" s="103" t="inlineStr"/>
+      <c r="G83" s="103" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="101" t="inlineStr">
+      <c r="A84" s="105" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B84" s="101" t="inlineStr">
+      <c r="B84" s="105" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -3354,22 +3323,22 @@
           <t>CooperazioneManifestazione di interesse per partecipare a Codeway Expo 2026ApertoAltri fondiFESR</t>
         </is>
       </c>
-      <c r="D84" s="102" t="inlineStr">
+      <c r="D84" s="106" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-partecipare-a-codeway-expo-2026/</t>
         </is>
       </c>
-      <c r="E84" s="101" t="inlineStr"/>
-      <c r="F84" s="101" t="inlineStr"/>
-      <c r="G84" s="101" t="inlineStr"/>
+      <c r="E84" s="105" t="inlineStr"/>
+      <c r="F84" s="105" t="inlineStr"/>
+      <c r="G84" s="105" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="99" t="inlineStr">
+      <c r="A85" s="103" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B85" s="99" t="inlineStr">
+      <c r="B85" s="103" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -3379,22 +3348,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Street art 2026ApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D85" s="100" t="inlineStr">
+      <c r="D85" s="104" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lazio-street-art-2026/</t>
         </is>
       </c>
-      <c r="E85" s="99" t="inlineStr"/>
-      <c r="F85" s="99" t="inlineStr"/>
-      <c r="G85" s="99" t="inlineStr"/>
+      <c r="E85" s="103" t="inlineStr"/>
+      <c r="F85" s="103" t="inlineStr"/>
+      <c r="G85" s="103" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="101" t="inlineStr">
+      <c r="A86" s="105" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B86" s="101" t="inlineStr">
+      <c r="B86" s="105" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -3404,22 +3373,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEBuoni servizio per le persone non autosufficienti nel territorio del LazioApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D86" s="102" t="inlineStr">
+      <c r="D86" s="106" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/buoni-servizio-per-le-persone-non-autosufficienti-nel-territorio-del-lazio/</t>
         </is>
       </c>
-      <c r="E86" s="101" t="inlineStr"/>
-      <c r="F86" s="101" t="inlineStr"/>
-      <c r="G86" s="101" t="inlineStr"/>
+      <c r="E86" s="105" t="inlineStr"/>
+      <c r="F86" s="105" t="inlineStr"/>
+      <c r="G86" s="105" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="99" t="inlineStr">
+      <c r="A87" s="103" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B87" s="99" t="inlineStr">
+      <c r="B87" s="103" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3429,30 +3398,30 @@
           <t>Avvisi pubbliciSERVIZIO 14 SERVIZIO PER IL TERRITORIO DI PALERMO AVVISO PUBBLICO PER LA CONCESSIONE AL PASCOLO NEI TERRENI DEL DEMANIO FORESTALE REGIO</t>
         </is>
       </c>
-      <c r="D87" s="100" t="inlineStr">
+      <c r="D87" s="104" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-14-servizio-territorio-palermo-avviso-pubblico-concessione-al-pascolo-nei-terreni-demanio-forestale-regionale-gestiti-dipartimento-sviluppo-rurale</t>
         </is>
       </c>
-      <c r="E87" s="99" t="inlineStr">
+      <c r="E87" s="103" t="inlineStr">
         <is>
           <t>05/05/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F87" s="99" t="inlineStr">
+      <c r="F87" s="103" t="inlineStr">
         <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="G87" s="99" t="inlineStr"/>
+      <c r="G87" s="103" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="101" t="inlineStr">
+      <c r="A88" s="105" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B88" s="101" t="inlineStr">
+      <c r="B88" s="105" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3462,30 +3431,30 @@
           <t>Avvisi pubbliciAtto di interpello rivolto al personale del Comparto non dirigenziale per la designazione del  Consegnatario e del Vice Consegnatario d</t>
         </is>
       </c>
-      <c r="D88" s="102" t="inlineStr">
+      <c r="D88" s="106" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/atto-intepello-dipartimento-turismo-sport-spettacolo</t>
         </is>
       </c>
-      <c r="E88" s="101" t="inlineStr">
+      <c r="E88" s="105" t="inlineStr">
         <is>
           <t>30/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F88" s="101" t="inlineStr">
+      <c r="F88" s="105" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="G88" s="101" t="inlineStr"/>
+      <c r="G88" s="105" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="99" t="inlineStr">
+      <c r="A89" s="103" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B89" s="99" t="inlineStr">
+      <c r="B89" s="103" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3495,30 +3464,30 @@
           <t>Avvisi pubbliciAVVISO DI INDAGINE DI MERCATO - per la partecipazione alla successiva procedura negoziata a norma dell'art. 50, comma 1, lettera c) del</t>
         </is>
       </c>
-      <c r="D89" s="100" t="inlineStr">
+      <c r="D89" s="104" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-pa-avviso-indagine-mercato-partecipazione-alla-successiva-procedura-negoziata-norma-art-50-comma-1-lettera-c-dlgs-31-marzo-2023-n-36-ssmmii-finalizzata-all</t>
         </is>
       </c>
-      <c r="E89" s="99" t="inlineStr">
+      <c r="E89" s="103" t="inlineStr">
         <is>
           <t>02/05/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F89" s="99" t="inlineStr">
+      <c r="F89" s="103" t="inlineStr">
         <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="G89" s="99" t="inlineStr"/>
+      <c r="G89" s="103" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="101" t="inlineStr">
+      <c r="A90" s="105" t="inlineStr">
         <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B90" s="101" t="inlineStr">
+      <c r="B90" s="105" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -3528,22 +3497,22 @@
           <t>ACCESSO AL CREDITO E ALLE GARANZIE PER LE IMPRESEFondo Patrimonializzazione Pmi 2025 – Riapertura terminiProssima AperturaFESR</t>
         </is>
       </c>
-      <c r="D90" s="102" t="inlineStr">
+      <c r="D90" s="106" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/fondo-patrimonializzazione-pmi-riapertura-termini/</t>
         </is>
       </c>
-      <c r="E90" s="101" t="inlineStr"/>
-      <c r="F90" s="101" t="inlineStr"/>
-      <c r="G90" s="101" t="inlineStr"/>
+      <c r="E90" s="105" t="inlineStr"/>
+      <c r="F90" s="105" t="inlineStr"/>
+      <c r="G90" s="105" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="99" t="inlineStr">
+      <c r="A91" s="103" t="inlineStr">
         <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B91" s="99" t="inlineStr">
+      <c r="B91" s="103" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -3553,22 +3522,22 @@
           <t>ACCESSO AL CREDITO E ALLE GARANZIE PER LE IMPRESENuovo Fondo Piccolo Credito – sezione ordinaria (2026)Prossima AperturaFESRPOCRisorse regionali</t>
         </is>
       </c>
-      <c r="D91" s="100" t="inlineStr">
+      <c r="D91" s="104" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/nuovo-fondo-piccolo-credito-sezione-ordinaria-2026/</t>
         </is>
       </c>
-      <c r="E91" s="99" t="inlineStr"/>
-      <c r="F91" s="99" t="inlineStr"/>
-      <c r="G91" s="99" t="inlineStr"/>
+      <c r="E91" s="103" t="inlineStr"/>
+      <c r="F91" s="103" t="inlineStr"/>
+      <c r="G91" s="103" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="101" t="inlineStr">
+      <c r="A92" s="105" t="inlineStr">
         <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B92" s="101" t="inlineStr">
+      <c r="B92" s="105" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -3578,22 +3547,22 @@
           <t>ACCESSO AL CREDITO E ALLE GARANZIE PER LE IMPRESENuovo Fondo Futuro 2026Prossima AperturaFESRPOC</t>
         </is>
       </c>
-      <c r="D92" s="102" t="inlineStr">
+      <c r="D92" s="106" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/nuovo-fondo-futuro-2026/</t>
         </is>
       </c>
-      <c r="E92" s="101" t="inlineStr"/>
-      <c r="F92" s="101" t="inlineStr"/>
-      <c r="G92" s="101" t="inlineStr"/>
+      <c r="E92" s="105" t="inlineStr"/>
+      <c r="F92" s="105" t="inlineStr"/>
+      <c r="G92" s="105" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="99" t="inlineStr">
+      <c r="A93" s="103" t="inlineStr">
         <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B93" s="99" t="inlineStr">
+      <c r="B93" s="103" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3603,30 +3572,30 @@
           <t>Avvisi pubbliciAvviso pubblico di selezione interna, per titoli, per il conferimento, ai sensi degli artt. 19 e 20 del CCRL 2022-2024 del comparto non</t>
         </is>
       </c>
-      <c r="D93" s="100" t="inlineStr">
+      <c r="D93" s="104" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-selezione-interna-titoli-conferimento-ai-sensi-artt-19-20-ccrl-2022-2024-comparto-non-dirigenziale-posizioni-organizzative-dipartimento-regionale</t>
         </is>
       </c>
-      <c r="E93" s="99" t="inlineStr">
+      <c r="E93" s="103" t="inlineStr">
         <is>
           <t>24/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F93" s="99" t="inlineStr">
+      <c r="F93" s="103" t="inlineStr">
         <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="G93" s="99" t="inlineStr"/>
+      <c r="G93" s="103" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="101" t="inlineStr">
+      <c r="A94" s="105" t="inlineStr">
         <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B94" s="101" t="inlineStr">
+      <c r="B94" s="105" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3636,22 +3605,22 @@
           <t>Avvisi pubblici16 aprile 2026 - ST CATANIA - Avviso Concessione postazioni arnie - anno 2026Scade il:27/04/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D94" s="102" t="inlineStr">
+      <c r="D94" s="106" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/16-aprile-2026-st-catania-avviso-concessione-postazioni-arnie-anno-2026</t>
         </is>
       </c>
-      <c r="E94" s="101" t="inlineStr">
+      <c r="E94" s="105" t="inlineStr">
         <is>
           <t>27/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F94" s="101" t="inlineStr">
+      <c r="F94" s="105" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="G94" s="101" t="inlineStr"/>
+      <c r="G94" s="105" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="103" t="inlineStr">
@@ -3718,6 +3687,31 @@
         </is>
       </c>
       <c r="G96" s="105" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="107" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="107" t="inlineStr">
+        <is>
+          <t>Emilia-Romagna</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>Bando per la gestione e gli interventi di cura e salvaguardia degli alberi monumentali tutelati per l’annualità 2027</t>
+        </is>
+      </c>
+      <c r="D97" s="108" t="inlineStr">
+        <is>
+          <t>https://ambiente.regione.emilia-romagna.it/it/parchi-natura2000/bandi/bando-alberi-monumentali-annualita-2027</t>
+        </is>
+      </c>
+      <c r="E97" s="107" t="inlineStr"/>
+      <c r="F97" s="107" t="inlineStr"/>
+      <c r="G97" s="107" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -3816,6 +3810,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D94" r:id="rId93"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D95" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D97" r:id="rId96"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3860,20 +3855,20 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="103" t="inlineStr">
+      <c r="A3" s="107" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="105" t="inlineStr">
+      <c r="A4" s="109" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -3886,7 +3881,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="103" t="inlineStr">
+      <c r="A5" s="107" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3895,7 +3890,7 @@
         <v>51</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">

--- a/data/bandi_export.xlsx
+++ b/data/bandi_export.xlsx
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -441,6 +441,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -823,7 +835,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏛️  Nuovi Bandi — 19/04/2026 08:03</t>
+          <t>🏛️  Nuovi Bandi — 21/04/2026 08:29</t>
         </is>
       </c>
     </row>
@@ -868,23 +880,23 @@
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="107" t="inlineStr">
-        <is>
-          <t>Emilia-Romagna</t>
+      <c r="B3" s="110" t="inlineStr">
+        <is>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Bando per la gestione e gli interventi di cura e salvaguardia degli alberi monumentali tutelati per l’annualità 2027</t>
-        </is>
-      </c>
-      <c r="D3" s="108" t="inlineStr">
-        <is>
-          <t>https://ambiente.regione.emilia-romagna.it/it/parchi-natura2000/bandi/bando-alberi-monumentali-annualita-2027</t>
-        </is>
-      </c>
-      <c r="E3" s="107" t="inlineStr"/>
-      <c r="F3" s="107" t="inlineStr"/>
+          <t>CREATIVITÀ, CINEMA, TURISMO E CULTURAIscrizioni all’Albo regionale delle Rievocazioni storicheApertoBandi Regionali</t>
+        </is>
+      </c>
+      <c r="D3" s="111" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/iscrizioni-allalbo-regionale-delle-rievocazioni-storiche/</t>
+        </is>
+      </c>
+      <c r="E3" s="110" t="inlineStr"/>
+      <c r="F3" s="110" t="inlineStr"/>
       <c r="G3" s="5" t="inlineStr"/>
     </row>
   </sheetData>
@@ -904,7 +916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -954,12 +966,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="105" t="inlineStr">
+      <c r="A2" s="109" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B2" s="105" t="inlineStr">
+      <c r="B2" s="109" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -974,17 +986,17 @@
           <t>https://agricoltura.regione.emilia-romagna.it/feampa-2021-2027/bandi-galpa/2026/galpa-sostituzione-motori-secondo-bando</t>
         </is>
       </c>
-      <c r="E2" s="105" t="inlineStr"/>
-      <c r="F2" s="105" t="inlineStr"/>
-      <c r="G2" s="105" t="inlineStr"/>
+      <c r="E2" s="109" t="inlineStr"/>
+      <c r="F2" s="109" t="inlineStr"/>
+      <c r="G2" s="109" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="103" t="inlineStr">
+      <c r="A3" s="107" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B3" s="103" t="inlineStr">
+      <c r="B3" s="107" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -994,22 +1006,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0PRE-SEED 3.0Prossima AperturaFESR</t>
         </is>
       </c>
-      <c r="D3" s="104" t="inlineStr">
+      <c r="D3" s="108" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/pre-seed-3-0/</t>
         </is>
       </c>
-      <c r="E3" s="103" t="inlineStr"/>
-      <c r="F3" s="103" t="inlineStr"/>
-      <c r="G3" s="103" t="inlineStr"/>
+      <c r="E3" s="107" t="inlineStr"/>
+      <c r="F3" s="107" t="inlineStr"/>
+      <c r="G3" s="107" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="105" t="inlineStr">
+      <c r="A4" s="109" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B4" s="105" t="inlineStr">
+      <c r="B4" s="109" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1024,17 +1036,17 @@
           <t>https://www.lazioeuropa.it/bandi/contributo-su-finanziamenti-alle-imprese-del-lazio-erogati-su-provvista-bei/</t>
         </is>
       </c>
-      <c r="E4" s="105" t="inlineStr"/>
-      <c r="F4" s="105" t="inlineStr"/>
-      <c r="G4" s="105" t="inlineStr"/>
+      <c r="E4" s="109" t="inlineStr"/>
+      <c r="F4" s="109" t="inlineStr"/>
+      <c r="G4" s="109" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="103" t="inlineStr">
+      <c r="A5" s="107" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B5" s="103" t="inlineStr">
+      <c r="B5" s="107" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1044,22 +1056,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEIndividuazione degli enti iscritti al Registro unico nazionale del Terzo settoreApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D5" s="104" t="inlineStr">
+      <c r="D5" s="108" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/individuazione-degli-enti-iscritti-al-registro-unico-nazionale-del-terzo-settore/</t>
         </is>
       </c>
-      <c r="E5" s="103" t="inlineStr"/>
-      <c r="F5" s="103" t="inlineStr"/>
-      <c r="G5" s="103" t="inlineStr"/>
+      <c r="E5" s="107" t="inlineStr"/>
+      <c r="F5" s="107" t="inlineStr"/>
+      <c r="G5" s="107" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="105" t="inlineStr">
+      <c r="A6" s="109" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B6" s="105" t="inlineStr">
+      <c r="B6" s="109" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1074,17 +1086,17 @@
           <t>https://www.lazioeuropa.it/bandi/technology-transfer-lazio/</t>
         </is>
       </c>
-      <c r="E6" s="105" t="inlineStr"/>
-      <c r="F6" s="105" t="inlineStr"/>
-      <c r="G6" s="105" t="inlineStr"/>
+      <c r="E6" s="109" t="inlineStr"/>
+      <c r="F6" s="109" t="inlineStr"/>
+      <c r="G6" s="109" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="103" t="inlineStr">
+      <c r="A7" s="107" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B7" s="103" t="inlineStr">
+      <c r="B7" s="107" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1094,22 +1106,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Percorso di tutoraggio per le impreseApertoFESR</t>
         </is>
       </c>
-      <c r="D7" s="104" t="inlineStr">
+      <c r="D7" s="108" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/percorso-di-tutoraggio-per-le-imprese/</t>
         </is>
       </c>
-      <c r="E7" s="103" t="inlineStr"/>
-      <c r="F7" s="103" t="inlineStr"/>
-      <c r="G7" s="103" t="inlineStr"/>
+      <c r="E7" s="107" t="inlineStr"/>
+      <c r="F7" s="107" t="inlineStr"/>
+      <c r="G7" s="107" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="105" t="inlineStr">
+      <c r="A8" s="109" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B8" s="105" t="inlineStr">
+      <c r="B8" s="109" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1124,17 +1136,17 @@
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-partecipare-a-smau-parigi-2026/</t>
         </is>
       </c>
-      <c r="E8" s="105" t="inlineStr"/>
-      <c r="F8" s="105" t="inlineStr"/>
-      <c r="G8" s="105" t="inlineStr"/>
+      <c r="E8" s="109" t="inlineStr"/>
+      <c r="F8" s="109" t="inlineStr"/>
+      <c r="G8" s="109" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="103" t="inlineStr">
+      <c r="A9" s="107" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B9" s="103" t="inlineStr">
+      <c r="B9" s="107" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1144,22 +1156,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONERiconoscimento della funzione sociale ed educativa degli oratoriApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D9" s="104" t="inlineStr">
+      <c r="D9" s="108" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/riconoscimento-della-funzione-sociale-ed-educativa-degli-oratori/</t>
         </is>
       </c>
-      <c r="E9" s="103" t="inlineStr"/>
-      <c r="F9" s="103" t="inlineStr"/>
-      <c r="G9" s="103" t="inlineStr"/>
+      <c r="E9" s="107" t="inlineStr"/>
+      <c r="F9" s="107" t="inlineStr"/>
+      <c r="G9" s="107" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="105" t="inlineStr">
+      <c r="A10" s="109" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B10" s="105" t="inlineStr">
+      <c r="B10" s="109" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1174,17 +1186,17 @@
           <t>https://www.lazioeuropa.it/bandi/iscrizione-nellelenco-regionale-degli-idonei-allesercizio-dellattivita-di-direttore-dellistituto-jemolo/</t>
         </is>
       </c>
-      <c r="E10" s="105" t="inlineStr"/>
-      <c r="F10" s="105" t="inlineStr"/>
-      <c r="G10" s="105" t="inlineStr"/>
+      <c r="E10" s="109" t="inlineStr"/>
+      <c r="F10" s="109" t="inlineStr"/>
+      <c r="G10" s="109" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="103" t="inlineStr">
+      <c r="A11" s="107" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B11" s="103" t="inlineStr">
+      <c r="B11" s="107" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1194,22 +1206,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEVoucher per lo sport – seconda annualitàApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D11" s="104" t="inlineStr">
+      <c r="D11" s="108" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/voucher-per-lo-sport-seconda-annualita/</t>
         </is>
       </c>
-      <c r="E11" s="103" t="inlineStr"/>
-      <c r="F11" s="103" t="inlineStr"/>
-      <c r="G11" s="103" t="inlineStr"/>
+      <c r="E11" s="107" t="inlineStr"/>
+      <c r="F11" s="107" t="inlineStr"/>
+      <c r="G11" s="107" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="105" t="inlineStr">
+      <c r="A12" s="109" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B12" s="105" t="inlineStr">
+      <c r="B12" s="109" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1224,17 +1236,17 @@
           <t>https://www.lazioeuropa.it/bandi/bonus-occupazionale-salgo/</t>
         </is>
       </c>
-      <c r="E12" s="105" t="inlineStr"/>
-      <c r="F12" s="105" t="inlineStr"/>
-      <c r="G12" s="105" t="inlineStr"/>
+      <c r="E12" s="109" t="inlineStr"/>
+      <c r="F12" s="109" t="inlineStr"/>
+      <c r="G12" s="109" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="103" t="inlineStr">
+      <c r="A13" s="107" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B13" s="103" t="inlineStr">
+      <c r="B13" s="107" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1244,22 +1256,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEContributo di Libertà per le donne che hanno subito violenzaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D13" s="104" t="inlineStr">
+      <c r="D13" s="108" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-di-liberta-per-le-donne-che-hanno-subito-violenza/</t>
         </is>
       </c>
-      <c r="E13" s="103" t="inlineStr"/>
-      <c r="F13" s="103" t="inlineStr"/>
-      <c r="G13" s="103" t="inlineStr"/>
+      <c r="E13" s="107" t="inlineStr"/>
+      <c r="F13" s="107" t="inlineStr"/>
+      <c r="G13" s="107" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="105" t="inlineStr">
+      <c r="A14" s="109" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B14" s="105" t="inlineStr">
+      <c r="B14" s="109" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1274,17 +1286,17 @@
           <t>https://www.lazioeuropa.it/bandi/interventi-straordinari-di-valorizzazione-del-patrimonio-culturale-del-lazio/</t>
         </is>
       </c>
-      <c r="E14" s="105" t="inlineStr"/>
-      <c r="F14" s="105" t="inlineStr"/>
-      <c r="G14" s="105" t="inlineStr"/>
+      <c r="E14" s="109" t="inlineStr"/>
+      <c r="F14" s="109" t="inlineStr"/>
+      <c r="G14" s="109" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="103" t="inlineStr">
+      <c r="A15" s="107" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B15" s="103" t="inlineStr">
+      <c r="B15" s="107" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1294,30 +1306,30 @@
           <t>Bandi di garaBANDO ATTUAZIONE Ob. 1.1 Azione 1 codice 111102 _DIV - "SOSTEGNO ALLA DIVERSIFICAZIONE E NUOVE FORME DI REDDITO PER LA PICCOLA PESCA COST</t>
         </is>
       </c>
-      <c r="D15" s="104" t="inlineStr">
+      <c r="D15" s="108" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/bando-avviso-regia-ob-11-azione-1-codice-111102-div-sostegno-alla-diversificazione-nuove-forme-reddito-piccola-pesca-costiera</t>
         </is>
       </c>
-      <c r="E15" s="103" t="inlineStr">
+      <c r="E15" s="107" t="inlineStr">
         <is>
           <t>07/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F15" s="103" t="inlineStr">
+      <c r="F15" s="107" t="inlineStr">
         <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="G15" s="103" t="inlineStr"/>
+      <c r="G15" s="107" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="105" t="inlineStr">
+      <c r="A16" s="109" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B16" s="105" t="inlineStr">
+      <c r="B16" s="109" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1332,25 +1344,25 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/09-marzo-2026-st-siracusa-avviso-pubblico-costituzione-elenchi-operatori-economici-l-acquisizione-beni-servizi</t>
         </is>
       </c>
-      <c r="E16" s="105" t="inlineStr">
+      <c r="E16" s="109" t="inlineStr">
         <is>
           <t>31/12/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F16" s="105" t="inlineStr">
+      <c r="F16" s="109" t="inlineStr">
         <is>
           <t>31/12/2026</t>
         </is>
       </c>
-      <c r="G16" s="105" t="inlineStr"/>
+      <c r="G16" s="109" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="103" t="inlineStr">
+      <c r="A17" s="107" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B17" s="103" t="inlineStr">
+      <c r="B17" s="107" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1360,30 +1372,30 @@
           <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScade il:19/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D17" s="104" t="inlineStr">
+      <c r="D17" s="108" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
         </is>
       </c>
-      <c r="E17" s="103" t="inlineStr">
+      <c r="E17" s="107" t="inlineStr">
         <is>
           <t>19/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F17" s="103" t="inlineStr">
+      <c r="F17" s="107" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G17" s="103" t="inlineStr"/>
+      <c r="G17" s="107" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="105" t="inlineStr">
+      <c r="A18" s="109" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B18" s="105" t="inlineStr">
+      <c r="B18" s="109" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1398,17 +1410,17 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-distributori-automatici-bevande-snack</t>
         </is>
       </c>
-      <c r="E18" s="105" t="inlineStr"/>
-      <c r="F18" s="105" t="inlineStr"/>
-      <c r="G18" s="105" t="inlineStr"/>
+      <c r="E18" s="109" t="inlineStr"/>
+      <c r="F18" s="109" t="inlineStr"/>
+      <c r="G18" s="109" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="103" t="inlineStr">
+      <c r="A19" s="107" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B19" s="103" t="inlineStr">
+      <c r="B19" s="107" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1418,30 +1430,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D19" s="104" t="inlineStr">
+      <c r="D19" s="108" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo</t>
         </is>
       </c>
-      <c r="E19" s="103" t="inlineStr">
+      <c r="E19" s="107" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F19" s="103" t="inlineStr">
+      <c r="F19" s="107" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G19" s="103" t="inlineStr"/>
+      <c r="G19" s="107" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="105" t="inlineStr">
+      <c r="A20" s="109" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B20" s="105" t="inlineStr">
+      <c r="B20" s="109" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1456,25 +1468,25 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo-0</t>
         </is>
       </c>
-      <c r="E20" s="105" t="inlineStr">
+      <c r="E20" s="109" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F20" s="105" t="inlineStr">
+      <c r="F20" s="109" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G20" s="105" t="inlineStr"/>
+      <c r="G20" s="109" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="103" t="inlineStr">
+      <c r="A21" s="107" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B21" s="103" t="inlineStr">
+      <c r="B21" s="107" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1484,22 +1496,22 @@
           <t>Manifestazioni di interesseST SIRACUSA - AVVISO DI MANIFESTAZIONE DI INTERESSE - Fornitura applicativo extracontabile per la gestione progetti, ecc. e</t>
         </is>
       </c>
-      <c r="D21" s="104" t="inlineStr">
+      <c r="D21" s="108" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-siracusa-avviso-manifestazione-interesse-fornitura-applicativo-extracontabile-gestione-progetti-ecc-applicativo-gestione-ed-elaborazione-informatizzata-paghe</t>
         </is>
       </c>
-      <c r="E21" s="103" t="inlineStr"/>
-      <c r="F21" s="103" t="inlineStr"/>
-      <c r="G21" s="103" t="inlineStr"/>
+      <c r="E21" s="107" t="inlineStr"/>
+      <c r="F21" s="107" t="inlineStr"/>
+      <c r="G21" s="107" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="105" t="inlineStr">
+      <c r="A22" s="109" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B22" s="105" t="inlineStr">
+      <c r="B22" s="109" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1514,25 +1526,25 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-sito-nel-comune-capo-d-orlando-trazzera-marina</t>
         </is>
       </c>
-      <c r="E22" s="105" t="inlineStr">
+      <c r="E22" s="109" t="inlineStr">
         <is>
           <t>25/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F22" s="105" t="inlineStr">
+      <c r="F22" s="109" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="G22" s="105" t="inlineStr"/>
+      <c r="G22" s="109" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="103" t="inlineStr">
+      <c r="A23" s="107" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B23" s="103" t="inlineStr">
+      <c r="B23" s="107" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1542,22 +1554,22 @@
           <t xml:space="preserve">Avvisi pubbliciST CATANIA - Programma Regionale FESR Sicilia 2021-2027 - Azione 2.4.4 - “Interventi per la riduzione del rischio incendi” - AVVISO DI </t>
         </is>
       </c>
-      <c r="D23" s="104" t="inlineStr">
+      <c r="D23" s="108" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-catania-programma-regionale-fesr-sicilia-2021-2027-azione-244-interventi-riduzione-rischio-incendi-avviso-indagine-mercato</t>
         </is>
       </c>
-      <c r="E23" s="103" t="inlineStr"/>
-      <c r="F23" s="103" t="inlineStr"/>
-      <c r="G23" s="103" t="inlineStr"/>
+      <c r="E23" s="107" t="inlineStr"/>
+      <c r="F23" s="107" t="inlineStr"/>
+      <c r="G23" s="107" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="105" t="inlineStr">
+      <c r="A24" s="109" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B24" s="105" t="inlineStr">
+      <c r="B24" s="109" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1572,17 +1584,17 @@
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-romics-primavera-2026/</t>
         </is>
       </c>
-      <c r="E24" s="105" t="inlineStr"/>
-      <c r="F24" s="105" t="inlineStr"/>
-      <c r="G24" s="105" t="inlineStr"/>
+      <c r="E24" s="109" t="inlineStr"/>
+      <c r="F24" s="109" t="inlineStr"/>
+      <c r="G24" s="109" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="103" t="inlineStr">
+      <c r="A25" s="107" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B25" s="103" t="inlineStr">
+      <c r="B25" s="107" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1592,22 +1604,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Cinema International 2026 – I edizioneApertoFESR</t>
         </is>
       </c>
-      <c r="D25" s="104" t="inlineStr">
+      <c r="D25" s="108" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lazio-cinema-international-2026-i-edizione/</t>
         </is>
       </c>
-      <c r="E25" s="103" t="inlineStr"/>
-      <c r="F25" s="103" t="inlineStr"/>
-      <c r="G25" s="103" t="inlineStr"/>
+      <c r="E25" s="107" t="inlineStr"/>
+      <c r="F25" s="107" t="inlineStr"/>
+      <c r="G25" s="107" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="105" t="inlineStr">
+      <c r="A26" s="109" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B26" s="105" t="inlineStr">
+      <c r="B26" s="109" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1622,17 +1634,17 @@
           <t>https://www.lazioeuropa.it/bandi/manifestazioni-di-interesse-alla-costituzione-di-due-nuove-fondazioni-i-t-s-academy/</t>
         </is>
       </c>
-      <c r="E26" s="105" t="inlineStr"/>
-      <c r="F26" s="105" t="inlineStr"/>
-      <c r="G26" s="105" t="inlineStr"/>
+      <c r="E26" s="109" t="inlineStr"/>
+      <c r="F26" s="109" t="inlineStr"/>
+      <c r="G26" s="109" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="103" t="inlineStr">
+      <c r="A27" s="107" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B27" s="103" t="inlineStr">
+      <c r="B27" s="107" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1642,22 +1654,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURAContributi per sostenere la ripresa del settore della pescaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D27" s="104" t="inlineStr">
+      <c r="D27" s="108" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributi-per-sostenere-la-ripresa-del-settore-della-pesca/</t>
         </is>
       </c>
-      <c r="E27" s="103" t="inlineStr"/>
-      <c r="F27" s="103" t="inlineStr"/>
-      <c r="G27" s="103" t="inlineStr"/>
+      <c r="E27" s="107" t="inlineStr"/>
+      <c r="F27" s="107" t="inlineStr"/>
+      <c r="G27" s="107" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="105" t="inlineStr">
+      <c r="A28" s="109" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B28" s="105" t="inlineStr">
+      <c r="B28" s="109" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1672,25 +1684,25 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-storytelling-aziendale-expo-wild-natura-caccia-pesca-misterbianco-ct-10-12-aprile-2026</t>
         </is>
       </c>
-      <c r="E28" s="105" t="inlineStr">
+      <c r="E28" s="109" t="inlineStr">
         <is>
           <t>30/03/2026 - 13:00</t>
         </is>
       </c>
-      <c r="F28" s="105" t="inlineStr">
+      <c r="F28" s="109" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G28" s="105" t="inlineStr"/>
+      <c r="G28" s="109" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="103" t="inlineStr">
+      <c r="A29" s="107" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B29" s="103" t="inlineStr">
+      <c r="B29" s="107" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1700,30 +1712,30 @@
           <t>Manifestazioni di interesseInvaso Lentini - Interventi di ripristino delle pareti esterne in cls della Torre di presa Sud e della trave d’appoggio del</t>
         </is>
       </c>
-      <c r="D29" s="104" t="inlineStr">
+      <c r="D29" s="108" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/invaso-lentini-interventi-ripristino-pareti-esterne-cls-torre-presa-sud-trave-d-appoggio-cavalcavia-collegamento-alla-stessa-torre</t>
         </is>
       </c>
-      <c r="E29" s="103" t="inlineStr">
+      <c r="E29" s="107" t="inlineStr">
         <is>
           <t>19/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F29" s="103" t="inlineStr">
+      <c r="F29" s="107" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G29" s="103" t="inlineStr"/>
+      <c r="G29" s="107" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="105" t="inlineStr">
+      <c r="A30" s="109" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="B30" s="105" t="inlineStr">
+      <c r="B30" s="109" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1738,17 +1750,17 @@
           <t>https://www.lazioeuropa.it/bandi/ristrutturazione-e-riconversione-vigneti-campagna-2026-2027/</t>
         </is>
       </c>
-      <c r="E30" s="105" t="inlineStr"/>
-      <c r="F30" s="105" t="inlineStr"/>
-      <c r="G30" s="105" t="inlineStr"/>
+      <c r="E30" s="109" t="inlineStr"/>
+      <c r="F30" s="109" t="inlineStr"/>
+      <c r="G30" s="109" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="103" t="inlineStr">
+      <c r="A31" s="107" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="B31" s="103" t="inlineStr">
+      <c r="B31" s="107" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1758,30 +1770,30 @@
           <t>Manifestazioni di interessePR FESR 2021/27 Azione 1.3.3 e del POC 2014/20 - Azione 1.3.1  - Avviso a manifestazione d’interesse eventi fieristici inte</t>
         </is>
       </c>
-      <c r="D31" s="104" t="inlineStr">
+      <c r="D31" s="108" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-d-interesse-eventi-fieristici-internazionali-marzo-dicembre-2026</t>
         </is>
       </c>
-      <c r="E31" s="103" t="inlineStr">
+      <c r="E31" s="107" t="inlineStr">
         <is>
           <t>30/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F31" s="103" t="inlineStr">
+      <c r="F31" s="107" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="G31" s="103" t="inlineStr"/>
+      <c r="G31" s="107" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="105" t="inlineStr">
+      <c r="A32" s="109" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="B32" s="105" t="inlineStr">
+      <c r="B32" s="109" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1796,17 +1808,17 @@
           <t>https://www.lazioeuropa.it/bandi/lecosistema-dellinnovazione-a-innovit-focus-s3/</t>
         </is>
       </c>
-      <c r="E32" s="105" t="inlineStr"/>
-      <c r="F32" s="105" t="inlineStr"/>
-      <c r="G32" s="105" t="inlineStr"/>
+      <c r="E32" s="109" t="inlineStr"/>
+      <c r="F32" s="109" t="inlineStr"/>
+      <c r="G32" s="109" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="103" t="inlineStr">
+      <c r="A33" s="107" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="B33" s="103" t="inlineStr">
+      <c r="B33" s="107" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1816,22 +1828,22 @@
           <t>Manifestazioni di interessePR FESR SICILIA 2021/27 - NUOVO Avviso a manifestazione d’interesse per esperti valutatoriScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D33" s="104" t="inlineStr">
+      <c r="D33" s="108" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/pr-fesr-sicilia-202127-nuovo-avviso-manifestazione-d-interesse-esperti-valutatori</t>
         </is>
       </c>
-      <c r="E33" s="103" t="inlineStr"/>
-      <c r="F33" s="103" t="inlineStr"/>
-      <c r="G33" s="103" t="inlineStr"/>
+      <c r="E33" s="107" t="inlineStr"/>
+      <c r="F33" s="107" t="inlineStr"/>
+      <c r="G33" s="107" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="105" t="inlineStr">
+      <c r="A34" s="109" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="B34" s="105" t="inlineStr">
+      <c r="B34" s="109" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -1846,17 +1858,17 @@
           <t>https://ambiente.regione.emilia-romagna.it/it/parchi-natura2000/bandi/bando-2026-per-contributi-dedicati-alla-manutenzione-della-rete-dei-percorsi-escursionistici</t>
         </is>
       </c>
-      <c r="E34" s="105" t="inlineStr"/>
-      <c r="F34" s="105" t="inlineStr"/>
-      <c r="G34" s="105" t="inlineStr"/>
+      <c r="E34" s="109" t="inlineStr"/>
+      <c r="F34" s="109" t="inlineStr"/>
+      <c r="G34" s="109" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="103" t="inlineStr">
+      <c r="A35" s="107" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="B35" s="103" t="inlineStr">
+      <c r="B35" s="107" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1866,22 +1878,22 @@
           <t>Programma regionale in favore delle tradizioni storiche, artistiche, religiose e popolari (2026) – manifestazioni d’interesseApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D35" s="104" t="inlineStr">
+      <c r="D35" s="108" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/programma-regionale-in-favore-delle-tradizioni-storiche-artistiche-religiose-e-popolari-2026-manifestazioni-dinteresse/</t>
         </is>
       </c>
-      <c r="E35" s="103" t="inlineStr"/>
-      <c r="F35" s="103" t="inlineStr"/>
-      <c r="G35" s="103" t="inlineStr"/>
+      <c r="E35" s="107" t="inlineStr"/>
+      <c r="F35" s="107" t="inlineStr"/>
+      <c r="G35" s="107" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="105" t="inlineStr">
+      <c r="A36" s="109" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B36" s="105" t="inlineStr">
+      <c r="B36" s="109" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1896,17 +1908,17 @@
           <t>https://www.lazioeuropa.it/bandi/buoni-servizio-per-le-persone-non-autosufficienti-nel-territorio-del-lazio/</t>
         </is>
       </c>
-      <c r="E36" s="105" t="inlineStr"/>
-      <c r="F36" s="105" t="inlineStr"/>
-      <c r="G36" s="105" t="inlineStr"/>
+      <c r="E36" s="109" t="inlineStr"/>
+      <c r="F36" s="109" t="inlineStr"/>
+      <c r="G36" s="109" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="103" t="inlineStr">
+      <c r="A37" s="107" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B37" s="103" t="inlineStr">
+      <c r="B37" s="107" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1916,22 +1928,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONERimborso delle rette dei servizi educativi nel territorio del LazioProssima AperturaFSE / FSE+</t>
         </is>
       </c>
-      <c r="D37" s="104" t="inlineStr">
+      <c r="D37" s="108" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/rimborso-delle-rette-dei-servizi-educativi-nel-territorio-del-lazio/</t>
         </is>
       </c>
-      <c r="E37" s="103" t="inlineStr"/>
-      <c r="F37" s="103" t="inlineStr"/>
-      <c r="G37" s="103" t="inlineStr"/>
+      <c r="E37" s="107" t="inlineStr"/>
+      <c r="F37" s="107" t="inlineStr"/>
+      <c r="G37" s="107" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="105" t="inlineStr">
+      <c r="A38" s="109" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B38" s="105" t="inlineStr">
+      <c r="B38" s="109" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1946,25 +1958,25 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/atto-interpello-l-affidamento-incarico-collaudo-statico-strutture-diga-pietrarossa-progetto-ex-casmez-303219</t>
         </is>
       </c>
-      <c r="E38" s="105" t="inlineStr">
+      <c r="E38" s="109" t="inlineStr">
         <is>
           <t>27/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F38" s="105" t="inlineStr">
+      <c r="F38" s="109" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="G38" s="105" t="inlineStr"/>
+      <c r="G38" s="109" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="103" t="inlineStr">
+      <c r="A39" s="107" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B39" s="103" t="inlineStr">
+      <c r="B39" s="107" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1974,30 +1986,30 @@
           <t>Manifestazioni di interesseAvviso alle Case  Editrici della Regione siciliana per la partecipazione al Salone del Libro di Torino, 14-18  maggio 2026.</t>
         </is>
       </c>
-      <c r="D39" s="104" t="inlineStr">
+      <c r="D39" s="108" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/manifestazione-d-interesse-partecipare-al-xxxviii-salone-libro-torino-14-al-18-maggio-2026-attraverso-l-esposizione-pubblicazioni-presso-stand-assessorato-beni</t>
         </is>
       </c>
-      <c r="E39" s="103" t="inlineStr">
+      <c r="E39" s="107" t="inlineStr">
         <is>
           <t>30/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F39" s="103" t="inlineStr">
+      <c r="F39" s="107" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="G39" s="103" t="inlineStr"/>
+      <c r="G39" s="107" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="105" t="inlineStr">
+      <c r="A40" s="109" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B40" s="105" t="inlineStr">
+      <c r="B40" s="109" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2012,25 +2024,25 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/pr-fesr-sicilia-202127-nuovo-avviso-manifestazione-d-interesse-esperti-valutatori</t>
         </is>
       </c>
-      <c r="E40" s="105" t="inlineStr">
+      <c r="E40" s="109" t="inlineStr">
         <is>
           <t>06/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F40" s="105" t="inlineStr">
+      <c r="F40" s="109" t="inlineStr">
         <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="G40" s="105" t="inlineStr"/>
+      <c r="G40" s="109" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="103" t="inlineStr">
+      <c r="A41" s="107" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B41" s="103" t="inlineStr">
+      <c r="B41" s="107" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2040,22 +2052,22 @@
           <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D41" s="104" t="inlineStr">
+      <c r="D41" s="108" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
         </is>
       </c>
-      <c r="E41" s="103" t="inlineStr"/>
-      <c r="F41" s="103" t="inlineStr"/>
-      <c r="G41" s="103" t="inlineStr"/>
+      <c r="E41" s="107" t="inlineStr"/>
+      <c r="F41" s="107" t="inlineStr"/>
+      <c r="G41" s="107" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="105" t="inlineStr">
+      <c r="A42" s="109" t="inlineStr">
         <is>
           <t>24/03/2026</t>
         </is>
       </c>
-      <c r="B42" s="105" t="inlineStr">
+      <c r="B42" s="109" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2070,17 +2082,17 @@
           <t>https://agricoltura.regione.emilia-romagna.it/sviluppo-rurale-23-27/opportunita/bandi-gal/2026/du_as05b-promozione-di-fiere-agroalimentari-e-delle-filiere-del-cibo-bando-per-enti-pubblici</t>
         </is>
       </c>
-      <c r="E42" s="105" t="inlineStr"/>
-      <c r="F42" s="105" t="inlineStr"/>
-      <c r="G42" s="105" t="inlineStr"/>
+      <c r="E42" s="109" t="inlineStr"/>
+      <c r="F42" s="109" t="inlineStr"/>
+      <c r="G42" s="109" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="103" t="inlineStr">
+      <c r="A43" s="107" t="inlineStr">
         <is>
           <t>24/03/2026</t>
         </is>
       </c>
-      <c r="B43" s="103" t="inlineStr">
+      <c r="B43" s="107" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2090,30 +2102,30 @@
           <t>Manifestazioni di interesseAVVISO PUBBLICO PER MANIFESTAZIONE DI INTERESSE FINALIZZATA ALL'ASSEGNAZIONE DI SPAZI ESPOSITIVI (CORNER GRATUITI) ALL'INTE</t>
         </is>
       </c>
-      <c r="D43" s="104" t="inlineStr">
+      <c r="D43" s="108" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-manifestazione-interesse-finalizzata-all-assegnazione-spazi-espositivi-corner-gratuiti-all-interno-stand-istituzionale-dsrt-manifestazione</t>
         </is>
       </c>
-      <c r="E43" s="103" t="inlineStr">
+      <c r="E43" s="107" t="inlineStr">
         <is>
           <t>30/03/2026 - 13:00</t>
         </is>
       </c>
-      <c r="F43" s="103" t="inlineStr">
+      <c r="F43" s="107" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G43" s="103" t="inlineStr"/>
+      <c r="G43" s="107" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="105" t="inlineStr">
+      <c r="A44" s="109" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B44" s="105" t="inlineStr">
+      <c r="B44" s="109" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2128,17 +2140,17 @@
           <t>https://www.regione.emilia-romagna.it/sport/bandi/2026/bando-2026</t>
         </is>
       </c>
-      <c r="E44" s="105" t="inlineStr"/>
-      <c r="F44" s="105" t="inlineStr"/>
-      <c r="G44" s="105" t="inlineStr"/>
+      <c r="E44" s="109" t="inlineStr"/>
+      <c r="F44" s="109" t="inlineStr"/>
+      <c r="G44" s="109" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="103" t="inlineStr">
+      <c r="A45" s="107" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B45" s="103" t="inlineStr">
+      <c r="B45" s="107" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2148,22 +2160,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Street art 2026Prossima AperturaBandi Regionali</t>
         </is>
       </c>
-      <c r="D45" s="104" t="inlineStr">
+      <c r="D45" s="108" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lazio-street-art-2026/</t>
         </is>
       </c>
-      <c r="E45" s="103" t="inlineStr"/>
-      <c r="F45" s="103" t="inlineStr"/>
-      <c r="G45" s="103" t="inlineStr"/>
+      <c r="E45" s="107" t="inlineStr"/>
+      <c r="F45" s="107" t="inlineStr"/>
+      <c r="G45" s="107" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="105" t="inlineStr">
+      <c r="A46" s="109" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B46" s="105" t="inlineStr">
+      <c r="B46" s="109" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2178,25 +2190,25 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/manifestazione-interesse-partecipazione-all-evento-r2i-italy-2026-bologna-12-13052026</t>
         </is>
       </c>
-      <c r="E46" s="105" t="inlineStr">
+      <c r="E46" s="109" t="inlineStr">
         <is>
           <t>03/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F46" s="105" t="inlineStr">
+      <c r="F46" s="109" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="G46" s="105" t="inlineStr"/>
+      <c r="G46" s="109" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="103" t="inlineStr">
+      <c r="A47" s="107" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B47" s="103" t="inlineStr">
+      <c r="B47" s="107" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2206,30 +2218,30 @@
           <t>Manifestazioni di interesseST SIRACUSA - AVVISO PER MANIFESTAZIONE DI INTERESSE - Selezione di n. 5 unità di personale internoScade il:20/04/2026 - 12</t>
         </is>
       </c>
-      <c r="D47" s="104" t="inlineStr">
+      <c r="D47" s="108" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/24-marzo-2026-st-siracusa-avviso-manifestazione-interesse-selezione-n-5-unita-personale-interno</t>
         </is>
       </c>
-      <c r="E47" s="103" t="inlineStr">
+      <c r="E47" s="107" t="inlineStr">
         <is>
           <t>20/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F47" s="103" t="inlineStr">
+      <c r="F47" s="107" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="G47" s="103" t="inlineStr"/>
+      <c r="G47" s="107" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="105" t="inlineStr">
+      <c r="A48" s="109" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B48" s="105" t="inlineStr">
+      <c r="B48" s="109" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2244,25 +2256,25 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/revoca-avviso-concessione-titolo-gratuito-16122025-inerente-all-immobile-seguito-identificato-contestuale-nuovo-avviso-concessione-titolo-oneroso-stesso-sito-nel</t>
         </is>
       </c>
-      <c r="E48" s="105" t="inlineStr">
+      <c r="E48" s="109" t="inlineStr">
         <is>
           <t>08/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F48" s="105" t="inlineStr">
+      <c r="F48" s="109" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="G48" s="105" t="inlineStr"/>
+      <c r="G48" s="109" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="103" t="inlineStr">
+      <c r="A49" s="107" t="inlineStr">
         <is>
           <t>26/03/2026</t>
         </is>
       </c>
-      <c r="B49" s="103" t="inlineStr">
+      <c r="B49" s="107" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2272,22 +2284,22 @@
           <t>Bando studi di fattibilità per fusioni di Comuni</t>
         </is>
       </c>
-      <c r="D49" s="104" t="inlineStr">
+      <c r="D49" s="108" t="inlineStr">
         <is>
           <t>https://www.regione.emilia-romagna.it/autonomie-locali/bandi/bando_studi_fattibilita_fusioni_comuni</t>
         </is>
       </c>
-      <c r="E49" s="103" t="inlineStr"/>
-      <c r="F49" s="103" t="inlineStr"/>
-      <c r="G49" s="103" t="inlineStr"/>
+      <c r="E49" s="107" t="inlineStr"/>
+      <c r="F49" s="107" t="inlineStr"/>
+      <c r="G49" s="107" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="105" t="inlineStr">
+      <c r="A50" s="109" t="inlineStr">
         <is>
           <t>26/03/2026</t>
         </is>
       </c>
-      <c r="B50" s="105" t="inlineStr">
+      <c r="B50" s="109" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2302,25 +2314,25 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-selezione-interna-titoli-conferimento-po-professionali-ai-sensi-artt-19-20-21-ccrl-20222024-comparto-non-dirigenziale</t>
         </is>
       </c>
-      <c r="E50" s="105" t="inlineStr">
+      <c r="E50" s="109" t="inlineStr">
         <is>
           <t>30/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F50" s="105" t="inlineStr">
+      <c r="F50" s="109" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G50" s="105" t="inlineStr"/>
+      <c r="G50" s="109" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="103" t="inlineStr">
+      <c r="A51" s="107" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="B51" s="103" t="inlineStr">
+      <c r="B51" s="107" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2330,22 +2342,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0PRE-SEED 3.0ApertoFESR</t>
         </is>
       </c>
-      <c r="D51" s="104" t="inlineStr">
+      <c r="D51" s="108" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/pre-seed-3-0/</t>
         </is>
       </c>
-      <c r="E51" s="103" t="inlineStr"/>
-      <c r="F51" s="103" t="inlineStr"/>
-      <c r="G51" s="103" t="inlineStr"/>
+      <c r="E51" s="107" t="inlineStr"/>
+      <c r="F51" s="107" t="inlineStr"/>
+      <c r="G51" s="107" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="105" t="inlineStr">
+      <c r="A52" s="109" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B52" s="105" t="inlineStr">
+      <c r="B52" s="109" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2360,25 +2372,25 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-termini-imerese-locta-piazza-marina</t>
         </is>
       </c>
-      <c r="E52" s="105" t="inlineStr">
+      <c r="E52" s="109" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F52" s="105" t="inlineStr">
+      <c r="F52" s="109" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G52" s="105" t="inlineStr"/>
+      <c r="G52" s="109" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="103" t="inlineStr">
+      <c r="A53" s="107" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B53" s="103" t="inlineStr">
+      <c r="B53" s="107" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2388,30 +2400,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, Sig</t>
         </is>
       </c>
-      <c r="D53" s="104" t="inlineStr">
+      <c r="D53" s="108" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-porto-empedocle-locta-punta-piccola</t>
         </is>
       </c>
-      <c r="E53" s="103" t="inlineStr">
+      <c r="E53" s="107" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F53" s="103" t="inlineStr">
+      <c r="F53" s="107" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G53" s="103" t="inlineStr"/>
+      <c r="G53" s="107" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="105" t="inlineStr">
+      <c r="A54" s="109" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B54" s="105" t="inlineStr">
+      <c r="B54" s="109" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2426,25 +2438,25 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-messina-locta-torrente-bordonaro</t>
         </is>
       </c>
-      <c r="E54" s="105" t="inlineStr">
+      <c r="E54" s="109" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F54" s="105" t="inlineStr">
+      <c r="F54" s="109" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G54" s="105" t="inlineStr"/>
+      <c r="G54" s="109" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="103" t="inlineStr">
+      <c r="A55" s="107" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B55" s="103" t="inlineStr">
+      <c r="B55" s="107" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2454,30 +2466,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “Condomin</t>
         </is>
       </c>
-      <c r="D55" s="104" t="inlineStr">
+      <c r="D55" s="108" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-mascali-spiaggia-n-144150</t>
         </is>
       </c>
-      <c r="E55" s="103" t="inlineStr">
+      <c r="E55" s="107" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F55" s="103" t="inlineStr">
+      <c r="F55" s="107" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G55" s="103" t="inlineStr"/>
+      <c r="G55" s="107" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="105" t="inlineStr">
+      <c r="A56" s="109" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B56" s="105" t="inlineStr">
+      <c r="B56" s="109" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2492,25 +2504,25 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-lipari-isola-stromboli-locta-fico-grande</t>
         </is>
       </c>
-      <c r="E56" s="105" t="inlineStr">
+      <c r="E56" s="109" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F56" s="105" t="inlineStr">
+      <c r="F56" s="109" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G56" s="105" t="inlineStr"/>
+      <c r="G56" s="109" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="103" t="inlineStr">
+      <c r="A57" s="107" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B57" s="103" t="inlineStr">
+      <c r="B57" s="107" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2520,30 +2532,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione sito nel Comune di Favignana, isola di Le</t>
         </is>
       </c>
-      <c r="D57" s="104" t="inlineStr">
+      <c r="D57" s="108" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-favignana-isola-levanzo</t>
         </is>
       </c>
-      <c r="E57" s="103" t="inlineStr">
+      <c r="E57" s="107" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F57" s="103" t="inlineStr">
+      <c r="F57" s="107" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G57" s="103" t="inlineStr"/>
+      <c r="G57" s="107" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="105" t="inlineStr">
+      <c r="A58" s="109" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="B58" s="105" t="inlineStr">
+      <c r="B58" s="109" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2558,25 +2570,25 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-d-interesse-finalizzata-alla-selezione-organismi-attuatori-piani-gestione-locale-piccola-pesca-costiera-nelle-gsa-regione-siciliana</t>
         </is>
       </c>
-      <c r="E58" s="105" t="inlineStr">
+      <c r="E58" s="109" t="inlineStr">
         <is>
           <t>29/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F58" s="105" t="inlineStr">
+      <c r="F58" s="109" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="G58" s="105" t="inlineStr"/>
+      <c r="G58" s="109" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="103" t="inlineStr">
+      <c r="A59" s="107" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="B59" s="103" t="inlineStr">
+      <c r="B59" s="107" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2586,30 +2598,30 @@
           <t>Avvisi pubbliciLeggi e scarica l'avvisoScade il:02/04/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D59" s="104" t="inlineStr">
+      <c r="D59" s="108" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/proroga-termini-presentazione-candidature-po</t>
         </is>
       </c>
-      <c r="E59" s="103" t="inlineStr">
+      <c r="E59" s="107" t="inlineStr">
         <is>
           <t>02/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F59" s="103" t="inlineStr">
+      <c r="F59" s="107" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="G59" s="103" t="inlineStr"/>
+      <c r="G59" s="107" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="105" t="inlineStr">
+      <c r="A60" s="109" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="105" t="inlineStr">
+      <c r="B60" s="109" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2624,17 +2636,17 @@
           <t>https://www.lazioeuropa.it/bandi/smau-italy-restartsup-in-stoccolma/</t>
         </is>
       </c>
-      <c r="E60" s="105" t="inlineStr"/>
-      <c r="F60" s="105" t="inlineStr"/>
-      <c r="G60" s="105" t="inlineStr"/>
+      <c r="E60" s="109" t="inlineStr"/>
+      <c r="F60" s="109" t="inlineStr"/>
+      <c r="G60" s="109" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="103" t="inlineStr">
+      <c r="A61" s="107" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B61" s="103" t="inlineStr">
+      <c r="B61" s="107" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2644,22 +2656,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per Farnborough International AirshowApertoFESR</t>
         </is>
       </c>
-      <c r="D61" s="104" t="inlineStr">
+      <c r="D61" s="108" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-farnborough-international-airshow-2/</t>
         </is>
       </c>
-      <c r="E61" s="103" t="inlineStr"/>
-      <c r="F61" s="103" t="inlineStr"/>
-      <c r="G61" s="103" t="inlineStr"/>
+      <c r="E61" s="107" t="inlineStr"/>
+      <c r="F61" s="107" t="inlineStr"/>
+      <c r="G61" s="107" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="105" t="inlineStr">
+      <c r="A62" s="109" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="105" t="inlineStr">
+      <c r="B62" s="109" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2674,25 +2686,25 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proprieta-regionale-sito-nel-comune-termini-imerese-favore-ares-fabiola</t>
         </is>
       </c>
-      <c r="E62" s="105" t="inlineStr">
+      <c r="E62" s="109" t="inlineStr">
         <is>
           <t>30/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F62" s="105" t="inlineStr">
+      <c r="F62" s="109" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="G62" s="105" t="inlineStr"/>
+      <c r="G62" s="109" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="103" t="inlineStr">
+      <c r="A63" s="107" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B63" s="103" t="inlineStr">
+      <c r="B63" s="107" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2702,22 +2714,22 @@
           <t>Avviso per la concessione di contributi per progetti di contrasto all'abbandono sportivo giovanile (2026)</t>
         </is>
       </c>
-      <c r="D63" s="104" t="inlineStr">
+      <c r="D63" s="108" t="inlineStr">
         <is>
           <t>https://www.regione.emilia-romagna.it/sport/bandi/2026/contrasto-abbandono-2026</t>
         </is>
       </c>
-      <c r="E63" s="103" t="inlineStr"/>
-      <c r="F63" s="103" t="inlineStr"/>
-      <c r="G63" s="103" t="inlineStr"/>
+      <c r="E63" s="107" t="inlineStr"/>
+      <c r="F63" s="107" t="inlineStr"/>
+      <c r="G63" s="107" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="105" t="inlineStr">
+      <c r="A64" s="109" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="105" t="inlineStr">
+      <c r="B64" s="109" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2732,25 +2744,25 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-selezione-interna-conferimento-1-posizione-organizzativa-ai-sensi-artt-19-20-ccrl-2022-2024-comparto-non-dirigenziale</t>
         </is>
       </c>
-      <c r="E64" s="105" t="inlineStr">
+      <c r="E64" s="109" t="inlineStr">
         <is>
           <t>09/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F64" s="105" t="inlineStr">
+      <c r="F64" s="109" t="inlineStr">
         <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="G64" s="105" t="inlineStr"/>
+      <c r="G64" s="109" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="103" t="inlineStr">
+      <c r="A65" s="107" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B65" s="103" t="inlineStr">
+      <c r="B65" s="107" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2760,30 +2772,30 @@
           <t>Avvisi pubbliciST-MESSINA - AVVISO di INDAGINE DI MERCATO per affidamento "Interventi manutenzione straordinaria della strada/pista forestale "Annunzi</t>
         </is>
       </c>
-      <c r="D65" s="104" t="inlineStr">
+      <c r="D65" s="108" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-indagine-mercato-affidamento-interventi-manutenzione-straordinaria-stradapista-forestale-annunziata-comune-messina</t>
         </is>
       </c>
-      <c r="E65" s="103" t="inlineStr">
+      <c r="E65" s="107" t="inlineStr">
         <is>
           <t>16/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F65" s="103" t="inlineStr">
+      <c r="F65" s="107" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="G65" s="103" t="inlineStr"/>
+      <c r="G65" s="107" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="105" t="inlineStr">
+      <c r="A66" s="109" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="105" t="inlineStr">
+      <c r="B66" s="109" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2798,25 +2810,25 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-indagine-mercato-affidamento-interventi-manutenzione-straordinaria-stradapista-forestale-san-rizzo-san-leone-crupi-madonuzza-comune-messina</t>
         </is>
       </c>
-      <c r="E66" s="105" t="inlineStr">
+      <c r="E66" s="109" t="inlineStr">
         <is>
           <t>16/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F66" s="105" t="inlineStr">
+      <c r="F66" s="109" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="G66" s="105" t="inlineStr"/>
+      <c r="G66" s="109" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="103" t="inlineStr">
+      <c r="A67" s="107" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="103" t="inlineStr">
+      <c r="B67" s="107" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2826,22 +2838,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Manifestazione di interesse per Casaidea 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D67" s="104" t="inlineStr">
+      <c r="D67" s="108" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-casaidea-2026/</t>
         </is>
       </c>
-      <c r="E67" s="103" t="inlineStr"/>
-      <c r="F67" s="103" t="inlineStr"/>
-      <c r="G67" s="103" t="inlineStr"/>
+      <c r="E67" s="107" t="inlineStr"/>
+      <c r="F67" s="107" t="inlineStr"/>
+      <c r="G67" s="107" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="105" t="inlineStr">
+      <c r="A68" s="109" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="105" t="inlineStr">
+      <c r="B68" s="109" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2856,17 +2868,17 @@
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-il-salone-internazionale-del-libro-di-torino-2026/</t>
         </is>
       </c>
-      <c r="E68" s="105" t="inlineStr"/>
-      <c r="F68" s="105" t="inlineStr"/>
-      <c r="G68" s="105" t="inlineStr"/>
+      <c r="E68" s="109" t="inlineStr"/>
+      <c r="F68" s="109" t="inlineStr"/>
+      <c r="G68" s="109" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="103" t="inlineStr">
+      <c r="A69" s="107" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="103" t="inlineStr">
+      <c r="B69" s="107" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2876,30 +2888,30 @@
           <t>Avvisi pubbliciDDG 1112 del 02.04.2026 - Aggiornamento Avviso pubblico n. 4/2024 per l’attuazione del PAR GOL Sicilia da finanziare nell’ambito del Pi</t>
         </is>
       </c>
-      <c r="D69" s="104" t="inlineStr">
+      <c r="D69" s="108" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/ddg-1112-02042026-aggiornamento-avviso-pubblico-n-42024-l-attuazione-par-gol-sicilia-finanziare-nell-ambito-piano-nazionale-ripresa-resilienza-pnrr</t>
         </is>
       </c>
-      <c r="E69" s="103" t="inlineStr">
+      <c r="E69" s="107" t="inlineStr">
         <is>
           <t>05/04/2030 - 00:00</t>
         </is>
       </c>
-      <c r="F69" s="103" t="inlineStr">
+      <c r="F69" s="107" t="inlineStr">
         <is>
           <t>05/04/2030</t>
         </is>
       </c>
-      <c r="G69" s="103" t="inlineStr"/>
+      <c r="G69" s="107" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="105" t="inlineStr">
+      <c r="A70" s="109" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="105" t="inlineStr">
+      <c r="B70" s="109" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2914,25 +2926,25 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/ddg-1113-02042026-aggiornamento-avviso-pubblico-n-22022-smi-l-attuazione-par-gol-sicilia-finanziare-nell-ambito-piano-nazionale-ripresa-resilienza-pnrr</t>
         </is>
       </c>
-      <c r="E70" s="105" t="inlineStr">
+      <c r="E70" s="109" t="inlineStr">
         <is>
           <t>03/04/2030 - 00:00</t>
         </is>
       </c>
-      <c r="F70" s="105" t="inlineStr">
+      <c r="F70" s="109" t="inlineStr">
         <is>
           <t>03/04/2030</t>
         </is>
       </c>
-      <c r="G70" s="105" t="inlineStr"/>
+      <c r="G70" s="109" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="103" t="inlineStr">
+      <c r="A71" s="107" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B71" s="103" t="inlineStr">
+      <c r="B71" s="107" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2942,22 +2954,22 @@
           <t>Avvisi pubbliciLeggi e scarica l'avvisoScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D71" s="104" t="inlineStr">
+      <c r="D71" s="108" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/proroga-termini-presentazione-candidature-po</t>
         </is>
       </c>
-      <c r="E71" s="103" t="inlineStr"/>
-      <c r="F71" s="103" t="inlineStr"/>
-      <c r="G71" s="103" t="inlineStr"/>
+      <c r="E71" s="107" t="inlineStr"/>
+      <c r="F71" s="107" t="inlineStr"/>
+      <c r="G71" s="107" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="105" t="inlineStr">
+      <c r="A72" s="109" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="105" t="inlineStr">
+      <c r="B72" s="109" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2972,17 +2984,17 @@
           <t>https://www.lazioeuropa.it/bandi/comunicare-linclusione-contest-per-le-istituzioni-scolastiche-regionali/</t>
         </is>
       </c>
-      <c r="E72" s="105" t="inlineStr"/>
-      <c r="F72" s="105" t="inlineStr"/>
-      <c r="G72" s="105" t="inlineStr"/>
+      <c r="E72" s="109" t="inlineStr"/>
+      <c r="F72" s="109" t="inlineStr"/>
+      <c r="G72" s="109" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="103" t="inlineStr">
+      <c r="A73" s="107" t="inlineStr">
         <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B73" s="103" t="inlineStr">
+      <c r="B73" s="107" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2992,30 +3004,30 @@
           <t>Avvisi pubbliciAPPROVAZIONE AVVISO PUBBLICOScade il:03/04/2027 - 00:00Leggi di più</t>
         </is>
       </c>
-      <c r="D73" s="104" t="inlineStr">
+      <c r="D73" s="108" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/approvazione-avviso-pubblico</t>
         </is>
       </c>
-      <c r="E73" s="103" t="inlineStr">
+      <c r="E73" s="107" t="inlineStr">
         <is>
           <t>03/04/2027 - 00:00</t>
         </is>
       </c>
-      <c r="F73" s="103" t="inlineStr">
+      <c r="F73" s="107" t="inlineStr">
         <is>
           <t>03/04/2027</t>
         </is>
       </c>
-      <c r="G73" s="103" t="inlineStr"/>
+      <c r="G73" s="107" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="105" t="inlineStr">
+      <c r="A74" s="109" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="105" t="inlineStr">
+      <c r="B74" s="109" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -3030,17 +3042,17 @@
           <t>https://www.lazioeuropa.it/bandi/donne-e-impresa-2026/</t>
         </is>
       </c>
-      <c r="E74" s="105" t="inlineStr"/>
-      <c r="F74" s="105" t="inlineStr"/>
-      <c r="G74" s="105" t="inlineStr"/>
+      <c r="E74" s="109" t="inlineStr"/>
+      <c r="F74" s="109" t="inlineStr"/>
+      <c r="G74" s="109" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="103" t="inlineStr">
+      <c r="A75" s="107" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B75" s="103" t="inlineStr">
+      <c r="B75" s="107" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3050,30 +3062,30 @@
           <t>Bandi di garaCodice Intervento 111302_FELUCHE - Investimenti a bordo e nei porti per incrementare la qualità delle produzioni e migliorare le condizio</t>
         </is>
       </c>
-      <c r="D75" s="104" t="inlineStr">
+      <c r="D75" s="108" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/bandoavviso-regia-ob-11-azione-3-codice-111302feluche-investimenti-bordo-valorizzazione-feluche-miglioramento-condizioni-lavoro-salute-sicurezza-operatori-l</t>
         </is>
       </c>
-      <c r="E75" s="103" t="inlineStr">
+      <c r="E75" s="107" t="inlineStr">
         <is>
           <t>02/07/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F75" s="103" t="inlineStr">
+      <c r="F75" s="107" t="inlineStr">
         <is>
           <t>02/07/2026</t>
         </is>
       </c>
-      <c r="G75" s="103" t="inlineStr"/>
+      <c r="G75" s="107" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="105" t="inlineStr">
+      <c r="A76" s="109" t="inlineStr">
         <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="105" t="inlineStr">
+      <c r="B76" s="109" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -3088,17 +3100,17 @@
           <t>https://www.lazioeuropa.it/bandi/sostegno-agli-investimenti-nel-settore-vitivinicolo-campagna-2026-2027/</t>
         </is>
       </c>
-      <c r="E76" s="105" t="inlineStr"/>
-      <c r="F76" s="105" t="inlineStr"/>
-      <c r="G76" s="105" t="inlineStr"/>
+      <c r="E76" s="109" t="inlineStr"/>
+      <c r="F76" s="109" t="inlineStr"/>
+      <c r="G76" s="109" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="103" t="inlineStr">
+      <c r="A77" s="107" t="inlineStr">
         <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="103" t="inlineStr">
+      <c r="B77" s="107" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3108,30 +3120,30 @@
           <t>Manifestazioni di interesse9 aprile 2026 -ST PALERMO- Manifestazione di interesse - “Interventi di manutenzione straordinaria della strada-pista fores</t>
         </is>
       </c>
-      <c r="D77" s="104" t="inlineStr">
+      <c r="D77" s="108" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/9-aprile-2026-st-palermo-manifestazione-interesse-interventi-manutenzione-straordinaria-strada-pista-forestale-monte-cane-comune-caccamo-pa-distretto-forestale</t>
         </is>
       </c>
-      <c r="E77" s="103" t="inlineStr">
+      <c r="E77" s="107" t="inlineStr">
         <is>
           <t>24/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F77" s="103" t="inlineStr">
+      <c r="F77" s="107" t="inlineStr">
         <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="G77" s="103" t="inlineStr"/>
+      <c r="G77" s="107" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="105" t="inlineStr">
+      <c r="A78" s="109" t="inlineStr">
         <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="105" t="inlineStr">
+      <c r="B78" s="109" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3146,25 +3158,25 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-indagine-mercato-affidamento-interventi-manutenzione-straordinaria-stradapista-forestale-faggita-comune-tripi-me</t>
         </is>
       </c>
-      <c r="E78" s="105" t="inlineStr">
+      <c r="E78" s="109" t="inlineStr">
         <is>
           <t>23/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F78" s="105" t="inlineStr">
+      <c r="F78" s="109" t="inlineStr">
         <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="G78" s="105" t="inlineStr"/>
+      <c r="G78" s="109" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="103" t="inlineStr">
+      <c r="A79" s="107" t="inlineStr">
         <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B79" s="103" t="inlineStr">
+      <c r="B79" s="107" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3174,30 +3186,30 @@
           <t>Avvisi pubbliciST-MESSINA - AVVISO DI INDAGINE DI MERCATO per affidamento "Interventi manutenzione straordinaria della strada/pista forestale "Ferraro</t>
         </is>
       </c>
-      <c r="D79" s="104" t="inlineStr">
+      <c r="D79" s="108" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-indagine-mercato-affidamento-interventi-manutenzione-straordinaria-stradapista-forestale-ferraro-sanrizzo-badiazza-comune-messina</t>
         </is>
       </c>
-      <c r="E79" s="103" t="inlineStr">
+      <c r="E79" s="107" t="inlineStr">
         <is>
           <t>23/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F79" s="103" t="inlineStr">
+      <c r="F79" s="107" t="inlineStr">
         <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="G79" s="103" t="inlineStr"/>
+      <c r="G79" s="107" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="105" t="inlineStr">
+      <c r="A80" s="109" t="inlineStr">
         <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="105" t="inlineStr">
+      <c r="B80" s="109" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -3212,17 +3224,17 @@
           <t>https://www.lazioeuropa.it/bandi/acquisizione-di-servizi-di-comunicazione-e-informazione-pr-lazio-fesr-pr-lazio-fse-e-comunicazione-unitaria/</t>
         </is>
       </c>
-      <c r="E80" s="105" t="inlineStr"/>
-      <c r="F80" s="105" t="inlineStr"/>
-      <c r="G80" s="105" t="inlineStr"/>
+      <c r="E80" s="109" t="inlineStr"/>
+      <c r="F80" s="109" t="inlineStr"/>
+      <c r="G80" s="109" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="103" t="inlineStr">
+      <c r="A81" s="107" t="inlineStr">
         <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B81" s="103" t="inlineStr">
+      <c r="B81" s="107" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3232,30 +3244,30 @@
           <t>Avvisi pubbliciAvviso pubblico di selezione interna, per titoli, per il conferimento, ai sensi degli artt. 21 del CCRL 2022-2024 del comparto non diri</t>
         </is>
       </c>
-      <c r="D81" s="104" t="inlineStr">
+      <c r="D81" s="108" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-selezione-interna-titoli-conferimento-ai-sensi-artt-21-ccrl-2022-2024-comparto-non-dirigenziale-una-posizione-organizzativa-dipartimento</t>
         </is>
       </c>
-      <c r="E81" s="103" t="inlineStr">
+      <c r="E81" s="107" t="inlineStr">
         <is>
           <t>16/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F81" s="103" t="inlineStr">
+      <c r="F81" s="107" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="G81" s="103" t="inlineStr"/>
+      <c r="G81" s="107" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="105" t="inlineStr">
+      <c r="A82" s="109" t="inlineStr">
         <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="105" t="inlineStr">
+      <c r="B82" s="109" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3270,25 +3282,25 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-indagine-mercato-partecipazione-alla-successiva-procedura-negoziata-norma-art-50-comma-1-lettera-c-dlgs-31-marzo-2023-n-36-ssmmii-finalizzata-all</t>
         </is>
       </c>
-      <c r="E82" s="105" t="inlineStr">
+      <c r="E82" s="109" t="inlineStr">
         <is>
           <t>30/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F82" s="105" t="inlineStr">
+      <c r="F82" s="109" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="G82" s="105" t="inlineStr"/>
+      <c r="G82" s="109" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="103" t="inlineStr">
+      <c r="A83" s="107" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="103" t="inlineStr">
+      <c r="B83" s="107" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -3298,22 +3310,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEVoucher per lo Sport – individuazione dei destinatari (II edizione)ApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D83" s="104" t="inlineStr">
+      <c r="D83" s="108" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/voucher-per-lo-sport-individuazione-dei-destinatari-ii-edizione/</t>
         </is>
       </c>
-      <c r="E83" s="103" t="inlineStr"/>
-      <c r="F83" s="103" t="inlineStr"/>
-      <c r="G83" s="103" t="inlineStr"/>
+      <c r="E83" s="107" t="inlineStr"/>
+      <c r="F83" s="107" t="inlineStr"/>
+      <c r="G83" s="107" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="105" t="inlineStr">
+      <c r="A84" s="109" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B84" s="105" t="inlineStr">
+      <c r="B84" s="109" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -3328,17 +3340,17 @@
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-partecipare-a-codeway-expo-2026/</t>
         </is>
       </c>
-      <c r="E84" s="105" t="inlineStr"/>
-      <c r="F84" s="105" t="inlineStr"/>
-      <c r="G84" s="105" t="inlineStr"/>
+      <c r="E84" s="109" t="inlineStr"/>
+      <c r="F84" s="109" t="inlineStr"/>
+      <c r="G84" s="109" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="103" t="inlineStr">
+      <c r="A85" s="107" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B85" s="103" t="inlineStr">
+      <c r="B85" s="107" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -3348,22 +3360,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Street art 2026ApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D85" s="104" t="inlineStr">
+      <c r="D85" s="108" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lazio-street-art-2026/</t>
         </is>
       </c>
-      <c r="E85" s="103" t="inlineStr"/>
-      <c r="F85" s="103" t="inlineStr"/>
-      <c r="G85" s="103" t="inlineStr"/>
+      <c r="E85" s="107" t="inlineStr"/>
+      <c r="F85" s="107" t="inlineStr"/>
+      <c r="G85" s="107" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="105" t="inlineStr">
+      <c r="A86" s="109" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B86" s="105" t="inlineStr">
+      <c r="B86" s="109" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -3378,17 +3390,17 @@
           <t>https://www.lazioeuropa.it/bandi/buoni-servizio-per-le-persone-non-autosufficienti-nel-territorio-del-lazio/</t>
         </is>
       </c>
-      <c r="E86" s="105" t="inlineStr"/>
-      <c r="F86" s="105" t="inlineStr"/>
-      <c r="G86" s="105" t="inlineStr"/>
+      <c r="E86" s="109" t="inlineStr"/>
+      <c r="F86" s="109" t="inlineStr"/>
+      <c r="G86" s="109" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="103" t="inlineStr">
+      <c r="A87" s="107" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B87" s="103" t="inlineStr">
+      <c r="B87" s="107" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3398,30 +3410,30 @@
           <t>Avvisi pubbliciSERVIZIO 14 SERVIZIO PER IL TERRITORIO DI PALERMO AVVISO PUBBLICO PER LA CONCESSIONE AL PASCOLO NEI TERRENI DEL DEMANIO FORESTALE REGIO</t>
         </is>
       </c>
-      <c r="D87" s="104" t="inlineStr">
+      <c r="D87" s="108" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-14-servizio-territorio-palermo-avviso-pubblico-concessione-al-pascolo-nei-terreni-demanio-forestale-regionale-gestiti-dipartimento-sviluppo-rurale</t>
         </is>
       </c>
-      <c r="E87" s="103" t="inlineStr">
+      <c r="E87" s="107" t="inlineStr">
         <is>
           <t>05/05/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F87" s="103" t="inlineStr">
+      <c r="F87" s="107" t="inlineStr">
         <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="G87" s="103" t="inlineStr"/>
+      <c r="G87" s="107" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="105" t="inlineStr">
+      <c r="A88" s="109" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B88" s="105" t="inlineStr">
+      <c r="B88" s="109" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3436,25 +3448,25 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/atto-intepello-dipartimento-turismo-sport-spettacolo</t>
         </is>
       </c>
-      <c r="E88" s="105" t="inlineStr">
+      <c r="E88" s="109" t="inlineStr">
         <is>
           <t>30/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F88" s="105" t="inlineStr">
+      <c r="F88" s="109" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="G88" s="105" t="inlineStr"/>
+      <c r="G88" s="109" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="103" t="inlineStr">
+      <c r="A89" s="107" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B89" s="103" t="inlineStr">
+      <c r="B89" s="107" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3464,30 +3476,30 @@
           <t>Avvisi pubbliciAVVISO DI INDAGINE DI MERCATO - per la partecipazione alla successiva procedura negoziata a norma dell'art. 50, comma 1, lettera c) del</t>
         </is>
       </c>
-      <c r="D89" s="104" t="inlineStr">
+      <c r="D89" s="108" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-pa-avviso-indagine-mercato-partecipazione-alla-successiva-procedura-negoziata-norma-art-50-comma-1-lettera-c-dlgs-31-marzo-2023-n-36-ssmmii-finalizzata-all</t>
         </is>
       </c>
-      <c r="E89" s="103" t="inlineStr">
+      <c r="E89" s="107" t="inlineStr">
         <is>
           <t>02/05/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F89" s="103" t="inlineStr">
+      <c r="F89" s="107" t="inlineStr">
         <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="G89" s="103" t="inlineStr"/>
+      <c r="G89" s="107" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="105" t="inlineStr">
+      <c r="A90" s="109" t="inlineStr">
         <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B90" s="105" t="inlineStr">
+      <c r="B90" s="109" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -3502,17 +3514,17 @@
           <t>https://www.lazioeuropa.it/bandi/fondo-patrimonializzazione-pmi-riapertura-termini/</t>
         </is>
       </c>
-      <c r="E90" s="105" t="inlineStr"/>
-      <c r="F90" s="105" t="inlineStr"/>
-      <c r="G90" s="105" t="inlineStr"/>
+      <c r="E90" s="109" t="inlineStr"/>
+      <c r="F90" s="109" t="inlineStr"/>
+      <c r="G90" s="109" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="103" t="inlineStr">
+      <c r="A91" s="107" t="inlineStr">
         <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B91" s="103" t="inlineStr">
+      <c r="B91" s="107" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -3522,22 +3534,22 @@
           <t>ACCESSO AL CREDITO E ALLE GARANZIE PER LE IMPRESENuovo Fondo Piccolo Credito – sezione ordinaria (2026)Prossima AperturaFESRPOCRisorse regionali</t>
         </is>
       </c>
-      <c r="D91" s="104" t="inlineStr">
+      <c r="D91" s="108" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/nuovo-fondo-piccolo-credito-sezione-ordinaria-2026/</t>
         </is>
       </c>
-      <c r="E91" s="103" t="inlineStr"/>
-      <c r="F91" s="103" t="inlineStr"/>
-      <c r="G91" s="103" t="inlineStr"/>
+      <c r="E91" s="107" t="inlineStr"/>
+      <c r="F91" s="107" t="inlineStr"/>
+      <c r="G91" s="107" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="105" t="inlineStr">
+      <c r="A92" s="109" t="inlineStr">
         <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B92" s="105" t="inlineStr">
+      <c r="B92" s="109" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -3552,17 +3564,17 @@
           <t>https://www.lazioeuropa.it/bandi/nuovo-fondo-futuro-2026/</t>
         </is>
       </c>
-      <c r="E92" s="105" t="inlineStr"/>
-      <c r="F92" s="105" t="inlineStr"/>
-      <c r="G92" s="105" t="inlineStr"/>
+      <c r="E92" s="109" t="inlineStr"/>
+      <c r="F92" s="109" t="inlineStr"/>
+      <c r="G92" s="109" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="103" t="inlineStr">
+      <c r="A93" s="107" t="inlineStr">
         <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B93" s="103" t="inlineStr">
+      <c r="B93" s="107" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3572,30 +3584,30 @@
           <t>Avvisi pubbliciAvviso pubblico di selezione interna, per titoli, per il conferimento, ai sensi degli artt. 19 e 20 del CCRL 2022-2024 del comparto non</t>
         </is>
       </c>
-      <c r="D93" s="104" t="inlineStr">
+      <c r="D93" s="108" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-selezione-interna-titoli-conferimento-ai-sensi-artt-19-20-ccrl-2022-2024-comparto-non-dirigenziale-posizioni-organizzative-dipartimento-regionale</t>
         </is>
       </c>
-      <c r="E93" s="103" t="inlineStr">
+      <c r="E93" s="107" t="inlineStr">
         <is>
           <t>24/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F93" s="103" t="inlineStr">
+      <c r="F93" s="107" t="inlineStr">
         <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="G93" s="103" t="inlineStr"/>
+      <c r="G93" s="107" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="105" t="inlineStr">
+      <c r="A94" s="109" t="inlineStr">
         <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B94" s="105" t="inlineStr">
+      <c r="B94" s="109" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3610,25 +3622,25 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/16-aprile-2026-st-catania-avviso-concessione-postazioni-arnie-anno-2026</t>
         </is>
       </c>
-      <c r="E94" s="105" t="inlineStr">
+      <c r="E94" s="109" t="inlineStr">
         <is>
           <t>27/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F94" s="105" t="inlineStr">
+      <c r="F94" s="109" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="G94" s="105" t="inlineStr"/>
+      <c r="G94" s="109" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="103" t="inlineStr">
+      <c r="A95" s="107" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B95" s="103" t="inlineStr">
+      <c r="B95" s="107" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3638,30 +3650,30 @@
           <t>Manifestazioni di interesseIndividuazione delle Compagnie di Assicurazione disponibili a emettere polizze collettive e polizze individuali multirischi</t>
         </is>
       </c>
-      <c r="D95" s="104" t="inlineStr">
+      <c r="D95" s="108" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/polizze-collettive-polizze-individuali-multirischio-agricole-integrate-fondo-agricat-favore-agricoltori-siciliani-campagna-assicurativa-2026</t>
         </is>
       </c>
-      <c r="E95" s="103" t="inlineStr">
+      <c r="E95" s="107" t="inlineStr">
         <is>
           <t>29/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F95" s="103" t="inlineStr">
+      <c r="F95" s="107" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="G95" s="103" t="inlineStr"/>
+      <c r="G95" s="107" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="105" t="inlineStr">
+      <c r="A96" s="109" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B96" s="105" t="inlineStr">
+      <c r="B96" s="109" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -3676,17 +3688,17 @@
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-messina-avviso-pubblico-manifestazione-interesse-alla-licitazione-privata-concessione-al-pascolo-nei-terreni-demanio-forestale-regionale-gestiti-dipartimento</t>
         </is>
       </c>
-      <c r="E96" s="105" t="inlineStr">
+      <c r="E96" s="109" t="inlineStr">
         <is>
           <t>28/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F96" s="105" t="inlineStr">
+      <c r="F96" s="109" t="inlineStr">
         <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="G96" s="105" t="inlineStr"/>
+      <c r="G96" s="109" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="107" t="inlineStr">
@@ -3712,6 +3724,31 @@
       <c r="E97" s="107" t="inlineStr"/>
       <c r="F97" s="107" t="inlineStr"/>
       <c r="G97" s="107" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="112" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="112" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="C98" s="9" t="inlineStr">
+        <is>
+          <t>CREATIVITÀ, CINEMA, TURISMO E CULTURAIscrizioni all’Albo regionale delle Rievocazioni storicheApertoBandi Regionali</t>
+        </is>
+      </c>
+      <c r="D98" s="113" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/iscrizioni-allalbo-regionale-delle-rievocazioni-storiche/</t>
+        </is>
+      </c>
+      <c r="E98" s="112" t="inlineStr"/>
+      <c r="F98" s="112" t="inlineStr"/>
+      <c r="G98" s="112" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -3811,6 +3848,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D95" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D96" r:id="rId95"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D98" r:id="rId97"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3855,7 +3893,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="107" t="inlineStr">
+      <c r="A3" s="110" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -3864,24 +3902,24 @@
         <v>7</v>
       </c>
       <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="112" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>39</v>
+      </c>
+      <c r="C4" s="7" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="109" t="inlineStr">
-        <is>
-          <t>Lazio</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n">
-        <v>38</v>
-      </c>
-      <c r="C4" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
     <row r="5">
-      <c r="A5" s="107" t="inlineStr">
+      <c r="A5" s="110" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>

--- a/data/bandi_export.xlsx
+++ b/data/bandi_export.xlsx
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -441,6 +441,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -820,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -835,7 +847,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🏛️  Nuovi Bandi — 21/04/2026 08:29</t>
+          <t>🏛️  Nuovi Bandi — 22/04/2026 08:27</t>
         </is>
       </c>
     </row>
@@ -880,24 +892,70 @@
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="110" t="inlineStr">
+      <c r="B3" s="114" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>CREATIVITÀ, CINEMA, TURISMO E CULTURAIscrizioni all’Albo regionale delle Rievocazioni storicheApertoBandi Regionali</t>
-        </is>
-      </c>
-      <c r="D3" s="111" t="inlineStr">
-        <is>
-          <t>https://www.lazioeuropa.it/bandi/iscrizioni-allalbo-regionale-delle-rievocazioni-storiche/</t>
-        </is>
-      </c>
-      <c r="E3" s="110" t="inlineStr"/>
-      <c r="F3" s="110" t="inlineStr"/>
+          <t xml:space="preserve">IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURAInvestimenti per incrementare la qualità delle produzioni e migliorare le condizioni di sbarco delle </t>
+        </is>
+      </c>
+      <c r="D3" s="115" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/investimenti-per-incrementare-la-qualita-delle-produzioni-e-migliorare-le-condizioni-di-sbarco-delle-catture-indesiderate-nonche-promuovere-migliori-condizioni-di-lavoro-salute-e-sicurezza/</t>
+        </is>
+      </c>
+      <c r="E3" s="114" t="inlineStr"/>
+      <c r="F3" s="114" t="inlineStr"/>
       <c r="G3" s="5" t="inlineStr"/>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="116" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURAPesca e acquacoltura – competitività e sicurezza delle attività di commercializzazione e trasformazio</t>
+        </is>
+      </c>
+      <c r="D4" s="117" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/pesca-e-acquacoltura-competitivita-e-sicurezza-delle-attivita-di-commercializzazione-e-trasformazione-dei-prodotti/</t>
+        </is>
+      </c>
+      <c r="E4" s="116" t="inlineStr"/>
+      <c r="F4" s="116" t="inlineStr"/>
+      <c r="G4" s="9" t="inlineStr"/>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="114" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per SMAU New York 2026ApertoFESR</t>
+        </is>
+      </c>
+      <c r="D5" s="115" t="inlineStr">
+        <is>
+          <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-smau-new-york-2026/</t>
+        </is>
+      </c>
+      <c r="E5" s="114" t="inlineStr"/>
+      <c r="F5" s="114" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -905,6 +963,8 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -916,7 +976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -966,12 +1026,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="109" t="inlineStr">
+      <c r="A2" s="112" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B2" s="109" t="inlineStr">
+      <c r="B2" s="112" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -981,22 +1041,22 @@
           <t>FLAG GALPA Costa E-R. Sostituzione del motore principale e dei motori secondari. Secondo bando</t>
         </is>
       </c>
-      <c r="D2" s="106" t="inlineStr">
+      <c r="D2" s="113" t="inlineStr">
         <is>
           <t>https://agricoltura.regione.emilia-romagna.it/feampa-2021-2027/bandi-galpa/2026/galpa-sostituzione-motori-secondo-bando</t>
         </is>
       </c>
-      <c r="E2" s="109" t="inlineStr"/>
-      <c r="F2" s="109" t="inlineStr"/>
-      <c r="G2" s="109" t="inlineStr"/>
+      <c r="E2" s="112" t="inlineStr"/>
+      <c r="F2" s="112" t="inlineStr"/>
+      <c r="G2" s="112" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="107" t="inlineStr">
+      <c r="A3" s="110" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B3" s="107" t="inlineStr">
+      <c r="B3" s="110" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1006,22 +1066,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0PRE-SEED 3.0Prossima AperturaFESR</t>
         </is>
       </c>
-      <c r="D3" s="108" t="inlineStr">
+      <c r="D3" s="111" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/pre-seed-3-0/</t>
         </is>
       </c>
-      <c r="E3" s="107" t="inlineStr"/>
-      <c r="F3" s="107" t="inlineStr"/>
-      <c r="G3" s="107" t="inlineStr"/>
+      <c r="E3" s="110" t="inlineStr"/>
+      <c r="F3" s="110" t="inlineStr"/>
+      <c r="G3" s="110" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="109" t="inlineStr">
+      <c r="A4" s="112" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B4" s="109" t="inlineStr">
+      <c r="B4" s="112" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1031,22 +1091,22 @@
           <t>ACCESSO AL CREDITO E ALLE GARANZIE PER LE IMPRESEContributo su finanziamenti alle imprese del Lazio erogati su provvista BEIProssima AperturaFESR</t>
         </is>
       </c>
-      <c r="D4" s="106" t="inlineStr">
+      <c r="D4" s="113" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-su-finanziamenti-alle-imprese-del-lazio-erogati-su-provvista-bei/</t>
         </is>
       </c>
-      <c r="E4" s="109" t="inlineStr"/>
-      <c r="F4" s="109" t="inlineStr"/>
-      <c r="G4" s="109" t="inlineStr"/>
+      <c r="E4" s="112" t="inlineStr"/>
+      <c r="F4" s="112" t="inlineStr"/>
+      <c r="G4" s="112" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="107" t="inlineStr">
+      <c r="A5" s="110" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B5" s="107" t="inlineStr">
+      <c r="B5" s="110" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1056,22 +1116,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEIndividuazione degli enti iscritti al Registro unico nazionale del Terzo settoreApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D5" s="108" t="inlineStr">
+      <c r="D5" s="111" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/individuazione-degli-enti-iscritti-al-registro-unico-nazionale-del-terzo-settore/</t>
         </is>
       </c>
-      <c r="E5" s="107" t="inlineStr"/>
-      <c r="F5" s="107" t="inlineStr"/>
-      <c r="G5" s="107" t="inlineStr"/>
+      <c r="E5" s="110" t="inlineStr"/>
+      <c r="F5" s="110" t="inlineStr"/>
+      <c r="G5" s="110" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="109" t="inlineStr">
+      <c r="A6" s="112" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B6" s="109" t="inlineStr">
+      <c r="B6" s="112" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1081,22 +1141,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Technology Transfer LazioApertoFESR</t>
         </is>
       </c>
-      <c r="D6" s="106" t="inlineStr">
+      <c r="D6" s="113" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/technology-transfer-lazio/</t>
         </is>
       </c>
-      <c r="E6" s="109" t="inlineStr"/>
-      <c r="F6" s="109" t="inlineStr"/>
-      <c r="G6" s="109" t="inlineStr"/>
+      <c r="E6" s="112" t="inlineStr"/>
+      <c r="F6" s="112" t="inlineStr"/>
+      <c r="G6" s="112" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="107" t="inlineStr">
+      <c r="A7" s="110" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B7" s="107" t="inlineStr">
+      <c r="B7" s="110" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1106,22 +1166,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0Percorso di tutoraggio per le impreseApertoFESR</t>
         </is>
       </c>
-      <c r="D7" s="108" t="inlineStr">
+      <c r="D7" s="111" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/percorso-di-tutoraggio-per-le-imprese/</t>
         </is>
       </c>
-      <c r="E7" s="107" t="inlineStr"/>
-      <c r="F7" s="107" t="inlineStr"/>
-      <c r="G7" s="107" t="inlineStr"/>
+      <c r="E7" s="110" t="inlineStr"/>
+      <c r="F7" s="110" t="inlineStr"/>
+      <c r="G7" s="110" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="109" t="inlineStr">
+      <c r="A8" s="112" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B8" s="109" t="inlineStr">
+      <c r="B8" s="112" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1131,22 +1191,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per partecipare a SMAU Parigi 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D8" s="106" t="inlineStr">
+      <c r="D8" s="113" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-partecipare-a-smau-parigi-2026/</t>
         </is>
       </c>
-      <c r="E8" s="109" t="inlineStr"/>
-      <c r="F8" s="109" t="inlineStr"/>
-      <c r="G8" s="109" t="inlineStr"/>
+      <c r="E8" s="112" t="inlineStr"/>
+      <c r="F8" s="112" t="inlineStr"/>
+      <c r="G8" s="112" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="107" t="inlineStr">
+      <c r="A9" s="110" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B9" s="107" t="inlineStr">
+      <c r="B9" s="110" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1156,22 +1216,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONERiconoscimento della funzione sociale ed educativa degli oratoriApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D9" s="108" t="inlineStr">
+      <c r="D9" s="111" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/riconoscimento-della-funzione-sociale-ed-educativa-degli-oratori/</t>
         </is>
       </c>
-      <c r="E9" s="107" t="inlineStr"/>
-      <c r="F9" s="107" t="inlineStr"/>
-      <c r="G9" s="107" t="inlineStr"/>
+      <c r="E9" s="110" t="inlineStr"/>
+      <c r="F9" s="110" t="inlineStr"/>
+      <c r="G9" s="110" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="109" t="inlineStr">
+      <c r="A10" s="112" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B10" s="109" t="inlineStr">
+      <c r="B10" s="112" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1181,22 +1241,22 @@
           <t>GovernanceIscrizione nell’elenco regionale degli idonei all’esercizio dell’attività di direttore dell’Istituto JemoloApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D10" s="106" t="inlineStr">
+      <c r="D10" s="113" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/iscrizione-nellelenco-regionale-degli-idonei-allesercizio-dellattivita-di-direttore-dellistituto-jemolo/</t>
         </is>
       </c>
-      <c r="E10" s="109" t="inlineStr"/>
-      <c r="F10" s="109" t="inlineStr"/>
-      <c r="G10" s="109" t="inlineStr"/>
+      <c r="E10" s="112" t="inlineStr"/>
+      <c r="F10" s="112" t="inlineStr"/>
+      <c r="G10" s="112" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="107" t="inlineStr">
+      <c r="A11" s="110" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B11" s="107" t="inlineStr">
+      <c r="B11" s="110" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1206,22 +1266,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEVoucher per lo sport – seconda annualitàApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D11" s="108" t="inlineStr">
+      <c r="D11" s="111" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/voucher-per-lo-sport-seconda-annualita/</t>
         </is>
       </c>
-      <c r="E11" s="107" t="inlineStr"/>
-      <c r="F11" s="107" t="inlineStr"/>
-      <c r="G11" s="107" t="inlineStr"/>
+      <c r="E11" s="110" t="inlineStr"/>
+      <c r="F11" s="110" t="inlineStr"/>
+      <c r="G11" s="110" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="109" t="inlineStr">
+      <c r="A12" s="112" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B12" s="109" t="inlineStr">
+      <c r="B12" s="112" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1231,22 +1291,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEBonus occupazionale SALGOApertoFSE / FSE+</t>
         </is>
       </c>
-      <c r="D12" s="106" t="inlineStr">
+      <c r="D12" s="113" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/bonus-occupazionale-salgo/</t>
         </is>
       </c>
-      <c r="E12" s="109" t="inlineStr"/>
-      <c r="F12" s="109" t="inlineStr"/>
-      <c r="G12" s="109" t="inlineStr"/>
+      <c r="E12" s="112" t="inlineStr"/>
+      <c r="F12" s="112" t="inlineStr"/>
+      <c r="G12" s="112" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="107" t="inlineStr">
+      <c r="A13" s="110" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B13" s="107" t="inlineStr">
+      <c r="B13" s="110" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1256,22 +1316,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEContributo di Libertà per le donne che hanno subito violenzaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D13" s="108" t="inlineStr">
+      <c r="D13" s="111" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributo-di-liberta-per-le-donne-che-hanno-subito-violenza/</t>
         </is>
       </c>
-      <c r="E13" s="107" t="inlineStr"/>
-      <c r="F13" s="107" t="inlineStr"/>
-      <c r="G13" s="107" t="inlineStr"/>
+      <c r="E13" s="110" t="inlineStr"/>
+      <c r="F13" s="110" t="inlineStr"/>
+      <c r="G13" s="110" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="109" t="inlineStr">
+      <c r="A14" s="112" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B14" s="109" t="inlineStr">
+      <c r="B14" s="112" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1281,22 +1341,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURAInterventi straordinari di valorizzazione del patrimonio culturale del LazioApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D14" s="106" t="inlineStr">
+      <c r="D14" s="113" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/interventi-straordinari-di-valorizzazione-del-patrimonio-culturale-del-lazio/</t>
         </is>
       </c>
-      <c r="E14" s="109" t="inlineStr"/>
-      <c r="F14" s="109" t="inlineStr"/>
-      <c r="G14" s="109" t="inlineStr"/>
+      <c r="E14" s="112" t="inlineStr"/>
+      <c r="F14" s="112" t="inlineStr"/>
+      <c r="G14" s="112" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="107" t="inlineStr">
+      <c r="A15" s="110" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B15" s="107" t="inlineStr">
+      <c r="B15" s="110" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1306,30 +1366,30 @@
           <t>Bandi di garaBANDO ATTUAZIONE Ob. 1.1 Azione 1 codice 111102 _DIV - "SOSTEGNO ALLA DIVERSIFICAZIONE E NUOVE FORME DI REDDITO PER LA PICCOLA PESCA COST</t>
         </is>
       </c>
-      <c r="D15" s="108" t="inlineStr">
+      <c r="D15" s="111" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/bando-avviso-regia-ob-11-azione-1-codice-111102-div-sostegno-alla-diversificazione-nuove-forme-reddito-piccola-pesca-costiera</t>
         </is>
       </c>
-      <c r="E15" s="107" t="inlineStr">
+      <c r="E15" s="110" t="inlineStr">
         <is>
           <t>07/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F15" s="107" t="inlineStr">
+      <c r="F15" s="110" t="inlineStr">
         <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="G15" s="107" t="inlineStr"/>
+      <c r="G15" s="110" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="109" t="inlineStr">
+      <c r="A16" s="112" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B16" s="109" t="inlineStr">
+      <c r="B16" s="112" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1339,30 +1399,30 @@
           <t>Avvisi pubblici09 marzo 2026 - ST SIRACUSA - AVVISO PUBBLICO PER LA COSTITUZIONE DI ELENCHI DI OPERATORI ECONOMICI PER L’ACQUISIZIONE DI BENI E SERVIZ</t>
         </is>
       </c>
-      <c r="D16" s="106" t="inlineStr">
+      <c r="D16" s="113" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/09-marzo-2026-st-siracusa-avviso-pubblico-costituzione-elenchi-operatori-economici-l-acquisizione-beni-servizi</t>
         </is>
       </c>
-      <c r="E16" s="109" t="inlineStr">
+      <c r="E16" s="112" t="inlineStr">
         <is>
           <t>31/12/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F16" s="109" t="inlineStr">
+      <c r="F16" s="112" t="inlineStr">
         <is>
           <t>31/12/2026</t>
         </is>
       </c>
-      <c r="G16" s="109" t="inlineStr"/>
+      <c r="G16" s="112" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="107" t="inlineStr">
+      <c r="A17" s="110" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B17" s="107" t="inlineStr">
+      <c r="B17" s="110" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1372,30 +1432,30 @@
           <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScade il:19/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D17" s="108" t="inlineStr">
+      <c r="D17" s="111" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
         </is>
       </c>
-      <c r="E17" s="107" t="inlineStr">
+      <c r="E17" s="110" t="inlineStr">
         <is>
           <t>19/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F17" s="107" t="inlineStr">
+      <c r="F17" s="110" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G17" s="107" t="inlineStr"/>
+      <c r="G17" s="110" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="109" t="inlineStr">
+      <c r="A18" s="112" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B18" s="109" t="inlineStr">
+      <c r="B18" s="112" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1405,22 +1465,22 @@
           <t>Manifestazioni di interesseAvviso Manifestazione Interesse DISTRIBUTORI AUTOMATICI di bevande e snackScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D18" s="106" t="inlineStr">
+      <c r="D18" s="113" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-distributori-automatici-bevande-snack</t>
         </is>
       </c>
-      <c r="E18" s="109" t="inlineStr"/>
-      <c r="F18" s="109" t="inlineStr"/>
-      <c r="G18" s="109" t="inlineStr"/>
+      <c r="E18" s="112" t="inlineStr"/>
+      <c r="F18" s="112" t="inlineStr"/>
+      <c r="G18" s="112" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="107" t="inlineStr">
+      <c r="A19" s="110" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B19" s="107" t="inlineStr">
+      <c r="B19" s="110" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1430,30 +1490,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D19" s="108" t="inlineStr">
+      <c r="D19" s="111" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo</t>
         </is>
       </c>
-      <c r="E19" s="107" t="inlineStr">
+      <c r="E19" s="110" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F19" s="107" t="inlineStr">
+      <c r="F19" s="110" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G19" s="107" t="inlineStr"/>
+      <c r="G19" s="110" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="109" t="inlineStr">
+      <c r="A20" s="112" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B20" s="109" t="inlineStr">
+      <c r="B20" s="112" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1463,30 +1523,30 @@
           <t>Avvisi pubbliciAVVISO DI NOTIFICAZIONE PER PUBBLICI PROCLAMI GIUDIZIO N. 273/2026 R.G. T.A.R. SICILIA - SEDE DI PALERMOScade il:30/03/2026 - 23:59Legg</t>
         </is>
       </c>
-      <c r="D20" s="106" t="inlineStr">
+      <c r="D20" s="113" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/servizio-5-sostegno-alle-attivita-sportive-dipartimento-turismo-0</t>
         </is>
       </c>
-      <c r="E20" s="109" t="inlineStr">
+      <c r="E20" s="112" t="inlineStr">
         <is>
           <t>30/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F20" s="109" t="inlineStr">
+      <c r="F20" s="112" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G20" s="109" t="inlineStr"/>
+      <c r="G20" s="112" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="107" t="inlineStr">
+      <c r="A21" s="110" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B21" s="107" t="inlineStr">
+      <c r="B21" s="110" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1496,22 +1556,22 @@
           <t>Manifestazioni di interesseST SIRACUSA - AVVISO DI MANIFESTAZIONE DI INTERESSE - Fornitura applicativo extracontabile per la gestione progetti, ecc. e</t>
         </is>
       </c>
-      <c r="D21" s="108" t="inlineStr">
+      <c r="D21" s="111" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-siracusa-avviso-manifestazione-interesse-fornitura-applicativo-extracontabile-gestione-progetti-ecc-applicativo-gestione-ed-elaborazione-informatizzata-paghe</t>
         </is>
       </c>
-      <c r="E21" s="107" t="inlineStr"/>
-      <c r="F21" s="107" t="inlineStr"/>
-      <c r="G21" s="107" t="inlineStr"/>
+      <c r="E21" s="110" t="inlineStr"/>
+      <c r="F21" s="110" t="inlineStr"/>
+      <c r="G21" s="110" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="109" t="inlineStr">
+      <c r="A22" s="112" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B22" s="109" t="inlineStr">
+      <c r="B22" s="112" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1521,30 +1581,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile sito nel Comune di Capo D'Orlando, Via Trazzera MarinaScade il:25/03/2026 - 12:00Leggi di più</t>
         </is>
       </c>
-      <c r="D22" s="106" t="inlineStr">
+      <c r="D22" s="113" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-sito-nel-comune-capo-d-orlando-trazzera-marina</t>
         </is>
       </c>
-      <c r="E22" s="109" t="inlineStr">
+      <c r="E22" s="112" t="inlineStr">
         <is>
           <t>25/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F22" s="109" t="inlineStr">
+      <c r="F22" s="112" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="G22" s="109" t="inlineStr"/>
+      <c r="G22" s="112" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="107" t="inlineStr">
+      <c r="A23" s="110" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
       </c>
-      <c r="B23" s="107" t="inlineStr">
+      <c r="B23" s="110" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1554,22 +1614,22 @@
           <t xml:space="preserve">Avvisi pubbliciST CATANIA - Programma Regionale FESR Sicilia 2021-2027 - Azione 2.4.4 - “Interventi per la riduzione del rischio incendi” - AVVISO DI </t>
         </is>
       </c>
-      <c r="D23" s="108" t="inlineStr">
+      <c r="D23" s="111" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/st-catania-programma-regionale-fesr-sicilia-2021-2027-azione-244-interventi-riduzione-rischio-incendi-avviso-indagine-mercato</t>
         </is>
       </c>
-      <c r="E23" s="107" t="inlineStr"/>
-      <c r="F23" s="107" t="inlineStr"/>
-      <c r="G23" s="107" t="inlineStr"/>
+      <c r="E23" s="110" t="inlineStr"/>
+      <c r="F23" s="110" t="inlineStr"/>
+      <c r="G23" s="110" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="109" t="inlineStr">
+      <c r="A24" s="112" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B24" s="109" t="inlineStr">
+      <c r="B24" s="112" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1579,22 +1639,22 @@
           <t>INTERNAZIONALIZZAZIONEManifestazione di interesse per ROMICS – Primavera 2026ApertoFESR</t>
         </is>
       </c>
-      <c r="D24" s="106" t="inlineStr">
+      <c r="D24" s="113" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazione-di-interesse-per-romics-primavera-2026/</t>
         </is>
       </c>
-      <c r="E24" s="109" t="inlineStr"/>
-      <c r="F24" s="109" t="inlineStr"/>
-      <c r="G24" s="109" t="inlineStr"/>
+      <c r="E24" s="112" t="inlineStr"/>
+      <c r="F24" s="112" t="inlineStr"/>
+      <c r="G24" s="112" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="107" t="inlineStr">
+      <c r="A25" s="110" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
       </c>
-      <c r="B25" s="107" t="inlineStr">
+      <c r="B25" s="110" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1604,22 +1664,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Cinema International 2026 – I edizioneApertoFESR</t>
         </is>
       </c>
-      <c r="D25" s="108" t="inlineStr">
+      <c r="D25" s="111" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lazio-cinema-international-2026-i-edizione/</t>
         </is>
       </c>
-      <c r="E25" s="107" t="inlineStr"/>
-      <c r="F25" s="107" t="inlineStr"/>
-      <c r="G25" s="107" t="inlineStr"/>
+      <c r="E25" s="110" t="inlineStr"/>
+      <c r="F25" s="110" t="inlineStr"/>
+      <c r="G25" s="110" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="109" t="inlineStr">
+      <c r="A26" s="112" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B26" s="109" t="inlineStr">
+      <c r="B26" s="112" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1629,22 +1689,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEManifestazioni di interesse alla costituzione di due nuove Fondazioni I.T.S. AcademyApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D26" s="106" t="inlineStr">
+      <c r="D26" s="113" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/manifestazioni-di-interesse-alla-costituzione-di-due-nuove-fondazioni-i-t-s-academy/</t>
         </is>
       </c>
-      <c r="E26" s="109" t="inlineStr"/>
-      <c r="F26" s="109" t="inlineStr"/>
-      <c r="G26" s="109" t="inlineStr"/>
+      <c r="E26" s="112" t="inlineStr"/>
+      <c r="F26" s="112" t="inlineStr"/>
+      <c r="G26" s="112" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="107" t="inlineStr">
+      <c r="A27" s="110" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B27" s="107" t="inlineStr">
+      <c r="B27" s="110" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1654,22 +1714,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURAContributi per sostenere la ripresa del settore della pescaApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D27" s="108" t="inlineStr">
+      <c r="D27" s="111" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/contributi-per-sostenere-la-ripresa-del-settore-della-pesca/</t>
         </is>
       </c>
-      <c r="E27" s="107" t="inlineStr"/>
-      <c r="F27" s="107" t="inlineStr"/>
-      <c r="G27" s="107" t="inlineStr"/>
+      <c r="E27" s="110" t="inlineStr"/>
+      <c r="F27" s="110" t="inlineStr"/>
+      <c r="G27" s="110" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="109" t="inlineStr">
+      <c r="A28" s="112" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B28" s="109" t="inlineStr">
+      <c r="B28" s="112" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1679,30 +1739,30 @@
           <t>Manifestazioni di interesseAVVISO - Manifestazione Interesse “Storytelling aziendale” Expo Wild Natura - Caccia - Pesca. Misterbianco (CT), 10-12 apri</t>
         </is>
       </c>
-      <c r="D28" s="106" t="inlineStr">
+      <c r="D28" s="113" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-interesse-storytelling-aziendale-expo-wild-natura-caccia-pesca-misterbianco-ct-10-12-aprile-2026</t>
         </is>
       </c>
-      <c r="E28" s="109" t="inlineStr">
+      <c r="E28" s="112" t="inlineStr">
         <is>
           <t>30/03/2026 - 13:00</t>
         </is>
       </c>
-      <c r="F28" s="109" t="inlineStr">
+      <c r="F28" s="112" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G28" s="109" t="inlineStr"/>
+      <c r="G28" s="112" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="107" t="inlineStr">
+      <c r="A29" s="110" t="inlineStr">
         <is>
           <t>14/03/2026</t>
         </is>
       </c>
-      <c r="B29" s="107" t="inlineStr">
+      <c r="B29" s="110" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1712,30 +1772,30 @@
           <t>Manifestazioni di interesseInvaso Lentini - Interventi di ripristino delle pareti esterne in cls della Torre di presa Sud e della trave d’appoggio del</t>
         </is>
       </c>
-      <c r="D29" s="108" t="inlineStr">
+      <c r="D29" s="111" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/invaso-lentini-interventi-ripristino-pareti-esterne-cls-torre-presa-sud-trave-d-appoggio-cavalcavia-collegamento-alla-stessa-torre</t>
         </is>
       </c>
-      <c r="E29" s="107" t="inlineStr">
+      <c r="E29" s="110" t="inlineStr">
         <is>
           <t>19/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F29" s="107" t="inlineStr">
+      <c r="F29" s="110" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="G29" s="107" t="inlineStr"/>
+      <c r="G29" s="110" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="109" t="inlineStr">
+      <c r="A30" s="112" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="B30" s="109" t="inlineStr">
+      <c r="B30" s="112" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1745,22 +1805,22 @@
           <t>IMPRESE AGRICOLE, DELLA PESCA E DELL’ACQUACOLTURARistrutturazione e riconversione vigneti – campagna 2026-2027ApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D30" s="106" t="inlineStr">
+      <c r="D30" s="113" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/ristrutturazione-e-riconversione-vigneti-campagna-2026-2027/</t>
         </is>
       </c>
-      <c r="E30" s="109" t="inlineStr"/>
-      <c r="F30" s="109" t="inlineStr"/>
-      <c r="G30" s="109" t="inlineStr"/>
+      <c r="E30" s="112" t="inlineStr"/>
+      <c r="F30" s="112" t="inlineStr"/>
+      <c r="G30" s="112" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="107" t="inlineStr">
+      <c r="A31" s="110" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="B31" s="107" t="inlineStr">
+      <c r="B31" s="110" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1770,30 +1830,30 @@
           <t>Manifestazioni di interessePR FESR 2021/27 Azione 1.3.3 e del POC 2014/20 - Azione 1.3.1  - Avviso a manifestazione d’interesse eventi fieristici inte</t>
         </is>
       </c>
-      <c r="D31" s="108" t="inlineStr">
+      <c r="D31" s="111" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-manifestazione-d-interesse-eventi-fieristici-internazionali-marzo-dicembre-2026</t>
         </is>
       </c>
-      <c r="E31" s="107" t="inlineStr">
+      <c r="E31" s="110" t="inlineStr">
         <is>
           <t>30/06/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F31" s="107" t="inlineStr">
+      <c r="F31" s="110" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="G31" s="107" t="inlineStr"/>
+      <c r="G31" s="110" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="109" t="inlineStr">
+      <c r="A32" s="112" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="B32" s="109" t="inlineStr">
+      <c r="B32" s="112" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1803,22 +1863,22 @@
           <t>INTERNAZIONALIZZAZIONEL’Ecosistema dell’Innovazione a INNOVIT – Focus S3ApertoFESR</t>
         </is>
       </c>
-      <c r="D32" s="106" t="inlineStr">
+      <c r="D32" s="113" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lecosistema-dellinnovazione-a-innovit-focus-s3/</t>
         </is>
       </c>
-      <c r="E32" s="109" t="inlineStr"/>
-      <c r="F32" s="109" t="inlineStr"/>
-      <c r="G32" s="109" t="inlineStr"/>
+      <c r="E32" s="112" t="inlineStr"/>
+      <c r="F32" s="112" t="inlineStr"/>
+      <c r="G32" s="112" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="107" t="inlineStr">
+      <c r="A33" s="110" t="inlineStr">
         <is>
           <t>18/03/2026</t>
         </is>
       </c>
-      <c r="B33" s="107" t="inlineStr">
+      <c r="B33" s="110" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1828,22 +1888,22 @@
           <t>Manifestazioni di interessePR FESR SICILIA 2021/27 - NUOVO Avviso a manifestazione d’interesse per esperti valutatoriScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D33" s="108" t="inlineStr">
+      <c r="D33" s="111" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/pr-fesr-sicilia-202127-nuovo-avviso-manifestazione-d-interesse-esperti-valutatori</t>
         </is>
       </c>
-      <c r="E33" s="107" t="inlineStr"/>
-      <c r="F33" s="107" t="inlineStr"/>
-      <c r="G33" s="107" t="inlineStr"/>
+      <c r="E33" s="110" t="inlineStr"/>
+      <c r="F33" s="110" t="inlineStr"/>
+      <c r="G33" s="110" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="109" t="inlineStr">
+      <c r="A34" s="112" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="B34" s="109" t="inlineStr">
+      <c r="B34" s="112" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -1853,22 +1913,22 @@
           <t>Bando 2026 per contributi dedicati alla manutenzione della rete dei percorsi escursionistici</t>
         </is>
       </c>
-      <c r="D34" s="106" t="inlineStr">
+      <c r="D34" s="113" t="inlineStr">
         <is>
           <t>https://ambiente.regione.emilia-romagna.it/it/parchi-natura2000/bandi/bando-2026-per-contributi-dedicati-alla-manutenzione-della-rete-dei-percorsi-escursionistici</t>
         </is>
       </c>
-      <c r="E34" s="109" t="inlineStr"/>
-      <c r="F34" s="109" t="inlineStr"/>
-      <c r="G34" s="109" t="inlineStr"/>
+      <c r="E34" s="112" t="inlineStr"/>
+      <c r="F34" s="112" t="inlineStr"/>
+      <c r="G34" s="112" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="107" t="inlineStr">
+      <c r="A35" s="110" t="inlineStr">
         <is>
           <t>19/03/2026</t>
         </is>
       </c>
-      <c r="B35" s="107" t="inlineStr">
+      <c r="B35" s="110" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1878,22 +1938,22 @@
           <t>Programma regionale in favore delle tradizioni storiche, artistiche, religiose e popolari (2026) – manifestazioni d’interesseApertoBandi Regionali</t>
         </is>
       </c>
-      <c r="D35" s="108" t="inlineStr">
+      <c r="D35" s="111" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/programma-regionale-in-favore-delle-tradizioni-storiche-artistiche-religiose-e-popolari-2026-manifestazioni-dinteresse/</t>
         </is>
       </c>
-      <c r="E35" s="107" t="inlineStr"/>
-      <c r="F35" s="107" t="inlineStr"/>
-      <c r="G35" s="107" t="inlineStr"/>
+      <c r="E35" s="110" t="inlineStr"/>
+      <c r="F35" s="110" t="inlineStr"/>
+      <c r="G35" s="110" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="109" t="inlineStr">
+      <c r="A36" s="112" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B36" s="109" t="inlineStr">
+      <c r="B36" s="112" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1903,22 +1963,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONEBuoni servizio per le persone non autosufficienti nel territorio del LazioProssima AperturaFSE / FSE+</t>
         </is>
       </c>
-      <c r="D36" s="106" t="inlineStr">
+      <c r="D36" s="113" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/buoni-servizio-per-le-persone-non-autosufficienti-nel-territorio-del-lazio/</t>
         </is>
       </c>
-      <c r="E36" s="109" t="inlineStr"/>
-      <c r="F36" s="109" t="inlineStr"/>
-      <c r="G36" s="109" t="inlineStr"/>
+      <c r="E36" s="112" t="inlineStr"/>
+      <c r="F36" s="112" t="inlineStr"/>
+      <c r="G36" s="112" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="107" t="inlineStr">
+      <c r="A37" s="110" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B37" s="107" t="inlineStr">
+      <c r="B37" s="110" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -1928,22 +1988,22 @@
           <t>LAVORO, FORMAZIONE E INCLUSIONERimborso delle rette dei servizi educativi nel territorio del LazioProssima AperturaFSE / FSE+</t>
         </is>
       </c>
-      <c r="D37" s="108" t="inlineStr">
+      <c r="D37" s="111" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/rimborso-delle-rette-dei-servizi-educativi-nel-territorio-del-lazio/</t>
         </is>
       </c>
-      <c r="E37" s="107" t="inlineStr"/>
-      <c r="F37" s="107" t="inlineStr"/>
-      <c r="G37" s="107" t="inlineStr"/>
+      <c r="E37" s="110" t="inlineStr"/>
+      <c r="F37" s="110" t="inlineStr"/>
+      <c r="G37" s="110" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="109" t="inlineStr">
+      <c r="A38" s="112" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B38" s="109" t="inlineStr">
+      <c r="B38" s="112" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1953,30 +2013,30 @@
           <t>Manifestazioni di interesseATTO DI INTERPELLO PER L’AFFIDAMENTO DELL’INCARICO DI COLLAUDO STATICO DELLE STRUTTURE - Diga di Pietrarossa (Progetto ex C</t>
         </is>
       </c>
-      <c r="D38" s="106" t="inlineStr">
+      <c r="D38" s="113" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/atto-interpello-l-affidamento-incarico-collaudo-statico-strutture-diga-pietrarossa-progetto-ex-casmez-303219</t>
         </is>
       </c>
-      <c r="E38" s="109" t="inlineStr">
+      <c r="E38" s="112" t="inlineStr">
         <is>
           <t>27/03/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F38" s="109" t="inlineStr">
+      <c r="F38" s="112" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="G38" s="109" t="inlineStr"/>
+      <c r="G38" s="112" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="107" t="inlineStr">
+      <c r="A39" s="110" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B39" s="107" t="inlineStr">
+      <c r="B39" s="110" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -1986,30 +2046,30 @@
           <t>Manifestazioni di interesseAvviso alle Case  Editrici della Regione siciliana per la partecipazione al Salone del Libro di Torino, 14-18  maggio 2026.</t>
         </is>
       </c>
-      <c r="D39" s="108" t="inlineStr">
+      <c r="D39" s="111" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/manifestazione-d-interesse-partecipare-al-xxxviii-salone-libro-torino-14-al-18-maggio-2026-attraverso-l-esposizione-pubblicazioni-presso-stand-assessorato-beni</t>
         </is>
       </c>
-      <c r="E39" s="107" t="inlineStr">
+      <c r="E39" s="110" t="inlineStr">
         <is>
           <t>30/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F39" s="107" t="inlineStr">
+      <c r="F39" s="110" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="G39" s="107" t="inlineStr"/>
+      <c r="G39" s="110" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="109" t="inlineStr">
+      <c r="A40" s="112" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B40" s="109" t="inlineStr">
+      <c r="B40" s="112" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2019,30 +2079,30 @@
           <t xml:space="preserve">Manifestazioni di interessePR FESR SICILIA 2021/27 - NUOVO Avviso a manifestazione d’interesse per esperti valutatoriScade il:06/04/2026 - 23:59Leggi </t>
         </is>
       </c>
-      <c r="D40" s="106" t="inlineStr">
+      <c r="D40" s="113" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/pr-fesr-sicilia-202127-nuovo-avviso-manifestazione-d-interesse-esperti-valutatori</t>
         </is>
       </c>
-      <c r="E40" s="109" t="inlineStr">
+      <c r="E40" s="112" t="inlineStr">
         <is>
           <t>06/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F40" s="109" t="inlineStr">
+      <c r="F40" s="112" t="inlineStr">
         <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="G40" s="109" t="inlineStr"/>
+      <c r="G40" s="112" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="107" t="inlineStr">
+      <c r="A41" s="110" t="inlineStr">
         <is>
           <t>20/03/2026</t>
         </is>
       </c>
-      <c r="B41" s="107" t="inlineStr">
+      <c r="B41" s="110" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2052,22 +2112,22 @@
           <t>Avvisi pubbliciAVVISO RINNOVO LOCAZIONE di un immobile, di proprietà regionale sito nel Comune di AgrigentoScadutoLeggi di più</t>
         </is>
       </c>
-      <c r="D41" s="108" t="inlineStr">
+      <c r="D41" s="111" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/rinnovo-concessione-locazione-bene-immobile-proprieta-regione-siciliana-sito-nel-comune-agrigento</t>
         </is>
       </c>
-      <c r="E41" s="107" t="inlineStr"/>
-      <c r="F41" s="107" t="inlineStr"/>
-      <c r="G41" s="107" t="inlineStr"/>
+      <c r="E41" s="110" t="inlineStr"/>
+      <c r="F41" s="110" t="inlineStr"/>
+      <c r="G41" s="110" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="109" t="inlineStr">
+      <c r="A42" s="112" t="inlineStr">
         <is>
           <t>24/03/2026</t>
         </is>
       </c>
-      <c r="B42" s="109" t="inlineStr">
+      <c r="B42" s="112" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2077,22 +2137,22 @@
           <t>GAL del Ducato - Promozione di fiere agroalimentari e delle filiere del cibo – Bando per Enti pubblici (DU AS 05B)</t>
         </is>
       </c>
-      <c r="D42" s="106" t="inlineStr">
+      <c r="D42" s="113" t="inlineStr">
         <is>
           <t>https://agricoltura.regione.emilia-romagna.it/sviluppo-rurale-23-27/opportunita/bandi-gal/2026/du_as05b-promozione-di-fiere-agroalimentari-e-delle-filiere-del-cibo-bando-per-enti-pubblici</t>
         </is>
       </c>
-      <c r="E42" s="109" t="inlineStr"/>
-      <c r="F42" s="109" t="inlineStr"/>
-      <c r="G42" s="109" t="inlineStr"/>
+      <c r="E42" s="112" t="inlineStr"/>
+      <c r="F42" s="112" t="inlineStr"/>
+      <c r="G42" s="112" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="107" t="inlineStr">
+      <c r="A43" s="110" t="inlineStr">
         <is>
           <t>24/03/2026</t>
         </is>
       </c>
-      <c r="B43" s="107" t="inlineStr">
+      <c r="B43" s="110" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2102,30 +2162,30 @@
           <t>Manifestazioni di interesseAVVISO PUBBLICO PER MANIFESTAZIONE DI INTERESSE FINALIZZATA ALL'ASSEGNAZIONE DI SPAZI ESPOSITIVI (CORNER GRATUITI) ALL'INTE</t>
         </is>
       </c>
-      <c r="D43" s="108" t="inlineStr">
+      <c r="D43" s="111" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-manifestazione-interesse-finalizzata-all-assegnazione-spazi-espositivi-corner-gratuiti-all-interno-stand-istituzionale-dsrt-manifestazione</t>
         </is>
       </c>
-      <c r="E43" s="107" t="inlineStr">
+      <c r="E43" s="110" t="inlineStr">
         <is>
           <t>30/03/2026 - 13:00</t>
         </is>
       </c>
-      <c r="F43" s="107" t="inlineStr">
+      <c r="F43" s="110" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G43" s="107" t="inlineStr"/>
+      <c r="G43" s="110" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="109" t="inlineStr">
+      <c r="A44" s="112" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B44" s="109" t="inlineStr">
+      <c r="B44" s="112" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2135,22 +2195,22 @@
           <t>Avviso per la concessione di contributi per eventi sportivi realizzati in Emilia-Romagna - Anno 2026</t>
         </is>
       </c>
-      <c r="D44" s="106" t="inlineStr">
+      <c r="D44" s="113" t="inlineStr">
         <is>
           <t>https://www.regione.emilia-romagna.it/sport/bandi/2026/bando-2026</t>
         </is>
       </c>
-      <c r="E44" s="109" t="inlineStr"/>
-      <c r="F44" s="109" t="inlineStr"/>
-      <c r="G44" s="109" t="inlineStr"/>
+      <c r="E44" s="112" t="inlineStr"/>
+      <c r="F44" s="112" t="inlineStr"/>
+      <c r="G44" s="112" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="107" t="inlineStr">
+      <c r="A45" s="110" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B45" s="107" t="inlineStr">
+      <c r="B45" s="110" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2160,22 +2220,22 @@
           <t>CREATIVITÀ, CINEMA, TURISMO E CULTURALazio Street art 2026Prossima AperturaBandi Regionali</t>
         </is>
       </c>
-      <c r="D45" s="108" t="inlineStr">
+      <c r="D45" s="111" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/lazio-street-art-2026/</t>
         </is>
       </c>
-      <c r="E45" s="107" t="inlineStr"/>
-      <c r="F45" s="107" t="inlineStr"/>
-      <c r="G45" s="107" t="inlineStr"/>
+      <c r="E45" s="110" t="inlineStr"/>
+      <c r="F45" s="110" t="inlineStr"/>
+      <c r="G45" s="110" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="109" t="inlineStr">
+      <c r="A46" s="112" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B46" s="109" t="inlineStr">
+      <c r="B46" s="112" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2185,30 +2245,30 @@
           <t>Manifestazioni di interesseManifestazione di interesse per la partecipazione all’evento “R2I Italy 2026” – Bologna, 12-13/05/2026Scade il:03/04/2026 -</t>
         </is>
       </c>
-      <c r="D46" s="106" t="inlineStr">
+      <c r="D46" s="113" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/manifestazione-interesse-partecipazione-all-evento-r2i-italy-2026-bologna-12-13052026</t>
         </is>
       </c>
-      <c r="E46" s="109" t="inlineStr">
+      <c r="E46" s="112" t="inlineStr">
         <is>
           <t>03/04/2026 - 23:59</t>
         </is>
       </c>
-      <c r="F46" s="109" t="inlineStr">
+      <c r="F46" s="112" t="inlineStr">
         <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="G46" s="109" t="inlineStr"/>
+      <c r="G46" s="112" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="107" t="inlineStr">
+      <c r="A47" s="110" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B47" s="107" t="inlineStr">
+      <c r="B47" s="110" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2218,30 +2278,30 @@
           <t>Manifestazioni di interesseST SIRACUSA - AVVISO PER MANIFESTAZIONE DI INTERESSE - Selezione di n. 5 unità di personale internoScade il:20/04/2026 - 12</t>
         </is>
       </c>
-      <c r="D47" s="108" t="inlineStr">
+      <c r="D47" s="111" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/24-marzo-2026-st-siracusa-avviso-manifestazione-interesse-selezione-n-5-unita-personale-interno</t>
         </is>
       </c>
-      <c r="E47" s="107" t="inlineStr">
+      <c r="E47" s="110" t="inlineStr">
         <is>
           <t>20/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F47" s="107" t="inlineStr">
+      <c r="F47" s="110" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="G47" s="107" t="inlineStr"/>
+      <c r="G47" s="110" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="109" t="inlineStr">
+      <c r="A48" s="112" t="inlineStr">
         <is>
           <t>25/03/2026</t>
         </is>
       </c>
-      <c r="B48" s="109" t="inlineStr">
+      <c r="B48" s="112" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2251,30 +2311,30 @@
           <t>Avvisi pubbliciRevoca dell’avviso di concessione a titolo gratuito del 16.12.2025 inerente all’immobile di seguito identificato e contestuale nuovo av</t>
         </is>
       </c>
-      <c r="D48" s="106" t="inlineStr">
+      <c r="D48" s="113" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/revoca-avviso-concessione-titolo-gratuito-16122025-inerente-all-immobile-seguito-identificato-contestuale-nuovo-avviso-concessione-titolo-oneroso-stesso-sito-nel</t>
         </is>
       </c>
-      <c r="E48" s="109" t="inlineStr">
+      <c r="E48" s="112" t="inlineStr">
         <is>
           <t>08/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F48" s="109" t="inlineStr">
+      <c r="F48" s="112" t="inlineStr">
         <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="G48" s="109" t="inlineStr"/>
+      <c r="G48" s="112" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="107" t="inlineStr">
+      <c r="A49" s="110" t="inlineStr">
         <is>
           <t>26/03/2026</t>
         </is>
       </c>
-      <c r="B49" s="107" t="inlineStr">
+      <c r="B49" s="110" t="inlineStr">
         <is>
           <t>Emilia-Romagna</t>
         </is>
@@ -2284,22 +2344,22 @@
           <t>Bando studi di fattibilità per fusioni di Comuni</t>
         </is>
       </c>
-      <c r="D49" s="108" t="inlineStr">
+      <c r="D49" s="111" t="inlineStr">
         <is>
           <t>https://www.regione.emilia-romagna.it/autonomie-locali/bandi/bando_studi_fattibilita_fusioni_comuni</t>
         </is>
       </c>
-      <c r="E49" s="107" t="inlineStr"/>
-      <c r="F49" s="107" t="inlineStr"/>
-      <c r="G49" s="107" t="inlineStr"/>
+      <c r="E49" s="110" t="inlineStr"/>
+      <c r="F49" s="110" t="inlineStr"/>
+      <c r="G49" s="110" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="109" t="inlineStr">
+      <c r="A50" s="112" t="inlineStr">
         <is>
           <t>26/03/2026</t>
         </is>
       </c>
-      <c r="B50" s="109" t="inlineStr">
+      <c r="B50" s="112" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2309,30 +2369,30 @@
           <t xml:space="preserve">Manifestazioni di interesseAvviso pubblico di selezione interna, per titoli, per il conferimento di PO e professionali, ai sensi degli artt. 19, 20 e </t>
         </is>
       </c>
-      <c r="D50" s="106" t="inlineStr">
+      <c r="D50" s="113" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-selezione-interna-titoli-conferimento-po-professionali-ai-sensi-artt-19-20-21-ccrl-20222024-comparto-non-dirigenziale</t>
         </is>
       </c>
-      <c r="E50" s="109" t="inlineStr">
+      <c r="E50" s="112" t="inlineStr">
         <is>
           <t>30/03/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F50" s="109" t="inlineStr">
+      <c r="F50" s="112" t="inlineStr">
         <is>
           <t>30/03/2026</t>
         </is>
       </c>
-      <c r="G50" s="109" t="inlineStr"/>
+      <c r="G50" s="112" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="107" t="inlineStr">
+      <c r="A51" s="110" t="inlineStr">
         <is>
           <t>27/03/2026</t>
         </is>
       </c>
-      <c r="B51" s="107" t="inlineStr">
+      <c r="B51" s="110" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
@@ -2342,22 +2402,22 @@
           <t>INNOVAZIONE, COMPETITIVITÀ, INDUSTRIA 4.0PRE-SEED 3.0ApertoFESR</t>
         </is>
       </c>
-      <c r="D51" s="108" t="inlineStr">
+      <c r="D51" s="111" t="inlineStr">
         <is>
           <t>https://www.lazioeuropa.it/bandi/pre-seed-3-0/</t>
         </is>
       </c>
-      <c r="E51" s="107" t="inlineStr"/>
-      <c r="F51" s="107" t="inlineStr"/>
-      <c r="G51" s="107" t="inlineStr"/>
+      <c r="E51" s="110" t="inlineStr"/>
+      <c r="F51" s="110" t="inlineStr"/>
+      <c r="G51" s="110" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="109" t="inlineStr">
+      <c r="A52" s="112" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B52" s="109" t="inlineStr">
+      <c r="B52" s="112" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2367,30 +2427,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “So</t>
         </is>
       </c>
-      <c r="D52" s="106" t="inlineStr">
+      <c r="D52" s="113" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-termini-imerese-locta-piazza-marina</t>
         </is>
       </c>
-      <c r="E52" s="109" t="inlineStr">
+      <c r="E52" s="112" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F52" s="109" t="inlineStr">
+      <c r="F52" s="112" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G52" s="109" t="inlineStr"/>
+      <c r="G52" s="112" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="107" t="inlineStr">
+      <c r="A53" s="110" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B53" s="107" t="inlineStr">
+      <c r="B53" s="110" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2400,30 +2460,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA di un bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, Sig</t>
         </is>
       </c>
-      <c r="D53" s="108" t="inlineStr">
+      <c r="D53" s="111" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-porto-empedocle-locta-punta-piccola</t>
         </is>
       </c>
-      <c r="E53" s="107" t="inlineStr">
+      <c r="E53" s="110" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F53" s="107" t="inlineStr">
+      <c r="F53" s="110" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G53" s="107" t="inlineStr"/>
+      <c r="G53" s="110" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="109" t="inlineStr">
+      <c r="A54" s="112" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B54" s="109" t="inlineStr">
+      <c r="B54" s="112" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2433,30 +2493,30 @@
           <t xml:space="preserve">Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “Società </t>
         </is>
       </c>
-      <c r="D54" s="106" t="inlineStr">
+      <c r="D54" s="113" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-messina-locta-torrente-bordonaro</t>
         </is>
       </c>
-      <c r="E54" s="109" t="inlineStr">
+      <c r="E54" s="112" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F54" s="109" t="inlineStr">
+      <c r="F54" s="112" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G54" s="109" t="inlineStr"/>
+      <c r="G54" s="112" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="107" t="inlineStr">
+      <c r="A55" s="110" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B55" s="107" t="inlineStr">
+      <c r="B55" s="110" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2466,30 +2526,30 @@
           <t>Avvisi pubbliciAVVISO PUBBLICO DI VENDITA bene immobile proveniente da procedura di sdemanializzazione, in favore dell'attuale utilizzatore, “Condomin</t>
         </is>
       </c>
-      <c r="D55" s="108" t="inlineStr">
+      <c r="D55" s="111" t="inlineStr">
         <is>
           <t>https://www.regione.sicilia.it/istituzioni/servizi-informativi/bandi/istituzioni/servizi-informativi/bandi/avviso-pubblico-vendita-bene-immobile-proveniente-procedura-sdemanializzazione-sito-nel-comune-mascali-spiaggia-n-144150</t>
         </is>
       </c>
-      <c r="E55" s="107" t="inlineStr">
+      <c r="E55" s="110" t="inlineStr">
         <is>
           <t>26/04/2026 - 12:00</t>
         </is>
       </c>
-      <c r="F55" s="107" t="inlineStr">
+      <c r="F55" s="110" t="inlineStr">
         <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="G55" s="107" t="inlineStr"/>
+      <c r="G55" s="110" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="109" t="inlineStr">
+      <c r="A56" s="112" t="inlineStr">
         <is>
           <t>28/03/2026</t>
         </is>
       </c>
-      <c r="B56" s="109" t="inlineStr">
+      <c r="B56" s="112" t="inlineStr">
         <is>
           <t>Sicilia</t>
         </is>
@@ -2499,30 +2559,30 @@
           <t xml:space="preserve">Avvisi p